--- a/financial_models/opportunities/0639.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0639.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DCCD496-1E4A-46AE-B7AE-71B1FEFEC917}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BDD483C-1124-499C-98E1-7112D8CB6440}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3885,29 +3885,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4323,7 +4323,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>2.64</v>
+        <v>2.59</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4344,7 +4344,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>13440.4136328</v>
+        <v>13185.860344299999</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4381,13 +4381,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="356" t="s">
         <v>362</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="356"/>
+      <c r="D18" s="356"/>
+      <c r="E18" s="356"/>
+      <c r="F18" s="356"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4463,14 +4463,14 @@
       </c>
       <c r="C26" s="304">
         <f>C132</f>
-        <v>4.3070025867398245</v>
+        <v>4.4858408799140586</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>402</v>
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.27545168163665656</v>
+        <v>0.29938655516441326</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4502,7 +4502,7 @@
       </c>
       <c r="C29" s="310">
         <f>C149</f>
-        <v>2.04628374152326</v>
+        <v>2.2516930066250125</v>
       </c>
       <c r="D29" s="310" t="str">
         <f>D149</f>
@@ -4512,7 +4512,7 @@
         <v>426</v>
       </c>
       <c r="F29" s="302">
-        <v>0.4</v>
+        <v>0.3674</v>
       </c>
     </row>
     <row r="30" spans="2:6">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="C30" s="311">
         <f>C157</f>
-        <v>2.9845684147240434</v>
+        <v>3.101365529948271</v>
       </c>
       <c r="D30" s="311" t="str">
         <f>D157</f>
@@ -4531,7 +4531,7 @@
         <v>439</v>
       </c>
       <c r="F30" s="312">
-        <v>0.22</v>
+        <v>0.21740000000000001</v>
       </c>
     </row>
     <row r="31" spans="2:6">
@@ -4540,7 +4540,7 @@
       </c>
       <c r="C31" s="311">
         <f>C165</f>
-        <v>4.1921666116857068</v>
+        <v>4.3910827513866675</v>
       </c>
       <c r="D31" s="311" t="str">
         <f>D165</f>
@@ -4550,7 +4550,7 @@
         <v>438</v>
       </c>
       <c r="F31" s="312">
-        <v>0.08</v>
+        <v>7.4999999999999997E-2</v>
       </c>
     </row>
     <row r="32" spans="2:6">
@@ -4559,7 +4559,7 @@
       </c>
       <c r="C32" s="311">
         <f>C173</f>
-        <v>3.7861887489891468</v>
+        <v>3.939054009870663</v>
       </c>
       <c r="D32" s="311" t="str">
         <f>D173</f>
@@ -4569,7 +4569,7 @@
         <v>440</v>
       </c>
       <c r="F32" s="312">
-        <v>0.12</v>
+        <v>0.1174</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -4587,22 +4587,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="356" t="s">
         <v>363</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="356"/>
+      <c r="D36" s="356"/>
+      <c r="E36" s="356"/>
+      <c r="F36" s="356"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="361" t="s">
+      <c r="B37" s="358" t="s">
         <v>341</v>
       </c>
-      <c r="C37" s="361"/>
-      <c r="D37" s="361"/>
-      <c r="E37" s="361"/>
-      <c r="F37" s="361"/>
+      <c r="C37" s="358"/>
+      <c r="D37" s="358"/>
+      <c r="E37" s="358"/>
+      <c r="F37" s="358"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4614,13 +4614,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="357" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="357"/>
+      <c r="D40" s="357"/>
+      <c r="E40" s="357"/>
+      <c r="F40" s="357"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4640,13 +4640,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="357" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="357"/>
+      <c r="D43" s="357"/>
+      <c r="E43" s="357"/>
+      <c r="F43" s="357"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4675,13 +4675,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="357" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="357"/>
+      <c r="D47" s="357"/>
+      <c r="E47" s="357"/>
+      <c r="F47" s="357"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4697,13 +4697,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="357" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="357"/>
+      <c r="D50" s="357"/>
+      <c r="E50" s="357"/>
+      <c r="F50" s="357"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4767,13 +4767,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="357" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="357"/>
+      <c r="D58" s="357"/>
+      <c r="E58" s="357"/>
+      <c r="F58" s="357"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4789,7 +4789,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="357" t="s">
         <v>340</v>
       </c>
       <c r="C61" s="360"/>
@@ -4811,22 +4811,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="356" t="s">
         <v>345</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="356"/>
+      <c r="D64" s="356"/>
+      <c r="E64" s="356"/>
+      <c r="F64" s="356"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="356" t="s">
         <v>364</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="356"/>
+      <c r="D65" s="356"/>
+      <c r="E65" s="356"/>
+      <c r="F65" s="356"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4860,7 +4860,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>8.1234663007527477E-2</v>
+        <v>8.2802899745124545E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4870,7 +4870,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>0.11363636363636363</v>
+        <v>0.11583011583011583</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>450</v>
@@ -4961,22 +4961,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="356" t="s">
         <v>365</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="356"/>
+      <c r="D80" s="356"/>
+      <c r="E80" s="356"/>
+      <c r="F80" s="356"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="361" t="s">
+      <c r="B81" s="358" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="361"/>
-      <c r="D81" s="361"/>
-      <c r="E81" s="361"/>
-      <c r="F81" s="361"/>
+      <c r="C81" s="358"/>
+      <c r="D81" s="358"/>
+      <c r="E81" s="358"/>
+      <c r="F81" s="358"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -4989,7 +4989,7 @@
       </c>
       <c r="C84" s="92">
         <f>F31</f>
-        <v>0.08</v>
+        <v>7.4999999999999997E-2</v>
       </c>
     </row>
     <row r="85" spans="1:6">
@@ -5007,7 +5007,7 @@
       </c>
       <c r="C86" s="236">
         <f>F31+C85</f>
-        <v>0.08</v>
+        <v>7.4999999999999997E-2</v>
       </c>
     </row>
     <row r="87" spans="1:6">
@@ -5020,22 +5020,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="356" t="s">
         <v>366</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="356"/>
+      <c r="D89" s="356"/>
+      <c r="E89" s="356"/>
+      <c r="F89" s="356"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="356" t="s">
         <v>367</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="356"/>
+      <c r="D90" s="356"/>
+      <c r="E90" s="356"/>
+      <c r="F90" s="356"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="C93" s="223">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>2.6807438792484075</v>
+        <v>2.8594601378649682</v>
       </c>
       <c r="D93" s="1" t="str">
         <f>Market_currency</f>
@@ -5072,13 +5072,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="356" t="s">
         <v>368</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="356"/>
+      <c r="D97" s="356"/>
+      <c r="E97" s="356"/>
+      <c r="F97" s="356"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5091,13 +5091,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="356" t="s">
         <v>346</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="356"/>
+      <c r="D101" s="356"/>
+      <c r="E101" s="356"/>
+      <c r="F101" s="356"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5219,13 +5219,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="356" t="s">
         <v>369</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="356"/>
+      <c r="D116" s="356"/>
+      <c r="E116" s="356"/>
+      <c r="F116" s="356"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5233,7 +5233,7 @@
       </c>
       <c r="C118" s="223">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>4.3034503288027297</v>
+        <v>4.4821665874192913</v>
       </c>
       <c r="D118" s="1" t="str">
         <f>Market_currency</f>
@@ -5264,13 +5264,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="357" t="s">
         <v>370</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="357"/>
+      <c r="D123" s="357"/>
+      <c r="E123" s="357"/>
+      <c r="F123" s="357"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5304,7 +5304,7 @@
       </c>
       <c r="E126" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E74,DDM!E69),2)&amp;" "&amp;Market_currency</f>
-        <v>4.67 HKD</v>
+        <v>4.86 HKD</v>
       </c>
       <c r="F126" s="232">
         <f>DCF!F74</f>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="E127" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E75,DDM!E70),2)&amp;" "&amp;Market_currency</f>
-        <v>4.39 HKD</v>
+        <v>4.57 HKD</v>
       </c>
       <c r="F127" s="221">
         <f>DCF!F75</f>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="E128" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E76,DDM!E71),2)&amp;" "&amp;Market_currency</f>
-        <v>4.3 HKD</v>
+        <v>4.48 HKD</v>
       </c>
       <c r="F128" s="221">
         <f>DCF!F76</f>
@@ -5370,7 +5370,7 @@
       </c>
       <c r="E129" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E77,DDM!E72),2)&amp;" "&amp;Market_currency</f>
-        <v>4.22 HKD</v>
+        <v>4.39 HKD</v>
       </c>
       <c r="F129" s="221">
         <f>DCF!F77</f>
@@ -5392,7 +5392,7 @@
       </c>
       <c r="E130" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E78,DDM!E73),2)&amp;" "&amp;Market_currency</f>
-        <v>4 HKD</v>
+        <v>4.17 HKD</v>
       </c>
       <c r="F130" s="221">
         <f>DCF!F78</f>
@@ -5405,7 +5405,7 @@
       </c>
       <c r="C132" s="217">
         <f>Scenarios!C60</f>
-        <v>4.3070025867398245</v>
+        <v>4.4858408799140586</v>
       </c>
       <c r="D132" s="212" t="str">
         <f>Market_currency</f>
@@ -5413,13 +5413,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="362" t="s">
+      <c r="B134" s="361" t="s">
         <v>373</v>
       </c>
-      <c r="C134" s="362"/>
-      <c r="D134" s="362"/>
-      <c r="E134" s="362"/>
-      <c r="F134" s="362"/>
+      <c r="C134" s="361"/>
+      <c r="D134" s="361"/>
+      <c r="E134" s="361"/>
+      <c r="F134" s="361"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5432,22 +5432,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="363" t="s">
+      <c r="B138" s="359" t="s">
         <v>371</v>
       </c>
-      <c r="C138" s="363"/>
-      <c r="D138" s="363"/>
-      <c r="E138" s="363"/>
-      <c r="F138" s="363"/>
+      <c r="C138" s="359"/>
+      <c r="D138" s="359"/>
+      <c r="E138" s="359"/>
+      <c r="F138" s="359"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="356" t="s">
         <v>372</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="356"/>
+      <c r="D139" s="356"/>
+      <c r="E139" s="356"/>
+      <c r="F139" s="356"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5469,7 +5469,7 @@
       </c>
       <c r="C142" s="224">
         <f>F29</f>
-        <v>0.4</v>
+        <v>0.3674</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -5504,7 +5504,7 @@
       </c>
       <c r="C146" s="297">
         <f>F29</f>
-        <v>0.4</v>
+        <v>0.3674</v>
       </c>
     </row>
     <row r="147" spans="2:4">
@@ -5514,7 +5514,7 @@
       </c>
       <c r="C147" s="216">
         <f>Scenarios!C81</f>
-        <v>0.47667638483964997</v>
+        <v>0.49717779580945759</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -5524,7 +5524,7 @@
       </c>
       <c r="C148" s="216">
         <f>Scenarios!C82</f>
-        <v>1.56960735668361</v>
+        <v>1.7545152108155548</v>
       </c>
     </row>
     <row r="149" spans="2:4">
@@ -5533,7 +5533,7 @@
       </c>
       <c r="C149" s="215">
         <f>Scenarios!C83</f>
-        <v>2.04628374152326</v>
+        <v>2.2516930066250125</v>
       </c>
       <c r="D149" s="300" t="str">
         <f>IF($D$11="","",C149*$E$25)</f>
@@ -5559,7 +5559,7 @@
       </c>
       <c r="C151" s="92">
         <f>Scenarios!F83</f>
-        <v>0.52489377465821541</v>
+        <v>0.4980443874620557</v>
       </c>
     </row>
     <row r="153" spans="2:4">
@@ -5573,7 +5573,7 @@
       </c>
       <c r="C154" s="297">
         <f>Scenarios!C90</f>
-        <v>0.22</v>
+        <v>0.21740000000000001</v>
       </c>
     </row>
     <row r="155" spans="2:4">
@@ -5583,7 +5583,7 @@
       </c>
       <c r="C155" s="216">
         <f>Scenarios!C91</f>
-        <v>0.6126724263264326</v>
+        <v>0.61512024715948099</v>
       </c>
     </row>
     <row r="156" spans="2:4">
@@ -5593,7 +5593,7 @@
       </c>
       <c r="C156" s="216">
         <f>Scenarios!C92</f>
-        <v>2.3718959883976107</v>
+        <v>2.48624528278879</v>
       </c>
     </row>
     <row r="157" spans="2:4">
@@ -5602,7 +5602,7 @@
       </c>
       <c r="C157" s="215">
         <f>Scenarios!C93</f>
-        <v>2.9845684147240434</v>
+        <v>3.101365529948271</v>
       </c>
       <c r="D157" s="300" t="str">
         <f>IF($D$11="","",C157*$E$25)</f>
@@ -5628,7 +5628,7 @@
       </c>
       <c r="C159" s="92">
         <f>Scenarios!F93</f>
-        <v>0.30704280886369151</v>
+        <v>0.30863229147626647</v>
       </c>
     </row>
     <row r="161" spans="2:4">
@@ -5642,7 +5642,7 @@
       </c>
       <c r="C162" s="92">
         <f>Scenarios!C96</f>
-        <v>0.08</v>
+        <v>7.4999999999999997E-2</v>
       </c>
     </row>
     <row r="163" spans="2:4">
@@ -5652,7 +5652,7 @@
       </c>
       <c r="C163" s="216">
         <f>Scenarios!C97</f>
-        <v>0.77312909617436398</v>
+        <v>0.78015772196158795</v>
       </c>
     </row>
     <row r="164" spans="2:4">
@@ -5662,7 +5662,7 @@
       </c>
       <c r="C164" s="216">
         <f>Scenarios!C98</f>
-        <v>3.4190375155113424</v>
+        <v>3.6109250294250792</v>
       </c>
     </row>
     <row r="165" spans="2:4">
@@ -5671,7 +5671,7 @@
       </c>
       <c r="C165" s="215">
         <f>Scenarios!C99</f>
-        <v>4.1921666116857068</v>
+        <v>4.3910827513866675</v>
       </c>
       <c r="D165" s="300" t="str">
         <f>IF($D$11="","",C165*$E$25)</f>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="C167" s="92">
         <f>Scenarios!F99</f>
-        <v>2.6662620405120907E-2</v>
+        <v>2.1123827408074836E-2</v>
       </c>
     </row>
     <row r="169" spans="2:4">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="C170" s="92">
         <f>F32</f>
-        <v>0.12</v>
+        <v>0.1174</v>
       </c>
     </row>
     <row r="171" spans="2:4">
@@ -5721,7 +5721,7 @@
       </c>
       <c r="C171" s="216">
         <f>Scenarios!C103</f>
-        <v>0.72054938046647277</v>
+        <v>0.72378093778159469</v>
       </c>
     </row>
     <row r="172" spans="2:4">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="C172" s="216">
         <f>Scenarios!C104</f>
-        <v>3.0656393685226742</v>
+        <v>3.2152730720890683</v>
       </c>
     </row>
     <row r="173" spans="2:4">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C173" s="215">
         <f>Scenarios!C105</f>
-        <v>3.7861887489891468</v>
+        <v>3.939054009870663</v>
       </c>
       <c r="D173" s="300" t="str">
         <f>IF($D$11="","",C173*$E$25)</f>
@@ -5766,7 +5766,7 @@
       </c>
       <c r="C175" s="92">
         <f>Scenarios!F105</f>
-        <v>0.12131187496789031</v>
+        <v>0.12229326468444657</v>
       </c>
     </row>
     <row r="177" spans="1:6" ht="13.9">
@@ -5780,13 +5780,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="357" t="s">
+      <c r="B179" s="363" t="s">
         <v>379</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="356"/>
+      <c r="D179" s="356"/>
+      <c r="E179" s="356"/>
+      <c r="F179" s="356"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5823,13 +5823,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="357" t="s">
         <v>384</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="357"/>
+      <c r="D188" s="357"/>
+      <c r="E188" s="357"/>
+      <c r="F188" s="357"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5837,22 +5837,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="356" t="s">
+      <c r="B191" s="362" t="s">
         <v>385</v>
       </c>
-      <c r="C191" s="356"/>
-      <c r="D191" s="356"/>
-      <c r="E191" s="356"/>
-      <c r="F191" s="356"/>
+      <c r="C191" s="362"/>
+      <c r="D191" s="362"/>
+      <c r="E191" s="362"/>
+      <c r="F191" s="362"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="356" t="s">
+      <c r="B192" s="362" t="s">
         <v>386</v>
       </c>
-      <c r="C192" s="356"/>
-      <c r="D192" s="356"/>
-      <c r="E192" s="356"/>
-      <c r="F192" s="356"/>
+      <c r="C192" s="362"/>
+      <c r="D192" s="362"/>
+      <c r="E192" s="362"/>
+      <c r="F192" s="362"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5876,6 +5876,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5892,17 +5903,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13425,20 +13425,20 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>0.11363636363636363</v>
+        <v>0.11583011583011583</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>0.11363636363636363</v>
+        <v>0.11583011583011583</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>0.10606060606060606</v>
+        <v>0.10810810810810813</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>0.1628787878787879</v>
+        <v>0.16602316602316605</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
@@ -14624,50 +14624,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>8.1234663007527477E-2</v>
+        <v>8.2802899745124545E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>9.4795102616059265E-2</v>
+        <v>9.6625123902083596E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.13044396142094439</v>
+        <v>0.13296218461439893</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.21155361593205166</v>
+        <v>0.21563766257166658</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.17382448110043563</v>
+        <v>0.17718016606376452</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>6.2359241530678552E-2</v>
+        <v>6.3563087892274661E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>7.9164155886052176E-2</v>
+        <v>8.0692421443697968E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>7.0485107518424017E-2</v>
+        <v>7.1845823879783555E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>6.6944591482230684E-2</v>
+        <v>6.8236958113161786E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>1.1850528142326115E-2</v>
+        <v>1.2079302816888397E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>5.133621768277816E-3</v>
+        <v>5.2327264356190869E-3</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14681,43 +14681,43 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13503862675555853</v>
+        <v>0.13764555005199791</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.17119547529287255</v>
+        <v>0.17450040724833343</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.24613491000952342</v>
+        <v>0.25088654919889647</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.22773339300587778</v>
+        <v>0.23212979055425381</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.8336790253430386E-2</v>
+        <v>9.0042133694616305E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.7507797909563145E-2</v>
+        <v>8.9197137637547011E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.57062908531947E-2</v>
+        <v>8.7360852452677232E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.798717303714676E-2</v>
+        <v>8.9685767111222961E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.0337736507522516E-3</v>
+        <v>5.1309507482571225E-3</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-5.2935498820044911E-2</v>
+        <v>-5.3957419646686711E-2</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -15488,7 +15488,7 @@
       </c>
       <c r="C5" s="206">
         <f>Equity_Cost</f>
-        <v>0.08</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="E5" s="148"/>
       <c r="H5" s="120"/>
@@ -15499,7 +15499,7 @@
       </c>
       <c r="C6" s="347">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>13647843.401778579</v>
+        <v>14557699.628563819</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -15565,7 +15565,7 @@
       </c>
       <c r="C10" s="347">
         <f>C6-C7+C8+C9</f>
-        <v>21909148.661862824</v>
+        <v>22819004.888648067</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -15593,7 +15593,7 @@
       </c>
       <c r="C12" s="111">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>4.3034503288027297</v>
+        <v>4.4821665874192913</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15646,7 +15646,7 @@
       </c>
       <c r="C18" s="140">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>4.3089107968208733</v>
+        <v>4.4878931098261345</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -15689,11 +15689,11 @@
       </c>
       <c r="E21" s="124">
         <f t="shared" ref="E21:E50" si="0">IF($C$17&lt;B21,0,1/(1+Equity_Cost)^B21)</f>
-        <v>0.92592592592592582</v>
+        <v>0.93023255813953487</v>
       </c>
       <c r="F21" s="125">
         <f t="shared" ref="F21:F51" si="1">C21*E21</f>
-        <v>1012245.4379024026</v>
+        <v>1016953.5562182278</v>
       </c>
       <c r="H21" s="120"/>
     </row>
@@ -15711,11 +15711,11 @@
       </c>
       <c r="E22" s="124">
         <f t="shared" si="0"/>
-        <v>0.85733882030178321</v>
+        <v>0.86533261222282321</v>
       </c>
       <c r="F22" s="125">
         <f t="shared" si="1"/>
-        <v>938464.04555453092</v>
+        <v>947214.24574131321</v>
       </c>
       <c r="H22" s="120"/>
     </row>
@@ -15733,11 +15733,11 @@
       </c>
       <c r="E23" s="124">
         <f t="shared" si="0"/>
-        <v>0.79383224102016958</v>
+        <v>0.80496056950960304</v>
       </c>
       <c r="F23" s="125">
         <f t="shared" si="1"/>
-        <v>870060.49305948301</v>
+        <v>882257.4264568988</v>
       </c>
       <c r="G23" s="338"/>
       <c r="H23" s="339"/>
@@ -15765,11 +15765,11 @@
       </c>
       <c r="E24" s="124">
         <f t="shared" si="0"/>
-        <v>0.73502985279645328</v>
+        <v>0.7488005297763749</v>
       </c>
       <c r="F24" s="125">
         <f t="shared" si="1"/>
-        <v>806642.79592682968</v>
+        <v>821755.13094101753</v>
       </c>
       <c r="G24" s="338"/>
       <c r="H24" s="339"/>
@@ -15797,11 +15797,11 @@
       </c>
       <c r="E25" s="124">
         <f t="shared" si="0"/>
-        <v>0.68058319703375303</v>
+        <v>0.69655863235011617</v>
       </c>
       <c r="F25" s="125">
         <f t="shared" si="1"/>
-        <v>747847.54095962492</v>
+        <v>765401.88269061712</v>
       </c>
       <c r="G25" s="338"/>
       <c r="H25" s="339"/>
@@ -16441,7 +16441,7 @@
       </c>
       <c r="C51" s="123">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
-        <v>13665313.411682436</v>
+        <v>14576334.3057946</v>
       </c>
       <c r="D51" s="139">
         <f>Terminal_Growth</f>
@@ -16449,11 +16449,11 @@
       </c>
       <c r="E51" s="124">
         <f>1/(1+Equity_Cost)^C17</f>
-        <v>0.68058319703375303</v>
+        <v>0.69655863235011617</v>
       </c>
       <c r="F51" s="125">
         <f t="shared" si="1"/>
-        <v>9300382.6901910547</v>
+        <v>10153271.488722367</v>
       </c>
       <c r="H51" s="120"/>
     </row>
@@ -16464,7 +16464,7 @@
       </c>
       <c r="F52" s="137">
         <f>SUM(F21:F51)</f>
-        <v>13675643.003593925</v>
+        <v>14586853.730770443</v>
       </c>
       <c r="H52" s="120"/>
     </row>
@@ -16485,7 +16485,7 @@
     <row r="55" spans="1:17" ht="13.15">
       <c r="A55" s="133">
         <f>F52</f>
-        <v>13675643.003593925</v>
+        <v>14586853.730770443</v>
       </c>
       <c r="B55" s="131">
         <f>C78</f>
@@ -16515,19 +16515,19 @@
       </c>
       <c r="B56" s="123">
         <f t="dataTable" ref="B56:F61" dt2D="1" dtr="1" r1="C16" r2="C17"/>
-        <v>12804479.510939486</v>
+        <v>13672505.518759407</v>
       </c>
       <c r="C56" s="123">
-        <v>13220119.73549787</v>
+        <v>14108942.734726747</v>
       </c>
       <c r="D56" s="123">
-        <v>13647843.401778575</v>
+        <v>14557699.628563819</v>
       </c>
       <c r="E56" s="123">
-        <v>14088194.272720031</v>
+        <v>15019331.61089927</v>
       </c>
       <c r="F56" s="123">
-        <v>14541733.460084772</v>
+        <v>15494411.833815483</v>
       </c>
       <c r="H56" s="120"/>
     </row>
@@ -16536,19 +16536,19 @@
         <v>10</v>
       </c>
       <c r="B57" s="123">
-        <v>12113555.768015305</v>
+        <v>12955108.439982355</v>
       </c>
       <c r="C57" s="123">
-        <v>12845551.930679034</v>
+        <v>13719989.140097706</v>
       </c>
       <c r="D57" s="123">
-        <v>13647843.401778575</v>
+        <v>14557699.628563823</v>
       </c>
       <c r="E57" s="123">
-        <v>14528950.637227219</v>
+        <v>15477098.956767809</v>
       </c>
       <c r="F57" s="123">
-        <v>15498368.674558256</v>
+        <v>16488061.793532752</v>
       </c>
       <c r="H57" s="120"/>
     </row>
@@ -16557,19 +16557,19 @@
         <v>15</v>
       </c>
       <c r="B58" s="123">
-        <v>11372250.66945334</v>
+        <v>12167776.087823538</v>
       </c>
       <c r="C58" s="341">
-        <v>12424995.11635674</v>
+        <v>13273282.802226119</v>
       </c>
       <c r="D58" s="123">
-        <v>13647843.401778571</v>
+        <v>14557699.628563821</v>
       </c>
       <c r="E58" s="123">
-        <v>15074508.84859287</v>
+        <v>16056686.024123048</v>
       </c>
       <c r="F58" s="123">
-        <v>16745463.992453478</v>
+        <v>17813076.586079646</v>
       </c>
       <c r="G58" s="338"/>
       <c r="H58" s="339"/>
@@ -16588,19 +16588,19 @@
         <v>20</v>
       </c>
       <c r="B59" s="123">
-        <v>10717304.058497958</v>
+        <v>11455995.924470538</v>
       </c>
       <c r="C59" s="341">
-        <v>12036875.357431564</v>
+        <v>12851450.277163751</v>
       </c>
       <c r="D59" s="123">
-        <v>13647843.401778573</v>
+        <v>14557699.628563821</v>
       </c>
       <c r="E59" s="123">
-        <v>15630345.176144257</v>
+        <v>16660914.997537248</v>
       </c>
       <c r="F59" s="123">
-        <v>18087745.176089145</v>
+        <v>19272373.380068447</v>
       </c>
       <c r="G59" s="338"/>
       <c r="H59" s="339"/>
@@ -16619,19 +16619,19 @@
         <v>25</v>
       </c>
       <c r="B60" s="123">
-        <v>10188082.203419503</v>
+        <v>10867419.89059219</v>
       </c>
       <c r="C60" s="341">
-        <v>11710041.921529837</v>
+        <v>12487934.233331686</v>
       </c>
       <c r="D60" s="123">
-        <v>13647843.401778571</v>
+        <v>14557699.628563821</v>
       </c>
       <c r="E60" s="123">
-        <v>16147303.8041302</v>
+        <v>17236001.525174189</v>
       </c>
       <c r="F60" s="123">
-        <v>19409937.805411715</v>
+        <v>20743396.603690114</v>
       </c>
       <c r="G60" s="338"/>
       <c r="H60" s="339"/>
@@ -16650,19 +16650,19 @@
         <v>30</v>
       </c>
       <c r="B61" s="123">
-        <v>9781579.342550965</v>
+        <v>10404747.649858402</v>
       </c>
       <c r="C61" s="341">
-        <v>11449040.784862339</v>
+        <v>12190847.98829755</v>
       </c>
       <c r="D61" s="123">
-        <v>13647843.401778571</v>
+        <v>14557699.628563823</v>
       </c>
       <c r="E61" s="123">
-        <v>16603333.227187388</v>
+        <v>17755175.924272951</v>
       </c>
       <c r="F61" s="123">
-        <v>20648182.92034046</v>
+        <v>22153257.413827296</v>
       </c>
       <c r="G61" s="338"/>
       <c r="H61" s="339"/>
@@ -16742,23 +16742,23 @@
       </c>
       <c r="B65" s="124">
         <f>C12</f>
-        <v>4.3034503288027297</v>
+        <v>4.4821665874192913</v>
       </c>
       <c r="C65" s="124">
         <f>C12</f>
-        <v>4.3034503288027297</v>
+        <v>4.4821665874192913</v>
       </c>
       <c r="D65" s="124">
         <f>C12</f>
-        <v>4.3034503288027297</v>
+        <v>4.4821665874192913</v>
       </c>
       <c r="E65" s="141">
         <f>C12</f>
-        <v>4.3034503288027297</v>
+        <v>4.4821665874192913</v>
       </c>
       <c r="F65" s="124">
         <f>C12</f>
-        <v>4.3034503288027297</v>
+        <v>4.4821665874192913</v>
       </c>
       <c r="H65" s="120"/>
     </row>
@@ -16769,23 +16769,23 @@
       </c>
       <c r="B66" s="124">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>4.1377946627909568</v>
+        <v>4.3082945241235127</v>
       </c>
       <c r="C66" s="124">
         <f t="shared" si="4"/>
-        <v>4.2194357657222161</v>
+        <v>4.3940206246463394</v>
       </c>
       <c r="D66" s="124">
         <f t="shared" si="4"/>
-        <v>4.3034503288027297</v>
+        <v>4.4821665874192913</v>
       </c>
       <c r="E66" s="124">
         <f t="shared" si="4"/>
-        <v>4.3899451593225587</v>
+        <v>4.5728415076011704</v>
       </c>
       <c r="F66" s="124">
         <f t="shared" si="4"/>
-        <v>4.4790304722716279</v>
+        <v>4.6661579651719434</v>
       </c>
       <c r="H66" s="120"/>
     </row>
@@ -16796,23 +16796,23 @@
       </c>
       <c r="B67" s="124">
         <f t="shared" si="4"/>
-        <v>4.0020816757390962</v>
+        <v>4.1673815775643765</v>
       </c>
       <c r="C67" s="124">
         <f t="shared" si="4"/>
-        <v>4.145862211236623</v>
+        <v>4.3176213769836949</v>
       </c>
       <c r="D67" s="124">
         <f t="shared" si="4"/>
-        <v>4.3034503288027297</v>
+        <v>4.4821665874192922</v>
       </c>
       <c r="E67" s="124">
         <f t="shared" si="4"/>
-        <v>4.4765196379129595</v>
+        <v>4.6627573261250674</v>
       </c>
       <c r="F67" s="124">
         <f t="shared" si="4"/>
-        <v>4.6669351778267245</v>
+        <v>4.8613332004974268</v>
       </c>
       <c r="H67" s="120"/>
     </row>
@@ -16823,23 +16823,23 @@
       </c>
       <c r="B68" s="124">
         <f t="shared" si="4"/>
-        <v>3.8564726555354611</v>
+        <v>4.0127317679315277</v>
       </c>
       <c r="C68" s="124">
         <f t="shared" si="4"/>
-        <v>4.0632553793232544</v>
+        <v>4.2298781895937605</v>
       </c>
       <c r="D68" s="124">
         <f t="shared" si="4"/>
-        <v>4.3034503288027288</v>
+        <v>4.4821665874192913</v>
       </c>
       <c r="E68" s="124">
         <f t="shared" si="4"/>
-        <v>4.5836795600220892</v>
+        <v>4.7766012820940826</v>
       </c>
       <c r="F68" s="124">
         <f t="shared" si="4"/>
-        <v>4.9118927906794108</v>
+        <v>5.1215959534075886</v>
       </c>
       <c r="H68" s="120"/>
     </row>
@@ -16850,23 +16850,23 @@
       </c>
       <c r="B69" s="124">
         <f t="shared" si="4"/>
-        <v>3.7278263876332134</v>
+        <v>3.8729221100898852</v>
       </c>
       <c r="C69" s="124">
         <f t="shared" si="4"/>
-        <v>3.9870199157760657</v>
+        <v>4.1470207793540244</v>
       </c>
       <c r="D69" s="124">
         <f t="shared" si="4"/>
-        <v>4.3034503288027297</v>
+        <v>4.4821665874192913</v>
       </c>
       <c r="E69" s="124">
         <f t="shared" si="4"/>
-        <v>4.6928583356778164</v>
+        <v>4.895285463503547</v>
       </c>
       <c r="F69" s="124">
         <f t="shared" si="4"/>
-        <v>5.1755470517469639</v>
+        <v>5.4082347162748778</v>
       </c>
       <c r="H69" s="120"/>
     </row>
@@ -16877,23 +16877,23 @@
       </c>
       <c r="B70" s="124">
         <f t="shared" si="4"/>
-        <v>3.6238752938962224</v>
+        <v>3.7573125186077561</v>
       </c>
       <c r="C70" s="124">
         <f t="shared" si="4"/>
-        <v>3.9228224666235421</v>
+        <v>4.0756180396812933</v>
       </c>
       <c r="D70" s="124">
         <f t="shared" si="4"/>
-        <v>4.3034503288027288</v>
+        <v>4.4821665874192913</v>
       </c>
       <c r="E70" s="124">
         <f t="shared" si="4"/>
-        <v>4.7944006553689533</v>
+        <v>5.0082454120914717</v>
       </c>
       <c r="F70" s="124">
         <f t="shared" si="4"/>
-        <v>5.4352554682270311</v>
+        <v>5.6971768140748962</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -16903,23 +16903,23 @@
       </c>
       <c r="B71" s="124">
         <f t="shared" si="4"/>
-        <v>3.5440289750244598</v>
+        <v>3.6664332682432916</v>
       </c>
       <c r="C71" s="124">
         <f t="shared" si="4"/>
-        <v>3.8715559639974138</v>
+        <v>4.017263608908709</v>
       </c>
       <c r="D71" s="124">
         <f t="shared" si="4"/>
-        <v>4.3034503288027288</v>
+        <v>4.4821665874192922</v>
       </c>
       <c r="E71" s="124">
         <f t="shared" si="4"/>
-        <v>4.8839751067037644</v>
+        <v>5.1102229591422459</v>
       </c>
       <c r="F71" s="124">
         <f t="shared" si="4"/>
-        <v>5.6784747018549524</v>
+        <v>5.9741052361049229</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -16954,7 +16954,7 @@
       </c>
       <c r="E74" s="135">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>4.6669351778267245</v>
+        <v>4.8613332004974268</v>
       </c>
       <c r="F74" s="142">
         <f>Scenarios!C58</f>
@@ -16976,7 +16976,7 @@
       </c>
       <c r="E75" s="135">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>4.3899451593225587</v>
+        <v>4.5728415076011704</v>
       </c>
       <c r="F75" s="142">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16999,7 +16999,7 @@
       </c>
       <c r="E76" s="135">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>4.3034503288027297</v>
+        <v>4.4821665874192913</v>
       </c>
       <c r="F76" s="142">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -17022,7 +17022,7 @@
       </c>
       <c r="E77" s="135">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>4.2194357657222161</v>
+        <v>4.3940206246463394</v>
       </c>
       <c r="F77" s="142">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -17045,7 +17045,7 @@
       </c>
       <c r="E78" s="135">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>4.0020816757390962</v>
+        <v>4.1673815775643765</v>
       </c>
       <c r="F78" s="142">
         <f>Scenarios!C52</f>
@@ -17248,7 +17248,7 @@
       </c>
       <c r="C5" s="206">
         <f>Equity_Cost</f>
-        <v>0.08</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="E5" s="148"/>
       <c r="H5" s="120"/>
@@ -17259,7 +17259,7 @@
       </c>
       <c r="C6" s="319">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>19091496.637499999</v>
+        <v>20364263.079999998</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -17275,7 +17275,7 @@
       </c>
       <c r="C7" s="111">
         <f>(C6*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="D7" t="str">
         <f>Market_currency</f>
@@ -17328,7 +17328,7 @@
       </c>
       <c r="C13" s="140">
         <f>F47/Common_Shares*scaling_factor</f>
-        <v>3.7576384600657096</v>
+        <v>4.0080106343585813</v>
       </c>
       <c r="D13" t="str">
         <f>Market_currency</f>
@@ -17371,11 +17371,11 @@
       </c>
       <c r="E16" s="124">
         <f t="shared" ref="E16:E45" si="0">IF($C$12&lt;B16,0,1/(1+Equity_Cost)^B16)</f>
-        <v>0.92592592592592582</v>
+        <v>0.93023255813953487</v>
       </c>
       <c r="F16" s="125">
         <f t="shared" ref="F16:F46" si="1">C16*E16</f>
-        <v>1415995.1726526972</v>
+        <v>1422581.196711547</v>
       </c>
       <c r="H16" s="120"/>
     </row>
@@ -17393,11 +17393,11 @@
       </c>
       <c r="E17" s="124">
         <f t="shared" si="0"/>
-        <v>0.85733882030178321</v>
+        <v>0.86533261222282321</v>
       </c>
       <c r="F17" s="125">
         <f t="shared" si="1"/>
-        <v>1312784.9318511435</v>
+        <v>1325025.2845959321</v>
       </c>
       <c r="H17" s="120"/>
     </row>
@@ -17415,11 +17415,11 @@
       </c>
       <c r="E18" s="124">
         <f t="shared" si="0"/>
-        <v>0.79383224102016958</v>
+        <v>0.80496056950960304</v>
       </c>
       <c r="F18" s="125">
         <f t="shared" si="1"/>
-        <v>1217097.5654294221</v>
+        <v>1234159.4341869599</v>
       </c>
       <c r="H18" s="120"/>
     </row>
@@ -17437,11 +17437,11 @@
       </c>
       <c r="E19" s="124">
         <f t="shared" si="0"/>
-        <v>0.73502985279645328</v>
+        <v>0.7488005297763749</v>
       </c>
       <c r="F19" s="125">
         <f t="shared" si="1"/>
-        <v>1128384.7398259088</v>
+        <v>1149524.8631856581</v>
       </c>
       <c r="H19" s="120"/>
     </row>
@@ -17459,11 +17459,11 @@
       </c>
       <c r="E20" s="124">
         <f t="shared" si="0"/>
-        <v>0.68058319703375303</v>
+        <v>0.69655863235011617</v>
       </c>
       <c r="F20" s="125">
         <f t="shared" si="1"/>
-        <v>1046138.08887437</v>
+        <v>1070694.2510653201</v>
       </c>
       <c r="H20" s="120"/>
     </row>
@@ -18023,7 +18023,7 @@
       </c>
       <c r="C46" s="123">
         <f>C$16*(1+F4)^$C$12/Equity_Cost</f>
-        <v>19115934.830811411</v>
+        <v>20390330.486198843</v>
       </c>
       <c r="D46" s="139">
         <f>Terminal_Growth</f>
@@ -18031,11 +18031,11 @@
       </c>
       <c r="E46" s="124">
         <f>1/(1+Equity_Cost)^C12</f>
-        <v>0.68058319703375303</v>
+        <v>0.69655863235011617</v>
       </c>
       <c r="F46" s="125">
         <f t="shared" si="1"/>
-        <v>13009984.041442504</v>
+        <v>14203060.716633545</v>
       </c>
       <c r="H46" s="120"/>
     </row>
@@ -18046,7 +18046,7 @@
       </c>
       <c r="F47" s="137">
         <f>SUM(F16:F46)</f>
-        <v>19130384.540076047</v>
+        <v>20405045.746378962</v>
       </c>
       <c r="H47" s="120"/>
     </row>
@@ -18067,7 +18067,7 @@
     <row r="50" spans="1:8" ht="13.15">
       <c r="A50" s="133">
         <f>F47</f>
-        <v>19130384.540076047</v>
+        <v>20405045.746378962</v>
       </c>
       <c r="B50" s="131">
         <f>C73</f>
@@ -18097,19 +18097,19 @@
       </c>
       <c r="B51" s="123">
         <f t="dataTable" ref="B51:F56" dt2D="1" dtr="1" r1="C11" r2="C12"/>
-        <v>17911744.026618987</v>
+        <v>19125995.620932922</v>
       </c>
       <c r="C51" s="123">
-        <v>18493168.777472451</v>
+        <v>19736512.564586785</v>
       </c>
       <c r="D51" s="123">
-        <v>19091496.637499996</v>
+        <v>20364263.079999998</v>
       </c>
       <c r="E51" s="123">
-        <v>19707488.257890612</v>
+        <v>21010024.111913007</v>
       </c>
       <c r="F51" s="123">
-        <v>20341928.558503971</v>
+        <v>21674597.422972955</v>
       </c>
       <c r="H51" s="120"/>
     </row>
@@ -18118,19 +18118,19 @@
         <v>10</v>
       </c>
       <c r="B52" s="123">
-        <v>16945234.672248252</v>
+        <v>18122453.631622031</v>
       </c>
       <c r="C52" s="123">
-        <v>17969198.815648105</v>
+        <v>19192418.818388306</v>
       </c>
       <c r="D52" s="123">
-        <v>19091496.637499988</v>
+        <v>20364263.080000002</v>
       </c>
       <c r="E52" s="123">
-        <v>20324047.109221589</v>
+        <v>21650379.037385523</v>
       </c>
       <c r="F52" s="123">
-        <v>21680132.510789536</v>
+        <v>23064580.02361754</v>
       </c>
       <c r="H52" s="120"/>
     </row>
@@ -18139,19 +18139,19 @@
         <v>15</v>
       </c>
       <c r="B53" s="123">
-        <v>15908248.580019716</v>
+        <v>17021081.604457933</v>
       </c>
       <c r="C53" s="123">
-        <v>17380896.417229209</v>
+        <v>18567536.754873864</v>
       </c>
       <c r="D53" s="123">
-        <v>19091496.637499984</v>
+        <v>20364263.080000002</v>
       </c>
       <c r="E53" s="123">
-        <v>21087209.643493522</v>
+        <v>22461143.362693436</v>
       </c>
       <c r="F53" s="123">
-        <v>23424651.067115869</v>
+        <v>24918097.4411203</v>
       </c>
       <c r="H53" s="120"/>
     </row>
@@ -18160,19 +18160,19 @@
         <v>20</v>
       </c>
       <c r="B54" s="123">
-        <v>14992066.392644446</v>
+        <v>16025396.924084028</v>
       </c>
       <c r="C54" s="123">
-        <v>16837969.094990022</v>
+        <v>17977449.808773149</v>
       </c>
       <c r="D54" s="123">
-        <v>19091496.637499984</v>
+        <v>20364263.080000002</v>
       </c>
       <c r="E54" s="123">
-        <v>21864749.879415683</v>
+        <v>23306378.399073903</v>
       </c>
       <c r="F54" s="123">
-        <v>25302321.842604116</v>
+        <v>26959457.311348669</v>
       </c>
       <c r="H54" s="120"/>
     </row>
@@ -18181,19 +18181,19 @@
         <v>25</v>
       </c>
       <c r="B55" s="123">
-        <v>14251756.222804341</v>
+        <v>15202058.244052194</v>
       </c>
       <c r="C55" s="123">
-        <v>16380773.092746381</v>
+        <v>17468939.7735838</v>
       </c>
       <c r="D55" s="123">
-        <v>19091496.637499984</v>
+        <v>20364263.080000002</v>
       </c>
       <c r="E55" s="123">
-        <v>22587905.444538455</v>
+        <v>24110847.074851751</v>
       </c>
       <c r="F55" s="123">
-        <v>27151891.433470726</v>
+        <v>29017220.878873013</v>
       </c>
       <c r="H55" s="120"/>
     </row>
@@ -18202,19 +18202,19 @@
         <v>30</v>
       </c>
       <c r="B56" s="123">
-        <v>13683113.414344627</v>
+        <v>14554842.030603953</v>
       </c>
       <c r="C56" s="123">
-        <v>16015667.619567968</v>
+        <v>17053356.088957295</v>
       </c>
       <c r="D56" s="123">
-        <v>19091496.637499981</v>
+        <v>20364263.080000006</v>
       </c>
       <c r="E56" s="123">
-        <v>23225829.249830857</v>
+        <v>24837102.205635149</v>
       </c>
       <c r="F56" s="123">
-        <v>28884029.746618588</v>
+        <v>30989426.459175114</v>
       </c>
       <c r="H56" s="120"/>
     </row>
@@ -18264,23 +18264,23 @@
       </c>
       <c r="B60" s="124">
         <f>C7</f>
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="C60" s="124">
         <f>C7</f>
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="D60" s="124">
         <f>C7</f>
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="E60" s="141">
         <f>C7</f>
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="F60" s="124">
         <f>C7</f>
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="H60" s="120"/>
     </row>
@@ -18291,23 +18291,23 @@
       </c>
       <c r="B61" s="124">
         <f t="shared" ref="B61:F66" si="4">B51/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>3.5182700117855652</v>
+        <v>3.7567763774799796</v>
       </c>
       <c r="C61" s="124">
         <f t="shared" si="4"/>
-        <v>3.6324749301898041</v>
+        <v>3.8766956578890914</v>
       </c>
       <c r="D61" s="124">
         <f t="shared" si="4"/>
-        <v>3.7499999999999991</v>
+        <v>3.9999999999999991</v>
       </c>
       <c r="E61" s="124">
         <f t="shared" si="4"/>
-        <v>3.8709946302443097</v>
+        <v>4.1268420132614008</v>
       </c>
       <c r="F61" s="124">
         <f t="shared" si="4"/>
-        <v>3.9956129968644998</v>
+        <v>4.2573791819179254</v>
       </c>
       <c r="H61" s="120"/>
     </row>
@@ -18318,23 +18318,23 @@
       </c>
       <c r="B62" s="124">
         <f t="shared" si="4"/>
-        <v>3.3284258027270099</v>
+        <v>3.5596581247116812</v>
       </c>
       <c r="C62" s="124">
         <f t="shared" si="4"/>
-        <v>3.5295554265935372</v>
+        <v>3.7698233897277476</v>
       </c>
       <c r="D62" s="124">
         <f t="shared" si="4"/>
-        <v>3.7499999999999978</v>
+        <v>4</v>
       </c>
       <c r="E62" s="124">
         <f t="shared" si="4"/>
-        <v>3.9921006774229095</v>
+        <v>4.2526221454384245</v>
       </c>
       <c r="F62" s="124">
         <f t="shared" si="4"/>
-        <v>4.2584663978500394</v>
+        <v>4.5304030758214973</v>
       </c>
       <c r="H62" s="120"/>
     </row>
@@ -18345,23 +18345,23 @@
       </c>
       <c r="B63" s="124">
         <f t="shared" si="4"/>
-        <v>3.1247383747744659</v>
+        <v>3.3433238487622079</v>
       </c>
       <c r="C63" s="124">
         <f t="shared" si="4"/>
-        <v>3.4139995832796339</v>
+        <v>3.6470824761853087</v>
       </c>
       <c r="D63" s="124">
         <f t="shared" si="4"/>
-        <v>3.7499999999999969</v>
+        <v>4</v>
       </c>
       <c r="E63" s="124">
         <f t="shared" si="4"/>
-        <v>4.1420029903666951</v>
+        <v>4.4118745224329396</v>
       </c>
       <c r="F63" s="124">
         <f t="shared" si="4"/>
-        <v>4.601129139825642</v>
+        <v>4.8944756494709951</v>
       </c>
       <c r="H63" s="120"/>
     </row>
@@ -18372,23 +18372,23 @@
       </c>
       <c r="B64" s="124">
         <f t="shared" si="4"/>
-        <v>2.9447795549976652</v>
+        <v>3.1477489484650731</v>
       </c>
       <c r="C64" s="124">
         <f t="shared" si="4"/>
-        <v>3.3073564270590876</v>
+        <v>3.5311761075074757</v>
       </c>
       <c r="D64" s="124">
         <f t="shared" si="4"/>
-        <v>3.7499999999999969</v>
+        <v>4</v>
       </c>
       <c r="E64" s="124">
         <f t="shared" si="4"/>
-        <v>4.2947294077907161</v>
+        <v>4.5778977235789871</v>
       </c>
       <c r="F64" s="124">
         <f t="shared" si="4"/>
-        <v>4.9699459770687886</v>
+        <v>5.2954447122274493</v>
       </c>
       <c r="H64" s="120"/>
     </row>
@@ -18399,23 +18399,23 @@
       </c>
       <c r="B65" s="124">
         <f t="shared" si="4"/>
-        <v>2.7993659612070467</v>
+        <v>2.9860266849493469</v>
       </c>
       <c r="C65" s="124">
         <f t="shared" si="4"/>
-        <v>3.2175528332933676</v>
+        <v>3.4312932817569552</v>
       </c>
       <c r="D65" s="124">
         <f t="shared" si="4"/>
-        <v>3.7499999999999969</v>
+        <v>4</v>
       </c>
       <c r="E65" s="124">
         <f t="shared" si="4"/>
-        <v>4.4367734507854246</v>
+        <v>4.7359134931882343</v>
       </c>
       <c r="F65" s="124">
         <f t="shared" si="4"/>
-        <v>5.3332431086370988</v>
+        <v>5.6996358306471091</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="13.15">
@@ -18425,23 +18425,23 @@
       </c>
       <c r="B66" s="124">
         <f t="shared" si="4"/>
-        <v>2.6876717042185505</v>
+        <v>2.8588988412545988</v>
       </c>
       <c r="C66" s="124">
         <f t="shared" si="4"/>
-        <v>3.1458378938930833</v>
+        <v>3.3496632845419505</v>
       </c>
       <c r="D66" s="124">
         <f t="shared" si="4"/>
-        <v>3.7499999999999964</v>
+        <v>4.0000000000000009</v>
       </c>
       <c r="E66" s="124">
         <f t="shared" si="4"/>
-        <v>4.5620760561949796</v>
+        <v>4.8785663607003737</v>
       </c>
       <c r="F66" s="124">
         <f t="shared" si="4"/>
-        <v>5.6734740919716273</v>
+        <v>6.0870214330731605</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="13.15">
@@ -18476,7 +18476,7 @@
       </c>
       <c r="E69" s="135">
         <f>INDEX(B$60:F$66, MATCH(D69, A$60:A$66, 0), MATCH(C69, B$59:F$59, 0))</f>
-        <v>4.2584663978500394</v>
+        <v>4.5304030758214973</v>
       </c>
       <c r="F69" s="142">
         <f>Scenarios!C58</f>
@@ -18498,7 +18498,7 @@
       </c>
       <c r="E70" s="135">
         <f>INDEX(B$60:F$66, MATCH(D70, A$60:A$66, 0), MATCH(C70, B$59:F$59, 0))</f>
-        <v>3.8709946302443097</v>
+        <v>4.1268420132614008</v>
       </c>
       <c r="F70" s="142">
         <f>Scenarios!C40*(1-F$69-F$73)</f>
@@ -18521,7 +18521,7 @@
       </c>
       <c r="E71" s="135">
         <f>INDEX(B$60:F$66, MATCH(D71, A$60:A$66, 0), MATCH(C71, B$59:F$59, 0))</f>
-        <v>3.7499999999999991</v>
+        <v>3.9999999999999991</v>
       </c>
       <c r="F71" s="142">
         <f>Scenarios!C28*(1-F$69-F$73)</f>
@@ -18544,7 +18544,7 @@
       </c>
       <c r="E72" s="135">
         <f>INDEX(B$60:F$66, MATCH(D72, A$60:A$66, 0), MATCH(C72, B$59:F$59, 0))</f>
-        <v>3.6324749301898041</v>
+        <v>3.8766956578890914</v>
       </c>
       <c r="F72" s="142">
         <f>Scenarios!C34*(1-F$69-F$73)</f>
@@ -18567,7 +18567,7 @@
       </c>
       <c r="E73" s="135">
         <f>INDEX(B$60:F$66, MATCH(D73, A$60:A$66, 0), MATCH(C73, B$59:F$59, 0))</f>
-        <v>3.3284258027270099</v>
+        <v>3.5596581247116812</v>
       </c>
       <c r="F73" s="142">
         <f>Scenarios!C52</f>
@@ -18667,7 +18667,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-2.64</v>
+        <v>-2.59</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18716,7 +18716,7 @@
       </c>
       <c r="I6" s="124">
         <f t="shared" si="0"/>
-        <v>4.6070025867398243</v>
+        <v>4.7858408799140584</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -18907,7 +18907,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>2.64</v>
+        <v>2.59</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -18922,7 +18922,7 @@
       </c>
       <c r="C22" s="160">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>4.3034503288027297</v>
+        <v>4.4821665874192913</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -18969,7 +18969,7 @@
       </c>
       <c r="C27" s="160">
         <f>IF(valuation_method="DCF",DCF!E76,DDM!E71)</f>
-        <v>4.3034503288027297</v>
+        <v>4.4821665874192913</v>
       </c>
       <c r="D27" s="160" t="str">
         <f>Market_currency</f>
@@ -19027,7 +19027,7 @@
       </c>
       <c r="C33" s="160">
         <f>IF(valuation_method="DCF",DCF!E77,DDM!E72)</f>
-        <v>4.2194357657222161</v>
+        <v>4.3940206246463394</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -19085,7 +19085,7 @@
       </c>
       <c r="C39" s="160">
         <f>IF(valuation_method="DCF",DCF!E75,DDM!E70)</f>
-        <v>4.3899451593225587</v>
+        <v>4.5728415076011704</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -19112,7 +19112,7 @@
       </c>
       <c r="C42" s="154">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>4.3039463822905928</v>
+        <v>4.4826723789010767</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -19186,7 +19186,7 @@
       </c>
       <c r="C51" s="160">
         <f>IF(valuation_method="DCF",DCF!E78,DDM!E73)</f>
-        <v>4.0020816757390962</v>
+        <v>4.1673815775643765</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -19244,7 +19244,7 @@
       </c>
       <c r="C57" s="160">
         <f>IF(valuation_method="DCF",DCF!E74,DDM!E69)</f>
-        <v>4.6669351778267245</v>
+        <v>4.8613332004974268</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -19270,7 +19270,7 @@
       </c>
       <c r="C60" s="154">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>4.3070025867398245</v>
+        <v>4.4858408799140586</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -19332,7 +19332,7 @@
       </c>
       <c r="C66" s="160">
         <f>IF(valuation_method="DCF",DCF!C18,DDM!C13)</f>
-        <v>4.3089107968208733</v>
+        <v>4.4878931098261345</v>
       </c>
       <c r="D66" s="160" t="str">
         <f>Market_currency</f>
@@ -19395,7 +19395,7 @@
       </c>
       <c r="F72" s="291">
         <f>BS!D89/C60</f>
-        <v>0.37676003598192104</v>
+        <v>0.36173963655737423</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9">
@@ -19446,7 +19446,7 @@
       </c>
       <c r="C80" s="167">
         <f>Thesis!F29</f>
-        <v>0.4</v>
+        <v>0.3674</v>
       </c>
     </row>
     <row r="81" spans="2:8">
@@ -19455,7 +19455,7 @@
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>0.47667638483964997</v>
+        <v>0.49717779580945759</v>
       </c>
       <c r="D81" s="116"/>
       <c r="E81" s="100"/>
@@ -19467,7 +19467,7 @@
       </c>
       <c r="C82" s="116">
         <f>C60/(1+C80)^C76</f>
-        <v>1.56960735668361</v>
+        <v>1.7545152108155548</v>
       </c>
       <c r="D82" s="116"/>
     </row>
@@ -19477,7 +19477,7 @@
       </c>
       <c r="C83" s="111">
         <f>C81+C82</f>
-        <v>2.04628374152326</v>
+        <v>2.2516930066250125</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -19488,7 +19488,7 @@
       </c>
       <c r="F83" s="291">
         <f>(1-C83/C60)</f>
-        <v>0.52489377465821541</v>
+        <v>0.4980443874620557</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -19505,7 +19505,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>2.64</v>
+        <v>2.59</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19518,7 +19518,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.27545168163665656</v>
+        <v>0.29938655516441326</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -19535,7 +19535,7 @@
       </c>
       <c r="C90" s="167">
         <f>Thesis!F30</f>
-        <v>0.22</v>
+        <v>0.21740000000000001</v>
       </c>
     </row>
     <row r="91" spans="2:8">
@@ -19544,7 +19544,7 @@
       </c>
       <c r="C91" s="116">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>0.6126724263264326</v>
+        <v>0.61512024715948099</v>
       </c>
       <c r="D91" s="116"/>
       <c r="E91" s="100"/>
@@ -19556,7 +19556,7 @@
       </c>
       <c r="C92" s="116">
         <f>C60/(1+C90)^C76</f>
-        <v>2.3718959883976107</v>
+        <v>2.48624528278879</v>
       </c>
       <c r="D92" s="116"/>
     </row>
@@ -19566,7 +19566,7 @@
       </c>
       <c r="C93" s="111">
         <f>C91+C92</f>
-        <v>2.9845684147240434</v>
+        <v>3.101365529948271</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -19577,7 +19577,7 @@
       </c>
       <c r="F93" s="291">
         <f>(1-C93/C60)</f>
-        <v>0.30704280886369151</v>
+        <v>0.30863229147626647</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
@@ -19593,7 +19593,7 @@
       </c>
       <c r="C96" s="134">
         <f>Thesis!F31</f>
-        <v>0.08</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="G96" s="2"/>
       <c r="H96" s="281"/>
@@ -19604,7 +19604,7 @@
       </c>
       <c r="C97" s="116">
         <f>PV(C96, C76, -C77, 0)</f>
-        <v>0.77312909617436398</v>
+        <v>0.78015772196158795</v>
       </c>
       <c r="D97" s="116"/>
       <c r="G97" s="2"/>
@@ -19616,7 +19616,7 @@
       </c>
       <c r="C98" s="116">
         <f>C60/(1+C96)^C76</f>
-        <v>3.4190375155113424</v>
+        <v>3.6109250294250792</v>
       </c>
       <c r="D98" s="116"/>
       <c r="G98" s="2"/>
@@ -19628,7 +19628,7 @@
       </c>
       <c r="C99" s="111">
         <f>C97+C98</f>
-        <v>4.1921666116857068</v>
+        <v>4.3910827513866675</v>
       </c>
       <c r="D99" t="s">
         <v>399</v>
@@ -19638,7 +19638,7 @@
       </c>
       <c r="F99" s="291">
         <f>(1-C99/C60)</f>
-        <v>2.6662620405120907E-2</v>
+        <v>2.1123827408074836E-2</v>
       </c>
     </row>
     <row r="100" spans="2:8">
@@ -19655,7 +19655,7 @@
       </c>
       <c r="C102" s="134">
         <f>Thesis!F32</f>
-        <v>0.12</v>
+        <v>0.1174</v>
       </c>
     </row>
     <row r="103" spans="2:8">
@@ -19664,7 +19664,7 @@
       </c>
       <c r="C103" s="116">
         <f>PV(C102, C76, -C77, 0)</f>
-        <v>0.72054938046647277</v>
+        <v>0.72378093778159469</v>
       </c>
       <c r="D103" s="116"/>
     </row>
@@ -19674,7 +19674,7 @@
       </c>
       <c r="C104" s="116">
         <f>C60/(1+C102)^C76</f>
-        <v>3.0656393685226742</v>
+        <v>3.2152730720890683</v>
       </c>
       <c r="D104" s="116"/>
     </row>
@@ -19684,7 +19684,7 @@
       </c>
       <c r="C105" s="111">
         <f>C103+C104</f>
-        <v>3.7861887489891468</v>
+        <v>3.939054009870663</v>
       </c>
       <c r="D105" t="s">
         <v>399</v>
@@ -19694,7 +19694,7 @@
       </c>
       <c r="F105" s="291">
         <f>(1-C105/C66)</f>
-        <v>0.12131187496789031</v>
+        <v>0.12229326468444657</v>
       </c>
     </row>
     <row r="106" spans="2:8">

--- a/financial_models/opportunities/0639.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0639.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BDD483C-1124-499C-98E1-7112D8CB6440}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABE2F132-4E9D-487E-9002-4F501FD21056}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3885,29 +3885,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4323,7 +4323,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4344,7 +4344,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>13185.860344299999</v>
+        <v>13033.1283712</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4381,13 +4381,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="356" t="s">
+      <c r="B18" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C18" s="356"/>
-      <c r="D18" s="356"/>
-      <c r="E18" s="356"/>
-      <c r="F18" s="356"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4470,7 +4470,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.29938655516441326</v>
+        <v>0.30489849810760594</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4587,22 +4587,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="356" t="s">
+      <c r="B36" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C36" s="356"/>
-      <c r="D36" s="356"/>
-      <c r="E36" s="356"/>
-      <c r="F36" s="356"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="358" t="s">
+      <c r="B37" s="361" t="s">
         <v>341</v>
       </c>
-      <c r="C37" s="358"/>
-      <c r="D37" s="358"/>
-      <c r="E37" s="358"/>
-      <c r="F37" s="358"/>
+      <c r="C37" s="361"/>
+      <c r="D37" s="361"/>
+      <c r="E37" s="361"/>
+      <c r="F37" s="361"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4614,13 +4614,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="357" t="s">
+      <c r="B40" s="359" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="357"/>
-      <c r="D40" s="357"/>
-      <c r="E40" s="357"/>
-      <c r="F40" s="357"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4640,13 +4640,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="357" t="s">
+      <c r="B43" s="359" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="357"/>
-      <c r="D43" s="357"/>
-      <c r="E43" s="357"/>
-      <c r="F43" s="357"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4675,13 +4675,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="357" t="s">
+      <c r="B47" s="359" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="357"/>
-      <c r="D47" s="357"/>
-      <c r="E47" s="357"/>
-      <c r="F47" s="357"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4697,13 +4697,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="357" t="s">
+      <c r="B50" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="357"/>
-      <c r="D50" s="357"/>
-      <c r="E50" s="357"/>
-      <c r="F50" s="357"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4767,13 +4767,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="357" t="s">
+      <c r="B58" s="359" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="357"/>
-      <c r="D58" s="357"/>
-      <c r="E58" s="357"/>
-      <c r="F58" s="357"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4789,7 +4789,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="357" t="s">
+      <c r="B61" s="359" t="s">
         <v>340</v>
       </c>
       <c r="C61" s="360"/>
@@ -4811,22 +4811,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="356" t="s">
+      <c r="B64" s="358" t="s">
         <v>345</v>
       </c>
-      <c r="C64" s="356"/>
-      <c r="D64" s="356"/>
-      <c r="E64" s="356"/>
-      <c r="F64" s="356"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="356" t="s">
+      <c r="B65" s="358" t="s">
         <v>364</v>
       </c>
-      <c r="C65" s="356"/>
-      <c r="D65" s="356"/>
-      <c r="E65" s="356"/>
-      <c r="F65" s="356"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4860,7 +4860,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>8.2802899745124545E-2</v>
+        <v>8.3773246226512721E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4870,7 +4870,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>0.11583011583011583</v>
+        <v>0.1171875</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>450</v>
@@ -4961,22 +4961,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="356" t="s">
+      <c r="B80" s="358" t="s">
         <v>365</v>
       </c>
-      <c r="C80" s="356"/>
-      <c r="D80" s="356"/>
-      <c r="E80" s="356"/>
-      <c r="F80" s="356"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="358" t="s">
+      <c r="B81" s="361" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="358"/>
-      <c r="D81" s="358"/>
-      <c r="E81" s="358"/>
-      <c r="F81" s="358"/>
+      <c r="C81" s="361"/>
+      <c r="D81" s="361"/>
+      <c r="E81" s="361"/>
+      <c r="F81" s="361"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5020,22 +5020,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="356" t="s">
+      <c r="B89" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C89" s="356"/>
-      <c r="D89" s="356"/>
-      <c r="E89" s="356"/>
-      <c r="F89" s="356"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="356" t="s">
+      <c r="B90" s="358" t="s">
         <v>367</v>
       </c>
-      <c r="C90" s="356"/>
-      <c r="D90" s="356"/>
-      <c r="E90" s="356"/>
-      <c r="F90" s="356"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5072,13 +5072,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="356" t="s">
+      <c r="B97" s="358" t="s">
         <v>368</v>
       </c>
-      <c r="C97" s="356"/>
-      <c r="D97" s="356"/>
-      <c r="E97" s="356"/>
-      <c r="F97" s="356"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5091,13 +5091,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="356" t="s">
+      <c r="B101" s="358" t="s">
         <v>346</v>
       </c>
-      <c r="C101" s="356"/>
-      <c r="D101" s="356"/>
-      <c r="E101" s="356"/>
-      <c r="F101" s="356"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5219,13 +5219,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="356" t="s">
+      <c r="B116" s="358" t="s">
         <v>369</v>
       </c>
-      <c r="C116" s="356"/>
-      <c r="D116" s="356"/>
-      <c r="E116" s="356"/>
-      <c r="F116" s="356"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5264,13 +5264,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="357" t="s">
+      <c r="B123" s="359" t="s">
         <v>370</v>
       </c>
-      <c r="C123" s="357"/>
-      <c r="D123" s="357"/>
-      <c r="E123" s="357"/>
-      <c r="F123" s="357"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5413,13 +5413,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="361" t="s">
+      <c r="B134" s="362" t="s">
         <v>373</v>
       </c>
-      <c r="C134" s="361"/>
-      <c r="D134" s="361"/>
-      <c r="E134" s="361"/>
-      <c r="F134" s="361"/>
+      <c r="C134" s="362"/>
+      <c r="D134" s="362"/>
+      <c r="E134" s="362"/>
+      <c r="F134" s="362"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5432,22 +5432,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="359" t="s">
+      <c r="B138" s="363" t="s">
         <v>371</v>
       </c>
-      <c r="C138" s="359"/>
-      <c r="D138" s="359"/>
-      <c r="E138" s="359"/>
-      <c r="F138" s="359"/>
+      <c r="C138" s="363"/>
+      <c r="D138" s="363"/>
+      <c r="E138" s="363"/>
+      <c r="F138" s="363"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="356" t="s">
+      <c r="B139" s="358" t="s">
         <v>372</v>
       </c>
-      <c r="C139" s="356"/>
-      <c r="D139" s="356"/>
-      <c r="E139" s="356"/>
-      <c r="F139" s="356"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5780,13 +5780,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="363" t="s">
+      <c r="B179" s="357" t="s">
         <v>379</v>
       </c>
-      <c r="C179" s="356"/>
-      <c r="D179" s="356"/>
-      <c r="E179" s="356"/>
-      <c r="F179" s="356"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5823,13 +5823,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="357" t="s">
+      <c r="B188" s="359" t="s">
         <v>384</v>
       </c>
-      <c r="C188" s="357"/>
-      <c r="D188" s="357"/>
-      <c r="E188" s="357"/>
-      <c r="F188" s="357"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5837,22 +5837,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="362" t="s">
+      <c r="B191" s="356" t="s">
         <v>385</v>
       </c>
-      <c r="C191" s="362"/>
-      <c r="D191" s="362"/>
-      <c r="E191" s="362"/>
-      <c r="F191" s="362"/>
+      <c r="C191" s="356"/>
+      <c r="D191" s="356"/>
+      <c r="E191" s="356"/>
+      <c r="F191" s="356"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="362" t="s">
+      <c r="B192" s="356" t="s">
         <v>386</v>
       </c>
-      <c r="C192" s="362"/>
-      <c r="D192" s="362"/>
-      <c r="E192" s="362"/>
-      <c r="F192" s="362"/>
+      <c r="C192" s="356"/>
+      <c r="D192" s="356"/>
+      <c r="E192" s="356"/>
+      <c r="F192" s="356"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5876,17 +5876,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5903,6 +5892,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13425,20 +13425,20 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>0.11583011583011583</v>
+        <v>0.1171875</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>0.11583011583011583</v>
+        <v>0.1171875</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>0.10810810810810813</v>
+        <v>0.10937500000000001</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>0.16602316602316605</v>
+        <v>0.16796875000000003</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
@@ -14624,50 +14624,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>8.2802899745124545E-2</v>
+        <v>8.3773246226512721E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>9.6625123902083596E-2</v>
+        <v>9.7757449572811128E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.13296218461439893</v>
+        <v>0.1345203352153489</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.21563766257166658</v>
+        <v>0.21816466642992829</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.17718016606376452</v>
+        <v>0.17925649613482425</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>6.3563087892274661E-2</v>
+        <v>6.4307967828512252E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>8.0692421443697968E-2</v>
+        <v>8.1638035757491303E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>7.1845823879783555E-2</v>
+        <v>7.2687767128374769E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>6.8236958113161786E-2</v>
+        <v>6.9036609966050391E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>1.2079302816888397E-2</v>
+        <v>1.2220857146773807E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>5.2327264356190869E-3</v>
+        <v>5.2940474485364975E-3</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14681,43 +14681,43 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13764555005199791</v>
+        <v>0.13925858384166975</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.17450040724833343</v>
+        <v>0.17654533389577481</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.25088654919889647</v>
+        <v>0.25382662594732103</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.23212979055425381</v>
+        <v>0.23485006153731144</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.0042133694616305E-2</v>
+        <v>9.1097314948850081E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.9197137637547011E-2</v>
+        <v>9.0242416594236999E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.7360852452677232E-2</v>
+        <v>8.8384612442357027E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.9685767111222961E-2</v>
+        <v>9.0736772194557599E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.1309507482571225E-3</v>
+        <v>5.1910790773382603E-3</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-5.3957419646686711E-2</v>
+        <v>-5.4589733158171318E-2</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18667,7 +18667,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-2.59</v>
+        <v>-2.56</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18907,7 +18907,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19505,7 +19505,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19518,7 +19518,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.29938655516441326</v>
+        <v>0.30489849810760594</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/0639.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0639.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABE2F132-4E9D-487E-9002-4F501FD21056}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D69B9FB-46F6-452C-B50D-F95FA559BD8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="368" yWindow="368" windowWidth="12689" windowHeight="7642" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3885,29 +3885,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4323,7 +4323,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>2.56</v>
+        <v>2.57</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4344,7 +4344,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>13033.1283712</v>
+        <v>13084.039028899999</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4381,13 +4381,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="356" t="s">
         <v>362</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="356"/>
+      <c r="D18" s="356"/>
+      <c r="E18" s="356"/>
+      <c r="F18" s="356"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4470,7 +4470,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.30489849810760594</v>
+        <v>0.30305109613357195</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4587,22 +4587,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="356" t="s">
         <v>363</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="356"/>
+      <c r="D36" s="356"/>
+      <c r="E36" s="356"/>
+      <c r="F36" s="356"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="361" t="s">
+      <c r="B37" s="358" t="s">
         <v>341</v>
       </c>
-      <c r="C37" s="361"/>
-      <c r="D37" s="361"/>
-      <c r="E37" s="361"/>
-      <c r="F37" s="361"/>
+      <c r="C37" s="358"/>
+      <c r="D37" s="358"/>
+      <c r="E37" s="358"/>
+      <c r="F37" s="358"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4614,13 +4614,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="357" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="357"/>
+      <c r="D40" s="357"/>
+      <c r="E40" s="357"/>
+      <c r="F40" s="357"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4640,13 +4640,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="357" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="357"/>
+      <c r="D43" s="357"/>
+      <c r="E43" s="357"/>
+      <c r="F43" s="357"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4675,13 +4675,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="357" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="357"/>
+      <c r="D47" s="357"/>
+      <c r="E47" s="357"/>
+      <c r="F47" s="357"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4697,13 +4697,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="357" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="357"/>
+      <c r="D50" s="357"/>
+      <c r="E50" s="357"/>
+      <c r="F50" s="357"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4767,13 +4767,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="357" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="357"/>
+      <c r="D58" s="357"/>
+      <c r="E58" s="357"/>
+      <c r="F58" s="357"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4789,7 +4789,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="357" t="s">
         <v>340</v>
       </c>
       <c r="C61" s="360"/>
@@ -4811,22 +4811,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="356" t="s">
         <v>345</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="356"/>
+      <c r="D64" s="356"/>
+      <c r="E64" s="356"/>
+      <c r="F64" s="356"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="356" t="s">
         <v>364</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="356"/>
+      <c r="D65" s="356"/>
+      <c r="E65" s="356"/>
+      <c r="F65" s="356"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4860,7 +4860,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>8.3773246226512721E-2</v>
+        <v>8.3447280287888156E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4870,7 +4870,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>0.1171875</v>
+        <v>0.11673151750972763</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>450</v>
@@ -4961,22 +4961,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="356" t="s">
         <v>365</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="356"/>
+      <c r="D80" s="356"/>
+      <c r="E80" s="356"/>
+      <c r="F80" s="356"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="361" t="s">
+      <c r="B81" s="358" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="361"/>
-      <c r="D81" s="361"/>
-      <c r="E81" s="361"/>
-      <c r="F81" s="361"/>
+      <c r="C81" s="358"/>
+      <c r="D81" s="358"/>
+      <c r="E81" s="358"/>
+      <c r="F81" s="358"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5020,22 +5020,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="356" t="s">
         <v>366</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="356"/>
+      <c r="D89" s="356"/>
+      <c r="E89" s="356"/>
+      <c r="F89" s="356"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="356" t="s">
         <v>367</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="356"/>
+      <c r="D90" s="356"/>
+      <c r="E90" s="356"/>
+      <c r="F90" s="356"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5072,13 +5072,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="356" t="s">
         <v>368</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="356"/>
+      <c r="D97" s="356"/>
+      <c r="E97" s="356"/>
+      <c r="F97" s="356"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5091,13 +5091,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="356" t="s">
         <v>346</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="356"/>
+      <c r="D101" s="356"/>
+      <c r="E101" s="356"/>
+      <c r="F101" s="356"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5219,13 +5219,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="356" t="s">
         <v>369</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="356"/>
+      <c r="D116" s="356"/>
+      <c r="E116" s="356"/>
+      <c r="F116" s="356"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5264,13 +5264,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="357" t="s">
         <v>370</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="357"/>
+      <c r="D123" s="357"/>
+      <c r="E123" s="357"/>
+      <c r="F123" s="357"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5413,13 +5413,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="362" t="s">
+      <c r="B134" s="361" t="s">
         <v>373</v>
       </c>
-      <c r="C134" s="362"/>
-      <c r="D134" s="362"/>
-      <c r="E134" s="362"/>
-      <c r="F134" s="362"/>
+      <c r="C134" s="361"/>
+      <c r="D134" s="361"/>
+      <c r="E134" s="361"/>
+      <c r="F134" s="361"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5432,22 +5432,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="363" t="s">
+      <c r="B138" s="359" t="s">
         <v>371</v>
       </c>
-      <c r="C138" s="363"/>
-      <c r="D138" s="363"/>
-      <c r="E138" s="363"/>
-      <c r="F138" s="363"/>
+      <c r="C138" s="359"/>
+      <c r="D138" s="359"/>
+      <c r="E138" s="359"/>
+      <c r="F138" s="359"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="356" t="s">
         <v>372</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="356"/>
+      <c r="D139" s="356"/>
+      <c r="E139" s="356"/>
+      <c r="F139" s="356"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5780,13 +5780,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="357" t="s">
+      <c r="B179" s="363" t="s">
         <v>379</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="356"/>
+      <c r="D179" s="356"/>
+      <c r="E179" s="356"/>
+      <c r="F179" s="356"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5823,13 +5823,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="357" t="s">
         <v>384</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="357"/>
+      <c r="D188" s="357"/>
+      <c r="E188" s="357"/>
+      <c r="F188" s="357"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5837,22 +5837,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="356" t="s">
+      <c r="B191" s="362" t="s">
         <v>385</v>
       </c>
-      <c r="C191" s="356"/>
-      <c r="D191" s="356"/>
-      <c r="E191" s="356"/>
-      <c r="F191" s="356"/>
+      <c r="C191" s="362"/>
+      <c r="D191" s="362"/>
+      <c r="E191" s="362"/>
+      <c r="F191" s="362"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="356" t="s">
+      <c r="B192" s="362" t="s">
         <v>386</v>
       </c>
-      <c r="C192" s="356"/>
-      <c r="D192" s="356"/>
-      <c r="E192" s="356"/>
-      <c r="F192" s="356"/>
+      <c r="C192" s="362"/>
+      <c r="D192" s="362"/>
+      <c r="E192" s="362"/>
+      <c r="F192" s="362"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5876,6 +5876,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5892,17 +5903,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13425,20 +13425,20 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>0.1171875</v>
+        <v>0.11673151750972763</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>0.1171875</v>
+        <v>0.11673151750972763</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>0.10937500000000001</v>
+        <v>0.10894941634241247</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>0.16796875000000003</v>
+        <v>0.16731517509727628</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
@@ -14624,50 +14624,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>8.3773246226512721E-2</v>
+        <v>8.3447280287888156E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>9.7757449572811128E-2</v>
+        <v>9.7377070391593976E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.1345203352153489</v>
+        <v>0.13399690978649542</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.21816466642992829</v>
+        <v>0.21731577667728266</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.17925649613482425</v>
+        <v>0.17855900004091443</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>6.4307967828512252E-2</v>
+        <v>6.4057742272759302E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>8.1638035757491303E-2</v>
+        <v>8.1320378030808466E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>7.2687767128374769E-2</v>
+        <v>7.2404935349665148E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>6.9036609966050391E-2</v>
+        <v>6.8767985024548256E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>1.2220857146773807E-2</v>
+        <v>1.2173305173440058E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>5.2940474485364975E-3</v>
+        <v>5.2734480421219596E-3</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14681,43 +14681,43 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13925858384166975</v>
+        <v>0.1387167216477333</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.17654533389577481</v>
+        <v>0.17585838707127766</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.25382662594732103</v>
+        <v>0.25283897370628089</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.23485006153731144</v>
+        <v>0.23393624806829469</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.1097314948850081E-2</v>
+        <v>9.0742850688348725E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.0242416594236999E-2</v>
+        <v>8.9891278786477333E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.8384612442357027E-2</v>
+        <v>8.8040703444526858E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.0736772194557599E-2</v>
+        <v>9.0383710824150768E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.1910790773382603E-3</v>
+        <v>5.1708803260645704E-3</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-5.4589733158171318E-2</v>
+        <v>-5.4377321745104505E-2</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18667,7 +18667,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-2.56</v>
+        <v>-2.57</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18907,7 +18907,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>2.56</v>
+        <v>2.57</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19505,7 +19505,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>2.56</v>
+        <v>2.57</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19518,7 +19518,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.30489849810760594</v>
+        <v>0.30305109613357195</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/0639.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0639.HK_Valuation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D69B9FB-46F6-452C-B50D-F95FA559BD8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89408EFE-3140-4225-B237-7DD8C292473E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="368" yWindow="368" windowWidth="12689" windowHeight="7642" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3885,29 +3885,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4323,7 +4323,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>2.57</v>
+        <v>2.67</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4344,7 +4344,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>13084.039028899999</v>
+        <v>13593.145605899999</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4381,13 +4381,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="356" t="s">
+      <c r="B18" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C18" s="356"/>
-      <c r="D18" s="356"/>
-      <c r="E18" s="356"/>
-      <c r="F18" s="356"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4470,7 +4470,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.30305109613357195</v>
+        <v>0.28511828789831495</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4587,22 +4587,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="356" t="s">
+      <c r="B36" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C36" s="356"/>
-      <c r="D36" s="356"/>
-      <c r="E36" s="356"/>
-      <c r="F36" s="356"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="358" t="s">
+      <c r="B37" s="361" t="s">
         <v>341</v>
       </c>
-      <c r="C37" s="358"/>
-      <c r="D37" s="358"/>
-      <c r="E37" s="358"/>
-      <c r="F37" s="358"/>
+      <c r="C37" s="361"/>
+      <c r="D37" s="361"/>
+      <c r="E37" s="361"/>
+      <c r="F37" s="361"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4614,13 +4614,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="357" t="s">
+      <c r="B40" s="359" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="357"/>
-      <c r="D40" s="357"/>
-      <c r="E40" s="357"/>
-      <c r="F40" s="357"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4640,13 +4640,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="357" t="s">
+      <c r="B43" s="359" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="357"/>
-      <c r="D43" s="357"/>
-      <c r="E43" s="357"/>
-      <c r="F43" s="357"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4675,13 +4675,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="357" t="s">
+      <c r="B47" s="359" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="357"/>
-      <c r="D47" s="357"/>
-      <c r="E47" s="357"/>
-      <c r="F47" s="357"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4697,13 +4697,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="357" t="s">
+      <c r="B50" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="357"/>
-      <c r="D50" s="357"/>
-      <c r="E50" s="357"/>
-      <c r="F50" s="357"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4767,13 +4767,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="357" t="s">
+      <c r="B58" s="359" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="357"/>
-      <c r="D58" s="357"/>
-      <c r="E58" s="357"/>
-      <c r="F58" s="357"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4789,7 +4789,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="357" t="s">
+      <c r="B61" s="359" t="s">
         <v>340</v>
       </c>
       <c r="C61" s="360"/>
@@ -4811,22 +4811,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="356" t="s">
+      <c r="B64" s="358" t="s">
         <v>345</v>
       </c>
-      <c r="C64" s="356"/>
-      <c r="D64" s="356"/>
-      <c r="E64" s="356"/>
-      <c r="F64" s="356"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="356" t="s">
+      <c r="B65" s="358" t="s">
         <v>364</v>
       </c>
-      <c r="C65" s="356"/>
-      <c r="D65" s="356"/>
-      <c r="E65" s="356"/>
-      <c r="F65" s="356"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4860,7 +4860,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>8.3447280287888156E-2</v>
+        <v>8.0321913984971002E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4870,7 +4870,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>0.11673151750972763</v>
+        <v>0.11235955056179775</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>450</v>
@@ -4961,22 +4961,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="356" t="s">
+      <c r="B80" s="358" t="s">
         <v>365</v>
       </c>
-      <c r="C80" s="356"/>
-      <c r="D80" s="356"/>
-      <c r="E80" s="356"/>
-      <c r="F80" s="356"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="358" t="s">
+      <c r="B81" s="361" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="358"/>
-      <c r="D81" s="358"/>
-      <c r="E81" s="358"/>
-      <c r="F81" s="358"/>
+      <c r="C81" s="361"/>
+      <c r="D81" s="361"/>
+      <c r="E81" s="361"/>
+      <c r="F81" s="361"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5020,22 +5020,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="356" t="s">
+      <c r="B89" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C89" s="356"/>
-      <c r="D89" s="356"/>
-      <c r="E89" s="356"/>
-      <c r="F89" s="356"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="356" t="s">
+      <c r="B90" s="358" t="s">
         <v>367</v>
       </c>
-      <c r="C90" s="356"/>
-      <c r="D90" s="356"/>
-      <c r="E90" s="356"/>
-      <c r="F90" s="356"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5072,13 +5072,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="356" t="s">
+      <c r="B97" s="358" t="s">
         <v>368</v>
       </c>
-      <c r="C97" s="356"/>
-      <c r="D97" s="356"/>
-      <c r="E97" s="356"/>
-      <c r="F97" s="356"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5091,13 +5091,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="356" t="s">
+      <c r="B101" s="358" t="s">
         <v>346</v>
       </c>
-      <c r="C101" s="356"/>
-      <c r="D101" s="356"/>
-      <c r="E101" s="356"/>
-      <c r="F101" s="356"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5219,13 +5219,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="356" t="s">
+      <c r="B116" s="358" t="s">
         <v>369</v>
       </c>
-      <c r="C116" s="356"/>
-      <c r="D116" s="356"/>
-      <c r="E116" s="356"/>
-      <c r="F116" s="356"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5264,13 +5264,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="357" t="s">
+      <c r="B123" s="359" t="s">
         <v>370</v>
       </c>
-      <c r="C123" s="357"/>
-      <c r="D123" s="357"/>
-      <c r="E123" s="357"/>
-      <c r="F123" s="357"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5413,13 +5413,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="361" t="s">
+      <c r="B134" s="362" t="s">
         <v>373</v>
       </c>
-      <c r="C134" s="361"/>
-      <c r="D134" s="361"/>
-      <c r="E134" s="361"/>
-      <c r="F134" s="361"/>
+      <c r="C134" s="362"/>
+      <c r="D134" s="362"/>
+      <c r="E134" s="362"/>
+      <c r="F134" s="362"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5432,22 +5432,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="359" t="s">
+      <c r="B138" s="363" t="s">
         <v>371</v>
       </c>
-      <c r="C138" s="359"/>
-      <c r="D138" s="359"/>
-      <c r="E138" s="359"/>
-      <c r="F138" s="359"/>
+      <c r="C138" s="363"/>
+      <c r="D138" s="363"/>
+      <c r="E138" s="363"/>
+      <c r="F138" s="363"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="356" t="s">
+      <c r="B139" s="358" t="s">
         <v>372</v>
       </c>
-      <c r="C139" s="356"/>
-      <c r="D139" s="356"/>
-      <c r="E139" s="356"/>
-      <c r="F139" s="356"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5780,13 +5780,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="363" t="s">
+      <c r="B179" s="357" t="s">
         <v>379</v>
       </c>
-      <c r="C179" s="356"/>
-      <c r="D179" s="356"/>
-      <c r="E179" s="356"/>
-      <c r="F179" s="356"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5823,13 +5823,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="357" t="s">
+      <c r="B188" s="359" t="s">
         <v>384</v>
       </c>
-      <c r="C188" s="357"/>
-      <c r="D188" s="357"/>
-      <c r="E188" s="357"/>
-      <c r="F188" s="357"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5837,22 +5837,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="362" t="s">
+      <c r="B191" s="356" t="s">
         <v>385</v>
       </c>
-      <c r="C191" s="362"/>
-      <c r="D191" s="362"/>
-      <c r="E191" s="362"/>
-      <c r="F191" s="362"/>
+      <c r="C191" s="356"/>
+      <c r="D191" s="356"/>
+      <c r="E191" s="356"/>
+      <c r="F191" s="356"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="362" t="s">
+      <c r="B192" s="356" t="s">
         <v>386</v>
       </c>
-      <c r="C192" s="362"/>
-      <c r="D192" s="362"/>
-      <c r="E192" s="362"/>
-      <c r="F192" s="362"/>
+      <c r="C192" s="356"/>
+      <c r="D192" s="356"/>
+      <c r="E192" s="356"/>
+      <c r="F192" s="356"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5876,17 +5876,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5903,6 +5892,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13425,20 +13425,20 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>0.11673151750972763</v>
+        <v>0.11235955056179775</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>0.11673151750972763</v>
+        <v>0.11235955056179775</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>0.10894941634241247</v>
+        <v>0.10486891385767791</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>0.16731517509727628</v>
+        <v>0.16104868913857681</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
@@ -14624,50 +14624,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>8.3447280287888156E-2</v>
+        <v>8.0321913984971002E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>9.7377070391593976E-2</v>
+        <v>9.372998910351929E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.13399690978649542</v>
+        <v>0.12897829893306861</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.21731577667728266</v>
+        <v>0.20917660901146684</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.17855900004091443</v>
+        <v>0.17187139704312737</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>6.4057742272759302E-2</v>
+        <v>6.1658575895502395E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>8.1320378030808466E-2</v>
+        <v>7.8274670988456085E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>7.2404935349665148E-2</v>
+        <v>6.9693140018217012E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>6.8767985024548256E-2</v>
+        <v>6.6192405061082024E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>1.2173305173440058E-2</v>
+        <v>1.1717376140726947E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>5.2734480421219596E-3</v>
+        <v>5.0759406248140201E-3</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14681,43 +14681,43 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1387167216477333</v>
+        <v>0.13352133881448486</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.17585838707127766</v>
+        <v>0.16927193062666052</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.25283897370628089</v>
+        <v>0.2433693492228996</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.23393624806829469</v>
+        <v>0.22517459083727243</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.0742850688348725E-2</v>
+        <v>8.7344242048335671E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.9891278786477333E-2</v>
+        <v>8.6524564225186049E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.8040703444526858E-2</v>
+        <v>8.4743298821136334E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.0383710824150768E-2</v>
+        <v>8.6998553115381072E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.1708803260645704E-3</v>
+        <v>4.9772143962494185E-3</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-5.4377321745104505E-2</v>
+        <v>-5.2340717934426434E-2</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18667,7 +18667,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-2.57</v>
+        <v>-2.67</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18907,7 +18907,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>2.57</v>
+        <v>2.67</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19505,7 +19505,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>2.57</v>
+        <v>2.67</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19518,7 +19518,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.30305109613357195</v>
+        <v>0.28511828789831495</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/0639.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0639.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89408EFE-3140-4225-B237-7DD8C292473E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CA0707B-306A-405A-AC3A-CB245E23F14D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3885,29 +3885,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4381,13 +4381,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="356" t="s">
         <v>362</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="356"/>
+      <c r="D18" s="356"/>
+      <c r="E18" s="356"/>
+      <c r="F18" s="356"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4587,22 +4587,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="356" t="s">
         <v>363</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="356"/>
+      <c r="D36" s="356"/>
+      <c r="E36" s="356"/>
+      <c r="F36" s="356"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="361" t="s">
+      <c r="B37" s="358" t="s">
         <v>341</v>
       </c>
-      <c r="C37" s="361"/>
-      <c r="D37" s="361"/>
-      <c r="E37" s="361"/>
-      <c r="F37" s="361"/>
+      <c r="C37" s="358"/>
+      <c r="D37" s="358"/>
+      <c r="E37" s="358"/>
+      <c r="F37" s="358"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4614,13 +4614,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="357" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="357"/>
+      <c r="D40" s="357"/>
+      <c r="E40" s="357"/>
+      <c r="F40" s="357"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4640,13 +4640,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="357" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="357"/>
+      <c r="D43" s="357"/>
+      <c r="E43" s="357"/>
+      <c r="F43" s="357"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4675,13 +4675,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="357" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="357"/>
+      <c r="D47" s="357"/>
+      <c r="E47" s="357"/>
+      <c r="F47" s="357"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4697,13 +4697,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="357" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="357"/>
+      <c r="D50" s="357"/>
+      <c r="E50" s="357"/>
+      <c r="F50" s="357"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4767,13 +4767,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="357" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="357"/>
+      <c r="D58" s="357"/>
+      <c r="E58" s="357"/>
+      <c r="F58" s="357"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4789,7 +4789,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="357" t="s">
         <v>340</v>
       </c>
       <c r="C61" s="360"/>
@@ -4811,22 +4811,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="356" t="s">
         <v>345</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="356"/>
+      <c r="D64" s="356"/>
+      <c r="E64" s="356"/>
+      <c r="F64" s="356"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="356" t="s">
         <v>364</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="356"/>
+      <c r="D65" s="356"/>
+      <c r="E65" s="356"/>
+      <c r="F65" s="356"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4961,22 +4961,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="356" t="s">
         <v>365</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="356"/>
+      <c r="D80" s="356"/>
+      <c r="E80" s="356"/>
+      <c r="F80" s="356"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="361" t="s">
+      <c r="B81" s="358" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="361"/>
-      <c r="D81" s="361"/>
-      <c r="E81" s="361"/>
-      <c r="F81" s="361"/>
+      <c r="C81" s="358"/>
+      <c r="D81" s="358"/>
+      <c r="E81" s="358"/>
+      <c r="F81" s="358"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5020,22 +5020,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="356" t="s">
         <v>366</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="356"/>
+      <c r="D89" s="356"/>
+      <c r="E89" s="356"/>
+      <c r="F89" s="356"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="356" t="s">
         <v>367</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="356"/>
+      <c r="D90" s="356"/>
+      <c r="E90" s="356"/>
+      <c r="F90" s="356"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5072,13 +5072,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="356" t="s">
         <v>368</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="356"/>
+      <c r="D97" s="356"/>
+      <c r="E97" s="356"/>
+      <c r="F97" s="356"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5091,13 +5091,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="356" t="s">
         <v>346</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="356"/>
+      <c r="D101" s="356"/>
+      <c r="E101" s="356"/>
+      <c r="F101" s="356"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5219,13 +5219,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="356" t="s">
         <v>369</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="356"/>
+      <c r="D116" s="356"/>
+      <c r="E116" s="356"/>
+      <c r="F116" s="356"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5264,13 +5264,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="357" t="s">
         <v>370</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="357"/>
+      <c r="D123" s="357"/>
+      <c r="E123" s="357"/>
+      <c r="F123" s="357"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5413,13 +5413,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="362" t="s">
+      <c r="B134" s="361" t="s">
         <v>373</v>
       </c>
-      <c r="C134" s="362"/>
-      <c r="D134" s="362"/>
-      <c r="E134" s="362"/>
-      <c r="F134" s="362"/>
+      <c r="C134" s="361"/>
+      <c r="D134" s="361"/>
+      <c r="E134" s="361"/>
+      <c r="F134" s="361"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5432,22 +5432,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="363" t="s">
+      <c r="B138" s="359" t="s">
         <v>371</v>
       </c>
-      <c r="C138" s="363"/>
-      <c r="D138" s="363"/>
-      <c r="E138" s="363"/>
-      <c r="F138" s="363"/>
+      <c r="C138" s="359"/>
+      <c r="D138" s="359"/>
+      <c r="E138" s="359"/>
+      <c r="F138" s="359"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="356" t="s">
         <v>372</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="356"/>
+      <c r="D139" s="356"/>
+      <c r="E139" s="356"/>
+      <c r="F139" s="356"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5780,13 +5780,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="357" t="s">
+      <c r="B179" s="363" t="s">
         <v>379</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="356"/>
+      <c r="D179" s="356"/>
+      <c r="E179" s="356"/>
+      <c r="F179" s="356"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5823,13 +5823,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="357" t="s">
         <v>384</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="357"/>
+      <c r="D188" s="357"/>
+      <c r="E188" s="357"/>
+      <c r="F188" s="357"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5837,22 +5837,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="356" t="s">
+      <c r="B191" s="362" t="s">
         <v>385</v>
       </c>
-      <c r="C191" s="356"/>
-      <c r="D191" s="356"/>
-      <c r="E191" s="356"/>
-      <c r="F191" s="356"/>
+      <c r="C191" s="362"/>
+      <c r="D191" s="362"/>
+      <c r="E191" s="362"/>
+      <c r="F191" s="362"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="356" t="s">
+      <c r="B192" s="362" t="s">
         <v>386</v>
       </c>
-      <c r="C192" s="356"/>
-      <c r="D192" s="356"/>
-      <c r="E192" s="356"/>
-      <c r="F192" s="356"/>
+      <c r="C192" s="362"/>
+      <c r="D192" s="362"/>
+      <c r="E192" s="362"/>
+      <c r="F192" s="362"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5876,6 +5876,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5892,17 +5903,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">

--- a/financial_models/opportunities/0639.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0639.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CA0707B-306A-405A-AC3A-CB245E23F14D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53D84F46-08D8-4DB2-A89F-D5C5A5BDB23C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3885,29 +3885,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4323,7 +4323,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4344,7 +4344,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>13593.145605899999</v>
+        <v>13644.0562636</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4381,13 +4381,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="356" t="s">
+      <c r="B18" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C18" s="356"/>
-      <c r="D18" s="356"/>
-      <c r="E18" s="356"/>
-      <c r="F18" s="356"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4470,7 +4470,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.28511828789831495</v>
+        <v>0.28337714642224543</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4587,22 +4587,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="356" t="s">
+      <c r="B36" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C36" s="356"/>
-      <c r="D36" s="356"/>
-      <c r="E36" s="356"/>
-      <c r="F36" s="356"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="358" t="s">
+      <c r="B37" s="361" t="s">
         <v>341</v>
       </c>
-      <c r="C37" s="358"/>
-      <c r="D37" s="358"/>
-      <c r="E37" s="358"/>
-      <c r="F37" s="358"/>
+      <c r="C37" s="361"/>
+      <c r="D37" s="361"/>
+      <c r="E37" s="361"/>
+      <c r="F37" s="361"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4614,13 +4614,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="357" t="s">
+      <c r="B40" s="359" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="357"/>
-      <c r="D40" s="357"/>
-      <c r="E40" s="357"/>
-      <c r="F40" s="357"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4640,13 +4640,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="357" t="s">
+      <c r="B43" s="359" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="357"/>
-      <c r="D43" s="357"/>
-      <c r="E43" s="357"/>
-      <c r="F43" s="357"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4675,13 +4675,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="357" t="s">
+      <c r="B47" s="359" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="357"/>
-      <c r="D47" s="357"/>
-      <c r="E47" s="357"/>
-      <c r="F47" s="357"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4697,13 +4697,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="357" t="s">
+      <c r="B50" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="357"/>
-      <c r="D50" s="357"/>
-      <c r="E50" s="357"/>
-      <c r="F50" s="357"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4767,13 +4767,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="357" t="s">
+      <c r="B58" s="359" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="357"/>
-      <c r="D58" s="357"/>
-      <c r="E58" s="357"/>
-      <c r="F58" s="357"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4789,7 +4789,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="357" t="s">
+      <c r="B61" s="359" t="s">
         <v>340</v>
       </c>
       <c r="C61" s="360"/>
@@ -4811,22 +4811,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="356" t="s">
+      <c r="B64" s="358" t="s">
         <v>345</v>
       </c>
-      <c r="C64" s="356"/>
-      <c r="D64" s="356"/>
-      <c r="E64" s="356"/>
-      <c r="F64" s="356"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="356" t="s">
+      <c r="B65" s="358" t="s">
         <v>364</v>
       </c>
-      <c r="C65" s="356"/>
-      <c r="D65" s="356"/>
-      <c r="E65" s="356"/>
-      <c r="F65" s="356"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4860,7 +4860,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>8.0321913984971002E-2</v>
+        <v>8.0022205350698719E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4870,7 +4870,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>0.11235955056179775</v>
+        <v>0.11194029850746268</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>450</v>
@@ -4961,22 +4961,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="356" t="s">
+      <c r="B80" s="358" t="s">
         <v>365</v>
       </c>
-      <c r="C80" s="356"/>
-      <c r="D80" s="356"/>
-      <c r="E80" s="356"/>
-      <c r="F80" s="356"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="358" t="s">
+      <c r="B81" s="361" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="358"/>
-      <c r="D81" s="358"/>
-      <c r="E81" s="358"/>
-      <c r="F81" s="358"/>
+      <c r="C81" s="361"/>
+      <c r="D81" s="361"/>
+      <c r="E81" s="361"/>
+      <c r="F81" s="361"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5020,22 +5020,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="356" t="s">
+      <c r="B89" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C89" s="356"/>
-      <c r="D89" s="356"/>
-      <c r="E89" s="356"/>
-      <c r="F89" s="356"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="356" t="s">
+      <c r="B90" s="358" t="s">
         <v>367</v>
       </c>
-      <c r="C90" s="356"/>
-      <c r="D90" s="356"/>
-      <c r="E90" s="356"/>
-      <c r="F90" s="356"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5072,13 +5072,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="356" t="s">
+      <c r="B97" s="358" t="s">
         <v>368</v>
       </c>
-      <c r="C97" s="356"/>
-      <c r="D97" s="356"/>
-      <c r="E97" s="356"/>
-      <c r="F97" s="356"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5091,13 +5091,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="356" t="s">
+      <c r="B101" s="358" t="s">
         <v>346</v>
       </c>
-      <c r="C101" s="356"/>
-      <c r="D101" s="356"/>
-      <c r="E101" s="356"/>
-      <c r="F101" s="356"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5219,13 +5219,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="356" t="s">
+      <c r="B116" s="358" t="s">
         <v>369</v>
       </c>
-      <c r="C116" s="356"/>
-      <c r="D116" s="356"/>
-      <c r="E116" s="356"/>
-      <c r="F116" s="356"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5264,13 +5264,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="357" t="s">
+      <c r="B123" s="359" t="s">
         <v>370</v>
       </c>
-      <c r="C123" s="357"/>
-      <c r="D123" s="357"/>
-      <c r="E123" s="357"/>
-      <c r="F123" s="357"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5413,13 +5413,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="361" t="s">
+      <c r="B134" s="362" t="s">
         <v>373</v>
       </c>
-      <c r="C134" s="361"/>
-      <c r="D134" s="361"/>
-      <c r="E134" s="361"/>
-      <c r="F134" s="361"/>
+      <c r="C134" s="362"/>
+      <c r="D134" s="362"/>
+      <c r="E134" s="362"/>
+      <c r="F134" s="362"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5432,22 +5432,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="359" t="s">
+      <c r="B138" s="363" t="s">
         <v>371</v>
       </c>
-      <c r="C138" s="359"/>
-      <c r="D138" s="359"/>
-      <c r="E138" s="359"/>
-      <c r="F138" s="359"/>
+      <c r="C138" s="363"/>
+      <c r="D138" s="363"/>
+      <c r="E138" s="363"/>
+      <c r="F138" s="363"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="356" t="s">
+      <c r="B139" s="358" t="s">
         <v>372</v>
       </c>
-      <c r="C139" s="356"/>
-      <c r="D139" s="356"/>
-      <c r="E139" s="356"/>
-      <c r="F139" s="356"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5780,13 +5780,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="363" t="s">
+      <c r="B179" s="357" t="s">
         <v>379</v>
       </c>
-      <c r="C179" s="356"/>
-      <c r="D179" s="356"/>
-      <c r="E179" s="356"/>
-      <c r="F179" s="356"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5823,13 +5823,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="357" t="s">
+      <c r="B188" s="359" t="s">
         <v>384</v>
       </c>
-      <c r="C188" s="357"/>
-      <c r="D188" s="357"/>
-      <c r="E188" s="357"/>
-      <c r="F188" s="357"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5837,22 +5837,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="362" t="s">
+      <c r="B191" s="356" t="s">
         <v>385</v>
       </c>
-      <c r="C191" s="362"/>
-      <c r="D191" s="362"/>
-      <c r="E191" s="362"/>
-      <c r="F191" s="362"/>
+      <c r="C191" s="356"/>
+      <c r="D191" s="356"/>
+      <c r="E191" s="356"/>
+      <c r="F191" s="356"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="362" t="s">
+      <c r="B192" s="356" t="s">
         <v>386</v>
       </c>
-      <c r="C192" s="362"/>
-      <c r="D192" s="362"/>
-      <c r="E192" s="362"/>
-      <c r="F192" s="362"/>
+      <c r="C192" s="356"/>
+      <c r="D192" s="356"/>
+      <c r="E192" s="356"/>
+      <c r="F192" s="356"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5876,17 +5876,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5903,6 +5892,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13425,20 +13425,20 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>0.11235955056179775</v>
+        <v>0.11194029850746268</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>0.11235955056179775</v>
+        <v>0.11194029850746268</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>0.10486891385767791</v>
+        <v>0.10447761194029852</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>0.16104868913857681</v>
+        <v>0.16044776119402987</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
@@ -14624,50 +14624,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>8.0321913984971002E-2</v>
+        <v>8.0022205350698719E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>9.372998910351929E-2</v>
+        <v>9.338025033820764E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.12897829893306861</v>
+        <v>0.12849703662361686</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.20917660901146684</v>
+        <v>0.20839609927634939</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.17187139704312737</v>
+        <v>0.17123008586013061</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>6.1658575895502395E-2</v>
+        <v>6.1428506582459463E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>7.8274670988456085E-2</v>
+        <v>7.7982601320588707E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>6.9693140018217012E-2</v>
+        <v>6.9433090988298279E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>6.6192405061082024E-2</v>
+        <v>6.5945418475033199E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>1.1717376140726947E-2</v>
+        <v>1.167365458796304E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>5.0759406248140201E-3</v>
+        <v>5.0570005478557589E-3</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14681,43 +14681,43 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13352133881448486</v>
+        <v>0.13302312486368453</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16927193062666052</v>
+        <v>0.16864031894521775</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.2433693492228996</v>
+        <v>0.24246125463624696</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.22517459083727243</v>
+        <v>0.22433438714011841</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.7344242048335671E-2</v>
+        <v>8.7018330697409038E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.6524564225186049E-2</v>
+        <v>8.6201711373599527E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.4743298821136334E-2</v>
+        <v>8.4427092482251498E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.6998553115381072E-2</v>
+        <v>8.667393164853264E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.9772143962494185E-3</v>
+        <v>4.9586427007410243E-3</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-5.2340717934426434E-2</v>
+        <v>-5.2145416748103947E-2</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18667,7 +18667,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-2.67</v>
+        <v>-2.68</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18907,7 +18907,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19505,7 +19505,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19518,7 +19518,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.28511828789831495</v>
+        <v>0.28337714642224543</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/0639.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0639.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53D84F46-08D8-4DB2-A89F-D5C5A5BDB23C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA655E47-AEF5-4021-A234-A32E9BFF4FA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3885,29 +3885,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4323,7 +4323,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4344,7 +4344,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>13644.0562636</v>
+        <v>13694.9669213</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4381,13 +4381,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="356" t="s">
         <v>362</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="356"/>
+      <c r="D18" s="356"/>
+      <c r="E18" s="356"/>
+      <c r="F18" s="356"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4470,7 +4470,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.28337714642224543</v>
+        <v>0.28164513964422611</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4587,22 +4587,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="356" t="s">
         <v>363</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="356"/>
+      <c r="D36" s="356"/>
+      <c r="E36" s="356"/>
+      <c r="F36" s="356"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="361" t="s">
+      <c r="B37" s="358" t="s">
         <v>341</v>
       </c>
-      <c r="C37" s="361"/>
-      <c r="D37" s="361"/>
-      <c r="E37" s="361"/>
-      <c r="F37" s="361"/>
+      <c r="C37" s="358"/>
+      <c r="D37" s="358"/>
+      <c r="E37" s="358"/>
+      <c r="F37" s="358"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4614,13 +4614,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="357" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="357"/>
+      <c r="D40" s="357"/>
+      <c r="E40" s="357"/>
+      <c r="F40" s="357"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4640,13 +4640,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="357" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="357"/>
+      <c r="D43" s="357"/>
+      <c r="E43" s="357"/>
+      <c r="F43" s="357"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4675,13 +4675,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="357" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="357"/>
+      <c r="D47" s="357"/>
+      <c r="E47" s="357"/>
+      <c r="F47" s="357"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4697,13 +4697,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="357" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="357"/>
+      <c r="D50" s="357"/>
+      <c r="E50" s="357"/>
+      <c r="F50" s="357"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4767,13 +4767,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="357" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="357"/>
+      <c r="D58" s="357"/>
+      <c r="E58" s="357"/>
+      <c r="F58" s="357"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4789,7 +4789,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="357" t="s">
         <v>340</v>
       </c>
       <c r="C61" s="360"/>
@@ -4811,22 +4811,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="356" t="s">
         <v>345</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="356"/>
+      <c r="D64" s="356"/>
+      <c r="E64" s="356"/>
+      <c r="F64" s="356"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="356" t="s">
         <v>364</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="356"/>
+      <c r="D65" s="356"/>
+      <c r="E65" s="356"/>
+      <c r="F65" s="356"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4860,7 +4860,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>8.0022205350698719E-2</v>
+        <v>7.9724725033409882E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4870,7 +4870,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>0.11194029850746268</v>
+        <v>0.11152416356877323</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>450</v>
@@ -4961,22 +4961,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="356" t="s">
         <v>365</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="356"/>
+      <c r="D80" s="356"/>
+      <c r="E80" s="356"/>
+      <c r="F80" s="356"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="361" t="s">
+      <c r="B81" s="358" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="361"/>
-      <c r="D81" s="361"/>
-      <c r="E81" s="361"/>
-      <c r="F81" s="361"/>
+      <c r="C81" s="358"/>
+      <c r="D81" s="358"/>
+      <c r="E81" s="358"/>
+      <c r="F81" s="358"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5020,22 +5020,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="356" t="s">
         <v>366</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="356"/>
+      <c r="D89" s="356"/>
+      <c r="E89" s="356"/>
+      <c r="F89" s="356"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="356" t="s">
         <v>367</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="356"/>
+      <c r="D90" s="356"/>
+      <c r="E90" s="356"/>
+      <c r="F90" s="356"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5072,13 +5072,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="356" t="s">
         <v>368</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="356"/>
+      <c r="D97" s="356"/>
+      <c r="E97" s="356"/>
+      <c r="F97" s="356"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5091,13 +5091,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="356" t="s">
         <v>346</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="356"/>
+      <c r="D101" s="356"/>
+      <c r="E101" s="356"/>
+      <c r="F101" s="356"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5219,13 +5219,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="356" t="s">
         <v>369</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="356"/>
+      <c r="D116" s="356"/>
+      <c r="E116" s="356"/>
+      <c r="F116" s="356"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5264,13 +5264,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="357" t="s">
         <v>370</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="357"/>
+      <c r="D123" s="357"/>
+      <c r="E123" s="357"/>
+      <c r="F123" s="357"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5413,13 +5413,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="362" t="s">
+      <c r="B134" s="361" t="s">
         <v>373</v>
       </c>
-      <c r="C134" s="362"/>
-      <c r="D134" s="362"/>
-      <c r="E134" s="362"/>
-      <c r="F134" s="362"/>
+      <c r="C134" s="361"/>
+      <c r="D134" s="361"/>
+      <c r="E134" s="361"/>
+      <c r="F134" s="361"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5432,22 +5432,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="363" t="s">
+      <c r="B138" s="359" t="s">
         <v>371</v>
       </c>
-      <c r="C138" s="363"/>
-      <c r="D138" s="363"/>
-      <c r="E138" s="363"/>
-      <c r="F138" s="363"/>
+      <c r="C138" s="359"/>
+      <c r="D138" s="359"/>
+      <c r="E138" s="359"/>
+      <c r="F138" s="359"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="356" t="s">
         <v>372</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="356"/>
+      <c r="D139" s="356"/>
+      <c r="E139" s="356"/>
+      <c r="F139" s="356"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5780,13 +5780,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="357" t="s">
+      <c r="B179" s="363" t="s">
         <v>379</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="356"/>
+      <c r="D179" s="356"/>
+      <c r="E179" s="356"/>
+      <c r="F179" s="356"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5823,13 +5823,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="357" t="s">
         <v>384</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="357"/>
+      <c r="D188" s="357"/>
+      <c r="E188" s="357"/>
+      <c r="F188" s="357"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5837,22 +5837,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="356" t="s">
+      <c r="B191" s="362" t="s">
         <v>385</v>
       </c>
-      <c r="C191" s="356"/>
-      <c r="D191" s="356"/>
-      <c r="E191" s="356"/>
-      <c r="F191" s="356"/>
+      <c r="C191" s="362"/>
+      <c r="D191" s="362"/>
+      <c r="E191" s="362"/>
+      <c r="F191" s="362"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="356" t="s">
+      <c r="B192" s="362" t="s">
         <v>386</v>
       </c>
-      <c r="C192" s="356"/>
-      <c r="D192" s="356"/>
-      <c r="E192" s="356"/>
-      <c r="F192" s="356"/>
+      <c r="C192" s="362"/>
+      <c r="D192" s="362"/>
+      <c r="E192" s="362"/>
+      <c r="F192" s="362"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5876,6 +5876,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5892,17 +5903,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13425,20 +13425,20 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>0.11194029850746268</v>
+        <v>0.11152416356877323</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>0.11194029850746268</v>
+        <v>0.11152416356877323</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>0.10447761194029852</v>
+        <v>0.10408921933085503</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>0.16044776119402987</v>
+        <v>0.15985130111524165</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
@@ -14624,50 +14624,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>8.0022205350698719E-2</v>
+        <v>7.9724725033409882E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>9.338025033820764E-2</v>
+        <v>9.3033111861113932E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.12849703662361686</v>
+        <v>0.12801935247259968</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.20839609927634939</v>
+        <v>0.20762139258758974</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.17123008586013061</v>
+        <v>0.17059354279001862</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>6.1428506582459463E-2</v>
+        <v>6.1200147821929882E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>7.7982601320588707E-2</v>
+        <v>7.7692703174415526E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>6.9433090988298279E-2</v>
+        <v>6.9174975408416134E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>6.5945418475033199E-2</v>
+        <v>6.5700268220479183E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>1.167365458796304E-2</v>
+        <v>1.1630258102505928E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>5.0570005478557589E-3</v>
+        <v>5.0382012893135444E-3</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14681,43 +14681,43 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13302312486368453</v>
+        <v>0.13252861510582697</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16864031894521775</v>
+        <v>0.16801340326140654</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.24246125463624696</v>
+        <v>0.24155991168220889</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.22433438714011841</v>
+        <v>0.22350043031060127</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.7018330697409038E-2</v>
+        <v>8.669484247920306E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.6201711373599527E-2</v>
+        <v>8.5881258914961622E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.4427092482251498E-2</v>
+        <v>8.4113237119863946E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.667393164853264E-2</v>
+        <v>8.6351723724188659E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.9586427007410243E-3</v>
+        <v>4.9402090847531404E-3</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-5.2145416748103947E-2</v>
+        <v>-5.1951567615211372E-2</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18667,7 +18667,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-2.68</v>
+        <v>-2.69</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18907,7 +18907,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19505,7 +19505,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19518,7 +19518,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.28337714642224543</v>
+        <v>0.28164513964422611</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/0639.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0639.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA655E47-AEF5-4021-A234-A32E9BFF4FA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{812DB708-1E1C-44F1-B0B3-FA7634261AE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -25,6 +25,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">DCF!$B$73:$H$73</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">DDM!$B$68:$H$68</definedName>
     <definedName name="Common_Shares">Thesis!$C$6</definedName>
+    <definedName name="dividend_tax_rate">Normalized_FCF!$C$93</definedName>
     <definedName name="Equity_Cost">Thesis!$C$86</definedName>
     <definedName name="Exchange_Rate">Thesis!$C$16</definedName>
     <definedName name="Market_currency">Thesis!$C$13</definedName>
@@ -47,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="684" uniqueCount="462">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="686" uniqueCount="465">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -465,10 +466,6 @@
   <si>
     <t>PV of FCFE</t>
     <phoneticPr fontId="28" type="noConversion"/>
-  </si>
-  <si>
-    <t>Annual Dividend per share</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>HGP</t>
@@ -1401,10 +1398,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Y</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Asset Play</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1501,14 +1494,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Dividend/Market Cap =</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Dividend Yield</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Note of the formulas:</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1550,10 +1535,6 @@
   </si>
   <si>
     <t>Operating Cash Requirement</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>N</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1761,10 +1742,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Historical Average or D&amp;A</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Step 1: Establishing the Company’s Sustainable Earning Power (Calculating Normalized FCFE)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2457,16 +2434,43 @@
     <t>LT AR and Prepayments</t>
   </si>
   <si>
+    <t>Dividend after tax Yield</t>
+  </si>
+  <si>
+    <t>Dividend tax rate</t>
+  </si>
+  <si>
+    <t>After tax Dividend/Market Cap =</t>
+  </si>
+  <si>
+    <t>After-tax Dividend per share</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>首钢资源</t>
+  </si>
+  <si>
     <t>0639.HK</t>
   </si>
   <si>
-    <t>首钢资源</t>
+    <t/>
+  </si>
+  <si>
+    <t>MAT_01</t>
+  </si>
+  <si>
+    <t>N</t>
   </si>
   <si>
     <t>DCF</t>
   </si>
   <si>
-    <t>MAT_01</t>
+    <t>Latest Asset Value</t>
+  </si>
+  <si>
+    <t>Historical Average or D&amp;A</t>
   </si>
 </sst>
 </file>
@@ -3140,7 +3144,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="368">
+  <cellXfs count="370">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3885,29 +3889,33 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4229,18 +4237,18 @@
         <v>45807</v>
       </c>
       <c r="D1" s="316" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="E1" s="292" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="F1" s="254" t="s">
-        <v>284</v>
+        <v>456</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
       <c r="A2" s="222" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B2" s="36"/>
       <c r="C2" s="36"/>
@@ -4254,7 +4262,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="B4" s="45" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="C4" s="46"/>
       <c r="D4" s="5"/>
@@ -4263,10 +4271,10 @@
     </row>
     <row r="5" spans="1:10" ht="12.4">
       <c r="B5" s="4" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="C5" s="294" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4280,7 +4288,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="B7" s="2" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C7" s="250">
         <v>6</v>
@@ -4290,7 +4298,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="B8" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C8" s="33">
         <f>EOMONTH(EDATE(BS!C1,C7+2),0)</f>
@@ -4303,19 +4311,21 @@
     </row>
     <row r="10" spans="1:10">
       <c r="B10" s="45" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="C10" s="46"/>
       <c r="E10" s="34"/>
     </row>
     <row r="11" spans="1:10">
       <c r="B11" s="1" t="s">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="C11" s="49" t="s">
         <v>458</v>
       </c>
-      <c r="D11" s="49"/>
+      <c r="D11" s="49" t="s">
+        <v>459</v>
+      </c>
       <c r="E11" s="34"/>
     </row>
     <row r="12" spans="1:10">
@@ -4330,17 +4340,17 @@
     </row>
     <row r="13" spans="1:10">
       <c r="B13" s="1" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="C13" s="48" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="D13" s="48"/>
       <c r="E13" s="5"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="4" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
@@ -4354,7 +4364,7 @@
     </row>
     <row r="15" spans="1:10">
       <c r="B15" s="4" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="C15" s="32" t="str">
         <f>IF(C25=C13,C13,C25&amp;"/"&amp;C13)</f>
@@ -4381,34 +4391,34 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="356" t="s">
-        <v>362</v>
-      </c>
-      <c r="C18" s="356"/>
-      <c r="D18" s="356"/>
-      <c r="E18" s="356"/>
-      <c r="F18" s="356"/>
+      <c r="B18" s="360" t="s">
+        <v>356</v>
+      </c>
+      <c r="C18" s="360"/>
+      <c r="D18" s="360"/>
+      <c r="E18" s="360"/>
+      <c r="F18" s="360"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C20" s="46"/>
       <c r="D20" s="5"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="2" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="C21" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
         <v xml:space="preserve">Low Growth </v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>441</v>
+        <v>435</v>
       </c>
       <c r="E21" s="308" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="22" spans="2:6">
@@ -4416,7 +4426,7 @@
         <v>56</v>
       </c>
       <c r="C22" s="48" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D22" s="1" t="str">
         <f>IF(valuation_method="DDM","DDM Terminal Value","")</f>
@@ -4426,26 +4436,26 @@
     </row>
     <row r="23" spans="2:6">
       <c r="B23" s="1" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="C23" s="262" t="s">
-        <v>322</v>
+        <v>461</v>
       </c>
     </row>
     <row r="24" spans="2:6">
       <c r="B24" s="1" t="s">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="C24" s="262" t="s">
-        <v>322</v>
+        <v>461</v>
       </c>
     </row>
     <row r="25" spans="2:6">
       <c r="B25" s="4" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="C25" s="48" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="D25" s="32" t="str">
         <f>IF(D11="","",Market_currency&amp;"/"&amp;D13&amp;":")</f>
@@ -4466,11 +4476,11 @@
         <v>4.4858408799140586</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.28164513964422611</v>
+        <v>0.27199281553693067</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4479,7 +4489,7 @@
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="45" t="s">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="C28" s="309" t="str">
         <f>C145&amp;" ("&amp;Market_currency&amp;")"</f>
@@ -4490,7 +4500,7 @@
         <v/>
       </c>
       <c r="E28" s="305" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="F28" s="303">
         <v>3</v>
@@ -4498,18 +4508,18 @@
     </row>
     <row r="29" spans="2:6">
       <c r="B29" s="1" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="C29" s="310">
         <f>C149</f>
-        <v>2.2516930066250125</v>
+        <v>2.2019752270440667</v>
       </c>
       <c r="D29" s="310" t="str">
         <f>D149</f>
         <v/>
       </c>
       <c r="E29" s="306" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="F29" s="302">
         <v>0.3674</v>
@@ -4517,18 +4527,18 @@
     </row>
     <row r="30" spans="2:6">
       <c r="B30" s="1" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="C30" s="311">
         <f>C157</f>
-        <v>3.101365529948271</v>
+        <v>3.039853505232323</v>
       </c>
       <c r="D30" s="311" t="str">
         <f>D157</f>
         <v/>
       </c>
       <c r="E30" s="307" t="s">
-        <v>439</v>
+        <v>433</v>
       </c>
       <c r="F30" s="312">
         <v>0.21740000000000001</v>
@@ -4536,18 +4546,18 @@
     </row>
     <row r="31" spans="2:6">
       <c r="B31" s="1" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="C31" s="311">
         <f>C165</f>
-        <v>4.3910827513866675</v>
+        <v>4.3130669791905083</v>
       </c>
       <c r="D31" s="311" t="str">
         <f>D165</f>
         <v/>
       </c>
       <c r="E31" s="307" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="F31" s="312">
         <v>7.4999999999999997E-2</v>
@@ -4555,18 +4565,18 @@
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="1" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="C32" s="311">
         <f>C173</f>
-        <v>3.939054009870663</v>
+        <v>3.8666759160925035</v>
       </c>
       <c r="D32" s="311" t="str">
         <f>D173</f>
         <v/>
       </c>
       <c r="E32" s="307" t="s">
-        <v>440</v>
+        <v>434</v>
       </c>
       <c r="F32" s="312">
         <v>0.1174</v>
@@ -4578,7 +4588,7 @@
     </row>
     <row r="34" spans="1:6" ht="13.9">
       <c r="A34" s="222" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="B34" s="36"/>
       <c r="C34" s="36"/>
@@ -4587,26 +4597,26 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="356" t="s">
-        <v>363</v>
-      </c>
-      <c r="C36" s="356"/>
-      <c r="D36" s="356"/>
-      <c r="E36" s="356"/>
-      <c r="F36" s="356"/>
+      <c r="B36" s="360" t="s">
+        <v>357</v>
+      </c>
+      <c r="C36" s="360"/>
+      <c r="D36" s="360"/>
+      <c r="E36" s="360"/>
+      <c r="F36" s="360"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="358" t="s">
-        <v>341</v>
-      </c>
-      <c r="C37" s="358"/>
-      <c r="D37" s="358"/>
-      <c r="E37" s="358"/>
-      <c r="F37" s="358"/>
+      <c r="B37" s="363" t="s">
+        <v>336</v>
+      </c>
+      <c r="C37" s="363"/>
+      <c r="D37" s="363"/>
+      <c r="E37" s="363"/>
+      <c r="F37" s="363"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C39" s="108">
         <f>scaling_factor</f>
@@ -4614,17 +4624,17 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="357" t="s">
-        <v>231</v>
-      </c>
-      <c r="C40" s="357"/>
-      <c r="D40" s="357"/>
-      <c r="E40" s="357"/>
-      <c r="F40" s="357"/>
+      <c r="B40" s="361" t="s">
+        <v>230</v>
+      </c>
+      <c r="C40" s="361"/>
+      <c r="D40" s="361"/>
+      <c r="E40" s="361"/>
+      <c r="F40" s="361"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C41" s="349">
         <f>Normalized_FCF!C8</f>
@@ -4640,17 +4650,17 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="357" t="s">
-        <v>233</v>
-      </c>
-      <c r="C43" s="357"/>
-      <c r="D43" s="357"/>
-      <c r="E43" s="357"/>
-      <c r="F43" s="357"/>
+      <c r="B43" s="361" t="s">
+        <v>232</v>
+      </c>
+      <c r="C43" s="361"/>
+      <c r="D43" s="361"/>
+      <c r="E43" s="361"/>
+      <c r="F43" s="361"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C44" s="349">
         <f>Normalized_FCF!C9</f>
@@ -4663,7 +4673,7 @@
     </row>
     <row r="45" spans="1:6">
       <c r="B45" s="52" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C45" s="349">
         <f>Normalized_FCF!C10</f>
@@ -4675,17 +4685,17 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="357" t="s">
-        <v>236</v>
-      </c>
-      <c r="C47" s="357"/>
-      <c r="D47" s="357"/>
-      <c r="E47" s="357"/>
-      <c r="F47" s="357"/>
+      <c r="B47" s="361" t="s">
+        <v>235</v>
+      </c>
+      <c r="C47" s="361"/>
+      <c r="D47" s="361"/>
+      <c r="E47" s="361"/>
+      <c r="F47" s="361"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C48" s="349">
         <f>Normalized_FCF!C11</f>
@@ -4697,17 +4707,17 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="357" t="s">
-        <v>240</v>
-      </c>
-      <c r="C50" s="357"/>
-      <c r="D50" s="357"/>
-      <c r="E50" s="357"/>
-      <c r="F50" s="357"/>
+      <c r="B50" s="361" t="s">
+        <v>239</v>
+      </c>
+      <c r="C50" s="361"/>
+      <c r="D50" s="361"/>
+      <c r="E50" s="361"/>
+      <c r="F50" s="361"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="C51" s="350">
         <f>Normalized_FCF!C48</f>
@@ -4722,7 +4732,7 @@
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="47" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="C52" s="350">
         <f>Normalized_FCF!C47</f>
@@ -4737,7 +4747,7 @@
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C53" s="349">
         <f>Normalized_FCF!C12</f>
@@ -4750,12 +4760,12 @@
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="47" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C56" s="349">
         <f>Normalized_FCF!C15</f>
@@ -4767,17 +4777,17 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="357" t="s">
-        <v>241</v>
-      </c>
-      <c r="C58" s="357"/>
-      <c r="D58" s="357"/>
-      <c r="E58" s="357"/>
-      <c r="F58" s="357"/>
+      <c r="B58" s="361" t="s">
+        <v>240</v>
+      </c>
+      <c r="C58" s="361"/>
+      <c r="D58" s="361"/>
+      <c r="E58" s="361"/>
+      <c r="F58" s="361"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C59" s="349">
         <f>Normalized_FCF!C14</f>
@@ -4789,17 +4799,17 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="357" t="s">
-        <v>340</v>
-      </c>
-      <c r="C61" s="360"/>
-      <c r="D61" s="360"/>
-      <c r="E61" s="360"/>
-      <c r="F61" s="360"/>
+      <c r="B61" s="361" t="s">
+        <v>335</v>
+      </c>
+      <c r="C61" s="362"/>
+      <c r="D61" s="362"/>
+      <c r="E61" s="362"/>
+      <c r="F61" s="362"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C62" s="349">
         <f>Normalized_FCF!C17</f>
@@ -4811,26 +4821,26 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="356" t="s">
-        <v>345</v>
-      </c>
-      <c r="C64" s="356"/>
-      <c r="D64" s="356"/>
-      <c r="E64" s="356"/>
-      <c r="F64" s="356"/>
+      <c r="B64" s="360" t="s">
+        <v>340</v>
+      </c>
+      <c r="C64" s="360"/>
+      <c r="D64" s="360"/>
+      <c r="E64" s="360"/>
+      <c r="F64" s="360"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="356" t="s">
-        <v>364</v>
-      </c>
-      <c r="C65" s="356"/>
-      <c r="D65" s="356"/>
-      <c r="E65" s="356"/>
-      <c r="F65" s="356"/>
+      <c r="B65" s="360" t="s">
+        <v>358</v>
+      </c>
+      <c r="C65" s="360"/>
+      <c r="D65" s="360"/>
+      <c r="E65" s="360"/>
+      <c r="F65" s="360"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C67" s="349">
         <f>Normalized_FCF!G19</f>
@@ -4843,7 +4853,7 @@
     </row>
     <row r="68" spans="1:6">
       <c r="B68" s="47" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C68" s="349">
         <f>Normalized_FCF!C19</f>
@@ -4856,24 +4866,24 @@
     </row>
     <row r="69" spans="1:6">
       <c r="B69" s="227" t="s">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="C69" s="92">
-        <f>Normalized_FCF!C125</f>
+        <f>Normalized_FCF!C126</f>
         <v>7.9724725033409882E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
     <row r="70" spans="1:6">
       <c r="B70" s="227" t="s">
-        <v>309</v>
+        <v>454</v>
       </c>
       <c r="C70" s="92">
-        <f>Normalized_FCF!C93</f>
-        <v>0.11152416356877323</v>
+        <f>Normalized_FCF!C94</f>
+        <v>0.10037174721189591</v>
       </c>
       <c r="E70" s="47" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="F70" s="315">
         <f>Normalized_FCF!C92</f>
@@ -4882,73 +4892,73 @@
     </row>
     <row r="72" spans="1:6">
       <c r="B72" s="210" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="C72" s="323" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D72" s="323" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
     </row>
     <row r="73" spans="1:6">
       <c r="B73" s="47" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="C73" s="92">
-        <f>Normalized_FCF!C120</f>
+        <f>Normalized_FCF!C121</f>
         <v>0.10048924474005361</v>
       </c>
       <c r="D73" s="92">
-        <f>Normalized_FCF!G120</f>
+        <f>Normalized_FCF!G121</f>
         <v>0.12199804433766272</v>
       </c>
     </row>
     <row r="74" spans="1:6">
       <c r="B74" s="259" t="str">
-        <f>Normalized_FCF!B117</f>
+        <f>Normalized_FCF!B118</f>
         <v>Pre-tax Profit/Sales</v>
       </c>
       <c r="C74" s="322">
-        <f>Normalized_FCF!C117</f>
+        <f>Normalized_FCF!C118</f>
         <v>0.42143224397986156</v>
       </c>
       <c r="D74" s="322">
-        <f>Normalized_FCF!G117</f>
+        <f>Normalized_FCF!G118</f>
         <v>0.45598504835348186</v>
       </c>
     </row>
     <row r="75" spans="1:6">
       <c r="B75" s="259" t="str">
-        <f>Normalized_FCF!B118</f>
+        <f>Normalized_FCF!B119</f>
         <v>Sales/Total Assets</v>
       </c>
       <c r="C75" s="324">
-        <f>Normalized_FCF!C118</f>
+        <f>Normalized_FCF!C119</f>
         <v>0.19639123104483397</v>
       </c>
       <c r="D75" s="324">
-        <f>Normalized_FCF!G118</f>
+        <f>Normalized_FCF!G119</f>
         <v>0.22035988512352028</v>
       </c>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="259" t="str">
-        <f>Normalized_FCF!B119</f>
+        <f>Normalized_FCF!B120</f>
         <v>Total Assets/Equity</v>
       </c>
       <c r="C76" s="324">
-        <f>Normalized_FCF!C119</f>
+        <f>Normalized_FCF!C120</f>
         <v>1.2141426890285656</v>
       </c>
       <c r="D76" s="324">
-        <f>Normalized_FCF!G119</f>
+        <f>Normalized_FCF!G120</f>
         <v>1.2141426890285656</v>
       </c>
     </row>
     <row r="78" spans="1:6" ht="13.9">
       <c r="A78" s="222" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="B78" s="36"/>
       <c r="C78" s="36"/>
@@ -4961,31 +4971,31 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="356" t="s">
-        <v>365</v>
-      </c>
-      <c r="C80" s="356"/>
-      <c r="D80" s="356"/>
-      <c r="E80" s="356"/>
-      <c r="F80" s="356"/>
+      <c r="B80" s="360" t="s">
+        <v>359</v>
+      </c>
+      <c r="C80" s="360"/>
+      <c r="D80" s="360"/>
+      <c r="E80" s="360"/>
+      <c r="F80" s="360"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="358" t="s">
-        <v>252</v>
-      </c>
-      <c r="C81" s="358"/>
-      <c r="D81" s="358"/>
-      <c r="E81" s="358"/>
-      <c r="F81" s="358"/>
+      <c r="B81" s="363" t="s">
+        <v>251</v>
+      </c>
+      <c r="C81" s="363"/>
+      <c r="D81" s="363"/>
+      <c r="E81" s="363"/>
+      <c r="F81" s="363"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="84" spans="1:6">
       <c r="B84" s="1" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="C84" s="92">
         <f>F31</f>
@@ -4994,7 +5004,7 @@
     </row>
     <row r="85" spans="1:6">
       <c r="B85" s="1" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="C85" s="92">
         <f>IF(C23="Y",1%,0)+IF(C24="Y",1%,0)</f>
@@ -5003,7 +5013,7 @@
     </row>
     <row r="86" spans="1:6">
       <c r="B86" s="80" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C86" s="236">
         <f>F31+C85</f>
@@ -5015,31 +5025,31 @@
     </row>
     <row r="88" spans="1:6">
       <c r="B88" s="293" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="356" t="s">
-        <v>366</v>
-      </c>
-      <c r="C89" s="356"/>
-      <c r="D89" s="356"/>
-      <c r="E89" s="356"/>
-      <c r="F89" s="356"/>
+      <c r="B89" s="360" t="s">
+        <v>360</v>
+      </c>
+      <c r="C89" s="360"/>
+      <c r="D89" s="360"/>
+      <c r="E89" s="360"/>
+      <c r="F89" s="360"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="356" t="s">
-        <v>367</v>
-      </c>
-      <c r="C90" s="356"/>
-      <c r="D90" s="356"/>
-      <c r="E90" s="356"/>
-      <c r="F90" s="356"/>
+      <c r="B90" s="360" t="s">
+        <v>361</v>
+      </c>
+      <c r="C90" s="360"/>
+      <c r="D90" s="360"/>
+      <c r="E90" s="360"/>
+      <c r="F90" s="360"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C92" s="236">
         <v>0</v>
@@ -5047,7 +5057,7 @@
     </row>
     <row r="93" spans="1:6">
       <c r="B93" s="47" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C93" s="223">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
@@ -5060,7 +5070,7 @@
     </row>
     <row r="95" spans="1:6" ht="13.9">
       <c r="A95" s="222" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="B95" s="36"/>
       <c r="C95" s="36"/>
@@ -5072,36 +5082,36 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="356" t="s">
-        <v>368</v>
-      </c>
-      <c r="C97" s="356"/>
-      <c r="D97" s="356"/>
-      <c r="E97" s="356"/>
-      <c r="F97" s="356"/>
+      <c r="B97" s="360" t="s">
+        <v>362</v>
+      </c>
+      <c r="C97" s="360"/>
+      <c r="D97" s="360"/>
+      <c r="E97" s="360"/>
+      <c r="F97" s="360"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="210" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="356" t="s">
-        <v>346</v>
-      </c>
-      <c r="C101" s="356"/>
-      <c r="D101" s="356"/>
-      <c r="E101" s="356"/>
-      <c r="F101" s="356"/>
+      <c r="B101" s="360" t="s">
+        <v>341</v>
+      </c>
+      <c r="C101" s="360"/>
+      <c r="D101" s="360"/>
+      <c r="E101" s="360"/>
+      <c r="F101" s="360"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C102" s="349">
         <f>DCF!C7</f>
@@ -5114,7 +5124,7 @@
     </row>
     <row r="103" spans="2:6">
       <c r="B103" s="47" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C103" s="223">
         <f>C102*scaling_factor*Exchange_Rate/Common_Shares</f>
@@ -5127,7 +5137,7 @@
     </row>
     <row r="104" spans="2:6">
       <c r="B104" s="296" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="C104" s="325">
         <f>IF(BS!G31/BS!G27&gt;300%,"nm",BS!G31/BS!G27)</f>
@@ -5136,7 +5146,7 @@
     </row>
     <row r="105" spans="2:6">
       <c r="B105" s="296" t="s">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="C105" s="326">
         <f>IF(BS!C50&gt;30,"nm",BS!C50)</f>
@@ -5145,12 +5155,12 @@
     </row>
     <row r="107" spans="2:6">
       <c r="B107" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="108" spans="2:6">
       <c r="B108" s="47" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C108" s="349">
         <f>BS!C66</f>
@@ -5163,7 +5173,7 @@
     </row>
     <row r="109" spans="2:6">
       <c r="B109" s="47" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C109" s="349">
         <f>DCF!C8</f>
@@ -5176,7 +5186,7 @@
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="47" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C110" s="223">
         <f>C109*scaling_factor*Exchange_Rate/Common_Shares</f>
@@ -5189,12 +5199,12 @@
     </row>
     <row r="112" spans="2:6">
       <c r="B112" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="113" spans="1:6">
       <c r="B113" s="47" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C113" s="349">
         <f>DCF!C9</f>
@@ -5207,7 +5217,7 @@
     </row>
     <row r="114" spans="1:6">
       <c r="B114" s="47" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C114" s="223">
         <f>C113*scaling_factor*Exchange_Rate/Common_Shares</f>
@@ -5219,17 +5229,17 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="356" t="s">
-        <v>369</v>
-      </c>
-      <c r="C116" s="356"/>
-      <c r="D116" s="356"/>
-      <c r="E116" s="356"/>
-      <c r="F116" s="356"/>
+      <c r="B116" s="360" t="s">
+        <v>363</v>
+      </c>
+      <c r="C116" s="360"/>
+      <c r="D116" s="360"/>
+      <c r="E116" s="360"/>
+      <c r="F116" s="360"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
-        <v>451</v>
+        <v>445</v>
       </c>
       <c r="C118" s="223">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
@@ -5242,7 +5252,7 @@
     </row>
     <row r="119" spans="1:6">
       <c r="B119" s="296" t="s">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="C119" s="223">
         <f>BS!D47</f>
@@ -5255,7 +5265,7 @@
     </row>
     <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="222" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="B121" s="36"/>
       <c r="C121" s="36"/>
@@ -5264,29 +5274,29 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="357" t="s">
-        <v>370</v>
-      </c>
-      <c r="C123" s="357"/>
-      <c r="D123" s="357"/>
-      <c r="E123" s="357"/>
-      <c r="F123" s="357"/>
+      <c r="B123" s="361" t="s">
+        <v>364</v>
+      </c>
+      <c r="C123" s="361"/>
+      <c r="D123" s="361"/>
+      <c r="E123" s="361"/>
+      <c r="F123" s="361"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C125" s="233" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D125" s="233" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E125" s="233" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F125" s="233" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="126" spans="1:6">
@@ -5401,7 +5411,7 @@
     </row>
     <row r="132" spans="1:6">
       <c r="B132" s="211" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C132" s="217">
         <f>Scenarios!C60</f>
@@ -5413,17 +5423,17 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="361" t="s">
-        <v>373</v>
-      </c>
-      <c r="C134" s="361"/>
-      <c r="D134" s="361"/>
-      <c r="E134" s="361"/>
-      <c r="F134" s="361"/>
+      <c r="B134" s="364" t="s">
+        <v>367</v>
+      </c>
+      <c r="C134" s="364"/>
+      <c r="D134" s="364"/>
+      <c r="E134" s="364"/>
+      <c r="F134" s="364"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="B136" s="36"/>
       <c r="C136" s="36"/>
@@ -5432,31 +5442,31 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="359" t="s">
-        <v>371</v>
-      </c>
-      <c r="C138" s="359"/>
-      <c r="D138" s="359"/>
-      <c r="E138" s="359"/>
-      <c r="F138" s="359"/>
+      <c r="B138" s="365" t="s">
+        <v>365</v>
+      </c>
+      <c r="C138" s="365"/>
+      <c r="D138" s="365"/>
+      <c r="E138" s="365"/>
+      <c r="F138" s="365"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="356" t="s">
-        <v>372</v>
-      </c>
-      <c r="C139" s="356"/>
-      <c r="D139" s="356"/>
-      <c r="E139" s="356"/>
-      <c r="F139" s="356"/>
+      <c r="B139" s="360" t="s">
+        <v>366</v>
+      </c>
+      <c r="C139" s="360"/>
+      <c r="D139" s="360"/>
+      <c r="E139" s="360"/>
+      <c r="F139" s="360"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="141" spans="1:6">
       <c r="B141" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C141" s="225">
         <f>F28</f>
@@ -5465,7 +5475,7 @@
     </row>
     <row r="142" spans="1:6">
       <c r="B142" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C142" s="224">
         <f>F29</f>
@@ -5474,11 +5484,11 @@
     </row>
     <row r="143" spans="1:6">
       <c r="B143" s="212" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C143" s="213">
         <f>Scenarios!C77</f>
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="D143" s="212" t="str">
         <f>Market_currency</f>
@@ -5487,7 +5497,7 @@
     </row>
     <row r="145" spans="2:4">
       <c r="B145" s="210" t="s">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="C145" s="241" t="str">
         <f>C11</f>
@@ -5500,7 +5510,7 @@
     </row>
     <row r="146" spans="2:4">
       <c r="B146" s="1" t="s">
-        <v>410</v>
+        <v>404</v>
       </c>
       <c r="C146" s="297">
         <f>F29</f>
@@ -5514,7 +5524,7 @@
       </c>
       <c r="C147" s="216">
         <f>Scenarios!C81</f>
-        <v>0.49717779580945759</v>
+        <v>0.44746001622851189</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -5529,11 +5539,11 @@
     </row>
     <row r="149" spans="2:4">
       <c r="B149" s="80" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C149" s="215">
         <f>Scenarios!C83</f>
-        <v>2.2516930066250125</v>
+        <v>2.2019752270440667</v>
       </c>
       <c r="D149" s="300" t="str">
         <f>IF($D$11="","",C149*$E$25)</f>
@@ -5542,7 +5552,7 @@
     </row>
     <row r="150" spans="2:4">
       <c r="B150" s="259" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="C150" s="298" t="str">
         <f>Market_currency</f>
@@ -5555,21 +5565,21 @@
     </row>
     <row r="151" spans="2:4">
       <c r="B151" s="214" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C151" s="92">
         <f>Scenarios!F83</f>
-        <v>0.4980443874620557</v>
+        <v>0.50912765610931499</v>
       </c>
     </row>
     <row r="153" spans="2:4">
       <c r="B153" s="210" t="s">
-        <v>414</v>
+        <v>408</v>
       </c>
     </row>
     <row r="154" spans="2:4">
       <c r="B154" s="1" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="C154" s="297">
         <f>Scenarios!C90</f>
@@ -5583,7 +5593,7 @@
       </c>
       <c r="C155" s="216">
         <f>Scenarios!C91</f>
-        <v>0.61512024715948099</v>
+        <v>0.55360822244353303</v>
       </c>
     </row>
     <row r="156" spans="2:4">
@@ -5598,11 +5608,11 @@
     </row>
     <row r="157" spans="2:4">
       <c r="B157" s="80" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C157" s="215">
         <f>Scenarios!C93</f>
-        <v>3.101365529948271</v>
+        <v>3.039853505232323</v>
       </c>
       <c r="D157" s="300" t="str">
         <f>IF($D$11="","",C157*$E$25)</f>
@@ -5611,7 +5621,7 @@
     </row>
     <row r="158" spans="2:4">
       <c r="B158" s="259" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="C158" s="298" t="str">
         <f>Market_currency</f>
@@ -5624,21 +5634,21 @@
     </row>
     <row r="159" spans="2:4">
       <c r="B159" s="214" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C159" s="92">
         <f>Scenarios!F93</f>
-        <v>0.30863229147626647</v>
+        <v>0.32234477623946356</v>
       </c>
     </row>
     <row r="161" spans="2:4">
       <c r="B161" s="210" t="s">
-        <v>403</v>
+        <v>397</v>
       </c>
     </row>
     <row r="162" spans="2:4">
       <c r="B162" s="1" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="C162" s="92">
         <f>Scenarios!C96</f>
@@ -5652,7 +5662,7 @@
       </c>
       <c r="C163" s="216">
         <f>Scenarios!C97</f>
-        <v>0.78015772196158795</v>
+        <v>0.70214194976542921</v>
       </c>
     </row>
     <row r="164" spans="2:4">
@@ -5667,11 +5677,11 @@
     </row>
     <row r="165" spans="2:4">
       <c r="B165" s="80" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="C165" s="215">
         <f>Scenarios!C99</f>
-        <v>4.3910827513866675</v>
+        <v>4.3130669791905083</v>
       </c>
       <c r="D165" s="300" t="str">
         <f>IF($D$11="","",C165*$E$25)</f>
@@ -5680,7 +5690,7 @@
     </row>
     <row r="166" spans="2:4">
       <c r="B166" s="259" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="C166" s="298" t="str">
         <f>Market_currency</f>
@@ -5693,21 +5703,21 @@
     </row>
     <row r="167" spans="2:4">
       <c r="B167" s="214" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C167" s="92">
         <f>Scenarios!F99</f>
-        <v>2.1123827408074836E-2</v>
+        <v>3.8515387716307137E-2</v>
       </c>
     </row>
     <row r="169" spans="2:4">
       <c r="B169" s="210" t="s">
-        <v>434</v>
+        <v>428</v>
       </c>
     </row>
     <row r="170" spans="2:4">
       <c r="B170" s="1" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="C170" s="92">
         <f>F32</f>
@@ -5721,7 +5731,7 @@
       </c>
       <c r="C171" s="216">
         <f>Scenarios!C103</f>
-        <v>0.72378093778159469</v>
+        <v>0.65140284400343529</v>
       </c>
     </row>
     <row r="172" spans="2:4">
@@ -5736,11 +5746,11 @@
     </row>
     <row r="173" spans="2:4">
       <c r="B173" s="80" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="C173" s="215">
         <f>Scenarios!C105</f>
-        <v>3.939054009870663</v>
+        <v>3.8666759160925035</v>
       </c>
       <c r="D173" s="300" t="str">
         <f>IF($D$11="","",C173*$E$25)</f>
@@ -5749,7 +5759,7 @@
     </row>
     <row r="174" spans="2:4">
       <c r="B174" s="259" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="C174" s="298" t="str">
         <f>Market_currency</f>
@@ -5762,16 +5772,16 @@
     </row>
     <row r="175" spans="2:4">
       <c r="B175" s="214" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C175" s="92">
         <f>Scenarios!F105</f>
-        <v>0.12229326468444657</v>
+        <v>0.13842067503200794</v>
       </c>
     </row>
     <row r="177" spans="1:6" ht="13.9">
       <c r="A177" s="222" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="B177" s="36"/>
       <c r="C177" s="36"/>
@@ -5780,113 +5790,102 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="363" t="s">
-        <v>379</v>
-      </c>
-      <c r="C179" s="356"/>
-      <c r="D179" s="356"/>
-      <c r="E179" s="356"/>
-      <c r="F179" s="356"/>
+      <c r="B179" s="359" t="s">
+        <v>373</v>
+      </c>
+      <c r="C179" s="360"/>
+      <c r="D179" s="360"/>
+      <c r="E179" s="360"/>
+      <c r="F179" s="360"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="360" t="s">
-        <v>383</v>
-      </c>
-      <c r="C182" s="360"/>
-      <c r="D182" s="360"/>
-      <c r="E182" s="360"/>
-      <c r="F182" s="360"/>
+      <c r="B182" s="362" t="s">
+        <v>377</v>
+      </c>
+      <c r="C182" s="362"/>
+      <c r="D182" s="362"/>
+      <c r="E182" s="362"/>
+      <c r="F182" s="362"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
     </row>
     <row r="184" spans="1:6">
       <c r="B184" s="214" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
     </row>
     <row r="185" spans="1:6">
       <c r="B185" s="214" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
     </row>
     <row r="187" spans="1:6">
       <c r="B187" s="1" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="357" t="s">
-        <v>384</v>
-      </c>
-      <c r="C188" s="357"/>
-      <c r="D188" s="357"/>
-      <c r="E188" s="357"/>
-      <c r="F188" s="357"/>
+      <c r="B188" s="361" t="s">
+        <v>378</v>
+      </c>
+      <c r="C188" s="361"/>
+      <c r="D188" s="361"/>
+      <c r="E188" s="361"/>
+      <c r="F188" s="361"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="362" t="s">
-        <v>385</v>
-      </c>
-      <c r="C191" s="362"/>
-      <c r="D191" s="362"/>
-      <c r="E191" s="362"/>
-      <c r="F191" s="362"/>
+      <c r="B191" s="358" t="s">
+        <v>379</v>
+      </c>
+      <c r="C191" s="358"/>
+      <c r="D191" s="358"/>
+      <c r="E191" s="358"/>
+      <c r="F191" s="358"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="362" t="s">
-        <v>386</v>
-      </c>
-      <c r="C192" s="362"/>
-      <c r="D192" s="362"/>
-      <c r="E192" s="362"/>
-      <c r="F192" s="362"/>
+      <c r="B192" s="358" t="s">
+        <v>380</v>
+      </c>
+      <c r="C192" s="358"/>
+      <c r="D192" s="358"/>
+      <c r="E192" s="358"/>
+      <c r="F192" s="358"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
     </row>
     <row r="195" spans="2:2">
       <c r="B195" s="214" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
     </row>
     <row r="196" spans="2:2">
       <c r="B196" s="214" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
     </row>
     <row r="197" spans="2:2">
       <c r="B197" s="214" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5903,13 +5902,24 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1" xr:uid="{45F807FD-9E0F-415A-9BBD-D5FB6470B56D}">
       <formula1>"Y, N"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C23:C25" xr:uid="{342D2C68-3352-49DC-9D77-964DC8D8A160}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C23:C24" xr:uid="{342D2C68-3352-49DC-9D77-964DC8D8A160}">
       <formula1>"Y,N"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="C25:D25" xr:uid="{00000000-0002-0000-0000-000001000000}">
@@ -6176,7 +6186,7 @@
     </row>
     <row r="9" spans="2:13">
       <c r="B9" s="40" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C9" s="351"/>
       <c r="D9" s="351"/>
@@ -6192,7 +6202,7 @@
     </row>
     <row r="10" spans="2:13">
       <c r="B10" s="40" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C10" s="351"/>
       <c r="D10" s="351"/>
@@ -6208,7 +6218,7 @@
     </row>
     <row r="11" spans="2:13">
       <c r="B11" s="40" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C11" s="351"/>
       <c r="D11" s="351"/>
@@ -6434,7 +6444,7 @@
     </row>
     <row r="22" spans="2:13">
       <c r="B22" s="27" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="C22" s="351">
         <v>2369874</v>
@@ -6470,7 +6480,7 @@
     </row>
     <row r="23" spans="2:13">
       <c r="B23" s="27" t="s">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="C23" s="351">
         <v>-182373</v>
@@ -6506,7 +6516,7 @@
     </row>
     <row r="24" spans="2:13">
       <c r="B24" s="27" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="C24" s="351">
         <v>-971717</v>
@@ -6571,7 +6581,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>219</v>
+        <v>463</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -6724,7 +6734,7 @@
     </row>
     <row r="32" spans="2:13">
       <c r="B32" s="26" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C32" s="333">
         <f>BS!G28</f>
@@ -7125,7 +7135,7 @@
     </row>
     <row r="43" spans="2:13">
       <c r="B43" s="43" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C43" s="334">
         <f>IF(C$4="","",C38+C39+C42)</f>
@@ -7174,7 +7184,7 @@
     </row>
     <row r="44" spans="2:13">
       <c r="B44" s="43" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C44" s="354">
         <f t="shared" ref="C44:M44" si="18">IF(C$4="","",C47-C46-C45-C43)</f>
@@ -7522,12 +7532,12 @@
     </row>
     <row r="54" spans="2:13">
       <c r="B54" s="174" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="55" spans="2:13">
       <c r="B55" s="40" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C55" s="349">
         <f t="shared" ref="C55:M55" si="25">IF(C$4="","",C9)</f>
@@ -7576,7 +7586,7 @@
     </row>
     <row r="56" spans="2:13">
       <c r="B56" s="40" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C56" s="349">
         <f t="shared" ref="C56:M56" si="26">IF(C$4="","",C10)</f>
@@ -7625,7 +7635,7 @@
     </row>
     <row r="57" spans="2:13">
       <c r="B57" s="40" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C57" s="349">
         <f t="shared" ref="C57:M57" si="27">IF(C$4="","",C11)</f>
@@ -7674,7 +7684,7 @@
     </row>
     <row r="58" spans="2:13">
       <c r="B58" s="40" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C58" s="349">
         <f>IF(C$4="","",C44-C55-C56-C57)</f>
@@ -7876,7 +7886,7 @@
     </row>
     <row r="64" spans="2:13">
       <c r="B64" s="27" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="C64" s="333">
         <f>IF(C$4="","",C22+C23+C24)</f>
@@ -8128,7 +8138,7 @@
     </row>
     <row r="71" spans="2:13">
       <c r="B71" s="43" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C71" s="101">
         <f>IF(D$36="","",C44/D44-1)</f>
@@ -8523,7 +8533,7 @@
     </row>
     <row r="2" spans="2:8" ht="15" customHeight="1">
       <c r="B2" s="79" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
@@ -8534,19 +8544,19 @@
     </row>
     <row r="3" spans="2:8" ht="15" customHeight="1">
       <c r="B3" s="16" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C3" s="182" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D3" s="183" t="s">
         <v>35</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G3" s="182" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H3" s="183" t="s">
         <v>35</v>
@@ -8608,7 +8618,7 @@
       </c>
       <c r="E6" s="25"/>
       <c r="F6" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G6" s="19">
         <v>0</v>
@@ -8629,7 +8639,7 @@
       </c>
       <c r="E7" s="25"/>
       <c r="F7" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G7" s="19">
         <v>0</v>
@@ -8640,7 +8650,7 @@
     </row>
     <row r="8" spans="2:8" ht="15" customHeight="1">
       <c r="B8" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C8" s="19">
         <v>0</v>
@@ -8650,7 +8660,7 @@
       </c>
       <c r="E8" s="25"/>
       <c r="F8" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G8" s="19">
         <v>0</v>
@@ -8671,7 +8681,7 @@
       </c>
       <c r="E9" s="25"/>
       <c r="F9" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G9" s="19">
         <v>0</v>
@@ -8735,19 +8745,19 @@
     </row>
     <row r="14" spans="2:8" ht="15" customHeight="1">
       <c r="B14" s="16" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C14" s="182" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D14" s="183" t="s">
         <v>35</v>
       </c>
       <c r="F14" s="16" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G14" s="182" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H14" s="183" t="s">
         <v>35</v>
@@ -8755,7 +8765,7 @@
     </row>
     <row r="15" spans="2:8" ht="15" customHeight="1">
       <c r="B15" s="4" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="C15" s="19">
         <v>453310</v>
@@ -8784,7 +8794,7 @@
         <v>0.5</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G16" s="19">
         <v>0</v>
@@ -8804,7 +8814,7 @@
         <v>0.6</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G17" s="19">
         <f>439187</f>
@@ -8816,7 +8826,7 @@
     </row>
     <row r="18" spans="2:8" ht="15" customHeight="1">
       <c r="B18" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C18" s="19">
         <v>0</v>
@@ -8825,7 +8835,7 @@
         <v>0.6</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G18" s="19">
         <v>0</v>
@@ -8846,7 +8856,7 @@
         <v>0.1</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G19" s="19">
         <v>0</v>
@@ -8866,7 +8876,7 @@
         <v>0.05</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G20" s="19">
         <v>0</v>
@@ -8886,7 +8896,7 @@
         <v>0.05</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G21" s="19">
         <v>0</v>
@@ -8946,16 +8956,16 @@
     </row>
     <row r="26" spans="2:8" ht="15" customHeight="1">
       <c r="B26" s="16" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C26" s="182" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F26" s="184" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G26" s="185" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H26" s="186" t="s">
         <v>35</v>
@@ -8988,7 +8998,7 @@
         <v>12125</v>
       </c>
       <c r="F28" s="189" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G28" s="12">
         <v>2421183</v>
@@ -9032,7 +9042,7 @@
     </row>
     <row r="31" spans="2:8" ht="15" customHeight="1">
       <c r="B31" s="80" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C31" s="81">
         <f>SUM(C27:C30)</f>
@@ -9082,10 +9092,10 @@
       <c r="B34" s="83"/>
       <c r="C34" s="84"/>
       <c r="F34" s="196" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G34" s="197" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H34" s="198" t="s">
         <v>35</v>
@@ -9093,10 +9103,10 @@
     </row>
     <row r="35" spans="2:8" ht="15" customHeight="1">
       <c r="B35" s="16" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C35" s="182" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F35" s="199" t="s">
         <v>31</v>
@@ -9118,7 +9128,7 @@
         <v>0</v>
       </c>
       <c r="F36" s="190" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G36" s="191">
         <f>C4+C15</f>
@@ -9134,7 +9144,7 @@
         <v>31552</v>
       </c>
       <c r="F37" s="190" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G37" s="191">
         <f>C6</f>
@@ -9150,7 +9160,7 @@
         <v>0</v>
       </c>
       <c r="F38" s="190" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G38" s="191">
         <f>C7+C17</f>
@@ -9179,14 +9189,14 @@
     </row>
     <row r="40" spans="2:8" ht="15" customHeight="1">
       <c r="B40" s="80" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C40" s="81">
         <f>SUM(C36:C39)</f>
         <v>31552</v>
       </c>
       <c r="F40" s="199" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G40" s="193">
         <f>G12+G24</f>
@@ -9206,7 +9216,7 @@
         <v>1424979</v>
       </c>
       <c r="F41" s="190" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G41" s="191">
         <f>C70</f>
@@ -9225,7 +9235,7 @@
         <v>1456531</v>
       </c>
       <c r="F42" s="201" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G42" s="202">
         <f>C82</f>
@@ -9249,13 +9259,13 @@
     </row>
     <row r="45" spans="2:8" ht="15" customHeight="1">
       <c r="B45" s="16" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C45" s="234" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D45" s="182" t="s">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="F45" s="256" t="s">
         <v>59</v>
@@ -9263,7 +9273,7 @@
     </row>
     <row r="46" spans="2:8" ht="15" customHeight="1">
       <c r="B46" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C46" s="76">
         <f>G29</f>
@@ -9295,7 +9305,7 @@
     </row>
     <row r="49" spans="2:8" ht="15" customHeight="1">
       <c r="B49" s="157" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C49" s="235" t="s">
         <v>57</v>
@@ -9322,7 +9332,7 @@
     </row>
     <row r="51" spans="2:8" ht="15" customHeight="1">
       <c r="B51" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C51" s="181"/>
       <c r="D51" s="92">
@@ -9336,7 +9346,7 @@
     </row>
     <row r="53" spans="2:8" ht="15" customHeight="1">
       <c r="B53" s="157" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C53" s="235" t="s">
         <v>57</v>
@@ -9348,7 +9358,7 @@
     </row>
     <row r="54" spans="2:8" ht="15" customHeight="1">
       <c r="B54" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C54" s="92">
         <f>Normalized_FCF!C8/G35</f>
@@ -9362,7 +9372,7 @@
     </row>
     <row r="55" spans="2:8" ht="15" customHeight="1">
       <c r="B55" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C55" s="92">
         <f>Normalized_FCF!C11/G40</f>
@@ -9379,7 +9389,7 @@
     </row>
     <row r="57" spans="2:8" ht="15" customHeight="1">
       <c r="B57" s="157" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C57" s="235" t="s">
         <v>57</v>
@@ -9416,10 +9426,10 @@
     </row>
     <row r="61" spans="2:8" ht="15" customHeight="1">
       <c r="B61" s="157" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C61" s="235" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D61" s="197" t="s">
         <v>95</v>
@@ -9428,7 +9438,7 @@
     </row>
     <row r="62" spans="2:8" ht="15" customHeight="1">
       <c r="B62" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C62" s="92">
         <f>IF(G28&lt;=0,0,G28/G29)</f>
@@ -9439,12 +9449,12 @@
         <v>0.14691578448009396</v>
       </c>
       <c r="F62" s="253" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" customHeight="1">
       <c r="B64" s="79" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C64" s="37"/>
       <c r="D64" s="37"/>
@@ -9455,13 +9465,13 @@
     </row>
     <row r="65" spans="2:6" ht="15" customHeight="1">
       <c r="B65" s="16" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C65" s="234" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D65" s="183" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F65" s="256" t="s">
         <v>59</v>
@@ -9469,7 +9479,7 @@
     </row>
     <row r="66" spans="2:6" ht="15" customHeight="1">
       <c r="B66" s="105" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C66" s="20">
         <f>G4+G5+G15</f>
@@ -9480,12 +9490,12 @@
         <v>8041470.060084247</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="67" spans="2:6" ht="15" customHeight="1">
       <c r="B67" s="105" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C67" s="20">
         <f>G6+G16</f>
@@ -9495,7 +9505,7 @@
     </row>
     <row r="68" spans="2:6" ht="15" customHeight="1">
       <c r="B68" s="105" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C68" s="20">
         <f>G18</f>
@@ -9505,7 +9515,7 @@
     </row>
     <row r="69" spans="2:6" ht="15" customHeight="1">
       <c r="B69" s="105" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C69" s="20">
         <f>G8+G20</f>
@@ -9515,7 +9525,7 @@
     </row>
     <row r="70" spans="2:6" ht="15" customHeight="1">
       <c r="B70" s="80" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C70" s="81">
         <f>SUM(C66:C69)</f>
@@ -9528,7 +9538,7 @@
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1">
       <c r="B72" s="255" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="C72" s="234" t="s">
         <v>95</v>
@@ -9540,7 +9550,7 @@
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1">
       <c r="B73" s="105" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="C73" s="349">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
@@ -9551,12 +9561,12 @@
         <v>-346159.82331929216</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1">
       <c r="B74" s="257" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="C74" s="258">
         <f>-$C$66/C73</f>
@@ -9567,12 +9577,12 @@
         <v>29.230512377130857</v>
       </c>
       <c r="F74" s="253" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
     </row>
     <row r="75" spans="2:6" ht="15" customHeight="1">
       <c r="B75" s="80" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="C75" s="320"/>
       <c r="D75" s="321">
@@ -9580,12 +9590,12 @@
         <v>2076958.939915753</v>
       </c>
       <c r="F75" s="253" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1">
       <c r="B76" s="259" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="C76" s="260"/>
       <c r="D76" s="290">
@@ -9593,7 +9603,7 @@
         <v>6</v>
       </c>
       <c r="F76" s="253" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1">
@@ -9601,10 +9611,10 @@
     </row>
     <row r="78" spans="2:6" ht="15" customHeight="1">
       <c r="B78" s="16" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C78" s="234" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D78" s="183" t="s">
         <v>35</v>
@@ -9613,7 +9623,7 @@
     </row>
     <row r="79" spans="2:6" ht="15" customHeight="1">
       <c r="B79" s="105" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C79" s="20">
         <f>G7+G17</f>
@@ -9627,7 +9637,7 @@
     </row>
     <row r="80" spans="2:6" ht="15" customHeight="1">
       <c r="B80" s="105" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C80" s="20">
         <f>G19</f>
@@ -9641,7 +9651,7 @@
     </row>
     <row r="81" spans="2:8" ht="15" customHeight="1">
       <c r="B81" s="105" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C81" s="20">
         <f>G9+G21</f>
@@ -9655,7 +9665,7 @@
     </row>
     <row r="82" spans="2:8" ht="15" customHeight="1">
       <c r="B82" s="80" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C82" s="81">
         <f>SUM(C79:C81)</f>
@@ -9669,7 +9679,7 @@
     </row>
     <row r="84" spans="2:8" ht="15" customHeight="1">
       <c r="B84" s="79" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C84" s="37"/>
       <c r="D84" s="37"/>
@@ -9680,15 +9690,15 @@
     </row>
     <row r="85" spans="2:8" ht="15" customHeight="1">
       <c r="B85" s="16" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="D85" s="241" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="15" customHeight="1">
       <c r="B86" s="238" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C86" s="76">
         <f>-DCF!C7*Exchange_Rate</f>
@@ -9705,7 +9715,7 @@
     </row>
     <row r="87" spans="2:8" ht="15" customHeight="1">
       <c r="B87" s="238" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C87" s="76">
         <f>DCF!C8*Exchange_Rate</f>
@@ -9722,7 +9732,7 @@
     </row>
     <row r="88" spans="2:8" ht="15" customHeight="1">
       <c r="B88" s="239" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C88" s="76">
         <f>DCF!C9*Exchange_Rate</f>
@@ -9739,7 +9749,7 @@
     </row>
     <row r="89" spans="2:8" ht="15" customHeight="1">
       <c r="B89" s="80" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C89" s="180">
         <f>SUM(C86:C88)</f>
@@ -9767,7 +9777,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q808"/>
+  <dimension ref="A1:Q809"/>
   <sheetFormatPr defaultColWidth="12.265625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="1.265625" style="2" customWidth="1"/>
@@ -10099,7 +10109,7 @@
     <row r="8" spans="1:17" ht="15.75" customHeight="1">
       <c r="A8" s="10"/>
       <c r="B8" s="29" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C8" s="330">
         <f>C6+C7</f>
@@ -10266,7 +10276,7 @@
     <row r="11" spans="1:17" ht="15.75" customHeight="1">
       <c r="A11" s="10"/>
       <c r="B11" s="31" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C11" s="331">
         <f>C63</f>
@@ -10378,7 +10388,7 @@
     <row r="13" spans="1:17" ht="15.75" customHeight="1">
       <c r="A13" s="10"/>
       <c r="B13" s="70" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C13" s="329">
         <f>SUM(C8:C12)</f>
@@ -10488,7 +10498,7 @@
     <row r="15" spans="1:17" ht="15.75" customHeight="1">
       <c r="A15" s="10"/>
       <c r="B15" s="40" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C15" s="328">
         <f>-C4*C83</f>
@@ -10545,7 +10555,7 @@
     <row r="16" spans="1:17" ht="15.75" customHeight="1">
       <c r="A16" s="10"/>
       <c r="B16" s="41" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C16" s="332">
         <f>SUM(C13:C15)</f>
@@ -10610,7 +10620,7 @@
       </c>
       <c r="D17" s="58"/>
       <c r="E17" s="267" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="F17" s="58"/>
       <c r="G17" s="335"/>
@@ -10635,7 +10645,7 @@
       </c>
       <c r="D18" s="58"/>
       <c r="E18" s="267" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="F18" s="58"/>
       <c r="G18" s="336"/>
@@ -10729,7 +10739,7 @@
     <row r="21" spans="1:17" ht="15.75" customHeight="1">
       <c r="A21" s="10"/>
       <c r="B21" s="54" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C21" s="54"/>
       <c r="D21" s="56"/>
@@ -10948,7 +10958,7 @@
     <row r="27" spans="1:17" ht="15.75" customHeight="1">
       <c r="A27" s="10"/>
       <c r="B27" s="64" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E27" s="268"/>
     </row>
@@ -10963,7 +10973,7 @@
       </c>
       <c r="D28" s="26"/>
       <c r="E28" s="266" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -11023,7 +11033,7 @@
       </c>
       <c r="D29" s="26"/>
       <c r="E29" s="266" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -11140,14 +11150,14 @@
     <row r="33" spans="1:17" ht="15.75" customHeight="1">
       <c r="A33" s="10"/>
       <c r="B33" s="8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C33" s="340">
         <f>G33</f>
         <v>-208899</v>
       </c>
       <c r="E33" s="266" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="G33" s="328">
         <f>Data!C41</f>
@@ -11205,7 +11215,7 @@
       </c>
       <c r="D34" s="58"/>
       <c r="E34" s="266" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="F34" s="58"/>
       <c r="G34" s="333">
@@ -11317,7 +11327,7 @@
     <row r="37" spans="1:17" ht="15.75" customHeight="1">
       <c r="A37" s="10"/>
       <c r="B37" s="64" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E37" s="268"/>
     </row>
@@ -11499,21 +11509,21 @@
     <row r="42" spans="1:17" ht="15.75" customHeight="1">
       <c r="A42" s="10"/>
       <c r="B42" s="64" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E42" s="268"/>
     </row>
     <row r="43" spans="1:17" ht="15.75" customHeight="1">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C43" s="263">
         <v>0.25</v>
       </c>
       <c r="D43" s="27"/>
       <c r="E43" s="265" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
@@ -11567,7 +11577,7 @@
     <row r="45" spans="1:17" ht="15.75" customHeight="1">
       <c r="A45" s="10"/>
       <c r="B45" s="54" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C45" s="54"/>
       <c r="D45" s="56"/>
@@ -11652,7 +11662,7 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="C48" s="328">
         <f>BS!D75*C53</f>
@@ -11707,7 +11717,7 @@
     <row r="49" spans="1:17" ht="15.75" customHeight="1">
       <c r="A49" s="10"/>
       <c r="B49" s="287" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="C49" s="342">
         <f>BS!$C$66*C53</f>
@@ -11823,11 +11833,11 @@
     <row r="52" spans="1:17" ht="15.75" customHeight="1">
       <c r="A52" s="10"/>
       <c r="B52" s="72" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E52" s="268"/>
       <c r="G52" s="97" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="53" spans="1:17" ht="15.75" customHeight="1">
@@ -11839,7 +11849,7 @@
         <v>0.01</v>
       </c>
       <c r="E53" s="265" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
@@ -11866,7 +11876,7 @@
         <v>3.9975273026993614E-2</v>
       </c>
       <c r="E54" s="265" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -11945,17 +11955,17 @@
     <row r="57" spans="1:17" ht="15.75" customHeight="1">
       <c r="A57" s="10"/>
       <c r="B57" s="64" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E57" s="268"/>
       <c r="G57" s="97" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="58" spans="1:17" ht="15.75" customHeight="1">
       <c r="A58" s="10"/>
       <c r="B58" s="40" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C58" s="328">
         <f>BS!$C67*C66</f>
@@ -12010,7 +12020,7 @@
     <row r="59" spans="1:17" ht="15.75" customHeight="1">
       <c r="A59" s="10"/>
       <c r="B59" s="40" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C59" s="328">
         <f>BS!$C68*C67</f>
@@ -12065,7 +12075,7 @@
     <row r="60" spans="1:17" ht="15.75" customHeight="1">
       <c r="A60" s="10"/>
       <c r="B60" s="40" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C60" s="328">
         <f>BS!$C69*C68</f>
@@ -12120,7 +12130,7 @@
     <row r="61" spans="1:17" ht="15.75" customHeight="1">
       <c r="A61" s="10"/>
       <c r="B61" s="31" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C61" s="329">
         <f>SUM(C58:C60)</f>
@@ -12175,13 +12185,13 @@
     <row r="62" spans="1:17" ht="15.75" customHeight="1">
       <c r="A62" s="10"/>
       <c r="B62" s="40" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C62" s="343">
         <v>0</v>
       </c>
       <c r="E62" s="266" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="G62" s="328">
         <f>Data!C58</f>
@@ -12231,7 +12241,7 @@
     <row r="63" spans="1:17" ht="15.75" customHeight="1">
       <c r="A63" s="10"/>
       <c r="B63" s="31" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C63" s="329">
         <f>C61+C62</f>
@@ -12290,17 +12300,17 @@
     <row r="65" spans="1:17" ht="15.75" customHeight="1">
       <c r="A65" s="10"/>
       <c r="B65" s="96" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E65" s="268"/>
       <c r="G65" s="97" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="66" spans="1:17" ht="15.75" customHeight="1">
       <c r="A66" s="10"/>
       <c r="B66" s="40" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C66" s="176">
         <f>G66</f>
@@ -12325,7 +12335,7 @@
     <row r="67" spans="1:17" ht="15.75" customHeight="1">
       <c r="A67" s="10"/>
       <c r="B67" s="105" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C67" s="176">
         <f>G67</f>
@@ -12350,7 +12360,7 @@
     <row r="68" spans="1:17" ht="15.75" customHeight="1">
       <c r="A68" s="10"/>
       <c r="B68" s="105" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C68" s="176">
         <f>G68</f>
@@ -12375,7 +12385,7 @@
     <row r="69" spans="1:17" ht="15.75" customHeight="1">
       <c r="A69" s="10"/>
       <c r="B69" s="31" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C69" s="71">
         <f>C61/BS!C70</f>
@@ -12405,7 +12415,7 @@
     <row r="71" spans="1:17" ht="15.75" customHeight="1">
       <c r="A71" s="10"/>
       <c r="B71" s="54" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
@@ -12428,7 +12438,7 @@
     <row r="72" spans="1:17" ht="15.75" customHeight="1">
       <c r="A72" s="10"/>
       <c r="B72" s="72" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C72" s="62"/>
       <c r="D72" s="27"/>
@@ -12620,7 +12630,7 @@
     <row r="76" spans="1:17" ht="15.75" customHeight="1">
       <c r="A76" s="10"/>
       <c r="B76" s="29" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C76" s="78">
         <f>ABS(C8/C$4)</f>
@@ -12742,7 +12752,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="266" t="s">
-        <v>356</v>
+        <v>464</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -12793,7 +12803,7 @@
     <row r="79" spans="1:17" ht="15.75" customHeight="1">
       <c r="A79" s="10"/>
       <c r="B79" s="31" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C79" s="78">
         <f>ABS(C11/C$4)</f>
@@ -12907,7 +12917,7 @@
     <row r="81" spans="1:17" ht="15.75" customHeight="1">
       <c r="A81" s="10"/>
       <c r="B81" s="70" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C81" s="78">
         <f>C13/C4</f>
@@ -13079,7 +13089,7 @@
     <row r="84" spans="1:17" ht="15.75" customHeight="1">
       <c r="A84" s="10"/>
       <c r="B84" s="41" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C84" s="78">
         <f>ABS(C16/C$4)</f>
@@ -13186,7 +13196,7 @@
     <row r="87" spans="1:17" ht="15.75" customHeight="1">
       <c r="A87" s="10"/>
       <c r="B87" s="31" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C87" s="78">
         <f>ABS(C19/C$4)</f>
@@ -13247,7 +13257,7 @@
     <row r="89" spans="1:17" ht="15.75" customHeight="1">
       <c r="A89" s="10"/>
       <c r="B89" s="64" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E89" s="268"/>
     </row>
@@ -13366,7 +13376,7 @@
     <row r="92" spans="1:17" ht="15.75" customHeight="1">
       <c r="A92" s="10"/>
       <c r="B92" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
@@ -13421,1310 +13431,1330 @@
     <row r="93" spans="1:17" ht="15.75" customHeight="1">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="C93" s="23">
-        <f>C90/Market_Price</f>
-        <v>0.11152416356877323</v>
+        <v>453</v>
+      </c>
+      <c r="C93" s="356">
+        <v>0.1</v>
       </c>
       <c r="E93" s="268"/>
-      <c r="G93" s="23">
-        <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>0.11152416356877323</v>
-      </c>
-      <c r="H93" s="23">
+      <c r="G93" s="357"/>
+      <c r="H93" s="357"/>
+      <c r="I93" s="357"/>
+      <c r="J93" s="357"/>
+      <c r="K93" s="357"/>
+      <c r="L93" s="357"/>
+      <c r="M93" s="357"/>
+      <c r="N93" s="357"/>
+      <c r="O93" s="357"/>
+      <c r="P93" s="357"/>
+      <c r="Q93" s="357"/>
+    </row>
+    <row r="94" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A94" s="10"/>
+      <c r="B94" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="C94" s="23">
+        <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
+        <v>0.10037174721189591</v>
+      </c>
+      <c r="E94" s="268"/>
+      <c r="G94" s="23">
+        <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
+        <v>0.10037174721189591</v>
+      </c>
+      <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>0.10408921933085503</v>
-      </c>
-      <c r="I93" s="23">
+        <v>9.3680297397769535E-2</v>
+      </c>
+      <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>0.15985130111524165</v>
-      </c>
-      <c r="J93" s="23">
+        <v>0.14386617100371751</v>
+      </c>
+      <c r="J94" s="23">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="K93" s="23">
+      <c r="K94" s="23">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="L93" s="23">
+      <c r="L94" s="23">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="M93" s="23">
+      <c r="M94" s="23">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="N93" s="23">
+      <c r="N94" s="23">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="O93" s="23">
+      <c r="O94" s="23">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="P93" s="23">
+      <c r="P94" s="23">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="Q93" s="23" t="str">
+      <c r="Q94" s="23" t="str">
         <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
-    <row r="94" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A94" s="10"/>
-      <c r="E94" s="268"/>
-    </row>
     <row r="95" spans="1:17" ht="15.75" customHeight="1">
       <c r="A95" s="10"/>
-      <c r="B95" s="157" t="s">
-        <v>84</v>
-      </c>
-      <c r="C95" s="62"/>
-      <c r="D95" s="27"/>
-      <c r="E95" s="265"/>
-      <c r="F95" s="27"/>
-      <c r="G95" s="12"/>
-      <c r="H95" s="12"/>
-      <c r="I95" s="12"/>
-      <c r="J95" s="12"/>
-      <c r="K95" s="12"/>
-      <c r="L95" s="12"/>
-      <c r="M95" s="12"/>
-      <c r="N95" s="12"/>
-      <c r="O95" s="12"/>
-      <c r="P95" s="12"/>
-      <c r="Q95" s="12"/>
+      <c r="E95" s="268"/>
     </row>
     <row r="96" spans="1:17" ht="15.75" customHeight="1">
       <c r="A96" s="10"/>
-      <c r="B96" s="27" t="s">
-        <v>144</v>
-      </c>
-      <c r="C96" s="77">
-        <f>C4/G4-1</f>
-        <v>-0.10877049634170466</v>
-      </c>
+      <c r="B96" s="157" t="s">
+        <v>84</v>
+      </c>
+      <c r="C96" s="62"/>
       <c r="D96" s="27"/>
       <c r="E96" s="265"/>
       <c r="F96" s="27"/>
-      <c r="G96" s="6">
-        <f t="shared" ref="G96:Q96" si="40">IF(H4="","",G4/H4-1)</f>
-        <v>-0.1415817980712496</v>
-      </c>
-      <c r="H96" s="6">
-        <f t="shared" si="40"/>
-        <v>-0.28286433169533853</v>
-      </c>
-      <c r="I96" s="6">
-        <f t="shared" si="40"/>
-        <v>0.16095679679720432</v>
-      </c>
-      <c r="J96" s="6">
-        <f t="shared" si="40"/>
-        <v>0.77030391415856747</v>
-      </c>
-      <c r="K96" s="6">
-        <f t="shared" si="40"/>
-        <v>3.2988586072755233E-2</v>
-      </c>
-      <c r="L96" s="6">
-        <f t="shared" si="40"/>
-        <v>4.9680753170765479E-2</v>
-      </c>
-      <c r="M96" s="6">
-        <f t="shared" si="40"/>
-        <v>6.1710487735611608E-2</v>
-      </c>
-      <c r="N96" s="6">
-        <f t="shared" si="40"/>
-        <v>0.91831083190368457</v>
-      </c>
-      <c r="O96" s="6">
-        <f t="shared" si="40"/>
-        <v>-9.3529644215324947E-2</v>
-      </c>
-      <c r="P96" s="6" t="str">
-        <f t="shared" si="40"/>
-        <v/>
-      </c>
-      <c r="Q96" s="6" t="str">
-        <f t="shared" si="40"/>
-        <v/>
-      </c>
+      <c r="G96" s="12"/>
+      <c r="H96" s="12"/>
+      <c r="I96" s="12"/>
+      <c r="J96" s="12"/>
+      <c r="K96" s="12"/>
+      <c r="L96" s="12"/>
+      <c r="M96" s="12"/>
+      <c r="N96" s="12"/>
+      <c r="O96" s="12"/>
+      <c r="P96" s="12"/>
+      <c r="Q96" s="12"/>
     </row>
     <row r="97" spans="1:17" ht="15.75" customHeight="1">
       <c r="A97" s="10"/>
-      <c r="B97" s="70" t="s">
-        <v>164</v>
+      <c r="B97" s="27" t="s">
+        <v>143</v>
       </c>
       <c r="C97" s="77">
-        <f>C13/G13-1</f>
-        <v>-0.17630446220988327</v>
+        <f>C4/G4-1</f>
+        <v>-0.10877049634170466</v>
       </c>
       <c r="D97" s="27"/>
       <c r="E97" s="265"/>
       <c r="F97" s="27"/>
       <c r="G97" s="6">
-        <f t="shared" ref="G97:Q97" si="41">IF(H5="","",G13/H13-1)</f>
+        <f t="shared" ref="G97:Q97" si="40">IF(H4="","",G4/H4-1)</f>
+        <v>-0.1415817980712496</v>
+      </c>
+      <c r="H97" s="6">
+        <f t="shared" si="40"/>
+        <v>-0.28286433169533853</v>
+      </c>
+      <c r="I97" s="6">
+        <f t="shared" si="40"/>
+        <v>0.16095679679720432</v>
+      </c>
+      <c r="J97" s="6">
+        <f t="shared" si="40"/>
+        <v>0.77030391415856747</v>
+      </c>
+      <c r="K97" s="6">
+        <f t="shared" si="40"/>
+        <v>3.2988586072755233E-2</v>
+      </c>
+      <c r="L97" s="6">
+        <f t="shared" si="40"/>
+        <v>4.9680753170765479E-2</v>
+      </c>
+      <c r="M97" s="6">
+        <f t="shared" si="40"/>
+        <v>6.1710487735611608E-2</v>
+      </c>
+      <c r="N97" s="6">
+        <f t="shared" si="40"/>
+        <v>0.91831083190368457</v>
+      </c>
+      <c r="O97" s="6">
+        <f t="shared" si="40"/>
+        <v>-9.3529644215324947E-2</v>
+      </c>
+      <c r="P97" s="6" t="str">
+        <f t="shared" si="40"/>
+        <v/>
+      </c>
+      <c r="Q97" s="6" t="str">
+        <f t="shared" si="40"/>
+        <v/>
+      </c>
+    </row>
+    <row r="98" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A98" s="10"/>
+      <c r="B98" s="70" t="s">
+        <v>163</v>
+      </c>
+      <c r="C98" s="77">
+        <f>C13/G13-1</f>
+        <v>-0.17630446220988327</v>
+      </c>
+      <c r="D98" s="27"/>
+      <c r="E98" s="265"/>
+      <c r="F98" s="27"/>
+      <c r="G98" s="6">
+        <f t="shared" ref="G98:Q98" si="41">IF(H5="","",G13/H13-1)</f>
         <v>-0.2520278721940431</v>
       </c>
-      <c r="H97" s="6">
+      <c r="H98" s="6">
         <f t="shared" si="41"/>
         <v>-0.3515010495227936</v>
       </c>
-      <c r="I97" s="6">
+      <c r="I98" s="6">
         <f t="shared" si="41"/>
         <v>0.20965989881388936</v>
       </c>
-      <c r="J97" s="6">
+      <c r="J98" s="6">
         <f t="shared" si="41"/>
         <v>1.867087514324127</v>
       </c>
-      <c r="K97" s="6">
+      <c r="K98" s="6">
         <f t="shared" si="41"/>
         <v>-0.11930986937171073</v>
       </c>
-      <c r="L97" s="6">
+      <c r="L98" s="6">
         <f t="shared" si="41"/>
         <v>4.6974579064557931E-2</v>
       </c>
-      <c r="M97" s="6">
+      <c r="M98" s="6">
         <f t="shared" si="41"/>
         <v>1.3525306599978748E-2</v>
       </c>
-      <c r="N97" s="6">
+      <c r="N98" s="6">
         <f t="shared" si="41"/>
         <v>5.2182333090267772</v>
       </c>
-      <c r="O97" s="6">
+      <c r="O98" s="6">
         <f t="shared" si="41"/>
         <v>-5.2530066172625807</v>
       </c>
-      <c r="P97" s="6" t="str">
+      <c r="P98" s="6" t="str">
         <f t="shared" si="41"/>
         <v/>
       </c>
-      <c r="Q97" s="6" t="str">
+      <c r="Q98" s="6" t="str">
         <f t="shared" si="41"/>
         <v/>
       </c>
     </row>
-    <row r="98" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A98" s="10"/>
-    </row>
     <row r="99" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A99" s="3"/>
-      <c r="B99" s="54" t="s">
-        <v>215</v>
-      </c>
-      <c r="C99" s="54"/>
-      <c r="D99" s="56"/>
-      <c r="E99" s="66" t="s">
+      <c r="A99" s="10"/>
+    </row>
+    <row r="100" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A100" s="3"/>
+      <c r="B100" s="54" t="s">
+        <v>214</v>
+      </c>
+      <c r="C100" s="54"/>
+      <c r="D100" s="56"/>
+      <c r="E100" s="66" t="s">
         <v>59</v>
       </c>
-      <c r="F99" s="56"/>
-      <c r="G99" s="37"/>
-      <c r="H99" s="37"/>
-      <c r="I99" s="37"/>
-      <c r="J99" s="37"/>
-      <c r="K99" s="37"/>
-      <c r="L99" s="37"/>
-      <c r="M99" s="37"/>
-      <c r="N99" s="37"/>
-      <c r="O99" s="37"/>
-      <c r="P99" s="37"/>
-      <c r="Q99" s="37"/>
-    </row>
-    <row r="100" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A100" s="10"/>
-      <c r="B100" s="64" t="s">
-        <v>28</v>
-      </c>
-      <c r="E100" s="268"/>
-      <c r="G100" s="97" t="s">
-        <v>219</v>
-      </c>
+      <c r="F100" s="56"/>
+      <c r="G100" s="37"/>
+      <c r="H100" s="37"/>
+      <c r="I100" s="37"/>
+      <c r="J100" s="37"/>
+      <c r="K100" s="37"/>
+      <c r="L100" s="37"/>
+      <c r="M100" s="37"/>
+      <c r="N100" s="37"/>
+      <c r="O100" s="37"/>
+      <c r="P100" s="37"/>
+      <c r="Q100" s="37"/>
     </row>
     <row r="101" spans="1:17" ht="15.75" customHeight="1">
       <c r="A101" s="10"/>
-      <c r="B101" s="26" t="s">
+      <c r="B101" s="64" t="s">
+        <v>28</v>
+      </c>
+      <c r="E101" s="268"/>
+      <c r="G101" s="97" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="102" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A102" s="10"/>
+      <c r="B102" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="C101" s="344">
+      <c r="C102" s="344">
         <f>BS!G32</f>
         <v>22948823</v>
       </c>
-      <c r="D101" s="26"/>
-      <c r="E101" s="269"/>
-      <c r="F101" s="26"/>
-      <c r="G101" s="333">
-        <f t="shared" ref="G101:Q101" si="42">IF(G$4="","",G105+G104)</f>
+      <c r="D102" s="26"/>
+      <c r="E102" s="269"/>
+      <c r="F102" s="26"/>
+      <c r="G102" s="333">
+        <f t="shared" ref="G102:Q102" si="42">IF(G$4="","",G106+G105)</f>
         <v>22948823</v>
       </c>
-      <c r="H101" s="333">
+      <c r="H102" s="333">
         <f t="shared" si="42"/>
         <v>22491544</v>
       </c>
-      <c r="I101" s="333">
+      <c r="I102" s="333">
         <f t="shared" si="42"/>
         <v>23463484</v>
       </c>
-      <c r="J101" s="333">
+      <c r="J102" s="333">
         <f t="shared" si="42"/>
         <v>24779977</v>
       </c>
-      <c r="K101" s="333">
+      <c r="K102" s="333">
         <f t="shared" si="42"/>
         <v>21433646</v>
       </c>
-      <c r="L101" s="333">
+      <c r="L102" s="333">
         <f t="shared" si="42"/>
         <v>21472710</v>
       </c>
-      <c r="M101" s="333">
+      <c r="M102" s="333">
         <f t="shared" si="42"/>
         <v>21251042</v>
       </c>
-      <c r="N101" s="333">
+      <c r="N102" s="333">
         <f t="shared" si="42"/>
         <v>21694645</v>
       </c>
-      <c r="O101" s="333">
+      <c r="O102" s="333">
         <f t="shared" si="42"/>
         <v>19104456</v>
       </c>
-      <c r="P101" s="333">
+      <c r="P102" s="333">
         <f t="shared" si="42"/>
         <v>20727669</v>
       </c>
-      <c r="Q101" s="333" t="str">
+      <c r="Q102" s="333" t="str">
         <f t="shared" si="42"/>
-        <v/>
-      </c>
-    </row>
-    <row r="102" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A102" s="10"/>
-      <c r="B102" s="93" t="s">
-        <v>210</v>
-      </c>
-      <c r="C102" s="345">
-        <f>BS!C4</f>
-        <v>537904</v>
-      </c>
-      <c r="D102" s="89"/>
-      <c r="E102" s="270"/>
-      <c r="F102" s="89"/>
-      <c r="G102" s="346">
-        <f>IF(G$4="","",Data!D77)</f>
-        <v>687833</v>
-      </c>
-      <c r="H102" s="346">
-        <f>IF(H$4="","",Data!E77)</f>
-        <v>2889765</v>
-      </c>
-      <c r="I102" s="346">
-        <f>IF(I$4="","",Data!F77)</f>
-        <v>3144251</v>
-      </c>
-      <c r="J102" s="346">
-        <f>IF(J$4="","",Data!G77)</f>
-        <v>2049144</v>
-      </c>
-      <c r="K102" s="346">
-        <f>IF(K$4="","",Data!H77)</f>
-        <v>1797319</v>
-      </c>
-      <c r="L102" s="346">
-        <f>IF(L$4="","",Data!I77)</f>
-        <v>0</v>
-      </c>
-      <c r="M102" s="346">
-        <f>IF(M$4="","",Data!J77)</f>
-        <v>0</v>
-      </c>
-      <c r="N102" s="346">
-        <f>IF(N$4="","",Data!K77)</f>
-        <v>0</v>
-      </c>
-      <c r="O102" s="346">
-        <f>IF(O$4="","",Data!L77)</f>
-        <v>0</v>
-      </c>
-      <c r="P102" s="346">
-        <f>IF(P$4="","",Data!M77)</f>
-        <v>0</v>
-      </c>
-      <c r="Q102" s="346" t="str">
-        <f>IF(Q$4="","",Data!N77)</f>
         <v/>
       </c>
     </row>
     <row r="103" spans="1:17" ht="15.75" customHeight="1">
       <c r="A103" s="10"/>
       <c r="B103" s="93" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C103" s="345">
-        <f>BS!C6+BS!C7</f>
-        <v>137638</v>
+        <f>BS!C4</f>
+        <v>537904</v>
       </c>
       <c r="D103" s="89"/>
       <c r="E103" s="270"/>
       <c r="F103" s="89"/>
       <c r="G103" s="346">
+        <f>IF(G$4="","",Data!D77)</f>
+        <v>687833</v>
+      </c>
+      <c r="H103" s="346">
+        <f>IF(H$4="","",Data!E77)</f>
+        <v>2889765</v>
+      </c>
+      <c r="I103" s="346">
+        <f>IF(I$4="","",Data!F77)</f>
+        <v>3144251</v>
+      </c>
+      <c r="J103" s="346">
+        <f>IF(J$4="","",Data!G77)</f>
+        <v>2049144</v>
+      </c>
+      <c r="K103" s="346">
+        <f>IF(K$4="","",Data!H77)</f>
+        <v>1797319</v>
+      </c>
+      <c r="L103" s="346">
+        <f>IF(L$4="","",Data!I77)</f>
+        <v>0</v>
+      </c>
+      <c r="M103" s="346">
+        <f>IF(M$4="","",Data!J77)</f>
+        <v>0</v>
+      </c>
+      <c r="N103" s="346">
+        <f>IF(N$4="","",Data!K77)</f>
+        <v>0</v>
+      </c>
+      <c r="O103" s="346">
+        <f>IF(O$4="","",Data!L77)</f>
+        <v>0</v>
+      </c>
+      <c r="P103" s="346">
+        <f>IF(P$4="","",Data!M77)</f>
+        <v>0</v>
+      </c>
+      <c r="Q103" s="346" t="str">
+        <f>IF(Q$4="","",Data!N77)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="104" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A104" s="10"/>
+      <c r="B104" s="93" t="s">
+        <v>210</v>
+      </c>
+      <c r="C104" s="345">
+        <f>BS!C6+BS!C7</f>
+        <v>137638</v>
+      </c>
+      <c r="D104" s="89"/>
+      <c r="E104" s="270"/>
+      <c r="F104" s="89"/>
+      <c r="G104" s="346">
         <f>IF(G$4="","",Data!D78)</f>
         <v>125636</v>
       </c>
-      <c r="H103" s="346">
+      <c r="H104" s="346">
         <f>IF(H$4="","",Data!E78)</f>
         <v>42046</v>
       </c>
-      <c r="I103" s="346">
+      <c r="I104" s="346">
         <f>IF(I$4="","",Data!F78)</f>
         <v>142658</v>
       </c>
-      <c r="J103" s="346">
+      <c r="J104" s="346">
         <f>IF(J$4="","",Data!G78)</f>
         <v>131170</v>
       </c>
-      <c r="K103" s="346">
+      <c r="K104" s="346">
         <f>IF(K$4="","",Data!H78)</f>
         <v>123530</v>
       </c>
-      <c r="L103" s="346">
+      <c r="L104" s="346">
         <f>IF(L$4="","",Data!I78)</f>
         <v>0</v>
       </c>
-      <c r="M103" s="346">
+      <c r="M104" s="346">
         <f>IF(M$4="","",Data!J78)</f>
         <v>0</v>
       </c>
-      <c r="N103" s="346">
+      <c r="N104" s="346">
         <f>IF(N$4="","",Data!K78)</f>
         <v>0</v>
       </c>
-      <c r="O103" s="346">
+      <c r="O104" s="346">
         <f>IF(O$4="","",Data!L78)</f>
         <v>0</v>
       </c>
-      <c r="P103" s="346">
+      <c r="P104" s="346">
         <f>IF(P$4="","",Data!M78)</f>
         <v>0</v>
       </c>
-      <c r="Q103" s="346" t="str">
+      <c r="Q104" s="346" t="str">
         <f>IF(Q$4="","",Data!N78)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="104" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A104" s="10"/>
-      <c r="B104" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="C104" s="344">
-        <f>BS!G30</f>
-        <v>4047566</v>
-      </c>
-      <c r="D104" s="26"/>
-      <c r="E104" s="269"/>
-      <c r="F104" s="26"/>
-      <c r="G104" s="333">
-        <f>Data!C79</f>
-        <v>4047566</v>
-      </c>
-      <c r="H104" s="333">
-        <f>Data!D79</f>
-        <v>4021026</v>
-      </c>
-      <c r="I104" s="333">
-        <f>Data!E79</f>
-        <v>4786265</v>
-      </c>
-      <c r="J104" s="333">
-        <f>Data!F79</f>
-        <v>5631759</v>
-      </c>
-      <c r="K104" s="333">
-        <f>Data!G79</f>
-        <v>4142576</v>
-      </c>
-      <c r="L104" s="333">
-        <f>Data!H79</f>
-        <v>4426398</v>
-      </c>
-      <c r="M104" s="333">
-        <f>Data!I79</f>
-        <v>4475236</v>
-      </c>
-      <c r="N104" s="333">
-        <f>Data!J79</f>
-        <v>4318962</v>
-      </c>
-      <c r="O104" s="333">
-        <f>Data!K79</f>
-        <v>3438763</v>
-      </c>
-      <c r="P104" s="333">
-        <f>Data!L79</f>
-        <v>3683389</v>
-      </c>
-      <c r="Q104" s="333" t="str">
-        <f>Data!M79</f>
         <v/>
       </c>
     </row>
     <row r="105" spans="1:17" ht="15.75" customHeight="1">
       <c r="A105" s="10"/>
       <c r="B105" s="26" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="C105" s="344">
-        <f>BS!G27</f>
-        <v>18901257</v>
+        <f>BS!G30</f>
+        <v>4047566</v>
       </c>
       <c r="D105" s="26"/>
       <c r="E105" s="269"/>
       <c r="F105" s="26"/>
       <c r="G105" s="333">
+        <f>Data!C79</f>
+        <v>4047566</v>
+      </c>
+      <c r="H105" s="333">
+        <f>Data!D79</f>
+        <v>4021026</v>
+      </c>
+      <c r="I105" s="333">
+        <f>Data!E79</f>
+        <v>4786265</v>
+      </c>
+      <c r="J105" s="333">
+        <f>Data!F79</f>
+        <v>5631759</v>
+      </c>
+      <c r="K105" s="333">
+        <f>Data!G79</f>
+        <v>4142576</v>
+      </c>
+      <c r="L105" s="333">
+        <f>Data!H79</f>
+        <v>4426398</v>
+      </c>
+      <c r="M105" s="333">
+        <f>Data!I79</f>
+        <v>4475236</v>
+      </c>
+      <c r="N105" s="333">
+        <f>Data!J79</f>
+        <v>4318962</v>
+      </c>
+      <c r="O105" s="333">
+        <f>Data!K79</f>
+        <v>3438763</v>
+      </c>
+      <c r="P105" s="333">
+        <f>Data!L79</f>
+        <v>3683389</v>
+      </c>
+      <c r="Q105" s="333" t="str">
+        <f>Data!M79</f>
+        <v/>
+      </c>
+    </row>
+    <row r="106" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A106" s="10"/>
+      <c r="B106" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="C106" s="344">
+        <f>BS!G27</f>
+        <v>18901257</v>
+      </c>
+      <c r="D106" s="26"/>
+      <c r="E106" s="269"/>
+      <c r="F106" s="26"/>
+      <c r="G106" s="333">
         <f>Data!C80</f>
         <v>18901257</v>
       </c>
-      <c r="H105" s="333">
+      <c r="H106" s="333">
         <f>Data!D80</f>
         <v>18470518</v>
       </c>
-      <c r="I105" s="333">
+      <c r="I106" s="333">
         <f>Data!E80</f>
         <v>18677219</v>
       </c>
-      <c r="J105" s="333">
+      <c r="J106" s="333">
         <f>Data!F80</f>
         <v>19148218</v>
       </c>
-      <c r="K105" s="333">
+      <c r="K106" s="333">
         <f>Data!G80</f>
         <v>17291070</v>
       </c>
-      <c r="L105" s="333">
+      <c r="L106" s="333">
         <f>Data!H80</f>
         <v>17046312</v>
       </c>
-      <c r="M105" s="333">
+      <c r="M106" s="333">
         <f>Data!I80</f>
         <v>16775806</v>
       </c>
-      <c r="N105" s="333">
+      <c r="N106" s="333">
         <f>Data!J80</f>
         <v>17375683</v>
       </c>
-      <c r="O105" s="333">
+      <c r="O106" s="333">
         <f>Data!K80</f>
         <v>15665693</v>
       </c>
-      <c r="P105" s="333">
+      <c r="P106" s="333">
         <f>Data!L80</f>
         <v>17044280</v>
       </c>
-      <c r="Q105" s="333" t="str">
+      <c r="Q106" s="333" t="str">
         <f>Data!M80</f>
         <v/>
       </c>
     </row>
-    <row r="106" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A106" s="10"/>
-      <c r="E106" s="268"/>
-    </row>
     <row r="107" spans="1:17" ht="15.75" customHeight="1">
       <c r="A107" s="10"/>
-      <c r="B107" s="91" t="s">
-        <v>220</v>
-      </c>
-      <c r="C107" s="26"/>
-      <c r="D107" s="26"/>
-      <c r="E107" s="269"/>
-      <c r="F107" s="26"/>
-      <c r="G107" s="97" t="s">
-        <v>219</v>
-      </c>
-      <c r="H107" s="12"/>
-      <c r="I107" s="12"/>
-      <c r="J107" s="12"/>
-      <c r="K107" s="12"/>
-      <c r="L107" s="12"/>
-      <c r="M107" s="12"/>
-      <c r="N107" s="12"/>
-      <c r="O107" s="12"/>
-      <c r="P107" s="12"/>
-      <c r="Q107" s="12"/>
+      <c r="E107" s="268"/>
     </row>
     <row r="108" spans="1:17" ht="15.75" customHeight="1">
       <c r="A108" s="10"/>
-      <c r="B108" s="26" t="s">
-        <v>217</v>
-      </c>
-      <c r="C108" s="94">
-        <f>C102/C$4</f>
-        <v>0.11934995649827392</v>
-      </c>
+      <c r="B108" s="91" t="s">
+        <v>219</v>
+      </c>
+      <c r="C108" s="26"/>
       <c r="D108" s="26"/>
       <c r="E108" s="269"/>
       <c r="F108" s="26"/>
-      <c r="G108" s="94">
-        <f t="shared" ref="G108:Q108" si="43">IF(G$4="","",G102/G$4)</f>
-        <v>0.1360160174016215</v>
-      </c>
-      <c r="H108" s="94">
-        <f t="shared" si="43"/>
-        <v>0.49053329549073277</v>
-      </c>
-      <c r="I108" s="94">
-        <f t="shared" si="43"/>
-        <v>0.38275819294610075</v>
-      </c>
-      <c r="J108" s="94">
-        <f t="shared" si="43"/>
-        <v>0.28959817790678055</v>
-      </c>
-      <c r="K108" s="94">
-        <f t="shared" si="43"/>
-        <v>0.44967251287293741</v>
-      </c>
-      <c r="L108" s="94">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="M108" s="94">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="N108" s="94">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="O108" s="94">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="P108" s="94">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="Q108" s="94" t="str">
-        <f t="shared" si="43"/>
-        <v/>
-      </c>
+      <c r="G108" s="97" t="s">
+        <v>218</v>
+      </c>
+      <c r="H108" s="12"/>
+      <c r="I108" s="12"/>
+      <c r="J108" s="12"/>
+      <c r="K108" s="12"/>
+      <c r="L108" s="12"/>
+      <c r="M108" s="12"/>
+      <c r="N108" s="12"/>
+      <c r="O108" s="12"/>
+      <c r="P108" s="12"/>
+      <c r="Q108" s="12"/>
     </row>
     <row r="109" spans="1:17" ht="15.75" customHeight="1">
       <c r="A109" s="10"/>
       <c r="B109" s="26" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C109" s="94">
         <f>C103/C$4</f>
-        <v>3.0539072608698627E-2</v>
+        <v>0.11934995649827392</v>
       </c>
       <c r="D109" s="26"/>
       <c r="E109" s="269"/>
       <c r="F109" s="26"/>
       <c r="G109" s="94">
-        <f t="shared" ref="G109:Q109" si="44">IF(G$4="","",G103/G$4)</f>
-        <v>2.4843978643464503E-2</v>
+        <f t="shared" ref="G109:Q109" si="43">IF(G$4="","",G103/G$4)</f>
+        <v>0.1360160174016215</v>
       </c>
       <c r="H109" s="94">
-        <f t="shared" si="44"/>
-        <v>7.1372457421981887E-3</v>
+        <f t="shared" si="43"/>
+        <v>0.49053329549073277</v>
       </c>
       <c r="I109" s="94">
-        <f t="shared" si="44"/>
-        <v>1.7366144843177229E-2</v>
+        <f t="shared" si="43"/>
+        <v>0.38275819294610075</v>
       </c>
       <c r="J109" s="94">
-        <f t="shared" si="44"/>
-        <v>1.8537786019934374E-2</v>
+        <f t="shared" si="43"/>
+        <v>0.28959817790678055</v>
       </c>
       <c r="K109" s="94">
-        <f t="shared" si="44"/>
-        <v>3.0906058142819364E-2</v>
+        <f t="shared" si="43"/>
+        <v>0.44967251287293741</v>
       </c>
       <c r="L109" s="94">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="M109" s="94">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="N109" s="94">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="O109" s="94">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="P109" s="94">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="Q109" s="94" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
     </row>
     <row r="110" spans="1:17" ht="15.75" customHeight="1">
       <c r="A110" s="10"/>
       <c r="B110" s="26" t="s">
-        <v>69</v>
+        <v>217</v>
       </c>
       <c r="C110" s="94">
-        <f>BS!$G$38/C$4</f>
-        <v>0</v>
+        <f>C104/C$4</f>
+        <v>3.0539072608698627E-2</v>
       </c>
       <c r="D110" s="26"/>
       <c r="E110" s="269"/>
       <c r="F110" s="26"/>
       <c r="G110" s="94">
-        <f>BS!$G$38/G$4</f>
-        <v>0</v>
-      </c>
-      <c r="H110" s="204"/>
-      <c r="I110" s="204"/>
-      <c r="J110" s="204"/>
-      <c r="K110" s="204"/>
-      <c r="L110" s="204"/>
-      <c r="M110" s="204"/>
-      <c r="N110" s="204"/>
-      <c r="O110" s="204"/>
-      <c r="P110" s="204"/>
-      <c r="Q110" s="204"/>
+        <f t="shared" ref="G110:Q110" si="44">IF(G$4="","",G104/G$4)</f>
+        <v>2.4843978643464503E-2</v>
+      </c>
+      <c r="H110" s="94">
+        <f t="shared" si="44"/>
+        <v>7.1372457421981887E-3</v>
+      </c>
+      <c r="I110" s="94">
+        <f t="shared" si="44"/>
+        <v>1.7366144843177229E-2</v>
+      </c>
+      <c r="J110" s="94">
+        <f t="shared" si="44"/>
+        <v>1.8537786019934374E-2</v>
+      </c>
+      <c r="K110" s="94">
+        <f t="shared" si="44"/>
+        <v>3.0906058142819364E-2</v>
+      </c>
+      <c r="L110" s="94">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="M110" s="94">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="N110" s="94">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="O110" s="94">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="P110" s="94">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="Q110" s="94" t="str">
+        <f t="shared" si="44"/>
+        <v/>
+      </c>
     </row>
     <row r="111" spans="1:17" ht="15.75" customHeight="1">
       <c r="A111" s="10"/>
-      <c r="E111" s="268"/>
+      <c r="B111" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="C111" s="94">
+        <f>BS!$G$38/C$4</f>
+        <v>0</v>
+      </c>
+      <c r="D111" s="26"/>
+      <c r="E111" s="269"/>
+      <c r="F111" s="26"/>
+      <c r="G111" s="94">
+        <f>BS!$G$38/G$4</f>
+        <v>0</v>
+      </c>
+      <c r="H111" s="204"/>
+      <c r="I111" s="204"/>
+      <c r="J111" s="204"/>
+      <c r="K111" s="204"/>
+      <c r="L111" s="204"/>
+      <c r="M111" s="204"/>
+      <c r="N111" s="204"/>
+      <c r="O111" s="204"/>
+      <c r="P111" s="204"/>
+      <c r="Q111" s="204"/>
     </row>
     <row r="112" spans="1:17" ht="15.75" customHeight="1">
       <c r="A112" s="10"/>
-      <c r="B112" s="64" t="s">
-        <v>51</v>
-      </c>
       <c r="E112" s="268"/>
     </row>
     <row r="113" spans="1:17" ht="15.75" customHeight="1">
       <c r="A113" s="10"/>
-      <c r="B113" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="C113" s="169"/>
+      <c r="B113" s="64" t="s">
+        <v>51</v>
+      </c>
       <c r="E113" s="268"/>
-      <c r="G113" s="295">
-        <f>IF(G$4="","",Data!C$22/Data!C15)</f>
-        <v>1.3057336877918428</v>
-      </c>
-      <c r="H113" s="295">
-        <f>IF(H$4="","",Data!D$22/Data!D15)</f>
-        <v>1.9744169551721951</v>
-      </c>
-      <c r="I113" s="295">
-        <f>IF(I$4="","",Data!E$22/Data!E15)</f>
-        <v>1.1630549354549591</v>
-      </c>
-      <c r="J113" s="295">
-        <f>IF(J$4="","",Data!F$22/Data!F15)</f>
-        <v>1.260471094287793</v>
-      </c>
-      <c r="K113" s="295">
-        <f>IF(K$4="","",Data!G$22/Data!G15)</f>
-        <v>0.70481763825473787</v>
-      </c>
-      <c r="L113" s="295">
-        <f>IF(L$4="","",Data!H$22/Data!H15)</f>
-        <v>1.6343627167150878</v>
-      </c>
-      <c r="M113" s="295">
-        <f>IF(M$4="","",Data!I$22/Data!I15)</f>
-        <v>1.4261750734420902</v>
-      </c>
-      <c r="N113" s="295">
-        <f>IF(N$4="","",Data!J$22/Data!J15)</f>
-        <v>1.2985902058542986</v>
-      </c>
-      <c r="O113" s="295">
-        <f>IF(O$4="","",Data!K$22/Data!K15)</f>
-        <v>3.2823548539671279</v>
-      </c>
-      <c r="P113" s="295">
-        <f>IF(P$4="","",Data!L$22/Data!L15)</f>
-        <v>-1.1544903194068661</v>
-      </c>
-      <c r="Q113" s="295" t="str">
-        <f>IF(Q$4="","",Data!M$22/Data!M15)</f>
-        <v/>
-      </c>
     </row>
     <row r="114" spans="1:17" ht="15.75" customHeight="1">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
-        <v>395</v>
+        <v>388</v>
       </c>
       <c r="C114" s="169"/>
       <c r="E114" s="268"/>
       <c r="G114" s="295">
+        <f>IF(G$4="","",Data!C$22/Data!C15)</f>
+        <v>1.3057336877918428</v>
+      </c>
+      <c r="H114" s="295">
+        <f>IF(H$4="","",Data!D$22/Data!D15)</f>
+        <v>1.9744169551721951</v>
+      </c>
+      <c r="I114" s="295">
+        <f>IF(I$4="","",Data!E$22/Data!E15)</f>
+        <v>1.1630549354549591</v>
+      </c>
+      <c r="J114" s="295">
+        <f>IF(J$4="","",Data!F$22/Data!F15)</f>
+        <v>1.260471094287793</v>
+      </c>
+      <c r="K114" s="295">
+        <f>IF(K$4="","",Data!G$22/Data!G15)</f>
+        <v>0.70481763825473787</v>
+      </c>
+      <c r="L114" s="295">
+        <f>IF(L$4="","",Data!H$22/Data!H15)</f>
+        <v>1.6343627167150878</v>
+      </c>
+      <c r="M114" s="295">
+        <f>IF(M$4="","",Data!I$22/Data!I15)</f>
+        <v>1.4261750734420902</v>
+      </c>
+      <c r="N114" s="295">
+        <f>IF(N$4="","",Data!J$22/Data!J15)</f>
+        <v>1.2985902058542986</v>
+      </c>
+      <c r="O114" s="295">
+        <f>IF(O$4="","",Data!K$22/Data!K15)</f>
+        <v>3.2823548539671279</v>
+      </c>
+      <c r="P114" s="295">
+        <f>IF(P$4="","",Data!L$22/Data!L15)</f>
+        <v>-1.1544903194068661</v>
+      </c>
+      <c r="Q114" s="295" t="str">
+        <f>IF(Q$4="","",Data!M$22/Data!M15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="115" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A115" s="10"/>
+      <c r="B115" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="C115" s="169"/>
+      <c r="E115" s="268"/>
+      <c r="G115" s="295">
         <f>IF(G$4="","",Data!C$22/G19)</f>
         <v>1.8600590034912892</v>
       </c>
-      <c r="H114" s="295">
+      <c r="H115" s="295">
         <f>IF(H$4="","",Data!D$22/H19)</f>
         <v>2.5912372285003169</v>
       </c>
-      <c r="I114" s="295">
+      <c r="I115" s="295">
         <f>IF(I$4="","",Data!E$22/I19)</f>
         <v>1.3531719635852699</v>
       </c>
-      <c r="J114" s="295">
+      <c r="J115" s="295">
         <f>IF(J$4="","",Data!F$22/J19)</f>
         <v>1.6513862562439221</v>
       </c>
-      <c r="K114" s="295">
+      <c r="K115" s="295">
         <f>IF(K$4="","",Data!G$22/K19)</f>
         <v>0.99842984534692547</v>
       </c>
-      <c r="L114" s="295">
+      <c r="L115" s="295">
         <f>IF(L$4="","",Data!H$22/L19)</f>
         <v>1.8066191791533639</v>
       </c>
-      <c r="M114" s="295">
+      <c r="M115" s="295">
         <f>IF(M$4="","",Data!I$22/M19)</f>
         <v>1.7341560501990292</v>
       </c>
-      <c r="N114" s="295">
+      <c r="N115" s="295">
         <f>IF(N$4="","",Data!J$22/N19)</f>
         <v>1.7067738949034357</v>
       </c>
-      <c r="O114" s="295">
+      <c r="O115" s="295">
         <f>IF(O$4="","",Data!K$22/O19)</f>
         <v>1.3942527436650844</v>
       </c>
-      <c r="P114" s="295">
+      <c r="P115" s="295">
         <f>IF(P$4="","",Data!L$22/P19)</f>
         <v>11.904562451085539</v>
       </c>
-      <c r="Q114" s="295" t="str">
+      <c r="Q115" s="295" t="str">
         <f>IF(Q$4="","",Data!M$22/Q19)</f>
         <v/>
       </c>
     </row>
-    <row r="115" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A115" s="10"/>
-      <c r="E115" s="268"/>
-    </row>
     <row r="116" spans="1:17" ht="15.75" customHeight="1">
       <c r="A116" s="10"/>
-      <c r="B116" s="91" t="s">
-        <v>38</v>
-      </c>
-      <c r="C116" s="55"/>
-      <c r="D116" s="55"/>
-      <c r="E116" s="271"/>
-      <c r="F116" s="55"/>
-      <c r="G116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*G118*(1/#REF!)=G120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="H116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*H118*(1/#REF!)=H120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="I116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*I118*(1/#REF!)=I120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="J116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*J118*(1/#REF!)=J120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="K116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*K118*(1/#REF!)=K120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="L116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*L118*(1/#REF!)=L120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="M116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*M118*(1/#REF!)=M120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="N116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*N118*(1/#REF!)=N120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="O116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*O118*(1/#REF!)=O120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="P116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*P118*(1/#REF!)=P120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="Q116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*Q118*(1/#REF!)=Q120,"","Error"),"")</f>
-        <v/>
-      </c>
+      <c r="E116" s="268"/>
     </row>
     <row r="117" spans="1:17" ht="15.75" customHeight="1">
       <c r="A117" s="10"/>
-      <c r="B117" s="7" t="s">
-        <v>221</v>
-      </c>
-      <c r="C117" s="23">
+      <c r="B117" s="91" t="s">
+        <v>38</v>
+      </c>
+      <c r="C117" s="55"/>
+      <c r="D117" s="55"/>
+      <c r="E117" s="271"/>
+      <c r="F117" s="55"/>
+      <c r="G117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*G119*(1/#REF!)=G121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="H117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*H119*(1/#REF!)=H121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="I117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*I119*(1/#REF!)=I121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="J117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*J119*(1/#REF!)=J121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="K117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*K119*(1/#REF!)=K121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="L117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*L119*(1/#REF!)=L121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="M117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*M119*(1/#REF!)=M121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="N117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*N119*(1/#REF!)=N121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="O117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*O119*(1/#REF!)=O121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="P117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*P119*(1/#REF!)=P121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="Q117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*Q119*(1/#REF!)=Q121,"","Error"),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="118" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A118" s="10"/>
+      <c r="B118" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="C118" s="23">
         <f>IF(valuation_method="DDM",C13/(C4+C12),C81)</f>
         <v>0.42143224397986156</v>
       </c>
-      <c r="E117" s="268"/>
-      <c r="G117" s="23">
-        <f t="shared" ref="G117:Q117" si="45">IF(G4="","",IF(valuation_method="DDM",G13/(G4+G12),G81))</f>
+      <c r="E118" s="268"/>
+      <c r="G118" s="23">
+        <f t="shared" ref="G118:Q118" si="45">IF(G4="","",IF(valuation_method="DDM",G13/(G4+G12),G81))</f>
         <v>0.45598504835348186</v>
       </c>
-      <c r="H117" s="23">
+      <c r="H118" s="23">
         <f t="shared" si="45"/>
         <v>0.52331611133982803</v>
       </c>
-      <c r="I117" s="23">
+      <c r="I118" s="23">
         <f t="shared" si="45"/>
         <v>0.57870355682784558</v>
       </c>
-      <c r="J117" s="23">
+      <c r="J118" s="23">
         <f t="shared" si="45"/>
         <v>0.55540390178162879</v>
       </c>
-      <c r="K117" s="23">
+      <c r="K118" s="23">
         <f t="shared" si="45"/>
         <v>0.3429381546083502</v>
       </c>
-      <c r="L117" s="23">
+      <c r="L118" s="23">
         <f t="shared" si="45"/>
         <v>0.40224272660641125</v>
       </c>
-      <c r="M117" s="23">
+      <c r="M118" s="23">
         <f t="shared" si="45"/>
         <v>0.40328242601546971</v>
       </c>
-      <c r="N117" s="23">
+      <c r="N118" s="23">
         <f t="shared" si="45"/>
         <v>0.42245534317879263</v>
       </c>
-      <c r="O117" s="23">
+      <c r="O118" s="23">
         <f t="shared" si="45"/>
         <v>0.13032651245797386</v>
       </c>
-      <c r="P117" s="23">
+      <c r="P118" s="23">
         <f t="shared" si="45"/>
         <v>-2.777731867061933E-2</v>
       </c>
-      <c r="Q117" s="23" t="str">
+      <c r="Q118" s="23" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
     </row>
-    <row r="118" spans="1:17" ht="15.75" customHeight="1">
-      <c r="B118" s="7" t="s">
+    <row r="119" spans="1:17" ht="15.75" customHeight="1">
+      <c r="B119" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="C118" s="42">
-        <f>IF(valuation_method="DDM",(C4+C12)/C101,C4/C101)</f>
+      <c r="C119" s="42">
+        <f>IF(valuation_method="DDM",(C4+C12)/C102,C4/C102)</f>
         <v>0.19639123104483397</v>
       </c>
-      <c r="E118" s="268"/>
-      <c r="G118" s="42">
-        <f t="shared" ref="G118:Q118" si="46">IF(G4="","",IF(valuation_method="DDM",(G4+G12)/G101,G4/G101))</f>
+      <c r="E119" s="268"/>
+      <c r="G119" s="42">
+        <f t="shared" ref="G119:Q119" si="46">IF(G4="","",IF(valuation_method="DDM",(G4+G12)/G102,G4/G102))</f>
         <v>0.22035988512352028</v>
       </c>
-      <c r="H118" s="42">
+      <c r="H119" s="42">
         <f t="shared" si="46"/>
         <v>0.26192368118435977</v>
       </c>
-      <c r="I118" s="42">
+      <c r="I119" s="42">
         <f t="shared" si="46"/>
         <v>0.3501065314937884</v>
       </c>
-      <c r="J118" s="42">
+      <c r="J119" s="42">
         <f t="shared" si="46"/>
         <v>0.2855457856155395</v>
       </c>
-      <c r="K118" s="42">
+      <c r="K119" s="42">
         <f t="shared" si="46"/>
         <v>0.18648021899773842</v>
       </c>
-      <c r="L118" s="42">
+      <c r="L119" s="42">
         <f t="shared" si="46"/>
         <v>0.18019653783802789</v>
       </c>
-      <c r="M118" s="42">
+      <c r="M119" s="42">
         <f t="shared" si="46"/>
         <v>0.17345860028887053</v>
       </c>
-      <c r="N118" s="42">
+      <c r="N119" s="42">
         <f t="shared" si="46"/>
         <v>0.16003589825968575</v>
       </c>
-      <c r="O118" s="42">
+      <c r="O119" s="42">
         <f t="shared" si="46"/>
         <v>9.4736275139161247E-2</v>
       </c>
-      <c r="P118" s="42">
+      <c r="P119" s="42">
         <f t="shared" si="46"/>
         <v>9.632675048988866E-2</v>
       </c>
-      <c r="Q118" s="42" t="str">
+      <c r="Q119" s="42" t="str">
         <f t="shared" si="46"/>
         <v/>
       </c>
     </row>
-    <row r="119" spans="1:17" ht="15.75" customHeight="1">
-      <c r="B119" s="7" t="s">
+    <row r="120" spans="1:17" ht="15.75" customHeight="1">
+      <c r="B120" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="C119" s="15">
-        <f>C101/C105</f>
+      <c r="C120" s="15">
+        <f>C102/C106</f>
         <v>1.2141426890285656</v>
       </c>
-      <c r="D119" s="11"/>
-      <c r="E119" s="272"/>
-      <c r="F119" s="11"/>
-      <c r="G119" s="15">
-        <f t="shared" ref="G119:Q119" si="47">IF(G$4="","",G101/G105)</f>
+      <c r="D120" s="11"/>
+      <c r="E120" s="272"/>
+      <c r="F120" s="11"/>
+      <c r="G120" s="15">
+        <f t="shared" ref="G120:Q120" si="47">IF(G$4="","",G102/G106)</f>
         <v>1.2141426890285656</v>
       </c>
-      <c r="H119" s="15">
+      <c r="H120" s="15">
         <f t="shared" si="47"/>
         <v>1.2176996876860735</v>
       </c>
-      <c r="I119" s="15">
+      <c r="I120" s="15">
         <f t="shared" si="47"/>
         <v>1.2562621876415327</v>
       </c>
-      <c r="J119" s="15">
+      <c r="J120" s="15">
         <f t="shared" si="47"/>
         <v>1.2941140005821952</v>
       </c>
-      <c r="K119" s="15">
+      <c r="K120" s="15">
         <f t="shared" si="47"/>
         <v>1.2395789271571973</v>
       </c>
-      <c r="L119" s="15">
+      <c r="L120" s="15">
         <f t="shared" si="47"/>
         <v>1.2596689536129575</v>
       </c>
-      <c r="M119" s="15">
+      <c r="M120" s="15">
         <f t="shared" si="47"/>
         <v>1.2667672718675931</v>
       </c>
-      <c r="N119" s="15">
+      <c r="N120" s="15">
         <f t="shared" si="47"/>
         <v>1.2485635816445315</v>
       </c>
-      <c r="O119" s="15">
+      <c r="O120" s="15">
         <f t="shared" si="47"/>
         <v>1.2195091528986302</v>
       </c>
-      <c r="P119" s="15">
+      <c r="P120" s="15">
         <f t="shared" si="47"/>
         <v>1.2161070458828416</v>
       </c>
-      <c r="Q119" s="15" t="str">
+      <c r="Q120" s="15" t="str">
         <f t="shared" si="47"/>
         <v/>
       </c>
     </row>
-    <row r="120" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A120" s="10"/>
-      <c r="B120" s="70" t="s">
-        <v>222</v>
-      </c>
-      <c r="C120" s="102">
-        <f>C13/C105</f>
+    <row r="121" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A121" s="10"/>
+      <c r="B121" s="70" t="s">
+        <v>221</v>
+      </c>
+      <c r="C121" s="102">
+        <f>C13/C106</f>
         <v>0.10048924474005361</v>
       </c>
-      <c r="D120" s="103"/>
-      <c r="E120" s="271"/>
-      <c r="F120" s="103"/>
-      <c r="G120" s="102">
-        <f>IF(G$4="","",G13/G105)</f>
+      <c r="D121" s="103"/>
+      <c r="E121" s="271"/>
+      <c r="F121" s="103"/>
+      <c r="G121" s="102">
+        <f t="shared" ref="G121:Q121" si="48">IF(G$4="","",G13/G106)</f>
         <v>0.12199804433766272</v>
       </c>
-      <c r="H120" s="102">
-        <f t="shared" ref="H120:Q120" si="48">IF(H$4="","",H13/H105)</f>
+      <c r="H121" s="102">
+        <f t="shared" si="48"/>
         <v>0.16690873517453589</v>
       </c>
-      <c r="I120" s="102">
+      <c r="I121" s="102">
         <f t="shared" si="48"/>
         <v>0.25452863746156656</v>
       </c>
-      <c r="J120" s="102">
+      <c r="J121" s="102">
         <f t="shared" si="48"/>
         <v>0.20523773676990104</v>
       </c>
-      <c r="K120" s="102">
+      <c r="K121" s="102">
         <f t="shared" si="48"/>
         <v>7.927253778973771E-2</v>
       </c>
-      <c r="L120" s="102">
+      <c r="L121" s="102">
         <f t="shared" si="48"/>
         <v>9.1304265696885045E-2</v>
       </c>
-      <c r="M120" s="102">
+      <c r="M121" s="102">
         <f t="shared" si="48"/>
         <v>8.8613924123824517E-2</v>
       </c>
-      <c r="N120" s="102">
+      <c r="N121" s="102">
         <f t="shared" si="48"/>
         <v>8.4412911998912502E-2</v>
       </c>
-      <c r="O120" s="102">
+      <c r="O121" s="102">
         <f t="shared" si="48"/>
         <v>1.5056850660867668E-2</v>
       </c>
-      <c r="P120" s="102">
+      <c r="P121" s="102">
         <f t="shared" si="48"/>
         <v>-3.2539362178983212E-3</v>
       </c>
-      <c r="Q120" s="102" t="str">
+      <c r="Q121" s="102" t="str">
         <f t="shared" si="48"/>
         <v/>
       </c>
     </row>
-    <row r="121" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A121" s="10"/>
-      <c r="B121" s="27"/>
-      <c r="C121" s="62"/>
-      <c r="D121" s="27"/>
-      <c r="E121" s="67"/>
-      <c r="F121" s="27"/>
-      <c r="G121" s="12"/>
-      <c r="H121" s="12"/>
-      <c r="I121" s="12"/>
-      <c r="J121" s="12"/>
-      <c r="K121" s="12"/>
-      <c r="L121" s="12"/>
-      <c r="M121" s="12"/>
-      <c r="N121" s="12"/>
-      <c r="O121" s="12"/>
-      <c r="P121" s="12"/>
-      <c r="Q121" s="12"/>
-    </row>
     <row r="122" spans="1:17" ht="15.75" customHeight="1">
       <c r="A122" s="10"/>
-      <c r="B122" s="54" t="s">
-        <v>223</v>
-      </c>
-      <c r="C122" s="54"/>
-      <c r="D122" s="56"/>
-      <c r="E122" s="66" t="s">
-        <v>59</v>
-      </c>
-      <c r="F122" s="56"/>
-      <c r="G122" s="37"/>
-      <c r="H122" s="37"/>
-      <c r="I122" s="37"/>
-      <c r="J122" s="37"/>
-      <c r="K122" s="37"/>
-      <c r="L122" s="37"/>
-      <c r="M122" s="37"/>
-      <c r="N122" s="37"/>
-      <c r="O122" s="37"/>
-      <c r="P122" s="37"/>
-      <c r="Q122" s="37"/>
+      <c r="B122" s="27"/>
+      <c r="C122" s="62"/>
+      <c r="D122" s="27"/>
+      <c r="E122" s="67"/>
+      <c r="F122" s="27"/>
+      <c r="G122" s="12"/>
+      <c r="H122" s="12"/>
+      <c r="I122" s="12"/>
+      <c r="J122" s="12"/>
+      <c r="K122" s="12"/>
+      <c r="L122" s="12"/>
+      <c r="M122" s="12"/>
+      <c r="N122" s="12"/>
+      <c r="O122" s="12"/>
+      <c r="P122" s="12"/>
+      <c r="Q122" s="12"/>
     </row>
     <row r="123" spans="1:17" ht="15.75" customHeight="1">
       <c r="A123" s="10"/>
-      <c r="B123" s="178" t="s">
-        <v>170</v>
-      </c>
-      <c r="C123" s="179"/>
-      <c r="D123" s="27"/>
-      <c r="E123" s="265"/>
-      <c r="F123" s="27"/>
-      <c r="G123" s="12"/>
-      <c r="H123" s="12"/>
-      <c r="I123" s="12"/>
-      <c r="J123" s="12"/>
-      <c r="K123" s="12"/>
-      <c r="L123" s="12"/>
-      <c r="M123" s="12"/>
-      <c r="N123" s="12"/>
-      <c r="O123" s="12"/>
-      <c r="P123" s="12"/>
-      <c r="Q123" s="12"/>
+      <c r="B123" s="54" t="s">
+        <v>222</v>
+      </c>
+      <c r="C123" s="54"/>
+      <c r="D123" s="56"/>
+      <c r="E123" s="66" t="s">
+        <v>59</v>
+      </c>
+      <c r="F123" s="56"/>
+      <c r="G123" s="37"/>
+      <c r="H123" s="37"/>
+      <c r="I123" s="37"/>
+      <c r="J123" s="37"/>
+      <c r="K123" s="37"/>
+      <c r="L123" s="37"/>
+      <c r="M123" s="37"/>
+      <c r="N123" s="37"/>
+      <c r="O123" s="37"/>
+      <c r="P123" s="37"/>
+      <c r="Q123" s="37"/>
     </row>
     <row r="124" spans="1:17" ht="15.75" customHeight="1">
       <c r="A124" s="10"/>
-      <c r="B124" s="27" t="str">
-        <f>"FCFE per share ("&amp;Market_currency&amp;")"</f>
-        <v>FCFE per share (HKD)</v>
-      </c>
-      <c r="C124" s="177">
-        <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.21445951033987257</v>
-      </c>
+      <c r="B124" s="178" t="s">
+        <v>169</v>
+      </c>
+      <c r="C124" s="179"/>
       <c r="D124" s="27"/>
       <c r="E124" s="265"/>
       <c r="F124" s="27"/>
-      <c r="G124" s="177">
-        <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>0.25025907090639649</v>
-      </c>
-      <c r="H124" s="177">
-        <f t="shared" si="49"/>
-        <v>0.34437205815129318</v>
-      </c>
-      <c r="I124" s="177">
-        <f t="shared" si="49"/>
-        <v>0.55850154606061642</v>
-      </c>
-      <c r="J124" s="177">
-        <f t="shared" si="49"/>
-        <v>0.45889663010515008</v>
-      </c>
-      <c r="K124" s="177">
-        <f t="shared" si="49"/>
-        <v>0.16462839764099138</v>
-      </c>
-      <c r="L124" s="177">
-        <f t="shared" si="49"/>
-        <v>0.20899337153917774</v>
-      </c>
-      <c r="M124" s="177">
-        <f t="shared" si="49"/>
-        <v>0.18608068384863941</v>
-      </c>
-      <c r="N124" s="177">
-        <f t="shared" si="49"/>
-        <v>0.176733721513089</v>
-      </c>
-      <c r="O124" s="177">
-        <f t="shared" si="49"/>
-        <v>3.1285394295740947E-2</v>
-      </c>
-      <c r="P124" s="177">
-        <f t="shared" si="49"/>
-        <v>1.3552761468253434E-2</v>
-      </c>
-      <c r="Q124" s="177" t="str">
-        <f t="shared" si="49"/>
-        <v/>
-      </c>
+      <c r="G124" s="12"/>
+      <c r="H124" s="12"/>
+      <c r="I124" s="12"/>
+      <c r="J124" s="12"/>
+      <c r="K124" s="12"/>
+      <c r="L124" s="12"/>
+      <c r="M124" s="12"/>
+      <c r="N124" s="12"/>
+      <c r="O124" s="12"/>
+      <c r="P124" s="12"/>
+      <c r="Q124" s="12"/>
     </row>
     <row r="125" spans="1:17" ht="15.75" customHeight="1">
       <c r="A125" s="10"/>
-      <c r="B125" s="27" t="s">
-        <v>269</v>
-      </c>
-      <c r="C125" s="77">
-        <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>7.9724725033409882E-2</v>
+      <c r="B125" s="27" t="str">
+        <f>"FCFE per share ("&amp;Market_currency&amp;")"</f>
+        <v>FCFE per share (HKD)</v>
+      </c>
+      <c r="C125" s="177">
+        <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
+        <v>0.21445951033987257</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
-      <c r="G125" s="77">
-        <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
+      <c r="G125" s="177">
+        <f t="shared" ref="G125:Q125" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
+        <v>0.25025907090639649</v>
+      </c>
+      <c r="H125" s="177">
+        <f t="shared" si="49"/>
+        <v>0.34437205815129318</v>
+      </c>
+      <c r="I125" s="177">
+        <f t="shared" si="49"/>
+        <v>0.55850154606061642</v>
+      </c>
+      <c r="J125" s="177">
+        <f t="shared" si="49"/>
+        <v>0.45889663010515008</v>
+      </c>
+      <c r="K125" s="177">
+        <f t="shared" si="49"/>
+        <v>0.16462839764099138</v>
+      </c>
+      <c r="L125" s="177">
+        <f t="shared" si="49"/>
+        <v>0.20899337153917774</v>
+      </c>
+      <c r="M125" s="177">
+        <f t="shared" si="49"/>
+        <v>0.18608068384863941</v>
+      </c>
+      <c r="N125" s="177">
+        <f t="shared" si="49"/>
+        <v>0.176733721513089</v>
+      </c>
+      <c r="O125" s="177">
+        <f t="shared" si="49"/>
+        <v>3.1285394295740947E-2</v>
+      </c>
+      <c r="P125" s="177">
+        <f t="shared" si="49"/>
+        <v>1.3552761468253434E-2</v>
+      </c>
+      <c r="Q125" s="177" t="str">
+        <f t="shared" si="49"/>
+        <v/>
+      </c>
+    </row>
+    <row r="126" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A126" s="10"/>
+      <c r="B126" s="27" t="s">
+        <v>268</v>
+      </c>
+      <c r="C126" s="77">
+        <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
+        <v>7.9724725033409882E-2</v>
+      </c>
+      <c r="D126" s="27"/>
+      <c r="E126" s="265"/>
+      <c r="F126" s="27"/>
+      <c r="G126" s="77">
+        <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
         <v>9.3033111861113932E-2</v>
       </c>
-      <c r="H125" s="77">
-        <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
+      <c r="H126" s="77">
+        <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
         <v>0.12801935247259968</v>
       </c>
-      <c r="I125" s="77">
-        <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
+      <c r="I126" s="77">
+        <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
         <v>0.20762139258758974</v>
       </c>
-      <c r="J125" s="77">
-        <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
+      <c r="J126" s="77">
+        <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
         <v>0.17059354279001862</v>
       </c>
-      <c r="K125" s="77">
-        <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
+      <c r="K126" s="77">
+        <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
         <v>6.1200147821929882E-2</v>
       </c>
-      <c r="L125" s="77">
-        <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
+      <c r="L126" s="77">
+        <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
         <v>7.7692703174415526E-2</v>
       </c>
-      <c r="M125" s="77">
-        <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
+      <c r="M126" s="77">
+        <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
         <v>6.9174975408416134E-2</v>
       </c>
-      <c r="N125" s="77">
-        <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
+      <c r="N126" s="77">
+        <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
         <v>6.5700268220479183E-2</v>
       </c>
-      <c r="O125" s="77">
-        <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
+      <c r="O126" s="77">
+        <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
         <v>1.1630258102505928E-2</v>
       </c>
-      <c r="P125" s="77">
-        <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
+      <c r="P126" s="77">
+        <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
         <v>5.0382012893135444E-3</v>
       </c>
-      <c r="Q125" s="77" t="str">
-        <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
+      <c r="Q126" s="77" t="str">
+        <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
         <v/>
       </c>
     </row>
-    <row r="126" spans="1:17" ht="15.75" customHeight="1">
-      <c r="B126" s="2" t="s">
-        <v>397</v>
-      </c>
-      <c r="C126" s="169"/>
-      <c r="G126" s="23">
+    <row r="127" spans="1:17" ht="15.75" customHeight="1">
+      <c r="B127" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C127" s="169"/>
+      <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
         <v>0.13252861510582697</v>
       </c>
-      <c r="H126" s="23">
+      <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
         <v>0.16801340326140654</v>
       </c>
-      <c r="I126" s="23">
+      <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
         <v>0.24155991168220889</v>
       </c>
-      <c r="J126" s="23">
+      <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
         <v>0.22350043031060127</v>
       </c>
-      <c r="K126" s="23">
+      <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
         <v>8.669484247920306E-2</v>
       </c>
-      <c r="L126" s="23">
+      <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
         <v>8.5881258914961622E-2</v>
       </c>
-      <c r="M126" s="23">
+      <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
         <v>8.4113237119863946E-2</v>
       </c>
-      <c r="N126" s="23">
+      <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
         <v>8.6351723724188659E-2</v>
       </c>
-      <c r="O126" s="23">
+      <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
         <v>4.9402090847531404E-3</v>
       </c>
-      <c r="P126" s="23">
+      <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
         <v>-5.1951567615211372E-2</v>
       </c>
-      <c r="Q126" s="23" t="str">
+      <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
         <v/>
       </c>
     </row>
-    <row r="127" spans="1:17" ht="15.75" customHeight="1"/>
     <row r="128" spans="1:17" ht="15.75" customHeight="1"/>
     <row r="129" ht="15.75" customHeight="1"/>
     <row r="130" ht="15.75" customHeight="1"/>
@@ -15406,6 +15436,7 @@
     <row r="806" ht="15.75" customHeight="1"/>
     <row r="807" ht="15.75" customHeight="1"/>
     <row r="808" ht="15.75" customHeight="1"/>
+    <row r="809" ht="15.75" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="G4:Q13 G15:Q16 G23:Q24 G34:Q34">
@@ -15413,7 +15444,7 @@
       <formula>ISBLANK(G4)</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="1">
+  <dataValidations disablePrompts="1" count="1">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G1" xr:uid="{00000000-0002-0000-0100-000001000000}"/>
   </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -15450,20 +15481,20 @@
     </row>
     <row r="3" spans="2:8" ht="13.15">
       <c r="B3" s="109" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C3" s="107">
         <f>scaling_factor</f>
         <v>1000</v>
       </c>
       <c r="E3" s="109" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H3" s="120"/>
     </row>
     <row r="4" spans="2:8">
       <c r="B4" s="100" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C4" s="338">
         <f>Normalized_FCF!C19</f>
@@ -15474,7 +15505,7 @@
         <v>HKD</v>
       </c>
       <c r="E4" s="100" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F4" s="134">
         <f>Terminal_Growth</f>
@@ -15484,7 +15515,7 @@
     </row>
     <row r="5" spans="2:8">
       <c r="B5" s="205" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C5" s="206">
         <f>Equity_Cost</f>
@@ -15495,7 +15526,7 @@
     </row>
     <row r="6" spans="2:8" ht="13.35" customHeight="1">
       <c r="B6" s="149" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C6" s="347">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
@@ -15505,15 +15536,15 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E6" s="364" t="s">
-        <v>249</v>
-      </c>
-      <c r="F6" s="364"/>
+      <c r="E6" s="366" t="s">
+        <v>248</v>
+      </c>
+      <c r="F6" s="366"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8">
       <c r="B7" s="148" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C7" s="338">
         <f>BS!G31</f>
@@ -15523,13 +15554,13 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E7" s="364"/>
-      <c r="F7" s="364"/>
+      <c r="E7" s="366"/>
+      <c r="F7" s="366"/>
       <c r="H7" s="120"/>
     </row>
     <row r="8" spans="2:8">
       <c r="B8" s="148" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C8" s="338">
         <f>BS!D66</f>
@@ -15539,13 +15570,13 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E8" s="364"/>
-      <c r="F8" s="364"/>
+      <c r="E8" s="366"/>
+      <c r="F8" s="366"/>
       <c r="H8" s="120"/>
     </row>
     <row r="9" spans="2:8">
       <c r="B9" s="205" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C9" s="348">
         <f>BS!H42</f>
@@ -15555,13 +15586,13 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E9" s="364"/>
-      <c r="F9" s="364"/>
+      <c r="E9" s="366"/>
+      <c r="F9" s="366"/>
       <c r="H9" s="120"/>
     </row>
     <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="149" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C10" s="347">
         <f>C6-C7+C8+C9</f>
@@ -15575,7 +15606,7 @@
     </row>
     <row r="11" spans="2:8" ht="13.15" thickBot="1">
       <c r="B11" s="207" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C11" s="208">
         <f>Exchange_Rate</f>
@@ -15606,7 +15637,7 @@
     </row>
     <row r="14" spans="2:8" ht="13.9">
       <c r="B14" s="36" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C14" s="37"/>
       <c r="D14" s="37"/>
@@ -15616,23 +15647,23 @@
     </row>
     <row r="15" spans="2:8" ht="13.15">
       <c r="B15" s="119" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H15" s="120"/>
     </row>
     <row r="16" spans="2:8" ht="13.35" customHeight="1">
       <c r="B16" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C16" s="161">
         <f>Scenarios!C65</f>
-        <v>1.280056444784558E-3</v>
+        <v>1.28005644478456E-3</v>
       </c>
       <c r="H16" s="120"/>
     </row>
     <row r="17" spans="2:17" ht="13.35" customHeight="1">
       <c r="B17" s="118" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C17" s="162">
         <f>Scenarios!C64</f>
@@ -15665,7 +15696,7 @@
         <v>108</v>
       </c>
       <c r="D20" s="128" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E20" s="128" t="s">
         <v>109</v>
@@ -15685,7 +15716,7 @@
       </c>
       <c r="D21" s="138">
         <f>IF($C$17&lt;B21,0,DCF!$C$16)</f>
-        <v>1.280056444784558E-3</v>
+        <v>1.28005644478456E-3</v>
       </c>
       <c r="E21" s="124">
         <f t="shared" ref="E21:E50" si="0">IF($C$17&lt;B21,0,1/(1+Equity_Cost)^B21)</f>
@@ -15707,7 +15738,7 @@
       </c>
       <c r="D22" s="138">
         <f>IF($C$17&lt;B22,0,DCF!$C$16)</f>
-        <v>1.280056444784558E-3</v>
+        <v>1.28005644478456E-3</v>
       </c>
       <c r="E22" s="124">
         <f t="shared" si="0"/>
@@ -15729,7 +15760,7 @@
       </c>
       <c r="D23" s="138">
         <f>IF($C$17&lt;B23,0,DCF!$C$16)</f>
-        <v>1.280056444784558E-3</v>
+        <v>1.28005644478456E-3</v>
       </c>
       <c r="E23" s="124">
         <f t="shared" si="0"/>
@@ -15761,7 +15792,7 @@
       </c>
       <c r="D24" s="138">
         <f>IF($C$17&lt;B24,0,DCF!$C$16)</f>
-        <v>1.280056444784558E-3</v>
+        <v>1.28005644478456E-3</v>
       </c>
       <c r="E24" s="124">
         <f t="shared" si="0"/>
@@ -15793,7 +15824,7 @@
       </c>
       <c r="D25" s="138">
         <f>IF($C$17&lt;B25,0,DCF!$C$16)</f>
-        <v>1.280056444784558E-3</v>
+        <v>1.28005644478456E-3</v>
       </c>
       <c r="E25" s="124">
         <f t="shared" si="0"/>
@@ -16437,7 +16468,7 @@
     </row>
     <row r="51" spans="1:17">
       <c r="B51" s="126" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C51" s="123">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
@@ -16474,7 +16505,7 @@
     </row>
     <row r="54" spans="1:17" ht="13.15">
       <c r="B54" s="119" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C54" s="136"/>
       <c r="D54" s="136"/>
@@ -16695,7 +16726,7 @@
     </row>
     <row r="63" spans="1:17" ht="13.15">
       <c r="B63" s="119" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C63" s="338"/>
       <c r="D63" s="114"/>
@@ -16924,19 +16955,19 @@
     </row>
     <row r="73" spans="1:8" ht="13.15">
       <c r="B73" s="171" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C73" s="171" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D73" s="171" t="s">
+        <v>111</v>
+      </c>
+      <c r="E73" s="172" t="s">
         <v>112</v>
       </c>
-      <c r="E73" s="172" t="s">
-        <v>113</v>
-      </c>
       <c r="F73" s="172" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="74" spans="1:8">
@@ -17061,7 +17092,7 @@
     </row>
     <row r="80" spans="1:8">
       <c r="B80" s="155" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="C80" s="155" t="s">
         <v>105</v>
@@ -17198,7 +17229,7 @@
   <sheetData>
     <row r="2" spans="2:8" ht="13.9">
       <c r="B2" s="36" t="s">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
@@ -17210,31 +17241,31 @@
     </row>
     <row r="3" spans="2:8" ht="13.15">
       <c r="B3" s="109" t="s">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="C3" s="107">
         <f>scaling_factor</f>
         <v>1000</v>
       </c>
       <c r="E3" s="109" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H3" s="120"/>
     </row>
     <row r="4" spans="2:8">
       <c r="B4" s="100" t="s">
-        <v>442</v>
+        <v>436</v>
       </c>
       <c r="C4" s="114">
-        <f>Normalized_FCF!C91</f>
-        <v>1527319.7309999999</v>
+        <f>Normalized_FCF!C91*(1-dividend_tax_rate)</f>
+        <v>1374587.7578999999</v>
       </c>
       <c r="D4" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
       <c r="E4" s="100" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F4" s="134">
         <f>Thesis!E22</f>
@@ -17244,7 +17275,7 @@
     </row>
     <row r="5" spans="2:8">
       <c r="B5" s="205" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C5" s="206">
         <f>Equity_Cost</f>
@@ -17255,27 +17286,27 @@
     </row>
     <row r="6" spans="2:8" ht="13.35" customHeight="1">
       <c r="B6" s="149" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="C6" s="319">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>20364263.079999998</v>
+        <v>18327836.772</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E6" s="364"/>
-      <c r="F6" s="364"/>
+      <c r="E6" s="366"/>
+      <c r="F6" s="366"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8" ht="13.15">
       <c r="B7" s="149" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="C7" s="111">
         <f>(C6*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="D7" t="str">
         <f>Market_currency</f>
@@ -17288,7 +17319,7 @@
     </row>
     <row r="9" spans="2:8" ht="13.9">
       <c r="B9" s="36" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C9" s="37"/>
       <c r="D9" s="37"/>
@@ -17298,23 +17329,23 @@
     </row>
     <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="119" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H10" s="120"/>
     </row>
     <row r="11" spans="2:8" ht="13.35" customHeight="1">
       <c r="B11" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C11" s="161">
         <f>Scenarios!C65</f>
-        <v>1.280056444784558E-3</v>
+        <v>1.28005644478456E-3</v>
       </c>
       <c r="H11" s="120"/>
     </row>
     <row r="12" spans="2:8" ht="13.35" customHeight="1">
       <c r="B12" s="118" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C12" s="162">
         <f>Scenarios!C64</f>
@@ -17328,7 +17359,7 @@
       </c>
       <c r="C13" s="140">
         <f>F47/Common_Shares*scaling_factor</f>
-        <v>4.0080106343585813</v>
+        <v>3.6072095709227234</v>
       </c>
       <c r="D13" t="str">
         <f>Market_currency</f>
@@ -17344,16 +17375,16 @@
         <v>107</v>
       </c>
       <c r="C15" s="128" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="D15" s="128" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E15" s="128" t="s">
         <v>109</v>
       </c>
       <c r="F15" s="129" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="H15" s="120"/>
     </row>
@@ -17363,11 +17394,11 @@
       </c>
       <c r="C16" s="123">
         <f>C4*(1+D16)</f>
-        <v>1529274.786464913</v>
+        <v>1376347.3078184216</v>
       </c>
       <c r="D16" s="138">
         <f>IF($C$12&lt;B16,0,DDM!$C$11)</f>
-        <v>1.280056444784558E-3</v>
+        <v>1.28005644478456E-3</v>
       </c>
       <c r="E16" s="124">
         <f t="shared" ref="E16:E45" si="0">IF($C$12&lt;B16,0,1/(1+Equity_Cost)^B16)</f>
@@ -17375,7 +17406,7 @@
       </c>
       <c r="F16" s="125">
         <f t="shared" ref="F16:F46" si="1">C16*E16</f>
-        <v>1422581.196711547</v>
+        <v>1280323.0770403922</v>
       </c>
       <c r="H16" s="120"/>
     </row>
@@ -17385,11 +17416,11 @@
       </c>
       <c r="C17" s="123">
         <f t="shared" ref="C17:C45" si="2">IF(ROW()-ROW($C$16)&lt;$C$12, $C$16*(1+D17)^(ROW()-ROW($C$16)), 0)</f>
-        <v>1531232.3445111739</v>
+        <v>1378109.1100600564</v>
       </c>
       <c r="D17" s="138">
         <f>IF($C$12&lt;B17,0,DDM!$C$11)</f>
-        <v>1.280056444784558E-3</v>
+        <v>1.28005644478456E-3</v>
       </c>
       <c r="E17" s="124">
         <f t="shared" si="0"/>
@@ -17397,7 +17428,7 @@
       </c>
       <c r="F17" s="125">
         <f t="shared" si="1"/>
-        <v>1325025.2845959321</v>
+        <v>1192522.7561363387</v>
       </c>
       <c r="H17" s="120"/>
     </row>
@@ -17407,11 +17438,11 @@
       </c>
       <c r="C18" s="123">
         <f t="shared" si="2"/>
-        <v>1533192.4083422283</v>
+        <v>1379873.1675080052</v>
       </c>
       <c r="D18" s="138">
         <f>IF($C$12&lt;B18,0,DDM!$C$11)</f>
-        <v>1.280056444784558E-3</v>
+        <v>1.28005644478456E-3</v>
       </c>
       <c r="E18" s="124">
         <f t="shared" si="0"/>
@@ -17419,7 +17450,7 @@
       </c>
       <c r="F18" s="125">
         <f t="shared" si="1"/>
-        <v>1234159.4341869599</v>
+        <v>1110743.4907682638</v>
       </c>
       <c r="H18" s="120"/>
     </row>
@@ -17429,11 +17460,11 @@
       </c>
       <c r="C19" s="123">
         <f t="shared" si="2"/>
-        <v>1535154.9811656214</v>
+        <v>1381639.4830490591</v>
       </c>
       <c r="D19" s="138">
         <f>IF($C$12&lt;B19,0,DDM!$C$11)</f>
-        <v>1.280056444784558E-3</v>
+        <v>1.28005644478456E-3</v>
       </c>
       <c r="E19" s="124">
         <f t="shared" si="0"/>
@@ -17441,7 +17472,7 @@
       </c>
       <c r="F19" s="125">
         <f t="shared" si="1"/>
-        <v>1149524.8631856581</v>
+        <v>1034572.3768670922</v>
       </c>
       <c r="H19" s="120"/>
     </row>
@@ -17451,11 +17482,11 @@
       </c>
       <c r="C20" s="123">
         <f t="shared" si="2"/>
-        <v>1537120.0661930058</v>
+        <v>1383408.0595737051</v>
       </c>
       <c r="D20" s="138">
         <f>IF($C$12&lt;B20,0,DDM!$C$11)</f>
-        <v>1.280056444784558E-3</v>
+        <v>1.28005644478456E-3</v>
       </c>
       <c r="E20" s="124">
         <f t="shared" si="0"/>
@@ -17463,7 +17494,7 @@
       </c>
       <c r="F20" s="125">
         <f t="shared" si="1"/>
-        <v>1070694.2510653201</v>
+        <v>963624.82595878805</v>
       </c>
       <c r="H20" s="120"/>
     </row>
@@ -18019,11 +18050,11 @@
     </row>
     <row r="46" spans="2:8">
       <c r="B46" s="126" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C46" s="123">
         <f>C$16*(1+F4)^$C$12/Equity_Cost</f>
-        <v>20390330.486198843</v>
+        <v>18351297.437578958</v>
       </c>
       <c r="D46" s="139">
         <f>Terminal_Growth</f>
@@ -18035,7 +18066,7 @@
       </c>
       <c r="F46" s="125">
         <f t="shared" si="1"/>
-        <v>14203060.716633545</v>
+        <v>12782754.64497019</v>
       </c>
       <c r="H46" s="120"/>
     </row>
@@ -18046,7 +18077,7 @@
       </c>
       <c r="F47" s="137">
         <f>SUM(F16:F46)</f>
-        <v>20405045.746378962</v>
+        <v>18364541.171741065</v>
       </c>
       <c r="H47" s="120"/>
     </row>
@@ -18056,7 +18087,7 @@
     </row>
     <row r="49" spans="1:8" ht="13.15">
       <c r="B49" s="119" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C49" s="136"/>
       <c r="D49" s="136"/>
@@ -18067,7 +18098,7 @@
     <row r="50" spans="1:8" ht="13.15">
       <c r="A50" s="133">
         <f>F47</f>
-        <v>20405045.746378962</v>
+        <v>18364541.171741065</v>
       </c>
       <c r="B50" s="131">
         <f>C73</f>
@@ -18097,19 +18128,19 @@
       </c>
       <c r="B51" s="123">
         <f t="dataTable" ref="B51:F56" dt2D="1" dtr="1" r1="C11" r2="C12"/>
-        <v>19125995.620932922</v>
+        <v>17213396.058839627</v>
       </c>
       <c r="C51" s="123">
-        <v>19736512.564586785</v>
+        <v>17762861.308128104</v>
       </c>
       <c r="D51" s="123">
-        <v>20364263.079999998</v>
+        <v>18327836.772</v>
       </c>
       <c r="E51" s="123">
-        <v>21010024.111913007</v>
+        <v>18909021.700721703</v>
       </c>
       <c r="F51" s="123">
-        <v>21674597.422972955</v>
+        <v>19507137.680675663</v>
       </c>
       <c r="H51" s="120"/>
     </row>
@@ -18118,19 +18149,19 @@
         <v>10</v>
       </c>
       <c r="B52" s="123">
-        <v>18122453.631622031</v>
+        <v>16310208.268459827</v>
       </c>
       <c r="C52" s="123">
-        <v>19192418.818388306</v>
+        <v>17273176.936549474</v>
       </c>
       <c r="D52" s="123">
-        <v>20364263.080000002</v>
+        <v>18327836.772000004</v>
       </c>
       <c r="E52" s="123">
-        <v>21650379.037385523</v>
+        <v>19485341.133646969</v>
       </c>
       <c r="F52" s="123">
-        <v>23064580.02361754</v>
+        <v>20758122.021255791</v>
       </c>
       <c r="H52" s="120"/>
     </row>
@@ -18139,19 +18170,19 @@
         <v>15</v>
       </c>
       <c r="B53" s="123">
-        <v>17021081.604457933</v>
+        <v>15318973.444012141</v>
       </c>
       <c r="C53" s="123">
-        <v>18567536.754873864</v>
+        <v>16710783.079386476</v>
       </c>
       <c r="D53" s="123">
-        <v>20364263.080000002</v>
+        <v>18327836.772</v>
       </c>
       <c r="E53" s="123">
-        <v>22461143.362693436</v>
+        <v>20215029.026424088</v>
       </c>
       <c r="F53" s="123">
-        <v>24918097.4411203</v>
+        <v>22426287.697008274</v>
       </c>
       <c r="H53" s="120"/>
     </row>
@@ -18160,19 +18191,19 @@
         <v>20</v>
       </c>
       <c r="B54" s="123">
-        <v>16025396.924084028</v>
+        <v>14422857.231675627</v>
       </c>
       <c r="C54" s="123">
-        <v>17977449.808773149</v>
+        <v>16179704.827895835</v>
       </c>
       <c r="D54" s="123">
-        <v>20364263.080000002</v>
+        <v>18327836.772000004</v>
       </c>
       <c r="E54" s="123">
-        <v>23306378.399073903</v>
+        <v>20975740.559166513</v>
       </c>
       <c r="F54" s="123">
-        <v>26959457.311348669</v>
+        <v>24263511.580213804</v>
       </c>
       <c r="H54" s="120"/>
     </row>
@@ -18181,19 +18212,19 @@
         <v>25</v>
       </c>
       <c r="B55" s="123">
-        <v>15202058.244052194</v>
+        <v>13681852.419646977</v>
       </c>
       <c r="C55" s="123">
-        <v>17468939.7735838</v>
+        <v>15722045.796225419</v>
       </c>
       <c r="D55" s="123">
-        <v>20364263.080000002</v>
+        <v>18327836.772000004</v>
       </c>
       <c r="E55" s="123">
-        <v>24110847.074851751</v>
+        <v>21699762.367366578</v>
       </c>
       <c r="F55" s="123">
-        <v>29017220.878873013</v>
+        <v>26115498.790985707</v>
       </c>
       <c r="H55" s="120"/>
     </row>
@@ -18202,19 +18233,19 @@
         <v>30</v>
       </c>
       <c r="B56" s="123">
-        <v>14554842.030603953</v>
+        <v>13099357.827543562</v>
       </c>
       <c r="C56" s="123">
-        <v>17053356.088957295</v>
+        <v>15348020.480061561</v>
       </c>
       <c r="D56" s="123">
-        <v>20364263.080000006</v>
+        <v>18327836.772000004</v>
       </c>
       <c r="E56" s="123">
-        <v>24837102.205635149</v>
+        <v>22353391.985071633</v>
       </c>
       <c r="F56" s="123">
-        <v>30989426.459175114</v>
+        <v>27890483.813257601</v>
       </c>
       <c r="H56" s="120"/>
     </row>
@@ -18227,7 +18258,7 @@
     </row>
     <row r="58" spans="1:8" ht="13.15">
       <c r="B58" s="119" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C58" s="114"/>
       <c r="D58" s="114"/>
@@ -18264,23 +18295,23 @@
       </c>
       <c r="B60" s="124">
         <f>C7</f>
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="C60" s="124">
         <f>C7</f>
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="D60" s="124">
         <f>C7</f>
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="E60" s="141">
         <f>C7</f>
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="F60" s="124">
         <f>C7</f>
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="H60" s="120"/>
     </row>
@@ -18291,23 +18322,23 @@
       </c>
       <c r="B61" s="124">
         <f t="shared" ref="B61:F66" si="4">B51/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>3.7567763774799796</v>
+        <v>3.3810987397319807</v>
       </c>
       <c r="C61" s="124">
         <f t="shared" si="4"/>
-        <v>3.8766956578890914</v>
+        <v>3.4890260921001817</v>
       </c>
       <c r="D61" s="124">
         <f t="shared" si="4"/>
-        <v>3.9999999999999991</v>
+        <v>3.6</v>
       </c>
       <c r="E61" s="124">
         <f t="shared" si="4"/>
-        <v>4.1268420132614008</v>
+        <v>3.714157811935261</v>
       </c>
       <c r="F61" s="124">
         <f t="shared" si="4"/>
-        <v>4.2573791819179254</v>
+        <v>3.8316412637261341</v>
       </c>
       <c r="H61" s="120"/>
     </row>
@@ -18318,23 +18349,23 @@
       </c>
       <c r="B62" s="124">
         <f t="shared" si="4"/>
-        <v>3.5596581247116812</v>
+        <v>3.2036923122405128</v>
       </c>
       <c r="C62" s="124">
         <f t="shared" si="4"/>
-        <v>3.7698233897277476</v>
+        <v>3.3928410507549724</v>
       </c>
       <c r="D62" s="124">
         <f t="shared" si="4"/>
-        <v>4</v>
+        <v>3.600000000000001</v>
       </c>
       <c r="E62" s="124">
         <f t="shared" si="4"/>
-        <v>4.2526221454384245</v>
+        <v>3.8273599308945814</v>
       </c>
       <c r="F62" s="124">
         <f t="shared" si="4"/>
-        <v>4.5304030758214973</v>
+        <v>4.0773627682393494</v>
       </c>
       <c r="H62" s="120"/>
     </row>
@@ -18345,23 +18376,23 @@
       </c>
       <c r="B63" s="124">
         <f t="shared" si="4"/>
-        <v>3.3433238487622079</v>
+        <v>3.0089914638859874</v>
       </c>
       <c r="C63" s="124">
         <f t="shared" si="4"/>
-        <v>3.6470824761853087</v>
+        <v>3.2823742285667774</v>
       </c>
       <c r="D63" s="124">
         <f t="shared" si="4"/>
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="E63" s="124">
         <f t="shared" si="4"/>
-        <v>4.4118745224329396</v>
+        <v>3.9706870701896446</v>
       </c>
       <c r="F63" s="124">
         <f t="shared" si="4"/>
-        <v>4.8944756494709951</v>
+        <v>4.405028084523896</v>
       </c>
       <c r="H63" s="120"/>
     </row>
@@ -18372,23 +18403,23 @@
       </c>
       <c r="B64" s="124">
         <f t="shared" si="4"/>
-        <v>3.1477489484650731</v>
+        <v>2.8329740536185661</v>
       </c>
       <c r="C64" s="124">
         <f t="shared" si="4"/>
-        <v>3.5311761075074757</v>
+        <v>3.1780584967567282</v>
       </c>
       <c r="D64" s="124">
         <f t="shared" si="4"/>
-        <v>4</v>
+        <v>3.600000000000001</v>
       </c>
       <c r="E64" s="124">
         <f t="shared" si="4"/>
-        <v>4.5778977235789871</v>
+        <v>4.1201079512210885</v>
       </c>
       <c r="F64" s="124">
         <f t="shared" si="4"/>
-        <v>5.2954447122274493</v>
+        <v>4.7659002410047053</v>
       </c>
       <c r="H64" s="120"/>
     </row>
@@ -18399,23 +18430,23 @@
       </c>
       <c r="B65" s="124">
         <f t="shared" si="4"/>
-        <v>2.9860266849493469</v>
+        <v>2.6874240164544125</v>
       </c>
       <c r="C65" s="124">
         <f t="shared" si="4"/>
-        <v>3.4312932817569552</v>
+        <v>3.0881639535812595</v>
       </c>
       <c r="D65" s="124">
         <f t="shared" si="4"/>
-        <v>4</v>
+        <v>3.600000000000001</v>
       </c>
       <c r="E65" s="124">
         <f t="shared" si="4"/>
-        <v>4.7359134931882343</v>
+        <v>4.2623221438694117</v>
       </c>
       <c r="F65" s="124">
         <f t="shared" si="4"/>
-        <v>5.6996358306471091</v>
+        <v>5.1296722475823975</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="13.15">
@@ -18425,40 +18456,40 @@
       </c>
       <c r="B66" s="124">
         <f t="shared" si="4"/>
-        <v>2.8588988412545988</v>
+        <v>2.5730089571291401</v>
       </c>
       <c r="C66" s="124">
         <f t="shared" si="4"/>
-        <v>3.3496632845419505</v>
+        <v>3.014696956087755</v>
       </c>
       <c r="D66" s="124">
         <f t="shared" si="4"/>
-        <v>4.0000000000000009</v>
+        <v>3.600000000000001</v>
       </c>
       <c r="E66" s="124">
         <f t="shared" si="4"/>
-        <v>4.8785663607003737</v>
+        <v>4.3907097246303373</v>
       </c>
       <c r="F66" s="124">
         <f t="shared" si="4"/>
-        <v>6.0870214330731605</v>
+        <v>5.4783192897658441</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="13.15">
       <c r="B68" s="171" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C68" s="171" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D68" s="171" t="s">
+        <v>111</v>
+      </c>
+      <c r="E68" s="172" t="s">
         <v>112</v>
       </c>
-      <c r="E68" s="172" t="s">
-        <v>113</v>
-      </c>
       <c r="F68" s="172" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="69" spans="1:8">
@@ -18476,7 +18507,7 @@
       </c>
       <c r="E69" s="135">
         <f>INDEX(B$60:F$66, MATCH(D69, A$60:A$66, 0), MATCH(C69, B$59:F$59, 0))</f>
-        <v>4.5304030758214973</v>
+        <v>4.0773627682393494</v>
       </c>
       <c r="F69" s="142">
         <f>Scenarios!C58</f>
@@ -18498,7 +18529,7 @@
       </c>
       <c r="E70" s="135">
         <f>INDEX(B$60:F$66, MATCH(D70, A$60:A$66, 0), MATCH(C70, B$59:F$59, 0))</f>
-        <v>4.1268420132614008</v>
+        <v>3.714157811935261</v>
       </c>
       <c r="F70" s="142">
         <f>Scenarios!C40*(1-F$69-F$73)</f>
@@ -18521,7 +18552,7 @@
       </c>
       <c r="E71" s="135">
         <f>INDEX(B$60:F$66, MATCH(D71, A$60:A$66, 0), MATCH(C71, B$59:F$59, 0))</f>
-        <v>3.9999999999999991</v>
+        <v>3.6</v>
       </c>
       <c r="F71" s="142">
         <f>Scenarios!C28*(1-F$69-F$73)</f>
@@ -18544,7 +18575,7 @@
       </c>
       <c r="E72" s="135">
         <f>INDEX(B$60:F$66, MATCH(D72, A$60:A$66, 0), MATCH(C72, B$59:F$59, 0))</f>
-        <v>3.8766956578890914</v>
+        <v>3.4890260921001817</v>
       </c>
       <c r="F72" s="142">
         <f>Scenarios!C34*(1-F$69-F$73)</f>
@@ -18567,7 +18598,7 @@
       </c>
       <c r="E73" s="135">
         <f>INDEX(B$60:F$66, MATCH(D73, A$60:A$66, 0), MATCH(C73, B$59:F$59, 0))</f>
-        <v>3.5596581247116812</v>
+        <v>3.2036923122405128</v>
       </c>
       <c r="F73" s="142">
         <f>Scenarios!C52</f>
@@ -18583,7 +18614,7 @@
     </row>
     <row r="75" spans="1:8">
       <c r="B75" s="155" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="C75" s="155" t="s">
         <v>105</v>
@@ -18647,20 +18678,20 @@
   <sheetData>
     <row r="2" spans="2:9" ht="13.9">
       <c r="B2" s="36" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
       <c r="H2" s="248" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="I2" s="249"/>
     </row>
     <row r="3" spans="2:9" ht="13.15">
       <c r="B3" s="159" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H3" s="247">
         <v>0</v>
@@ -18672,14 +18703,14 @@
     </row>
     <row r="4" spans="2:9">
       <c r="B4" s="152" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C4" s="120">
         <v>3</v>
       </c>
       <c r="D4" s="120"/>
       <c r="E4" s="155" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F4" s="155"/>
       <c r="H4" s="247">
@@ -18687,7 +18718,7 @@
       </c>
       <c r="I4" s="124">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="5" spans="2:9">
@@ -18696,7 +18727,7 @@
       </c>
       <c r="I5" s="124">
         <f t="shared" si="0"/>
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="13.15">
@@ -18708,7 +18739,7 @@
         <v>1000</v>
       </c>
       <c r="E6" s="100" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F6" s="100"/>
       <c r="H6" s="247">
@@ -18716,12 +18747,12 @@
       </c>
       <c r="I6" s="124">
         <f t="shared" si="0"/>
-        <v>4.7858408799140584</v>
+        <v>4.755840879914059</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
       <c r="B7" s="100" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C7" s="338">
         <f>Normalized_FCF!G8</f>
@@ -18731,11 +18762,11 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E7" s="366" t="str">
+      <c r="E7" s="368" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 5-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 10-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 首钢资源(0639.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="366"/>
+      <c r="F7" s="368"/>
       <c r="H7" s="247">
         <v>4</v>
       </c>
@@ -18756,8 +18787,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E8" s="366"/>
-      <c r="F8" s="366"/>
+      <c r="E8" s="368"/>
+      <c r="F8" s="368"/>
       <c r="H8" s="247">
         <v>5</v>
       </c>
@@ -18778,8 +18809,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E9" s="366"/>
-      <c r="F9" s="366"/>
+      <c r="E9" s="368"/>
+      <c r="F9" s="368"/>
       <c r="H9" s="247">
         <v>6</v>
       </c>
@@ -18789,8 +18820,8 @@
       </c>
     </row>
     <row r="10" spans="2:9">
-      <c r="E10" s="366"/>
-      <c r="F10" s="366"/>
+      <c r="E10" s="368"/>
+      <c r="F10" s="368"/>
       <c r="H10" s="247">
         <v>7</v>
       </c>
@@ -18801,10 +18832,10 @@
     </row>
     <row r="11" spans="2:9" ht="13.15">
       <c r="B11" s="159" t="s">
-        <v>449</v>
-      </c>
-      <c r="E11" s="366"/>
-      <c r="F11" s="366"/>
+        <v>443</v>
+      </c>
+      <c r="E11" s="368"/>
+      <c r="F11" s="368"/>
       <c r="H11" s="247">
         <v>8</v>
       </c>
@@ -18815,15 +18846,15 @@
     </row>
     <row r="12" spans="2:9">
       <c r="B12" s="118" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C12" s="158">
         <f ca="1">(Normalized_FCF!G4/OFFSET(Normalized_FCF!G4, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.1059288114314666</v>
       </c>
       <c r="D12" s="158"/>
-      <c r="E12" s="366"/>
-      <c r="F12" s="366"/>
+      <c r="E12" s="368"/>
+      <c r="F12" s="368"/>
       <c r="H12" s="247">
         <v>9</v>
       </c>
@@ -18834,14 +18865,14 @@
     </row>
     <row r="13" spans="2:9">
       <c r="B13" s="148" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C13" s="158">
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.1663504856430581</v>
       </c>
-      <c r="E13" s="366"/>
-      <c r="F13" s="366"/>
+      <c r="E13" s="368"/>
+      <c r="F13" s="368"/>
       <c r="H13" s="247">
         <v>10</v>
       </c>
@@ -18858,12 +18889,12 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.18299448813777219</v>
       </c>
-      <c r="E14" s="366"/>
-      <c r="F14" s="366"/>
+      <c r="E14" s="368"/>
+      <c r="F14" s="368"/>
     </row>
     <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C16" s="37"/>
       <c r="D16" s="37"/>
@@ -18872,38 +18903,38 @@
     </row>
     <row r="17" spans="2:6" ht="13.15">
       <c r="B17" s="109" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E17" s="159" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
     </row>
     <row r="18" spans="2:6">
       <c r="B18" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C18" s="150">
         <v>5</v>
       </c>
-      <c r="E18" s="366" t="s">
-        <v>332</v>
-      </c>
-      <c r="F18" s="367"/>
+      <c r="E18" s="368" t="s">
+        <v>327</v>
+      </c>
+      <c r="F18" s="369"/>
     </row>
     <row r="19" spans="2:6">
-      <c r="E19" s="367"/>
-      <c r="F19" s="367"/>
+      <c r="E19" s="369"/>
+      <c r="F19" s="369"/>
     </row>
     <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="159" t="s">
-        <v>304</v>
-      </c>
-      <c r="E20" s="367"/>
-      <c r="F20" s="367"/>
+        <v>302</v>
+      </c>
+      <c r="E20" s="369"/>
+      <c r="F20" s="369"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
@@ -18913,12 +18944,12 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E21" s="367"/>
-      <c r="F21" s="367"/>
+      <c r="E21" s="369"/>
+      <c r="F21" s="369"/>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C22" s="160">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
@@ -18928,44 +18959,44 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E22" s="367"/>
-      <c r="F22" s="367"/>
+      <c r="E22" s="369"/>
+      <c r="F22" s="369"/>
     </row>
     <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="159" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E24" s="159" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F24" s="159"/>
     </row>
     <row r="25" spans="2:6">
       <c r="B25" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C25" s="166">
         <f>C18</f>
         <v>5</v>
       </c>
       <c r="D25" s="163"/>
-      <c r="E25" s="365"/>
-      <c r="F25" s="365"/>
+      <c r="E25" s="367"/>
+      <c r="F25" s="367"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="118" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C26" s="164">
         <v>0</v>
       </c>
       <c r="D26" s="164"/>
-      <c r="E26" s="365"/>
-      <c r="F26" s="365"/>
+      <c r="E26" s="367"/>
+      <c r="F26" s="367"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C27" s="160">
         <f>IF(valuation_method="DCF",DCF!E76,DDM!E71)</f>
@@ -18975,55 +19006,55 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E27" s="365"/>
-      <c r="F27" s="365"/>
+      <c r="E27" s="367"/>
+      <c r="F27" s="367"/>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C28" s="165">
         <v>0.6</v>
       </c>
       <c r="D28" s="165"/>
-      <c r="E28" s="365"/>
-      <c r="F28" s="365"/>
+      <c r="E28" s="367"/>
+      <c r="F28" s="367"/>
     </row>
     <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="159" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E30" s="159" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F30" s="159"/>
     </row>
     <row r="31" spans="2:6">
       <c r="B31" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C31" s="166">
         <f>C18</f>
         <v>5</v>
       </c>
       <c r="D31" s="163"/>
-      <c r="E31" s="365"/>
-      <c r="F31" s="365"/>
+      <c r="E31" s="367"/>
+      <c r="F31" s="367"/>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="118" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C32" s="164">
         <v>-0.02</v>
       </c>
       <c r="D32" s="164"/>
-      <c r="E32" s="365"/>
-      <c r="F32" s="365"/>
+      <c r="E32" s="367"/>
+      <c r="F32" s="367"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C33" s="160">
         <f>IF(valuation_method="DCF",DCF!E77,DDM!E72)</f>
@@ -19033,55 +19064,55 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E33" s="365"/>
-      <c r="F33" s="365"/>
+      <c r="E33" s="367"/>
+      <c r="F33" s="367"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C34" s="165">
         <v>0.2</v>
       </c>
       <c r="D34" s="165"/>
-      <c r="E34" s="365"/>
-      <c r="F34" s="365"/>
+      <c r="E34" s="367"/>
+      <c r="F34" s="367"/>
     </row>
     <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="159" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E36" s="159" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F36" s="159"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C37" s="166">
         <f>C18</f>
         <v>5</v>
       </c>
       <c r="D37" s="163"/>
-      <c r="E37" s="365"/>
-      <c r="F37" s="365"/>
+      <c r="E37" s="367"/>
+      <c r="F37" s="367"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="118" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C38" s="164">
         <v>0.02</v>
       </c>
       <c r="D38" s="164"/>
-      <c r="E38" s="365"/>
-      <c r="F38" s="365"/>
+      <c r="E38" s="367"/>
+      <c r="F38" s="367"/>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C39" s="160">
         <f>IF(valuation_method="DCF",DCF!E75,DDM!E70)</f>
@@ -19091,24 +19122,24 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E39" s="365"/>
-      <c r="F39" s="365"/>
+      <c r="E39" s="367"/>
+      <c r="F39" s="367"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C40" s="167">
         <f>1-C28-C34</f>
         <v>0.2</v>
       </c>
       <c r="D40" s="165"/>
-      <c r="E40" s="365"/>
-      <c r="F40" s="365"/>
+      <c r="E40" s="367"/>
+      <c r="F40" s="367"/>
     </row>
     <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C42" s="154">
         <f>C27*C28+C33*C34+C39*C40</f>
@@ -19121,7 +19152,7 @@
     </row>
     <row r="44" spans="2:6" ht="13.9">
       <c r="B44" s="36" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C44" s="37"/>
       <c r="D44" s="37"/>
@@ -19130,12 +19161,12 @@
     </row>
     <row r="45" spans="2:6" ht="13.15">
       <c r="B45" s="109" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="46" spans="2:6">
       <c r="B46" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C46" s="150">
         <v>10</v>
@@ -19150,39 +19181,39 @@
     </row>
     <row r="48" spans="2:6" ht="13.15">
       <c r="B48" s="159" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E48" s="159" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F48" s="159"/>
     </row>
     <row r="49" spans="2:6" ht="12.75" customHeight="1">
       <c r="B49" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C49" s="166">
         <f>C46</f>
         <v>10</v>
       </c>
       <c r="D49" s="163"/>
-      <c r="E49" s="365"/>
-      <c r="F49" s="365"/>
+      <c r="E49" s="367"/>
+      <c r="F49" s="367"/>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="118" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C50" s="164">
         <v>-0.04</v>
       </c>
       <c r="D50" s="164"/>
-      <c r="E50" s="365"/>
-      <c r="F50" s="365"/>
+      <c r="E50" s="367"/>
+      <c r="F50" s="367"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C51" s="160">
         <f>IF(valuation_method="DCF",DCF!E78,DDM!E73)</f>
@@ -19192,55 +19223,55 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E51" s="365"/>
-      <c r="F51" s="365"/>
+      <c r="E51" s="367"/>
+      <c r="F51" s="367"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C52" s="165">
         <v>0.05</v>
       </c>
       <c r="D52" s="165"/>
-      <c r="E52" s="365"/>
-      <c r="F52" s="365"/>
+      <c r="E52" s="367"/>
+      <c r="F52" s="367"/>
     </row>
     <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="159" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="E54" s="159" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F54" s="159"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C55" s="166">
         <f>C46</f>
         <v>10</v>
       </c>
       <c r="D55" s="163"/>
-      <c r="E55" s="365"/>
-      <c r="F55" s="365"/>
+      <c r="E55" s="367"/>
+      <c r="F55" s="367"/>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="118" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C56" s="164">
         <v>0.04</v>
       </c>
       <c r="D56" s="164"/>
-      <c r="E56" s="365"/>
-      <c r="F56" s="365"/>
+      <c r="E56" s="367"/>
+      <c r="F56" s="367"/>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C57" s="160">
         <f>IF(valuation_method="DCF",DCF!E74,DDM!E69)</f>
@@ -19250,23 +19281,23 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E57" s="365"/>
-      <c r="F57" s="365"/>
+      <c r="E57" s="367"/>
+      <c r="F57" s="367"/>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C58" s="165">
         <v>0.05</v>
       </c>
       <c r="D58" s="165"/>
-      <c r="E58" s="365"/>
-      <c r="F58" s="365"/>
+      <c r="E58" s="367"/>
+      <c r="F58" s="367"/>
     </row>
     <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C60" s="154">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
@@ -19277,7 +19308,7 @@
         <v>HKD</v>
       </c>
       <c r="E60" s="100" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F60" s="277">
         <f>Thesis!F28</f>
@@ -19286,7 +19317,7 @@
     </row>
     <row r="62" spans="2:6" ht="13.9">
       <c r="B62" s="36" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="C62" s="37"/>
       <c r="D62" s="37"/>
@@ -19295,15 +19326,15 @@
     </row>
     <row r="63" spans="2:6" ht="13.15">
       <c r="B63" s="109" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="E63" s="252" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
     </row>
     <row r="64" spans="2:6">
       <c r="B64" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C64" s="166">
         <f>C18</f>
@@ -19311,19 +19342,19 @@
       </c>
       <c r="D64" s="150"/>
       <c r="E64" s="251" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
     </row>
     <row r="65" spans="2:6">
       <c r="B65" s="118" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C65" s="151">
-        <v>1.280056444784558E-3</v>
+        <v>1.28005644478456E-3</v>
       </c>
       <c r="D65" s="151"/>
       <c r="E65" s="251" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
     </row>
     <row r="66" spans="2:6">
@@ -19339,20 +19370,20 @@
         <v>HKD</v>
       </c>
       <c r="E66" s="251" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
     </row>
     <row r="68" spans="2:6" ht="13.15">
       <c r="B68" s="109" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="E68" s="252" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
     </row>
     <row r="69" spans="2:6">
       <c r="B69" s="100" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C69" s="244" t="str">
         <f>IF(C60&lt;C22,"Y","N")</f>
@@ -19362,19 +19393,19 @@
     </row>
     <row r="70" spans="2:6">
       <c r="B70" s="100" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C70" s="244" t="str">
         <f>IF(C69="Y","N",IF(C65&gt;8%,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="E70" s="251" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="71" spans="2:6">
       <c r="B71" s="100" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C71" s="244" t="str">
         <f>IF(C65&gt;8%,"Y","N")</f>
@@ -19384,14 +19415,14 @@
     </row>
     <row r="72" spans="2:6">
       <c r="B72" s="100" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C72" s="243" t="str">
         <f>IF(F72&gt;50%,"Y","N")</f>
         <v>N</v>
       </c>
       <c r="E72" s="134" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="F72" s="291">
         <f>BS!D89/C60</f>
@@ -19400,7 +19431,7 @@
     </row>
     <row r="74" spans="2:6" ht="13.9">
       <c r="B74" s="36" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C74" s="37"/>
       <c r="D74" s="37"/>
@@ -19409,12 +19440,12 @@
     </row>
     <row r="75" spans="2:6" ht="13.15">
       <c r="B75" s="109" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="76" spans="2:6">
       <c r="B76" s="246" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C76" s="245">
         <f>F60</f>
@@ -19424,11 +19455,11 @@
     </row>
     <row r="77" spans="2:6">
       <c r="B77" s="100" t="s">
-        <v>111</v>
+        <v>455</v>
       </c>
       <c r="C77" s="173">
-        <f>Normalized_FCF!C90</f>
-        <v>0.3</v>
+        <f>Normalized_FCF!C90*(1-dividend_tax_rate)</f>
+        <v>0.27</v>
       </c>
       <c r="D77" t="str">
         <f>Market_currency</f>
@@ -19437,12 +19468,12 @@
     </row>
     <row r="79" spans="2:6" ht="13.15">
       <c r="B79" s="109" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="80" spans="2:6">
       <c r="B80" s="148" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C80" s="167">
         <f>Thesis!F29</f>
@@ -19451,11 +19482,11 @@
     </row>
     <row r="81" spans="2:8">
       <c r="B81" s="100" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>0.49717779580945759</v>
+        <v>0.44746001622851189</v>
       </c>
       <c r="D81" s="116"/>
       <c r="E81" s="100"/>
@@ -19463,7 +19494,7 @@
     </row>
     <row r="82" spans="2:8">
       <c r="B82" s="100" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C82" s="116">
         <f>C60/(1+C80)^C76</f>
@@ -19477,18 +19508,18 @@
       </c>
       <c r="C83" s="111">
         <f>C81+C82</f>
-        <v>2.2516930066250125</v>
+        <v>2.2019752270440667</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
       <c r="E83" s="146" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F83" s="291">
         <f>(1-C83/C60)</f>
-        <v>0.4980443874620557</v>
+        <v>0.50912765610931499</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -19496,12 +19527,12 @@
     </row>
     <row r="85" spans="2:8" ht="13.15">
       <c r="B85" s="109" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="86" spans="2:8">
       <c r="B86" s="148" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
@@ -19514,11 +19545,11 @@
     </row>
     <row r="87" spans="2:8" ht="13.15">
       <c r="B87" s="100" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.28164513964422611</v>
+        <v>0.27199281553693067</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -19526,12 +19557,12 @@
     </row>
     <row r="89" spans="2:8" ht="13.15">
       <c r="B89" s="109" t="s">
-        <v>415</v>
+        <v>409</v>
       </c>
     </row>
     <row r="90" spans="2:8">
       <c r="B90" s="148" t="s">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="C90" s="167">
         <f>Thesis!F30</f>
@@ -19540,11 +19571,11 @@
     </row>
     <row r="91" spans="2:8">
       <c r="B91" s="100" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C91" s="116">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>0.61512024715948099</v>
+        <v>0.55360822244353303</v>
       </c>
       <c r="D91" s="116"/>
       <c r="E91" s="100"/>
@@ -19552,7 +19583,7 @@
     </row>
     <row r="92" spans="2:8">
       <c r="B92" s="100" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C92" s="116">
         <f>C60/(1+C90)^C76</f>
@@ -19566,30 +19597,30 @@
       </c>
       <c r="C93" s="111">
         <f>C91+C92</f>
-        <v>3.101365529948271</v>
+        <v>3.039853505232323</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
       <c r="E93" s="146" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F93" s="291">
         <f>(1-C93/C60)</f>
-        <v>0.30863229147626647</v>
+        <v>0.32234477623946356</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
       <c r="B95" s="109" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="G95" s="2"/>
       <c r="H95" s="281"/>
     </row>
     <row r="96" spans="2:8">
       <c r="B96" s="148" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="C96" s="134">
         <f>Thesis!F31</f>
@@ -19600,11 +19631,11 @@
     </row>
     <row r="97" spans="2:8">
       <c r="B97" s="100" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C97" s="116">
         <f>PV(C96, C76, -C77, 0)</f>
-        <v>0.78015772196158795</v>
+        <v>0.70214194976542921</v>
       </c>
       <c r="D97" s="116"/>
       <c r="G97" s="2"/>
@@ -19612,7 +19643,7 @@
     </row>
     <row r="98" spans="2:8">
       <c r="B98" s="100" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C98" s="116">
         <f>C60/(1+C96)^C76</f>
@@ -19624,21 +19655,21 @@
     </row>
     <row r="99" spans="2:8" ht="13.15">
       <c r="B99" s="110" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="C99" s="111">
         <f>C97+C98</f>
-        <v>4.3910827513866675</v>
+        <v>4.3130669791905083</v>
       </c>
       <c r="D99" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="E99" s="146" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F99" s="291">
         <f>(1-C99/C60)</f>
-        <v>2.1123827408074836E-2</v>
+        <v>3.8515387716307137E-2</v>
       </c>
     </row>
     <row r="100" spans="2:8">
@@ -19646,12 +19677,12 @@
     </row>
     <row r="101" spans="2:8" ht="13.15">
       <c r="B101" s="109" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
     </row>
     <row r="102" spans="2:8">
       <c r="B102" s="148" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="C102" s="134">
         <f>Thesis!F32</f>
@@ -19660,17 +19691,17 @@
     </row>
     <row r="103" spans="2:8">
       <c r="B103" s="100" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C103" s="116">
         <f>PV(C102, C76, -C77, 0)</f>
-        <v>0.72378093778159469</v>
+        <v>0.65140284400343529</v>
       </c>
       <c r="D103" s="116"/>
     </row>
     <row r="104" spans="2:8">
       <c r="B104" s="100" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C104" s="116">
         <f>C60/(1+C102)^C76</f>
@@ -19680,21 +19711,21 @@
     </row>
     <row r="105" spans="2:8" ht="13.15">
       <c r="B105" s="110" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="C105" s="111">
         <f>C103+C104</f>
-        <v>3.939054009870663</v>
+        <v>3.8666759160925035</v>
       </c>
       <c r="D105" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="E105" s="146" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F105" s="291">
         <f>(1-C105/C66)</f>
-        <v>0.12229326468444657</v>
+        <v>0.13842067503200794</v>
       </c>
     </row>
     <row r="106" spans="2:8">
@@ -19702,32 +19733,32 @@
     </row>
     <row r="107" spans="2:8" ht="14.65">
       <c r="E107" s="285" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="F107" s="282"/>
     </row>
     <row r="108" spans="2:8" ht="13.9">
       <c r="E108" s="278" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="F108" s="283" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
     </row>
     <row r="109" spans="2:8" ht="13.9">
       <c r="E109" s="279" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="F109" s="283" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
     </row>
     <row r="110" spans="2:8" ht="13.9">
       <c r="E110" s="280" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="F110" s="284" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
     </row>
   </sheetData>

--- a/financial_models/opportunities/0639.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0639.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{812DB708-1E1C-44F1-B0B3-FA7634261AE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C0EFEEE-8F19-40BD-932C-55AE7C054557}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3893,29 +3893,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4333,7 +4333,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>2.69</v>
+        <v>2.73</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>13694.9669213</v>
+        <v>13898.609552100001</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4391,13 +4391,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="360" t="s">
+      <c r="B18" s="358" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="360"/>
-      <c r="D18" s="360"/>
-      <c r="E18" s="360"/>
-      <c r="F18" s="360"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.27199281553693067</v>
+        <v>0.26525952363332039</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4597,22 +4597,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="360" t="s">
+      <c r="B36" s="358" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="360"/>
-      <c r="D36" s="360"/>
-      <c r="E36" s="360"/>
-      <c r="F36" s="360"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="363" t="s">
+      <c r="B37" s="360" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="363"/>
-      <c r="D37" s="363"/>
-      <c r="E37" s="363"/>
-      <c r="F37" s="363"/>
+      <c r="C37" s="360"/>
+      <c r="D37" s="360"/>
+      <c r="E37" s="360"/>
+      <c r="F37" s="360"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4624,13 +4624,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="361" t="s">
+      <c r="B40" s="359" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="361"/>
-      <c r="D40" s="361"/>
-      <c r="E40" s="361"/>
-      <c r="F40" s="361"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4650,13 +4650,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="361" t="s">
+      <c r="B43" s="359" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="361"/>
-      <c r="D43" s="361"/>
-      <c r="E43" s="361"/>
-      <c r="F43" s="361"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4685,13 +4685,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="361" t="s">
+      <c r="B47" s="359" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="361"/>
-      <c r="D47" s="361"/>
-      <c r="E47" s="361"/>
-      <c r="F47" s="361"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4707,13 +4707,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="361" t="s">
+      <c r="B50" s="359" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="361"/>
-      <c r="D50" s="361"/>
-      <c r="E50" s="361"/>
-      <c r="F50" s="361"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4777,13 +4777,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="361" t="s">
+      <c r="B58" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="361"/>
-      <c r="D58" s="361"/>
-      <c r="E58" s="361"/>
-      <c r="F58" s="361"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4799,7 +4799,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="361" t="s">
+      <c r="B61" s="359" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4821,22 +4821,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="360" t="s">
+      <c r="B64" s="358" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="360"/>
-      <c r="D64" s="360"/>
-      <c r="E64" s="360"/>
-      <c r="F64" s="360"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="360" t="s">
+      <c r="B65" s="358" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="360"/>
-      <c r="D65" s="360"/>
-      <c r="E65" s="360"/>
-      <c r="F65" s="360"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>7.9724725033409882E-2</v>
+        <v>7.8556597194092512E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>0.10037174721189591</v>
+        <v>9.8901098901098911E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>444</v>
@@ -4971,22 +4971,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="360" t="s">
+      <c r="B80" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="360"/>
-      <c r="D80" s="360"/>
-      <c r="E80" s="360"/>
-      <c r="F80" s="360"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="363" t="s">
+      <c r="B81" s="360" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="363"/>
-      <c r="D81" s="363"/>
-      <c r="E81" s="363"/>
-      <c r="F81" s="363"/>
+      <c r="C81" s="360"/>
+      <c r="D81" s="360"/>
+      <c r="E81" s="360"/>
+      <c r="F81" s="360"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5030,22 +5030,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="360" t="s">
+      <c r="B89" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="360"/>
-      <c r="D89" s="360"/>
-      <c r="E89" s="360"/>
-      <c r="F89" s="360"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="360" t="s">
+      <c r="B90" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="360"/>
-      <c r="D90" s="360"/>
-      <c r="E90" s="360"/>
-      <c r="F90" s="360"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5082,13 +5082,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="360" t="s">
+      <c r="B97" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="360"/>
-      <c r="D97" s="360"/>
-      <c r="E97" s="360"/>
-      <c r="F97" s="360"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5101,13 +5101,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="360" t="s">
+      <c r="B101" s="358" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="360"/>
-      <c r="D101" s="360"/>
-      <c r="E101" s="360"/>
-      <c r="F101" s="360"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5229,13 +5229,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="360" t="s">
+      <c r="B116" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="360"/>
-      <c r="D116" s="360"/>
-      <c r="E116" s="360"/>
-      <c r="F116" s="360"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5274,13 +5274,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="361" t="s">
+      <c r="B123" s="359" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="361"/>
-      <c r="D123" s="361"/>
-      <c r="E123" s="361"/>
-      <c r="F123" s="361"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5423,13 +5423,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="364" t="s">
+      <c r="B134" s="363" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="364"/>
-      <c r="D134" s="364"/>
-      <c r="E134" s="364"/>
-      <c r="F134" s="364"/>
+      <c r="C134" s="363"/>
+      <c r="D134" s="363"/>
+      <c r="E134" s="363"/>
+      <c r="F134" s="363"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5442,22 +5442,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="365" t="s">
+      <c r="B138" s="361" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="365"/>
-      <c r="D138" s="365"/>
-      <c r="E138" s="365"/>
-      <c r="F138" s="365"/>
+      <c r="C138" s="361"/>
+      <c r="D138" s="361"/>
+      <c r="E138" s="361"/>
+      <c r="F138" s="361"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="360" t="s">
+      <c r="B139" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="360"/>
-      <c r="D139" s="360"/>
-      <c r="E139" s="360"/>
-      <c r="F139" s="360"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5790,13 +5790,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="359" t="s">
+      <c r="B179" s="365" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="360"/>
-      <c r="D179" s="360"/>
-      <c r="E179" s="360"/>
-      <c r="F179" s="360"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5833,13 +5833,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="361" t="s">
+      <c r="B188" s="359" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="361"/>
-      <c r="D188" s="361"/>
-      <c r="E188" s="361"/>
-      <c r="F188" s="361"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5847,22 +5847,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="358" t="s">
+      <c r="B191" s="364" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="358"/>
-      <c r="D191" s="358"/>
-      <c r="E191" s="358"/>
-      <c r="F191" s="358"/>
+      <c r="C191" s="364"/>
+      <c r="D191" s="364"/>
+      <c r="E191" s="364"/>
+      <c r="F191" s="364"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="358" t="s">
+      <c r="B192" s="364" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="358"/>
-      <c r="D192" s="358"/>
-      <c r="E192" s="358"/>
-      <c r="F192" s="358"/>
+      <c r="C192" s="364"/>
+      <c r="D192" s="364"/>
+      <c r="E192" s="364"/>
+      <c r="F192" s="364"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5886,6 +5886,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5902,17 +5913,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13456,20 +13456,20 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>0.10037174721189591</v>
+        <v>9.8901098901098911E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>0.10037174721189591</v>
+        <v>9.8901098901098911E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>9.3680297397769535E-2</v>
+        <v>9.2307692307692327E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>0.14386617100371751</v>
+        <v>0.14175824175824178</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
@@ -14655,50 +14655,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>7.9724725033409882E-2</v>
+        <v>7.8556597194092512E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>9.3033111861113932E-2</v>
+        <v>9.166998934300237E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>0.12801935247259968</v>
+        <v>0.12614361104442973</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>0.20762139258758974</v>
+        <v>0.20457932090132469</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>0.17059354279001862</v>
+        <v>0.16809400370152017</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>6.1200147821929882E-2</v>
+        <v>6.0303442359337503E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>7.7692703174415526E-2</v>
+        <v>7.6554348549149359E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>6.9174975408416134E-2</v>
+        <v>6.8161422655179271E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>6.5700268220479183E-2</v>
+        <v>6.4737626927871425E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>1.1630258102505928E-2</v>
+        <v>1.1459851390381299E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>5.0382012893135444E-3</v>
+        <v>4.9643814902027234E-3</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14712,43 +14712,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13252861510582697</v>
+        <v>0.13058680389548519</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16801340326140654</v>
+        <v>0.16555166841508556</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.24155991168220889</v>
+        <v>0.23802057231690177</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.22350043031060127</v>
+        <v>0.22022569873095874</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.669484247920306E-2</v>
+        <v>8.5424588376943666E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.5881258914961622E-2</v>
+        <v>8.4622925451006123E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.4113237119863946E-2</v>
+        <v>8.2880808737155309E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.6351723724188659E-2</v>
+        <v>8.5086497002955119E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.9402090847531404E-3</v>
+        <v>4.8678250688593211E-3</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-5.1951567615211372E-2</v>
+        <v>-5.1190372485318159E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18698,7 +18698,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-2.69</v>
+        <v>-2.73</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18938,7 +18938,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>2.69</v>
+        <v>2.73</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19536,7 +19536,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>2.69</v>
+        <v>2.73</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19549,7 +19549,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.27199281553693067</v>
+        <v>0.26525952363332039</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/0639.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0639.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C0EFEEE-8F19-40BD-932C-55AE7C054557}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C31EFA98-A2FB-4A5D-8383-F0AD441800B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1470" yWindow="1470" windowWidth="12690" windowHeight="7643" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3893,29 +3893,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4333,7 +4333,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>2.73</v>
+        <v>2.69</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>13898.609552100001</v>
+        <v>13694.9669213</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4391,13 +4391,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="360" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="360"/>
+      <c r="D18" s="360"/>
+      <c r="E18" s="360"/>
+      <c r="F18" s="360"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.26525952363332039</v>
+        <v>0.27199281553693067</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4597,22 +4597,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="360" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="360"/>
+      <c r="D36" s="360"/>
+      <c r="E36" s="360"/>
+      <c r="F36" s="360"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="360" t="s">
+      <c r="B37" s="363" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="360"/>
-      <c r="D37" s="360"/>
-      <c r="E37" s="360"/>
-      <c r="F37" s="360"/>
+      <c r="C37" s="363"/>
+      <c r="D37" s="363"/>
+      <c r="E37" s="363"/>
+      <c r="F37" s="363"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4624,13 +4624,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="361" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="361"/>
+      <c r="D40" s="361"/>
+      <c r="E40" s="361"/>
+      <c r="F40" s="361"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4650,13 +4650,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="361" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="361"/>
+      <c r="D43" s="361"/>
+      <c r="E43" s="361"/>
+      <c r="F43" s="361"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4685,13 +4685,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="361" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="361"/>
+      <c r="D47" s="361"/>
+      <c r="E47" s="361"/>
+      <c r="F47" s="361"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4707,13 +4707,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="361" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="361"/>
+      <c r="D50" s="361"/>
+      <c r="E50" s="361"/>
+      <c r="F50" s="361"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4777,13 +4777,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="361" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="361"/>
+      <c r="D58" s="361"/>
+      <c r="E58" s="361"/>
+      <c r="F58" s="361"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4799,7 +4799,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="361" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4821,22 +4821,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="360" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="360"/>
+      <c r="D64" s="360"/>
+      <c r="E64" s="360"/>
+      <c r="F64" s="360"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="360" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="360"/>
+      <c r="D65" s="360"/>
+      <c r="E65" s="360"/>
+      <c r="F65" s="360"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>7.8556597194092512E-2</v>
+        <v>7.9724725033409882E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>9.8901098901098911E-2</v>
+        <v>0.10037174721189591</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>444</v>
@@ -4971,22 +4971,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="360" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="360"/>
+      <c r="D80" s="360"/>
+      <c r="E80" s="360"/>
+      <c r="F80" s="360"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="360" t="s">
+      <c r="B81" s="363" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="360"/>
-      <c r="D81" s="360"/>
-      <c r="E81" s="360"/>
-      <c r="F81" s="360"/>
+      <c r="C81" s="363"/>
+      <c r="D81" s="363"/>
+      <c r="E81" s="363"/>
+      <c r="F81" s="363"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5030,22 +5030,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="360" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="360"/>
+      <c r="D89" s="360"/>
+      <c r="E89" s="360"/>
+      <c r="F89" s="360"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="360" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="360"/>
+      <c r="D90" s="360"/>
+      <c r="E90" s="360"/>
+      <c r="F90" s="360"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5082,13 +5082,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="360" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="360"/>
+      <c r="D97" s="360"/>
+      <c r="E97" s="360"/>
+      <c r="F97" s="360"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5101,13 +5101,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="360" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="360"/>
+      <c r="D101" s="360"/>
+      <c r="E101" s="360"/>
+      <c r="F101" s="360"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5229,13 +5229,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="360" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="360"/>
+      <c r="D116" s="360"/>
+      <c r="E116" s="360"/>
+      <c r="F116" s="360"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5274,13 +5274,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="361" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="361"/>
+      <c r="D123" s="361"/>
+      <c r="E123" s="361"/>
+      <c r="F123" s="361"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5423,13 +5423,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="363" t="s">
+      <c r="B134" s="364" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="363"/>
-      <c r="D134" s="363"/>
-      <c r="E134" s="363"/>
-      <c r="F134" s="363"/>
+      <c r="C134" s="364"/>
+      <c r="D134" s="364"/>
+      <c r="E134" s="364"/>
+      <c r="F134" s="364"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5442,22 +5442,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="361" t="s">
+      <c r="B138" s="365" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="361"/>
-      <c r="D138" s="361"/>
-      <c r="E138" s="361"/>
-      <c r="F138" s="361"/>
+      <c r="C138" s="365"/>
+      <c r="D138" s="365"/>
+      <c r="E138" s="365"/>
+      <c r="F138" s="365"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="360" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="360"/>
+      <c r="D139" s="360"/>
+      <c r="E139" s="360"/>
+      <c r="F139" s="360"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5790,13 +5790,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="365" t="s">
+      <c r="B179" s="359" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="360"/>
+      <c r="D179" s="360"/>
+      <c r="E179" s="360"/>
+      <c r="F179" s="360"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5833,13 +5833,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="361" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="361"/>
+      <c r="D188" s="361"/>
+      <c r="E188" s="361"/>
+      <c r="F188" s="361"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5847,22 +5847,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="364" t="s">
+      <c r="B191" s="358" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="364"/>
-      <c r="D191" s="364"/>
-      <c r="E191" s="364"/>
-      <c r="F191" s="364"/>
+      <c r="C191" s="358"/>
+      <c r="D191" s="358"/>
+      <c r="E191" s="358"/>
+      <c r="F191" s="358"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="364" t="s">
+      <c r="B192" s="358" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="364"/>
-      <c r="D192" s="364"/>
-      <c r="E192" s="364"/>
-      <c r="F192" s="364"/>
+      <c r="C192" s="358"/>
+      <c r="D192" s="358"/>
+      <c r="E192" s="358"/>
+      <c r="F192" s="358"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5886,17 +5886,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5913,6 +5902,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13456,20 +13456,20 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>9.8901098901098911E-2</v>
+        <v>0.10037174721189591</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>9.8901098901098911E-2</v>
+        <v>0.10037174721189591</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>9.2307692307692327E-2</v>
+        <v>9.3680297397769535E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>0.14175824175824178</v>
+        <v>0.14386617100371751</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
@@ -14655,50 +14655,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>7.8556597194092512E-2</v>
+        <v>7.9724725033409882E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>9.166998934300237E-2</v>
+        <v>9.3033111861113932E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>0.12614361104442973</v>
+        <v>0.12801935247259968</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>0.20457932090132469</v>
+        <v>0.20762139258758974</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>0.16809400370152017</v>
+        <v>0.17059354279001862</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>6.0303442359337503E-2</v>
+        <v>6.1200147821929882E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>7.6554348549149359E-2</v>
+        <v>7.7692703174415526E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>6.8161422655179271E-2</v>
+        <v>6.9174975408416134E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>6.4737626927871425E-2</v>
+        <v>6.5700268220479183E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>1.1459851390381299E-2</v>
+        <v>1.1630258102505928E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>4.9643814902027234E-3</v>
+        <v>5.0382012893135444E-3</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14712,43 +14712,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13058680389548519</v>
+        <v>0.13252861510582697</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16555166841508556</v>
+        <v>0.16801340326140654</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.23802057231690177</v>
+        <v>0.24155991168220889</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.22022569873095874</v>
+        <v>0.22350043031060127</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.5424588376943666E-2</v>
+        <v>8.669484247920306E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.4622925451006123E-2</v>
+        <v>8.5881258914961622E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.2880808737155309E-2</v>
+        <v>8.4113237119863946E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.5086497002955119E-2</v>
+        <v>8.6351723724188659E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.8678250688593211E-3</v>
+        <v>4.9402090847531404E-3</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-5.1190372485318159E-2</v>
+        <v>-5.1951567615211372E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18698,7 +18698,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-2.73</v>
+        <v>-2.69</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18938,7 +18938,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>2.73</v>
+        <v>2.69</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19536,7 +19536,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>2.73</v>
+        <v>2.69</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19549,7 +19549,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.26525952363332039</v>
+        <v>0.27199281553693067</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/0639.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0639.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C31EFA98-A2FB-4A5D-8383-F0AD441800B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E572C321-710D-4739-B8C9-C17E792E9F80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1470" yWindow="1470" windowWidth="12690" windowHeight="7643" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3893,29 +3893,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4333,7 +4333,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>2.69</v>
+        <v>2.6</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>13694.9669213</v>
+        <v>13236.771001999999</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4391,13 +4391,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="360" t="s">
+      <c r="B18" s="358" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="360"/>
-      <c r="D18" s="360"/>
-      <c r="E18" s="360"/>
-      <c r="F18" s="360"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.27199281553693067</v>
+        <v>0.28766954280717139</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4597,22 +4597,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="360" t="s">
+      <c r="B36" s="358" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="360"/>
-      <c r="D36" s="360"/>
-      <c r="E36" s="360"/>
-      <c r="F36" s="360"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="363" t="s">
+      <c r="B37" s="360" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="363"/>
-      <c r="D37" s="363"/>
-      <c r="E37" s="363"/>
-      <c r="F37" s="363"/>
+      <c r="C37" s="360"/>
+      <c r="D37" s="360"/>
+      <c r="E37" s="360"/>
+      <c r="F37" s="360"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4624,13 +4624,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="361" t="s">
+      <c r="B40" s="359" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="361"/>
-      <c r="D40" s="361"/>
-      <c r="E40" s="361"/>
-      <c r="F40" s="361"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4650,13 +4650,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="361" t="s">
+      <c r="B43" s="359" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="361"/>
-      <c r="D43" s="361"/>
-      <c r="E43" s="361"/>
-      <c r="F43" s="361"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4685,13 +4685,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="361" t="s">
+      <c r="B47" s="359" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="361"/>
-      <c r="D47" s="361"/>
-      <c r="E47" s="361"/>
-      <c r="F47" s="361"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4707,13 +4707,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="361" t="s">
+      <c r="B50" s="359" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="361"/>
-      <c r="D50" s="361"/>
-      <c r="E50" s="361"/>
-      <c r="F50" s="361"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4777,13 +4777,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="361" t="s">
+      <c r="B58" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="361"/>
-      <c r="D58" s="361"/>
-      <c r="E58" s="361"/>
-      <c r="F58" s="361"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4799,7 +4799,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="361" t="s">
+      <c r="B61" s="359" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4821,22 +4821,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="360" t="s">
+      <c r="B64" s="358" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="360"/>
-      <c r="D64" s="360"/>
-      <c r="E64" s="360"/>
-      <c r="F64" s="360"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="360" t="s">
+      <c r="B65" s="358" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="360"/>
-      <c r="D65" s="360"/>
-      <c r="E65" s="360"/>
-      <c r="F65" s="360"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>7.9724725033409882E-2</v>
+        <v>8.2484427053797146E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>0.10037174721189591</v>
+        <v>0.10384615384615385</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>444</v>
@@ -4971,22 +4971,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="360" t="s">
+      <c r="B80" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="360"/>
-      <c r="D80" s="360"/>
-      <c r="E80" s="360"/>
-      <c r="F80" s="360"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="363" t="s">
+      <c r="B81" s="360" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="363"/>
-      <c r="D81" s="363"/>
-      <c r="E81" s="363"/>
-      <c r="F81" s="363"/>
+      <c r="C81" s="360"/>
+      <c r="D81" s="360"/>
+      <c r="E81" s="360"/>
+      <c r="F81" s="360"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5030,22 +5030,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="360" t="s">
+      <c r="B89" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="360"/>
-      <c r="D89" s="360"/>
-      <c r="E89" s="360"/>
-      <c r="F89" s="360"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="360" t="s">
+      <c r="B90" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="360"/>
-      <c r="D90" s="360"/>
-      <c r="E90" s="360"/>
-      <c r="F90" s="360"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5082,13 +5082,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="360" t="s">
+      <c r="B97" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="360"/>
-      <c r="D97" s="360"/>
-      <c r="E97" s="360"/>
-      <c r="F97" s="360"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5101,13 +5101,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="360" t="s">
+      <c r="B101" s="358" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="360"/>
-      <c r="D101" s="360"/>
-      <c r="E101" s="360"/>
-      <c r="F101" s="360"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5229,13 +5229,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="360" t="s">
+      <c r="B116" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="360"/>
-      <c r="D116" s="360"/>
-      <c r="E116" s="360"/>
-      <c r="F116" s="360"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5274,13 +5274,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="361" t="s">
+      <c r="B123" s="359" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="361"/>
-      <c r="D123" s="361"/>
-      <c r="E123" s="361"/>
-      <c r="F123" s="361"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5423,13 +5423,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="364" t="s">
+      <c r="B134" s="363" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="364"/>
-      <c r="D134" s="364"/>
-      <c r="E134" s="364"/>
-      <c r="F134" s="364"/>
+      <c r="C134" s="363"/>
+      <c r="D134" s="363"/>
+      <c r="E134" s="363"/>
+      <c r="F134" s="363"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5442,22 +5442,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="365" t="s">
+      <c r="B138" s="361" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="365"/>
-      <c r="D138" s="365"/>
-      <c r="E138" s="365"/>
-      <c r="F138" s="365"/>
+      <c r="C138" s="361"/>
+      <c r="D138" s="361"/>
+      <c r="E138" s="361"/>
+      <c r="F138" s="361"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="360" t="s">
+      <c r="B139" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="360"/>
-      <c r="D139" s="360"/>
-      <c r="E139" s="360"/>
-      <c r="F139" s="360"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5790,13 +5790,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="359" t="s">
+      <c r="B179" s="365" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="360"/>
-      <c r="D179" s="360"/>
-      <c r="E179" s="360"/>
-      <c r="F179" s="360"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5833,13 +5833,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="361" t="s">
+      <c r="B188" s="359" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="361"/>
-      <c r="D188" s="361"/>
-      <c r="E188" s="361"/>
-      <c r="F188" s="361"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5847,22 +5847,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="358" t="s">
+      <c r="B191" s="364" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="358"/>
-      <c r="D191" s="358"/>
-      <c r="E191" s="358"/>
-      <c r="F191" s="358"/>
+      <c r="C191" s="364"/>
+      <c r="D191" s="364"/>
+      <c r="E191" s="364"/>
+      <c r="F191" s="364"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="358" t="s">
+      <c r="B192" s="364" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="358"/>
-      <c r="D192" s="358"/>
-      <c r="E192" s="358"/>
-      <c r="F192" s="358"/>
+      <c r="C192" s="364"/>
+      <c r="D192" s="364"/>
+      <c r="E192" s="364"/>
+      <c r="F192" s="364"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5886,6 +5886,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5902,17 +5913,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13456,20 +13456,20 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>0.10037174721189591</v>
+        <v>0.10384615384615385</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>0.10037174721189591</v>
+        <v>0.10384615384615385</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>9.3680297397769535E-2</v>
+        <v>9.6923076923076945E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>0.14386617100371751</v>
+        <v>0.14884615384615388</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
@@ -14655,50 +14655,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>7.9724725033409882E-2</v>
+        <v>8.2484427053797146E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>9.3033111861113932E-2</v>
+        <v>9.6253488810152485E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>0.12801935247259968</v>
+        <v>0.13245079159665121</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>0.20762139258758974</v>
+        <v>0.21480828694639093</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>0.17059354279001862</v>
+        <v>0.17649870388659619</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>6.1200147821929882E-2</v>
+        <v>6.3318614477304372E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>7.7692703174415526E-2</v>
+        <v>8.0382065976606826E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>6.9174975408416134E-2</v>
+        <v>7.1569493787938226E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>6.5700268220479183E-2</v>
+        <v>6.7974508274265003E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>1.1630258102505928E-2</v>
+        <v>1.2032843959900364E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>5.0382012893135444E-3</v>
+        <v>5.2126005647128593E-3</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14712,43 +14712,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13252861510582697</v>
+        <v>0.13711614409025946</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16801340326140654</v>
+        <v>0.17382925183583983</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.24155991168220889</v>
+        <v>0.24992160093274687</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.22350043031060127</v>
+        <v>0.23123698366750667</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.669484247920306E-2</v>
+        <v>8.9695817795790861E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.5881258914961622E-2</v>
+        <v>8.885407172355643E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.4113237119863946E-2</v>
+        <v>8.7024849174013083E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.6351723724188659E-2</v>
+        <v>8.9340821853102867E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.9402090847531404E-3</v>
+        <v>5.1112163223022873E-3</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-5.1951567615211372E-2</v>
+        <v>-5.3749891109584065E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18698,7 +18698,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-2.69</v>
+        <v>-2.6</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18938,7 +18938,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>2.69</v>
+        <v>2.6</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19536,7 +19536,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>2.69</v>
+        <v>2.6</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19549,7 +19549,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.27199281553693067</v>
+        <v>0.28766954280717139</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/0639.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0639.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E572C321-710D-4739-B8C9-C17E792E9F80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4602AA5-8BD7-4ED2-8E2F-91A148713039}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1470" yWindow="1470" windowWidth="12690" windowHeight="7643" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3893,29 +3893,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4333,7 +4333,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>13236.771001999999</v>
+        <v>13287.6816597</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4391,13 +4391,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="360" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="360"/>
+      <c r="D18" s="360"/>
+      <c r="E18" s="360"/>
+      <c r="F18" s="360"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.28766954280717139</v>
+        <v>0.28589032424265848</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4597,22 +4597,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="360" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="360"/>
+      <c r="D36" s="360"/>
+      <c r="E36" s="360"/>
+      <c r="F36" s="360"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="360" t="s">
+      <c r="B37" s="363" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="360"/>
-      <c r="D37" s="360"/>
-      <c r="E37" s="360"/>
-      <c r="F37" s="360"/>
+      <c r="C37" s="363"/>
+      <c r="D37" s="363"/>
+      <c r="E37" s="363"/>
+      <c r="F37" s="363"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4624,13 +4624,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="361" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="361"/>
+      <c r="D40" s="361"/>
+      <c r="E40" s="361"/>
+      <c r="F40" s="361"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4650,13 +4650,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="361" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="361"/>
+      <c r="D43" s="361"/>
+      <c r="E43" s="361"/>
+      <c r="F43" s="361"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4685,13 +4685,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="361" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="361"/>
+      <c r="D47" s="361"/>
+      <c r="E47" s="361"/>
+      <c r="F47" s="361"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4707,13 +4707,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="361" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="361"/>
+      <c r="D50" s="361"/>
+      <c r="E50" s="361"/>
+      <c r="F50" s="361"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4777,13 +4777,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="361" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="361"/>
+      <c r="D58" s="361"/>
+      <c r="E58" s="361"/>
+      <c r="F58" s="361"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4799,7 +4799,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="361" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4821,22 +4821,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="360" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="360"/>
+      <c r="D64" s="360"/>
+      <c r="E64" s="360"/>
+      <c r="F64" s="360"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="360" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="360"/>
+      <c r="D65" s="360"/>
+      <c r="E65" s="360"/>
+      <c r="F65" s="360"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>8.2484427053797146E-2</v>
+        <v>8.2168394766234706E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>0.10384615384615385</v>
+        <v>0.10344827586206898</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>444</v>
@@ -4971,22 +4971,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="360" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="360"/>
+      <c r="D80" s="360"/>
+      <c r="E80" s="360"/>
+      <c r="F80" s="360"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="360" t="s">
+      <c r="B81" s="363" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="360"/>
-      <c r="D81" s="360"/>
-      <c r="E81" s="360"/>
-      <c r="F81" s="360"/>
+      <c r="C81" s="363"/>
+      <c r="D81" s="363"/>
+      <c r="E81" s="363"/>
+      <c r="F81" s="363"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5030,22 +5030,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="360" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="360"/>
+      <c r="D89" s="360"/>
+      <c r="E89" s="360"/>
+      <c r="F89" s="360"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="360" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="360"/>
+      <c r="D90" s="360"/>
+      <c r="E90" s="360"/>
+      <c r="F90" s="360"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5082,13 +5082,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="360" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="360"/>
+      <c r="D97" s="360"/>
+      <c r="E97" s="360"/>
+      <c r="F97" s="360"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5101,13 +5101,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="360" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="360"/>
+      <c r="D101" s="360"/>
+      <c r="E101" s="360"/>
+      <c r="F101" s="360"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5229,13 +5229,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="360" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="360"/>
+      <c r="D116" s="360"/>
+      <c r="E116" s="360"/>
+      <c r="F116" s="360"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5274,13 +5274,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="361" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="361"/>
+      <c r="D123" s="361"/>
+      <c r="E123" s="361"/>
+      <c r="F123" s="361"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5423,13 +5423,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="363" t="s">
+      <c r="B134" s="364" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="363"/>
-      <c r="D134" s="363"/>
-      <c r="E134" s="363"/>
-      <c r="F134" s="363"/>
+      <c r="C134" s="364"/>
+      <c r="D134" s="364"/>
+      <c r="E134" s="364"/>
+      <c r="F134" s="364"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5442,22 +5442,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="361" t="s">
+      <c r="B138" s="365" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="361"/>
-      <c r="D138" s="361"/>
-      <c r="E138" s="361"/>
-      <c r="F138" s="361"/>
+      <c r="C138" s="365"/>
+      <c r="D138" s="365"/>
+      <c r="E138" s="365"/>
+      <c r="F138" s="365"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="360" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="360"/>
+      <c r="D139" s="360"/>
+      <c r="E139" s="360"/>
+      <c r="F139" s="360"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5790,13 +5790,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="365" t="s">
+      <c r="B179" s="359" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="360"/>
+      <c r="D179" s="360"/>
+      <c r="E179" s="360"/>
+      <c r="F179" s="360"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5833,13 +5833,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="361" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="361"/>
+      <c r="D188" s="361"/>
+      <c r="E188" s="361"/>
+      <c r="F188" s="361"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5847,22 +5847,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="364" t="s">
+      <c r="B191" s="358" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="364"/>
-      <c r="D191" s="364"/>
-      <c r="E191" s="364"/>
-      <c r="F191" s="364"/>
+      <c r="C191" s="358"/>
+      <c r="D191" s="358"/>
+      <c r="E191" s="358"/>
+      <c r="F191" s="358"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="364" t="s">
+      <c r="B192" s="358" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="364"/>
-      <c r="D192" s="364"/>
-      <c r="E192" s="364"/>
-      <c r="F192" s="364"/>
+      <c r="C192" s="358"/>
+      <c r="D192" s="358"/>
+      <c r="E192" s="358"/>
+      <c r="F192" s="358"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5886,17 +5886,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5913,6 +5902,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13456,20 +13456,20 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>0.10384615384615385</v>
+        <v>0.10344827586206898</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>0.10384615384615385</v>
+        <v>0.10344827586206898</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>9.6923076923076945E-2</v>
+        <v>9.6551724137931061E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>0.14884615384615388</v>
+        <v>0.14827586206896554</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
@@ -14655,50 +14655,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>8.2484427053797146E-2</v>
+        <v>8.2168394766234706E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>9.6253488810152485E-2</v>
+        <v>9.5884701496703639E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>0.13245079159665121</v>
+        <v>0.13194331729934605</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>0.21480828694639093</v>
+        <v>0.21398526668989135</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>0.17649870388659619</v>
+        <v>0.17582246364181997</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>6.3318614477304372E-2</v>
+        <v>6.3076014421835774E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>8.0382065976606826E-2</v>
+        <v>8.0074088712328642E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>7.1569493787938226E-2</v>
+        <v>7.1295281168061081E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>6.7974508274265003E-2</v>
+        <v>6.7714069545244823E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>1.2032843959900364E-2</v>
+        <v>1.1986741109479291E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>5.2126005647128593E-3</v>
+        <v>5.1926289150396304E-3</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14712,43 +14712,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13711614409025946</v>
+        <v>0.13659079487918568</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.17382925183583983</v>
+        <v>0.1731632393766987</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.24992160093274687</v>
+        <v>0.24896404690618465</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.23123698366750667</v>
+        <v>0.23035101821284193</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.9695817795790861E-2</v>
+        <v>8.9352155658642241E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.885407172355643E-2</v>
+        <v>8.8513634667144347E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.7024849174013083E-2</v>
+        <v>8.6691420633116481E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.9340821853102867E-2</v>
+        <v>8.8998519853665706E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.1112163223022873E-3</v>
+        <v>5.0916331180022789E-3</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-5.3749891109584065E-2</v>
+        <v>-5.3543952829470727E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18698,7 +18698,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-2.6</v>
+        <v>-2.61</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18938,7 +18938,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19536,7 +19536,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19549,7 +19549,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.28766954280717139</v>
+        <v>0.28589032424265848</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/0639.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0639.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4602AA5-8BD7-4ED2-8E2F-91A148713039}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{963A2D4F-C389-46C2-855B-DF9041C615AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3893,29 +3893,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4333,7 +4333,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>2.61</v>
+        <v>2.64</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>13287.6816597</v>
+        <v>13440.4136328</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4391,13 +4391,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="360" t="s">
+      <c r="B18" s="358" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="360"/>
-      <c r="D18" s="360"/>
-      <c r="E18" s="360"/>
-      <c r="F18" s="360"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.28589032424265848</v>
+        <v>0.28060956942594761</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4597,22 +4597,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="360" t="s">
+      <c r="B36" s="358" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="360"/>
-      <c r="D36" s="360"/>
-      <c r="E36" s="360"/>
-      <c r="F36" s="360"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="363" t="s">
+      <c r="B37" s="360" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="363"/>
-      <c r="D37" s="363"/>
-      <c r="E37" s="363"/>
-      <c r="F37" s="363"/>
+      <c r="C37" s="360"/>
+      <c r="D37" s="360"/>
+      <c r="E37" s="360"/>
+      <c r="F37" s="360"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4624,13 +4624,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="361" t="s">
+      <c r="B40" s="359" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="361"/>
-      <c r="D40" s="361"/>
-      <c r="E40" s="361"/>
-      <c r="F40" s="361"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4650,13 +4650,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="361" t="s">
+      <c r="B43" s="359" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="361"/>
-      <c r="D43" s="361"/>
-      <c r="E43" s="361"/>
-      <c r="F43" s="361"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4685,13 +4685,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="361" t="s">
+      <c r="B47" s="359" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="361"/>
-      <c r="D47" s="361"/>
-      <c r="E47" s="361"/>
-      <c r="F47" s="361"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4707,13 +4707,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="361" t="s">
+      <c r="B50" s="359" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="361"/>
-      <c r="D50" s="361"/>
-      <c r="E50" s="361"/>
-      <c r="F50" s="361"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4777,13 +4777,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="361" t="s">
+      <c r="B58" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="361"/>
-      <c r="D58" s="361"/>
-      <c r="E58" s="361"/>
-      <c r="F58" s="361"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4799,7 +4799,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="361" t="s">
+      <c r="B61" s="359" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4821,22 +4821,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="360" t="s">
+      <c r="B64" s="358" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="360"/>
-      <c r="D64" s="360"/>
-      <c r="E64" s="360"/>
-      <c r="F64" s="360"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="360" t="s">
+      <c r="B65" s="358" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="360"/>
-      <c r="D65" s="360"/>
-      <c r="E65" s="360"/>
-      <c r="F65" s="360"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>8.2168394766234706E-2</v>
+        <v>8.1234663007527477E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>0.10344827586206898</v>
+        <v>0.10227272727272728</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>444</v>
@@ -4971,22 +4971,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="360" t="s">
+      <c r="B80" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="360"/>
-      <c r="D80" s="360"/>
-      <c r="E80" s="360"/>
-      <c r="F80" s="360"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="363" t="s">
+      <c r="B81" s="360" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="363"/>
-      <c r="D81" s="363"/>
-      <c r="E81" s="363"/>
-      <c r="F81" s="363"/>
+      <c r="C81" s="360"/>
+      <c r="D81" s="360"/>
+      <c r="E81" s="360"/>
+      <c r="F81" s="360"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5030,22 +5030,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="360" t="s">
+      <c r="B89" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="360"/>
-      <c r="D89" s="360"/>
-      <c r="E89" s="360"/>
-      <c r="F89" s="360"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="360" t="s">
+      <c r="B90" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="360"/>
-      <c r="D90" s="360"/>
-      <c r="E90" s="360"/>
-      <c r="F90" s="360"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5082,13 +5082,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="360" t="s">
+      <c r="B97" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="360"/>
-      <c r="D97" s="360"/>
-      <c r="E97" s="360"/>
-      <c r="F97" s="360"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5101,13 +5101,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="360" t="s">
+      <c r="B101" s="358" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="360"/>
-      <c r="D101" s="360"/>
-      <c r="E101" s="360"/>
-      <c r="F101" s="360"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5229,13 +5229,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="360" t="s">
+      <c r="B116" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="360"/>
-      <c r="D116" s="360"/>
-      <c r="E116" s="360"/>
-      <c r="F116" s="360"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5274,13 +5274,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="361" t="s">
+      <c r="B123" s="359" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="361"/>
-      <c r="D123" s="361"/>
-      <c r="E123" s="361"/>
-      <c r="F123" s="361"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5423,13 +5423,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="364" t="s">
+      <c r="B134" s="363" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="364"/>
-      <c r="D134" s="364"/>
-      <c r="E134" s="364"/>
-      <c r="F134" s="364"/>
+      <c r="C134" s="363"/>
+      <c r="D134" s="363"/>
+      <c r="E134" s="363"/>
+      <c r="F134" s="363"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5442,22 +5442,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="365" t="s">
+      <c r="B138" s="361" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="365"/>
-      <c r="D138" s="365"/>
-      <c r="E138" s="365"/>
-      <c r="F138" s="365"/>
+      <c r="C138" s="361"/>
+      <c r="D138" s="361"/>
+      <c r="E138" s="361"/>
+      <c r="F138" s="361"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="360" t="s">
+      <c r="B139" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="360"/>
-      <c r="D139" s="360"/>
-      <c r="E139" s="360"/>
-      <c r="F139" s="360"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5790,13 +5790,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="359" t="s">
+      <c r="B179" s="365" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="360"/>
-      <c r="D179" s="360"/>
-      <c r="E179" s="360"/>
-      <c r="F179" s="360"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5833,13 +5833,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="361" t="s">
+      <c r="B188" s="359" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="361"/>
-      <c r="D188" s="361"/>
-      <c r="E188" s="361"/>
-      <c r="F188" s="361"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5847,22 +5847,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="358" t="s">
+      <c r="B191" s="364" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="358"/>
-      <c r="D191" s="358"/>
-      <c r="E191" s="358"/>
-      <c r="F191" s="358"/>
+      <c r="C191" s="364"/>
+      <c r="D191" s="364"/>
+      <c r="E191" s="364"/>
+      <c r="F191" s="364"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="358" t="s">
+      <c r="B192" s="364" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="358"/>
-      <c r="D192" s="358"/>
-      <c r="E192" s="358"/>
-      <c r="F192" s="358"/>
+      <c r="C192" s="364"/>
+      <c r="D192" s="364"/>
+      <c r="E192" s="364"/>
+      <c r="F192" s="364"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5886,6 +5886,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5902,17 +5913,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13456,20 +13456,20 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>0.10344827586206898</v>
+        <v>0.10227272727272728</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>0.10344827586206898</v>
+        <v>0.10227272727272728</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>9.6551724137931061E-2</v>
+        <v>9.5454545454545472E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>0.14827586206896554</v>
+        <v>0.14659090909090911</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
@@ -14655,50 +14655,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>8.2168394766234706E-2</v>
+        <v>8.1234663007527477E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>9.5884701496703639E-2</v>
+        <v>9.4795102616059265E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>0.13194331729934605</v>
+        <v>0.13044396142094439</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>0.21398526668989135</v>
+        <v>0.21155361593205166</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>0.17582246364181997</v>
+        <v>0.17382448110043563</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>6.3076014421835774E-2</v>
+        <v>6.2359241530678552E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>8.0074088712328642E-2</v>
+        <v>7.9164155886052176E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>7.1295281168061081E-2</v>
+        <v>7.0485107518424017E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>6.7714069545244823E-2</v>
+        <v>6.6944591482230684E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>1.1986741109479291E-2</v>
+        <v>1.1850528142326115E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>5.1926289150396304E-3</v>
+        <v>5.133621768277816E-3</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14712,43 +14712,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13659079487918568</v>
+        <v>0.13503862675555853</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1731632393766987</v>
+        <v>0.17119547529287255</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.24896404690618465</v>
+        <v>0.24613491000952342</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.23035101821284193</v>
+        <v>0.22773339300587778</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.9352155658642241E-2</v>
+        <v>8.8336790253430386E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.8513634667144347E-2</v>
+        <v>8.7507797909563145E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.6691420633116481E-2</v>
+        <v>8.57062908531947E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.8998519853665706E-2</v>
+        <v>8.798717303714676E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.0916331180022789E-3</v>
+        <v>5.0337736507522516E-3</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-5.3543952829470727E-2</v>
+        <v>-5.2935498820044911E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18698,7 +18698,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-2.61</v>
+        <v>-2.64</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18938,7 +18938,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>2.61</v>
+        <v>2.64</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19536,7 +19536,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>2.61</v>
+        <v>2.64</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19549,7 +19549,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.28589032424265848</v>
+        <v>0.28060956942594761</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/0639.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0639.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{963A2D4F-C389-46C2-855B-DF9041C615AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF60E0FA-D148-4088-9D59-031E4AEA4026}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3893,29 +3893,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4333,7 +4333,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>13440.4136328</v>
+        <v>13745.877579</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4391,13 +4391,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="360" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="360"/>
+      <c r="D18" s="360"/>
+      <c r="E18" s="360"/>
+      <c r="F18" s="360"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.28060956942594761</v>
+        <v>0.27029639042727904</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4597,22 +4597,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="360" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="360"/>
+      <c r="D36" s="360"/>
+      <c r="E36" s="360"/>
+      <c r="F36" s="360"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="360" t="s">
+      <c r="B37" s="363" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="360"/>
-      <c r="D37" s="360"/>
-      <c r="E37" s="360"/>
-      <c r="F37" s="360"/>
+      <c r="C37" s="363"/>
+      <c r="D37" s="363"/>
+      <c r="E37" s="363"/>
+      <c r="F37" s="363"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4624,13 +4624,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="361" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="361"/>
+      <c r="D40" s="361"/>
+      <c r="E40" s="361"/>
+      <c r="F40" s="361"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4650,13 +4650,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="361" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="361"/>
+      <c r="D43" s="361"/>
+      <c r="E43" s="361"/>
+      <c r="F43" s="361"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4685,13 +4685,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="361" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="361"/>
+      <c r="D47" s="361"/>
+      <c r="E47" s="361"/>
+      <c r="F47" s="361"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4707,13 +4707,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="361" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="361"/>
+      <c r="D50" s="361"/>
+      <c r="E50" s="361"/>
+      <c r="F50" s="361"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4777,13 +4777,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="361" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="361"/>
+      <c r="D58" s="361"/>
+      <c r="E58" s="361"/>
+      <c r="F58" s="361"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4799,7 +4799,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="361" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4821,22 +4821,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="360" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="360"/>
+      <c r="D64" s="360"/>
+      <c r="E64" s="360"/>
+      <c r="F64" s="360"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="360" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="360"/>
+      <c r="D65" s="360"/>
+      <c r="E65" s="360"/>
+      <c r="F65" s="360"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>8.1234663007527477E-2</v>
+        <v>7.942944827402687E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>0.10227272727272728</v>
+        <v>0.1</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>444</v>
@@ -4971,22 +4971,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="360" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="360"/>
+      <c r="D80" s="360"/>
+      <c r="E80" s="360"/>
+      <c r="F80" s="360"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="360" t="s">
+      <c r="B81" s="363" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="360"/>
-      <c r="D81" s="360"/>
-      <c r="E81" s="360"/>
-      <c r="F81" s="360"/>
+      <c r="C81" s="363"/>
+      <c r="D81" s="363"/>
+      <c r="E81" s="363"/>
+      <c r="F81" s="363"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5030,22 +5030,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="360" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="360"/>
+      <c r="D89" s="360"/>
+      <c r="E89" s="360"/>
+      <c r="F89" s="360"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="360" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="360"/>
+      <c r="D90" s="360"/>
+      <c r="E90" s="360"/>
+      <c r="F90" s="360"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5082,13 +5082,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="360" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="360"/>
+      <c r="D97" s="360"/>
+      <c r="E97" s="360"/>
+      <c r="F97" s="360"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5101,13 +5101,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="360" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="360"/>
+      <c r="D101" s="360"/>
+      <c r="E101" s="360"/>
+      <c r="F101" s="360"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5229,13 +5229,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="360" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="360"/>
+      <c r="D116" s="360"/>
+      <c r="E116" s="360"/>
+      <c r="F116" s="360"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5274,13 +5274,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="361" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="361"/>
+      <c r="D123" s="361"/>
+      <c r="E123" s="361"/>
+      <c r="F123" s="361"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5423,13 +5423,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="363" t="s">
+      <c r="B134" s="364" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="363"/>
-      <c r="D134" s="363"/>
-      <c r="E134" s="363"/>
-      <c r="F134" s="363"/>
+      <c r="C134" s="364"/>
+      <c r="D134" s="364"/>
+      <c r="E134" s="364"/>
+      <c r="F134" s="364"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5442,22 +5442,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="361" t="s">
+      <c r="B138" s="365" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="361"/>
-      <c r="D138" s="361"/>
-      <c r="E138" s="361"/>
-      <c r="F138" s="361"/>
+      <c r="C138" s="365"/>
+      <c r="D138" s="365"/>
+      <c r="E138" s="365"/>
+      <c r="F138" s="365"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="360" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="360"/>
+      <c r="D139" s="360"/>
+      <c r="E139" s="360"/>
+      <c r="F139" s="360"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5790,13 +5790,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="365" t="s">
+      <c r="B179" s="359" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="360"/>
+      <c r="D179" s="360"/>
+      <c r="E179" s="360"/>
+      <c r="F179" s="360"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5833,13 +5833,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="361" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="361"/>
+      <c r="D188" s="361"/>
+      <c r="E188" s="361"/>
+      <c r="F188" s="361"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5847,22 +5847,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="364" t="s">
+      <c r="B191" s="358" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="364"/>
-      <c r="D191" s="364"/>
-      <c r="E191" s="364"/>
-      <c r="F191" s="364"/>
+      <c r="C191" s="358"/>
+      <c r="D191" s="358"/>
+      <c r="E191" s="358"/>
+      <c r="F191" s="358"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="364" t="s">
+      <c r="B192" s="358" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="364"/>
-      <c r="D192" s="364"/>
-      <c r="E192" s="364"/>
-      <c r="F192" s="364"/>
+      <c r="C192" s="358"/>
+      <c r="D192" s="358"/>
+      <c r="E192" s="358"/>
+      <c r="F192" s="358"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5886,17 +5886,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5913,6 +5902,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13456,20 +13456,20 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>0.10227272727272728</v>
+        <v>0.1</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>0.10227272727272728</v>
+        <v>0.1</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>9.5454545454545472E-2</v>
+        <v>9.3333333333333351E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>0.14659090909090911</v>
+        <v>0.14333333333333334</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
@@ -14655,50 +14655,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>8.1234663007527477E-2</v>
+        <v>7.942944827402687E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>9.4795102616059265E-2</v>
+        <v>9.2688544780146834E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>0.13044396142094439</v>
+        <v>0.12754520672270117</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>0.21155361593205166</v>
+        <v>0.20685242446689495</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>0.17382448110043563</v>
+        <v>0.16996171485375927</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>6.2359241530678552E-2</v>
+        <v>6.0973480607774584E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>7.9164155886052176E-2</v>
+        <v>7.740495242191768E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>7.0485107518424017E-2</v>
+        <v>6.8918771795792366E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>6.6944591482230684E-2</v>
+        <v>6.5456933893736663E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>1.1850528142326115E-2</v>
+        <v>1.1587183072496647E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>5.133621768277816E-3</v>
+        <v>5.0195412845383085E-3</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14712,43 +14712,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13503862675555853</v>
+        <v>0.13203776838321279</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.17119547529287255</v>
+        <v>0.16739113139747538</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.24613491000952342</v>
+        <v>0.24066524534264513</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.22773339300587778</v>
+        <v>0.22267265093908051</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.8336790253430386E-2</v>
+        <v>8.6373750470020827E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.7507797909563145E-2</v>
+        <v>8.5563180178239537E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.57062908531947E-2</v>
+        <v>8.3801706612012597E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.798717303714676E-2</v>
+        <v>8.6031902525210174E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.0337736507522516E-3</v>
+        <v>4.921912014068869E-3</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-5.2935498820044911E-2</v>
+        <v>-5.1759154401821696E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18698,7 +18698,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-2.64</v>
+        <v>-2.7</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18938,7 +18938,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19536,7 +19536,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19549,7 +19549,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.28060956942594761</v>
+        <v>0.27029639042727904</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/0639.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0639.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF60E0FA-D148-4088-9D59-031E4AEA4026}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F1CA534-0D70-4921-95B9-19F5C34B6786}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3893,29 +3893,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4391,13 +4391,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="360" t="s">
+      <c r="B18" s="358" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="360"/>
-      <c r="D18" s="360"/>
-      <c r="E18" s="360"/>
-      <c r="F18" s="360"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4597,22 +4597,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="360" t="s">
+      <c r="B36" s="358" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="360"/>
-      <c r="D36" s="360"/>
-      <c r="E36" s="360"/>
-      <c r="F36" s="360"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="363" t="s">
+      <c r="B37" s="360" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="363"/>
-      <c r="D37" s="363"/>
-      <c r="E37" s="363"/>
-      <c r="F37" s="363"/>
+      <c r="C37" s="360"/>
+      <c r="D37" s="360"/>
+      <c r="E37" s="360"/>
+      <c r="F37" s="360"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4624,13 +4624,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="361" t="s">
+      <c r="B40" s="359" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="361"/>
-      <c r="D40" s="361"/>
-      <c r="E40" s="361"/>
-      <c r="F40" s="361"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4650,13 +4650,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="361" t="s">
+      <c r="B43" s="359" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="361"/>
-      <c r="D43" s="361"/>
-      <c r="E43" s="361"/>
-      <c r="F43" s="361"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4685,13 +4685,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="361" t="s">
+      <c r="B47" s="359" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="361"/>
-      <c r="D47" s="361"/>
-      <c r="E47" s="361"/>
-      <c r="F47" s="361"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4707,13 +4707,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="361" t="s">
+      <c r="B50" s="359" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="361"/>
-      <c r="D50" s="361"/>
-      <c r="E50" s="361"/>
-      <c r="F50" s="361"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4777,13 +4777,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="361" t="s">
+      <c r="B58" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="361"/>
-      <c r="D58" s="361"/>
-      <c r="E58" s="361"/>
-      <c r="F58" s="361"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4799,7 +4799,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="361" t="s">
+      <c r="B61" s="359" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4821,22 +4821,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="360" t="s">
+      <c r="B64" s="358" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="360"/>
-      <c r="D64" s="360"/>
-      <c r="E64" s="360"/>
-      <c r="F64" s="360"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="360" t="s">
+      <c r="B65" s="358" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="360"/>
-      <c r="D65" s="360"/>
-      <c r="E65" s="360"/>
-      <c r="F65" s="360"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4971,22 +4971,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="360" t="s">
+      <c r="B80" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="360"/>
-      <c r="D80" s="360"/>
-      <c r="E80" s="360"/>
-      <c r="F80" s="360"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="363" t="s">
+      <c r="B81" s="360" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="363"/>
-      <c r="D81" s="363"/>
-      <c r="E81" s="363"/>
-      <c r="F81" s="363"/>
+      <c r="C81" s="360"/>
+      <c r="D81" s="360"/>
+      <c r="E81" s="360"/>
+      <c r="F81" s="360"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5030,22 +5030,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="360" t="s">
+      <c r="B89" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="360"/>
-      <c r="D89" s="360"/>
-      <c r="E89" s="360"/>
-      <c r="F89" s="360"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="360" t="s">
+      <c r="B90" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="360"/>
-      <c r="D90" s="360"/>
-      <c r="E90" s="360"/>
-      <c r="F90" s="360"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5082,13 +5082,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="360" t="s">
+      <c r="B97" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="360"/>
-      <c r="D97" s="360"/>
-      <c r="E97" s="360"/>
-      <c r="F97" s="360"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5101,13 +5101,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="360" t="s">
+      <c r="B101" s="358" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="360"/>
-      <c r="D101" s="360"/>
-      <c r="E101" s="360"/>
-      <c r="F101" s="360"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5229,13 +5229,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="360" t="s">
+      <c r="B116" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="360"/>
-      <c r="D116" s="360"/>
-      <c r="E116" s="360"/>
-      <c r="F116" s="360"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5274,13 +5274,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="361" t="s">
+      <c r="B123" s="359" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="361"/>
-      <c r="D123" s="361"/>
-      <c r="E123" s="361"/>
-      <c r="F123" s="361"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5423,13 +5423,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="364" t="s">
+      <c r="B134" s="363" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="364"/>
-      <c r="D134" s="364"/>
-      <c r="E134" s="364"/>
-      <c r="F134" s="364"/>
+      <c r="C134" s="363"/>
+      <c r="D134" s="363"/>
+      <c r="E134" s="363"/>
+      <c r="F134" s="363"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5442,22 +5442,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="365" t="s">
+      <c r="B138" s="361" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="365"/>
-      <c r="D138" s="365"/>
-      <c r="E138" s="365"/>
-      <c r="F138" s="365"/>
+      <c r="C138" s="361"/>
+      <c r="D138" s="361"/>
+      <c r="E138" s="361"/>
+      <c r="F138" s="361"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="360" t="s">
+      <c r="B139" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="360"/>
-      <c r="D139" s="360"/>
-      <c r="E139" s="360"/>
-      <c r="F139" s="360"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5790,13 +5790,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="359" t="s">
+      <c r="B179" s="365" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="360"/>
-      <c r="D179" s="360"/>
-      <c r="E179" s="360"/>
-      <c r="F179" s="360"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5833,13 +5833,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="361" t="s">
+      <c r="B188" s="359" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="361"/>
-      <c r="D188" s="361"/>
-      <c r="E188" s="361"/>
-      <c r="F188" s="361"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5847,22 +5847,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="358" t="s">
+      <c r="B191" s="364" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="358"/>
-      <c r="D191" s="358"/>
-      <c r="E191" s="358"/>
-      <c r="F191" s="358"/>
+      <c r="C191" s="364"/>
+      <c r="D191" s="364"/>
+      <c r="E191" s="364"/>
+      <c r="F191" s="364"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="358" t="s">
+      <c r="B192" s="364" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="358"/>
-      <c r="D192" s="358"/>
-      <c r="E192" s="358"/>
-      <c r="F192" s="358"/>
+      <c r="C192" s="364"/>
+      <c r="D192" s="364"/>
+      <c r="E192" s="364"/>
+      <c r="F192" s="364"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5886,6 +5886,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5902,17 +5913,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">

--- a/financial_models/opportunities/0639.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0639.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F1CA534-0D70-4921-95B9-19F5C34B6786}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF8C2FBD-9483-42F2-A240-EBEA479F5232}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3893,29 +3893,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4333,7 +4333,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>2.7</v>
+        <v>2.87</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>13745.877579</v>
+        <v>14611.3587599</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4391,13 +4391,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="360" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="360"/>
+      <c r="D18" s="360"/>
+      <c r="E18" s="360"/>
+      <c r="F18" s="360"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.27029639042727904</v>
+        <v>0.24274033838293119</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4597,22 +4597,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="360" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="360"/>
+      <c r="D36" s="360"/>
+      <c r="E36" s="360"/>
+      <c r="F36" s="360"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="360" t="s">
+      <c r="B37" s="363" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="360"/>
-      <c r="D37" s="360"/>
-      <c r="E37" s="360"/>
-      <c r="F37" s="360"/>
+      <c r="C37" s="363"/>
+      <c r="D37" s="363"/>
+      <c r="E37" s="363"/>
+      <c r="F37" s="363"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4624,13 +4624,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="361" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="361"/>
+      <c r="D40" s="361"/>
+      <c r="E40" s="361"/>
+      <c r="F40" s="361"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4650,13 +4650,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="361" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="361"/>
+      <c r="D43" s="361"/>
+      <c r="E43" s="361"/>
+      <c r="F43" s="361"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4685,13 +4685,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="361" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="361"/>
+      <c r="D47" s="361"/>
+      <c r="E47" s="361"/>
+      <c r="F47" s="361"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4707,13 +4707,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="361" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="361"/>
+      <c r="D50" s="361"/>
+      <c r="E50" s="361"/>
+      <c r="F50" s="361"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4777,13 +4777,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="361" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="361"/>
+      <c r="D58" s="361"/>
+      <c r="E58" s="361"/>
+      <c r="F58" s="361"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4799,7 +4799,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="361" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4821,22 +4821,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="360" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="360"/>
+      <c r="D64" s="360"/>
+      <c r="E64" s="360"/>
+      <c r="F64" s="360"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="360" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="360"/>
+      <c r="D65" s="360"/>
+      <c r="E65" s="360"/>
+      <c r="F65" s="360"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>7.942944827402687E-2</v>
+        <v>7.4724568062673372E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>0.1</v>
+        <v>9.4076655052264813E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>444</v>
@@ -4971,22 +4971,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="360" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="360"/>
+      <c r="D80" s="360"/>
+      <c r="E80" s="360"/>
+      <c r="F80" s="360"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="360" t="s">
+      <c r="B81" s="363" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="360"/>
-      <c r="D81" s="360"/>
-      <c r="E81" s="360"/>
-      <c r="F81" s="360"/>
+      <c r="C81" s="363"/>
+      <c r="D81" s="363"/>
+      <c r="E81" s="363"/>
+      <c r="F81" s="363"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5030,22 +5030,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="360" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="360"/>
+      <c r="D89" s="360"/>
+      <c r="E89" s="360"/>
+      <c r="F89" s="360"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="360" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="360"/>
+      <c r="D90" s="360"/>
+      <c r="E90" s="360"/>
+      <c r="F90" s="360"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5082,13 +5082,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="360" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="360"/>
+      <c r="D97" s="360"/>
+      <c r="E97" s="360"/>
+      <c r="F97" s="360"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5101,13 +5101,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="360" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="360"/>
+      <c r="D101" s="360"/>
+      <c r="E101" s="360"/>
+      <c r="F101" s="360"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5229,13 +5229,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="360" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="360"/>
+      <c r="D116" s="360"/>
+      <c r="E116" s="360"/>
+      <c r="F116" s="360"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5274,13 +5274,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="361" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="361"/>
+      <c r="D123" s="361"/>
+      <c r="E123" s="361"/>
+      <c r="F123" s="361"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5423,13 +5423,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="363" t="s">
+      <c r="B134" s="364" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="363"/>
-      <c r="D134" s="363"/>
-      <c r="E134" s="363"/>
-      <c r="F134" s="363"/>
+      <c r="C134" s="364"/>
+      <c r="D134" s="364"/>
+      <c r="E134" s="364"/>
+      <c r="F134" s="364"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5442,22 +5442,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="361" t="s">
+      <c r="B138" s="365" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="361"/>
-      <c r="D138" s="361"/>
-      <c r="E138" s="361"/>
-      <c r="F138" s="361"/>
+      <c r="C138" s="365"/>
+      <c r="D138" s="365"/>
+      <c r="E138" s="365"/>
+      <c r="F138" s="365"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="360" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="360"/>
+      <c r="D139" s="360"/>
+      <c r="E139" s="360"/>
+      <c r="F139" s="360"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5790,13 +5790,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="365" t="s">
+      <c r="B179" s="359" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="360"/>
+      <c r="D179" s="360"/>
+      <c r="E179" s="360"/>
+      <c r="F179" s="360"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5833,13 +5833,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="361" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="361"/>
+      <c r="D188" s="361"/>
+      <c r="E188" s="361"/>
+      <c r="F188" s="361"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5847,22 +5847,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="364" t="s">
+      <c r="B191" s="358" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="364"/>
-      <c r="D191" s="364"/>
-      <c r="E191" s="364"/>
-      <c r="F191" s="364"/>
+      <c r="C191" s="358"/>
+      <c r="D191" s="358"/>
+      <c r="E191" s="358"/>
+      <c r="F191" s="358"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="364" t="s">
+      <c r="B192" s="358" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="364"/>
-      <c r="D192" s="364"/>
-      <c r="E192" s="364"/>
-      <c r="F192" s="364"/>
+      <c r="C192" s="358"/>
+      <c r="D192" s="358"/>
+      <c r="E192" s="358"/>
+      <c r="F192" s="358"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5886,17 +5886,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5913,6 +5902,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13456,20 +13456,20 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>0.1</v>
+        <v>9.4076655052264813E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>0.1</v>
+        <v>9.4076655052264813E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>9.3333333333333351E-2</v>
+        <v>8.780487804878051E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>0.14333333333333334</v>
+        <v>0.13484320557491292</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
@@ -14655,50 +14655,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>7.942944827402687E-2</v>
+        <v>7.4724568062673372E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>9.2688544780146834E-2</v>
+        <v>8.719828254578274E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>0.12754520672270117</v>
+        <v>0.11999026416421364</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>0.20685242446689495</v>
+        <v>0.19459984183296739</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>0.16996171485375927</v>
+        <v>0.15989429620388504</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>6.0973480607774584E-2</v>
+        <v>5.7361811024735671E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>7.740495242191768E-2</v>
+        <v>7.2819990083337185E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>6.8918771795792366E-2</v>
+        <v>6.4836475208585154E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>6.5456933893736663E-2</v>
+        <v>6.1579693906999647E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>1.1587183072496647E-2</v>
+        <v>1.0900834249387089E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>5.0195412845383085E-3</v>
+        <v>4.7222165394611264E-3</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14712,43 +14712,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13203776838321279</v>
+        <v>0.12421671590058347</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16739113139747538</v>
+        <v>0.15747597727288626</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.24066524534264513</v>
+        <v>0.22640981269168708</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.22267265093908051</v>
+        <v>0.20948298171969246</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.6373750470020827E-2</v>
+        <v>8.1257535285385443E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.5563180178239537E-2</v>
+        <v>8.0494977868030226E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.3801706612012597E-2</v>
+        <v>7.8837842457294083E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.6031902525210174E-2</v>
+        <v>8.093593617354268E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.921912014068869E-3</v>
+        <v>4.630370187451549E-3</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-5.1759154401821696E-2</v>
+        <v>-4.8693281144570937E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18698,7 +18698,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-2.7</v>
+        <v>-2.87</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18938,7 +18938,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>2.7</v>
+        <v>2.87</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19536,7 +19536,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>2.7</v>
+        <v>2.87</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19549,7 +19549,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.27029639042727904</v>
+        <v>0.24274033838293119</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/0639.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0639.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF8C2FBD-9483-42F2-A240-EBEA479F5232}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BC43084-EF1D-4A40-BFB8-80B2220089EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3893,29 +3893,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4333,7 +4333,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>2.87</v>
+        <v>2.89</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>14611.3587599</v>
+        <v>14713.180075300001</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4391,13 +4391,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="360" t="s">
+      <c r="B18" s="358" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="360"/>
-      <c r="D18" s="360"/>
-      <c r="E18" s="360"/>
-      <c r="F18" s="360"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.24274033838293119</v>
+        <v>0.23964880679790124</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4597,22 +4597,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="360" t="s">
+      <c r="B36" s="358" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="360"/>
-      <c r="D36" s="360"/>
-      <c r="E36" s="360"/>
-      <c r="F36" s="360"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="363" t="s">
+      <c r="B37" s="360" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="363"/>
-      <c r="D37" s="363"/>
-      <c r="E37" s="363"/>
-      <c r="F37" s="363"/>
+      <c r="C37" s="360"/>
+      <c r="D37" s="360"/>
+      <c r="E37" s="360"/>
+      <c r="F37" s="360"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4624,13 +4624,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="361" t="s">
+      <c r="B40" s="359" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="361"/>
-      <c r="D40" s="361"/>
-      <c r="E40" s="361"/>
-      <c r="F40" s="361"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4650,13 +4650,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="361" t="s">
+      <c r="B43" s="359" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="361"/>
-      <c r="D43" s="361"/>
-      <c r="E43" s="361"/>
-      <c r="F43" s="361"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4685,13 +4685,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="361" t="s">
+      <c r="B47" s="359" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="361"/>
-      <c r="D47" s="361"/>
-      <c r="E47" s="361"/>
-      <c r="F47" s="361"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4707,13 +4707,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="361" t="s">
+      <c r="B50" s="359" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="361"/>
-      <c r="D50" s="361"/>
-      <c r="E50" s="361"/>
-      <c r="F50" s="361"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4777,13 +4777,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="361" t="s">
+      <c r="B58" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="361"/>
-      <c r="D58" s="361"/>
-      <c r="E58" s="361"/>
-      <c r="F58" s="361"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4799,7 +4799,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="361" t="s">
+      <c r="B61" s="359" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4821,22 +4821,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="360" t="s">
+      <c r="B64" s="358" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="360"/>
-      <c r="D64" s="360"/>
-      <c r="E64" s="360"/>
-      <c r="F64" s="360"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="360" t="s">
+      <c r="B65" s="358" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="360"/>
-      <c r="D65" s="360"/>
-      <c r="E65" s="360"/>
-      <c r="F65" s="360"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>7.4724568062673372E-2</v>
+        <v>7.4207443024177352E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>9.4076655052264813E-2</v>
+        <v>9.3425605536332182E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>444</v>
@@ -4971,22 +4971,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="360" t="s">
+      <c r="B80" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="360"/>
-      <c r="D80" s="360"/>
-      <c r="E80" s="360"/>
-      <c r="F80" s="360"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="363" t="s">
+      <c r="B81" s="360" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="363"/>
-      <c r="D81" s="363"/>
-      <c r="E81" s="363"/>
-      <c r="F81" s="363"/>
+      <c r="C81" s="360"/>
+      <c r="D81" s="360"/>
+      <c r="E81" s="360"/>
+      <c r="F81" s="360"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5030,22 +5030,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="360" t="s">
+      <c r="B89" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="360"/>
-      <c r="D89" s="360"/>
-      <c r="E89" s="360"/>
-      <c r="F89" s="360"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="360" t="s">
+      <c r="B90" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="360"/>
-      <c r="D90" s="360"/>
-      <c r="E90" s="360"/>
-      <c r="F90" s="360"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5082,13 +5082,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="360" t="s">
+      <c r="B97" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="360"/>
-      <c r="D97" s="360"/>
-      <c r="E97" s="360"/>
-      <c r="F97" s="360"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5101,13 +5101,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="360" t="s">
+      <c r="B101" s="358" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="360"/>
-      <c r="D101" s="360"/>
-      <c r="E101" s="360"/>
-      <c r="F101" s="360"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5229,13 +5229,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="360" t="s">
+      <c r="B116" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="360"/>
-      <c r="D116" s="360"/>
-      <c r="E116" s="360"/>
-      <c r="F116" s="360"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5274,13 +5274,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="361" t="s">
+      <c r="B123" s="359" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="361"/>
-      <c r="D123" s="361"/>
-      <c r="E123" s="361"/>
-      <c r="F123" s="361"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5423,13 +5423,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="364" t="s">
+      <c r="B134" s="363" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="364"/>
-      <c r="D134" s="364"/>
-      <c r="E134" s="364"/>
-      <c r="F134" s="364"/>
+      <c r="C134" s="363"/>
+      <c r="D134" s="363"/>
+      <c r="E134" s="363"/>
+      <c r="F134" s="363"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5442,22 +5442,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="365" t="s">
+      <c r="B138" s="361" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="365"/>
-      <c r="D138" s="365"/>
-      <c r="E138" s="365"/>
-      <c r="F138" s="365"/>
+      <c r="C138" s="361"/>
+      <c r="D138" s="361"/>
+      <c r="E138" s="361"/>
+      <c r="F138" s="361"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="360" t="s">
+      <c r="B139" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="360"/>
-      <c r="D139" s="360"/>
-      <c r="E139" s="360"/>
-      <c r="F139" s="360"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5790,13 +5790,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="359" t="s">
+      <c r="B179" s="365" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="360"/>
-      <c r="D179" s="360"/>
-      <c r="E179" s="360"/>
-      <c r="F179" s="360"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5833,13 +5833,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="361" t="s">
+      <c r="B188" s="359" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="361"/>
-      <c r="D188" s="361"/>
-      <c r="E188" s="361"/>
-      <c r="F188" s="361"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5847,22 +5847,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="358" t="s">
+      <c r="B191" s="364" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="358"/>
-      <c r="D191" s="358"/>
-      <c r="E191" s="358"/>
-      <c r="F191" s="358"/>
+      <c r="C191" s="364"/>
+      <c r="D191" s="364"/>
+      <c r="E191" s="364"/>
+      <c r="F191" s="364"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="358" t="s">
+      <c r="B192" s="364" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="358"/>
-      <c r="D192" s="358"/>
-      <c r="E192" s="358"/>
-      <c r="F192" s="358"/>
+      <c r="C192" s="364"/>
+      <c r="D192" s="364"/>
+      <c r="E192" s="364"/>
+      <c r="F192" s="364"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5886,6 +5886,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5902,17 +5913,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13456,20 +13456,20 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>9.4076655052264813E-2</v>
+        <v>9.3425605536332182E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>9.4076655052264813E-2</v>
+        <v>9.3425605536332182E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>8.780487804878051E-2</v>
+        <v>8.7197231833910052E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>0.13484320557491292</v>
+        <v>0.13391003460207615</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
@@ -14655,50 +14655,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>7.4724568062673372E-2</v>
+        <v>7.4207443024177352E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>8.719828254578274E-2</v>
+        <v>8.6594834223666595E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>0.11999026416421364</v>
+        <v>0.11915988171325023</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>0.19459984183296739</v>
+        <v>0.19325313012478076</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>0.15989429620388504</v>
+        <v>0.15878776128205885</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>5.7361811024735671E-2</v>
+        <v>5.6964843474391479E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>7.2819990083337185E-2</v>
+        <v>7.2316045515286406E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>6.4836475208585154E-2</v>
+        <v>6.4387779878421939E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>6.1579693906999647E-2</v>
+        <v>6.1153536855740133E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>1.0900834249387089E-2</v>
+        <v>1.0825395950083373E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>4.7222165394611264E-3</v>
+        <v>4.6895368402261016E-3</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14712,43 +14712,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12421671590058347</v>
+        <v>0.12335708464867631</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15747597727288626</v>
+        <v>0.15638617812220884</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.22640981269168708</v>
+        <v>0.22484296277686569</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.20948298171969246</v>
+        <v>0.2080332725036392</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.1257535285385443E-2</v>
+        <v>8.0695199401057516E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.0494977868030226E-2</v>
+        <v>7.9937919197663229E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.8837842457294083E-2</v>
+        <v>7.8292251852053282E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.093593617354268E-2</v>
+        <v>8.037582588860466E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.630370187451549E-3</v>
+        <v>4.5983261031093238E-3</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-4.8693281144570937E-2</v>
+        <v>-4.8356303420387048E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18698,7 +18698,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-2.87</v>
+        <v>-2.89</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18938,7 +18938,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>2.87</v>
+        <v>2.89</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19536,7 +19536,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>2.87</v>
+        <v>2.89</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19549,7 +19549,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.24274033838293119</v>
+        <v>0.23964880679790124</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/0639.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0639.HK_Valuation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BC43084-EF1D-4A40-BFB8-80B2220089EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B16E9AA-B118-4A84-86A5-98220B3DA2BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3893,29 +3893,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4333,7 +4333,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>2.89</v>
+        <v>2.57</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>14713.180075300001</v>
+        <v>13084.039028899999</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4391,13 +4391,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="360" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="360"/>
+      <c r="D18" s="360"/>
+      <c r="E18" s="360"/>
+      <c r="F18" s="360"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.23964880679790124</v>
+        <v>0.29306535315093174</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4597,22 +4597,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="360" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="360"/>
+      <c r="D36" s="360"/>
+      <c r="E36" s="360"/>
+      <c r="F36" s="360"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="360" t="s">
+      <c r="B37" s="363" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="360"/>
-      <c r="D37" s="360"/>
-      <c r="E37" s="360"/>
-      <c r="F37" s="360"/>
+      <c r="C37" s="363"/>
+      <c r="D37" s="363"/>
+      <c r="E37" s="363"/>
+      <c r="F37" s="363"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4624,13 +4624,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="361" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="361"/>
+      <c r="D40" s="361"/>
+      <c r="E40" s="361"/>
+      <c r="F40" s="361"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4650,13 +4650,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="361" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="361"/>
+      <c r="D43" s="361"/>
+      <c r="E43" s="361"/>
+      <c r="F43" s="361"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4685,13 +4685,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="361" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="361"/>
+      <c r="D47" s="361"/>
+      <c r="E47" s="361"/>
+      <c r="F47" s="361"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4707,13 +4707,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="361" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="361"/>
+      <c r="D50" s="361"/>
+      <c r="E50" s="361"/>
+      <c r="F50" s="361"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4777,13 +4777,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="361" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="361"/>
+      <c r="D58" s="361"/>
+      <c r="E58" s="361"/>
+      <c r="F58" s="361"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4799,7 +4799,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="361" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4821,22 +4821,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="360" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="360"/>
+      <c r="D64" s="360"/>
+      <c r="E64" s="360"/>
+      <c r="F64" s="360"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="360" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="360"/>
+      <c r="D65" s="360"/>
+      <c r="E65" s="360"/>
+      <c r="F65" s="360"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>7.4207443024177352E-2</v>
+        <v>8.3447280287888156E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>9.3425605536332182E-2</v>
+        <v>0.10505836575875488</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>444</v>
@@ -4971,22 +4971,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="360" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="360"/>
+      <c r="D80" s="360"/>
+      <c r="E80" s="360"/>
+      <c r="F80" s="360"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="360" t="s">
+      <c r="B81" s="363" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="360"/>
-      <c r="D81" s="360"/>
-      <c r="E81" s="360"/>
-      <c r="F81" s="360"/>
+      <c r="C81" s="363"/>
+      <c r="D81" s="363"/>
+      <c r="E81" s="363"/>
+      <c r="F81" s="363"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5030,22 +5030,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="360" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="360"/>
+      <c r="D89" s="360"/>
+      <c r="E89" s="360"/>
+      <c r="F89" s="360"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="360" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="360"/>
+      <c r="D90" s="360"/>
+      <c r="E90" s="360"/>
+      <c r="F90" s="360"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5082,13 +5082,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="360" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="360"/>
+      <c r="D97" s="360"/>
+      <c r="E97" s="360"/>
+      <c r="F97" s="360"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5101,13 +5101,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="360" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="360"/>
+      <c r="D101" s="360"/>
+      <c r="E101" s="360"/>
+      <c r="F101" s="360"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5229,13 +5229,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="360" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="360"/>
+      <c r="D116" s="360"/>
+      <c r="E116" s="360"/>
+      <c r="F116" s="360"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5274,13 +5274,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="361" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="361"/>
+      <c r="D123" s="361"/>
+      <c r="E123" s="361"/>
+      <c r="F123" s="361"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5423,13 +5423,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="363" t="s">
+      <c r="B134" s="364" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="363"/>
-      <c r="D134" s="363"/>
-      <c r="E134" s="363"/>
-      <c r="F134" s="363"/>
+      <c r="C134" s="364"/>
+      <c r="D134" s="364"/>
+      <c r="E134" s="364"/>
+      <c r="F134" s="364"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5442,22 +5442,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="361" t="s">
+      <c r="B138" s="365" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="361"/>
-      <c r="D138" s="361"/>
-      <c r="E138" s="361"/>
-      <c r="F138" s="361"/>
+      <c r="C138" s="365"/>
+      <c r="D138" s="365"/>
+      <c r="E138" s="365"/>
+      <c r="F138" s="365"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="360" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="360"/>
+      <c r="D139" s="360"/>
+      <c r="E139" s="360"/>
+      <c r="F139" s="360"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5790,13 +5790,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="365" t="s">
+      <c r="B179" s="359" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="360"/>
+      <c r="D179" s="360"/>
+      <c r="E179" s="360"/>
+      <c r="F179" s="360"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5833,13 +5833,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="361" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="361"/>
+      <c r="D188" s="361"/>
+      <c r="E188" s="361"/>
+      <c r="F188" s="361"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5847,22 +5847,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="364" t="s">
+      <c r="B191" s="358" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="364"/>
-      <c r="D191" s="364"/>
-      <c r="E191" s="364"/>
-      <c r="F191" s="364"/>
+      <c r="C191" s="358"/>
+      <c r="D191" s="358"/>
+      <c r="E191" s="358"/>
+      <c r="F191" s="358"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="364" t="s">
+      <c r="B192" s="358" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="364"/>
-      <c r="D192" s="364"/>
-      <c r="E192" s="364"/>
-      <c r="F192" s="364"/>
+      <c r="C192" s="358"/>
+      <c r="D192" s="358"/>
+      <c r="E192" s="358"/>
+      <c r="F192" s="358"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5886,17 +5886,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5913,6 +5902,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13456,20 +13456,20 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>9.3425605536332182E-2</v>
+        <v>0.10505836575875488</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>9.3425605536332182E-2</v>
+        <v>0.10505836575875488</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>8.7197231833910052E-2</v>
+        <v>9.8054474708171233E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>0.13391003460207615</v>
+        <v>0.15058365758754869</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
@@ -14655,50 +14655,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>7.4207443024177352E-2</v>
+        <v>8.3447280287888156E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>8.6594834223666595E-2</v>
+        <v>9.7377070391593976E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>0.11915988171325023</v>
+        <v>0.13399690978649542</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>0.19325313012478076</v>
+        <v>0.21731577667728266</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>0.15878776128205885</v>
+        <v>0.17855900004091443</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>5.6964843474391479E-2</v>
+        <v>6.4057742272759302E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>7.2316045515286406E-2</v>
+        <v>8.1320378030808466E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>6.4387779878421939E-2</v>
+        <v>7.2404935349665148E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>6.1153536855740133E-2</v>
+        <v>6.8767985024548256E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>1.0825395950083373E-2</v>
+        <v>1.2173305173440058E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>4.6895368402261016E-3</v>
+        <v>5.2734480421219596E-3</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14712,43 +14712,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12335708464867631</v>
+        <v>0.1387167216477333</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15638617812220884</v>
+        <v>0.17585838707127766</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.22484296277686569</v>
+        <v>0.25283897370628089</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.2080332725036392</v>
+        <v>0.23393624806829469</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.0695199401057516E-2</v>
+        <v>9.0742850688348725E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.9937919197663229E-2</v>
+        <v>8.9891278786477333E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.8292251852053282E-2</v>
+        <v>8.8040703444526858E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.037582588860466E-2</v>
+        <v>9.0383710824150768E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.5983261031093238E-3</v>
+        <v>5.1708803260645704E-3</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-4.8356303420387048E-2</v>
+        <v>-5.4377321745104505E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18698,7 +18698,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-2.89</v>
+        <v>-2.57</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18938,7 +18938,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>2.89</v>
+        <v>2.57</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19536,7 +19536,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>2.89</v>
+        <v>2.57</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19549,7 +19549,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.23964880679790124</v>
+        <v>0.29306535315093174</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/0639.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0639.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B16E9AA-B118-4A84-86A5-98220B3DA2BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25D8DF97-4079-423E-B6E5-72A284F8E2DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3893,29 +3893,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4333,7 +4333,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>2.57</v>
+        <v>2.89</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>13084.039028899999</v>
+        <v>14713.180075300001</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4391,13 +4391,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="360" t="s">
+      <c r="B18" s="358" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="360"/>
-      <c r="D18" s="360"/>
-      <c r="E18" s="360"/>
-      <c r="F18" s="360"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.29306535315093174</v>
+        <v>0.23964880679790124</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4512,7 +4512,7 @@
       </c>
       <c r="C29" s="310">
         <f>C149</f>
-        <v>2.2019752270440667</v>
+        <v>2.2811221378505544</v>
       </c>
       <c r="D29" s="310" t="str">
         <f>D149</f>
@@ -4522,7 +4522,7 @@
         <v>420</v>
       </c>
       <c r="F29" s="302">
-        <v>0.3674</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="30" spans="2:6">
@@ -4531,7 +4531,7 @@
       </c>
       <c r="C30" s="311">
         <f>C157</f>
-        <v>3.039853505232323</v>
+        <v>2.823790530515998</v>
       </c>
       <c r="D30" s="311" t="str">
         <f>D157</f>
@@ -4541,7 +4541,7 @@
         <v>433</v>
       </c>
       <c r="F30" s="312">
-        <v>0.21740000000000001</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="31" spans="2:6">
@@ -4597,22 +4597,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="360" t="s">
+      <c r="B36" s="358" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="360"/>
-      <c r="D36" s="360"/>
-      <c r="E36" s="360"/>
-      <c r="F36" s="360"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="363" t="s">
+      <c r="B37" s="360" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="363"/>
-      <c r="D37" s="363"/>
-      <c r="E37" s="363"/>
-      <c r="F37" s="363"/>
+      <c r="C37" s="360"/>
+      <c r="D37" s="360"/>
+      <c r="E37" s="360"/>
+      <c r="F37" s="360"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4624,13 +4624,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="361" t="s">
+      <c r="B40" s="359" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="361"/>
-      <c r="D40" s="361"/>
-      <c r="E40" s="361"/>
-      <c r="F40" s="361"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4650,13 +4650,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="361" t="s">
+      <c r="B43" s="359" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="361"/>
-      <c r="D43" s="361"/>
-      <c r="E43" s="361"/>
-      <c r="F43" s="361"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4685,13 +4685,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="361" t="s">
+      <c r="B47" s="359" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="361"/>
-      <c r="D47" s="361"/>
-      <c r="E47" s="361"/>
-      <c r="F47" s="361"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4707,13 +4707,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="361" t="s">
+      <c r="B50" s="359" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="361"/>
-      <c r="D50" s="361"/>
-      <c r="E50" s="361"/>
-      <c r="F50" s="361"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4777,13 +4777,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="361" t="s">
+      <c r="B58" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="361"/>
-      <c r="D58" s="361"/>
-      <c r="E58" s="361"/>
-      <c r="F58" s="361"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4799,7 +4799,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="361" t="s">
+      <c r="B61" s="359" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4821,22 +4821,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="360" t="s">
+      <c r="B64" s="358" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="360"/>
-      <c r="D64" s="360"/>
-      <c r="E64" s="360"/>
-      <c r="F64" s="360"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="360" t="s">
+      <c r="B65" s="358" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="360"/>
-      <c r="D65" s="360"/>
-      <c r="E65" s="360"/>
-      <c r="F65" s="360"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>8.3447280287888156E-2</v>
+        <v>7.4207443024177352E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>0.10505836575875488</v>
+        <v>9.3425605536332182E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>444</v>
@@ -4971,22 +4971,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="360" t="s">
+      <c r="B80" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="360"/>
-      <c r="D80" s="360"/>
-      <c r="E80" s="360"/>
-      <c r="F80" s="360"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="363" t="s">
+      <c r="B81" s="360" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="363"/>
-      <c r="D81" s="363"/>
-      <c r="E81" s="363"/>
-      <c r="F81" s="363"/>
+      <c r="C81" s="360"/>
+      <c r="D81" s="360"/>
+      <c r="E81" s="360"/>
+      <c r="F81" s="360"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5030,22 +5030,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="360" t="s">
+      <c r="B89" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="360"/>
-      <c r="D89" s="360"/>
-      <c r="E89" s="360"/>
-      <c r="F89" s="360"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="360" t="s">
+      <c r="B90" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="360"/>
-      <c r="D90" s="360"/>
-      <c r="E90" s="360"/>
-      <c r="F90" s="360"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5082,13 +5082,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="360" t="s">
+      <c r="B97" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="360"/>
-      <c r="D97" s="360"/>
-      <c r="E97" s="360"/>
-      <c r="F97" s="360"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5101,13 +5101,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="360" t="s">
+      <c r="B101" s="358" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="360"/>
-      <c r="D101" s="360"/>
-      <c r="E101" s="360"/>
-      <c r="F101" s="360"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5229,13 +5229,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="360" t="s">
+      <c r="B116" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="360"/>
-      <c r="D116" s="360"/>
-      <c r="E116" s="360"/>
-      <c r="F116" s="360"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5274,13 +5274,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="361" t="s">
+      <c r="B123" s="359" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="361"/>
-      <c r="D123" s="361"/>
-      <c r="E123" s="361"/>
-      <c r="F123" s="361"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5423,13 +5423,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="364" t="s">
+      <c r="B134" s="363" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="364"/>
-      <c r="D134" s="364"/>
-      <c r="E134" s="364"/>
-      <c r="F134" s="364"/>
+      <c r="C134" s="363"/>
+      <c r="D134" s="363"/>
+      <c r="E134" s="363"/>
+      <c r="F134" s="363"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5442,22 +5442,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="365" t="s">
+      <c r="B138" s="361" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="365"/>
-      <c r="D138" s="365"/>
-      <c r="E138" s="365"/>
-      <c r="F138" s="365"/>
+      <c r="C138" s="361"/>
+      <c r="D138" s="361"/>
+      <c r="E138" s="361"/>
+      <c r="F138" s="361"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="360" t="s">
+      <c r="B139" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="360"/>
-      <c r="D139" s="360"/>
-      <c r="E139" s="360"/>
-      <c r="F139" s="360"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5479,7 +5479,7 @@
       </c>
       <c r="C142" s="224">
         <f>F29</f>
-        <v>0.3674</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -5514,7 +5514,7 @@
       </c>
       <c r="C146" s="297">
         <f>F29</f>
-        <v>0.3674</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="147" spans="2:4">
@@ -5524,7 +5524,7 @@
       </c>
       <c r="C147" s="216">
         <f>Scenarios!C81</f>
-        <v>0.44746001622851189</v>
+        <v>0.45788751714677645</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -5534,7 +5534,7 @@
       </c>
       <c r="C148" s="216">
         <f>Scenarios!C82</f>
-        <v>1.7545152108155548</v>
+        <v>1.823234620703778</v>
       </c>
     </row>
     <row r="149" spans="2:4">
@@ -5543,7 +5543,7 @@
       </c>
       <c r="C149" s="215">
         <f>Scenarios!C83</f>
-        <v>2.2019752270440667</v>
+        <v>2.2811221378505544</v>
       </c>
       <c r="D149" s="300" t="str">
         <f>IF($D$11="","",C149*$E$25)</f>
@@ -5569,7 +5569,7 @@
       </c>
       <c r="C151" s="92">
         <f>Scenarios!F83</f>
-        <v>0.50912765610931499</v>
+        <v>0.49148393825902781</v>
       </c>
     </row>
     <row r="153" spans="2:4">
@@ -5583,7 +5583,7 @@
       </c>
       <c r="C154" s="297">
         <f>Scenarios!C90</f>
-        <v>0.21740000000000001</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="155" spans="2:4">
@@ -5593,7 +5593,7 @@
       </c>
       <c r="C155" s="216">
         <f>Scenarios!C91</f>
-        <v>0.55360822244353303</v>
+        <v>0.52704000000000006</v>
       </c>
     </row>
     <row r="156" spans="2:4">
@@ -5603,7 +5603,7 @@
       </c>
       <c r="C156" s="216">
         <f>Scenarios!C92</f>
-        <v>2.48624528278879</v>
+        <v>2.2967505305159981</v>
       </c>
     </row>
     <row r="157" spans="2:4">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C157" s="215">
         <f>Scenarios!C93</f>
-        <v>3.039853505232323</v>
+        <v>2.823790530515998</v>
       </c>
       <c r="D157" s="300" t="str">
         <f>IF($D$11="","",C157*$E$25)</f>
@@ -5638,7 +5638,7 @@
       </c>
       <c r="C159" s="92">
         <f>Scenarios!F93</f>
-        <v>0.32234477623946356</v>
+        <v>0.37051032212045443</v>
       </c>
     </row>
     <row r="161" spans="2:4">
@@ -5790,13 +5790,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="359" t="s">
+      <c r="B179" s="365" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="360"/>
-      <c r="D179" s="360"/>
-      <c r="E179" s="360"/>
-      <c r="F179" s="360"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5833,13 +5833,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="361" t="s">
+      <c r="B188" s="359" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="361"/>
-      <c r="D188" s="361"/>
-      <c r="E188" s="361"/>
-      <c r="F188" s="361"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5847,22 +5847,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="358" t="s">
+      <c r="B191" s="364" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="358"/>
-      <c r="D191" s="358"/>
-      <c r="E191" s="358"/>
-      <c r="F191" s="358"/>
+      <c r="C191" s="364"/>
+      <c r="D191" s="364"/>
+      <c r="E191" s="364"/>
+      <c r="F191" s="364"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="358" t="s">
+      <c r="B192" s="364" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="358"/>
-      <c r="D192" s="358"/>
-      <c r="E192" s="358"/>
-      <c r="F192" s="358"/>
+      <c r="C192" s="364"/>
+      <c r="D192" s="364"/>
+      <c r="E192" s="364"/>
+      <c r="F192" s="364"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5886,6 +5886,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5902,17 +5913,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13456,20 +13456,20 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>0.10505836575875488</v>
+        <v>9.3425605536332182E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>0.10505836575875488</v>
+        <v>9.3425605536332182E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>9.8054474708171233E-2</v>
+        <v>8.7197231833910052E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>0.15058365758754869</v>
+        <v>0.13391003460207615</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
@@ -14655,50 +14655,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>8.3447280287888156E-2</v>
+        <v>7.4207443024177352E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>9.7377070391593976E-2</v>
+        <v>8.6594834223666595E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>0.13399690978649542</v>
+        <v>0.11915988171325023</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>0.21731577667728266</v>
+        <v>0.19325313012478076</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>0.17855900004091443</v>
+        <v>0.15878776128205885</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>6.4057742272759302E-2</v>
+        <v>5.6964843474391479E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>8.1320378030808466E-2</v>
+        <v>7.2316045515286406E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>7.2404935349665148E-2</v>
+        <v>6.4387779878421939E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>6.8767985024548256E-2</v>
+        <v>6.1153536855740133E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>1.2173305173440058E-2</v>
+        <v>1.0825395950083373E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>5.2734480421219596E-3</v>
+        <v>4.6895368402261016E-3</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14712,43 +14712,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1387167216477333</v>
+        <v>0.12335708464867631</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.17585838707127766</v>
+        <v>0.15638617812220884</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.25283897370628089</v>
+        <v>0.22484296277686569</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.23393624806829469</v>
+        <v>0.2080332725036392</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.0742850688348725E-2</v>
+        <v>8.0695199401057516E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.9891278786477333E-2</v>
+        <v>7.9937919197663229E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.8040703444526858E-2</v>
+        <v>7.8292251852053282E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.0383710824150768E-2</v>
+        <v>8.037582588860466E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.1708803260645704E-3</v>
+        <v>4.5983261031093238E-3</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-5.4377321745104505E-2</v>
+        <v>-4.8356303420387048E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18698,7 +18698,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-2.57</v>
+        <v>-2.89</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18938,7 +18938,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>2.57</v>
+        <v>2.89</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19477,7 +19477,7 @@
       </c>
       <c r="C80" s="167">
         <f>Thesis!F29</f>
-        <v>0.3674</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="81" spans="2:8">
@@ -19486,7 +19486,7 @@
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>0.44746001622851189</v>
+        <v>0.45788751714677645</v>
       </c>
       <c r="D81" s="116"/>
       <c r="E81" s="100"/>
@@ -19498,7 +19498,7 @@
       </c>
       <c r="C82" s="116">
         <f>C60/(1+C80)^C76</f>
-        <v>1.7545152108155548</v>
+        <v>1.823234620703778</v>
       </c>
       <c r="D82" s="116"/>
     </row>
@@ -19508,7 +19508,7 @@
       </c>
       <c r="C83" s="111">
         <f>C81+C82</f>
-        <v>2.2019752270440667</v>
+        <v>2.2811221378505544</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -19519,7 +19519,7 @@
       </c>
       <c r="F83" s="291">
         <f>(1-C83/C60)</f>
-        <v>0.50912765610931499</v>
+        <v>0.49148393825902781</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -19536,7 +19536,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>2.57</v>
+        <v>2.89</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19549,7 +19549,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.29306535315093174</v>
+        <v>0.23964880679790124</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -19566,7 +19566,7 @@
       </c>
       <c r="C90" s="167">
         <f>Thesis!F30</f>
-        <v>0.21740000000000001</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="91" spans="2:8">
@@ -19575,7 +19575,7 @@
       </c>
       <c r="C91" s="116">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>0.55360822244353303</v>
+        <v>0.52704000000000006</v>
       </c>
       <c r="D91" s="116"/>
       <c r="E91" s="100"/>
@@ -19587,7 +19587,7 @@
       </c>
       <c r="C92" s="116">
         <f>C60/(1+C90)^C76</f>
-        <v>2.48624528278879</v>
+        <v>2.2967505305159981</v>
       </c>
       <c r="D92" s="116"/>
     </row>
@@ -19597,7 +19597,7 @@
       </c>
       <c r="C93" s="111">
         <f>C91+C92</f>
-        <v>3.039853505232323</v>
+        <v>2.823790530515998</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -19608,7 +19608,7 @@
       </c>
       <c r="F93" s="291">
         <f>(1-C93/C60)</f>
-        <v>0.32234477623946356</v>
+        <v>0.37051032212045443</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">

--- a/financial_models/opportunities/0639.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0639.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25D8DF97-4079-423E-B6E5-72A284F8E2DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5D4DF18-C5DD-4924-A504-A1722F975ADA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3893,29 +3893,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4391,13 +4391,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="360" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="360"/>
+      <c r="D18" s="360"/>
+      <c r="E18" s="360"/>
+      <c r="F18" s="360"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4597,22 +4597,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="360" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="360"/>
+      <c r="D36" s="360"/>
+      <c r="E36" s="360"/>
+      <c r="F36" s="360"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="360" t="s">
+      <c r="B37" s="363" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="360"/>
-      <c r="D37" s="360"/>
-      <c r="E37" s="360"/>
-      <c r="F37" s="360"/>
+      <c r="C37" s="363"/>
+      <c r="D37" s="363"/>
+      <c r="E37" s="363"/>
+      <c r="F37" s="363"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4624,13 +4624,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="361" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="361"/>
+      <c r="D40" s="361"/>
+      <c r="E40" s="361"/>
+      <c r="F40" s="361"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4650,13 +4650,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="361" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="361"/>
+      <c r="D43" s="361"/>
+      <c r="E43" s="361"/>
+      <c r="F43" s="361"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4685,13 +4685,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="361" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="361"/>
+      <c r="D47" s="361"/>
+      <c r="E47" s="361"/>
+      <c r="F47" s="361"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4707,13 +4707,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="361" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="361"/>
+      <c r="D50" s="361"/>
+      <c r="E50" s="361"/>
+      <c r="F50" s="361"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4777,13 +4777,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="361" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="361"/>
+      <c r="D58" s="361"/>
+      <c r="E58" s="361"/>
+      <c r="F58" s="361"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4799,7 +4799,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="361" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4821,22 +4821,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="360" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="360"/>
+      <c r="D64" s="360"/>
+      <c r="E64" s="360"/>
+      <c r="F64" s="360"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="360" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="360"/>
+      <c r="D65" s="360"/>
+      <c r="E65" s="360"/>
+      <c r="F65" s="360"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4971,22 +4971,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="360" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="360"/>
+      <c r="D80" s="360"/>
+      <c r="E80" s="360"/>
+      <c r="F80" s="360"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="360" t="s">
+      <c r="B81" s="363" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="360"/>
-      <c r="D81" s="360"/>
-      <c r="E81" s="360"/>
-      <c r="F81" s="360"/>
+      <c r="C81" s="363"/>
+      <c r="D81" s="363"/>
+      <c r="E81" s="363"/>
+      <c r="F81" s="363"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5030,22 +5030,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="360" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="360"/>
+      <c r="D89" s="360"/>
+      <c r="E89" s="360"/>
+      <c r="F89" s="360"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="360" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="360"/>
+      <c r="D90" s="360"/>
+      <c r="E90" s="360"/>
+      <c r="F90" s="360"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5082,13 +5082,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="360" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="360"/>
+      <c r="D97" s="360"/>
+      <c r="E97" s="360"/>
+      <c r="F97" s="360"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5101,13 +5101,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="360" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="360"/>
+      <c r="D101" s="360"/>
+      <c r="E101" s="360"/>
+      <c r="F101" s="360"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5229,13 +5229,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="360" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="360"/>
+      <c r="D116" s="360"/>
+      <c r="E116" s="360"/>
+      <c r="F116" s="360"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5274,13 +5274,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="361" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="361"/>
+      <c r="D123" s="361"/>
+      <c r="E123" s="361"/>
+      <c r="F123" s="361"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5423,13 +5423,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="363" t="s">
+      <c r="B134" s="364" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="363"/>
-      <c r="D134" s="363"/>
-      <c r="E134" s="363"/>
-      <c r="F134" s="363"/>
+      <c r="C134" s="364"/>
+      <c r="D134" s="364"/>
+      <c r="E134" s="364"/>
+      <c r="F134" s="364"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5442,22 +5442,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="361" t="s">
+      <c r="B138" s="365" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="361"/>
-      <c r="D138" s="361"/>
-      <c r="E138" s="361"/>
-      <c r="F138" s="361"/>
+      <c r="C138" s="365"/>
+      <c r="D138" s="365"/>
+      <c r="E138" s="365"/>
+      <c r="F138" s="365"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="360" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="360"/>
+      <c r="D139" s="360"/>
+      <c r="E139" s="360"/>
+      <c r="F139" s="360"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5790,13 +5790,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="365" t="s">
+      <c r="B179" s="359" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="360"/>
+      <c r="D179" s="360"/>
+      <c r="E179" s="360"/>
+      <c r="F179" s="360"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5833,13 +5833,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="361" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="361"/>
+      <c r="D188" s="361"/>
+      <c r="E188" s="361"/>
+      <c r="F188" s="361"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5847,22 +5847,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="364" t="s">
+      <c r="B191" s="358" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="364"/>
-      <c r="D191" s="364"/>
-      <c r="E191" s="364"/>
-      <c r="F191" s="364"/>
+      <c r="C191" s="358"/>
+      <c r="D191" s="358"/>
+      <c r="E191" s="358"/>
+      <c r="F191" s="358"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="364" t="s">
+      <c r="B192" s="358" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="364"/>
-      <c r="D192" s="364"/>
-      <c r="E192" s="364"/>
-      <c r="F192" s="364"/>
+      <c r="C192" s="358"/>
+      <c r="D192" s="358"/>
+      <c r="E192" s="358"/>
+      <c r="F192" s="358"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5886,17 +5886,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5913,6 +5902,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">

--- a/financial_models/opportunities/0639.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0639.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5D4DF18-C5DD-4924-A504-A1722F975ADA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AA73D3E-EC39-4F0E-A55B-FEFE2DF18CD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3893,29 +3893,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4391,13 +4391,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="360" t="s">
+      <c r="B18" s="358" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="360"/>
-      <c r="D18" s="360"/>
-      <c r="E18" s="360"/>
-      <c r="F18" s="360"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4597,22 +4597,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="360" t="s">
+      <c r="B36" s="358" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="360"/>
-      <c r="D36" s="360"/>
-      <c r="E36" s="360"/>
-      <c r="F36" s="360"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="363" t="s">
+      <c r="B37" s="360" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="363"/>
-      <c r="D37" s="363"/>
-      <c r="E37" s="363"/>
-      <c r="F37" s="363"/>
+      <c r="C37" s="360"/>
+      <c r="D37" s="360"/>
+      <c r="E37" s="360"/>
+      <c r="F37" s="360"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4624,13 +4624,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="361" t="s">
+      <c r="B40" s="359" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="361"/>
-      <c r="D40" s="361"/>
-      <c r="E40" s="361"/>
-      <c r="F40" s="361"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4650,13 +4650,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="361" t="s">
+      <c r="B43" s="359" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="361"/>
-      <c r="D43" s="361"/>
-      <c r="E43" s="361"/>
-      <c r="F43" s="361"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4685,13 +4685,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="361" t="s">
+      <c r="B47" s="359" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="361"/>
-      <c r="D47" s="361"/>
-      <c r="E47" s="361"/>
-      <c r="F47" s="361"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4707,13 +4707,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="361" t="s">
+      <c r="B50" s="359" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="361"/>
-      <c r="D50" s="361"/>
-      <c r="E50" s="361"/>
-      <c r="F50" s="361"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4777,13 +4777,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="361" t="s">
+      <c r="B58" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="361"/>
-      <c r="D58" s="361"/>
-      <c r="E58" s="361"/>
-      <c r="F58" s="361"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4799,7 +4799,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="361" t="s">
+      <c r="B61" s="359" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4821,22 +4821,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="360" t="s">
+      <c r="B64" s="358" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="360"/>
-      <c r="D64" s="360"/>
-      <c r="E64" s="360"/>
-      <c r="F64" s="360"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="360" t="s">
+      <c r="B65" s="358" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="360"/>
-      <c r="D65" s="360"/>
-      <c r="E65" s="360"/>
-      <c r="F65" s="360"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4971,22 +4971,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="360" t="s">
+      <c r="B80" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="360"/>
-      <c r="D80" s="360"/>
-      <c r="E80" s="360"/>
-      <c r="F80" s="360"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="363" t="s">
+      <c r="B81" s="360" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="363"/>
-      <c r="D81" s="363"/>
-      <c r="E81" s="363"/>
-      <c r="F81" s="363"/>
+      <c r="C81" s="360"/>
+      <c r="D81" s="360"/>
+      <c r="E81" s="360"/>
+      <c r="F81" s="360"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5030,22 +5030,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="360" t="s">
+      <c r="B89" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="360"/>
-      <c r="D89" s="360"/>
-      <c r="E89" s="360"/>
-      <c r="F89" s="360"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="360" t="s">
+      <c r="B90" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="360"/>
-      <c r="D90" s="360"/>
-      <c r="E90" s="360"/>
-      <c r="F90" s="360"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5082,13 +5082,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="360" t="s">
+      <c r="B97" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="360"/>
-      <c r="D97" s="360"/>
-      <c r="E97" s="360"/>
-      <c r="F97" s="360"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5101,13 +5101,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="360" t="s">
+      <c r="B101" s="358" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="360"/>
-      <c r="D101" s="360"/>
-      <c r="E101" s="360"/>
-      <c r="F101" s="360"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5229,13 +5229,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="360" t="s">
+      <c r="B116" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="360"/>
-      <c r="D116" s="360"/>
-      <c r="E116" s="360"/>
-      <c r="F116" s="360"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5274,13 +5274,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="361" t="s">
+      <c r="B123" s="359" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="361"/>
-      <c r="D123" s="361"/>
-      <c r="E123" s="361"/>
-      <c r="F123" s="361"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5423,13 +5423,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="364" t="s">
+      <c r="B134" s="363" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="364"/>
-      <c r="D134" s="364"/>
-      <c r="E134" s="364"/>
-      <c r="F134" s="364"/>
+      <c r="C134" s="363"/>
+      <c r="D134" s="363"/>
+      <c r="E134" s="363"/>
+      <c r="F134" s="363"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5442,22 +5442,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="365" t="s">
+      <c r="B138" s="361" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="365"/>
-      <c r="D138" s="365"/>
-      <c r="E138" s="365"/>
-      <c r="F138" s="365"/>
+      <c r="C138" s="361"/>
+      <c r="D138" s="361"/>
+      <c r="E138" s="361"/>
+      <c r="F138" s="361"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="360" t="s">
+      <c r="B139" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="360"/>
-      <c r="D139" s="360"/>
-      <c r="E139" s="360"/>
-      <c r="F139" s="360"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5790,13 +5790,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="359" t="s">
+      <c r="B179" s="365" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="360"/>
-      <c r="D179" s="360"/>
-      <c r="E179" s="360"/>
-      <c r="F179" s="360"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5833,13 +5833,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="361" t="s">
+      <c r="B188" s="359" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="361"/>
-      <c r="D188" s="361"/>
-      <c r="E188" s="361"/>
-      <c r="F188" s="361"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5847,22 +5847,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="358" t="s">
+      <c r="B191" s="364" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="358"/>
-      <c r="D191" s="358"/>
-      <c r="E191" s="358"/>
-      <c r="F191" s="358"/>
+      <c r="C191" s="364"/>
+      <c r="D191" s="364"/>
+      <c r="E191" s="364"/>
+      <c r="F191" s="364"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="358" t="s">
+      <c r="B192" s="364" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="358"/>
-      <c r="D192" s="358"/>
-      <c r="E192" s="358"/>
-      <c r="F192" s="358"/>
+      <c r="C192" s="364"/>
+      <c r="D192" s="364"/>
+      <c r="E192" s="364"/>
+      <c r="F192" s="364"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5886,6 +5886,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5902,17 +5913,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">

--- a/financial_models/opportunities/0639.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0639.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AA73D3E-EC39-4F0E-A55B-FEFE2DF18CD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AFA3BC1-B97E-4F78-9DA7-261315A2F910}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -20,6 +20,7 @@
     <sheet name="DCF" sheetId="8" r:id="rId5"/>
     <sheet name="DDM" sheetId="10" r:id="rId6"/>
     <sheet name="Scenarios" sheetId="9" r:id="rId7"/>
+    <sheet name="Breakdown" sheetId="11" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">DCF!$B$73:$H$73</definedName>
@@ -48,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="686" uniqueCount="465">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="687" uniqueCount="466">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -2444,6 +2445,9 @@
   </si>
   <si>
     <t>After-tax Dividend per share</t>
+  </si>
+  <si>
+    <t>Divisional Analysis (Optional)</t>
   </si>
   <si>
     <t>Y</t>
@@ -3893,29 +3897,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4243,7 +4247,7 @@
         <v>350</v>
       </c>
       <c r="F1" s="254" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
@@ -4274,7 +4278,7 @@
         <v>312</v>
       </c>
       <c r="C5" s="294" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4321,10 +4325,10 @@
         <v>413</v>
       </c>
       <c r="C11" s="49" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D11" s="49" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="E11" s="34"/>
     </row>
@@ -4391,13 +4395,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="360" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="360"/>
+      <c r="D18" s="360"/>
+      <c r="E18" s="360"/>
+      <c r="F18" s="360"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4418,7 +4422,7 @@
         <v>435</v>
       </c>
       <c r="E21" s="308" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="22" spans="2:6">
@@ -4426,7 +4430,7 @@
         <v>56</v>
       </c>
       <c r="C22" s="48" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D22" s="1" t="str">
         <f>IF(valuation_method="DDM","DDM Terminal Value","")</f>
@@ -4439,7 +4443,7 @@
         <v>430</v>
       </c>
       <c r="C23" s="262" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="24" spans="2:6">
@@ -4447,7 +4451,7 @@
         <v>431</v>
       </c>
       <c r="C24" s="262" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="25" spans="2:6">
@@ -4597,22 +4601,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="360" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="360"/>
+      <c r="D36" s="360"/>
+      <c r="E36" s="360"/>
+      <c r="F36" s="360"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="360" t="s">
+      <c r="B37" s="363" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="360"/>
-      <c r="D37" s="360"/>
-      <c r="E37" s="360"/>
-      <c r="F37" s="360"/>
+      <c r="C37" s="363"/>
+      <c r="D37" s="363"/>
+      <c r="E37" s="363"/>
+      <c r="F37" s="363"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4624,13 +4628,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="361" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="361"/>
+      <c r="D40" s="361"/>
+      <c r="E40" s="361"/>
+      <c r="F40" s="361"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4650,13 +4654,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="361" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="361"/>
+      <c r="D43" s="361"/>
+      <c r="E43" s="361"/>
+      <c r="F43" s="361"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4685,13 +4689,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="361" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="361"/>
+      <c r="D47" s="361"/>
+      <c r="E47" s="361"/>
+      <c r="F47" s="361"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4707,13 +4711,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="361" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="361"/>
+      <c r="D50" s="361"/>
+      <c r="E50" s="361"/>
+      <c r="F50" s="361"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4777,13 +4781,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="361" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="361"/>
+      <c r="D58" s="361"/>
+      <c r="E58" s="361"/>
+      <c r="F58" s="361"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4799,7 +4803,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="361" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4821,22 +4825,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="360" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="360"/>
+      <c r="D64" s="360"/>
+      <c r="E64" s="360"/>
+      <c r="F64" s="360"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="360" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="360"/>
+      <c r="D65" s="360"/>
+      <c r="E65" s="360"/>
+      <c r="F65" s="360"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4971,22 +4975,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="360" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="360"/>
+      <c r="D80" s="360"/>
+      <c r="E80" s="360"/>
+      <c r="F80" s="360"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="360" t="s">
+      <c r="B81" s="363" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="360"/>
-      <c r="D81" s="360"/>
-      <c r="E81" s="360"/>
-      <c r="F81" s="360"/>
+      <c r="C81" s="363"/>
+      <c r="D81" s="363"/>
+      <c r="E81" s="363"/>
+      <c r="F81" s="363"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5030,22 +5034,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="360" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="360"/>
+      <c r="D89" s="360"/>
+      <c r="E89" s="360"/>
+      <c r="F89" s="360"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="360" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="360"/>
+      <c r="D90" s="360"/>
+      <c r="E90" s="360"/>
+      <c r="F90" s="360"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5082,13 +5086,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="360" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="360"/>
+      <c r="D97" s="360"/>
+      <c r="E97" s="360"/>
+      <c r="F97" s="360"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5101,13 +5105,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="360" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="360"/>
+      <c r="D101" s="360"/>
+      <c r="E101" s="360"/>
+      <c r="F101" s="360"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5229,13 +5233,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="360" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="360"/>
+      <c r="D116" s="360"/>
+      <c r="E116" s="360"/>
+      <c r="F116" s="360"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5274,13 +5278,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="361" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="361"/>
+      <c r="D123" s="361"/>
+      <c r="E123" s="361"/>
+      <c r="F123" s="361"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5423,13 +5427,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="363" t="s">
+      <c r="B134" s="364" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="363"/>
-      <c r="D134" s="363"/>
-      <c r="E134" s="363"/>
-      <c r="F134" s="363"/>
+      <c r="C134" s="364"/>
+      <c r="D134" s="364"/>
+      <c r="E134" s="364"/>
+      <c r="F134" s="364"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5442,22 +5446,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="361" t="s">
+      <c r="B138" s="365" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="361"/>
-      <c r="D138" s="361"/>
-      <c r="E138" s="361"/>
-      <c r="F138" s="361"/>
+      <c r="C138" s="365"/>
+      <c r="D138" s="365"/>
+      <c r="E138" s="365"/>
+      <c r="F138" s="365"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="360" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="360"/>
+      <c r="D139" s="360"/>
+      <c r="E139" s="360"/>
+      <c r="F139" s="360"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5790,13 +5794,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="365" t="s">
+      <c r="B179" s="359" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="360"/>
+      <c r="D179" s="360"/>
+      <c r="E179" s="360"/>
+      <c r="F179" s="360"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5833,13 +5837,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="361" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="361"/>
+      <c r="D188" s="361"/>
+      <c r="E188" s="361"/>
+      <c r="F188" s="361"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5847,22 +5851,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="364" t="s">
+      <c r="B191" s="358" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="364"/>
-      <c r="D191" s="364"/>
-      <c r="E191" s="364"/>
-      <c r="F191" s="364"/>
+      <c r="C191" s="358"/>
+      <c r="D191" s="358"/>
+      <c r="E191" s="358"/>
+      <c r="F191" s="358"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="364" t="s">
+      <c r="B192" s="358" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="364"/>
-      <c r="D192" s="364"/>
-      <c r="E192" s="364"/>
-      <c r="F192" s="364"/>
+      <c r="C192" s="358"/>
+      <c r="D192" s="358"/>
+      <c r="E192" s="358"/>
+      <c r="F192" s="358"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5886,17 +5890,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5913,6 +5906,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -6581,7 +6585,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -12752,7 +12756,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="266" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -19775,4 +19779,27 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F820689B-F36D-4933-9EEF-92EBF45B6A8E}">
+  <dimension ref="B2:E2"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
+  <cols>
+    <col min="1" max="1" width="2.59765625" customWidth="1"/>
+    <col min="2" max="2" width="22.73046875" customWidth="1"/>
+    <col min="3" max="5" width="20.73046875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:5" ht="13.9">
+      <c r="B2" s="36" t="s">
+        <v>456</v>
+      </c>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/financial_models/opportunities/0639.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0639.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AFA3BC1-B97E-4F78-9DA7-261315A2F910}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78D84B3F-3482-4936-A2C2-46698FCDF187}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,20 +20,33 @@
     <sheet name="DCF" sheetId="8" r:id="rId5"/>
     <sheet name="DDM" sheetId="10" r:id="rId6"/>
     <sheet name="Scenarios" sheetId="9" r:id="rId7"/>
-    <sheet name="Breakdown" sheetId="11" r:id="rId8"/>
+    <sheet name="Breakdown" sheetId="12" r:id="rId8"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId9"/>
+  </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">DCF!$B$73:$H$73</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">DDM!$B$68:$H$68</definedName>
+    <definedName name="Common_Shares" localSheetId="7">[1]Thesis!$C$6</definedName>
     <definedName name="Common_Shares">Thesis!$C$6</definedName>
+    <definedName name="dividend_tax_rate" localSheetId="7">[1]Normalized_FCF!$C$93</definedName>
     <definedName name="dividend_tax_rate">Normalized_FCF!$C$93</definedName>
+    <definedName name="Equity_Cost" localSheetId="7">[1]Thesis!$C$86</definedName>
     <definedName name="Equity_Cost">Thesis!$C$86</definedName>
+    <definedName name="Exchange_Rate" localSheetId="7">[1]Thesis!$C$16</definedName>
     <definedName name="Exchange_Rate">Thesis!$C$16</definedName>
+    <definedName name="Market_currency" localSheetId="7">[1]Thesis!$C$13</definedName>
     <definedName name="Market_currency">Thesis!$C$13</definedName>
+    <definedName name="Market_Price" localSheetId="7">[1]Thesis!$C$12</definedName>
     <definedName name="Market_Price">Thesis!$C$12</definedName>
+    <definedName name="Reporting_currency" localSheetId="7">[1]Thesis!$C$25</definedName>
     <definedName name="Reporting_currency">Thesis!$C$25</definedName>
+    <definedName name="scaling_factor" localSheetId="7">[1]Data!$C$3</definedName>
     <definedName name="scaling_factor">Data!$C$3</definedName>
+    <definedName name="Terminal_Growth" localSheetId="7">[1]Thesis!$C$92</definedName>
     <definedName name="Terminal_Growth">Thesis!$C$92</definedName>
+    <definedName name="valuation_method" localSheetId="7">[1]Thesis!$E$21</definedName>
     <definedName name="valuation_method">Thesis!$E$21</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -42,7 +55,7 @@
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion1">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId9" roundtripDataSignature="AMtx7mi73Cg0ax9bLfpeUuF69nNRn7idDQ=="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId10" roundtripDataSignature="AMtx7mi73Cg0ax9bLfpeUuF69nNRn7idDQ=="/>
     </ext>
   </extLst>
 </workbook>
@@ -2501,7 +2514,7 @@
     <numFmt numFmtId="180" formatCode="0.000000000000000%"/>
     <numFmt numFmtId="181" formatCode="#,##0_);\(#,##0\);0;@"/>
   </numFmts>
-  <fonts count="59">
+  <fonts count="60">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -2941,6 +2954,12 @@
       <family val="2"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -3144,11 +3163,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="370">
+  <cellXfs count="373">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3933,9 +3953,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="1" xfId="2"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="常规 2" xfId="2" xr:uid="{01EDE6FD-0E0D-47F4-8B6F-FD2292C76C8D}"/>
     <cellStyle name="常规 2 2" xfId="1" xr:uid="{A35F4541-DCCE-4554-A311-39480A36979A}"/>
   </cellStyles>
   <dxfs count="8">
@@ -4020,6 +4046,89 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Thesis"/>
+      <sheetName val="Data"/>
+      <sheetName val="BS"/>
+      <sheetName val="Normalized_FCF"/>
+      <sheetName val="DCF"/>
+      <sheetName val="DDM"/>
+      <sheetName val="Scenarios"/>
+      <sheetName val="Breakdown"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="6">
+          <cell r="C6">
+            <v>5091065770</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="C12">
+            <v>2.89</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="C13" t="str">
+            <v>HKD</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="C16">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="E21" t="str">
+            <v>DCF</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="C25" t="str">
+            <v>HKD</v>
+          </cell>
+        </row>
+        <row r="86">
+          <cell r="C86">
+            <v>7.4999999999999997E-2</v>
+          </cell>
+        </row>
+        <row r="92">
+          <cell r="C92">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1">
+        <row r="3">
+          <cell r="C3">
+            <v>1000</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3">
+        <row r="93">
+          <cell r="C93">
+            <v>0.1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -19782,22 +19891,23 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F820689B-F36D-4933-9EEF-92EBF45B6A8E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0F5CFC9-8CA7-4AC0-A4D1-2C83D9428848}">
   <dimension ref="B2:E2"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="2.59765625" customWidth="1"/>
-    <col min="2" max="2" width="22.73046875" customWidth="1"/>
-    <col min="3" max="5" width="20.73046875" customWidth="1"/>
+    <col min="1" max="1" width="2.59765625" style="372" customWidth="1"/>
+    <col min="2" max="2" width="22.73046875" style="372" customWidth="1"/>
+    <col min="3" max="5" width="20.73046875" style="372" customWidth="1"/>
+    <col min="6" max="16384" width="9.06640625" style="372"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:5" ht="13.9">
-      <c r="B2" s="36" t="s">
+      <c r="B2" s="370" t="s">
         <v>456</v>
       </c>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
+      <c r="C2" s="371"/>
+      <c r="D2" s="371"/>
+      <c r="E2" s="371"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/financial_models/opportunities/0639.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0639.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78D84B3F-3482-4936-A2C2-46698FCDF187}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{883F8DA9-0C13-453C-8E9D-CCC63CD45326}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3917,47 +3917,47 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1"/>
     <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="59" fillId="0" borderId="1" xfId="2"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -4446,7 +4446,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>2.89</v>
+        <v>2.62</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4467,7 +4467,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>14713.180075300001</v>
+        <v>13338.5923174</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4504,13 +4504,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="360" t="s">
+      <c r="B18" s="361" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="360"/>
-      <c r="D18" s="360"/>
-      <c r="E18" s="360"/>
-      <c r="F18" s="360"/>
+      <c r="C18" s="361"/>
+      <c r="D18" s="361"/>
+      <c r="E18" s="361"/>
+      <c r="F18" s="361"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4593,7 +4593,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.23964880679790124</v>
+        <v>0.28412064787572122</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4710,13 +4710,13 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="360" t="s">
+      <c r="B36" s="361" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="360"/>
-      <c r="D36" s="360"/>
-      <c r="E36" s="360"/>
-      <c r="F36" s="360"/>
+      <c r="C36" s="361"/>
+      <c r="D36" s="361"/>
+      <c r="E36" s="361"/>
+      <c r="F36" s="361"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
       <c r="B37" s="363" t="s">
@@ -4737,13 +4737,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="361" t="s">
+      <c r="B40" s="362" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="361"/>
-      <c r="D40" s="361"/>
-      <c r="E40" s="361"/>
-      <c r="F40" s="361"/>
+      <c r="C40" s="362"/>
+      <c r="D40" s="362"/>
+      <c r="E40" s="362"/>
+      <c r="F40" s="362"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4763,13 +4763,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="361" t="s">
+      <c r="B43" s="362" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="361"/>
-      <c r="D43" s="361"/>
-      <c r="E43" s="361"/>
-      <c r="F43" s="361"/>
+      <c r="C43" s="362"/>
+      <c r="D43" s="362"/>
+      <c r="E43" s="362"/>
+      <c r="F43" s="362"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4798,13 +4798,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="361" t="s">
+      <c r="B47" s="362" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="361"/>
-      <c r="D47" s="361"/>
-      <c r="E47" s="361"/>
-      <c r="F47" s="361"/>
+      <c r="C47" s="362"/>
+      <c r="D47" s="362"/>
+      <c r="E47" s="362"/>
+      <c r="F47" s="362"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4820,13 +4820,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="361" t="s">
+      <c r="B50" s="362" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="361"/>
-      <c r="D50" s="361"/>
-      <c r="E50" s="361"/>
-      <c r="F50" s="361"/>
+      <c r="C50" s="362"/>
+      <c r="D50" s="362"/>
+      <c r="E50" s="362"/>
+      <c r="F50" s="362"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4890,13 +4890,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="361" t="s">
+      <c r="B58" s="362" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="361"/>
-      <c r="D58" s="361"/>
-      <c r="E58" s="361"/>
-      <c r="F58" s="361"/>
+      <c r="C58" s="362"/>
+      <c r="D58" s="362"/>
+      <c r="E58" s="362"/>
+      <c r="F58" s="362"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4912,13 +4912,13 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="361" t="s">
+      <c r="B61" s="362" t="s">
         <v>335</v>
       </c>
-      <c r="C61" s="362"/>
-      <c r="D61" s="362"/>
-      <c r="E61" s="362"/>
-      <c r="F61" s="362"/>
+      <c r="C61" s="365"/>
+      <c r="D61" s="365"/>
+      <c r="E61" s="365"/>
+      <c r="F61" s="365"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -4934,22 +4934,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="360" t="s">
+      <c r="B64" s="361" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="360"/>
-      <c r="D64" s="360"/>
-      <c r="E64" s="360"/>
-      <c r="F64" s="360"/>
+      <c r="C64" s="361"/>
+      <c r="D64" s="361"/>
+      <c r="E64" s="361"/>
+      <c r="F64" s="361"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="360" t="s">
+      <c r="B65" s="361" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="360"/>
-      <c r="D65" s="360"/>
-      <c r="E65" s="360"/>
-      <c r="F65" s="360"/>
+      <c r="C65" s="361"/>
+      <c r="D65" s="361"/>
+      <c r="E65" s="361"/>
+      <c r="F65" s="361"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4983,7 +4983,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>7.4207443024177352E-2</v>
+        <v>8.1854774938882657E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>9.3425605536332182E-2</v>
+        <v>0.10305343511450382</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>444</v>
@@ -5084,13 +5084,13 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="360" t="s">
+      <c r="B80" s="361" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="360"/>
-      <c r="D80" s="360"/>
-      <c r="E80" s="360"/>
-      <c r="F80" s="360"/>
+      <c r="C80" s="361"/>
+      <c r="D80" s="361"/>
+      <c r="E80" s="361"/>
+      <c r="F80" s="361"/>
     </row>
     <row r="81" spans="1:6">
       <c r="B81" s="363" t="s">
@@ -5143,22 +5143,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="360" t="s">
+      <c r="B89" s="361" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="360"/>
-      <c r="D89" s="360"/>
-      <c r="E89" s="360"/>
-      <c r="F89" s="360"/>
+      <c r="C89" s="361"/>
+      <c r="D89" s="361"/>
+      <c r="E89" s="361"/>
+      <c r="F89" s="361"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="360" t="s">
+      <c r="B90" s="361" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="360"/>
-      <c r="D90" s="360"/>
-      <c r="E90" s="360"/>
-      <c r="F90" s="360"/>
+      <c r="C90" s="361"/>
+      <c r="D90" s="361"/>
+      <c r="E90" s="361"/>
+      <c r="F90" s="361"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5195,13 +5195,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="360" t="s">
+      <c r="B97" s="361" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="360"/>
-      <c r="D97" s="360"/>
-      <c r="E97" s="360"/>
-      <c r="F97" s="360"/>
+      <c r="C97" s="361"/>
+      <c r="D97" s="361"/>
+      <c r="E97" s="361"/>
+      <c r="F97" s="361"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5214,13 +5214,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="360" t="s">
+      <c r="B101" s="361" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="360"/>
-      <c r="D101" s="360"/>
-      <c r="E101" s="360"/>
-      <c r="F101" s="360"/>
+      <c r="C101" s="361"/>
+      <c r="D101" s="361"/>
+      <c r="E101" s="361"/>
+      <c r="F101" s="361"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5342,13 +5342,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="360" t="s">
+      <c r="B116" s="361" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="360"/>
-      <c r="D116" s="360"/>
-      <c r="E116" s="360"/>
-      <c r="F116" s="360"/>
+      <c r="C116" s="361"/>
+      <c r="D116" s="361"/>
+      <c r="E116" s="361"/>
+      <c r="F116" s="361"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5387,13 +5387,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="361" t="s">
+      <c r="B123" s="362" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="361"/>
-      <c r="D123" s="361"/>
-      <c r="E123" s="361"/>
-      <c r="F123" s="361"/>
+      <c r="C123" s="362"/>
+      <c r="D123" s="362"/>
+      <c r="E123" s="362"/>
+      <c r="F123" s="362"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5536,13 +5536,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="364" t="s">
+      <c r="B134" s="366" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="364"/>
-      <c r="D134" s="364"/>
-      <c r="E134" s="364"/>
-      <c r="F134" s="364"/>
+      <c r="C134" s="366"/>
+      <c r="D134" s="366"/>
+      <c r="E134" s="366"/>
+      <c r="F134" s="366"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5555,22 +5555,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="365" t="s">
+      <c r="B138" s="364" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="365"/>
-      <c r="D138" s="365"/>
-      <c r="E138" s="365"/>
-      <c r="F138" s="365"/>
+      <c r="C138" s="364"/>
+      <c r="D138" s="364"/>
+      <c r="E138" s="364"/>
+      <c r="F138" s="364"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="360" t="s">
+      <c r="B139" s="361" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="360"/>
-      <c r="D139" s="360"/>
-      <c r="E139" s="360"/>
-      <c r="F139" s="360"/>
+      <c r="C139" s="361"/>
+      <c r="D139" s="361"/>
+      <c r="E139" s="361"/>
+      <c r="F139" s="361"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5903,13 +5903,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="359" t="s">
+      <c r="B179" s="368" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="360"/>
-      <c r="D179" s="360"/>
-      <c r="E179" s="360"/>
-      <c r="F179" s="360"/>
+      <c r="C179" s="361"/>
+      <c r="D179" s="361"/>
+      <c r="E179" s="361"/>
+      <c r="F179" s="361"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5917,13 +5917,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="362" t="s">
+      <c r="B182" s="365" t="s">
         <v>377</v>
       </c>
-      <c r="C182" s="362"/>
-      <c r="D182" s="362"/>
-      <c r="E182" s="362"/>
-      <c r="F182" s="362"/>
+      <c r="C182" s="365"/>
+      <c r="D182" s="365"/>
+      <c r="E182" s="365"/>
+      <c r="F182" s="365"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -5946,13 +5946,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="361" t="s">
+      <c r="B188" s="362" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="361"/>
-      <c r="D188" s="361"/>
-      <c r="E188" s="361"/>
-      <c r="F188" s="361"/>
+      <c r="C188" s="362"/>
+      <c r="D188" s="362"/>
+      <c r="E188" s="362"/>
+      <c r="F188" s="362"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5960,22 +5960,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="358" t="s">
+      <c r="B191" s="367" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="358"/>
-      <c r="D191" s="358"/>
-      <c r="E191" s="358"/>
-      <c r="F191" s="358"/>
+      <c r="C191" s="367"/>
+      <c r="D191" s="367"/>
+      <c r="E191" s="367"/>
+      <c r="F191" s="367"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="358" t="s">
+      <c r="B192" s="367" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="358"/>
-      <c r="D192" s="358"/>
-      <c r="E192" s="358"/>
-      <c r="F192" s="358"/>
+      <c r="C192" s="367"/>
+      <c r="D192" s="367"/>
+      <c r="E192" s="367"/>
+      <c r="F192" s="367"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5999,6 +5999,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -6015,17 +6026,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13569,20 +13569,20 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>9.3425605536332182E-2</v>
+        <v>0.10305343511450382</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>9.3425605536332182E-2</v>
+        <v>0.10305343511450382</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>8.7197231833910052E-2</v>
+        <v>9.6183206106870242E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>0.13391003460207615</v>
+        <v>0.14770992366412217</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
@@ -14768,50 +14768,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>7.4207443024177352E-2</v>
+        <v>8.1854774938882657E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>8.6594834223666595E-2</v>
+        <v>9.5518729353586435E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>0.11915988171325023</v>
+        <v>0.1314397168516386</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>0.19325313012478076</v>
+        <v>0.2131685290307696</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>0.15878776128205885</v>
+        <v>0.17515138553631682</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>5.6964843474391479E-2</v>
+        <v>6.2835266275187554E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>7.2316045515286406E-2</v>
+        <v>7.976846241953349E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>6.4387779878421939E-2</v>
+        <v>7.1023161774289842E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>6.1153536855740133E-2</v>
+        <v>6.7455618898125569E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>1.0825395950083373E-2</v>
+        <v>1.1940990189214101E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>4.6895368402261016E-3</v>
+        <v>5.1728097207074178E-3</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14825,43 +14825,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12335708464867631</v>
+        <v>0.13606945596743306</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15638617812220884</v>
+        <v>0.17250231098213115</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.22484296277686569</v>
+        <v>0.24801380245234422</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.2080332725036392</v>
+        <v>0.22947181585325091</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.0695199401057516E-2</v>
+        <v>8.9011116896586348E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.9937919197663229E-2</v>
+        <v>8.8175796366888076E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.8292251852053282E-2</v>
+        <v>8.6360537348257257E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.037582588860466E-2</v>
+        <v>8.8658830846590639E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.5983261031093238E-3</v>
+        <v>5.0721994038114299E-3</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-4.8356303420387048E-2</v>
+        <v>-5.3339586597297171E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -15649,10 +15649,10 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E6" s="366" t="s">
+      <c r="E6" s="369" t="s">
         <v>248</v>
       </c>
-      <c r="F6" s="366"/>
+      <c r="F6" s="369"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8">
@@ -15667,8 +15667,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E7" s="366"/>
-      <c r="F7" s="366"/>
+      <c r="E7" s="369"/>
+      <c r="F7" s="369"/>
       <c r="H7" s="120"/>
     </row>
     <row r="8" spans="2:8">
@@ -15683,8 +15683,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E8" s="366"/>
-      <c r="F8" s="366"/>
+      <c r="E8" s="369"/>
+      <c r="F8" s="369"/>
       <c r="H8" s="120"/>
     </row>
     <row r="9" spans="2:8">
@@ -15699,8 +15699,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E9" s="366"/>
-      <c r="F9" s="366"/>
+      <c r="E9" s="369"/>
+      <c r="F9" s="369"/>
       <c r="H9" s="120"/>
     </row>
     <row r="10" spans="2:8" ht="13.15">
@@ -17409,8 +17409,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E6" s="366"/>
-      <c r="F6" s="366"/>
+      <c r="E6" s="369"/>
+      <c r="F6" s="369"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8" ht="13.15">
@@ -18811,7 +18811,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-2.89</v>
+        <v>-2.62</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18875,11 +18875,11 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E7" s="368" t="str">
+      <c r="E7" s="371" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 5-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 10-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 首钢资源(0639.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="368"/>
+      <c r="F7" s="371"/>
       <c r="H7" s="247">
         <v>4</v>
       </c>
@@ -18900,8 +18900,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E8" s="368"/>
-      <c r="F8" s="368"/>
+      <c r="E8" s="371"/>
+      <c r="F8" s="371"/>
       <c r="H8" s="247">
         <v>5</v>
       </c>
@@ -18922,8 +18922,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E9" s="368"/>
-      <c r="F9" s="368"/>
+      <c r="E9" s="371"/>
+      <c r="F9" s="371"/>
       <c r="H9" s="247">
         <v>6</v>
       </c>
@@ -18933,8 +18933,8 @@
       </c>
     </row>
     <row r="10" spans="2:9">
-      <c r="E10" s="368"/>
-      <c r="F10" s="368"/>
+      <c r="E10" s="371"/>
+      <c r="F10" s="371"/>
       <c r="H10" s="247">
         <v>7</v>
       </c>
@@ -18947,8 +18947,8 @@
       <c r="B11" s="159" t="s">
         <v>443</v>
       </c>
-      <c r="E11" s="368"/>
-      <c r="F11" s="368"/>
+      <c r="E11" s="371"/>
+      <c r="F11" s="371"/>
       <c r="H11" s="247">
         <v>8</v>
       </c>
@@ -18966,8 +18966,8 @@
         <v>-0.1059288114314666</v>
       </c>
       <c r="D12" s="158"/>
-      <c r="E12" s="368"/>
-      <c r="F12" s="368"/>
+      <c r="E12" s="371"/>
+      <c r="F12" s="371"/>
       <c r="H12" s="247">
         <v>9</v>
       </c>
@@ -18984,8 +18984,8 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.1663504856430581</v>
       </c>
-      <c r="E13" s="368"/>
-      <c r="F13" s="368"/>
+      <c r="E13" s="371"/>
+      <c r="F13" s="371"/>
       <c r="H13" s="247">
         <v>10</v>
       </c>
@@ -19002,8 +19002,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.18299448813777219</v>
       </c>
-      <c r="E14" s="368"/>
-      <c r="F14" s="368"/>
+      <c r="E14" s="371"/>
+      <c r="F14" s="371"/>
     </row>
     <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
@@ -19029,21 +19029,21 @@
       <c r="C18" s="150">
         <v>5</v>
       </c>
-      <c r="E18" s="368" t="s">
+      <c r="E18" s="371" t="s">
         <v>327</v>
       </c>
-      <c r="F18" s="369"/>
+      <c r="F18" s="372"/>
     </row>
     <row r="19" spans="2:6">
-      <c r="E19" s="369"/>
-      <c r="F19" s="369"/>
+      <c r="E19" s="372"/>
+      <c r="F19" s="372"/>
     </row>
     <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="159" t="s">
         <v>302</v>
       </c>
-      <c r="E20" s="369"/>
-      <c r="F20" s="369"/>
+      <c r="E20" s="372"/>
+      <c r="F20" s="372"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
@@ -19051,14 +19051,14 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>2.89</v>
+        <v>2.62</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E21" s="369"/>
-      <c r="F21" s="369"/>
+      <c r="E21" s="372"/>
+      <c r="F21" s="372"/>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
@@ -19072,8 +19072,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E22" s="369"/>
-      <c r="F22" s="369"/>
+      <c r="E22" s="372"/>
+      <c r="F22" s="372"/>
     </row>
     <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="159" t="s">
@@ -19093,8 +19093,8 @@
         <v>5</v>
       </c>
       <c r="D25" s="163"/>
-      <c r="E25" s="367"/>
-      <c r="F25" s="367"/>
+      <c r="E25" s="370"/>
+      <c r="F25" s="370"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="118" t="s">
@@ -19104,8 +19104,8 @@
         <v>0</v>
       </c>
       <c r="D26" s="164"/>
-      <c r="E26" s="367"/>
-      <c r="F26" s="367"/>
+      <c r="E26" s="370"/>
+      <c r="F26" s="370"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
@@ -19119,8 +19119,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E27" s="367"/>
-      <c r="F27" s="367"/>
+      <c r="E27" s="370"/>
+      <c r="F27" s="370"/>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
@@ -19130,8 +19130,8 @@
         <v>0.6</v>
       </c>
       <c r="D28" s="165"/>
-      <c r="E28" s="367"/>
-      <c r="F28" s="367"/>
+      <c r="E28" s="370"/>
+      <c r="F28" s="370"/>
     </row>
     <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="159" t="s">
@@ -19151,8 +19151,8 @@
         <v>5</v>
       </c>
       <c r="D31" s="163"/>
-      <c r="E31" s="367"/>
-      <c r="F31" s="367"/>
+      <c r="E31" s="370"/>
+      <c r="F31" s="370"/>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="118" t="s">
@@ -19162,8 +19162,8 @@
         <v>-0.02</v>
       </c>
       <c r="D32" s="164"/>
-      <c r="E32" s="367"/>
-      <c r="F32" s="367"/>
+      <c r="E32" s="370"/>
+      <c r="F32" s="370"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
@@ -19177,8 +19177,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E33" s="367"/>
-      <c r="F33" s="367"/>
+      <c r="E33" s="370"/>
+      <c r="F33" s="370"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
@@ -19188,8 +19188,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="165"/>
-      <c r="E34" s="367"/>
-      <c r="F34" s="367"/>
+      <c r="E34" s="370"/>
+      <c r="F34" s="370"/>
     </row>
     <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="159" t="s">
@@ -19209,8 +19209,8 @@
         <v>5</v>
       </c>
       <c r="D37" s="163"/>
-      <c r="E37" s="367"/>
-      <c r="F37" s="367"/>
+      <c r="E37" s="370"/>
+      <c r="F37" s="370"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="118" t="s">
@@ -19220,8 +19220,8 @@
         <v>0.02</v>
       </c>
       <c r="D38" s="164"/>
-      <c r="E38" s="367"/>
-      <c r="F38" s="367"/>
+      <c r="E38" s="370"/>
+      <c r="F38" s="370"/>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
@@ -19235,8 +19235,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E39" s="367"/>
-      <c r="F39" s="367"/>
+      <c r="E39" s="370"/>
+      <c r="F39" s="370"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
@@ -19247,8 +19247,8 @@
         <v>0.2</v>
       </c>
       <c r="D40" s="165"/>
-      <c r="E40" s="367"/>
-      <c r="F40" s="367"/>
+      <c r="E40" s="370"/>
+      <c r="F40" s="370"/>
     </row>
     <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
@@ -19310,8 +19310,8 @@
         <v>10</v>
       </c>
       <c r="D49" s="163"/>
-      <c r="E49" s="367"/>
-      <c r="F49" s="367"/>
+      <c r="E49" s="370"/>
+      <c r="F49" s="370"/>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="118" t="s">
@@ -19321,8 +19321,8 @@
         <v>-0.04</v>
       </c>
       <c r="D50" s="164"/>
-      <c r="E50" s="367"/>
-      <c r="F50" s="367"/>
+      <c r="E50" s="370"/>
+      <c r="F50" s="370"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
@@ -19336,8 +19336,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E51" s="367"/>
-      <c r="F51" s="367"/>
+      <c r="E51" s="370"/>
+      <c r="F51" s="370"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
@@ -19347,8 +19347,8 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="165"/>
-      <c r="E52" s="367"/>
-      <c r="F52" s="367"/>
+      <c r="E52" s="370"/>
+      <c r="F52" s="370"/>
     </row>
     <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="159" t="s">
@@ -19368,8 +19368,8 @@
         <v>10</v>
       </c>
       <c r="D55" s="163"/>
-      <c r="E55" s="367"/>
-      <c r="F55" s="367"/>
+      <c r="E55" s="370"/>
+      <c r="F55" s="370"/>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="118" t="s">
@@ -19379,8 +19379,8 @@
         <v>0.04</v>
       </c>
       <c r="D56" s="164"/>
-      <c r="E56" s="367"/>
-      <c r="F56" s="367"/>
+      <c r="E56" s="370"/>
+      <c r="F56" s="370"/>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
@@ -19394,8 +19394,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E57" s="367"/>
-      <c r="F57" s="367"/>
+      <c r="E57" s="370"/>
+      <c r="F57" s="370"/>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
@@ -19405,8 +19405,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="165"/>
-      <c r="E58" s="367"/>
-      <c r="F58" s="367"/>
+      <c r="E58" s="370"/>
+      <c r="F58" s="370"/>
     </row>
     <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
@@ -19649,7 +19649,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>2.89</v>
+        <v>2.62</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19662,7 +19662,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.23964880679790124</v>
+        <v>0.28412064787572122</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -19895,19 +19895,19 @@
   <dimension ref="B2:E2"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="2.59765625" style="372" customWidth="1"/>
-    <col min="2" max="2" width="22.73046875" style="372" customWidth="1"/>
-    <col min="3" max="5" width="20.73046875" style="372" customWidth="1"/>
-    <col min="6" max="16384" width="9.06640625" style="372"/>
+    <col min="1" max="1" width="2.59765625" style="360" customWidth="1"/>
+    <col min="2" max="2" width="22.73046875" style="360" customWidth="1"/>
+    <col min="3" max="5" width="20.73046875" style="360" customWidth="1"/>
+    <col min="6" max="16384" width="9.06640625" style="360"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:5" ht="13.9">
-      <c r="B2" s="370" t="s">
+      <c r="B2" s="358" t="s">
         <v>456</v>
       </c>
-      <c r="C2" s="371"/>
-      <c r="D2" s="371"/>
-      <c r="E2" s="371"/>
+      <c r="C2" s="359"/>
+      <c r="D2" s="359"/>
+      <c r="E2" s="359"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/financial_models/opportunities/0639.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0639.HK_Valuation.xlsx
@@ -8,45 +8,46 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{883F8DA9-0C13-453C-8E9D-CCC63CD45326}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D00259FC-FAE8-4390-A867-C30EF65C19A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Thesis" sheetId="6" r:id="rId1"/>
-    <sheet name="Data" sheetId="4" r:id="rId2"/>
-    <sheet name="BS" sheetId="3" r:id="rId3"/>
-    <sheet name="Normalized_FCF" sheetId="2" r:id="rId4"/>
-    <sheet name="DCF" sheetId="8" r:id="rId5"/>
-    <sheet name="DDM" sheetId="10" r:id="rId6"/>
-    <sheet name="Scenarios" sheetId="9" r:id="rId7"/>
-    <sheet name="Breakdown" sheetId="12" r:id="rId8"/>
+    <sheet name="投资主题" sheetId="12" r:id="rId1"/>
+    <sheet name="Thesis" sheetId="6" r:id="rId2"/>
+    <sheet name="Data" sheetId="4" r:id="rId3"/>
+    <sheet name="BS" sheetId="3" r:id="rId4"/>
+    <sheet name="Normalized_FCF" sheetId="2" r:id="rId5"/>
+    <sheet name="DCF" sheetId="8" r:id="rId6"/>
+    <sheet name="DDM" sheetId="10" r:id="rId7"/>
+    <sheet name="Scenarios" sheetId="9" r:id="rId8"/>
+    <sheet name="Breakdown" sheetId="13" r:id="rId9"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId9"/>
+    <externalReference r:id="rId10"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">DCF!$B$73:$H$73</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">DDM!$B$68:$H$68</definedName>
-    <definedName name="Common_Shares" localSheetId="7">[1]Thesis!$C$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">DCF!$B$73:$H$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">DDM!$B$68:$H$68</definedName>
+    <definedName name="Common_Shares" localSheetId="8">[1]Thesis!$C$6</definedName>
     <definedName name="Common_Shares">Thesis!$C$6</definedName>
-    <definedName name="dividend_tax_rate" localSheetId="7">[1]Normalized_FCF!$C$93</definedName>
+    <definedName name="dividend_tax_rate" localSheetId="8">[1]Normalized_FCF!$C$93</definedName>
     <definedName name="dividend_tax_rate">Normalized_FCF!$C$93</definedName>
-    <definedName name="Equity_Cost" localSheetId="7">[1]Thesis!$C$86</definedName>
+    <definedName name="Equity_Cost" localSheetId="8">[1]Thesis!$C$86</definedName>
     <definedName name="Equity_Cost">Thesis!$C$86</definedName>
-    <definedName name="Exchange_Rate" localSheetId="7">[1]Thesis!$C$16</definedName>
+    <definedName name="Exchange_Rate" localSheetId="8">[1]Thesis!$C$16</definedName>
     <definedName name="Exchange_Rate">Thesis!$C$16</definedName>
-    <definedName name="Market_currency" localSheetId="7">[1]Thesis!$C$13</definedName>
+    <definedName name="Market_currency" localSheetId="8">[1]Thesis!$C$13</definedName>
     <definedName name="Market_currency">Thesis!$C$13</definedName>
-    <definedName name="Market_Price" localSheetId="7">[1]Thesis!$C$12</definedName>
+    <definedName name="Market_Price" localSheetId="8">[1]Thesis!$C$12</definedName>
     <definedName name="Market_Price">Thesis!$C$12</definedName>
-    <definedName name="Reporting_currency" localSheetId="7">[1]Thesis!$C$25</definedName>
+    <definedName name="Reporting_currency" localSheetId="8">[1]Thesis!$C$25</definedName>
     <definedName name="Reporting_currency">Thesis!$C$25</definedName>
-    <definedName name="scaling_factor" localSheetId="7">[1]Data!$C$3</definedName>
+    <definedName name="scaling_factor" localSheetId="8">[1]Data!$C$3</definedName>
     <definedName name="scaling_factor">Data!$C$3</definedName>
-    <definedName name="Terminal_Growth" localSheetId="7">[1]Thesis!$C$92</definedName>
+    <definedName name="Terminal_Growth" localSheetId="8">[1]Thesis!$C$92</definedName>
     <definedName name="Terminal_Growth">Thesis!$C$92</definedName>
-    <definedName name="valuation_method" localSheetId="7">[1]Thesis!$E$21</definedName>
+    <definedName name="valuation_method" localSheetId="8">[1]Thesis!$E$21</definedName>
     <definedName name="valuation_method">Thesis!$E$21</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -55,20 +56,14 @@
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion1">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId10" roundtripDataSignature="AMtx7mi73Cg0ax9bLfpeUuF69nNRn7idDQ=="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId11" roundtripDataSignature="AMtx7mi73Cg0ax9bLfpeUuF69nNRn7idDQ=="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="687" uniqueCount="466">
-  <si>
-    <t>Number of Shares:</t>
-  </si>
-  <si>
-    <t>Exchange Rate:</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="836" uniqueCount="560">
   <si>
     <t>Sales</t>
   </si>
@@ -411,10 +406,6 @@
   </si>
   <si>
     <t>Debt/EBIT</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Market Price:</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1348,10 +1339,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Update Required After:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>FCFE/Market Cap</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1504,10 +1491,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Report Interval:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Note of the formulas:</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1525,10 +1508,6 @@
   </si>
   <si>
     <t>Note on the logic</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Company Name</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1760,71 +1739,11 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Step 2: The No-Growth Baseline (Calculating Stable Income Value)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Note:</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>Step 3: Adjusting for Financial Structure (Calculating No Growth Equity Value)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Step 4: Incorporating Future Potential &amp; Risk (Scenario Analysis)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t xml:space="preserve">Guidance Note: </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>This model determines a target buy price consistent with defined investment criteria. It follows a logical progression: establishing current sustainable earnings, adjusting for financial structure, incorporating growth scenarios, and finally applying the investor’s required return.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>Goal:</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t xml:space="preserve"> To quantify the underlying FCFE the business consistently generates for its equity owners, stripping away temporary fluctuations or accounting choices.The FCFE/Market Cap yield gives a direct measure of this cash generation relative to the current market price.</t>
-    </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1864,32 +1783,6 @@
         <family val="2"/>
         <scheme val="major"/>
       </rPr>
-      <t>Goal:</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t xml:space="preserve"> To determine the intrinsic value of the company’s equity if the Normalized FCFE (calculated in Step 1) were to remain constant perpetually, with zero future growth. This establishes a baseline value derived solely from the current sustainable earnings power.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
       <t>Cost of Equity:</t>
     </r>
     <r>
@@ -1987,30 +1880,6 @@
     <r>
       <rPr>
         <b/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>Goal:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t xml:space="preserve"> To estimate the company’s intrinsic value by considering plausible future scenarios beyond the static no-growth assumption. Based on fundamental research, each scenario defines high growth periods (HGP), high growth rates (HGR), and its probability.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
         <i/>
         <sz val="9"/>
         <color rgb="FF000000"/>
@@ -2034,58 +1903,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>Calculation Logic:</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t xml:space="preserve"> The Target Buy Price is determined by discounting future cash flows—expected annual dividends and the Expected Equity Value—at the Target Annual Return, realized over the holding period.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>Insight:</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t xml:space="preserve"> Significant market volatility is analyzed as an indicator of the range of market-perceived outcomes, including extremes that define boundaries for scenarios like "Snowball" or "Devil’s Advocate." Scenario Analysis then filters these using fundamental reasoning to evaluate their likelihood.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>CFO</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2103,23 +1920,6 @@
   </si>
   <si>
     <t>Key Risk Factors</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Goal: </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>To identify and assess the key risk factors inherent in this valuation model, focusing on those with the greatest potential impact on the final result.</t>
-    </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -2162,10 +1962,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>The Cost of Equity is established as an investor’s hurdle rate. This rate serves as an opportunity cost threshold for capital allocation, prioritizing consistency and long-term decision-making over market-derived metrics.The model calculates intrinsic value using a standardized base cost of equity as the discount rate in DCF analysis. This rate serves as the minimum acceptable long-term return threshold, reflecting long-term risk-free rates plus an equity risk premium to account for ownership risks.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>- The Expected Equity Value is heavily dependent on the specific growth rates (HGR), durations (HGP), and probabilities assigned to each scenario. These are inherently forecasts about an uncertain future.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2284,10 +2080,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Step 5: Determining the Investment Decision</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>@Selling Yield</t>
     <phoneticPr fontId="28" type="noConversion"/>
   </si>
@@ -2331,136 +2123,1151 @@
     <t>Market Currency</t>
   </si>
   <si>
+    <t>Listing Information</t>
+  </si>
+  <si>
+    <t>@Benchmark Yield</t>
+  </si>
+  <si>
+    <t>Exit Price Output</t>
+  </si>
+  <si>
+    <t>Benchmark Yield</t>
+  </si>
+  <si>
+    <t>Target return</t>
+  </si>
+  <si>
+    <t>Target Price</t>
+  </si>
+  <si>
+    <t>Entry Price</t>
+  </si>
+  <si>
+    <t>Sell Price</t>
+  </si>
+  <si>
+    <t>Exit Price</t>
+  </si>
+  <si>
+    <t>Holding Period</t>
+  </si>
+  <si>
+    <t>Risk Premium</t>
+  </si>
+  <si>
+    <t>Base Cost of Equity</t>
+  </si>
+  <si>
+    <t>Result (Exit)</t>
+  </si>
+  <si>
+    <t>Valuation Outputs</t>
+  </si>
+  <si>
+    <t>Business Model Risk Premium:</t>
+  </si>
+  <si>
+    <t>Management Risk Premium:</t>
+  </si>
+  <si>
+    <t>Base equity cost</t>
+  </si>
+  <si>
+    <t>Entry yield</t>
+  </si>
+  <si>
+    <t>Benchmark yield</t>
+  </si>
+  <si>
+    <t>Valuation Method</t>
+  </si>
+  <si>
+    <t>Dividend</t>
+  </si>
+  <si>
+    <t>Dividend Value</t>
+  </si>
+  <si>
+    <t>No-Growth DDM</t>
+  </si>
+  <si>
+    <t>No-Growth DDM Valuation</t>
+  </si>
+  <si>
+    <t>Dividend Value per share</t>
+  </si>
+  <si>
+    <t>PV of Dividends</t>
+  </si>
+  <si>
+    <t>Dividends</t>
+  </si>
+  <si>
+    <t>YoY CAGR</t>
+  </si>
+  <si>
+    <t>Payout Ratio:</t>
+  </si>
+  <si>
+    <t>No Growth Equity Value per share =</t>
+  </si>
+  <si>
+    <t>INT</t>
+  </si>
+  <si>
+    <t>DuPont Analysis</t>
+  </si>
+  <si>
+    <t>ROE =</t>
+  </si>
+  <si>
+    <t>Normalized</t>
+  </si>
+  <si>
+    <t>Latest</t>
+  </si>
+  <si>
+    <t>LT AR and Prepayments</t>
+  </si>
+  <si>
+    <t>Dividend after tax Yield</t>
+  </si>
+  <si>
+    <t>Dividend tax rate</t>
+  </si>
+  <si>
+    <t>After tax Dividend/Market Cap =</t>
+  </si>
+  <si>
+    <t>After-tax Dividend per share</t>
+  </si>
+  <si>
+    <t>Divisional Analysis (Optional)</t>
+  </si>
+  <si>
+    <t>模型最后更新日期:</t>
+  </si>
+  <si>
+    <t>执行摘要</t>
+  </si>
+  <si>
+    <t>公司信息</t>
+  </si>
+  <si>
+    <t>上市信息</t>
+  </si>
+  <si>
+    <t>增长分类:</t>
+  </si>
+  <si>
+    <t>对比板块:</t>
+  </si>
+  <si>
+    <t>商业模式风险溢价:</t>
+  </si>
+  <si>
+    <t>管理风险溢价:</t>
+  </si>
+  <si>
+    <t>报告货币:</t>
+  </si>
+  <si>
+    <t>市场隐含年回报率:</t>
+  </si>
+  <si>
+    <t>估值方法</t>
+  </si>
+  <si>
+    <t>估值输出</t>
+  </si>
+  <si>
+    <t>目标价格</t>
+  </si>
+  <si>
+    <t>入场价格</t>
+  </si>
+  <si>
+    <t>卖出价格</t>
+  </si>
+  <si>
+    <t>退出价格</t>
+  </si>
+  <si>
+    <t>持有期</t>
+  </si>
+  <si>
+    <t>入场收益率</t>
+  </si>
+  <si>
+    <t>目标回报率</t>
+  </si>
+  <si>
+    <t>基准收益率</t>
+  </si>
+  <si>
+    <t>步骤1：确定公司可持续盈利能力（计算标准化FCFE）</t>
+  </si>
+  <si>
+    <t>Company Name:</t>
+  </si>
+  <si>
+    <t>Number of Shares:</t>
+  </si>
+  <si>
+    <t>Report Interval:</t>
+  </si>
+  <si>
+    <t>Update Required After:</t>
+  </si>
+  <si>
     <t>Symbol:</t>
   </si>
   <si>
-    <t>Listing Information</t>
+    <t>Market Price:</t>
+  </si>
+  <si>
+    <t>Market Currency:</t>
+  </si>
+  <si>
+    <t>Market Capitalization:</t>
   </si>
   <si>
     <t>Forex Symbol:</t>
   </si>
   <si>
-    <t>Capitalization:</t>
-  </si>
-  <si>
-    <t>@Benchmark Yield</t>
-  </si>
-  <si>
-    <t>Exit Price Output</t>
-  </si>
-  <si>
-    <t>Benchmark Yield</t>
-  </si>
-  <si>
-    <t>Target return</t>
-  </si>
-  <si>
-    <t>Target Price</t>
-  </si>
-  <si>
-    <t>Entry Price</t>
-  </si>
-  <si>
-    <t>Sell Price</t>
-  </si>
-  <si>
-    <t>Exit Price</t>
-  </si>
-  <si>
-    <t>Holding Period</t>
-  </si>
-  <si>
-    <t>Risk Premium</t>
-  </si>
-  <si>
-    <t>Base Cost of Equity</t>
-  </si>
-  <si>
-    <t>Result (Exit)</t>
-  </si>
-  <si>
-    <t>Valuation Outputs</t>
-  </si>
-  <si>
-    <t>Business Model Risk Premium:</t>
-  </si>
-  <si>
-    <t>Management Risk Premium:</t>
-  </si>
-  <si>
-    <t>Base equity cost</t>
-  </si>
-  <si>
-    <t>Entry yield</t>
-  </si>
-  <si>
-    <t>Benchmark yield</t>
-  </si>
-  <si>
-    <t>Valuation Method</t>
-  </si>
-  <si>
-    <t>Dividend</t>
-  </si>
-  <si>
-    <t>Dividend Value</t>
-  </si>
-  <si>
-    <t>No-Growth DDM</t>
-  </si>
-  <si>
-    <t>No-Growth DDM Valuation</t>
-  </si>
-  <si>
-    <t>Dividend Value per share</t>
-  </si>
-  <si>
-    <t>PV of Dividends</t>
-  </si>
-  <si>
-    <t>Dividends</t>
-  </si>
-  <si>
-    <t>YoY CAGR</t>
-  </si>
-  <si>
-    <t>Payout Ratio:</t>
-  </si>
-  <si>
-    <t>No Growth Equity Value per share =</t>
-  </si>
-  <si>
-    <t>INT</t>
-  </si>
-  <si>
-    <t>DuPont Analysis</t>
-  </si>
-  <si>
-    <t>ROE =</t>
-  </si>
-  <si>
-    <t>Normalized</t>
-  </si>
-  <si>
-    <t>Latest</t>
-  </si>
-  <si>
-    <t>LT AR and Prepayments</t>
-  </si>
-  <si>
-    <t>Dividend after tax Yield</t>
-  </si>
-  <si>
-    <t>Dividend tax rate</t>
-  </si>
-  <si>
-    <t>After tax Dividend/Market Cap =</t>
-  </si>
-  <si>
-    <t>After-tax Dividend per share</t>
-  </si>
-  <si>
-    <t>Divisional Analysis (Optional)</t>
+    <t>Exchange Rate:</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve">Guidance Note: </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>This model evaluates the company using a structured investment process to determine its intrinsic value and target prices. It focuses on sustainable FCF capacity, adjusts for financial structure, incorporates growth scenarios, and calculates expected returns based on the derived intrinsic value.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Goal:</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> To quantify the underlying FCFE the business consistently generates, stripping away temporary fluctuations or accounting choices.</t>
+    </r>
+  </si>
+  <si>
+    <t>Step 2: Calculating the No-Growth Baseline (Calculating Stable Income Value)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Goal:</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> Determine the intrinsic value assuming the current Normalized FCFE remains constant with no growth, providing a conservative baseline.</t>
+    </r>
+  </si>
+  <si>
+    <t>Step 4: Incorporating Future Potential (Scenario Analysis)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Goal:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> Estimate intrinsic value by modeling plausible FCFE/Dividend, high growth periods (HGP), and high growth rates (HGR) scenarios, weighted by probability.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Insight:</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> Significant market volatility is analyzed as an indicator of the range of market-perceived outcomes, including extremes that define boundaries for scenarios like "Snowball" or "Devil’s Advocate." Scenario Analysis then filters these using fundamental reasoning to evaluate their likelihood.</t>
+    </r>
+  </si>
+  <si>
+    <t>Step 5: Determining Investment Decisions</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Calculation Logic:</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> Discount future dividends and the expected equity value at the target return rates.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Goal: </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Highlight risks impacting the valuation, focusing on factors affecting FCFE/dividend sustainability.</t>
+    </r>
+  </si>
+  <si>
+    <t>The Cost of Equity is established as an investor’s hurdle rate. This rate serves as an opportunity cost threshold for capital allocation.The model calculates intrinsic value using a standardized base cost of equity as the discount rate in DCF/DDM analysis. This rate serves as the minimum acceptable long-term return threshold, reflecting long-term risk-free rates plus an equity risk premium.</t>
+  </si>
+  <si>
+    <t>公司名称：</t>
+  </si>
+  <si>
+    <t>股份数量：</t>
+  </si>
+  <si>
+    <t>报告间隔：</t>
+  </si>
+  <si>
+    <t>下次更新日期：</t>
+  </si>
+  <si>
+    <t>股票代码：</t>
+  </si>
+  <si>
+    <t>市场价格：</t>
+  </si>
+  <si>
+    <t>市价货币：</t>
+  </si>
+  <si>
+    <t>市值：</t>
+  </si>
+  <si>
+    <t>外汇符号：</t>
+  </si>
+  <si>
+    <t>汇率：</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>指导说明：</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>该模型使用结构化的投资流程来评估公司，确定其内在价值和目标价格。它关注可持续的自由现金流（FCF）能力，调整财务结构，纳入增长情景，并根据得出的内在价值计算预期回报。</t>
+    </r>
+  </si>
+  <si>
+    <t>估值概述</t>
+  </si>
+  <si>
+    <t>基础Equity Cost</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>目标：</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>量化业务持续生成的潜在自由现金流（FCFE），去除临时波动或会计选择的影响。</t>
+    </r>
+  </si>
+  <si>
+    <t>关键组成部分</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">• </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Normalized Operating EBIT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>：核心业务运营的税前息前利润，调整以剔除一次性或非经常性项目，形成可持续盈利基础。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">• </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Depreciation &amp; Amortization (D&amp;A):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> 非现金费用，加入以反映运营产生的现金。
+• </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Capital Expenditures (Capex)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>: 维持或扩展运营资产所需的现金流出。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">• </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve">Stable Non-Operating EBIT: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>来自非核心资产的持续收益，如固定收益投资、支付股息的股票或租赁物业。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">• </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Net Interest Income:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> 利息收入减去利息支出</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>• NCI’s Share of Profits:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> NCI代表子公司中母公司未拥有的股权部分。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">• </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Working Capital Investment (WCInv):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> WCInv仅在显著扭曲FCFE时纳入。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>关于净借款的说明：</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>理论上，本金偿还通过净借款核算。然而，该模型旨在避免明确预测债务发行或偿还。相反，本金偿还通过有息债务在股权价值调整中反映。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>洞察：</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>这一步骤通过纳入运营和稳定的非运营来源，同时考虑税金和再投资需求，确保现金流的全面衡量。</t>
+    </r>
+  </si>
+  <si>
+    <t>最新FCFE =</t>
+  </si>
+  <si>
+    <t>派息比率:</t>
+  </si>
+  <si>
+    <t>最新</t>
+  </si>
+  <si>
+    <t>步骤2：计算无增长基线（计算稳定收入价值）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>目标：</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>确定内在价值，假设当前的标准化FCFE保持不变且无增长，提供保守的基线。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Cost of Equity:</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> 反映公司的风险概况，代表投资者为承担拥有此类业务一般风险所需的最低回报，而目标年回报率作为投资者要求的回报率。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Terminal Growth Rate:</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> 将g设为0%是一个保守假设，仅基于公司当前表现的盈利能力估值，不依赖潜在乐观的未来增长预测。</t>
+    </r>
+  </si>
+  <si>
+    <t>步骤3：调整财务结构（计算无增长股权价值）</t>
+  </si>
+  <si>
+    <t>目标：通过纳入公司的资产负债表结构，细化稳定收入价值（SIV）。</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>关于债务的说明：</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>总有息债务包括本金偿还。理想情况下，应根据偿还时间表贴现。但为简单和保守起见，该模型使用总有息债务的账面价值。</t>
+    </r>
+  </si>
+  <si>
+    <t>说明：</t>
+  </si>
+  <si>
+    <t>杜邦分析</t>
+  </si>
+  <si>
+    <t>• Non-Operating Cash: 运营不需要的超额现金</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">• </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Other Non-Operating Assets:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> 不贡献FCFE的资产（如非收益性投资或物业）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>洞察：</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>无增长股权价值每股代表公司在考虑未来增长潜力前，基于当前可持续运营和净财务状况的内在价值估计，作为基本锚定的估值基线。</t>
+    </r>
+  </si>
+  <si>
+    <t>无增长股权价值每股 =</t>
+  </si>
+  <si>
+    <t>步骤4：纳入未来潜力（情景分析）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>目标：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>通过建模合理的FCFE/股息、高增长期（HGP）和高增长率（HGR）情景，并按概率加权，估计内在价值。</t>
+    </r>
+  </si>
+  <si>
+    <t>情景</t>
+  </si>
+  <si>
+    <t>HGR</t>
+  </si>
+  <si>
+    <t>每股EV</t>
+  </si>
+  <si>
+    <t>概率</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>洞察：</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>分析市场大幅波动作为市场感知结果范围的指标，包括定义“雪球”或“魔鬼代言人”等情景边界的极端情况。情景分析使用基本推理评估这些情景的可能性。</t>
+    </r>
+  </si>
+  <si>
+    <t>步骤5：确定投资决策</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>目标：</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>将公司内在价值估计（来自步骤4）转化为满足特定投资要求的具体买入价格。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>计算逻辑：</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>The Target Buy Price is determined by discounting future cash flows—expected annual dividends and the Expected Equity Value—at the Target Annual Return, realized over the holding period.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">预期持有期 = </t>
+  </si>
+  <si>
+    <t>目标年回报率 =</t>
+  </si>
+  <si>
+    <t xml:space="preserve">每股年度股息 = </t>
+  </si>
+  <si>
+    <t>结果 (Target)</t>
+  </si>
+  <si>
+    <t>市场货币</t>
+  </si>
+  <si>
+    <t>@ 安全边际</t>
+  </si>
+  <si>
+    <r>
+      <t>目标：</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>关注影响FCFE/股息可持续性的估值风险因素。</t>
+    </r>
+  </si>
+  <si>
+    <t>关键风险因素</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>标准化FCFE的准确性</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>, 受不确定性影响，包括：</t>
+    </r>
+  </si>
+  <si>
+    <t>- 可持续收入和利润率</t>
+  </si>
+  <si>
+    <t>- 资本支出</t>
+  </si>
+  <si>
+    <t>- 营运资金</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">2. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Cost of Equity的适当性</t>
+    </r>
+  </si>
+  <si>
+    <t>作为资本配置的机会成本门槛。该模型在DCF/DDM分析中使用标准化的贴现率，计算内在价值。此利率作为最低可接受的长期回报门槛，反映长期无风险利率加上股权风险溢价。</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">3. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>增长情景的可靠性</t>
+    </r>
+  </si>
+  <si>
+    <t>- 预期股权价值高度依赖各情景的特定增长率（HGR）、持续时间（HGP）和概率，这些是对不确定未来的预测。</t>
+  </si>
+  <si>
+    <t>- 极端情景（“雪球”、“魔鬼代言人”）概率较低；若市场条件剧变，可能变得比预期更相关。</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">4. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>外部和公司特定风险</t>
+    </r>
+  </si>
+  <si>
+    <t>- 宏观经济敏感性</t>
+  </si>
+  <si>
+    <t>- 投入成本波动</t>
+  </si>
+  <si>
+    <t>- 激烈竞争等</t>
+  </si>
+  <si>
+    <t>Est. (Net Asset) Realizable Value</t>
+  </si>
+  <si>
+    <t>估计(净资产)可变现价值</t>
   </si>
   <si>
     <t>Y</t>
@@ -3168,7 +3975,7 @@
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
     <xf numFmtId="0" fontId="59" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="373">
+  <cellXfs count="382">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3917,33 +4724,55 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="177" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="175" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="1" xfId="2"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
@@ -3958,10 +4787,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="1" xfId="2"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="2" xr:uid="{01EDE6FD-0E0D-47F4-8B6F-FD2292C76C8D}"/>
+    <cellStyle name="常规 2" xfId="2" xr:uid="{C04B486E-6FC7-49BB-B6BA-011B4CED336A}"/>
     <cellStyle name="常规 2 2" xfId="1" xr:uid="{A35F4541-DCCE-4554-A311-39480A36979A}"/>
   </cellStyles>
   <dxfs count="8">
@@ -4073,7 +4907,7 @@
         </row>
         <row r="12">
           <cell r="C12">
-            <v>2.89</v>
+            <v>2.62</v>
           </cell>
         </row>
         <row r="13">
@@ -4328,6 +5162,1749 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA287911-AF8F-41DE-9E8E-72556F041FFB}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:J197"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
+  <cols>
+    <col min="1" max="1" width="2.73046875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="32.73046875" style="1" customWidth="1"/>
+    <col min="3" max="4" width="25.73046875" style="1" customWidth="1"/>
+    <col min="5" max="6" width="15.73046875" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="B1" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="C1" s="33">
+        <f>Thesis!C1</f>
+        <v>45807</v>
+      </c>
+      <c r="D1" s="358" t="str">
+        <f>Thesis!D1</f>
+        <v>INT</v>
+      </c>
+      <c r="E1" s="292" t="s">
+        <v>344</v>
+      </c>
+      <c r="F1" s="307" t="str">
+        <f>Thesis!F1</f>
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="13.9">
+      <c r="A2" s="222" t="s">
+        <v>438</v>
+      </c>
+      <c r="B2" s="36"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="36"/>
+      <c r="F2" s="36"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
+      <c r="I2" s="22"/>
+      <c r="J2" s="22"/>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="B4" s="45" t="s">
+        <v>439</v>
+      </c>
+      <c r="C4" s="46"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+    </row>
+    <row r="5" spans="1:10" ht="12.4">
+      <c r="B5" s="4" t="s">
+        <v>479</v>
+      </c>
+      <c r="C5" s="359" t="str">
+        <f>Thesis!C5</f>
+        <v>首钢资源</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="B6" s="4" t="s">
+        <v>480</v>
+      </c>
+      <c r="C6" s="34">
+        <f>Common_Shares</f>
+        <v>5091065770</v>
+      </c>
+      <c r="E6" s="48"/>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="B7" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="C7" s="360">
+        <f>Thesis!C7</f>
+        <v>6</v>
+      </c>
+      <c r="D7" s="48"/>
+      <c r="E7" s="48"/>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="B8" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="C8" s="33">
+        <f>EOMONTH(EDATE(BS!C1,C7+2),0)</f>
+        <v>45900</v>
+      </c>
+      <c r="E8" s="48"/>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="E9" s="34"/>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="B10" s="45" t="s">
+        <v>440</v>
+      </c>
+      <c r="C10" s="46"/>
+      <c r="E10" s="34"/>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="B11" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="C11" s="365" t="str">
+        <f>Thesis!C11</f>
+        <v>0639.HK</v>
+      </c>
+      <c r="D11" s="49"/>
+      <c r="E11" s="34"/>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="B12" s="4" t="s">
+        <v>484</v>
+      </c>
+      <c r="C12" s="366">
+        <f>Market_Price</f>
+        <v>2.62</v>
+      </c>
+      <c r="D12" s="50"/>
+      <c r="E12" s="48"/>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="B13" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="C13" s="32" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+      <c r="D13" s="48"/>
+      <c r="E13" s="5"/>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="B14" s="4" t="s">
+        <v>486</v>
+      </c>
+      <c r="C14" s="35">
+        <f>投资主题!C12*Common_Shares/1000000</f>
+        <v>13338.5923174</v>
+      </c>
+      <c r="D14" s="35" t="str">
+        <f>IF(D11="","",投资主题!D12*Common_Shares/1000000)</f>
+        <v/>
+      </c>
+      <c r="E14" s="5"/>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="B15" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="C15" s="32" t="str">
+        <f>IF(C25=C13,C13,C25&amp;"/"&amp;C13)</f>
+        <v>HKD</v>
+      </c>
+      <c r="D15" s="32" t="str">
+        <f>IF(D11="","",IF(C25=D13,D13,C25&amp;"/"&amp;D13))</f>
+        <v/>
+      </c>
+      <c r="E15" s="5"/>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="B16" s="4" t="s">
+        <v>488</v>
+      </c>
+      <c r="C16" s="366">
+        <f>Exchange_Rate</f>
+        <v>1</v>
+      </c>
+      <c r="D16" s="50"/>
+      <c r="E16" s="5"/>
+    </row>
+    <row r="17" spans="2:6">
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+    </row>
+    <row r="18" spans="2:6" ht="24.6" customHeight="1">
+      <c r="B18" s="371" t="s">
+        <v>489</v>
+      </c>
+      <c r="C18" s="371"/>
+      <c r="D18" s="371"/>
+      <c r="E18" s="371"/>
+      <c r="F18" s="371"/>
+    </row>
+    <row r="20" spans="2:6">
+      <c r="B20" s="45" t="s">
+        <v>490</v>
+      </c>
+      <c r="C20" s="46"/>
+      <c r="D20" s="5"/>
+    </row>
+    <row r="21" spans="2:6">
+      <c r="B21" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="C21" s="32" t="str">
+        <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
+        <v xml:space="preserve">Low Growth </v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="E21" s="363" t="str">
+        <f>valuation_method</f>
+        <v>DCF</v>
+      </c>
+    </row>
+    <row r="22" spans="2:6">
+      <c r="B22" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="C22" s="32" t="str">
+        <f>Thesis!C22</f>
+        <v>MAT_01</v>
+      </c>
+      <c r="D22" s="1" t="str">
+        <f>IF(valuation_method="DDM","终值贴现率","")</f>
+        <v/>
+      </c>
+      <c r="E22" s="364">
+        <f>Thesis!E22</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="2:6">
+      <c r="B23" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="C23" s="253" t="str">
+        <f>Thesis!C23</f>
+        <v>N</v>
+      </c>
+    </row>
+    <row r="24" spans="2:6">
+      <c r="B24" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="C24" s="253" t="str">
+        <f>Thesis!C24</f>
+        <v>N</v>
+      </c>
+    </row>
+    <row r="25" spans="2:6">
+      <c r="B25" s="4" t="s">
+        <v>445</v>
+      </c>
+      <c r="C25" s="32" t="str">
+        <f>Reporting_currency</f>
+        <v>HKD</v>
+      </c>
+      <c r="D25" s="32" t="str">
+        <f>IF(D11="","",Market_currency&amp;"/"&amp;D13&amp;":")</f>
+        <v/>
+      </c>
+      <c r="E25" s="299" t="str">
+        <f>IF(D11="","",1/Exchange_Rate*D16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="2:6">
+      <c r="B26" s="1" t="str">
+        <f>"预期股权价值 ("&amp;C13&amp;") :"</f>
+        <v>预期股权价值 (HKD) :</v>
+      </c>
+      <c r="C26" s="304">
+        <f>C132</f>
+        <v>4.4858408799140586</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="E26" s="301">
+        <f ca="1">Scenarios!C87</f>
+        <v>0.28412064787572122</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6">
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+    </row>
+    <row r="28" spans="2:6">
+      <c r="B28" s="45" t="s">
+        <v>448</v>
+      </c>
+      <c r="C28" s="309" t="str">
+        <f>C145&amp;" ("&amp;Market_currency&amp;")"</f>
+        <v>0639.HK (HKD)</v>
+      </c>
+      <c r="D28" s="309" t="str">
+        <f>IF(D11="","",D145&amp;" ("&amp;D13&amp;")")</f>
+        <v/>
+      </c>
+      <c r="E28" s="305" t="s">
+        <v>453</v>
+      </c>
+      <c r="F28" s="361">
+        <f>Thesis!F28</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="2:6">
+      <c r="B29" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="C29" s="310">
+        <f>C149</f>
+        <v>2.2811221378505544</v>
+      </c>
+      <c r="D29" s="310" t="str">
+        <f>D149</f>
+        <v/>
+      </c>
+      <c r="E29" s="306" t="s">
+        <v>455</v>
+      </c>
+      <c r="F29" s="362">
+        <f>Thesis!F29</f>
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6">
+      <c r="B30" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="C30" s="311">
+        <f>C157</f>
+        <v>2.823790530515998</v>
+      </c>
+      <c r="D30" s="311" t="str">
+        <f>D157</f>
+        <v/>
+      </c>
+      <c r="E30" s="307" t="s">
+        <v>454</v>
+      </c>
+      <c r="F30" s="224">
+        <f>Thesis!F30</f>
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="31" spans="2:6">
+      <c r="B31" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="C31" s="311">
+        <f>C165</f>
+        <v>4.3130669791905083</v>
+      </c>
+      <c r="D31" s="311" t="str">
+        <f>D165</f>
+        <v/>
+      </c>
+      <c r="E31" s="307" t="s">
+        <v>491</v>
+      </c>
+      <c r="F31" s="224">
+        <f>Thesis!F31</f>
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="2:6">
+      <c r="B32" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="C32" s="311">
+        <f>C173</f>
+        <v>3.8666759160925035</v>
+      </c>
+      <c r="D32" s="311" t="str">
+        <f>D173</f>
+        <v/>
+      </c>
+      <c r="E32" s="307" t="s">
+        <v>456</v>
+      </c>
+      <c r="F32" s="224">
+        <f>Thesis!F32</f>
+        <v>0.1174</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="D33" s="5"/>
+      <c r="E33" s="5"/>
+    </row>
+    <row r="34" spans="1:6" ht="13.9">
+      <c r="A34" s="222" t="s">
+        <v>457</v>
+      </c>
+      <c r="B34" s="36"/>
+      <c r="C34" s="36"/>
+      <c r="D34" s="36"/>
+      <c r="E34" s="36"/>
+      <c r="F34" s="36"/>
+    </row>
+    <row r="36" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B36" s="371" t="s">
+        <v>492</v>
+      </c>
+      <c r="C36" s="371"/>
+      <c r="D36" s="371"/>
+      <c r="E36" s="371"/>
+      <c r="F36" s="371"/>
+    </row>
+    <row r="37" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B37" s="374" t="s">
+        <v>330</v>
+      </c>
+      <c r="C37" s="374"/>
+      <c r="D37" s="374"/>
+      <c r="E37" s="374"/>
+      <c r="F37" s="374"/>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="B39" s="210" t="s">
+        <v>493</v>
+      </c>
+      <c r="C39" s="108">
+        <f>scaling_factor</f>
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
+      <c r="B40" s="367" t="s">
+        <v>494</v>
+      </c>
+      <c r="C40" s="367"/>
+      <c r="D40" s="367"/>
+      <c r="E40" s="367"/>
+      <c r="F40" s="367"/>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="B41" s="47" t="s">
+        <v>228</v>
+      </c>
+      <c r="C41" s="349">
+        <f>Normalized_FCF!C8</f>
+        <v>1880349.4511684938</v>
+      </c>
+      <c r="D41" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
+      <c r="B42" s="47"/>
+      <c r="C42" s="76"/>
+    </row>
+    <row r="43" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B43" s="367" t="s">
+        <v>495</v>
+      </c>
+      <c r="C43" s="367"/>
+      <c r="D43" s="367"/>
+      <c r="E43" s="367"/>
+      <c r="F43" s="367"/>
+    </row>
+    <row r="44" spans="1:6">
+      <c r="B44" s="47" t="s">
+        <v>230</v>
+      </c>
+      <c r="C44" s="349">
+        <f>Normalized_FCF!C9</f>
+        <v>0</v>
+      </c>
+      <c r="D44" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6">
+      <c r="B45" s="52" t="s">
+        <v>231</v>
+      </c>
+      <c r="C45" s="349">
+        <f>Normalized_FCF!C10</f>
+        <v>0</v>
+      </c>
+      <c r="D45" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6">
+      <c r="B47" s="367" t="s">
+        <v>496</v>
+      </c>
+      <c r="C47" s="367"/>
+      <c r="D47" s="367"/>
+      <c r="E47" s="367"/>
+      <c r="F47" s="367"/>
+    </row>
+    <row r="48" spans="1:6">
+      <c r="B48" s="47" t="s">
+        <v>233</v>
+      </c>
+      <c r="C48" s="349">
+        <f>Normalized_FCF!C11</f>
+        <v>0</v>
+      </c>
+      <c r="D48" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="50" spans="2:6">
+      <c r="B50" s="367" t="s">
+        <v>497</v>
+      </c>
+      <c r="C50" s="367"/>
+      <c r="D50" s="367"/>
+      <c r="E50" s="367"/>
+      <c r="F50" s="367"/>
+    </row>
+    <row r="51" spans="2:6">
+      <c r="B51" s="47" t="s">
+        <v>331</v>
+      </c>
+      <c r="C51" s="350">
+        <f>Normalized_FCF!C48</f>
+        <v>20769.589399157529</v>
+      </c>
+      <c r="D51" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>HKD</v>
+      </c>
+      <c r="E51" s="286"/>
+      <c r="F51" s="286"/>
+    </row>
+    <row r="52" spans="2:6">
+      <c r="B52" s="47" t="s">
+        <v>332</v>
+      </c>
+      <c r="C52" s="350">
+        <f>Normalized_FCF!C47</f>
+        <v>-1746</v>
+      </c>
+      <c r="D52" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>HKD</v>
+      </c>
+      <c r="E52" s="286"/>
+      <c r="F52" s="286"/>
+    </row>
+    <row r="53" spans="2:6">
+      <c r="B53" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="C53" s="349">
+        <f>Normalized_FCF!C12</f>
+        <v>19023.589399157529</v>
+      </c>
+      <c r="D53" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="55" spans="2:6">
+      <c r="B55" s="1" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="56" spans="2:6">
+      <c r="B56" s="47" t="s">
+        <v>261</v>
+      </c>
+      <c r="C56" s="349">
+        <f>Normalized_FCF!C15</f>
+        <v>-332702.30828345218</v>
+      </c>
+      <c r="D56" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="58" spans="2:6">
+      <c r="B58" s="367" t="s">
+        <v>237</v>
+      </c>
+      <c r="C58" s="367"/>
+      <c r="D58" s="367"/>
+      <c r="E58" s="367"/>
+      <c r="F58" s="367"/>
+    </row>
+    <row r="59" spans="2:6">
+      <c r="B59" s="47" t="s">
+        <v>235</v>
+      </c>
+      <c r="C59" s="349">
+        <f>Normalized_FCF!C14</f>
+        <v>-474843.26014191285</v>
+      </c>
+      <c r="D59" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="61" spans="2:6">
+      <c r="B61" s="367" t="s">
+        <v>499</v>
+      </c>
+      <c r="C61" s="373"/>
+      <c r="D61" s="373"/>
+      <c r="E61" s="373"/>
+      <c r="F61" s="373"/>
+    </row>
+    <row r="62" spans="2:6">
+      <c r="B62" s="47" t="s">
+        <v>238</v>
+      </c>
+      <c r="C62" s="349">
+        <f>Normalized_FCF!C17</f>
+        <v>0</v>
+      </c>
+      <c r="D62" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="64" spans="2:6">
+      <c r="B64" s="371" t="s">
+        <v>500</v>
+      </c>
+      <c r="C64" s="371"/>
+      <c r="D64" s="371"/>
+      <c r="E64" s="371"/>
+      <c r="F64" s="371"/>
+    </row>
+    <row r="65" spans="1:6">
+      <c r="B65" s="371" t="s">
+        <v>501</v>
+      </c>
+      <c r="C65" s="371"/>
+      <c r="D65" s="371"/>
+      <c r="E65" s="371"/>
+      <c r="F65" s="371"/>
+    </row>
+    <row r="67" spans="1:6">
+      <c r="B67" s="47" t="s">
+        <v>502</v>
+      </c>
+      <c r="C67" s="349">
+        <f>Normalized_FCF!G19</f>
+        <v>1274085.3895235579</v>
+      </c>
+      <c r="D67" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6">
+      <c r="B68" s="47" t="s">
+        <v>244</v>
+      </c>
+      <c r="C68" s="349">
+        <f>Normalized_FCF!C19</f>
+        <v>1091827.4721422864</v>
+      </c>
+      <c r="D68" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6">
+      <c r="B69" s="227" t="s">
+        <v>371</v>
+      </c>
+      <c r="C69" s="92">
+        <f>Normalized_FCF!C126</f>
+        <v>8.1854774938882657E-2</v>
+      </c>
+      <c r="F69" s="314"/>
+    </row>
+    <row r="70" spans="1:6">
+      <c r="B70" s="227" t="s">
+        <v>434</v>
+      </c>
+      <c r="C70" s="92">
+        <f>Normalized_FCF!C94</f>
+        <v>0.10305343511450382</v>
+      </c>
+      <c r="E70" s="47" t="s">
+        <v>503</v>
+      </c>
+      <c r="F70" s="315">
+        <f>Normalized_FCF!C92</f>
+        <v>1.3988654526188369</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6">
+      <c r="B72" s="210" t="s">
+        <v>513</v>
+      </c>
+      <c r="C72" s="323" t="s">
+        <v>429</v>
+      </c>
+      <c r="D72" s="323" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6">
+      <c r="B73" s="47" t="s">
+        <v>428</v>
+      </c>
+      <c r="C73" s="92">
+        <f>Normalized_FCF!C121</f>
+        <v>0.10048924474005361</v>
+      </c>
+      <c r="D73" s="92">
+        <f>Normalized_FCF!G121</f>
+        <v>0.12199804433766272</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6">
+      <c r="B74" s="259" t="str">
+        <f>Normalized_FCF!B118</f>
+        <v>Pre-tax Profit/Sales</v>
+      </c>
+      <c r="C74" s="322">
+        <f>Normalized_FCF!C118</f>
+        <v>0.42143224397986156</v>
+      </c>
+      <c r="D74" s="322">
+        <f>Normalized_FCF!G118</f>
+        <v>0.45598504835348186</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6">
+      <c r="B75" s="259" t="str">
+        <f>Normalized_FCF!B119</f>
+        <v>Sales/Total Assets</v>
+      </c>
+      <c r="C75" s="324">
+        <f>Normalized_FCF!C119</f>
+        <v>0.19639123104483397</v>
+      </c>
+      <c r="D75" s="324">
+        <f>Normalized_FCF!G119</f>
+        <v>0.22035988512352028</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6">
+      <c r="B76" s="259" t="str">
+        <f>Normalized_FCF!B120</f>
+        <v>Total Assets/Equity</v>
+      </c>
+      <c r="C76" s="324">
+        <f>Normalized_FCF!C120</f>
+        <v>1.2141426890285656</v>
+      </c>
+      <c r="D76" s="324">
+        <f>Normalized_FCF!G120</f>
+        <v>1.2141426890285656</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" ht="13.9">
+      <c r="A78" s="222" t="s">
+        <v>505</v>
+      </c>
+      <c r="B78" s="36"/>
+      <c r="C78" s="36"/>
+      <c r="D78" s="36"/>
+      <c r="E78" s="36"/>
+      <c r="F78" s="36"/>
+    </row>
+    <row r="79" spans="1:6">
+      <c r="A79" s="209"/>
+    </row>
+    <row r="80" spans="1:6">
+      <c r="A80" s="17"/>
+      <c r="B80" s="371" t="s">
+        <v>506</v>
+      </c>
+      <c r="C80" s="371"/>
+      <c r="D80" s="371"/>
+      <c r="E80" s="371"/>
+      <c r="F80" s="371"/>
+    </row>
+    <row r="81" spans="1:6">
+      <c r="B81" s="374" t="s">
+        <v>248</v>
+      </c>
+      <c r="C81" s="374"/>
+      <c r="D81" s="374"/>
+      <c r="E81" s="374"/>
+      <c r="F81" s="374"/>
+    </row>
+    <row r="83" spans="1:6">
+      <c r="B83" s="210" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6">
+      <c r="B84" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="C84" s="92">
+        <f>F31</f>
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6">
+      <c r="B85" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="C85" s="92">
+        <f>IF(C23="Y",1%,0)+IF(C24="Y",1%,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6">
+      <c r="B86" s="80" t="s">
+        <v>243</v>
+      </c>
+      <c r="C86" s="236">
+        <f>F31+C85</f>
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6">
+      <c r="C87" s="121"/>
+    </row>
+    <row r="88" spans="1:6">
+      <c r="B88" s="293" t="s">
+        <v>512</v>
+      </c>
+      <c r="C88" s="121"/>
+    </row>
+    <row r="89" spans="1:6">
+      <c r="B89" s="371" t="s">
+        <v>507</v>
+      </c>
+      <c r="C89" s="371"/>
+      <c r="D89" s="371"/>
+      <c r="E89" s="371"/>
+      <c r="F89" s="371"/>
+    </row>
+    <row r="90" spans="1:6">
+      <c r="B90" s="371" t="s">
+        <v>508</v>
+      </c>
+      <c r="C90" s="371"/>
+      <c r="D90" s="371"/>
+      <c r="E90" s="371"/>
+      <c r="F90" s="371"/>
+    </row>
+    <row r="92" spans="1:6">
+      <c r="B92" s="47" t="s">
+        <v>247</v>
+      </c>
+      <c r="C92" s="236">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6">
+      <c r="B93" s="47" t="s">
+        <v>275</v>
+      </c>
+      <c r="C93" s="223">
+        <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <v>2.8594601378649682</v>
+      </c>
+      <c r="D93" s="1" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" ht="13.9">
+      <c r="A95" s="222" t="s">
+        <v>509</v>
+      </c>
+      <c r="B95" s="36"/>
+      <c r="C95" s="36"/>
+      <c r="D95" s="36"/>
+      <c r="E95" s="36"/>
+      <c r="F95" s="36"/>
+    </row>
+    <row r="96" spans="1:6">
+      <c r="A96" s="209"/>
+    </row>
+    <row r="97" spans="2:6">
+      <c r="B97" s="371" t="s">
+        <v>510</v>
+      </c>
+      <c r="C97" s="371"/>
+      <c r="D97" s="371"/>
+      <c r="E97" s="371"/>
+      <c r="F97" s="371"/>
+    </row>
+    <row r="98" spans="2:6">
+      <c r="B98" s="1" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="100" spans="2:6">
+      <c r="B100" s="210" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="101" spans="2:6">
+      <c r="B101" s="371" t="s">
+        <v>511</v>
+      </c>
+      <c r="C101" s="371"/>
+      <c r="D101" s="371"/>
+      <c r="E101" s="371"/>
+      <c r="F101" s="371"/>
+    </row>
+    <row r="102" spans="2:6">
+      <c r="B102" s="47" t="s">
+        <v>251</v>
+      </c>
+      <c r="C102" s="349">
+        <f>DCF!C7</f>
+        <v>43677</v>
+      </c>
+      <c r="D102" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="103" spans="2:6">
+      <c r="B103" s="47" t="s">
+        <v>276</v>
+      </c>
+      <c r="C103" s="223">
+        <f>C102*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <v>8.5791466803226933E-3</v>
+      </c>
+      <c r="D103" s="1" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="104" spans="2:6">
+      <c r="B104" s="296" t="s">
+        <v>384</v>
+      </c>
+      <c r="C104" s="325">
+        <f>IF(BS!G31/BS!G27&gt;300%,"nm",BS!G31/BS!G27)</f>
+        <v>2.3107986944995245E-3</v>
+      </c>
+    </row>
+    <row r="105" spans="2:6">
+      <c r="B105" s="296" t="s">
+        <v>386</v>
+      </c>
+      <c r="C105" s="326">
+        <f>IF(BS!C50&gt;30,"nm",BS!C50)</f>
+        <v>2.3228129203780753E-2</v>
+      </c>
+    </row>
+    <row r="107" spans="2:6">
+      <c r="B107" s="1" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="108" spans="2:6">
+      <c r="B108" s="47" t="s">
+        <v>260</v>
+      </c>
+      <c r="C108" s="349">
+        <f>BS!C66</f>
+        <v>10118429</v>
+      </c>
+      <c r="D108" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="109" spans="2:6">
+      <c r="B109" s="47" t="s">
+        <v>262</v>
+      </c>
+      <c r="C109" s="349">
+        <f>DCF!C8</f>
+        <v>8041470.060084247</v>
+      </c>
+      <c r="D109" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="110" spans="2:6">
+      <c r="B110" s="47" t="s">
+        <v>277</v>
+      </c>
+      <c r="C110" s="223">
+        <f>C109*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <v>1.5795258642050989</v>
+      </c>
+      <c r="D110" s="1" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="112" spans="2:6">
+      <c r="B112" s="1" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6">
+      <c r="B113" s="47" t="s">
+        <v>253</v>
+      </c>
+      <c r="C113" s="349">
+        <f>DCF!C9</f>
+        <v>263512.2</v>
+      </c>
+      <c r="D113" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6">
+      <c r="B114" s="47" t="s">
+        <v>278</v>
+      </c>
+      <c r="C114" s="223">
+        <f>C113*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <v>5.1759732029547124E-2</v>
+      </c>
+      <c r="D114" s="1" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6">
+      <c r="B116" s="371" t="s">
+        <v>516</v>
+      </c>
+      <c r="C116" s="371"/>
+      <c r="D116" s="371"/>
+      <c r="E116" s="371"/>
+      <c r="F116" s="371"/>
+    </row>
+    <row r="118" spans="1:6">
+      <c r="B118" s="47" t="s">
+        <v>517</v>
+      </c>
+      <c r="C118" s="223">
+        <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
+        <v>4.4821665874192913</v>
+      </c>
+      <c r="D118" s="1" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6">
+      <c r="B119" s="296" t="s">
+        <v>550</v>
+      </c>
+      <c r="C119" s="223">
+        <f>BS!D47</f>
+        <v>0.79833937207218564</v>
+      </c>
+      <c r="D119" s="1" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" ht="13.9">
+      <c r="A121" s="222" t="s">
+        <v>518</v>
+      </c>
+      <c r="B121" s="36"/>
+      <c r="C121" s="36"/>
+      <c r="D121" s="36"/>
+      <c r="E121" s="36"/>
+      <c r="F121" s="36"/>
+    </row>
+    <row r="123" spans="1:6">
+      <c r="B123" s="367" t="s">
+        <v>519</v>
+      </c>
+      <c r="C123" s="367"/>
+      <c r="D123" s="367"/>
+      <c r="E123" s="367"/>
+      <c r="F123" s="367"/>
+    </row>
+    <row r="125" spans="1:6" ht="12.4">
+      <c r="B125" s="233" t="s">
+        <v>520</v>
+      </c>
+      <c r="C125" s="233" t="s">
+        <v>521</v>
+      </c>
+      <c r="D125" s="233" t="s">
+        <v>108</v>
+      </c>
+      <c r="E125" s="233" t="s">
+        <v>522</v>
+      </c>
+      <c r="F125" s="233" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6">
+      <c r="B126" s="228" t="str">
+        <f>DCF!B74</f>
+        <v>Snowball Scenario</v>
+      </c>
+      <c r="C126" s="229">
+        <f>DCF!C74</f>
+        <v>0.04</v>
+      </c>
+      <c r="D126" s="230">
+        <f>DCF!D74</f>
+        <v>10</v>
+      </c>
+      <c r="E126" s="231" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E74,DDM!E69),2)&amp;" "&amp;Market_currency</f>
+        <v>4.86 HKD</v>
+      </c>
+      <c r="F126" s="232">
+        <f>DCF!F74</f>
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6">
+      <c r="B127" s="218" t="str">
+        <f>DCF!B75</f>
+        <v>Optimistic</v>
+      </c>
+      <c r="C127" s="219">
+        <f>DCF!C75</f>
+        <v>0.02</v>
+      </c>
+      <c r="D127" s="220">
+        <f>DCF!D75</f>
+        <v>5</v>
+      </c>
+      <c r="E127" s="231" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E75,DDM!E70),2)&amp;" "&amp;Market_currency</f>
+        <v>4.57 HKD</v>
+      </c>
+      <c r="F127" s="221">
+        <f>DCF!F75</f>
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6">
+      <c r="B128" s="218" t="str">
+        <f>DCF!B76</f>
+        <v>Base</v>
+      </c>
+      <c r="C128" s="219">
+        <f>DCF!C76</f>
+        <v>0</v>
+      </c>
+      <c r="D128" s="220">
+        <f>DCF!D76</f>
+        <v>5</v>
+      </c>
+      <c r="E128" s="231" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E76,DDM!E71),2)&amp;" "&amp;Market_currency</f>
+        <v>4.48 HKD</v>
+      </c>
+      <c r="F128" s="221">
+        <f>DCF!F76</f>
+        <v>0.53999999999999992</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6">
+      <c r="B129" s="218" t="str">
+        <f>DCF!B77</f>
+        <v>Pessimistic</v>
+      </c>
+      <c r="C129" s="219">
+        <f>DCF!C77</f>
+        <v>-0.02</v>
+      </c>
+      <c r="D129" s="220">
+        <f>DCF!D77</f>
+        <v>5</v>
+      </c>
+      <c r="E129" s="231" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E77,DDM!E72),2)&amp;" "&amp;Market_currency</f>
+        <v>4.39 HKD</v>
+      </c>
+      <c r="F129" s="221">
+        <f>DCF!F77</f>
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6">
+      <c r="B130" s="218" t="str">
+        <f>DCF!B78</f>
+        <v>Devil's advocate</v>
+      </c>
+      <c r="C130" s="219">
+        <f>DCF!C78</f>
+        <v>-0.04</v>
+      </c>
+      <c r="D130" s="220">
+        <f>DCF!D78</f>
+        <v>10</v>
+      </c>
+      <c r="E130" s="231" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E78,DDM!E73),2)&amp;" "&amp;Market_currency</f>
+        <v>4.17 HKD</v>
+      </c>
+      <c r="F130" s="221">
+        <f>DCF!F78</f>
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6">
+      <c r="B132" s="211" t="s">
+        <v>254</v>
+      </c>
+      <c r="C132" s="217">
+        <f>Scenarios!C60</f>
+        <v>4.4858408799140586</v>
+      </c>
+      <c r="D132" s="212" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6">
+      <c r="B134" s="369" t="s">
+        <v>524</v>
+      </c>
+      <c r="C134" s="369"/>
+      <c r="D134" s="369"/>
+      <c r="E134" s="369"/>
+      <c r="F134" s="369"/>
+    </row>
+    <row r="136" spans="1:6" ht="13.9">
+      <c r="A136" s="222" t="s">
+        <v>525</v>
+      </c>
+      <c r="B136" s="36"/>
+      <c r="C136" s="36"/>
+      <c r="D136" s="36"/>
+      <c r="E136" s="36"/>
+      <c r="F136" s="36"/>
+    </row>
+    <row r="138" spans="1:6">
+      <c r="B138" s="370" t="s">
+        <v>526</v>
+      </c>
+      <c r="C138" s="370"/>
+      <c r="D138" s="370"/>
+      <c r="E138" s="370"/>
+      <c r="F138" s="370"/>
+    </row>
+    <row r="139" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B139" s="371" t="s">
+        <v>527</v>
+      </c>
+      <c r="C139" s="371"/>
+      <c r="D139" s="371"/>
+      <c r="E139" s="371"/>
+      <c r="F139" s="371"/>
+    </row>
+    <row r="140" spans="1:6">
+      <c r="B140" s="210" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6">
+      <c r="B141" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="C141" s="225">
+        <f>F28</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6">
+      <c r="B142" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="C142" s="224">
+        <f>F29</f>
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6">
+      <c r="B143" s="212" t="s">
+        <v>530</v>
+      </c>
+      <c r="C143" s="213">
+        <f>Scenarios!C77</f>
+        <v>0.27</v>
+      </c>
+      <c r="D143" s="212" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="145" spans="2:4">
+      <c r="B145" s="210" t="s">
+        <v>531</v>
+      </c>
+      <c r="C145" s="241" t="str">
+        <f>C11</f>
+        <v>0639.HK</v>
+      </c>
+      <c r="D145" s="241" t="str">
+        <f>IF(D11="","",D11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="146" spans="2:4">
+      <c r="B146" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="C146" s="297">
+        <f>F29</f>
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="147" spans="2:4">
+      <c r="B147" s="212" t="str">
+        <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
+        <v>PV(3 yrs of Dividends)</v>
+      </c>
+      <c r="C147" s="216">
+        <f>Scenarios!C81</f>
+        <v>0.45788751714677645</v>
+      </c>
+    </row>
+    <row r="148" spans="2:4">
+      <c r="B148" s="212" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
+        <v>+ PV(Equity Value realized at year 3)</v>
+      </c>
+      <c r="C148" s="216">
+        <f>Scenarios!C82</f>
+        <v>1.823234620703778</v>
+      </c>
+    </row>
+    <row r="149" spans="2:4">
+      <c r="B149" s="80" t="s">
+        <v>256</v>
+      </c>
+      <c r="C149" s="215">
+        <f>Scenarios!C83</f>
+        <v>2.2811221378505544</v>
+      </c>
+      <c r="D149" s="300" t="str">
+        <f>IF($D$11="","",C149*$E$25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="150" spans="2:4">
+      <c r="B150" s="259" t="s">
+        <v>532</v>
+      </c>
+      <c r="C150" s="298" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+      <c r="D150" s="298" t="str">
+        <f>IF($D$11="","",D$13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="151" spans="2:4">
+      <c r="B151" s="214" t="s">
+        <v>533</v>
+      </c>
+      <c r="C151" s="92">
+        <f>Scenarios!F83</f>
+        <v>0.49148393825902781</v>
+      </c>
+    </row>
+    <row r="153" spans="2:4">
+      <c r="B153" s="210" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="154" spans="2:4">
+      <c r="B154" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="C154" s="297">
+        <f>Scenarios!C90</f>
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="155" spans="2:4">
+      <c r="B155" s="212" t="str">
+        <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
+        <v>PV(3 yrs of Dividends)</v>
+      </c>
+      <c r="C155" s="216">
+        <f>Scenarios!C91</f>
+        <v>0.52704000000000006</v>
+      </c>
+    </row>
+    <row r="156" spans="2:4">
+      <c r="B156" s="212" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
+        <v>+ PV(Equity Value realized at year 3)</v>
+      </c>
+      <c r="C156" s="216">
+        <f>Scenarios!C92</f>
+        <v>2.2967505305159981</v>
+      </c>
+    </row>
+    <row r="157" spans="2:4">
+      <c r="B157" s="80" t="s">
+        <v>256</v>
+      </c>
+      <c r="C157" s="215">
+        <f>Scenarios!C93</f>
+        <v>2.823790530515998</v>
+      </c>
+      <c r="D157" s="300" t="str">
+        <f>IF($D$11="","",C157*$E$25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="158" spans="2:4">
+      <c r="B158" s="259" t="s">
+        <v>532</v>
+      </c>
+      <c r="C158" s="298" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+      <c r="D158" s="298" t="str">
+        <f>IF($D$11="","",D$13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="159" spans="2:4">
+      <c r="B159" s="214" t="s">
+        <v>533</v>
+      </c>
+      <c r="C159" s="92">
+        <f>Scenarios!F93</f>
+        <v>0.37051032212045443</v>
+      </c>
+    </row>
+    <row r="161" spans="2:4">
+      <c r="B161" s="210" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="162" spans="2:4">
+      <c r="B162" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="C162" s="92">
+        <f>Scenarios!C96</f>
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="163" spans="2:4">
+      <c r="B163" s="212" t="str">
+        <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
+        <v>PV(3 yrs of Dividends)</v>
+      </c>
+      <c r="C163" s="216">
+        <f>Scenarios!C97</f>
+        <v>0.70214194976542921</v>
+      </c>
+    </row>
+    <row r="164" spans="2:4">
+      <c r="B164" s="212" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
+        <v>+ PV(Equity Value realized at year 3)</v>
+      </c>
+      <c r="C164" s="216">
+        <f>Scenarios!C98</f>
+        <v>3.6109250294250792</v>
+      </c>
+    </row>
+    <row r="165" spans="2:4">
+      <c r="B165" s="80" t="s">
+        <v>382</v>
+      </c>
+      <c r="C165" s="215">
+        <f>Scenarios!C99</f>
+        <v>4.3130669791905083</v>
+      </c>
+      <c r="D165" s="300" t="str">
+        <f>IF($D$11="","",C165*$E$25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="166" spans="2:4">
+      <c r="B166" s="259" t="s">
+        <v>532</v>
+      </c>
+      <c r="C166" s="298" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+      <c r="D166" s="298" t="str">
+        <f>IF($D$11="","",D$13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="167" spans="2:4">
+      <c r="B167" s="214" t="s">
+        <v>533</v>
+      </c>
+      <c r="C167" s="92">
+        <f>Scenarios!F99</f>
+        <v>3.8515387716307137E-2</v>
+      </c>
+    </row>
+    <row r="169" spans="2:4">
+      <c r="B169" s="210" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="170" spans="2:4">
+      <c r="B170" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="C170" s="92">
+        <f>F32</f>
+        <v>0.1174</v>
+      </c>
+    </row>
+    <row r="171" spans="2:4">
+      <c r="B171" s="212" t="str">
+        <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
+        <v>PV(3 yrs of Dividends)</v>
+      </c>
+      <c r="C171" s="216">
+        <f>Scenarios!C103</f>
+        <v>0.65140284400343529</v>
+      </c>
+    </row>
+    <row r="172" spans="2:4">
+      <c r="B172" s="212" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
+        <v>+ PV(Equity Value realized at year 3)</v>
+      </c>
+      <c r="C172" s="216">
+        <f>Scenarios!C104</f>
+        <v>3.2152730720890683</v>
+      </c>
+    </row>
+    <row r="173" spans="2:4">
+      <c r="B173" s="80" t="s">
+        <v>382</v>
+      </c>
+      <c r="C173" s="215">
+        <f>Scenarios!C105</f>
+        <v>3.8666759160925035</v>
+      </c>
+      <c r="D173" s="300" t="str">
+        <f>IF($D$11="","",C173*$E$25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="174" spans="2:4">
+      <c r="B174" s="259" t="s">
+        <v>532</v>
+      </c>
+      <c r="C174" s="298" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+      <c r="D174" s="298" t="str">
+        <f>IF($D$11="","",D$13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="175" spans="2:4">
+      <c r="B175" s="214" t="s">
+        <v>533</v>
+      </c>
+      <c r="C175" s="92">
+        <f>Scenarios!F105</f>
+        <v>0.13842067503200794</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6" ht="13.9">
+      <c r="A177" s="222" t="s">
+        <v>357</v>
+      </c>
+      <c r="B177" s="36"/>
+      <c r="C177" s="36"/>
+      <c r="D177" s="36"/>
+      <c r="E177" s="36"/>
+      <c r="F177" s="36"/>
+    </row>
+    <row r="179" spans="1:6">
+      <c r="B179" s="372" t="s">
+        <v>534</v>
+      </c>
+      <c r="C179" s="371"/>
+      <c r="D179" s="371"/>
+      <c r="E179" s="371"/>
+      <c r="F179" s="371"/>
+    </row>
+    <row r="181" spans="1:6">
+      <c r="B181" s="210" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6">
+      <c r="B182" s="373" t="s">
+        <v>536</v>
+      </c>
+      <c r="C182" s="373"/>
+      <c r="D182" s="373"/>
+      <c r="E182" s="373"/>
+      <c r="F182" s="373"/>
+    </row>
+    <row r="183" spans="1:6">
+      <c r="B183" s="214" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6">
+      <c r="B184" s="214" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6">
+      <c r="B185" s="214" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6">
+      <c r="B187" s="1" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B188" s="367" t="s">
+        <v>541</v>
+      </c>
+      <c r="C188" s="367"/>
+      <c r="D188" s="367"/>
+      <c r="E188" s="367"/>
+      <c r="F188" s="367"/>
+    </row>
+    <row r="190" spans="1:6">
+      <c r="B190" s="1" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6">
+      <c r="B191" s="368" t="s">
+        <v>543</v>
+      </c>
+      <c r="C191" s="368"/>
+      <c r="D191" s="368"/>
+      <c r="E191" s="368"/>
+      <c r="F191" s="368"/>
+    </row>
+    <row r="192" spans="1:6">
+      <c r="B192" s="368" t="s">
+        <v>544</v>
+      </c>
+      <c r="C192" s="368"/>
+      <c r="D192" s="368"/>
+      <c r="E192" s="368"/>
+      <c r="F192" s="368"/>
+    </row>
+    <row r="194" spans="2:2">
+      <c r="B194" s="1" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="195" spans="2:2">
+      <c r="B195" s="214" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="196" spans="2:2">
+      <c r="B196" s="214" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="197" spans="2:2">
+      <c r="B197" s="214" t="s">
+        <v>548</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="27">
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B116:F116"/>
+    <mergeCell ref="B50:F50"/>
+    <mergeCell ref="B58:F58"/>
+    <mergeCell ref="B61:F61"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B65:F65"/>
+    <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B90:F90"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B138:F138"/>
+    <mergeCell ref="B139:F139"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B182:F182"/>
+  </mergeCells>
+  <dataValidations count="5">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">
+      <formula1>"INT,CN"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E21 E25" xr:uid="{0BE1D34E-D50B-41CB-99F3-E9F8694C38CA}">
+      <formula1>"DCF,DDM"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="C25:D25" xr:uid="{4F076B80-6574-480B-B48C-99BFFF6B4B13}">
+      <formula1>"HKD,USD,CNY,EUR"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C23:C24" xr:uid="{B605A743-B0FC-4D89-AD54-945707F01FA1}">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1" xr:uid="{CF966412-2762-45A3-9589-2A9D9DD6B905}">
+      <formula1>"Y, N"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="85" fitToHeight="0" orientation="portrait" verticalDpi="300" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E03CB28-CABF-4F73-9474-1674E7E6FB22}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -4344,24 +6921,24 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="B1" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C1" s="44">
         <v>45807</v>
       </c>
       <c r="D1" s="316" t="s">
-        <v>446</v>
+        <v>426</v>
       </c>
       <c r="E1" s="292" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="F1" s="254" t="s">
-        <v>457</v>
+        <v>551</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
       <c r="A2" s="222" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="B2" s="36"/>
       <c r="C2" s="36"/>
@@ -4375,7 +6952,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="B4" s="45" t="s">
-        <v>411</v>
+        <v>394</v>
       </c>
       <c r="C4" s="46"/>
       <c r="D4" s="5"/>
@@ -4384,15 +6961,15 @@
     </row>
     <row r="5" spans="1:10" ht="12.4">
       <c r="B5" s="4" t="s">
-        <v>312</v>
+        <v>458</v>
       </c>
       <c r="C5" s="294" t="s">
-        <v>458</v>
+        <v>552</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="B6" s="4" t="s">
-        <v>0</v>
+        <v>459</v>
       </c>
       <c r="C6" s="51">
         <v>5091065770</v>
@@ -4401,7 +6978,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="B7" s="2" t="s">
-        <v>306</v>
+        <v>460</v>
       </c>
       <c r="C7" s="250">
         <v>6</v>
@@ -4411,7 +6988,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="B8" s="1" t="s">
-        <v>267</v>
+        <v>461</v>
       </c>
       <c r="C8" s="33">
         <f>EOMONTH(EDATE(BS!C1,C7+2),0)</f>
@@ -4424,26 +7001,26 @@
     </row>
     <row r="10" spans="1:10">
       <c r="B10" s="45" t="s">
-        <v>414</v>
+        <v>396</v>
       </c>
       <c r="C10" s="46"/>
       <c r="E10" s="34"/>
     </row>
     <row r="11" spans="1:10">
       <c r="B11" s="1" t="s">
-        <v>413</v>
+        <v>462</v>
       </c>
       <c r="C11" s="49" t="s">
-        <v>459</v>
+        <v>553</v>
       </c>
       <c r="D11" s="49" t="s">
-        <v>460</v>
+        <v>554</v>
       </c>
       <c r="E11" s="34"/>
     </row>
     <row r="12" spans="1:10">
       <c r="B12" s="4" t="s">
-        <v>94</v>
+        <v>463</v>
       </c>
       <c r="C12" s="50">
         <v>2.62</v>
@@ -4453,17 +7030,17 @@
     </row>
     <row r="13" spans="1:10">
       <c r="B13" s="1" t="s">
-        <v>412</v>
+        <v>464</v>
       </c>
       <c r="C13" s="48" t="s">
-        <v>393</v>
+        <v>377</v>
       </c>
       <c r="D13" s="48"/>
       <c r="E13" s="5"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="4" t="s">
-        <v>416</v>
+        <v>465</v>
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
@@ -4477,7 +7054,7 @@
     </row>
     <row r="15" spans="1:10">
       <c r="B15" s="4" t="s">
-        <v>415</v>
+        <v>466</v>
       </c>
       <c r="C15" s="32" t="str">
         <f>IF(C25=C13,C13,C25&amp;"/"&amp;C13)</f>
@@ -4491,7 +7068,7 @@
     </row>
     <row r="16" spans="1:10">
       <c r="B16" s="4" t="s">
-        <v>1</v>
+        <v>467</v>
       </c>
       <c r="C16" s="50">
         <v>1</v>
@@ -4504,71 +7081,71 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="361" t="s">
-        <v>356</v>
-      </c>
-      <c r="C18" s="361"/>
-      <c r="D18" s="361"/>
-      <c r="E18" s="361"/>
-      <c r="F18" s="361"/>
+      <c r="B18" s="371" t="s">
+        <v>468</v>
+      </c>
+      <c r="C18" s="371"/>
+      <c r="D18" s="371"/>
+      <c r="E18" s="371"/>
+      <c r="F18" s="371"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="C20" s="46"/>
       <c r="D20" s="5"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="2" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="C21" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
         <v xml:space="preserve">Low Growth </v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>435</v>
+        <v>415</v>
       </c>
       <c r="E21" s="308" t="s">
-        <v>463</v>
+        <v>557</v>
       </c>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C22" s="48" t="s">
-        <v>461</v>
+        <v>555</v>
       </c>
       <c r="D22" s="1" t="str">
-        <f>IF(valuation_method="DDM","DDM Terminal Value","")</f>
+        <f>IF(valuation_method="DDM","Terminal Value Discount Rate","")</f>
         <v/>
       </c>
       <c r="E22" s="313"/>
     </row>
     <row r="23" spans="2:6">
       <c r="B23" s="1" t="s">
-        <v>430</v>
+        <v>410</v>
       </c>
       <c r="C23" s="262" t="s">
-        <v>462</v>
+        <v>556</v>
       </c>
     </row>
     <row r="24" spans="2:6">
       <c r="B24" s="1" t="s">
-        <v>431</v>
+        <v>411</v>
       </c>
       <c r="C24" s="262" t="s">
-        <v>462</v>
+        <v>556</v>
       </c>
     </row>
     <row r="25" spans="2:6">
       <c r="B25" s="4" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="C25" s="48" t="s">
-        <v>393</v>
+        <v>377</v>
       </c>
       <c r="D25" s="32" t="str">
         <f>IF(D11="","",Market_currency&amp;"/"&amp;D13&amp;":")</f>
@@ -4589,7 +7166,7 @@
         <v>4.4858408799140586</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>396</v>
+        <v>380</v>
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
@@ -4602,7 +7179,7 @@
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="45" t="s">
-        <v>429</v>
+        <v>409</v>
       </c>
       <c r="C28" s="309" t="str">
         <f>C145&amp;" ("&amp;Market_currency&amp;")"</f>
@@ -4613,7 +7190,7 @@
         <v/>
       </c>
       <c r="E28" s="305" t="s">
-        <v>425</v>
+        <v>405</v>
       </c>
       <c r="F28" s="303">
         <v>3</v>
@@ -4621,7 +7198,7 @@
     </row>
     <row r="29" spans="2:6">
       <c r="B29" s="1" t="s">
-        <v>421</v>
+        <v>401</v>
       </c>
       <c r="C29" s="310">
         <f>C149</f>
@@ -4632,7 +7209,7 @@
         <v/>
       </c>
       <c r="E29" s="306" t="s">
-        <v>420</v>
+        <v>400</v>
       </c>
       <c r="F29" s="302">
         <v>0.35</v>
@@ -4640,7 +7217,7 @@
     </row>
     <row r="30" spans="2:6">
       <c r="B30" s="1" t="s">
-        <v>422</v>
+        <v>402</v>
       </c>
       <c r="C30" s="311">
         <f>C157</f>
@@ -4651,7 +7228,7 @@
         <v/>
       </c>
       <c r="E30" s="307" t="s">
-        <v>433</v>
+        <v>413</v>
       </c>
       <c r="F30" s="312">
         <v>0.25</v>
@@ -4659,7 +7236,7 @@
     </row>
     <row r="31" spans="2:6">
       <c r="B31" s="1" t="s">
-        <v>423</v>
+        <v>403</v>
       </c>
       <c r="C31" s="311">
         <f>C165</f>
@@ -4670,7 +7247,7 @@
         <v/>
       </c>
       <c r="E31" s="307" t="s">
-        <v>432</v>
+        <v>412</v>
       </c>
       <c r="F31" s="312">
         <v>7.4999999999999997E-2</v>
@@ -4678,7 +7255,7 @@
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="1" t="s">
-        <v>424</v>
+        <v>404</v>
       </c>
       <c r="C32" s="311">
         <f>C173</f>
@@ -4689,7 +7266,7 @@
         <v/>
       </c>
       <c r="E32" s="307" t="s">
-        <v>434</v>
+        <v>414</v>
       </c>
       <c r="F32" s="312">
         <v>0.1174</v>
@@ -4701,7 +7278,7 @@
     </row>
     <row r="34" spans="1:6" ht="13.9">
       <c r="A34" s="222" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="B34" s="36"/>
       <c r="C34" s="36"/>
@@ -4709,27 +7286,27 @@
       <c r="E34" s="36"/>
       <c r="F34" s="36"/>
     </row>
-    <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="361" t="s">
-        <v>357</v>
-      </c>
-      <c r="C36" s="361"/>
-      <c r="D36" s="361"/>
-      <c r="E36" s="361"/>
-      <c r="F36" s="361"/>
+    <row r="36" spans="1:6">
+      <c r="B36" s="371" t="s">
+        <v>469</v>
+      </c>
+      <c r="C36" s="371"/>
+      <c r="D36" s="371"/>
+      <c r="E36" s="371"/>
+      <c r="F36" s="371"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="363" t="s">
-        <v>336</v>
-      </c>
-      <c r="C37" s="363"/>
-      <c r="D37" s="363"/>
-      <c r="E37" s="363"/>
-      <c r="F37" s="363"/>
+      <c r="B37" s="374" t="s">
+        <v>330</v>
+      </c>
+      <c r="C37" s="374"/>
+      <c r="D37" s="374"/>
+      <c r="E37" s="374"/>
+      <c r="F37" s="374"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="C39" s="108">
         <f>scaling_factor</f>
@@ -4737,17 +7314,17 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="362" t="s">
-        <v>230</v>
-      </c>
-      <c r="C40" s="362"/>
-      <c r="D40" s="362"/>
-      <c r="E40" s="362"/>
-      <c r="F40" s="362"/>
+      <c r="B40" s="367" t="s">
+        <v>227</v>
+      </c>
+      <c r="C40" s="367"/>
+      <c r="D40" s="367"/>
+      <c r="E40" s="367"/>
+      <c r="F40" s="367"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="C41" s="349">
         <f>Normalized_FCF!C8</f>
@@ -4763,17 +7340,17 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="362" t="s">
-        <v>232</v>
-      </c>
-      <c r="C43" s="362"/>
-      <c r="D43" s="362"/>
-      <c r="E43" s="362"/>
-      <c r="F43" s="362"/>
+      <c r="B43" s="367" t="s">
+        <v>229</v>
+      </c>
+      <c r="C43" s="367"/>
+      <c r="D43" s="367"/>
+      <c r="E43" s="367"/>
+      <c r="F43" s="367"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="C44" s="349">
         <f>Normalized_FCF!C9</f>
@@ -4786,7 +7363,7 @@
     </row>
     <row r="45" spans="1:6">
       <c r="B45" s="52" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="C45" s="349">
         <f>Normalized_FCF!C10</f>
@@ -4798,17 +7375,17 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="362" t="s">
-        <v>235</v>
-      </c>
-      <c r="C47" s="362"/>
-      <c r="D47" s="362"/>
-      <c r="E47" s="362"/>
-      <c r="F47" s="362"/>
+      <c r="B47" s="367" t="s">
+        <v>232</v>
+      </c>
+      <c r="C47" s="367"/>
+      <c r="D47" s="367"/>
+      <c r="E47" s="367"/>
+      <c r="F47" s="367"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="C48" s="349">
         <f>Normalized_FCF!C11</f>
@@ -4820,17 +7397,17 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="362" t="s">
-        <v>239</v>
-      </c>
-      <c r="C50" s="362"/>
-      <c r="D50" s="362"/>
-      <c r="E50" s="362"/>
-      <c r="F50" s="362"/>
+      <c r="B50" s="367" t="s">
+        <v>236</v>
+      </c>
+      <c r="C50" s="367"/>
+      <c r="D50" s="367"/>
+      <c r="E50" s="367"/>
+      <c r="F50" s="367"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="C51" s="350">
         <f>Normalized_FCF!C48</f>
@@ -4845,7 +7422,7 @@
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="47" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="C52" s="350">
         <f>Normalized_FCF!C47</f>
@@ -4860,7 +7437,7 @@
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="C53" s="349">
         <f>Normalized_FCF!C12</f>
@@ -4873,12 +7450,12 @@
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="1" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="47" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C56" s="349">
         <f>Normalized_FCF!C15</f>
@@ -4890,17 +7467,17 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="362" t="s">
-        <v>240</v>
-      </c>
-      <c r="C58" s="362"/>
-      <c r="D58" s="362"/>
-      <c r="E58" s="362"/>
-      <c r="F58" s="362"/>
+      <c r="B58" s="367" t="s">
+        <v>237</v>
+      </c>
+      <c r="C58" s="367"/>
+      <c r="D58" s="367"/>
+      <c r="E58" s="367"/>
+      <c r="F58" s="367"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="C59" s="349">
         <f>Normalized_FCF!C14</f>
@@ -4912,17 +7489,17 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="362" t="s">
-        <v>335</v>
-      </c>
-      <c r="C61" s="365"/>
-      <c r="D61" s="365"/>
-      <c r="E61" s="365"/>
-      <c r="F61" s="365"/>
+      <c r="B61" s="367" t="s">
+        <v>329</v>
+      </c>
+      <c r="C61" s="373"/>
+      <c r="D61" s="373"/>
+      <c r="E61" s="373"/>
+      <c r="F61" s="373"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="C62" s="349">
         <f>Normalized_FCF!C17</f>
@@ -4934,26 +7511,26 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="361" t="s">
-        <v>340</v>
-      </c>
-      <c r="C64" s="361"/>
-      <c r="D64" s="361"/>
-      <c r="E64" s="361"/>
-      <c r="F64" s="361"/>
+      <c r="B64" s="371" t="s">
+        <v>334</v>
+      </c>
+      <c r="C64" s="371"/>
+      <c r="D64" s="371"/>
+      <c r="E64" s="371"/>
+      <c r="F64" s="371"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="361" t="s">
-        <v>358</v>
-      </c>
-      <c r="C65" s="361"/>
-      <c r="D65" s="361"/>
-      <c r="E65" s="361"/>
-      <c r="F65" s="361"/>
+      <c r="B65" s="371" t="s">
+        <v>348</v>
+      </c>
+      <c r="C65" s="371"/>
+      <c r="D65" s="371"/>
+      <c r="E65" s="371"/>
+      <c r="F65" s="371"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="C67" s="349">
         <f>Normalized_FCF!G19</f>
@@ -4966,7 +7543,7 @@
     </row>
     <row r="68" spans="1:6">
       <c r="B68" s="47" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="C68" s="349">
         <f>Normalized_FCF!C19</f>
@@ -4979,7 +7556,7 @@
     </row>
     <row r="69" spans="1:6">
       <c r="B69" s="227" t="s">
-        <v>387</v>
+        <v>371</v>
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
@@ -4989,14 +7566,14 @@
     </row>
     <row r="70" spans="1:6">
       <c r="B70" s="227" t="s">
-        <v>454</v>
+        <v>434</v>
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
         <v>0.10305343511450382</v>
       </c>
       <c r="E70" s="47" t="s">
-        <v>444</v>
+        <v>424</v>
       </c>
       <c r="F70" s="315">
         <f>Normalized_FCF!C92</f>
@@ -5005,18 +7582,18 @@
     </row>
     <row r="72" spans="1:6">
       <c r="B72" s="210" t="s">
-        <v>447</v>
+        <v>427</v>
       </c>
       <c r="C72" s="323" t="s">
-        <v>449</v>
+        <v>429</v>
       </c>
       <c r="D72" s="323" t="s">
-        <v>450</v>
+        <v>430</v>
       </c>
     </row>
     <row r="73" spans="1:6">
       <c r="B73" s="47" t="s">
-        <v>448</v>
+        <v>428</v>
       </c>
       <c r="C73" s="92">
         <f>Normalized_FCF!C121</f>
@@ -5071,7 +7648,7 @@
     </row>
     <row r="78" spans="1:6" ht="13.9">
       <c r="A78" s="222" t="s">
-        <v>352</v>
+        <v>470</v>
       </c>
       <c r="B78" s="36"/>
       <c r="C78" s="36"/>
@@ -5082,33 +7659,33 @@
     <row r="79" spans="1:6">
       <c r="A79" s="209"/>
     </row>
-    <row r="80" spans="1:6" ht="24.6" customHeight="1">
+    <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="361" t="s">
-        <v>359</v>
-      </c>
-      <c r="C80" s="361"/>
-      <c r="D80" s="361"/>
-      <c r="E80" s="361"/>
-      <c r="F80" s="361"/>
+      <c r="B80" s="371" t="s">
+        <v>471</v>
+      </c>
+      <c r="C80" s="371"/>
+      <c r="D80" s="371"/>
+      <c r="E80" s="371"/>
+      <c r="F80" s="371"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="363" t="s">
-        <v>251</v>
-      </c>
-      <c r="C81" s="363"/>
-      <c r="D81" s="363"/>
-      <c r="E81" s="363"/>
-      <c r="F81" s="363"/>
+      <c r="B81" s="374" t="s">
+        <v>248</v>
+      </c>
+      <c r="C81" s="374"/>
+      <c r="D81" s="374"/>
+      <c r="E81" s="374"/>
+      <c r="F81" s="374"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
     </row>
     <row r="84" spans="1:6">
       <c r="B84" s="1" t="s">
-        <v>427</v>
+        <v>407</v>
       </c>
       <c r="C84" s="92">
         <f>F31</f>
@@ -5117,7 +7694,7 @@
     </row>
     <row r="85" spans="1:6">
       <c r="B85" s="1" t="s">
-        <v>426</v>
+        <v>406</v>
       </c>
       <c r="C85" s="92">
         <f>IF(C23="Y",1%,0)+IF(C24="Y",1%,0)</f>
@@ -5126,7 +7703,7 @@
     </row>
     <row r="86" spans="1:6">
       <c r="B86" s="80" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="C86" s="236">
         <f>F31+C85</f>
@@ -5138,31 +7715,31 @@
     </row>
     <row r="88" spans="1:6">
       <c r="B88" s="293" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="361" t="s">
-        <v>360</v>
-      </c>
-      <c r="C89" s="361"/>
-      <c r="D89" s="361"/>
-      <c r="E89" s="361"/>
-      <c r="F89" s="361"/>
+      <c r="B89" s="371" t="s">
+        <v>349</v>
+      </c>
+      <c r="C89" s="371"/>
+      <c r="D89" s="371"/>
+      <c r="E89" s="371"/>
+      <c r="F89" s="371"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="361" t="s">
-        <v>361</v>
-      </c>
-      <c r="C90" s="361"/>
-      <c r="D90" s="361"/>
-      <c r="E90" s="361"/>
-      <c r="F90" s="361"/>
+      <c r="B90" s="371" t="s">
+        <v>350</v>
+      </c>
+      <c r="C90" s="371"/>
+      <c r="D90" s="371"/>
+      <c r="E90" s="371"/>
+      <c r="F90" s="371"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="C92" s="236">
         <v>0</v>
@@ -5170,7 +7747,7 @@
     </row>
     <row r="93" spans="1:6">
       <c r="B93" s="47" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="C93" s="223">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
@@ -5183,7 +7760,7 @@
     </row>
     <row r="95" spans="1:6" ht="13.9">
       <c r="A95" s="222" t="s">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="B95" s="36"/>
       <c r="C95" s="36"/>
@@ -5195,36 +7772,36 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="361" t="s">
-        <v>362</v>
-      </c>
-      <c r="C97" s="361"/>
-      <c r="D97" s="361"/>
-      <c r="E97" s="361"/>
-      <c r="F97" s="361"/>
+      <c r="B97" s="371" t="s">
+        <v>351</v>
+      </c>
+      <c r="C97" s="371"/>
+      <c r="D97" s="371"/>
+      <c r="E97" s="371"/>
+      <c r="F97" s="371"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="210" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="361" t="s">
-        <v>341</v>
-      </c>
-      <c r="C101" s="361"/>
-      <c r="D101" s="361"/>
-      <c r="E101" s="361"/>
-      <c r="F101" s="361"/>
+      <c r="B101" s="371" t="s">
+        <v>335</v>
+      </c>
+      <c r="C101" s="371"/>
+      <c r="D101" s="371"/>
+      <c r="E101" s="371"/>
+      <c r="F101" s="371"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C102" s="349">
         <f>DCF!C7</f>
@@ -5237,7 +7814,7 @@
     </row>
     <row r="103" spans="2:6">
       <c r="B103" s="47" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="C103" s="223">
         <f>C102*scaling_factor*Exchange_Rate/Common_Shares</f>
@@ -5250,7 +7827,7 @@
     </row>
     <row r="104" spans="2:6">
       <c r="B104" s="296" t="s">
-        <v>401</v>
+        <v>384</v>
       </c>
       <c r="C104" s="325">
         <f>IF(BS!G31/BS!G27&gt;300%,"nm",BS!G31/BS!G27)</f>
@@ -5259,7 +7836,7 @@
     </row>
     <row r="105" spans="2:6">
       <c r="B105" s="296" t="s">
-        <v>403</v>
+        <v>386</v>
       </c>
       <c r="C105" s="326">
         <f>IF(BS!C50&gt;30,"nm",BS!C50)</f>
@@ -5268,12 +7845,12 @@
     </row>
     <row r="107" spans="2:6">
       <c r="B107" s="1" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
     </row>
     <row r="108" spans="2:6">
       <c r="B108" s="47" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="C108" s="349">
         <f>BS!C66</f>
@@ -5286,7 +7863,7 @@
     </row>
     <row r="109" spans="2:6">
       <c r="B109" s="47" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="C109" s="349">
         <f>DCF!C8</f>
@@ -5299,7 +7876,7 @@
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="47" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="C110" s="223">
         <f>C109*scaling_factor*Exchange_Rate/Common_Shares</f>
@@ -5312,12 +7889,12 @@
     </row>
     <row r="112" spans="2:6">
       <c r="B112" s="1" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
     </row>
     <row r="113" spans="1:6">
       <c r="B113" s="47" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="C113" s="349">
         <f>DCF!C9</f>
@@ -5330,7 +7907,7 @@
     </row>
     <row r="114" spans="1:6">
       <c r="B114" s="47" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="C114" s="223">
         <f>C113*scaling_factor*Exchange_Rate/Common_Shares</f>
@@ -5342,17 +7919,17 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="361" t="s">
-        <v>363</v>
-      </c>
-      <c r="C116" s="361"/>
-      <c r="D116" s="361"/>
-      <c r="E116" s="361"/>
-      <c r="F116" s="361"/>
+      <c r="B116" s="371" t="s">
+        <v>352</v>
+      </c>
+      <c r="C116" s="371"/>
+      <c r="D116" s="371"/>
+      <c r="E116" s="371"/>
+      <c r="F116" s="371"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
-        <v>445</v>
+        <v>425</v>
       </c>
       <c r="C118" s="223">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
@@ -5365,7 +7942,7 @@
     </row>
     <row r="119" spans="1:6">
       <c r="B119" s="296" t="s">
-        <v>402</v>
+        <v>549</v>
       </c>
       <c r="C119" s="223">
         <f>BS!D47</f>
@@ -5378,7 +7955,7 @@
     </row>
     <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="222" t="s">
-        <v>355</v>
+        <v>472</v>
       </c>
       <c r="B121" s="36"/>
       <c r="C121" s="36"/>
@@ -5386,30 +7963,30 @@
       <c r="E121" s="36"/>
       <c r="F121" s="36"/>
     </row>
-    <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="362" t="s">
-        <v>364</v>
-      </c>
-      <c r="C123" s="362"/>
-      <c r="D123" s="362"/>
-      <c r="E123" s="362"/>
-      <c r="F123" s="362"/>
+    <row r="123" spans="1:6">
+      <c r="B123" s="367" t="s">
+        <v>473</v>
+      </c>
+      <c r="C123" s="367"/>
+      <c r="D123" s="367"/>
+      <c r="E123" s="367"/>
+      <c r="F123" s="367"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C125" s="233" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D125" s="233" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E125" s="233" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="F125" s="233" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
     </row>
     <row r="126" spans="1:6">
@@ -5524,7 +8101,7 @@
     </row>
     <row r="132" spans="1:6">
       <c r="B132" s="211" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="C132" s="217">
         <f>Scenarios!C60</f>
@@ -5536,17 +8113,17 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="366" t="s">
-        <v>367</v>
-      </c>
-      <c r="C134" s="366"/>
-      <c r="D134" s="366"/>
-      <c r="E134" s="366"/>
-      <c r="F134" s="366"/>
+      <c r="B134" s="369" t="s">
+        <v>474</v>
+      </c>
+      <c r="C134" s="369"/>
+      <c r="D134" s="369"/>
+      <c r="E134" s="369"/>
+      <c r="F134" s="369"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
-        <v>399</v>
+        <v>475</v>
       </c>
       <c r="B136" s="36"/>
       <c r="C136" s="36"/>
@@ -5555,31 +8132,31 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="364" t="s">
-        <v>365</v>
-      </c>
-      <c r="C138" s="364"/>
-      <c r="D138" s="364"/>
-      <c r="E138" s="364"/>
-      <c r="F138" s="364"/>
-    </row>
-    <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="361" t="s">
-        <v>366</v>
-      </c>
-      <c r="C139" s="361"/>
-      <c r="D139" s="361"/>
-      <c r="E139" s="361"/>
-      <c r="F139" s="361"/>
+      <c r="B138" s="370" t="s">
+        <v>353</v>
+      </c>
+      <c r="C138" s="370"/>
+      <c r="D138" s="370"/>
+      <c r="E138" s="370"/>
+      <c r="F138" s="370"/>
+    </row>
+    <row r="139" spans="1:6">
+      <c r="B139" s="371" t="s">
+        <v>476</v>
+      </c>
+      <c r="C139" s="371"/>
+      <c r="D139" s="371"/>
+      <c r="E139" s="371"/>
+      <c r="F139" s="371"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
     </row>
     <row r="141" spans="1:6">
       <c r="B141" s="1" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="C141" s="225">
         <f>F28</f>
@@ -5588,7 +8165,7 @@
     </row>
     <row r="142" spans="1:6">
       <c r="B142" s="1" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="C142" s="224">
         <f>F29</f>
@@ -5597,7 +8174,7 @@
     </row>
     <row r="143" spans="1:6">
       <c r="B143" s="212" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="C143" s="213">
         <f>Scenarios!C77</f>
@@ -5610,7 +8187,7 @@
     </row>
     <row r="145" spans="2:4">
       <c r="B145" s="210" t="s">
-        <v>405</v>
+        <v>388</v>
       </c>
       <c r="C145" s="241" t="str">
         <f>C11</f>
@@ -5623,7 +8200,7 @@
     </row>
     <row r="146" spans="2:4">
       <c r="B146" s="1" t="s">
-        <v>404</v>
+        <v>387</v>
       </c>
       <c r="C146" s="297">
         <f>F29</f>
@@ -5652,7 +8229,7 @@
     </row>
     <row r="149" spans="2:4">
       <c r="B149" s="80" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C149" s="215">
         <f>Scenarios!C83</f>
@@ -5665,7 +8242,7 @@
     </row>
     <row r="150" spans="2:4">
       <c r="B150" s="259" t="s">
-        <v>412</v>
+        <v>395</v>
       </c>
       <c r="C150" s="298" t="str">
         <f>Market_currency</f>
@@ -5678,7 +8255,7 @@
     </row>
     <row r="151" spans="2:4">
       <c r="B151" s="214" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C151" s="92">
         <f>Scenarios!F83</f>
@@ -5687,12 +8264,12 @@
     </row>
     <row r="153" spans="2:4">
       <c r="B153" s="210" t="s">
-        <v>408</v>
+        <v>391</v>
       </c>
     </row>
     <row r="154" spans="2:4">
       <c r="B154" s="1" t="s">
-        <v>407</v>
+        <v>390</v>
       </c>
       <c r="C154" s="297">
         <f>Scenarios!C90</f>
@@ -5721,7 +8298,7 @@
     </row>
     <row r="157" spans="2:4">
       <c r="B157" s="80" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C157" s="215">
         <f>Scenarios!C93</f>
@@ -5734,7 +8311,7 @@
     </row>
     <row r="158" spans="2:4">
       <c r="B158" s="259" t="s">
-        <v>412</v>
+        <v>395</v>
       </c>
       <c r="C158" s="298" t="str">
         <f>Market_currency</f>
@@ -5747,7 +8324,7 @@
     </row>
     <row r="159" spans="2:4">
       <c r="B159" s="214" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C159" s="92">
         <f>Scenarios!F93</f>
@@ -5756,12 +8333,12 @@
     </row>
     <row r="161" spans="2:4">
       <c r="B161" s="210" t="s">
-        <v>397</v>
+        <v>381</v>
       </c>
     </row>
     <row r="162" spans="2:4">
       <c r="B162" s="1" t="s">
-        <v>406</v>
+        <v>389</v>
       </c>
       <c r="C162" s="92">
         <f>Scenarios!C96</f>
@@ -5790,7 +8367,7 @@
     </row>
     <row r="165" spans="2:4">
       <c r="B165" s="80" t="s">
-        <v>398</v>
+        <v>382</v>
       </c>
       <c r="C165" s="215">
         <f>Scenarios!C99</f>
@@ -5803,7 +8380,7 @@
     </row>
     <row r="166" spans="2:4">
       <c r="B166" s="259" t="s">
-        <v>412</v>
+        <v>395</v>
       </c>
       <c r="C166" s="298" t="str">
         <f>Market_currency</f>
@@ -5816,7 +8393,7 @@
     </row>
     <row r="167" spans="2:4">
       <c r="B167" s="214" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C167" s="92">
         <f>Scenarios!F99</f>
@@ -5825,12 +8402,12 @@
     </row>
     <row r="169" spans="2:4">
       <c r="B169" s="210" t="s">
-        <v>428</v>
+        <v>408</v>
       </c>
     </row>
     <row r="170" spans="2:4">
       <c r="B170" s="1" t="s">
-        <v>419</v>
+        <v>399</v>
       </c>
       <c r="C170" s="92">
         <f>F32</f>
@@ -5859,7 +8436,7 @@
     </row>
     <row r="173" spans="2:4">
       <c r="B173" s="80" t="s">
-        <v>398</v>
+        <v>382</v>
       </c>
       <c r="C173" s="215">
         <f>Scenarios!C105</f>
@@ -5872,7 +8449,7 @@
     </row>
     <row r="174" spans="2:4">
       <c r="B174" s="259" t="s">
-        <v>412</v>
+        <v>395</v>
       </c>
       <c r="C174" s="298" t="str">
         <f>Market_currency</f>
@@ -5885,7 +8462,7 @@
     </row>
     <row r="175" spans="2:4">
       <c r="B175" s="214" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C175" s="92">
         <f>Scenarios!F105</f>
@@ -5894,7 +8471,7 @@
     </row>
     <row r="177" spans="1:6" ht="13.9">
       <c r="A177" s="222" t="s">
-        <v>371</v>
+        <v>357</v>
       </c>
       <c r="B177" s="36"/>
       <c r="C177" s="36"/>
@@ -5903,113 +8480,102 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="368" t="s">
-        <v>373</v>
-      </c>
-      <c r="C179" s="361"/>
-      <c r="D179" s="361"/>
-      <c r="E179" s="361"/>
-      <c r="F179" s="361"/>
+      <c r="B179" s="372" t="s">
+        <v>477</v>
+      </c>
+      <c r="C179" s="371"/>
+      <c r="D179" s="371"/>
+      <c r="E179" s="371"/>
+      <c r="F179" s="371"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
-        <v>372</v>
+        <v>358</v>
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="365" t="s">
-        <v>377</v>
-      </c>
-      <c r="C182" s="365"/>
-      <c r="D182" s="365"/>
-      <c r="E182" s="365"/>
-      <c r="F182" s="365"/>
+      <c r="B182" s="373" t="s">
+        <v>362</v>
+      </c>
+      <c r="C182" s="373"/>
+      <c r="D182" s="373"/>
+      <c r="E182" s="373"/>
+      <c r="F182" s="373"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
-        <v>374</v>
+        <v>359</v>
       </c>
     </row>
     <row r="184" spans="1:6">
       <c r="B184" s="214" t="s">
-        <v>375</v>
+        <v>360</v>
       </c>
     </row>
     <row r="185" spans="1:6">
       <c r="B185" s="214" t="s">
-        <v>376</v>
+        <v>361</v>
       </c>
     </row>
     <row r="187" spans="1:6">
       <c r="B187" s="1" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="362" t="s">
-        <v>378</v>
-      </c>
-      <c r="C188" s="362"/>
-      <c r="D188" s="362"/>
-      <c r="E188" s="362"/>
-      <c r="F188" s="362"/>
+        <v>365</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6" ht="34.35" customHeight="1">
+      <c r="B188" s="367" t="s">
+        <v>478</v>
+      </c>
+      <c r="C188" s="367"/>
+      <c r="D188" s="367"/>
+      <c r="E188" s="367"/>
+      <c r="F188" s="367"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
-        <v>382</v>
+        <v>366</v>
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="367" t="s">
-        <v>379</v>
-      </c>
-      <c r="C191" s="367"/>
-      <c r="D191" s="367"/>
-      <c r="E191" s="367"/>
-      <c r="F191" s="367"/>
+      <c r="B191" s="368" t="s">
+        <v>363</v>
+      </c>
+      <c r="C191" s="368"/>
+      <c r="D191" s="368"/>
+      <c r="E191" s="368"/>
+      <c r="F191" s="368"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="367" t="s">
-        <v>380</v>
-      </c>
-      <c r="C192" s="367"/>
-      <c r="D192" s="367"/>
-      <c r="E192" s="367"/>
-      <c r="F192" s="367"/>
+      <c r="B192" s="368" t="s">
+        <v>364</v>
+      </c>
+      <c r="C192" s="368"/>
+      <c r="D192" s="368"/>
+      <c r="E192" s="368"/>
+      <c r="F192" s="368"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
-        <v>386</v>
+        <v>370</v>
       </c>
     </row>
     <row r="195" spans="2:2">
       <c r="B195" s="214" t="s">
-        <v>383</v>
+        <v>367</v>
       </c>
     </row>
     <row r="196" spans="2:2">
       <c r="B196" s="214" t="s">
-        <v>384</v>
+        <v>368</v>
       </c>
     </row>
     <row r="197" spans="2:2">
       <c r="B197" s="214" t="s">
-        <v>385</v>
+        <v>369</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -6026,6 +8592,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -6050,7 +8627,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48ED7348-D356-493F-B1FA-0B9102624322}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -6115,7 +8692,7 @@
     </row>
     <row r="2" spans="2:13" ht="13.9">
       <c r="B2" s="36" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
@@ -6131,7 +8708,7 @@
     </row>
     <row r="3" spans="2:13">
       <c r="B3" s="16" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C3" s="106">
         <v>1000</v>
@@ -6139,7 +8716,7 @@
     </row>
     <row r="4" spans="2:13">
       <c r="B4" s="32" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C4" s="351">
         <v>5057000</v>
@@ -6175,7 +8752,7 @@
     </row>
     <row r="5" spans="2:13">
       <c r="B5" s="40" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C5" s="351">
         <v>2468686</v>
@@ -6211,7 +8788,7 @@
     </row>
     <row r="6" spans="2:13">
       <c r="B6" s="40" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C6" s="351">
         <v>318991</v>
@@ -6247,7 +8824,7 @@
     </row>
     <row r="7" spans="2:13">
       <c r="B7" s="69" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C7" s="352">
         <v>110092</v>
@@ -6283,7 +8860,7 @@
     </row>
     <row r="8" spans="2:13">
       <c r="B8" s="40" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C8" s="351"/>
       <c r="D8" s="351"/>
@@ -6299,7 +8876,7 @@
     </row>
     <row r="9" spans="2:13">
       <c r="B9" s="40" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C9" s="351"/>
       <c r="D9" s="351"/>
@@ -6315,7 +8892,7 @@
     </row>
     <row r="10" spans="2:13">
       <c r="B10" s="40" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C10" s="351"/>
       <c r="D10" s="351"/>
@@ -6331,7 +8908,7 @@
     </row>
     <row r="11" spans="2:13">
       <c r="B11" s="40" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C11" s="351"/>
       <c r="D11" s="351"/>
@@ -6347,7 +8924,7 @@
     </row>
     <row r="12" spans="2:13">
       <c r="B12" s="40" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C12" s="351">
         <v>1746</v>
@@ -6371,7 +8948,7 @@
     </row>
     <row r="13" spans="2:13">
       <c r="B13" s="40" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C13" s="351">
         <v>186780</v>
@@ -6395,7 +8972,7 @@
     </row>
     <row r="14" spans="2:13">
       <c r="B14" s="40" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C14" s="351">
         <v>710922</v>
@@ -6431,7 +9008,7 @@
     </row>
     <row r="15" spans="2:13">
       <c r="B15" s="43" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C15" s="353">
         <v>1814975</v>
@@ -6467,7 +9044,7 @@
     </row>
     <row r="16" spans="2:13">
       <c r="B16" s="28" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C16" s="351">
         <v>320909</v>
@@ -6503,13 +9080,13 @@
     </row>
     <row r="18" spans="2:13">
       <c r="B18" s="16" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C18" s="9"/>
     </row>
     <row r="19" spans="2:13">
       <c r="B19" s="27" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C19" s="351"/>
       <c r="D19" s="351"/>
@@ -6525,7 +9102,7 @@
     </row>
     <row r="20" spans="2:13">
       <c r="B20" s="27" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C20" s="351"/>
       <c r="D20" s="351"/>
@@ -6541,7 +9118,7 @@
     </row>
     <row r="21" spans="2:13">
       <c r="B21" s="27" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C21" s="351"/>
       <c r="D21" s="351"/>
@@ -6557,7 +9134,7 @@
     </row>
     <row r="22" spans="2:13">
       <c r="B22" s="27" t="s">
-        <v>368</v>
+        <v>354</v>
       </c>
       <c r="C22" s="351">
         <v>2369874</v>
@@ -6593,7 +9170,7 @@
     </row>
     <row r="23" spans="2:13">
       <c r="B23" s="27" t="s">
-        <v>370</v>
+        <v>356</v>
       </c>
       <c r="C23" s="351">
         <v>-182373</v>
@@ -6629,7 +9206,7 @@
     </row>
     <row r="24" spans="2:13">
       <c r="B24" s="27" t="s">
-        <v>369</v>
+        <v>355</v>
       </c>
       <c r="C24" s="351">
         <v>-971717</v>
@@ -6691,15 +9268,15 @@
     </row>
     <row r="27" spans="2:13">
       <c r="B27" s="16" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>464</v>
+        <v>558</v>
       </c>
     </row>
     <row r="28" spans="2:13">
       <c r="B28" s="26" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C28" s="333">
         <f>BS!C4</f>
@@ -6736,7 +9313,7 @@
     </row>
     <row r="29" spans="2:13">
       <c r="B29" s="26" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C29" s="333">
         <f>BS!C6</f>
@@ -6773,7 +9350,7 @@
     </row>
     <row r="30" spans="2:13">
       <c r="B30" s="29" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C30" s="334">
         <f>BS!C33+BS!C42</f>
@@ -6810,7 +9387,7 @@
     </row>
     <row r="31" spans="2:13">
       <c r="B31" s="29" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C31" s="334">
         <f>BS!G27</f>
@@ -6847,7 +9424,7 @@
     </row>
     <row r="32" spans="2:13">
       <c r="B32" s="26" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="C32" s="333">
         <f>BS!G28</f>
@@ -6884,7 +9461,7 @@
     </row>
     <row r="34" spans="2:13" ht="13.9">
       <c r="B34" s="36" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C34" s="37"/>
       <c r="D34" s="37"/>
@@ -6900,12 +9477,12 @@
     </row>
     <row r="35" spans="2:13">
       <c r="B35" s="16" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="36" spans="2:13">
       <c r="B36" s="32" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C36" s="333">
         <f t="shared" ref="C36:M36" si="1">IF(C$4="","",C4)</f>
@@ -6954,7 +9531,7 @@
     </row>
     <row r="37" spans="2:13">
       <c r="B37" s="40" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C37" s="333">
         <f t="shared" ref="C37:M37" si="2">IF(C$4="","",-C5)</f>
@@ -7003,7 +9580,7 @@
     </row>
     <row r="38" spans="2:13">
       <c r="B38" s="31" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C38" s="329">
         <f>IF(C36="","",C36+C37)</f>
@@ -7052,7 +9629,7 @@
     </row>
     <row r="39" spans="2:13">
       <c r="B39" s="40" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C39" s="333">
         <f t="shared" ref="C39:M39" si="13">IF(C$4="","",-C6)</f>
@@ -7101,7 +9678,7 @@
     </row>
     <row r="40" spans="2:13">
       <c r="B40" s="69" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C40" s="346">
         <f t="shared" ref="C40:M40" si="14">IF(C$4="","",-C7)</f>
@@ -7150,7 +9727,7 @@
     </row>
     <row r="41" spans="2:13">
       <c r="B41" s="69" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C41" s="346">
         <f>IF(C$4="","",C39-C40)</f>
@@ -7199,7 +9776,7 @@
     </row>
     <row r="42" spans="2:13">
       <c r="B42" s="40" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C42" s="333">
         <f t="shared" ref="C42:M42" si="16">IF(C$4="","",-C8)</f>
@@ -7248,7 +9825,7 @@
     </row>
     <row r="43" spans="2:13">
       <c r="B43" s="43" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C43" s="334">
         <f>IF(C$4="","",C38+C39+C42)</f>
@@ -7297,7 +9874,7 @@
     </row>
     <row r="44" spans="2:13">
       <c r="B44" s="43" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C44" s="354">
         <f t="shared" ref="C44:M44" si="18">IF(C$4="","",C47-C46-C45-C43)</f>
@@ -7346,7 +9923,7 @@
     </row>
     <row r="45" spans="2:13">
       <c r="B45" s="40" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C45" s="349">
         <f t="shared" ref="C45:M45" si="19">IF(C$4="","",C51+C52)</f>
@@ -7395,7 +9972,7 @@
     </row>
     <row r="46" spans="2:13">
       <c r="B46" s="40" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C46" s="333">
         <f t="shared" ref="C46:M46" si="20">IF(C$4="","",-C14)</f>
@@ -7444,7 +10021,7 @@
     </row>
     <row r="47" spans="2:13">
       <c r="B47" s="43" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C47" s="334">
         <f t="shared" ref="C47:M47" si="21">IF(C$4="","",C15)</f>
@@ -7493,7 +10070,7 @@
     </row>
     <row r="48" spans="2:13">
       <c r="B48" s="28" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C48" s="333">
         <f t="shared" ref="C48:M48" si="22">IF(C$4="","",MIN(-C16,0))</f>
@@ -7542,12 +10119,12 @@
     </row>
     <row r="50" spans="2:13">
       <c r="B50" s="16" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="51" spans="2:13">
       <c r="B51" s="40" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C51" s="333">
         <f t="shared" ref="C51:M51" si="23">IF(C$4="","",-C12)</f>
@@ -7596,7 +10173,7 @@
     </row>
     <row r="52" spans="2:13">
       <c r="B52" s="40" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C52" s="333">
         <f t="shared" ref="C52:M52" si="24">IF(C$4="","",C13)</f>
@@ -7645,12 +10222,12 @@
     </row>
     <row r="54" spans="2:13">
       <c r="B54" s="174" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="55" spans="2:13">
       <c r="B55" s="40" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C55" s="349">
         <f t="shared" ref="C55:M55" si="25">IF(C$4="","",C9)</f>
@@ -7699,7 +10276,7 @@
     </row>
     <row r="56" spans="2:13">
       <c r="B56" s="40" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C56" s="349">
         <f t="shared" ref="C56:M56" si="26">IF(C$4="","",C10)</f>
@@ -7748,7 +10325,7 @@
     </row>
     <row r="57" spans="2:13">
       <c r="B57" s="40" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C57" s="349">
         <f t="shared" ref="C57:M57" si="27">IF(C$4="","",C11)</f>
@@ -7797,7 +10374,7 @@
     </row>
     <row r="58" spans="2:13">
       <c r="B58" s="40" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C58" s="349">
         <f>IF(C$4="","",C44-C55-C56-C57)</f>
@@ -7846,13 +10423,13 @@
     </row>
     <row r="60" spans="2:13">
       <c r="B60" s="16" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C60" s="9"/>
     </row>
     <row r="61" spans="2:13">
       <c r="B61" s="27" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C61" s="333">
         <f>IF(C$4="","",-C19)</f>
@@ -7901,7 +10478,7 @@
     </row>
     <row r="62" spans="2:13">
       <c r="B62" s="27" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C62" s="333">
         <f>IF(C$4="","",IF(C20=0,C61,-C20))</f>
@@ -7950,7 +10527,7 @@
     </row>
     <row r="63" spans="2:13">
       <c r="B63" s="27" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C63" s="333">
         <f>IF(C$4="","",-C21)</f>
@@ -7999,7 +10576,7 @@
     </row>
     <row r="64" spans="2:13">
       <c r="B64" s="27" t="s">
-        <v>390</v>
+        <v>374</v>
       </c>
       <c r="C64" s="333">
         <f>IF(C$4="","",C22+C23+C24)</f>
@@ -8048,7 +10625,7 @@
     </row>
     <row r="65" spans="2:13">
       <c r="B65" s="24" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C65" s="73">
         <f>IF(C$4="","",C25)</f>
@@ -8097,7 +10674,7 @@
     </row>
     <row r="67" spans="2:13">
       <c r="B67" s="91" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="68" spans="2:13">
@@ -8152,7 +10729,7 @@
     </row>
     <row r="69" spans="2:13">
       <c r="B69" s="31" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C69" s="92">
         <f>IF(D$36="","",C38/D38-1)</f>
@@ -8251,7 +10828,7 @@
     </row>
     <row r="71" spans="2:13">
       <c r="B71" s="43" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C71" s="101">
         <f>IF(D$36="","",C44/D44-1)</f>
@@ -8350,7 +10927,7 @@
     </row>
     <row r="74" spans="2:13" ht="13.9">
       <c r="B74" s="36" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C74" s="37"/>
       <c r="D74" s="37"/>
@@ -8366,13 +10943,13 @@
     </row>
     <row r="75" spans="2:13">
       <c r="B75" s="16" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C75" s="9"/>
     </row>
     <row r="76" spans="2:13">
       <c r="B76" s="26" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C76" s="76">
         <f>IF(C$4="","",C79+C80)</f>
@@ -8421,7 +10998,7 @@
     </row>
     <row r="77" spans="2:13">
       <c r="B77" s="93" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C77" s="318">
         <f t="shared" ref="C77:H78" si="40">IF(C$4="","",C28)</f>
@@ -8455,7 +11032,7 @@
     </row>
     <row r="78" spans="2:13">
       <c r="B78" s="93" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C78" s="318">
         <f t="shared" si="40"/>
@@ -8489,7 +11066,7 @@
     </row>
     <row r="79" spans="2:13">
       <c r="B79" s="26" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C79" s="317">
         <f t="shared" ref="C79:M79" si="41">IF(C$4="","",C30)</f>
@@ -8538,7 +11115,7 @@
     </row>
     <row r="80" spans="2:13">
       <c r="B80" s="26" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C80" s="317">
         <f t="shared" ref="C80:M80" si="42">IF(C$4="","",C31)</f>
@@ -8610,7 +11187,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet3">
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -8630,7 +11207,7 @@
   <sheetData>
     <row r="1" spans="2:8" ht="15" customHeight="1">
       <c r="B1" s="18" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C1" s="99">
         <v>45657</v>
@@ -8646,7 +11223,7 @@
     </row>
     <row r="2" spans="2:8" ht="15" customHeight="1">
       <c r="B2" s="79" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
@@ -8657,27 +11234,27 @@
     </row>
     <row r="3" spans="2:8" ht="15" customHeight="1">
       <c r="B3" s="16" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C3" s="182" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D3" s="183" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="G3" s="182" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="H3" s="183" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="2:8" ht="15" customHeight="1">
       <c r="B4" s="4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C4" s="19">
         <f>519815+18089</f>
@@ -8688,7 +11265,7 @@
       </c>
       <c r="E4" s="25"/>
       <c r="F4" s="4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="G4" s="19">
         <f>1505443+7675879</f>
@@ -8700,7 +11277,7 @@
     </row>
     <row r="5" spans="2:8" ht="15" customHeight="1">
       <c r="B5" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C5" s="19">
         <v>0</v>
@@ -8710,7 +11287,7 @@
       </c>
       <c r="E5" s="25"/>
       <c r="F5" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G5" s="19">
         <v>937107</v>
@@ -8721,7 +11298,7 @@
     </row>
     <row r="6" spans="2:8" ht="15" customHeight="1">
       <c r="B6" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C6" s="19">
         <v>137638</v>
@@ -8731,7 +11308,7 @@
       </c>
       <c r="E6" s="25"/>
       <c r="F6" s="4" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="G6" s="19">
         <v>0</v>
@@ -8742,7 +11319,7 @@
     </row>
     <row r="7" spans="2:8" ht="15" customHeight="1">
       <c r="B7" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C7" s="19">
         <v>0</v>
@@ -8752,7 +11329,7 @@
       </c>
       <c r="E7" s="25"/>
       <c r="F7" s="4" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="G7" s="19">
         <v>0</v>
@@ -8763,7 +11340,7 @@
     </row>
     <row r="8" spans="2:8" ht="15" customHeight="1">
       <c r="B8" s="1" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C8" s="19">
         <v>0</v>
@@ -8773,7 +11350,7 @@
       </c>
       <c r="E8" s="25"/>
       <c r="F8" s="1" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="G8" s="19">
         <v>0</v>
@@ -8784,7 +11361,7 @@
     </row>
     <row r="9" spans="2:8" ht="15" customHeight="1">
       <c r="B9" s="4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C9" s="19">
         <v>207695</v>
@@ -8794,7 +11371,7 @@
       </c>
       <c r="E9" s="25"/>
       <c r="F9" s="4" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="G9" s="19">
         <v>0</v>
@@ -8805,7 +11382,7 @@
     </row>
     <row r="10" spans="2:8" ht="15" customHeight="1">
       <c r="B10" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C10" s="19">
         <v>0</v>
@@ -8817,7 +11394,7 @@
     </row>
     <row r="11" spans="2:8" ht="15" customHeight="1">
       <c r="B11" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C11" s="19">
         <v>0</v>
@@ -8829,7 +11406,7 @@
     </row>
     <row r="12" spans="2:8" ht="15" customHeight="1">
       <c r="B12" s="80" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C12" s="81">
         <f>SUM(C4:C11)</f>
@@ -8840,7 +11417,7 @@
         <v>412330.89999999997</v>
       </c>
       <c r="F12" s="80" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G12" s="81">
         <f>SUM(G4:G9)</f>
@@ -8858,27 +11435,27 @@
     </row>
     <row r="14" spans="2:8" ht="15" customHeight="1">
       <c r="B14" s="16" t="s">
+        <v>179</v>
+      </c>
+      <c r="C14" s="182" t="s">
+        <v>132</v>
+      </c>
+      <c r="D14" s="183" t="s">
+        <v>33</v>
+      </c>
+      <c r="F14" s="16" t="s">
         <v>182</v>
       </c>
-      <c r="C14" s="182" t="s">
-        <v>135</v>
-      </c>
-      <c r="D14" s="183" t="s">
-        <v>35</v>
-      </c>
-      <c r="F14" s="16" t="s">
-        <v>185</v>
-      </c>
       <c r="G14" s="182" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="H14" s="183" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" spans="2:8" ht="15" customHeight="1">
       <c r="B15" s="4" t="s">
-        <v>451</v>
+        <v>431</v>
       </c>
       <c r="C15" s="19">
         <v>453310</v>
@@ -8887,7 +11464,7 @@
         <v>0.4</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="G15" s="19">
         <v>0</v>
@@ -8898,7 +11475,7 @@
     </row>
     <row r="16" spans="2:8" ht="15" customHeight="1">
       <c r="B16" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C16" s="19">
         <v>0</v>
@@ -8907,7 +11484,7 @@
         <v>0.5</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="G16" s="19">
         <v>0</v>
@@ -8918,7 +11495,7 @@
     </row>
     <row r="17" spans="2:8" ht="15" customHeight="1">
       <c r="B17" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C17" s="19">
         <v>0</v>
@@ -8927,7 +11504,7 @@
         <v>0.6</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="G17" s="19">
         <f>439187</f>
@@ -8939,7 +11516,7 @@
     </row>
     <row r="18" spans="2:8" ht="15" customHeight="1">
       <c r="B18" s="4" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C18" s="19">
         <v>0</v>
@@ -8948,7 +11525,7 @@
         <v>0.6</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="G18" s="19">
         <v>0</v>
@@ -8959,7 +11536,7 @@
     </row>
     <row r="19" spans="2:8" ht="15" customHeight="1">
       <c r="B19" s="4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C19" s="19">
         <f>3715248+73168+31796</f>
@@ -8969,7 +11546,7 @@
         <v>0.1</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="G19" s="19">
         <v>0</v>
@@ -8980,7 +11557,7 @@
     </row>
     <row r="20" spans="2:8" ht="15" customHeight="1">
       <c r="B20" s="4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C20" s="19">
         <v>0</v>
@@ -8989,7 +11566,7 @@
         <v>0.05</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="G20" s="19">
         <v>0</v>
@@ -9000,7 +11577,7 @@
     </row>
     <row r="21" spans="2:8" ht="15" customHeight="1">
       <c r="B21" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" s="19">
         <v>5970133</v>
@@ -9009,7 +11586,7 @@
         <v>0.05</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="G21" s="19">
         <v>0</v>
@@ -9020,7 +11597,7 @@
     </row>
     <row r="22" spans="2:8" ht="15" customHeight="1">
       <c r="B22" s="4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C22" s="19">
         <v>84764</v>
@@ -9032,7 +11609,7 @@
     </row>
     <row r="23" spans="2:8" ht="15" customHeight="1">
       <c r="B23" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C23" s="19">
         <f>1179551</f>
@@ -9045,7 +11622,7 @@
     </row>
     <row r="24" spans="2:8" ht="15" customHeight="1">
       <c r="B24" s="80" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C24" s="81">
         <f>SUM(C15:C23)</f>
@@ -9056,7 +11633,7 @@
         <v>938139.45</v>
       </c>
       <c r="F24" s="80" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G24" s="81">
         <f>SUM(G15:G21)</f>
@@ -9069,30 +11646,30 @@
     </row>
     <row r="26" spans="2:8" ht="15" customHeight="1">
       <c r="B26" s="16" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C26" s="182" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="F26" s="184" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="G26" s="185" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="H26" s="186" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="27" spans="2:8" ht="15" customHeight="1">
       <c r="B27" s="4" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C27" s="19">
         <v>0</v>
       </c>
       <c r="F27" s="187" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G27" s="85">
         <f>G32-G30</f>
@@ -9105,13 +11682,13 @@
     </row>
     <row r="28" spans="2:8" ht="15" customHeight="1">
       <c r="B28" s="4" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C28" s="19">
         <v>12125</v>
       </c>
       <c r="F28" s="189" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="G28" s="12">
         <v>2421183</v>
@@ -9120,13 +11697,13 @@
     </row>
     <row r="29" spans="2:8" ht="15" customHeight="1">
       <c r="B29" s="4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C29" s="19">
         <v>0</v>
       </c>
       <c r="F29" s="190" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="G29" s="14">
         <f>G27-G28</f>
@@ -9139,13 +11716,13 @@
     </row>
     <row r="30" spans="2:8" ht="15" customHeight="1">
       <c r="B30" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C30" s="19">
         <v>0</v>
       </c>
       <c r="F30" s="187" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G30" s="85">
         <f>C33+C42</f>
@@ -9155,14 +11732,14 @@
     </row>
     <row r="31" spans="2:8" ht="15" customHeight="1">
       <c r="B31" s="80" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="C31" s="81">
         <f>SUM(C27:C30)</f>
         <v>12125</v>
       </c>
       <c r="F31" s="190" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G31" s="191">
         <f>C31+C40</f>
@@ -9172,14 +11749,14 @@
     </row>
     <row r="32" spans="2:8" ht="15" customHeight="1">
       <c r="B32" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C32" s="21">
         <f>C33-C31</f>
         <v>2578910</v>
       </c>
       <c r="F32" s="192" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G32" s="193">
         <f>G35+G40</f>
@@ -9192,7 +11769,7 @@
     </row>
     <row r="33" spans="2:8" ht="15" customHeight="1">
       <c r="B33" s="83" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C33" s="84">
         <v>2591035</v>
@@ -9205,24 +11782,24 @@
       <c r="B34" s="83"/>
       <c r="C34" s="84"/>
       <c r="F34" s="196" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="G34" s="197" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="H34" s="198" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="35" spans="2:8" ht="15" customHeight="1">
       <c r="B35" s="16" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="C35" s="182" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="F35" s="199" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G35" s="193">
         <f>C12+C24</f>
@@ -9235,13 +11812,13 @@
     </row>
     <row r="36" spans="2:8" ht="15" customHeight="1">
       <c r="B36" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C36" s="19">
         <v>0</v>
       </c>
       <c r="F36" s="190" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="G36" s="191">
         <f>C4+C15</f>
@@ -9251,13 +11828,13 @@
     </row>
     <row r="37" spans="2:8" ht="15" customHeight="1">
       <c r="B37" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C37" s="19">
         <v>31552</v>
       </c>
       <c r="F37" s="190" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="G37" s="191">
         <f>C6</f>
@@ -9267,13 +11844,13 @@
     </row>
     <row r="38" spans="2:8" ht="15" customHeight="1">
       <c r="B38" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C38" s="19">
         <v>0</v>
       </c>
       <c r="F38" s="190" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="G38" s="191">
         <f>C7+C17</f>
@@ -9283,13 +11860,13 @@
     </row>
     <row r="39" spans="2:8" ht="15" customHeight="1">
       <c r="B39" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C39" s="19">
         <v>0</v>
       </c>
       <c r="F39" s="190" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G39" s="191">
         <f>C7+C17+C19+C20</f>
@@ -9302,14 +11879,14 @@
     </row>
     <row r="40" spans="2:8" ht="15" customHeight="1">
       <c r="B40" s="80" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="C40" s="81">
         <f>SUM(C36:C39)</f>
         <v>31552</v>
       </c>
       <c r="F40" s="199" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="G40" s="193">
         <f>G12+G24</f>
@@ -9322,14 +11899,14 @@
     </row>
     <row r="41" spans="2:8" ht="15" customHeight="1">
       <c r="B41" s="4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C41" s="21">
         <f>C42-C40</f>
         <v>1424979</v>
       </c>
       <c r="F41" s="190" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="G41" s="191">
         <f>C70</f>
@@ -9342,13 +11919,13 @@
     </row>
     <row r="42" spans="2:8" ht="15" customHeight="1">
       <c r="B42" s="83" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C42" s="84">
         <v>1456531</v>
       </c>
       <c r="F42" s="201" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="G42" s="202">
         <f>C82</f>
@@ -9361,7 +11938,7 @@
     </row>
     <row r="44" spans="2:8" ht="15" customHeight="1">
       <c r="B44" s="79" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C44" s="37"/>
       <c r="D44" s="37"/>
@@ -9372,21 +11949,21 @@
     </row>
     <row r="45" spans="2:8" ht="15" customHeight="1">
       <c r="B45" s="16" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C45" s="234" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D45" s="182" t="s">
-        <v>402</v>
+        <v>385</v>
       </c>
       <c r="F45" s="256" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="46" spans="2:8" ht="15" customHeight="1">
       <c r="B46" s="1" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="C46" s="76">
         <f>G29</f>
@@ -9418,20 +11995,20 @@
     </row>
     <row r="49" spans="2:8" ht="15" customHeight="1">
       <c r="B49" s="157" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C49" s="235" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D49" s="197" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" s="253"/>
     </row>
     <row r="50" spans="2:8" ht="15" customHeight="1">
       <c r="B50" s="8" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C50" s="95">
         <f>G31/Normalized_FCF!C8</f>
@@ -9445,7 +12022,7 @@
     </row>
     <row r="51" spans="2:8" ht="15" customHeight="1">
       <c r="B51" s="1" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C51" s="181"/>
       <c r="D51" s="92">
@@ -9459,19 +12036,19 @@
     </row>
     <row r="53" spans="2:8" ht="15" customHeight="1">
       <c r="B53" s="157" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C53" s="235" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D53" s="197" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F53" s="253"/>
     </row>
     <row r="54" spans="2:8" ht="15" customHeight="1">
       <c r="B54" s="1" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C54" s="92">
         <f>Normalized_FCF!C8/G35</f>
@@ -9485,7 +12062,7 @@
     </row>
     <row r="55" spans="2:8" ht="15" customHeight="1">
       <c r="B55" s="1" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C55" s="92">
         <f>Normalized_FCF!C11/G40</f>
@@ -9502,19 +12079,19 @@
     </row>
     <row r="57" spans="2:8" ht="15" customHeight="1">
       <c r="B57" s="157" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="C57" s="235" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D57" s="197" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F57" s="253"/>
     </row>
     <row r="58" spans="2:8" ht="15" customHeight="1">
       <c r="B58" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C58" s="98"/>
       <c r="D58" s="23">
@@ -9525,7 +12102,7 @@
     </row>
     <row r="59" spans="2:8" ht="15" customHeight="1">
       <c r="B59" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C59" s="98"/>
       <c r="D59" s="92">
@@ -9539,19 +12116,19 @@
     </row>
     <row r="61" spans="2:8" ht="15" customHeight="1">
       <c r="B61" s="157" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="C61" s="235" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D61" s="197" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F61" s="253"/>
     </row>
     <row r="62" spans="2:8" ht="15" customHeight="1">
       <c r="B62" s="1" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C62" s="92">
         <f>IF(G28&lt;=0,0,G28/G29)</f>
@@ -9562,12 +12139,12 @@
         <v>0.14691578448009396</v>
       </c>
       <c r="F62" s="253" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" customHeight="1">
       <c r="B64" s="79" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="C64" s="37"/>
       <c r="D64" s="37"/>
@@ -9578,21 +12155,21 @@
     </row>
     <row r="65" spans="2:6" ht="15" customHeight="1">
       <c r="B65" s="16" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C65" s="234" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D65" s="183" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="F65" s="256" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="66" spans="2:6" ht="15" customHeight="1">
       <c r="B66" s="105" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C66" s="20">
         <f>G4+G5+G15</f>
@@ -9603,12 +12180,12 @@
         <v>8041470.060084247</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="67" spans="2:6" ht="15" customHeight="1">
       <c r="B67" s="105" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C67" s="20">
         <f>G6+G16</f>
@@ -9618,7 +12195,7 @@
     </row>
     <row r="68" spans="2:6" ht="15" customHeight="1">
       <c r="B68" s="105" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="C68" s="20">
         <f>G18</f>
@@ -9628,7 +12205,7 @@
     </row>
     <row r="69" spans="2:6" ht="15" customHeight="1">
       <c r="B69" s="105" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="C69" s="20">
         <f>G8+G20</f>
@@ -9638,7 +12215,7 @@
     </row>
     <row r="70" spans="2:6" ht="15" customHeight="1">
       <c r="B70" s="80" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C70" s="81">
         <f>SUM(C66:C69)</f>
@@ -9651,19 +12228,19 @@
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1">
       <c r="B72" s="255" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="C72" s="234" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D72" s="182" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F72" s="253"/>
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1">
       <c r="B73" s="105" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="C73" s="349">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
@@ -9674,12 +12251,12 @@
         <v>-346159.82331929216</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1">
       <c r="B74" s="257" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="C74" s="258">
         <f>-$C$66/C73</f>
@@ -9690,12 +12267,12 @@
         <v>29.230512377130857</v>
       </c>
       <c r="F74" s="253" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
     </row>
     <row r="75" spans="2:6" ht="15" customHeight="1">
       <c r="B75" s="80" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="C75" s="320"/>
       <c r="D75" s="321">
@@ -9703,12 +12280,12 @@
         <v>2076958.939915753</v>
       </c>
       <c r="F75" s="253" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1">
       <c r="B76" s="259" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="C76" s="260"/>
       <c r="D76" s="290">
@@ -9716,7 +12293,7 @@
         <v>6</v>
       </c>
       <c r="F76" s="253" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1">
@@ -9724,19 +12301,19 @@
     </row>
     <row r="78" spans="2:6" ht="15" customHeight="1">
       <c r="B78" s="16" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="C78" s="234" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D78" s="183" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F78" s="253"/>
     </row>
     <row r="79" spans="2:6" ht="15" customHeight="1">
       <c r="B79" s="105" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C79" s="20">
         <f>G7+G17</f>
@@ -9750,7 +12327,7 @@
     </row>
     <row r="80" spans="2:6" ht="15" customHeight="1">
       <c r="B80" s="105" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="C80" s="20">
         <f>G19</f>
@@ -9764,7 +12341,7 @@
     </row>
     <row r="81" spans="2:8" ht="15" customHeight="1">
       <c r="B81" s="105" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="C81" s="20">
         <f>G9+G21</f>
@@ -9778,7 +12355,7 @@
     </row>
     <row r="82" spans="2:8" ht="15" customHeight="1">
       <c r="B82" s="80" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="C82" s="81">
         <f>SUM(C79:C81)</f>
@@ -9792,7 +12369,7 @@
     </row>
     <row r="84" spans="2:8" ht="15" customHeight="1">
       <c r="B84" s="79" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="C84" s="37"/>
       <c r="D84" s="37"/>
@@ -9803,15 +12380,15 @@
     </row>
     <row r="85" spans="2:8" ht="15" customHeight="1">
       <c r="B85" s="16" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D85" s="241" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="15" customHeight="1">
       <c r="B86" s="238" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="C86" s="76">
         <f>-DCF!C7*Exchange_Rate</f>
@@ -9828,7 +12405,7 @@
     </row>
     <row r="87" spans="2:8" ht="15" customHeight="1">
       <c r="B87" s="238" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="C87" s="76">
         <f>DCF!C8*Exchange_Rate</f>
@@ -9845,7 +12422,7 @@
     </row>
     <row r="88" spans="2:8" ht="15" customHeight="1">
       <c r="B88" s="239" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="C88" s="76">
         <f>DCF!C9*Exchange_Rate</f>
@@ -9862,7 +12439,7 @@
     </row>
     <row r="89" spans="2:8" ht="15" customHeight="1">
       <c r="B89" s="80" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="C89" s="180">
         <f>SUM(C86:C88)</f>
@@ -9884,7 +12461,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2">
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -9910,7 +12487,7 @@
         <v>HKD</v>
       </c>
       <c r="C1" s="53" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D1" s="53"/>
       <c r="E1" s="53"/>
@@ -9963,12 +12540,12 @@
     <row r="2" spans="1:17" ht="15.75" customHeight="1">
       <c r="A2" s="3"/>
       <c r="B2" s="54" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C2" s="54"/>
       <c r="D2" s="56"/>
       <c r="E2" s="66" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F2" s="56"/>
       <c r="G2" s="37"/>
@@ -9986,7 +12563,7 @@
     <row r="3" spans="1:17" ht="15.75" customHeight="1">
       <c r="A3" s="10"/>
       <c r="B3" s="16" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C3" s="107">
         <f>scaling_factor</f>
@@ -10000,7 +12577,7 @@
     <row r="4" spans="1:17" ht="15.75" customHeight="1">
       <c r="A4" s="10"/>
       <c r="B4" s="26" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C4" s="327">
         <f>AVERAGE(G4:P4)</f>
@@ -10057,7 +12634,7 @@
     <row r="5" spans="1:17" ht="15.75" customHeight="1">
       <c r="A5" s="10"/>
       <c r="B5" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C5" s="328">
         <f>C25</f>
@@ -10112,7 +12689,7 @@
     <row r="6" spans="1:17" ht="15.75" customHeight="1">
       <c r="A6" s="10"/>
       <c r="B6" s="31" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C6" s="329">
         <f>C4+C5</f>
@@ -10167,7 +12744,7 @@
     <row r="7" spans="1:17" ht="15.75" customHeight="1">
       <c r="A7" s="10"/>
       <c r="B7" s="8" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C7" s="328">
         <f>C35</f>
@@ -10222,7 +12799,7 @@
     <row r="8" spans="1:17" ht="15.75" customHeight="1">
       <c r="A8" s="10"/>
       <c r="B8" s="29" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C8" s="330">
         <f>C6+C7</f>
@@ -10279,7 +12856,7 @@
     <row r="9" spans="1:17" ht="15.75" customHeight="1">
       <c r="A9" s="10"/>
       <c r="B9" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C9" s="328">
         <f>BS!$G$39*BS!D58</f>
@@ -10334,7 +12911,7 @@
     <row r="10" spans="1:17" ht="15.75" customHeight="1">
       <c r="A10" s="10"/>
       <c r="B10" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C10" s="328">
         <f>-C4*C78</f>
@@ -10389,7 +12966,7 @@
     <row r="11" spans="1:17" ht="15.75" customHeight="1">
       <c r="A11" s="10"/>
       <c r="B11" s="31" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C11" s="331">
         <f>C63</f>
@@ -10446,7 +13023,7 @@
     <row r="12" spans="1:17" ht="15.75" customHeight="1">
       <c r="A12" s="10"/>
       <c r="B12" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C12" s="328">
         <f>C50</f>
@@ -10501,7 +13078,7 @@
     <row r="13" spans="1:17" ht="15.75" customHeight="1">
       <c r="A13" s="10"/>
       <c r="B13" s="70" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C13" s="329">
         <f>SUM(C8:C12)</f>
@@ -10556,7 +13133,7 @@
     <row r="14" spans="1:17" ht="15.75" customHeight="1">
       <c r="A14" s="10"/>
       <c r="B14" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C14" s="328">
         <f>-SUM(C8+C11,C12)*C43</f>
@@ -10611,7 +13188,7 @@
     <row r="15" spans="1:17" ht="15.75" customHeight="1">
       <c r="A15" s="10"/>
       <c r="B15" s="40" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="C15" s="328">
         <f>-C4*C83</f>
@@ -10668,7 +13245,7 @@
     <row r="16" spans="1:17" ht="15.75" customHeight="1">
       <c r="A16" s="10"/>
       <c r="B16" s="41" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C16" s="332">
         <f>SUM(C13:C15)</f>
@@ -10725,7 +13302,7 @@
     <row r="17" spans="1:17" ht="15.75" customHeight="1">
       <c r="A17" s="10"/>
       <c r="B17" s="27" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C17" s="328">
         <f>-C4*C85</f>
@@ -10733,7 +13310,7 @@
       </c>
       <c r="D17" s="58"/>
       <c r="E17" s="267" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="F17" s="58"/>
       <c r="G17" s="335"/>
@@ -10751,14 +13328,14 @@
     <row r="18" spans="1:17" ht="15.75" customHeight="1">
       <c r="A18" s="10"/>
       <c r="B18" s="27" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C18" s="328">
         <v>0</v>
       </c>
       <c r="D18" s="58"/>
       <c r="E18" s="267" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="F18" s="58"/>
       <c r="G18" s="336"/>
@@ -10776,7 +13353,7 @@
     <row r="19" spans="1:17" ht="15.75" customHeight="1">
       <c r="A19" s="10"/>
       <c r="B19" s="31" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C19" s="329">
         <f>C16+C17</f>
@@ -10852,12 +13429,12 @@
     <row r="21" spans="1:17" ht="15.75" customHeight="1">
       <c r="A21" s="10"/>
       <c r="B21" s="54" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="C21" s="54"/>
       <c r="D21" s="56"/>
       <c r="E21" s="66" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F21" s="56"/>
       <c r="G21" s="37"/>
@@ -10875,7 +13452,7 @@
     <row r="22" spans="1:17" ht="15.75" customHeight="1">
       <c r="A22" s="10"/>
       <c r="B22" s="64" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C22" s="62"/>
       <c r="D22" s="27"/>
@@ -10896,7 +13473,7 @@
     <row r="23" spans="1:17" ht="15.75" customHeight="1">
       <c r="A23" s="10"/>
       <c r="B23" s="27" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C23" s="337">
         <f>-C4*C28</f>
@@ -10953,7 +13530,7 @@
     <row r="24" spans="1:17" ht="15.75" customHeight="1">
       <c r="A24" s="10"/>
       <c r="B24" s="68" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C24" s="328">
         <f>-C4*C29</f>
@@ -11010,7 +13587,7 @@
     <row r="25" spans="1:17" ht="15.75" customHeight="1">
       <c r="A25" s="10"/>
       <c r="B25" s="70" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C25" s="329">
         <f>C23+C24</f>
@@ -11071,14 +13648,14 @@
     <row r="27" spans="1:17" ht="15.75" customHeight="1">
       <c r="A27" s="10"/>
       <c r="B27" s="64" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="E27" s="268"/>
     </row>
     <row r="28" spans="1:17" ht="15.75" customHeight="1">
       <c r="A28" s="10"/>
       <c r="B28" s="26" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C28" s="63">
         <f>AVERAGE(G28:P28)</f>
@@ -11086,7 +13663,7 @@
       </c>
       <c r="D28" s="26"/>
       <c r="E28" s="266" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -11146,7 +13723,7 @@
       </c>
       <c r="D29" s="26"/>
       <c r="E29" s="266" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -11197,7 +13774,7 @@
     <row r="30" spans="1:17" ht="15.75" customHeight="1">
       <c r="A30" s="10"/>
       <c r="B30" s="70" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C30" s="71">
         <f>ABS(C25/$C$4)</f>
@@ -11256,21 +13833,21 @@
     <row r="32" spans="1:17" ht="15.75" customHeight="1">
       <c r="A32" s="10"/>
       <c r="B32" s="64" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E32" s="268"/>
     </row>
     <row r="33" spans="1:17" ht="15.75" customHeight="1">
       <c r="A33" s="10"/>
       <c r="B33" s="8" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C33" s="340">
         <f>G33</f>
         <v>-208899</v>
       </c>
       <c r="E33" s="266" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="G33" s="328">
         <f>Data!C41</f>
@@ -11320,7 +13897,7 @@
     <row r="34" spans="1:17" ht="15.75" customHeight="1">
       <c r="A34" s="10"/>
       <c r="B34" s="27" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C34" s="340">
         <f>AVERAGE(G34:J34)</f>
@@ -11328,7 +13905,7 @@
       </c>
       <c r="D34" s="58"/>
       <c r="E34" s="266" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="F34" s="58"/>
       <c r="G34" s="333">
@@ -11379,7 +13956,7 @@
     <row r="35" spans="1:17" ht="15.75" customHeight="1">
       <c r="A35" s="10"/>
       <c r="B35" s="70" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C35" s="329">
         <f>C33+C34</f>
@@ -11440,7 +14017,7 @@
     <row r="37" spans="1:17" ht="15.75" customHeight="1">
       <c r="A37" s="10"/>
       <c r="B37" s="64" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="E37" s="268"/>
     </row>
@@ -11563,7 +14140,7 @@
     <row r="40" spans="1:17" ht="15.75" customHeight="1">
       <c r="A40" s="10"/>
       <c r="B40" s="70" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C40" s="71">
         <f>ABS(C35/$C$4)</f>
@@ -11622,21 +14199,21 @@
     <row r="42" spans="1:17" ht="15.75" customHeight="1">
       <c r="A42" s="10"/>
       <c r="B42" s="64" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="E42" s="268"/>
     </row>
     <row r="43" spans="1:17" ht="15.75" customHeight="1">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C43" s="263">
         <v>0.25</v>
       </c>
       <c r="D43" s="27"/>
       <c r="E43" s="265" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
@@ -11690,12 +14267,12 @@
     <row r="45" spans="1:17" ht="15.75" customHeight="1">
       <c r="A45" s="10"/>
       <c r="B45" s="54" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="C45" s="54"/>
       <c r="D45" s="56"/>
       <c r="E45" s="66" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F45" s="56"/>
       <c r="G45" s="37"/>
@@ -11713,14 +14290,14 @@
     <row r="46" spans="1:17" ht="15.75" customHeight="1">
       <c r="A46" s="10"/>
       <c r="B46" s="64" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E46" s="268"/>
     </row>
     <row r="47" spans="1:17" ht="15.75" customHeight="1">
       <c r="A47" s="10"/>
       <c r="B47" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C47" s="328">
         <f>-BS!G31*Normalized_FCF!C54</f>
@@ -11775,7 +14352,7 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="C48" s="328">
         <f>BS!D75*C53</f>
@@ -11830,7 +14407,7 @@
     <row r="49" spans="1:17" ht="15.75" customHeight="1">
       <c r="A49" s="10"/>
       <c r="B49" s="287" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="C49" s="342">
         <f>BS!$C$66*C53</f>
@@ -11887,7 +14464,7 @@
     <row r="50" spans="1:17" ht="15.75" customHeight="1">
       <c r="A50" s="10"/>
       <c r="B50" s="70" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C50" s="329">
         <f>C47+C48</f>
@@ -11946,23 +14523,23 @@
     <row r="52" spans="1:17" ht="15.75" customHeight="1">
       <c r="A52" s="10"/>
       <c r="B52" s="72" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="E52" s="268"/>
       <c r="G52" s="97" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
     <row r="53" spans="1:17" ht="15.75" customHeight="1">
       <c r="A53" s="10"/>
       <c r="B53" s="8" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C53" s="87">
         <v>0.01</v>
       </c>
       <c r="E53" s="265" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
@@ -11982,14 +14559,14 @@
     <row r="54" spans="1:17" ht="15.75" customHeight="1">
       <c r="A54" s="10"/>
       <c r="B54" s="8" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C54" s="82">
         <f>G54</f>
         <v>3.9975273026993614E-2</v>
       </c>
       <c r="E54" s="265" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -12009,7 +14586,7 @@
     <row r="55" spans="1:17" ht="15.75" customHeight="1">
       <c r="A55" s="10"/>
       <c r="B55" s="26" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C55" s="42">
         <f>-C8/C47</f>
@@ -12068,17 +14645,17 @@
     <row r="57" spans="1:17" ht="15.75" customHeight="1">
       <c r="A57" s="10"/>
       <c r="B57" s="64" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="E57" s="268"/>
       <c r="G57" s="97" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
     <row r="58" spans="1:17" ht="15.75" customHeight="1">
       <c r="A58" s="10"/>
       <c r="B58" s="40" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C58" s="328">
         <f>BS!$C67*C66</f>
@@ -12133,7 +14710,7 @@
     <row r="59" spans="1:17" ht="15.75" customHeight="1">
       <c r="A59" s="10"/>
       <c r="B59" s="40" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C59" s="328">
         <f>BS!$C68*C67</f>
@@ -12188,7 +14765,7 @@
     <row r="60" spans="1:17" ht="15.75" customHeight="1">
       <c r="A60" s="10"/>
       <c r="B60" s="40" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C60" s="328">
         <f>BS!$C69*C68</f>
@@ -12243,7 +14820,7 @@
     <row r="61" spans="1:17" ht="15.75" customHeight="1">
       <c r="A61" s="10"/>
       <c r="B61" s="31" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C61" s="329">
         <f>SUM(C58:C60)</f>
@@ -12298,13 +14875,13 @@
     <row r="62" spans="1:17" ht="15.75" customHeight="1">
       <c r="A62" s="10"/>
       <c r="B62" s="40" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C62" s="343">
         <v>0</v>
       </c>
       <c r="E62" s="266" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="G62" s="328">
         <f>Data!C58</f>
@@ -12354,7 +14931,7 @@
     <row r="63" spans="1:17" ht="15.75" customHeight="1">
       <c r="A63" s="10"/>
       <c r="B63" s="31" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C63" s="329">
         <f>C61+C62</f>
@@ -12413,17 +14990,17 @@
     <row r="65" spans="1:17" ht="15.75" customHeight="1">
       <c r="A65" s="10"/>
       <c r="B65" s="96" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="E65" s="268"/>
       <c r="G65" s="97" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
     <row r="66" spans="1:17" ht="15.75" customHeight="1">
       <c r="A66" s="10"/>
       <c r="B66" s="40" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C66" s="176">
         <f>G66</f>
@@ -12448,7 +15025,7 @@
     <row r="67" spans="1:17" ht="15.75" customHeight="1">
       <c r="A67" s="10"/>
       <c r="B67" s="105" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C67" s="176">
         <f>G67</f>
@@ -12473,7 +15050,7 @@
     <row r="68" spans="1:17" ht="15.75" customHeight="1">
       <c r="A68" s="10"/>
       <c r="B68" s="105" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C68" s="176">
         <f>G68</f>
@@ -12498,7 +15075,7 @@
     <row r="69" spans="1:17" ht="15.75" customHeight="1">
       <c r="A69" s="10"/>
       <c r="B69" s="31" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C69" s="71">
         <f>C61/BS!C70</f>
@@ -12528,12 +15105,12 @@
     <row r="71" spans="1:17" ht="15.75" customHeight="1">
       <c r="A71" s="10"/>
       <c r="B71" s="54" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
       <c r="E71" s="66" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F71" s="56"/>
       <c r="G71" s="37"/>
@@ -12551,7 +15128,7 @@
     <row r="72" spans="1:17" ht="15.75" customHeight="1">
       <c r="A72" s="10"/>
       <c r="B72" s="72" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="C72" s="62"/>
       <c r="D72" s="27"/>
@@ -12572,7 +15149,7 @@
     <row r="73" spans="1:17" ht="15.75" customHeight="1">
       <c r="A73" s="10"/>
       <c r="B73" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C73" s="77">
         <f>ABS(C5/C$4)</f>
@@ -12629,7 +15206,7 @@
     <row r="74" spans="1:17" ht="15.75" customHeight="1">
       <c r="A74" s="10"/>
       <c r="B74" s="31" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C74" s="78">
         <f>ABS(C6/C$4)</f>
@@ -12686,7 +15263,7 @@
     <row r="75" spans="1:17" ht="15.75" customHeight="1">
       <c r="A75" s="10"/>
       <c r="B75" s="8" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C75" s="77">
         <f>ABS(C7/C$4)</f>
@@ -12743,7 +15320,7 @@
     <row r="76" spans="1:17" ht="15.75" customHeight="1">
       <c r="A76" s="10"/>
       <c r="B76" s="29" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C76" s="78">
         <f>ABS(C8/C$4)</f>
@@ -12800,7 +15377,7 @@
     <row r="77" spans="1:17" ht="15.75" customHeight="1">
       <c r="A77" s="10"/>
       <c r="B77" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C77" s="77">
         <f>ABS(C9/C$4)</f>
@@ -12857,7 +15434,7 @@
     <row r="78" spans="1:17" ht="15.75" customHeight="1">
       <c r="A78" s="10"/>
       <c r="B78" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C78" s="88">
         <f>MAX(AVERAGE(G78:J78),C77)</f>
@@ -12865,7 +15442,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="266" t="s">
-        <v>465</v>
+        <v>559</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -12916,7 +15493,7 @@
     <row r="79" spans="1:17" ht="15.75" customHeight="1">
       <c r="A79" s="10"/>
       <c r="B79" s="31" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C79" s="78">
         <f>ABS(C11/C$4)</f>
@@ -12973,7 +15550,7 @@
     <row r="80" spans="1:17" ht="15.75" customHeight="1">
       <c r="A80" s="10"/>
       <c r="B80" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C80" s="77">
         <f>ABS(C12/C$4)</f>
@@ -13030,7 +15607,7 @@
     <row r="81" spans="1:17" ht="15.75" customHeight="1">
       <c r="A81" s="10"/>
       <c r="B81" s="70" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C81" s="78">
         <f>C13/C4</f>
@@ -13087,7 +15664,7 @@
     <row r="82" spans="1:17" ht="15.75" customHeight="1">
       <c r="A82" s="10"/>
       <c r="B82" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C82" s="77">
         <f>ABS(C14/C$4)</f>
@@ -13202,7 +15779,7 @@
     <row r="84" spans="1:17" ht="15.75" customHeight="1">
       <c r="A84" s="10"/>
       <c r="B84" s="41" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C84" s="78">
         <f>ABS(C16/C$4)</f>
@@ -13259,7 +15836,7 @@
     <row r="85" spans="1:17" ht="15.75" customHeight="1">
       <c r="A85" s="10"/>
       <c r="B85" s="27" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C85" s="264">
         <v>0</v>
@@ -13285,7 +15862,7 @@
     <row r="86" spans="1:17" ht="15.75" customHeight="1">
       <c r="A86" s="10"/>
       <c r="B86" s="8" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C86" s="77">
         <v>0</v>
@@ -13309,7 +15886,7 @@
     <row r="87" spans="1:17" ht="15.75" customHeight="1">
       <c r="A87" s="10"/>
       <c r="B87" s="31" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C87" s="78">
         <f>ABS(C19/C$4)</f>
@@ -13370,7 +15947,7 @@
     <row r="89" spans="1:17" ht="15.75" customHeight="1">
       <c r="A89" s="10"/>
       <c r="B89" s="64" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="E89" s="268"/>
     </row>
@@ -13489,7 +16066,7 @@
     <row r="92" spans="1:17" ht="15.75" customHeight="1">
       <c r="A92" s="10"/>
       <c r="B92" s="2" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
@@ -13544,7 +16121,7 @@
     <row r="93" spans="1:17" ht="15.75" customHeight="1">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
-        <v>453</v>
+        <v>433</v>
       </c>
       <c r="C93" s="356">
         <v>0.1</v>
@@ -13565,7 +16142,7 @@
     <row r="94" spans="1:17" ht="15.75" customHeight="1">
       <c r="A94" s="10"/>
       <c r="B94" s="2" t="s">
-        <v>452</v>
+        <v>432</v>
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
@@ -13624,7 +16201,7 @@
     <row r="96" spans="1:17" ht="15.75" customHeight="1">
       <c r="A96" s="10"/>
       <c r="B96" s="157" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C96" s="62"/>
       <c r="D96" s="27"/>
@@ -13645,7 +16222,7 @@
     <row r="97" spans="1:17" ht="15.75" customHeight="1">
       <c r="A97" s="10"/>
       <c r="B97" s="27" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C97" s="77">
         <f>C4/G4-1</f>
@@ -13702,7 +16279,7 @@
     <row r="98" spans="1:17" ht="15.75" customHeight="1">
       <c r="A98" s="10"/>
       <c r="B98" s="70" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C98" s="77">
         <f>C13/G13-1</f>
@@ -13762,12 +16339,12 @@
     <row r="100" spans="1:17" ht="15.75" customHeight="1">
       <c r="A100" s="3"/>
       <c r="B100" s="54" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="C100" s="54"/>
       <c r="D100" s="56"/>
       <c r="E100" s="66" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F100" s="56"/>
       <c r="G100" s="37"/>
@@ -13785,17 +16362,17 @@
     <row r="101" spans="1:17" ht="15.75" customHeight="1">
       <c r="A101" s="10"/>
       <c r="B101" s="64" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E101" s="268"/>
       <c r="G101" s="97" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
     <row r="102" spans="1:17" ht="15.75" customHeight="1">
       <c r="A102" s="10"/>
       <c r="B102" s="26" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C102" s="344">
         <f>BS!G32</f>
@@ -13852,7 +16429,7 @@
     <row r="103" spans="1:17" ht="15.75" customHeight="1">
       <c r="A103" s="10"/>
       <c r="B103" s="93" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="C103" s="345">
         <f>BS!C4</f>
@@ -13909,7 +16486,7 @@
     <row r="104" spans="1:17" ht="15.75" customHeight="1">
       <c r="A104" s="10"/>
       <c r="B104" s="93" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="C104" s="345">
         <f>BS!C6+BS!C7</f>
@@ -13966,7 +16543,7 @@
     <row r="105" spans="1:17" ht="15.75" customHeight="1">
       <c r="A105" s="10"/>
       <c r="B105" s="26" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C105" s="344">
         <f>BS!G30</f>
@@ -14023,7 +16600,7 @@
     <row r="106" spans="1:17" ht="15.75" customHeight="1">
       <c r="A106" s="10"/>
       <c r="B106" s="26" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C106" s="344">
         <f>BS!G27</f>
@@ -14084,14 +16661,14 @@
     <row r="108" spans="1:17" ht="15.75" customHeight="1">
       <c r="A108" s="10"/>
       <c r="B108" s="91" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C108" s="26"/>
       <c r="D108" s="26"/>
       <c r="E108" s="269"/>
       <c r="F108" s="26"/>
       <c r="G108" s="97" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="H108" s="12"/>
       <c r="I108" s="12"/>
@@ -14107,7 +16684,7 @@
     <row r="109" spans="1:17" ht="15.75" customHeight="1">
       <c r="A109" s="10"/>
       <c r="B109" s="26" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="C109" s="94">
         <f>C103/C$4</f>
@@ -14164,7 +16741,7 @@
     <row r="110" spans="1:17" ht="15.75" customHeight="1">
       <c r="A110" s="10"/>
       <c r="B110" s="26" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="C110" s="94">
         <f>C104/C$4</f>
@@ -14221,7 +16798,7 @@
     <row r="111" spans="1:17" ht="15.75" customHeight="1">
       <c r="A111" s="10"/>
       <c r="B111" s="26" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C111" s="94">
         <f>BS!$G$38/C$4</f>
@@ -14252,14 +16829,14 @@
     <row r="113" spans="1:17" ht="15.75" customHeight="1">
       <c r="A113" s="10"/>
       <c r="B113" s="64" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E113" s="268"/>
     </row>
     <row r="114" spans="1:17" ht="15.75" customHeight="1">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
-        <v>388</v>
+        <v>372</v>
       </c>
       <c r="C114" s="169"/>
       <c r="E114" s="268"/>
@@ -14311,7 +16888,7 @@
     <row r="115" spans="1:17" ht="15.75" customHeight="1">
       <c r="A115" s="10"/>
       <c r="B115" s="2" t="s">
-        <v>389</v>
+        <v>373</v>
       </c>
       <c r="C115" s="169"/>
       <c r="E115" s="268"/>
@@ -14367,7 +16944,7 @@
     <row r="117" spans="1:17" ht="15.75" customHeight="1">
       <c r="A117" s="10"/>
       <c r="B117" s="91" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C117" s="55"/>
       <c r="D117" s="55"/>
@@ -14421,7 +16998,7 @@
     <row r="118" spans="1:17" ht="15.75" customHeight="1">
       <c r="A118" s="10"/>
       <c r="B118" s="7" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C118" s="23">
         <f>IF(valuation_method="DDM",C13/(C4+C12),C81)</f>
@@ -14475,7 +17052,7 @@
     </row>
     <row r="119" spans="1:17" ht="15.75" customHeight="1">
       <c r="B119" s="7" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C119" s="42">
         <f>IF(valuation_method="DDM",(C4+C12)/C102,C4/C102)</f>
@@ -14529,7 +17106,7 @@
     </row>
     <row r="120" spans="1:17" ht="15.75" customHeight="1">
       <c r="B120" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C120" s="15">
         <f>C102/C106</f>
@@ -14586,7 +17163,7 @@
     <row r="121" spans="1:17" ht="15.75" customHeight="1">
       <c r="A121" s="10"/>
       <c r="B121" s="70" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="C121" s="102">
         <f>C13/C106</f>
@@ -14662,12 +17239,12 @@
     <row r="123" spans="1:17" ht="15.75" customHeight="1">
       <c r="A123" s="10"/>
       <c r="B123" s="54" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="C123" s="54"/>
       <c r="D123" s="56"/>
       <c r="E123" s="66" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F123" s="56"/>
       <c r="G123" s="37"/>
@@ -14685,7 +17262,7 @@
     <row r="124" spans="1:17" ht="15.75" customHeight="1">
       <c r="A124" s="10"/>
       <c r="B124" s="178" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C124" s="179"/>
       <c r="D124" s="27"/>
@@ -14764,7 +17341,7 @@
     <row r="126" spans="1:17" ht="15.75" customHeight="1">
       <c r="A126" s="10"/>
       <c r="B126" s="27" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
@@ -14820,7 +17397,7 @@
     </row>
     <row r="127" spans="1:17" ht="15.75" customHeight="1">
       <c r="B127" s="2" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
       <c r="C127" s="169"/>
       <c r="G127" s="23">
@@ -15565,7 +18142,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3EAD7ED-D484-47B2-9C7C-1D1BCBEAE5A9}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -15582,32 +18159,32 @@
   <sheetData>
     <row r="2" spans="2:8" ht="13.9">
       <c r="B2" s="36" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
       <c r="H2" s="130" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="2:8" ht="13.15">
       <c r="B3" s="109" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C3" s="107">
         <f>scaling_factor</f>
         <v>1000</v>
       </c>
       <c r="E3" s="109" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="H3" s="120"/>
     </row>
     <row r="4" spans="2:8">
       <c r="B4" s="100" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C4" s="338">
         <f>Normalized_FCF!C19</f>
@@ -15618,7 +18195,7 @@
         <v>HKD</v>
       </c>
       <c r="E4" s="100" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="F4" s="134">
         <f>Terminal_Growth</f>
@@ -15628,7 +18205,7 @@
     </row>
     <row r="5" spans="2:8">
       <c r="B5" s="205" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C5" s="206">
         <f>Equity_Cost</f>
@@ -15639,7 +18216,7 @@
     </row>
     <row r="6" spans="2:8" ht="13.35" customHeight="1">
       <c r="B6" s="149" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="C6" s="347">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
@@ -15649,15 +18226,15 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E6" s="369" t="s">
-        <v>248</v>
-      </c>
-      <c r="F6" s="369"/>
+      <c r="E6" s="375" t="s">
+        <v>245</v>
+      </c>
+      <c r="F6" s="375"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8">
       <c r="B7" s="148" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C7" s="338">
         <f>BS!G31</f>
@@ -15667,13 +18244,13 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E7" s="369"/>
-      <c r="F7" s="369"/>
+      <c r="E7" s="375"/>
+      <c r="F7" s="375"/>
       <c r="H7" s="120"/>
     </row>
     <row r="8" spans="2:8">
       <c r="B8" s="148" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="C8" s="338">
         <f>BS!D66</f>
@@ -15683,13 +18260,13 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E8" s="369"/>
-      <c r="F8" s="369"/>
+      <c r="E8" s="375"/>
+      <c r="F8" s="375"/>
       <c r="H8" s="120"/>
     </row>
     <row r="9" spans="2:8">
       <c r="B9" s="205" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C9" s="348">
         <f>BS!H42</f>
@@ -15699,13 +18276,13 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E9" s="369"/>
-      <c r="F9" s="369"/>
+      <c r="E9" s="375"/>
+      <c r="F9" s="375"/>
       <c r="H9" s="120"/>
     </row>
     <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="149" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="C10" s="347">
         <f>C6-C7+C8+C9</f>
@@ -15719,7 +18296,7 @@
     </row>
     <row r="11" spans="2:8" ht="13.15" thickBot="1">
       <c r="B11" s="207" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C11" s="208">
         <f>Exchange_Rate</f>
@@ -15733,7 +18310,7 @@
     </row>
     <row r="12" spans="2:8" ht="13.5" thickTop="1">
       <c r="B12" s="149" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C12" s="111">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
@@ -15750,7 +18327,7 @@
     </row>
     <row r="14" spans="2:8" ht="13.9">
       <c r="B14" s="36" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="C14" s="37"/>
       <c r="D14" s="37"/>
@@ -15760,13 +18337,13 @@
     </row>
     <row r="15" spans="2:8" ht="13.15">
       <c r="B15" s="119" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="H15" s="120"/>
     </row>
     <row r="16" spans="2:8" ht="13.35" customHeight="1">
       <c r="B16" s="152" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C16" s="161">
         <f>Scenarios!C65</f>
@@ -15776,7 +18353,7 @@
     </row>
     <row r="17" spans="2:17" ht="13.35" customHeight="1">
       <c r="B17" s="118" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C17" s="162">
         <f>Scenarios!C64</f>
@@ -15786,7 +18363,7 @@
     </row>
     <row r="18" spans="2:17" ht="13.35" customHeight="1">
       <c r="B18" s="153" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C18" s="140">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
@@ -15803,19 +18380,19 @@
     </row>
     <row r="20" spans="2:17" ht="13.15">
       <c r="B20" s="128" t="s">
+        <v>104</v>
+      </c>
+      <c r="C20" s="128" t="s">
+        <v>105</v>
+      </c>
+      <c r="D20" s="128" t="s">
+        <v>114</v>
+      </c>
+      <c r="E20" s="128" t="s">
+        <v>106</v>
+      </c>
+      <c r="F20" s="129" t="s">
         <v>107</v>
-      </c>
-      <c r="C20" s="128" t="s">
-        <v>108</v>
-      </c>
-      <c r="D20" s="128" t="s">
-        <v>117</v>
-      </c>
-      <c r="E20" s="128" t="s">
-        <v>109</v>
-      </c>
-      <c r="F20" s="129" t="s">
-        <v>110</v>
       </c>
       <c r="H20" s="120"/>
     </row>
@@ -16581,7 +19158,7 @@
     </row>
     <row r="51" spans="1:17">
       <c r="B51" s="126" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C51" s="123">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
@@ -16604,7 +19181,7 @@
     <row r="52" spans="1:17">
       <c r="C52" s="114"/>
       <c r="E52" s="127" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F52" s="137">
         <f>SUM(F21:F51)</f>
@@ -16618,7 +19195,7 @@
     </row>
     <row r="54" spans="1:17" ht="13.15">
       <c r="B54" s="119" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C54" s="136"/>
       <c r="D54" s="136"/>
@@ -16839,7 +19416,7 @@
     </row>
     <row r="63" spans="1:17" ht="13.15">
       <c r="B63" s="119" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C63" s="338"/>
       <c r="D63" s="114"/>
@@ -17068,19 +19645,19 @@
     </row>
     <row r="73" spans="1:8" ht="13.15">
       <c r="B73" s="171" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C73" s="171" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D73" s="171" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E73" s="172" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="F73" s="172" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="74" spans="1:8">
@@ -17205,20 +19782,20 @@
     </row>
     <row r="80" spans="1:8">
       <c r="B80" s="155" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="C80" s="155" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="81" spans="3:3">
       <c r="C81" s="155" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="82" spans="3:3">
       <c r="C82" s="155" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="92" spans="3:3">
@@ -17325,7 +19902,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A27DB9BF-8D77-49A8-A09B-23E6CA7BEA90}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -17342,32 +19919,32 @@
   <sheetData>
     <row r="2" spans="2:8" ht="13.9">
       <c r="B2" s="36" t="s">
-        <v>439</v>
+        <v>419</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
       <c r="H2" s="130" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="2:8" ht="13.15">
       <c r="B3" s="109" t="s">
-        <v>438</v>
+        <v>418</v>
       </c>
       <c r="C3" s="107">
         <f>scaling_factor</f>
         <v>1000</v>
       </c>
       <c r="E3" s="109" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="H3" s="120"/>
     </row>
     <row r="4" spans="2:8">
       <c r="B4" s="100" t="s">
-        <v>436</v>
+        <v>416</v>
       </c>
       <c r="C4" s="114">
         <f>Normalized_FCF!C91*(1-dividend_tax_rate)</f>
@@ -17378,7 +19955,7 @@
         <v>HKD</v>
       </c>
       <c r="E4" s="100" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="F4" s="134">
         <f>Thesis!E22</f>
@@ -17388,7 +19965,7 @@
     </row>
     <row r="5" spans="2:8">
       <c r="B5" s="205" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C5" s="206">
         <f>Equity_Cost</f>
@@ -17399,7 +19976,7 @@
     </row>
     <row r="6" spans="2:8" ht="13.35" customHeight="1">
       <c r="B6" s="149" t="s">
-        <v>437</v>
+        <v>417</v>
       </c>
       <c r="C6" s="319">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
@@ -17409,13 +19986,13 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E6" s="369"/>
-      <c r="F6" s="369"/>
+      <c r="E6" s="375"/>
+      <c r="F6" s="375"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8" ht="13.15">
       <c r="B7" s="149" t="s">
-        <v>440</v>
+        <v>420</v>
       </c>
       <c r="C7" s="111">
         <f>(C6*scaling_factor)/Common_Shares*Exchange_Rate</f>
@@ -17432,7 +20009,7 @@
     </row>
     <row r="9" spans="2:8" ht="13.9">
       <c r="B9" s="36" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="C9" s="37"/>
       <c r="D9" s="37"/>
@@ -17442,13 +20019,13 @@
     </row>
     <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="119" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="H10" s="120"/>
     </row>
     <row r="11" spans="2:8" ht="13.35" customHeight="1">
       <c r="B11" s="152" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C11" s="161">
         <f>Scenarios!C65</f>
@@ -17458,7 +20035,7 @@
     </row>
     <row r="12" spans="2:8" ht="13.35" customHeight="1">
       <c r="B12" s="118" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C12" s="162">
         <f>Scenarios!C64</f>
@@ -17468,7 +20045,7 @@
     </row>
     <row r="13" spans="2:8" ht="13.35" customHeight="1">
       <c r="B13" s="153" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C13" s="140">
         <f>F47/Common_Shares*scaling_factor</f>
@@ -17485,19 +20062,19 @@
     </row>
     <row r="15" spans="2:8" ht="13.15">
       <c r="B15" s="128" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C15" s="128" t="s">
-        <v>442</v>
+        <v>422</v>
       </c>
       <c r="D15" s="128" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E15" s="128" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F15" s="129" t="s">
-        <v>441</v>
+        <v>421</v>
       </c>
       <c r="H15" s="120"/>
     </row>
@@ -18163,7 +20740,7 @@
     </row>
     <row r="46" spans="2:8">
       <c r="B46" s="126" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C46" s="123">
         <f>C$16*(1+F4)^$C$12/Equity_Cost</f>
@@ -18186,7 +20763,7 @@
     <row r="47" spans="2:8">
       <c r="C47" s="114"/>
       <c r="E47" s="127" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F47" s="137">
         <f>SUM(F16:F46)</f>
@@ -18200,7 +20777,7 @@
     </row>
     <row r="49" spans="1:8" ht="13.15">
       <c r="B49" s="119" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C49" s="136"/>
       <c r="D49" s="136"/>
@@ -18371,7 +20948,7 @@
     </row>
     <row r="58" spans="1:8" ht="13.15">
       <c r="B58" s="119" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C58" s="114"/>
       <c r="D58" s="114"/>
@@ -18590,19 +21167,19 @@
     </row>
     <row r="68" spans="1:8" ht="13.15">
       <c r="B68" s="171" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C68" s="171" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D68" s="171" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E68" s="172" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="F68" s="172" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="69" spans="1:8">
@@ -18727,20 +21304,20 @@
     </row>
     <row r="75" spans="1:8">
       <c r="B75" s="155" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="C75" s="155" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="76" spans="1:8">
       <c r="C76" s="155" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="77" spans="1:8">
       <c r="C77" s="155" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="87" spans="3:3">
@@ -18776,7 +21353,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
   <dimension ref="B2:I110"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
@@ -18791,20 +21368,20 @@
   <sheetData>
     <row r="2" spans="2:9" ht="13.9">
       <c r="B2" s="36" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
       <c r="H2" s="248" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="I2" s="249"/>
     </row>
     <row r="3" spans="2:9" ht="13.15">
       <c r="B3" s="159" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="H3" s="247">
         <v>0</v>
@@ -18816,14 +21393,14 @@
     </row>
     <row r="4" spans="2:9">
       <c r="B4" s="152" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C4" s="120">
         <v>3</v>
       </c>
       <c r="D4" s="120"/>
       <c r="E4" s="155" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="F4" s="155"/>
       <c r="H4" s="247">
@@ -18845,14 +21422,14 @@
     </row>
     <row r="6" spans="2:9" ht="13.15">
       <c r="B6" s="159" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C6" s="107">
         <f>DCF!C3</f>
         <v>1000</v>
       </c>
       <c r="E6" s="100" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="F6" s="100"/>
       <c r="H6" s="247">
@@ -18865,7 +21442,7 @@
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
       <c r="B7" s="100" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="C7" s="338">
         <f>Normalized_FCF!G8</f>
@@ -18875,11 +21452,11 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E7" s="371" t="str">
+      <c r="E7" s="377" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 5-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 10-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 首钢资源(0639.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="371"/>
+      <c r="F7" s="377"/>
       <c r="H7" s="247">
         <v>4</v>
       </c>
@@ -18890,7 +21467,7 @@
     </row>
     <row r="8" spans="2:9">
       <c r="B8" s="100" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C8" s="338">
         <f>Normalized_FCF!G19</f>
@@ -18900,8 +21477,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E8" s="371"/>
-      <c r="F8" s="371"/>
+      <c r="E8" s="377"/>
+      <c r="F8" s="377"/>
       <c r="H8" s="247">
         <v>5</v>
       </c>
@@ -18912,7 +21489,7 @@
     </row>
     <row r="9" spans="2:9">
       <c r="B9" s="100" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C9" s="338">
         <f>Normalized_FCF!C19</f>
@@ -18922,8 +21499,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E9" s="371"/>
-      <c r="F9" s="371"/>
+      <c r="E9" s="377"/>
+      <c r="F9" s="377"/>
       <c r="H9" s="247">
         <v>6</v>
       </c>
@@ -18933,8 +21510,8 @@
       </c>
     </row>
     <row r="10" spans="2:9">
-      <c r="E10" s="371"/>
-      <c r="F10" s="371"/>
+      <c r="E10" s="377"/>
+      <c r="F10" s="377"/>
       <c r="H10" s="247">
         <v>7</v>
       </c>
@@ -18945,10 +21522,10 @@
     </row>
     <row r="11" spans="2:9" ht="13.15">
       <c r="B11" s="159" t="s">
-        <v>443</v>
-      </c>
-      <c r="E11" s="371"/>
-      <c r="F11" s="371"/>
+        <v>423</v>
+      </c>
+      <c r="E11" s="377"/>
+      <c r="F11" s="377"/>
       <c r="H11" s="247">
         <v>8</v>
       </c>
@@ -18959,15 +21536,15 @@
     </row>
     <row r="12" spans="2:9">
       <c r="B12" s="118" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C12" s="158">
         <f ca="1">(Normalized_FCF!G4/OFFSET(Normalized_FCF!G4, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.1059288114314666</v>
       </c>
       <c r="D12" s="158"/>
-      <c r="E12" s="371"/>
-      <c r="F12" s="371"/>
+      <c r="E12" s="377"/>
+      <c r="F12" s="377"/>
       <c r="H12" s="247">
         <v>9</v>
       </c>
@@ -18978,14 +21555,14 @@
     </row>
     <row r="13" spans="2:9">
       <c r="B13" s="148" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C13" s="158">
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.1663504856430581</v>
       </c>
-      <c r="E13" s="371"/>
-      <c r="F13" s="371"/>
+      <c r="E13" s="377"/>
+      <c r="F13" s="377"/>
       <c r="H13" s="247">
         <v>10</v>
       </c>
@@ -18996,18 +21573,18 @@
     </row>
     <row r="14" spans="2:9">
       <c r="B14" s="100" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C14" s="158">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.18299448813777219</v>
       </c>
-      <c r="E14" s="371"/>
-      <c r="F14" s="371"/>
+      <c r="E14" s="377"/>
+      <c r="F14" s="377"/>
     </row>
     <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C16" s="37"/>
       <c r="D16" s="37"/>
@@ -19016,38 +21593,38 @@
     </row>
     <row r="17" spans="2:6" ht="13.15">
       <c r="B17" s="109" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E17" s="159" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
     </row>
     <row r="18" spans="2:6">
       <c r="B18" s="152" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C18" s="150">
         <v>5</v>
       </c>
-      <c r="E18" s="371" t="s">
-        <v>327</v>
-      </c>
-      <c r="F18" s="372"/>
+      <c r="E18" s="377" t="s">
+        <v>321</v>
+      </c>
+      <c r="F18" s="378"/>
     </row>
     <row r="19" spans="2:6">
-      <c r="E19" s="372"/>
-      <c r="F19" s="372"/>
+      <c r="E19" s="378"/>
+      <c r="F19" s="378"/>
     </row>
     <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="159" t="s">
-        <v>302</v>
-      </c>
-      <c r="E20" s="372"/>
-      <c r="F20" s="372"/>
+        <v>298</v>
+      </c>
+      <c r="E20" s="378"/>
+      <c r="F20" s="378"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
@@ -19057,12 +21634,12 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E21" s="372"/>
-      <c r="F21" s="372"/>
+      <c r="E21" s="378"/>
+      <c r="F21" s="378"/>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="C22" s="160">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
@@ -19072,44 +21649,44 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E22" s="372"/>
-      <c r="F22" s="372"/>
+      <c r="E22" s="378"/>
+      <c r="F22" s="378"/>
     </row>
     <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="159" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E24" s="159" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F24" s="159"/>
     </row>
     <row r="25" spans="2:6">
       <c r="B25" s="152" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C25" s="166">
         <f>C18</f>
         <v>5</v>
       </c>
       <c r="D25" s="163"/>
-      <c r="E25" s="370"/>
-      <c r="F25" s="370"/>
+      <c r="E25" s="376"/>
+      <c r="F25" s="376"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="118" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C26" s="164">
         <v>0</v>
       </c>
       <c r="D26" s="164"/>
-      <c r="E26" s="370"/>
-      <c r="F26" s="370"/>
+      <c r="E26" s="376"/>
+      <c r="F26" s="376"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C27" s="160">
         <f>IF(valuation_method="DCF",DCF!E76,DDM!E71)</f>
@@ -19119,55 +21696,55 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E27" s="370"/>
-      <c r="F27" s="370"/>
+      <c r="E27" s="376"/>
+      <c r="F27" s="376"/>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C28" s="165">
         <v>0.6</v>
       </c>
       <c r="D28" s="165"/>
-      <c r="E28" s="370"/>
-      <c r="F28" s="370"/>
+      <c r="E28" s="376"/>
+      <c r="F28" s="376"/>
     </row>
     <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="159" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="E30" s="159" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F30" s="159"/>
     </row>
     <row r="31" spans="2:6">
       <c r="B31" s="152" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C31" s="166">
         <f>C18</f>
         <v>5</v>
       </c>
       <c r="D31" s="163"/>
-      <c r="E31" s="370"/>
-      <c r="F31" s="370"/>
+      <c r="E31" s="376"/>
+      <c r="F31" s="376"/>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="118" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C32" s="164">
         <v>-0.02</v>
       </c>
       <c r="D32" s="164"/>
-      <c r="E32" s="370"/>
-      <c r="F32" s="370"/>
+      <c r="E32" s="376"/>
+      <c r="F32" s="376"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C33" s="160">
         <f>IF(valuation_method="DCF",DCF!E77,DDM!E72)</f>
@@ -19177,55 +21754,55 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E33" s="370"/>
-      <c r="F33" s="370"/>
+      <c r="E33" s="376"/>
+      <c r="F33" s="376"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C34" s="165">
         <v>0.2</v>
       </c>
       <c r="D34" s="165"/>
-      <c r="E34" s="370"/>
-      <c r="F34" s="370"/>
+      <c r="E34" s="376"/>
+      <c r="F34" s="376"/>
     </row>
     <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="159" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="E36" s="159" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F36" s="159"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="152" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C37" s="166">
         <f>C18</f>
         <v>5</v>
       </c>
       <c r="D37" s="163"/>
-      <c r="E37" s="370"/>
-      <c r="F37" s="370"/>
+      <c r="E37" s="376"/>
+      <c r="F37" s="376"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="118" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C38" s="164">
         <v>0.02</v>
       </c>
       <c r="D38" s="164"/>
-      <c r="E38" s="370"/>
-      <c r="F38" s="370"/>
+      <c r="E38" s="376"/>
+      <c r="F38" s="376"/>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C39" s="160">
         <f>IF(valuation_method="DCF",DCF!E75,DDM!E70)</f>
@@ -19235,24 +21812,24 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E39" s="370"/>
-      <c r="F39" s="370"/>
+      <c r="E39" s="376"/>
+      <c r="F39" s="376"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C40" s="167">
         <f>1-C28-C34</f>
         <v>0.2</v>
       </c>
       <c r="D40" s="165"/>
-      <c r="E40" s="370"/>
-      <c r="F40" s="370"/>
+      <c r="E40" s="376"/>
+      <c r="F40" s="376"/>
     </row>
     <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C42" s="154">
         <f>C27*C28+C33*C34+C39*C40</f>
@@ -19265,7 +21842,7 @@
     </row>
     <row r="44" spans="2:6" ht="13.9">
       <c r="B44" s="36" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C44" s="37"/>
       <c r="D44" s="37"/>
@@ -19274,12 +21851,12 @@
     </row>
     <row r="45" spans="2:6" ht="13.15">
       <c r="B45" s="109" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="46" spans="2:6">
       <c r="B46" s="152" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C46" s="150">
         <v>10</v>
@@ -19294,39 +21871,39 @@
     </row>
     <row r="48" spans="2:6" ht="13.15">
       <c r="B48" s="159" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="E48" s="159" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F48" s="159"/>
     </row>
     <row r="49" spans="2:6" ht="12.75" customHeight="1">
       <c r="B49" s="152" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C49" s="166">
         <f>C46</f>
         <v>10</v>
       </c>
       <c r="D49" s="163"/>
-      <c r="E49" s="370"/>
-      <c r="F49" s="370"/>
+      <c r="E49" s="376"/>
+      <c r="F49" s="376"/>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="118" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C50" s="164">
         <v>-0.04</v>
       </c>
       <c r="D50" s="164"/>
-      <c r="E50" s="370"/>
-      <c r="F50" s="370"/>
+      <c r="E50" s="376"/>
+      <c r="F50" s="376"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C51" s="160">
         <f>IF(valuation_method="DCF",DCF!E78,DDM!E73)</f>
@@ -19336,55 +21913,55 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E51" s="370"/>
-      <c r="F51" s="370"/>
+      <c r="E51" s="376"/>
+      <c r="F51" s="376"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C52" s="165">
         <v>0.05</v>
       </c>
       <c r="D52" s="165"/>
-      <c r="E52" s="370"/>
-      <c r="F52" s="370"/>
+      <c r="E52" s="376"/>
+      <c r="F52" s="376"/>
     </row>
     <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="159" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="E54" s="159" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F54" s="159"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="152" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C55" s="166">
         <f>C46</f>
         <v>10</v>
       </c>
       <c r="D55" s="163"/>
-      <c r="E55" s="370"/>
-      <c r="F55" s="370"/>
+      <c r="E55" s="376"/>
+      <c r="F55" s="376"/>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="118" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C56" s="164">
         <v>0.04</v>
       </c>
       <c r="D56" s="164"/>
-      <c r="E56" s="370"/>
-      <c r="F56" s="370"/>
+      <c r="E56" s="376"/>
+      <c r="F56" s="376"/>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C57" s="160">
         <f>IF(valuation_method="DCF",DCF!E74,DDM!E69)</f>
@@ -19394,23 +21971,23 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E57" s="370"/>
-      <c r="F57" s="370"/>
+      <c r="E57" s="376"/>
+      <c r="F57" s="376"/>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C58" s="165">
         <v>0.05</v>
       </c>
       <c r="D58" s="165"/>
-      <c r="E58" s="370"/>
-      <c r="F58" s="370"/>
+      <c r="E58" s="376"/>
+      <c r="F58" s="376"/>
     </row>
     <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C60" s="154">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
@@ -19421,7 +21998,7 @@
         <v>HKD</v>
       </c>
       <c r="E60" s="100" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="F60" s="277">
         <f>Thesis!F28</f>
@@ -19430,7 +22007,7 @@
     </row>
     <row r="62" spans="2:6" ht="13.9">
       <c r="B62" s="36" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="C62" s="37"/>
       <c r="D62" s="37"/>
@@ -19439,15 +22016,15 @@
     </row>
     <row r="63" spans="2:6" ht="13.15">
       <c r="B63" s="109" t="s">
+        <v>299</v>
+      </c>
+      <c r="E63" s="252" t="s">
         <v>303</v>
-      </c>
-      <c r="E63" s="252" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="64" spans="2:6">
       <c r="B64" s="152" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C64" s="166">
         <f>C18</f>
@@ -19455,24 +22032,24 @@
       </c>
       <c r="D64" s="150"/>
       <c r="E64" s="251" t="s">
-        <v>392</v>
+        <v>376</v>
       </c>
     </row>
     <row r="65" spans="2:6">
       <c r="B65" s="118" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C65" s="151">
         <v>1.28005644478456E-3</v>
       </c>
       <c r="D65" s="151"/>
       <c r="E65" s="251" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
     </row>
     <row r="66" spans="2:6">
       <c r="B66" s="100" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C66" s="160">
         <f>IF(valuation_method="DCF",DCF!C18,DDM!C13)</f>
@@ -19483,20 +22060,20 @@
         <v>HKD</v>
       </c>
       <c r="E66" s="251" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
     </row>
     <row r="68" spans="2:6" ht="13.15">
       <c r="B68" s="109" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="E68" s="252" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
     </row>
     <row r="69" spans="2:6">
       <c r="B69" s="100" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="C69" s="244" t="str">
         <f>IF(C60&lt;C22,"Y","N")</f>
@@ -19506,19 +22083,19 @@
     </row>
     <row r="70" spans="2:6">
       <c r="B70" s="100" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="C70" s="244" t="str">
         <f>IF(C69="Y","N",IF(C65&gt;8%,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="E70" s="251" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
     </row>
     <row r="71" spans="2:6">
       <c r="B71" s="100" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="C71" s="244" t="str">
         <f>IF(C65&gt;8%,"Y","N")</f>
@@ -19528,14 +22105,14 @@
     </row>
     <row r="72" spans="2:6">
       <c r="B72" s="100" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="C72" s="243" t="str">
         <f>IF(F72&gt;50%,"Y","N")</f>
         <v>N</v>
       </c>
       <c r="E72" s="134" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="F72" s="291">
         <f>BS!D89/C60</f>
@@ -19544,7 +22121,7 @@
     </row>
     <row r="74" spans="2:6" ht="13.9">
       <c r="B74" s="36" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C74" s="37"/>
       <c r="D74" s="37"/>
@@ -19553,12 +22130,12 @@
     </row>
     <row r="75" spans="2:6" ht="13.15">
       <c r="B75" s="109" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="76" spans="2:6">
       <c r="B76" s="246" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="C76" s="245">
         <f>F60</f>
@@ -19568,7 +22145,7 @@
     </row>
     <row r="77" spans="2:6">
       <c r="B77" s="100" t="s">
-        <v>455</v>
+        <v>435</v>
       </c>
       <c r="C77" s="173">
         <f>Normalized_FCF!C90*(1-dividend_tax_rate)</f>
@@ -19581,12 +22158,12 @@
     </row>
     <row r="79" spans="2:6" ht="13.15">
       <c r="B79" s="109" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
     </row>
     <row r="80" spans="2:6">
       <c r="B80" s="148" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="C80" s="167">
         <f>Thesis!F29</f>
@@ -19595,7 +22172,7 @@
     </row>
     <row r="81" spans="2:8">
       <c r="B81" s="100" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
@@ -19607,7 +22184,7 @@
     </row>
     <row r="82" spans="2:8">
       <c r="B82" s="100" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C82" s="116">
         <f>C60/(1+C80)^C76</f>
@@ -19617,7 +22194,7 @@
     </row>
     <row r="83" spans="2:8" ht="13.15">
       <c r="B83" s="110" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C83" s="111">
         <f>C81+C82</f>
@@ -19628,7 +22205,7 @@
         <v>HKD</v>
       </c>
       <c r="E83" s="146" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F83" s="291">
         <f>(1-C83/C60)</f>
@@ -19640,12 +22217,12 @@
     </row>
     <row r="85" spans="2:8" ht="13.15">
       <c r="B85" s="109" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
     </row>
     <row r="86" spans="2:8">
       <c r="B86" s="148" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
@@ -19658,7 +22235,7 @@
     </row>
     <row r="87" spans="2:8" ht="13.15">
       <c r="B87" s="100" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
@@ -19670,12 +22247,12 @@
     </row>
     <row r="89" spans="2:8" ht="13.15">
       <c r="B89" s="109" t="s">
-        <v>409</v>
+        <v>392</v>
       </c>
     </row>
     <row r="90" spans="2:8">
       <c r="B90" s="148" t="s">
-        <v>410</v>
+        <v>393</v>
       </c>
       <c r="C90" s="167">
         <f>Thesis!F30</f>
@@ -19684,7 +22261,7 @@
     </row>
     <row r="91" spans="2:8">
       <c r="B91" s="100" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C91" s="116">
         <f>PV(C90, C76, -C77, 0)</f>
@@ -19696,7 +22273,7 @@
     </row>
     <row r="92" spans="2:8">
       <c r="B92" s="100" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C92" s="116">
         <f>C60/(1+C90)^C76</f>
@@ -19706,7 +22283,7 @@
     </row>
     <row r="93" spans="2:8" ht="13.15">
       <c r="B93" s="110" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C93" s="111">
         <f>C91+C92</f>
@@ -19717,7 +22294,7 @@
         <v>HKD</v>
       </c>
       <c r="E93" s="146" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F93" s="291">
         <f>(1-C93/C60)</f>
@@ -19726,14 +22303,14 @@
     </row>
     <row r="95" spans="2:8" ht="13.15">
       <c r="B95" s="109" t="s">
-        <v>394</v>
+        <v>378</v>
       </c>
       <c r="G95" s="2"/>
       <c r="H95" s="281"/>
     </row>
     <row r="96" spans="2:8">
       <c r="B96" s="148" t="s">
-        <v>400</v>
+        <v>383</v>
       </c>
       <c r="C96" s="134">
         <f>Thesis!F31</f>
@@ -19744,7 +22321,7 @@
     </row>
     <row r="97" spans="2:8">
       <c r="B97" s="100" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C97" s="116">
         <f>PV(C96, C76, -C77, 0)</f>
@@ -19756,7 +22333,7 @@
     </row>
     <row r="98" spans="2:8">
       <c r="B98" s="100" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C98" s="116">
         <f>C60/(1+C96)^C76</f>
@@ -19768,17 +22345,17 @@
     </row>
     <row r="99" spans="2:8" ht="13.15">
       <c r="B99" s="110" t="s">
-        <v>395</v>
+        <v>379</v>
       </c>
       <c r="C99" s="111">
         <f>C97+C98</f>
         <v>4.3130669791905083</v>
       </c>
       <c r="D99" t="s">
-        <v>393</v>
+        <v>377</v>
       </c>
       <c r="E99" s="146" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F99" s="291">
         <f>(1-C99/C60)</f>
@@ -19790,12 +22367,12 @@
     </row>
     <row r="101" spans="2:8" ht="13.15">
       <c r="B101" s="109" t="s">
-        <v>418</v>
+        <v>398</v>
       </c>
     </row>
     <row r="102" spans="2:8">
       <c r="B102" s="148" t="s">
-        <v>417</v>
+        <v>397</v>
       </c>
       <c r="C102" s="134">
         <f>Thesis!F32</f>
@@ -19804,7 +22381,7 @@
     </row>
     <row r="103" spans="2:8">
       <c r="B103" s="100" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C103" s="116">
         <f>PV(C102, C76, -C77, 0)</f>
@@ -19814,7 +22391,7 @@
     </row>
     <row r="104" spans="2:8">
       <c r="B104" s="100" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C104" s="116">
         <f>C60/(1+C102)^C76</f>
@@ -19824,17 +22401,17 @@
     </row>
     <row r="105" spans="2:8" ht="13.15">
       <c r="B105" s="110" t="s">
-        <v>395</v>
+        <v>379</v>
       </c>
       <c r="C105" s="111">
         <f>C103+C104</f>
         <v>3.8666759160925035</v>
       </c>
       <c r="D105" t="s">
-        <v>393</v>
+        <v>377</v>
       </c>
       <c r="E105" s="146" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F105" s="291">
         <f>(1-C105/C66)</f>
@@ -19846,32 +22423,32 @@
     </row>
     <row r="107" spans="2:8" ht="14.65">
       <c r="E107" s="285" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="F107" s="282"/>
     </row>
     <row r="108" spans="2:8" ht="13.9">
       <c r="E108" s="278" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="F108" s="283" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
     </row>
     <row r="109" spans="2:8" ht="13.9">
       <c r="E109" s="279" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="F109" s="283" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
     </row>
     <row r="110" spans="2:8" ht="13.9">
       <c r="E110" s="280" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="F110" s="284" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
   </sheetData>
@@ -19890,24 +22467,24 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0F5CFC9-8CA7-4AC0-A4D1-2C83D9428848}">
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1687E01B-0970-4659-AAA7-C41D486D7CC3}">
   <dimension ref="B2:E2"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="2.59765625" style="360" customWidth="1"/>
-    <col min="2" max="2" width="22.73046875" style="360" customWidth="1"/>
-    <col min="3" max="5" width="20.73046875" style="360" customWidth="1"/>
-    <col min="6" max="16384" width="9.06640625" style="360"/>
+    <col min="1" max="1" width="2.59765625" style="381" customWidth="1"/>
+    <col min="2" max="2" width="22.73046875" style="381" customWidth="1"/>
+    <col min="3" max="5" width="20.73046875" style="381" customWidth="1"/>
+    <col min="6" max="16384" width="9.06640625" style="381"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:5" ht="13.9">
-      <c r="B2" s="358" t="s">
-        <v>456</v>
-      </c>
-      <c r="C2" s="359"/>
-      <c r="D2" s="359"/>
-      <c r="E2" s="359"/>
+      <c r="B2" s="379" t="s">
+        <v>436</v>
+      </c>
+      <c r="C2" s="380"/>
+      <c r="D2" s="380"/>
+      <c r="E2" s="380"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/financial_models/opportunities/0639.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0639.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D00259FC-FAE8-4390-A867-C30EF65C19A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{890F8B47-75E6-4793-9468-14B8F59B50AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4751,8 +4751,22 @@
     <xf numFmtId="4" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="1" xfId="2"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4763,16 +4777,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
@@ -4787,11 +4792,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="1" xfId="2"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="C12" s="366">
         <f>Market_Price</f>
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C14" s="35">
         <f>投资主题!C12*Common_Shares/1000000</f>
-        <v>13338.5923174</v>
+        <v>13389.5029751</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",投资主题!D12*Common_Shares/1000000)</f>
@@ -5443,7 +5443,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.28412064787572122</v>
+        <v>0.28236042533963035</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -5574,13 +5574,13 @@
       <c r="F36" s="371"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="374" t="s">
+      <c r="B37" s="372" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="374"/>
-      <c r="D37" s="374"/>
-      <c r="E37" s="374"/>
-      <c r="F37" s="374"/>
+      <c r="C37" s="372"/>
+      <c r="D37" s="372"/>
+      <c r="E37" s="372"/>
+      <c r="F37" s="372"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -5592,13 +5592,13 @@
       </c>
     </row>
     <row r="40" spans="1:6">
-      <c r="B40" s="367" t="s">
+      <c r="B40" s="370" t="s">
         <v>494</v>
       </c>
-      <c r="C40" s="367"/>
-      <c r="D40" s="367"/>
-      <c r="E40" s="367"/>
-      <c r="F40" s="367"/>
+      <c r="C40" s="370"/>
+      <c r="D40" s="370"/>
+      <c r="E40" s="370"/>
+      <c r="F40" s="370"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -5618,13 +5618,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="367" t="s">
+      <c r="B43" s="370" t="s">
         <v>495</v>
       </c>
-      <c r="C43" s="367"/>
-      <c r="D43" s="367"/>
-      <c r="E43" s="367"/>
-      <c r="F43" s="367"/>
+      <c r="C43" s="370"/>
+      <c r="D43" s="370"/>
+      <c r="E43" s="370"/>
+      <c r="F43" s="370"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -5653,13 +5653,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="367" t="s">
+      <c r="B47" s="370" t="s">
         <v>496</v>
       </c>
-      <c r="C47" s="367"/>
-      <c r="D47" s="367"/>
-      <c r="E47" s="367"/>
-      <c r="F47" s="367"/>
+      <c r="C47" s="370"/>
+      <c r="D47" s="370"/>
+      <c r="E47" s="370"/>
+      <c r="F47" s="370"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -5675,13 +5675,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="367" t="s">
+      <c r="B50" s="370" t="s">
         <v>497</v>
       </c>
-      <c r="C50" s="367"/>
-      <c r="D50" s="367"/>
-      <c r="E50" s="367"/>
-      <c r="F50" s="367"/>
+      <c r="C50" s="370"/>
+      <c r="D50" s="370"/>
+      <c r="E50" s="370"/>
+      <c r="F50" s="370"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -5745,13 +5745,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="367" t="s">
+      <c r="B58" s="370" t="s">
         <v>237</v>
       </c>
-      <c r="C58" s="367"/>
-      <c r="D58" s="367"/>
-      <c r="E58" s="367"/>
-      <c r="F58" s="367"/>
+      <c r="C58" s="370"/>
+      <c r="D58" s="370"/>
+      <c r="E58" s="370"/>
+      <c r="F58" s="370"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -5767,7 +5767,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="367" t="s">
+      <c r="B61" s="370" t="s">
         <v>499</v>
       </c>
       <c r="C61" s="373"/>
@@ -5838,7 +5838,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>8.1854774938882657E-2</v>
+        <v>8.1543540053183483E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -5848,7 +5848,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>0.10305343511450382</v>
+        <v>0.10266159695817492</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>503</v>
@@ -5948,13 +5948,13 @@
       <c r="F80" s="371"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="374" t="s">
+      <c r="B81" s="372" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="374"/>
-      <c r="D81" s="374"/>
-      <c r="E81" s="374"/>
-      <c r="F81" s="374"/>
+      <c r="C81" s="372"/>
+      <c r="D81" s="372"/>
+      <c r="E81" s="372"/>
+      <c r="F81" s="372"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -6242,13 +6242,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="367" t="s">
+      <c r="B123" s="370" t="s">
         <v>519</v>
       </c>
-      <c r="C123" s="367"/>
-      <c r="D123" s="367"/>
-      <c r="E123" s="367"/>
-      <c r="F123" s="367"/>
+      <c r="C123" s="370"/>
+      <c r="D123" s="370"/>
+      <c r="E123" s="370"/>
+      <c r="F123" s="370"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -6391,13 +6391,13 @@
       </c>
     </row>
     <row r="134" spans="1:6">
-      <c r="B134" s="369" t="s">
+      <c r="B134" s="375" t="s">
         <v>524</v>
       </c>
-      <c r="C134" s="369"/>
-      <c r="D134" s="369"/>
-      <c r="E134" s="369"/>
-      <c r="F134" s="369"/>
+      <c r="C134" s="375"/>
+      <c r="D134" s="375"/>
+      <c r="E134" s="375"/>
+      <c r="F134" s="375"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -6410,13 +6410,13 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="370" t="s">
+      <c r="B138" s="376" t="s">
         <v>526</v>
       </c>
-      <c r="C138" s="370"/>
-      <c r="D138" s="370"/>
-      <c r="E138" s="370"/>
-      <c r="F138" s="370"/>
+      <c r="C138" s="376"/>
+      <c r="D138" s="376"/>
+      <c r="E138" s="376"/>
+      <c r="F138" s="376"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
       <c r="B139" s="371" t="s">
@@ -6758,7 +6758,7 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="372" t="s">
+      <c r="B179" s="377" t="s">
         <v>534</v>
       </c>
       <c r="C179" s="371"/>
@@ -6801,13 +6801,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B188" s="367" t="s">
+      <c r="B188" s="370" t="s">
         <v>541</v>
       </c>
-      <c r="C188" s="367"/>
-      <c r="D188" s="367"/>
-      <c r="E188" s="367"/>
-      <c r="F188" s="367"/>
+      <c r="C188" s="370"/>
+      <c r="D188" s="370"/>
+      <c r="E188" s="370"/>
+      <c r="F188" s="370"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -6815,22 +6815,22 @@
       </c>
     </row>
     <row r="191" spans="1:6">
-      <c r="B191" s="368" t="s">
+      <c r="B191" s="374" t="s">
         <v>543</v>
       </c>
-      <c r="C191" s="368"/>
-      <c r="D191" s="368"/>
-      <c r="E191" s="368"/>
-      <c r="F191" s="368"/>
+      <c r="C191" s="374"/>
+      <c r="D191" s="374"/>
+      <c r="E191" s="374"/>
+      <c r="F191" s="374"/>
     </row>
     <row r="192" spans="1:6">
-      <c r="B192" s="368" t="s">
+      <c r="B192" s="374" t="s">
         <v>544</v>
       </c>
-      <c r="C192" s="368"/>
-      <c r="D192" s="368"/>
-      <c r="E192" s="368"/>
-      <c r="F192" s="368"/>
+      <c r="C192" s="374"/>
+      <c r="D192" s="374"/>
+      <c r="E192" s="374"/>
+      <c r="F192" s="374"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -6854,12 +6854,15 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B47:F47"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B138:F138"/>
+    <mergeCell ref="B139:F139"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B182:F182"/>
     <mergeCell ref="B116:F116"/>
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B58:F58"/>
@@ -6872,15 +6875,12 @@
     <mergeCell ref="B90:F90"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B138:F138"/>
-    <mergeCell ref="B139:F139"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B43:F43"/>
   </mergeCells>
   <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">
@@ -7023,7 +7023,7 @@
         <v>463</v>
       </c>
       <c r="C12" s="50">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -7044,7 +7044,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>13338.5923174</v>
+        <v>13389.5029751</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -7170,7 +7170,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.28412064787572122</v>
+        <v>0.28236042533963035</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -7296,13 +7296,13 @@
       <c r="F36" s="371"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="374" t="s">
+      <c r="B37" s="372" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="374"/>
-      <c r="D37" s="374"/>
-      <c r="E37" s="374"/>
-      <c r="F37" s="374"/>
+      <c r="C37" s="372"/>
+      <c r="D37" s="372"/>
+      <c r="E37" s="372"/>
+      <c r="F37" s="372"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -7314,13 +7314,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="367" t="s">
+      <c r="B40" s="370" t="s">
         <v>227</v>
       </c>
-      <c r="C40" s="367"/>
-      <c r="D40" s="367"/>
-      <c r="E40" s="367"/>
-      <c r="F40" s="367"/>
+      <c r="C40" s="370"/>
+      <c r="D40" s="370"/>
+      <c r="E40" s="370"/>
+      <c r="F40" s="370"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -7340,13 +7340,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="367" t="s">
+      <c r="B43" s="370" t="s">
         <v>229</v>
       </c>
-      <c r="C43" s="367"/>
-      <c r="D43" s="367"/>
-      <c r="E43" s="367"/>
-      <c r="F43" s="367"/>
+      <c r="C43" s="370"/>
+      <c r="D43" s="370"/>
+      <c r="E43" s="370"/>
+      <c r="F43" s="370"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -7375,13 +7375,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="367" t="s">
+      <c r="B47" s="370" t="s">
         <v>232</v>
       </c>
-      <c r="C47" s="367"/>
-      <c r="D47" s="367"/>
-      <c r="E47" s="367"/>
-      <c r="F47" s="367"/>
+      <c r="C47" s="370"/>
+      <c r="D47" s="370"/>
+      <c r="E47" s="370"/>
+      <c r="F47" s="370"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -7397,13 +7397,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="367" t="s">
+      <c r="B50" s="370" t="s">
         <v>236</v>
       </c>
-      <c r="C50" s="367"/>
-      <c r="D50" s="367"/>
-      <c r="E50" s="367"/>
-      <c r="F50" s="367"/>
+      <c r="C50" s="370"/>
+      <c r="D50" s="370"/>
+      <c r="E50" s="370"/>
+      <c r="F50" s="370"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -7467,13 +7467,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="367" t="s">
+      <c r="B58" s="370" t="s">
         <v>237</v>
       </c>
-      <c r="C58" s="367"/>
-      <c r="D58" s="367"/>
-      <c r="E58" s="367"/>
-      <c r="F58" s="367"/>
+      <c r="C58" s="370"/>
+      <c r="D58" s="370"/>
+      <c r="E58" s="370"/>
+      <c r="F58" s="370"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -7489,7 +7489,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="367" t="s">
+      <c r="B61" s="370" t="s">
         <v>329</v>
       </c>
       <c r="C61" s="373"/>
@@ -7560,7 +7560,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>8.1854774938882657E-2</v>
+        <v>8.1543540053183483E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -7570,7 +7570,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>0.10305343511450382</v>
+        <v>0.10266159695817492</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>424</v>
@@ -7670,13 +7670,13 @@
       <c r="F80" s="371"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="374" t="s">
+      <c r="B81" s="372" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="374"/>
-      <c r="D81" s="374"/>
-      <c r="E81" s="374"/>
-      <c r="F81" s="374"/>
+      <c r="C81" s="372"/>
+      <c r="D81" s="372"/>
+      <c r="E81" s="372"/>
+      <c r="F81" s="372"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -7964,13 +7964,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="367" t="s">
+      <c r="B123" s="370" t="s">
         <v>473</v>
       </c>
-      <c r="C123" s="367"/>
-      <c r="D123" s="367"/>
-      <c r="E123" s="367"/>
-      <c r="F123" s="367"/>
+      <c r="C123" s="370"/>
+      <c r="D123" s="370"/>
+      <c r="E123" s="370"/>
+      <c r="F123" s="370"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -8113,13 +8113,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="369" t="s">
+      <c r="B134" s="375" t="s">
         <v>474</v>
       </c>
-      <c r="C134" s="369"/>
-      <c r="D134" s="369"/>
-      <c r="E134" s="369"/>
-      <c r="F134" s="369"/>
+      <c r="C134" s="375"/>
+      <c r="D134" s="375"/>
+      <c r="E134" s="375"/>
+      <c r="F134" s="375"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -8132,13 +8132,13 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="370" t="s">
+      <c r="B138" s="376" t="s">
         <v>353</v>
       </c>
-      <c r="C138" s="370"/>
-      <c r="D138" s="370"/>
-      <c r="E138" s="370"/>
-      <c r="F138" s="370"/>
+      <c r="C138" s="376"/>
+      <c r="D138" s="376"/>
+      <c r="E138" s="376"/>
+      <c r="F138" s="376"/>
     </row>
     <row r="139" spans="1:6">
       <c r="B139" s="371" t="s">
@@ -8480,7 +8480,7 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="372" t="s">
+      <c r="B179" s="377" t="s">
         <v>477</v>
       </c>
       <c r="C179" s="371"/>
@@ -8523,13 +8523,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="34.35" customHeight="1">
-      <c r="B188" s="367" t="s">
+      <c r="B188" s="370" t="s">
         <v>478</v>
       </c>
-      <c r="C188" s="367"/>
-      <c r="D188" s="367"/>
-      <c r="E188" s="367"/>
-      <c r="F188" s="367"/>
+      <c r="C188" s="370"/>
+      <c r="D188" s="370"/>
+      <c r="E188" s="370"/>
+      <c r="F188" s="370"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -8537,22 +8537,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="368" t="s">
+      <c r="B191" s="374" t="s">
         <v>363</v>
       </c>
-      <c r="C191" s="368"/>
-      <c r="D191" s="368"/>
-      <c r="E191" s="368"/>
-      <c r="F191" s="368"/>
+      <c r="C191" s="374"/>
+      <c r="D191" s="374"/>
+      <c r="E191" s="374"/>
+      <c r="F191" s="374"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="368" t="s">
+      <c r="B192" s="374" t="s">
         <v>364</v>
       </c>
-      <c r="C192" s="368"/>
-      <c r="D192" s="368"/>
-      <c r="E192" s="368"/>
-      <c r="F192" s="368"/>
+      <c r="C192" s="374"/>
+      <c r="D192" s="374"/>
+      <c r="E192" s="374"/>
+      <c r="F192" s="374"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -8576,6 +8576,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -8592,17 +8603,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -16146,20 +16146,20 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>0.10305343511450382</v>
+        <v>0.10266159695817492</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>0.10305343511450382</v>
+        <v>0.10266159695817492</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>9.6183206106870242E-2</v>
+        <v>9.5817490494296609E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>0.14770992366412217</v>
+        <v>0.14714828897338406</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
@@ -17345,50 +17345,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>8.1854774938882657E-2</v>
+        <v>8.1543540053183483E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>9.5518729353586435E-2</v>
+        <v>9.5155540268591826E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>0.1314397168516386</v>
+        <v>0.13093994606513049</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>0.2131685290307696</v>
+        <v>0.2123580023044169</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>0.17515138553631682</v>
+        <v>0.17448541068636886</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>6.2835266275187554E-2</v>
+        <v>6.2596348912924482E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>7.976846241953349E-2</v>
+        <v>7.9465160281056185E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>7.1023161774289842E-2</v>
+        <v>7.0753111729520687E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>6.7455618898125569E-2</v>
+        <v>6.7199133655166929E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>1.1940990189214101E-2</v>
+        <v>1.1895587184692375E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>5.1728097207074178E-3</v>
+        <v>5.1531412426819145E-3</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -17402,43 +17402,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13606945596743306</v>
+        <v>0.13555208161014243</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.17250231098213115</v>
+        <v>0.17184640865900516</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.24801380245234422</v>
+        <v>0.24707078419206915</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.22947181585325091</v>
+        <v>0.22859929944316248</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.9011116896586348E-2</v>
+        <v>8.8672671585192486E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.8175796366888076E-2</v>
+        <v>8.7840527179181269E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.6360537348257257E-2</v>
+        <v>8.6032170286096582E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.8658830846590639E-2</v>
+        <v>8.8321725025881162E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.0721994038114299E-3</v>
+        <v>5.0529134745193709E-3</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-5.3339586597297171E-2</v>
+        <v>-5.3136774480957633E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18226,10 +18226,10 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E6" s="375" t="s">
+      <c r="E6" s="378" t="s">
         <v>245</v>
       </c>
-      <c r="F6" s="375"/>
+      <c r="F6" s="378"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8">
@@ -18244,8 +18244,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E7" s="375"/>
-      <c r="F7" s="375"/>
+      <c r="E7" s="378"/>
+      <c r="F7" s="378"/>
       <c r="H7" s="120"/>
     </row>
     <row r="8" spans="2:8">
@@ -18260,8 +18260,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E8" s="375"/>
-      <c r="F8" s="375"/>
+      <c r="E8" s="378"/>
+      <c r="F8" s="378"/>
       <c r="H8" s="120"/>
     </row>
     <row r="9" spans="2:8">
@@ -18276,8 +18276,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E9" s="375"/>
-      <c r="F9" s="375"/>
+      <c r="E9" s="378"/>
+      <c r="F9" s="378"/>
       <c r="H9" s="120"/>
     </row>
     <row r="10" spans="2:8" ht="13.15">
@@ -19986,8 +19986,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E6" s="375"/>
-      <c r="F6" s="375"/>
+      <c r="E6" s="378"/>
+      <c r="F6" s="378"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8" ht="13.15">
@@ -21388,7 +21388,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-2.62</v>
+        <v>-2.63</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -21452,11 +21452,11 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E7" s="377" t="str">
+      <c r="E7" s="380" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 5-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 10-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 首钢资源(0639.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="377"/>
+      <c r="F7" s="380"/>
       <c r="H7" s="247">
         <v>4</v>
       </c>
@@ -21477,8 +21477,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E8" s="377"/>
-      <c r="F8" s="377"/>
+      <c r="E8" s="380"/>
+      <c r="F8" s="380"/>
       <c r="H8" s="247">
         <v>5</v>
       </c>
@@ -21499,8 +21499,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E9" s="377"/>
-      <c r="F9" s="377"/>
+      <c r="E9" s="380"/>
+      <c r="F9" s="380"/>
       <c r="H9" s="247">
         <v>6</v>
       </c>
@@ -21510,8 +21510,8 @@
       </c>
     </row>
     <row r="10" spans="2:9">
-      <c r="E10" s="377"/>
-      <c r="F10" s="377"/>
+      <c r="E10" s="380"/>
+      <c r="F10" s="380"/>
       <c r="H10" s="247">
         <v>7</v>
       </c>
@@ -21524,8 +21524,8 @@
       <c r="B11" s="159" t="s">
         <v>423</v>
       </c>
-      <c r="E11" s="377"/>
-      <c r="F11" s="377"/>
+      <c r="E11" s="380"/>
+      <c r="F11" s="380"/>
       <c r="H11" s="247">
         <v>8</v>
       </c>
@@ -21543,8 +21543,8 @@
         <v>-0.1059288114314666</v>
       </c>
       <c r="D12" s="158"/>
-      <c r="E12" s="377"/>
-      <c r="F12" s="377"/>
+      <c r="E12" s="380"/>
+      <c r="F12" s="380"/>
       <c r="H12" s="247">
         <v>9</v>
       </c>
@@ -21561,8 +21561,8 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.1663504856430581</v>
       </c>
-      <c r="E13" s="377"/>
-      <c r="F13" s="377"/>
+      <c r="E13" s="380"/>
+      <c r="F13" s="380"/>
       <c r="H13" s="247">
         <v>10</v>
       </c>
@@ -21579,8 +21579,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.18299448813777219</v>
       </c>
-      <c r="E14" s="377"/>
-      <c r="F14" s="377"/>
+      <c r="E14" s="380"/>
+      <c r="F14" s="380"/>
     </row>
     <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
@@ -21606,21 +21606,21 @@
       <c r="C18" s="150">
         <v>5</v>
       </c>
-      <c r="E18" s="377" t="s">
+      <c r="E18" s="380" t="s">
         <v>321</v>
       </c>
-      <c r="F18" s="378"/>
+      <c r="F18" s="381"/>
     </row>
     <row r="19" spans="2:6">
-      <c r="E19" s="378"/>
-      <c r="F19" s="378"/>
+      <c r="E19" s="381"/>
+      <c r="F19" s="381"/>
     </row>
     <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="159" t="s">
         <v>298</v>
       </c>
-      <c r="E20" s="378"/>
-      <c r="F20" s="378"/>
+      <c r="E20" s="381"/>
+      <c r="F20" s="381"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
@@ -21628,14 +21628,14 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E21" s="378"/>
-      <c r="F21" s="378"/>
+      <c r="E21" s="381"/>
+      <c r="F21" s="381"/>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
@@ -21649,8 +21649,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E22" s="378"/>
-      <c r="F22" s="378"/>
+      <c r="E22" s="381"/>
+      <c r="F22" s="381"/>
     </row>
     <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="159" t="s">
@@ -21670,8 +21670,8 @@
         <v>5</v>
       </c>
       <c r="D25" s="163"/>
-      <c r="E25" s="376"/>
-      <c r="F25" s="376"/>
+      <c r="E25" s="379"/>
+      <c r="F25" s="379"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="118" t="s">
@@ -21681,8 +21681,8 @@
         <v>0</v>
       </c>
       <c r="D26" s="164"/>
-      <c r="E26" s="376"/>
-      <c r="F26" s="376"/>
+      <c r="E26" s="379"/>
+      <c r="F26" s="379"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
@@ -21696,8 +21696,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E27" s="376"/>
-      <c r="F27" s="376"/>
+      <c r="E27" s="379"/>
+      <c r="F27" s="379"/>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
@@ -21707,8 +21707,8 @@
         <v>0.6</v>
       </c>
       <c r="D28" s="165"/>
-      <c r="E28" s="376"/>
-      <c r="F28" s="376"/>
+      <c r="E28" s="379"/>
+      <c r="F28" s="379"/>
     </row>
     <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="159" t="s">
@@ -21728,8 +21728,8 @@
         <v>5</v>
       </c>
       <c r="D31" s="163"/>
-      <c r="E31" s="376"/>
-      <c r="F31" s="376"/>
+      <c r="E31" s="379"/>
+      <c r="F31" s="379"/>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="118" t="s">
@@ -21739,8 +21739,8 @@
         <v>-0.02</v>
       </c>
       <c r="D32" s="164"/>
-      <c r="E32" s="376"/>
-      <c r="F32" s="376"/>
+      <c r="E32" s="379"/>
+      <c r="F32" s="379"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
@@ -21754,8 +21754,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E33" s="376"/>
-      <c r="F33" s="376"/>
+      <c r="E33" s="379"/>
+      <c r="F33" s="379"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
@@ -21765,8 +21765,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="165"/>
-      <c r="E34" s="376"/>
-      <c r="F34" s="376"/>
+      <c r="E34" s="379"/>
+      <c r="F34" s="379"/>
     </row>
     <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="159" t="s">
@@ -21786,8 +21786,8 @@
         <v>5</v>
       </c>
       <c r="D37" s="163"/>
-      <c r="E37" s="376"/>
-      <c r="F37" s="376"/>
+      <c r="E37" s="379"/>
+      <c r="F37" s="379"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="118" t="s">
@@ -21797,8 +21797,8 @@
         <v>0.02</v>
       </c>
       <c r="D38" s="164"/>
-      <c r="E38" s="376"/>
-      <c r="F38" s="376"/>
+      <c r="E38" s="379"/>
+      <c r="F38" s="379"/>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
@@ -21812,8 +21812,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E39" s="376"/>
-      <c r="F39" s="376"/>
+      <c r="E39" s="379"/>
+      <c r="F39" s="379"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
@@ -21824,8 +21824,8 @@
         <v>0.2</v>
       </c>
       <c r="D40" s="165"/>
-      <c r="E40" s="376"/>
-      <c r="F40" s="376"/>
+      <c r="E40" s="379"/>
+      <c r="F40" s="379"/>
     </row>
     <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
@@ -21887,8 +21887,8 @@
         <v>10</v>
       </c>
       <c r="D49" s="163"/>
-      <c r="E49" s="376"/>
-      <c r="F49" s="376"/>
+      <c r="E49" s="379"/>
+      <c r="F49" s="379"/>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="118" t="s">
@@ -21898,8 +21898,8 @@
         <v>-0.04</v>
       </c>
       <c r="D50" s="164"/>
-      <c r="E50" s="376"/>
-      <c r="F50" s="376"/>
+      <c r="E50" s="379"/>
+      <c r="F50" s="379"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
@@ -21913,8 +21913,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E51" s="376"/>
-      <c r="F51" s="376"/>
+      <c r="E51" s="379"/>
+      <c r="F51" s="379"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
@@ -21924,8 +21924,8 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="165"/>
-      <c r="E52" s="376"/>
-      <c r="F52" s="376"/>
+      <c r="E52" s="379"/>
+      <c r="F52" s="379"/>
     </row>
     <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="159" t="s">
@@ -21945,8 +21945,8 @@
         <v>10</v>
       </c>
       <c r="D55" s="163"/>
-      <c r="E55" s="376"/>
-      <c r="F55" s="376"/>
+      <c r="E55" s="379"/>
+      <c r="F55" s="379"/>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="118" t="s">
@@ -21956,8 +21956,8 @@
         <v>0.04</v>
       </c>
       <c r="D56" s="164"/>
-      <c r="E56" s="376"/>
-      <c r="F56" s="376"/>
+      <c r="E56" s="379"/>
+      <c r="F56" s="379"/>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
@@ -21971,8 +21971,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E57" s="376"/>
-      <c r="F57" s="376"/>
+      <c r="E57" s="379"/>
+      <c r="F57" s="379"/>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
@@ -21982,8 +21982,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="165"/>
-      <c r="E58" s="376"/>
-      <c r="F58" s="376"/>
+      <c r="E58" s="379"/>
+      <c r="F58" s="379"/>
     </row>
     <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -22239,7 +22239,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.28412064787572122</v>
+        <v>0.28236042533963035</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -22472,19 +22472,19 @@
   <dimension ref="B2:E2"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="2.59765625" style="381" customWidth="1"/>
-    <col min="2" max="2" width="22.73046875" style="381" customWidth="1"/>
-    <col min="3" max="5" width="20.73046875" style="381" customWidth="1"/>
-    <col min="6" max="16384" width="9.06640625" style="381"/>
+    <col min="1" max="1" width="2.59765625" style="369" customWidth="1"/>
+    <col min="2" max="2" width="22.73046875" style="369" customWidth="1"/>
+    <col min="3" max="5" width="20.73046875" style="369" customWidth="1"/>
+    <col min="6" max="16384" width="9.06640625" style="369"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:5" ht="13.9">
-      <c r="B2" s="379" t="s">
+      <c r="B2" s="367" t="s">
         <v>436</v>
       </c>
-      <c r="C2" s="380"/>
-      <c r="D2" s="380"/>
-      <c r="E2" s="380"/>
+      <c r="C2" s="368"/>
+      <c r="D2" s="368"/>
+      <c r="E2" s="368"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/financial_models/opportunities/0639.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0639.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{890F8B47-75E6-4793-9468-14B8F59B50AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA13A0C7-16D2-465E-AAE1-980D8C0554FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2205" yWindow="2205" windowWidth="12690" windowHeight="7642" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="投资主题" sheetId="12" r:id="rId1"/>
@@ -4759,15 +4759,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4777,7 +4768,16 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="C12" s="366">
         <f>Market_Price</f>
-        <v>2.63</v>
+        <v>2.66</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C14" s="35">
         <f>投资主题!C12*Common_Shares/1000000</f>
-        <v>13389.5029751</v>
+        <v>13542.234948200001</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",投资主题!D12*Common_Shares/1000000)</f>
@@ -5346,13 +5346,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="371" t="s">
+      <c r="B18" s="374" t="s">
         <v>489</v>
       </c>
-      <c r="C18" s="371"/>
-      <c r="D18" s="371"/>
-      <c r="E18" s="371"/>
-      <c r="F18" s="371"/>
+      <c r="C18" s="374"/>
+      <c r="D18" s="374"/>
+      <c r="E18" s="374"/>
+      <c r="F18" s="374"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -5443,7 +5443,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.28236042533963035</v>
+        <v>0.2771356143063628</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -5565,22 +5565,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="371" t="s">
+      <c r="B36" s="374" t="s">
         <v>492</v>
       </c>
-      <c r="C36" s="371"/>
-      <c r="D36" s="371"/>
-      <c r="E36" s="371"/>
-      <c r="F36" s="371"/>
+      <c r="C36" s="374"/>
+      <c r="D36" s="374"/>
+      <c r="E36" s="374"/>
+      <c r="F36" s="374"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="372" t="s">
+      <c r="B37" s="377" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="372"/>
-      <c r="D37" s="372"/>
-      <c r="E37" s="372"/>
-      <c r="F37" s="372"/>
+      <c r="C37" s="377"/>
+      <c r="D37" s="377"/>
+      <c r="E37" s="377"/>
+      <c r="F37" s="377"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -5770,10 +5770,10 @@
       <c r="B61" s="370" t="s">
         <v>499</v>
       </c>
-      <c r="C61" s="373"/>
-      <c r="D61" s="373"/>
-      <c r="E61" s="373"/>
-      <c r="F61" s="373"/>
+      <c r="C61" s="376"/>
+      <c r="D61" s="376"/>
+      <c r="E61" s="376"/>
+      <c r="F61" s="376"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -5789,22 +5789,22 @@
       </c>
     </row>
     <row r="64" spans="2:6">
-      <c r="B64" s="371" t="s">
+      <c r="B64" s="374" t="s">
         <v>500</v>
       </c>
-      <c r="C64" s="371"/>
-      <c r="D64" s="371"/>
-      <c r="E64" s="371"/>
-      <c r="F64" s="371"/>
+      <c r="C64" s="374"/>
+      <c r="D64" s="374"/>
+      <c r="E64" s="374"/>
+      <c r="F64" s="374"/>
     </row>
     <row r="65" spans="1:6">
-      <c r="B65" s="371" t="s">
+      <c r="B65" s="374" t="s">
         <v>501</v>
       </c>
-      <c r="C65" s="371"/>
-      <c r="D65" s="371"/>
-      <c r="E65" s="371"/>
-      <c r="F65" s="371"/>
+      <c r="C65" s="374"/>
+      <c r="D65" s="374"/>
+      <c r="E65" s="374"/>
+      <c r="F65" s="374"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -5838,7 +5838,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>8.1543540053183483E-2</v>
+        <v>8.0623876067621267E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -5848,7 +5848,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>0.10266159695817492</v>
+        <v>0.10150375939849623</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>503</v>
@@ -5939,22 +5939,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="371" t="s">
+      <c r="B80" s="374" t="s">
         <v>506</v>
       </c>
-      <c r="C80" s="371"/>
-      <c r="D80" s="371"/>
-      <c r="E80" s="371"/>
-      <c r="F80" s="371"/>
+      <c r="C80" s="374"/>
+      <c r="D80" s="374"/>
+      <c r="E80" s="374"/>
+      <c r="F80" s="374"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="372" t="s">
+      <c r="B81" s="377" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="372"/>
-      <c r="D81" s="372"/>
-      <c r="E81" s="372"/>
-      <c r="F81" s="372"/>
+      <c r="C81" s="377"/>
+      <c r="D81" s="377"/>
+      <c r="E81" s="377"/>
+      <c r="F81" s="377"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5998,22 +5998,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6">
-      <c r="B89" s="371" t="s">
+      <c r="B89" s="374" t="s">
         <v>507</v>
       </c>
-      <c r="C89" s="371"/>
-      <c r="D89" s="371"/>
-      <c r="E89" s="371"/>
-      <c r="F89" s="371"/>
+      <c r="C89" s="374"/>
+      <c r="D89" s="374"/>
+      <c r="E89" s="374"/>
+      <c r="F89" s="374"/>
     </row>
     <row r="90" spans="1:6">
-      <c r="B90" s="371" t="s">
+      <c r="B90" s="374" t="s">
         <v>508</v>
       </c>
-      <c r="C90" s="371"/>
-      <c r="D90" s="371"/>
-      <c r="E90" s="371"/>
-      <c r="F90" s="371"/>
+      <c r="C90" s="374"/>
+      <c r="D90" s="374"/>
+      <c r="E90" s="374"/>
+      <c r="F90" s="374"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -6050,13 +6050,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="371" t="s">
+      <c r="B97" s="374" t="s">
         <v>510</v>
       </c>
-      <c r="C97" s="371"/>
-      <c r="D97" s="371"/>
-      <c r="E97" s="371"/>
-      <c r="F97" s="371"/>
+      <c r="C97" s="374"/>
+      <c r="D97" s="374"/>
+      <c r="E97" s="374"/>
+      <c r="F97" s="374"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -6069,13 +6069,13 @@
       </c>
     </row>
     <row r="101" spans="2:6">
-      <c r="B101" s="371" t="s">
+      <c r="B101" s="374" t="s">
         <v>511</v>
       </c>
-      <c r="C101" s="371"/>
-      <c r="D101" s="371"/>
-      <c r="E101" s="371"/>
-      <c r="F101" s="371"/>
+      <c r="C101" s="374"/>
+      <c r="D101" s="374"/>
+      <c r="E101" s="374"/>
+      <c r="F101" s="374"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -6197,13 +6197,13 @@
       </c>
     </row>
     <row r="116" spans="1:6">
-      <c r="B116" s="371" t="s">
+      <c r="B116" s="374" t="s">
         <v>516</v>
       </c>
-      <c r="C116" s="371"/>
-      <c r="D116" s="371"/>
-      <c r="E116" s="371"/>
-      <c r="F116" s="371"/>
+      <c r="C116" s="374"/>
+      <c r="D116" s="374"/>
+      <c r="E116" s="374"/>
+      <c r="F116" s="374"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -6391,13 +6391,13 @@
       </c>
     </row>
     <row r="134" spans="1:6">
-      <c r="B134" s="375" t="s">
+      <c r="B134" s="372" t="s">
         <v>524</v>
       </c>
-      <c r="C134" s="375"/>
-      <c r="D134" s="375"/>
-      <c r="E134" s="375"/>
-      <c r="F134" s="375"/>
+      <c r="C134" s="372"/>
+      <c r="D134" s="372"/>
+      <c r="E134" s="372"/>
+      <c r="F134" s="372"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -6410,22 +6410,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="376" t="s">
+      <c r="B138" s="373" t="s">
         <v>526</v>
       </c>
-      <c r="C138" s="376"/>
-      <c r="D138" s="376"/>
-      <c r="E138" s="376"/>
-      <c r="F138" s="376"/>
+      <c r="C138" s="373"/>
+      <c r="D138" s="373"/>
+      <c r="E138" s="373"/>
+      <c r="F138" s="373"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="371" t="s">
+      <c r="B139" s="374" t="s">
         <v>527</v>
       </c>
-      <c r="C139" s="371"/>
-      <c r="D139" s="371"/>
-      <c r="E139" s="371"/>
-      <c r="F139" s="371"/>
+      <c r="C139" s="374"/>
+      <c r="D139" s="374"/>
+      <c r="E139" s="374"/>
+      <c r="F139" s="374"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -6758,13 +6758,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="377" t="s">
+      <c r="B179" s="375" t="s">
         <v>534</v>
       </c>
-      <c r="C179" s="371"/>
-      <c r="D179" s="371"/>
-      <c r="E179" s="371"/>
-      <c r="F179" s="371"/>
+      <c r="C179" s="374"/>
+      <c r="D179" s="374"/>
+      <c r="E179" s="374"/>
+      <c r="F179" s="374"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -6772,13 +6772,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="373" t="s">
+      <c r="B182" s="376" t="s">
         <v>536</v>
       </c>
-      <c r="C182" s="373"/>
-      <c r="D182" s="373"/>
-      <c r="E182" s="373"/>
-      <c r="F182" s="373"/>
+      <c r="C182" s="376"/>
+      <c r="D182" s="376"/>
+      <c r="E182" s="376"/>
+      <c r="F182" s="376"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -6815,22 +6815,22 @@
       </c>
     </row>
     <row r="191" spans="1:6">
-      <c r="B191" s="374" t="s">
+      <c r="B191" s="371" t="s">
         <v>543</v>
       </c>
-      <c r="C191" s="374"/>
-      <c r="D191" s="374"/>
-      <c r="E191" s="374"/>
-      <c r="F191" s="374"/>
+      <c r="C191" s="371"/>
+      <c r="D191" s="371"/>
+      <c r="E191" s="371"/>
+      <c r="F191" s="371"/>
     </row>
     <row r="192" spans="1:6">
-      <c r="B192" s="374" t="s">
+      <c r="B192" s="371" t="s">
         <v>544</v>
       </c>
-      <c r="C192" s="374"/>
-      <c r="D192" s="374"/>
-      <c r="E192" s="374"/>
-      <c r="F192" s="374"/>
+      <c r="C192" s="371"/>
+      <c r="D192" s="371"/>
+      <c r="E192" s="371"/>
+      <c r="F192" s="371"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -6854,15 +6854,12 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B138:F138"/>
-    <mergeCell ref="B139:F139"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B43:F43"/>
     <mergeCell ref="B116:F116"/>
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B58:F58"/>
@@ -6875,12 +6872,15 @@
     <mergeCell ref="B90:F90"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B47:F47"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B138:F138"/>
+    <mergeCell ref="B139:F139"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">
@@ -7023,7 +7023,7 @@
         <v>463</v>
       </c>
       <c r="C12" s="50">
-        <v>2.63</v>
+        <v>2.66</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -7044,7 +7044,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>13389.5029751</v>
+        <v>13542.234948200001</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -7081,13 +7081,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="371" t="s">
+      <c r="B18" s="374" t="s">
         <v>468</v>
       </c>
-      <c r="C18" s="371"/>
-      <c r="D18" s="371"/>
-      <c r="E18" s="371"/>
-      <c r="F18" s="371"/>
+      <c r="C18" s="374"/>
+      <c r="D18" s="374"/>
+      <c r="E18" s="374"/>
+      <c r="F18" s="374"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -7170,7 +7170,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.28236042533963035</v>
+        <v>0.2771356143063628</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -7287,22 +7287,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6">
-      <c r="B36" s="371" t="s">
+      <c r="B36" s="374" t="s">
         <v>469</v>
       </c>
-      <c r="C36" s="371"/>
-      <c r="D36" s="371"/>
-      <c r="E36" s="371"/>
-      <c r="F36" s="371"/>
+      <c r="C36" s="374"/>
+      <c r="D36" s="374"/>
+      <c r="E36" s="374"/>
+      <c r="F36" s="374"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="372" t="s">
+      <c r="B37" s="377" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="372"/>
-      <c r="D37" s="372"/>
-      <c r="E37" s="372"/>
-      <c r="F37" s="372"/>
+      <c r="C37" s="377"/>
+      <c r="D37" s="377"/>
+      <c r="E37" s="377"/>
+      <c r="F37" s="377"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -7492,10 +7492,10 @@
       <c r="B61" s="370" t="s">
         <v>329</v>
       </c>
-      <c r="C61" s="373"/>
-      <c r="D61" s="373"/>
-      <c r="E61" s="373"/>
-      <c r="F61" s="373"/>
+      <c r="C61" s="376"/>
+      <c r="D61" s="376"/>
+      <c r="E61" s="376"/>
+      <c r="F61" s="376"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -7511,22 +7511,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="371" t="s">
+      <c r="B64" s="374" t="s">
         <v>334</v>
       </c>
-      <c r="C64" s="371"/>
-      <c r="D64" s="371"/>
-      <c r="E64" s="371"/>
-      <c r="F64" s="371"/>
+      <c r="C64" s="374"/>
+      <c r="D64" s="374"/>
+      <c r="E64" s="374"/>
+      <c r="F64" s="374"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="371" t="s">
+      <c r="B65" s="374" t="s">
         <v>348</v>
       </c>
-      <c r="C65" s="371"/>
-      <c r="D65" s="371"/>
-      <c r="E65" s="371"/>
-      <c r="F65" s="371"/>
+      <c r="C65" s="374"/>
+      <c r="D65" s="374"/>
+      <c r="E65" s="374"/>
+      <c r="F65" s="374"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -7560,7 +7560,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>8.1543540053183483E-2</v>
+        <v>8.0623876067621267E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -7570,7 +7570,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>0.10266159695817492</v>
+        <v>0.10150375939849623</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>424</v>
@@ -7661,22 +7661,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="371" t="s">
+      <c r="B80" s="374" t="s">
         <v>471</v>
       </c>
-      <c r="C80" s="371"/>
-      <c r="D80" s="371"/>
-      <c r="E80" s="371"/>
-      <c r="F80" s="371"/>
+      <c r="C80" s="374"/>
+      <c r="D80" s="374"/>
+      <c r="E80" s="374"/>
+      <c r="F80" s="374"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="372" t="s">
+      <c r="B81" s="377" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="372"/>
-      <c r="D81" s="372"/>
-      <c r="E81" s="372"/>
-      <c r="F81" s="372"/>
+      <c r="C81" s="377"/>
+      <c r="D81" s="377"/>
+      <c r="E81" s="377"/>
+      <c r="F81" s="377"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -7720,22 +7720,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="371" t="s">
+      <c r="B89" s="374" t="s">
         <v>349</v>
       </c>
-      <c r="C89" s="371"/>
-      <c r="D89" s="371"/>
-      <c r="E89" s="371"/>
-      <c r="F89" s="371"/>
+      <c r="C89" s="374"/>
+      <c r="D89" s="374"/>
+      <c r="E89" s="374"/>
+      <c r="F89" s="374"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="371" t="s">
+      <c r="B90" s="374" t="s">
         <v>350</v>
       </c>
-      <c r="C90" s="371"/>
-      <c r="D90" s="371"/>
-      <c r="E90" s="371"/>
-      <c r="F90" s="371"/>
+      <c r="C90" s="374"/>
+      <c r="D90" s="374"/>
+      <c r="E90" s="374"/>
+      <c r="F90" s="374"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -7772,13 +7772,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="371" t="s">
+      <c r="B97" s="374" t="s">
         <v>351</v>
       </c>
-      <c r="C97" s="371"/>
-      <c r="D97" s="371"/>
-      <c r="E97" s="371"/>
-      <c r="F97" s="371"/>
+      <c r="C97" s="374"/>
+      <c r="D97" s="374"/>
+      <c r="E97" s="374"/>
+      <c r="F97" s="374"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -7791,13 +7791,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="371" t="s">
+      <c r="B101" s="374" t="s">
         <v>335</v>
       </c>
-      <c r="C101" s="371"/>
-      <c r="D101" s="371"/>
-      <c r="E101" s="371"/>
-      <c r="F101" s="371"/>
+      <c r="C101" s="374"/>
+      <c r="D101" s="374"/>
+      <c r="E101" s="374"/>
+      <c r="F101" s="374"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -7919,13 +7919,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="371" t="s">
+      <c r="B116" s="374" t="s">
         <v>352</v>
       </c>
-      <c r="C116" s="371"/>
-      <c r="D116" s="371"/>
-      <c r="E116" s="371"/>
-      <c r="F116" s="371"/>
+      <c r="C116" s="374"/>
+      <c r="D116" s="374"/>
+      <c r="E116" s="374"/>
+      <c r="F116" s="374"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -8113,13 +8113,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="375" t="s">
+      <c r="B134" s="372" t="s">
         <v>474</v>
       </c>
-      <c r="C134" s="375"/>
-      <c r="D134" s="375"/>
-      <c r="E134" s="375"/>
-      <c r="F134" s="375"/>
+      <c r="C134" s="372"/>
+      <c r="D134" s="372"/>
+      <c r="E134" s="372"/>
+      <c r="F134" s="372"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -8132,22 +8132,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="376" t="s">
+      <c r="B138" s="373" t="s">
         <v>353</v>
       </c>
-      <c r="C138" s="376"/>
-      <c r="D138" s="376"/>
-      <c r="E138" s="376"/>
-      <c r="F138" s="376"/>
+      <c r="C138" s="373"/>
+      <c r="D138" s="373"/>
+      <c r="E138" s="373"/>
+      <c r="F138" s="373"/>
     </row>
     <row r="139" spans="1:6">
-      <c r="B139" s="371" t="s">
+      <c r="B139" s="374" t="s">
         <v>476</v>
       </c>
-      <c r="C139" s="371"/>
-      <c r="D139" s="371"/>
-      <c r="E139" s="371"/>
-      <c r="F139" s="371"/>
+      <c r="C139" s="374"/>
+      <c r="D139" s="374"/>
+      <c r="E139" s="374"/>
+      <c r="F139" s="374"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -8480,13 +8480,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="377" t="s">
+      <c r="B179" s="375" t="s">
         <v>477</v>
       </c>
-      <c r="C179" s="371"/>
-      <c r="D179" s="371"/>
-      <c r="E179" s="371"/>
-      <c r="F179" s="371"/>
+      <c r="C179" s="374"/>
+      <c r="D179" s="374"/>
+      <c r="E179" s="374"/>
+      <c r="F179" s="374"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -8494,13 +8494,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="373" t="s">
+      <c r="B182" s="376" t="s">
         <v>362</v>
       </c>
-      <c r="C182" s="373"/>
-      <c r="D182" s="373"/>
-      <c r="E182" s="373"/>
-      <c r="F182" s="373"/>
+      <c r="C182" s="376"/>
+      <c r="D182" s="376"/>
+      <c r="E182" s="376"/>
+      <c r="F182" s="376"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -8537,22 +8537,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="374" t="s">
+      <c r="B191" s="371" t="s">
         <v>363</v>
       </c>
-      <c r="C191" s="374"/>
-      <c r="D191" s="374"/>
-      <c r="E191" s="374"/>
-      <c r="F191" s="374"/>
+      <c r="C191" s="371"/>
+      <c r="D191" s="371"/>
+      <c r="E191" s="371"/>
+      <c r="F191" s="371"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="374" t="s">
+      <c r="B192" s="371" t="s">
         <v>364</v>
       </c>
-      <c r="C192" s="374"/>
-      <c r="D192" s="374"/>
-      <c r="E192" s="374"/>
-      <c r="F192" s="374"/>
+      <c r="C192" s="371"/>
+      <c r="D192" s="371"/>
+      <c r="E192" s="371"/>
+      <c r="F192" s="371"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -8576,17 +8576,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -8603,6 +8592,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -16146,20 +16146,20 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>0.10266159695817492</v>
+        <v>0.10150375939849623</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>0.10266159695817492</v>
+        <v>0.10150375939849623</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>9.5817490494296609E-2</v>
+        <v>9.4736842105263175E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>0.14714828897338406</v>
+        <v>0.14548872180451131</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
@@ -17345,50 +17345,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>8.1543540053183483E-2</v>
+        <v>8.0623876067621267E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>9.5155540268591826E-2</v>
+        <v>9.4082357483607701E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>0.13093994606513049</v>
+        <v>0.12946317975612526</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>0.2123580023044169</v>
+        <v>0.20996298724083323</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>0.17448541068636886</v>
+        <v>0.17251753011471807</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>6.2596348912924482E-2</v>
+        <v>6.1890375053004272E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>7.9465160281056185E-2</v>
+        <v>7.8568936668863804E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>7.0753111729520687E-2</v>
+        <v>6.9955144303999767E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>6.7199133655166929E-2</v>
+        <v>6.6441248689131205E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>1.1895587184692375E-2</v>
+        <v>1.176142642697028E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>5.1531412426819145E-3</v>
+        <v>5.0950231083659522E-3</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -17402,43 +17402,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13555208161014243</v>
+        <v>0.13402329873484006</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.17184640865900516</v>
+        <v>0.1699082912681141</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.24707078419206915</v>
+        <v>0.24428427158839919</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.22859929944316248</v>
+        <v>0.22602111185545765</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.8672671585192486E-2</v>
+        <v>8.7672603860547454E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.7840527179181269E-2</v>
+        <v>8.6849844541822083E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.6032170286096582E-2</v>
+        <v>8.5061882651290971E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.8321725025881162E-2</v>
+        <v>8.7325615345138136E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.0529134745193709E-3</v>
+        <v>4.9959257285661449E-3</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-5.3136774480957633E-2</v>
+        <v>-5.2537487550721268E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -21388,7 +21388,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-2.63</v>
+        <v>-2.66</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -21628,7 +21628,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>2.63</v>
+        <v>2.66</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>2.63</v>
+        <v>2.66</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -22239,7 +22239,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.28236042533963035</v>
+        <v>0.2771356143063628</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/0639.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0639.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA13A0C7-16D2-465E-AAE1-980D8C0554FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B15E725-DD75-467C-B7AA-8213EEC3A7C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2205" yWindow="2205" windowWidth="12690" windowHeight="7642" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4759,6 +4759,15 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4768,16 +4777,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="C12" s="366">
         <f>Market_Price</f>
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C14" s="35">
         <f>投资主题!C12*Common_Shares/1000000</f>
-        <v>13542.234948200001</v>
+        <v>13338.5923174</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",投资主题!D12*Common_Shares/1000000)</f>
@@ -5346,13 +5346,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="374" t="s">
+      <c r="B18" s="371" t="s">
         <v>489</v>
       </c>
-      <c r="C18" s="374"/>
-      <c r="D18" s="374"/>
-      <c r="E18" s="374"/>
-      <c r="F18" s="374"/>
+      <c r="C18" s="371"/>
+      <c r="D18" s="371"/>
+      <c r="E18" s="371"/>
+      <c r="F18" s="371"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -5443,7 +5443,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.2771356143063628</v>
+        <v>0.28412064787572122</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -5565,22 +5565,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="374" t="s">
+      <c r="B36" s="371" t="s">
         <v>492</v>
       </c>
-      <c r="C36" s="374"/>
-      <c r="D36" s="374"/>
-      <c r="E36" s="374"/>
-      <c r="F36" s="374"/>
+      <c r="C36" s="371"/>
+      <c r="D36" s="371"/>
+      <c r="E36" s="371"/>
+      <c r="F36" s="371"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="377" t="s">
+      <c r="B37" s="372" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="377"/>
-      <c r="D37" s="377"/>
-      <c r="E37" s="377"/>
-      <c r="F37" s="377"/>
+      <c r="C37" s="372"/>
+      <c r="D37" s="372"/>
+      <c r="E37" s="372"/>
+      <c r="F37" s="372"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -5770,10 +5770,10 @@
       <c r="B61" s="370" t="s">
         <v>499</v>
       </c>
-      <c r="C61" s="376"/>
-      <c r="D61" s="376"/>
-      <c r="E61" s="376"/>
-      <c r="F61" s="376"/>
+      <c r="C61" s="373"/>
+      <c r="D61" s="373"/>
+      <c r="E61" s="373"/>
+      <c r="F61" s="373"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -5789,22 +5789,22 @@
       </c>
     </row>
     <row r="64" spans="2:6">
-      <c r="B64" s="374" t="s">
+      <c r="B64" s="371" t="s">
         <v>500</v>
       </c>
-      <c r="C64" s="374"/>
-      <c r="D64" s="374"/>
-      <c r="E64" s="374"/>
-      <c r="F64" s="374"/>
+      <c r="C64" s="371"/>
+      <c r="D64" s="371"/>
+      <c r="E64" s="371"/>
+      <c r="F64" s="371"/>
     </row>
     <row r="65" spans="1:6">
-      <c r="B65" s="374" t="s">
+      <c r="B65" s="371" t="s">
         <v>501</v>
       </c>
-      <c r="C65" s="374"/>
-      <c r="D65" s="374"/>
-      <c r="E65" s="374"/>
-      <c r="F65" s="374"/>
+      <c r="C65" s="371"/>
+      <c r="D65" s="371"/>
+      <c r="E65" s="371"/>
+      <c r="F65" s="371"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -5838,7 +5838,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>8.0623876067621267E-2</v>
+        <v>8.1854774938882657E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -5848,7 +5848,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>0.10150375939849623</v>
+        <v>0.10305343511450382</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>503</v>
@@ -5939,22 +5939,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="374" t="s">
+      <c r="B80" s="371" t="s">
         <v>506</v>
       </c>
-      <c r="C80" s="374"/>
-      <c r="D80" s="374"/>
-      <c r="E80" s="374"/>
-      <c r="F80" s="374"/>
+      <c r="C80" s="371"/>
+      <c r="D80" s="371"/>
+      <c r="E80" s="371"/>
+      <c r="F80" s="371"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="377" t="s">
+      <c r="B81" s="372" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="377"/>
-      <c r="D81" s="377"/>
-      <c r="E81" s="377"/>
-      <c r="F81" s="377"/>
+      <c r="C81" s="372"/>
+      <c r="D81" s="372"/>
+      <c r="E81" s="372"/>
+      <c r="F81" s="372"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5998,22 +5998,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6">
-      <c r="B89" s="374" t="s">
+      <c r="B89" s="371" t="s">
         <v>507</v>
       </c>
-      <c r="C89" s="374"/>
-      <c r="D89" s="374"/>
-      <c r="E89" s="374"/>
-      <c r="F89" s="374"/>
+      <c r="C89" s="371"/>
+      <c r="D89" s="371"/>
+      <c r="E89" s="371"/>
+      <c r="F89" s="371"/>
     </row>
     <row r="90" spans="1:6">
-      <c r="B90" s="374" t="s">
+      <c r="B90" s="371" t="s">
         <v>508</v>
       </c>
-      <c r="C90" s="374"/>
-      <c r="D90" s="374"/>
-      <c r="E90" s="374"/>
-      <c r="F90" s="374"/>
+      <c r="C90" s="371"/>
+      <c r="D90" s="371"/>
+      <c r="E90" s="371"/>
+      <c r="F90" s="371"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -6050,13 +6050,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="374" t="s">
+      <c r="B97" s="371" t="s">
         <v>510</v>
       </c>
-      <c r="C97" s="374"/>
-      <c r="D97" s="374"/>
-      <c r="E97" s="374"/>
-      <c r="F97" s="374"/>
+      <c r="C97" s="371"/>
+      <c r="D97" s="371"/>
+      <c r="E97" s="371"/>
+      <c r="F97" s="371"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -6069,13 +6069,13 @@
       </c>
     </row>
     <row r="101" spans="2:6">
-      <c r="B101" s="374" t="s">
+      <c r="B101" s="371" t="s">
         <v>511</v>
       </c>
-      <c r="C101" s="374"/>
-      <c r="D101" s="374"/>
-      <c r="E101" s="374"/>
-      <c r="F101" s="374"/>
+      <c r="C101" s="371"/>
+      <c r="D101" s="371"/>
+      <c r="E101" s="371"/>
+      <c r="F101" s="371"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -6197,13 +6197,13 @@
       </c>
     </row>
     <row r="116" spans="1:6">
-      <c r="B116" s="374" t="s">
+      <c r="B116" s="371" t="s">
         <v>516</v>
       </c>
-      <c r="C116" s="374"/>
-      <c r="D116" s="374"/>
-      <c r="E116" s="374"/>
-      <c r="F116" s="374"/>
+      <c r="C116" s="371"/>
+      <c r="D116" s="371"/>
+      <c r="E116" s="371"/>
+      <c r="F116" s="371"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -6391,13 +6391,13 @@
       </c>
     </row>
     <row r="134" spans="1:6">
-      <c r="B134" s="372" t="s">
+      <c r="B134" s="375" t="s">
         <v>524</v>
       </c>
-      <c r="C134" s="372"/>
-      <c r="D134" s="372"/>
-      <c r="E134" s="372"/>
-      <c r="F134" s="372"/>
+      <c r="C134" s="375"/>
+      <c r="D134" s="375"/>
+      <c r="E134" s="375"/>
+      <c r="F134" s="375"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -6410,22 +6410,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="373" t="s">
+      <c r="B138" s="376" t="s">
         <v>526</v>
       </c>
-      <c r="C138" s="373"/>
-      <c r="D138" s="373"/>
-      <c r="E138" s="373"/>
-      <c r="F138" s="373"/>
+      <c r="C138" s="376"/>
+      <c r="D138" s="376"/>
+      <c r="E138" s="376"/>
+      <c r="F138" s="376"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="374" t="s">
+      <c r="B139" s="371" t="s">
         <v>527</v>
       </c>
-      <c r="C139" s="374"/>
-      <c r="D139" s="374"/>
-      <c r="E139" s="374"/>
-      <c r="F139" s="374"/>
+      <c r="C139" s="371"/>
+      <c r="D139" s="371"/>
+      <c r="E139" s="371"/>
+      <c r="F139" s="371"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -6758,13 +6758,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="375" t="s">
+      <c r="B179" s="377" t="s">
         <v>534</v>
       </c>
-      <c r="C179" s="374"/>
-      <c r="D179" s="374"/>
-      <c r="E179" s="374"/>
-      <c r="F179" s="374"/>
+      <c r="C179" s="371"/>
+      <c r="D179" s="371"/>
+      <c r="E179" s="371"/>
+      <c r="F179" s="371"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -6772,13 +6772,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="376" t="s">
+      <c r="B182" s="373" t="s">
         <v>536</v>
       </c>
-      <c r="C182" s="376"/>
-      <c r="D182" s="376"/>
-      <c r="E182" s="376"/>
-      <c r="F182" s="376"/>
+      <c r="C182" s="373"/>
+      <c r="D182" s="373"/>
+      <c r="E182" s="373"/>
+      <c r="F182" s="373"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -6815,22 +6815,22 @@
       </c>
     </row>
     <row r="191" spans="1:6">
-      <c r="B191" s="371" t="s">
+      <c r="B191" s="374" t="s">
         <v>543</v>
       </c>
-      <c r="C191" s="371"/>
-      <c r="D191" s="371"/>
-      <c r="E191" s="371"/>
-      <c r="F191" s="371"/>
+      <c r="C191" s="374"/>
+      <c r="D191" s="374"/>
+      <c r="E191" s="374"/>
+      <c r="F191" s="374"/>
     </row>
     <row r="192" spans="1:6">
-      <c r="B192" s="371" t="s">
+      <c r="B192" s="374" t="s">
         <v>544</v>
       </c>
-      <c r="C192" s="371"/>
-      <c r="D192" s="371"/>
-      <c r="E192" s="371"/>
-      <c r="F192" s="371"/>
+      <c r="C192" s="374"/>
+      <c r="D192" s="374"/>
+      <c r="E192" s="374"/>
+      <c r="F192" s="374"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -6854,12 +6854,15 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B47:F47"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B138:F138"/>
+    <mergeCell ref="B139:F139"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B182:F182"/>
     <mergeCell ref="B116:F116"/>
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B58:F58"/>
@@ -6872,15 +6875,12 @@
     <mergeCell ref="B90:F90"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B138:F138"/>
-    <mergeCell ref="B139:F139"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B43:F43"/>
   </mergeCells>
   <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">
@@ -7023,7 +7023,7 @@
         <v>463</v>
       </c>
       <c r="C12" s="50">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -7044,7 +7044,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>13542.234948200001</v>
+        <v>13338.5923174</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -7081,13 +7081,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="374" t="s">
+      <c r="B18" s="371" t="s">
         <v>468</v>
       </c>
-      <c r="C18" s="374"/>
-      <c r="D18" s="374"/>
-      <c r="E18" s="374"/>
-      <c r="F18" s="374"/>
+      <c r="C18" s="371"/>
+      <c r="D18" s="371"/>
+      <c r="E18" s="371"/>
+      <c r="F18" s="371"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -7170,7 +7170,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.2771356143063628</v>
+        <v>0.28412064787572122</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -7287,22 +7287,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6">
-      <c r="B36" s="374" t="s">
+      <c r="B36" s="371" t="s">
         <v>469</v>
       </c>
-      <c r="C36" s="374"/>
-      <c r="D36" s="374"/>
-      <c r="E36" s="374"/>
-      <c r="F36" s="374"/>
+      <c r="C36" s="371"/>
+      <c r="D36" s="371"/>
+      <c r="E36" s="371"/>
+      <c r="F36" s="371"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="377" t="s">
+      <c r="B37" s="372" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="377"/>
-      <c r="D37" s="377"/>
-      <c r="E37" s="377"/>
-      <c r="F37" s="377"/>
+      <c r="C37" s="372"/>
+      <c r="D37" s="372"/>
+      <c r="E37" s="372"/>
+      <c r="F37" s="372"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -7492,10 +7492,10 @@
       <c r="B61" s="370" t="s">
         <v>329</v>
       </c>
-      <c r="C61" s="376"/>
-      <c r="D61" s="376"/>
-      <c r="E61" s="376"/>
-      <c r="F61" s="376"/>
+      <c r="C61" s="373"/>
+      <c r="D61" s="373"/>
+      <c r="E61" s="373"/>
+      <c r="F61" s="373"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -7511,22 +7511,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="374" t="s">
+      <c r="B64" s="371" t="s">
         <v>334</v>
       </c>
-      <c r="C64" s="374"/>
-      <c r="D64" s="374"/>
-      <c r="E64" s="374"/>
-      <c r="F64" s="374"/>
+      <c r="C64" s="371"/>
+      <c r="D64" s="371"/>
+      <c r="E64" s="371"/>
+      <c r="F64" s="371"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="374" t="s">
+      <c r="B65" s="371" t="s">
         <v>348</v>
       </c>
-      <c r="C65" s="374"/>
-      <c r="D65" s="374"/>
-      <c r="E65" s="374"/>
-      <c r="F65" s="374"/>
+      <c r="C65" s="371"/>
+      <c r="D65" s="371"/>
+      <c r="E65" s="371"/>
+      <c r="F65" s="371"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -7560,7 +7560,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>8.0623876067621267E-2</v>
+        <v>8.1854774938882657E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -7570,7 +7570,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>0.10150375939849623</v>
+        <v>0.10305343511450382</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>424</v>
@@ -7661,22 +7661,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="374" t="s">
+      <c r="B80" s="371" t="s">
         <v>471</v>
       </c>
-      <c r="C80" s="374"/>
-      <c r="D80" s="374"/>
-      <c r="E80" s="374"/>
-      <c r="F80" s="374"/>
+      <c r="C80" s="371"/>
+      <c r="D80" s="371"/>
+      <c r="E80" s="371"/>
+      <c r="F80" s="371"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="377" t="s">
+      <c r="B81" s="372" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="377"/>
-      <c r="D81" s="377"/>
-      <c r="E81" s="377"/>
-      <c r="F81" s="377"/>
+      <c r="C81" s="372"/>
+      <c r="D81" s="372"/>
+      <c r="E81" s="372"/>
+      <c r="F81" s="372"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -7720,22 +7720,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="374" t="s">
+      <c r="B89" s="371" t="s">
         <v>349</v>
       </c>
-      <c r="C89" s="374"/>
-      <c r="D89" s="374"/>
-      <c r="E89" s="374"/>
-      <c r="F89" s="374"/>
+      <c r="C89" s="371"/>
+      <c r="D89" s="371"/>
+      <c r="E89" s="371"/>
+      <c r="F89" s="371"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="374" t="s">
+      <c r="B90" s="371" t="s">
         <v>350</v>
       </c>
-      <c r="C90" s="374"/>
-      <c r="D90" s="374"/>
-      <c r="E90" s="374"/>
-      <c r="F90" s="374"/>
+      <c r="C90" s="371"/>
+      <c r="D90" s="371"/>
+      <c r="E90" s="371"/>
+      <c r="F90" s="371"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -7772,13 +7772,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="374" t="s">
+      <c r="B97" s="371" t="s">
         <v>351</v>
       </c>
-      <c r="C97" s="374"/>
-      <c r="D97" s="374"/>
-      <c r="E97" s="374"/>
-      <c r="F97" s="374"/>
+      <c r="C97" s="371"/>
+      <c r="D97" s="371"/>
+      <c r="E97" s="371"/>
+      <c r="F97" s="371"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -7791,13 +7791,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="374" t="s">
+      <c r="B101" s="371" t="s">
         <v>335</v>
       </c>
-      <c r="C101" s="374"/>
-      <c r="D101" s="374"/>
-      <c r="E101" s="374"/>
-      <c r="F101" s="374"/>
+      <c r="C101" s="371"/>
+      <c r="D101" s="371"/>
+      <c r="E101" s="371"/>
+      <c r="F101" s="371"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -7919,13 +7919,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="374" t="s">
+      <c r="B116" s="371" t="s">
         <v>352</v>
       </c>
-      <c r="C116" s="374"/>
-      <c r="D116" s="374"/>
-      <c r="E116" s="374"/>
-      <c r="F116" s="374"/>
+      <c r="C116" s="371"/>
+      <c r="D116" s="371"/>
+      <c r="E116" s="371"/>
+      <c r="F116" s="371"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -8113,13 +8113,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="372" t="s">
+      <c r="B134" s="375" t="s">
         <v>474</v>
       </c>
-      <c r="C134" s="372"/>
-      <c r="D134" s="372"/>
-      <c r="E134" s="372"/>
-      <c r="F134" s="372"/>
+      <c r="C134" s="375"/>
+      <c r="D134" s="375"/>
+      <c r="E134" s="375"/>
+      <c r="F134" s="375"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -8132,22 +8132,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="373" t="s">
+      <c r="B138" s="376" t="s">
         <v>353</v>
       </c>
-      <c r="C138" s="373"/>
-      <c r="D138" s="373"/>
-      <c r="E138" s="373"/>
-      <c r="F138" s="373"/>
+      <c r="C138" s="376"/>
+      <c r="D138" s="376"/>
+      <c r="E138" s="376"/>
+      <c r="F138" s="376"/>
     </row>
     <row r="139" spans="1:6">
-      <c r="B139" s="374" t="s">
+      <c r="B139" s="371" t="s">
         <v>476</v>
       </c>
-      <c r="C139" s="374"/>
-      <c r="D139" s="374"/>
-      <c r="E139" s="374"/>
-      <c r="F139" s="374"/>
+      <c r="C139" s="371"/>
+      <c r="D139" s="371"/>
+      <c r="E139" s="371"/>
+      <c r="F139" s="371"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -8480,13 +8480,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="375" t="s">
+      <c r="B179" s="377" t="s">
         <v>477</v>
       </c>
-      <c r="C179" s="374"/>
-      <c r="D179" s="374"/>
-      <c r="E179" s="374"/>
-      <c r="F179" s="374"/>
+      <c r="C179" s="371"/>
+      <c r="D179" s="371"/>
+      <c r="E179" s="371"/>
+      <c r="F179" s="371"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -8494,13 +8494,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="376" t="s">
+      <c r="B182" s="373" t="s">
         <v>362</v>
       </c>
-      <c r="C182" s="376"/>
-      <c r="D182" s="376"/>
-      <c r="E182" s="376"/>
-      <c r="F182" s="376"/>
+      <c r="C182" s="373"/>
+      <c r="D182" s="373"/>
+      <c r="E182" s="373"/>
+      <c r="F182" s="373"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -8537,22 +8537,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="371" t="s">
+      <c r="B191" s="374" t="s">
         <v>363</v>
       </c>
-      <c r="C191" s="371"/>
-      <c r="D191" s="371"/>
-      <c r="E191" s="371"/>
-      <c r="F191" s="371"/>
+      <c r="C191" s="374"/>
+      <c r="D191" s="374"/>
+      <c r="E191" s="374"/>
+      <c r="F191" s="374"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="371" t="s">
+      <c r="B192" s="374" t="s">
         <v>364</v>
       </c>
-      <c r="C192" s="371"/>
-      <c r="D192" s="371"/>
-      <c r="E192" s="371"/>
-      <c r="F192" s="371"/>
+      <c r="C192" s="374"/>
+      <c r="D192" s="374"/>
+      <c r="E192" s="374"/>
+      <c r="F192" s="374"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -8576,6 +8576,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -8592,17 +8603,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -16146,20 +16146,20 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>0.10150375939849623</v>
+        <v>0.10305343511450382</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>0.10150375939849623</v>
+        <v>0.10305343511450382</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>9.4736842105263175E-2</v>
+        <v>9.6183206106870242E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>0.14548872180451131</v>
+        <v>0.14770992366412217</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
@@ -17345,50 +17345,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>8.0623876067621267E-2</v>
+        <v>8.1854774938882657E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>9.4082357483607701E-2</v>
+        <v>9.5518729353586435E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>0.12946317975612526</v>
+        <v>0.1314397168516386</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>0.20996298724083323</v>
+        <v>0.2131685290307696</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>0.17251753011471807</v>
+        <v>0.17515138553631682</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>6.1890375053004272E-2</v>
+        <v>6.2835266275187554E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>7.8568936668863804E-2</v>
+        <v>7.976846241953349E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>6.9955144303999767E-2</v>
+        <v>7.1023161774289842E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>6.6441248689131205E-2</v>
+        <v>6.7455618898125569E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>1.176142642697028E-2</v>
+        <v>1.1940990189214101E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>5.0950231083659522E-3</v>
+        <v>5.1728097207074178E-3</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -17402,43 +17402,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13402329873484006</v>
+        <v>0.13606945596743306</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1699082912681141</v>
+        <v>0.17250231098213115</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.24428427158839919</v>
+        <v>0.24801380245234422</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.22602111185545765</v>
+        <v>0.22947181585325091</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.7672603860547454E-2</v>
+        <v>8.9011116896586348E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.6849844541822083E-2</v>
+        <v>8.8175796366888076E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.5061882651290971E-2</v>
+        <v>8.6360537348257257E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.7325615345138136E-2</v>
+        <v>8.8658830846590639E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.9959257285661449E-3</v>
+        <v>5.0721994038114299E-3</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-5.2537487550721268E-2</v>
+        <v>-5.3339586597297171E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -21388,7 +21388,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-2.66</v>
+        <v>-2.62</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -21628,7 +21628,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -22239,7 +22239,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.2771356143063628</v>
+        <v>0.28412064787572122</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/0639.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0639.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B15E725-DD75-467C-B7AA-8213EEC3A7C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FC13866-967F-4659-9EF8-F6CF431566DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2205" yWindow="2205" windowWidth="12690" windowHeight="7642" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="368" yWindow="368" windowWidth="12689" windowHeight="7642" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="投资主题" sheetId="12" r:id="rId1"/>
@@ -4759,15 +4759,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4777,7 +4768,16 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="C12" s="366">
         <f>Market_Price</f>
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C14" s="35">
         <f>投资主题!C12*Common_Shares/1000000</f>
-        <v>13338.5923174</v>
+        <v>13542.234948200001</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",投资主题!D12*Common_Shares/1000000)</f>
@@ -5346,13 +5346,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="371" t="s">
+      <c r="B18" s="374" t="s">
         <v>489</v>
       </c>
-      <c r="C18" s="371"/>
-      <c r="D18" s="371"/>
-      <c r="E18" s="371"/>
-      <c r="F18" s="371"/>
+      <c r="C18" s="374"/>
+      <c r="D18" s="374"/>
+      <c r="E18" s="374"/>
+      <c r="F18" s="374"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -5443,7 +5443,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.28412064787572122</v>
+        <v>0.2771356143063628</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -5565,22 +5565,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="371" t="s">
+      <c r="B36" s="374" t="s">
         <v>492</v>
       </c>
-      <c r="C36" s="371"/>
-      <c r="D36" s="371"/>
-      <c r="E36" s="371"/>
-      <c r="F36" s="371"/>
+      <c r="C36" s="374"/>
+      <c r="D36" s="374"/>
+      <c r="E36" s="374"/>
+      <c r="F36" s="374"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="372" t="s">
+      <c r="B37" s="377" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="372"/>
-      <c r="D37" s="372"/>
-      <c r="E37" s="372"/>
-      <c r="F37" s="372"/>
+      <c r="C37" s="377"/>
+      <c r="D37" s="377"/>
+      <c r="E37" s="377"/>
+      <c r="F37" s="377"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -5770,10 +5770,10 @@
       <c r="B61" s="370" t="s">
         <v>499</v>
       </c>
-      <c r="C61" s="373"/>
-      <c r="D61" s="373"/>
-      <c r="E61" s="373"/>
-      <c r="F61" s="373"/>
+      <c r="C61" s="376"/>
+      <c r="D61" s="376"/>
+      <c r="E61" s="376"/>
+      <c r="F61" s="376"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -5789,22 +5789,22 @@
       </c>
     </row>
     <row r="64" spans="2:6">
-      <c r="B64" s="371" t="s">
+      <c r="B64" s="374" t="s">
         <v>500</v>
       </c>
-      <c r="C64" s="371"/>
-      <c r="D64" s="371"/>
-      <c r="E64" s="371"/>
-      <c r="F64" s="371"/>
+      <c r="C64" s="374"/>
+      <c r="D64" s="374"/>
+      <c r="E64" s="374"/>
+      <c r="F64" s="374"/>
     </row>
     <row r="65" spans="1:6">
-      <c r="B65" s="371" t="s">
+      <c r="B65" s="374" t="s">
         <v>501</v>
       </c>
-      <c r="C65" s="371"/>
-      <c r="D65" s="371"/>
-      <c r="E65" s="371"/>
-      <c r="F65" s="371"/>
+      <c r="C65" s="374"/>
+      <c r="D65" s="374"/>
+      <c r="E65" s="374"/>
+      <c r="F65" s="374"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -5838,7 +5838,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>8.1854774938882657E-2</v>
+        <v>8.0623876067621267E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -5848,7 +5848,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>0.10305343511450382</v>
+        <v>0.10150375939849623</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>503</v>
@@ -5939,22 +5939,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="371" t="s">
+      <c r="B80" s="374" t="s">
         <v>506</v>
       </c>
-      <c r="C80" s="371"/>
-      <c r="D80" s="371"/>
-      <c r="E80" s="371"/>
-      <c r="F80" s="371"/>
+      <c r="C80" s="374"/>
+      <c r="D80" s="374"/>
+      <c r="E80" s="374"/>
+      <c r="F80" s="374"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="372" t="s">
+      <c r="B81" s="377" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="372"/>
-      <c r="D81" s="372"/>
-      <c r="E81" s="372"/>
-      <c r="F81" s="372"/>
+      <c r="C81" s="377"/>
+      <c r="D81" s="377"/>
+      <c r="E81" s="377"/>
+      <c r="F81" s="377"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5998,22 +5998,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6">
-      <c r="B89" s="371" t="s">
+      <c r="B89" s="374" t="s">
         <v>507</v>
       </c>
-      <c r="C89" s="371"/>
-      <c r="D89" s="371"/>
-      <c r="E89" s="371"/>
-      <c r="F89" s="371"/>
+      <c r="C89" s="374"/>
+      <c r="D89" s="374"/>
+      <c r="E89" s="374"/>
+      <c r="F89" s="374"/>
     </row>
     <row r="90" spans="1:6">
-      <c r="B90" s="371" t="s">
+      <c r="B90" s="374" t="s">
         <v>508</v>
       </c>
-      <c r="C90" s="371"/>
-      <c r="D90" s="371"/>
-      <c r="E90" s="371"/>
-      <c r="F90" s="371"/>
+      <c r="C90" s="374"/>
+      <c r="D90" s="374"/>
+      <c r="E90" s="374"/>
+      <c r="F90" s="374"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -6050,13 +6050,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="371" t="s">
+      <c r="B97" s="374" t="s">
         <v>510</v>
       </c>
-      <c r="C97" s="371"/>
-      <c r="D97" s="371"/>
-      <c r="E97" s="371"/>
-      <c r="F97" s="371"/>
+      <c r="C97" s="374"/>
+      <c r="D97" s="374"/>
+      <c r="E97" s="374"/>
+      <c r="F97" s="374"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -6069,13 +6069,13 @@
       </c>
     </row>
     <row r="101" spans="2:6">
-      <c r="B101" s="371" t="s">
+      <c r="B101" s="374" t="s">
         <v>511</v>
       </c>
-      <c r="C101" s="371"/>
-      <c r="D101" s="371"/>
-      <c r="E101" s="371"/>
-      <c r="F101" s="371"/>
+      <c r="C101" s="374"/>
+      <c r="D101" s="374"/>
+      <c r="E101" s="374"/>
+      <c r="F101" s="374"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -6197,13 +6197,13 @@
       </c>
     </row>
     <row r="116" spans="1:6">
-      <c r="B116" s="371" t="s">
+      <c r="B116" s="374" t="s">
         <v>516</v>
       </c>
-      <c r="C116" s="371"/>
-      <c r="D116" s="371"/>
-      <c r="E116" s="371"/>
-      <c r="F116" s="371"/>
+      <c r="C116" s="374"/>
+      <c r="D116" s="374"/>
+      <c r="E116" s="374"/>
+      <c r="F116" s="374"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -6391,13 +6391,13 @@
       </c>
     </row>
     <row r="134" spans="1:6">
-      <c r="B134" s="375" t="s">
+      <c r="B134" s="372" t="s">
         <v>524</v>
       </c>
-      <c r="C134" s="375"/>
-      <c r="D134" s="375"/>
-      <c r="E134" s="375"/>
-      <c r="F134" s="375"/>
+      <c r="C134" s="372"/>
+      <c r="D134" s="372"/>
+      <c r="E134" s="372"/>
+      <c r="F134" s="372"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -6410,22 +6410,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="376" t="s">
+      <c r="B138" s="373" t="s">
         <v>526</v>
       </c>
-      <c r="C138" s="376"/>
-      <c r="D138" s="376"/>
-      <c r="E138" s="376"/>
-      <c r="F138" s="376"/>
+      <c r="C138" s="373"/>
+      <c r="D138" s="373"/>
+      <c r="E138" s="373"/>
+      <c r="F138" s="373"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="371" t="s">
+      <c r="B139" s="374" t="s">
         <v>527</v>
       </c>
-      <c r="C139" s="371"/>
-      <c r="D139" s="371"/>
-      <c r="E139" s="371"/>
-      <c r="F139" s="371"/>
+      <c r="C139" s="374"/>
+      <c r="D139" s="374"/>
+      <c r="E139" s="374"/>
+      <c r="F139" s="374"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -6758,13 +6758,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="377" t="s">
+      <c r="B179" s="375" t="s">
         <v>534</v>
       </c>
-      <c r="C179" s="371"/>
-      <c r="D179" s="371"/>
-      <c r="E179" s="371"/>
-      <c r="F179" s="371"/>
+      <c r="C179" s="374"/>
+      <c r="D179" s="374"/>
+      <c r="E179" s="374"/>
+      <c r="F179" s="374"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -6772,13 +6772,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="373" t="s">
+      <c r="B182" s="376" t="s">
         <v>536</v>
       </c>
-      <c r="C182" s="373"/>
-      <c r="D182" s="373"/>
-      <c r="E182" s="373"/>
-      <c r="F182" s="373"/>
+      <c r="C182" s="376"/>
+      <c r="D182" s="376"/>
+      <c r="E182" s="376"/>
+      <c r="F182" s="376"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -6815,22 +6815,22 @@
       </c>
     </row>
     <row r="191" spans="1:6">
-      <c r="B191" s="374" t="s">
+      <c r="B191" s="371" t="s">
         <v>543</v>
       </c>
-      <c r="C191" s="374"/>
-      <c r="D191" s="374"/>
-      <c r="E191" s="374"/>
-      <c r="F191" s="374"/>
+      <c r="C191" s="371"/>
+      <c r="D191" s="371"/>
+      <c r="E191" s="371"/>
+      <c r="F191" s="371"/>
     </row>
     <row r="192" spans="1:6">
-      <c r="B192" s="374" t="s">
+      <c r="B192" s="371" t="s">
         <v>544</v>
       </c>
-      <c r="C192" s="374"/>
-      <c r="D192" s="374"/>
-      <c r="E192" s="374"/>
-      <c r="F192" s="374"/>
+      <c r="C192" s="371"/>
+      <c r="D192" s="371"/>
+      <c r="E192" s="371"/>
+      <c r="F192" s="371"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -6854,15 +6854,12 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B138:F138"/>
-    <mergeCell ref="B139:F139"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B43:F43"/>
     <mergeCell ref="B116:F116"/>
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B58:F58"/>
@@ -6875,12 +6872,15 @@
     <mergeCell ref="B90:F90"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B47:F47"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B138:F138"/>
+    <mergeCell ref="B139:F139"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">
@@ -7023,7 +7023,7 @@
         <v>463</v>
       </c>
       <c r="C12" s="50">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -7044,7 +7044,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>13338.5923174</v>
+        <v>13542.234948200001</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -7081,13 +7081,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="371" t="s">
+      <c r="B18" s="374" t="s">
         <v>468</v>
       </c>
-      <c r="C18" s="371"/>
-      <c r="D18" s="371"/>
-      <c r="E18" s="371"/>
-      <c r="F18" s="371"/>
+      <c r="C18" s="374"/>
+      <c r="D18" s="374"/>
+      <c r="E18" s="374"/>
+      <c r="F18" s="374"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -7170,7 +7170,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.28412064787572122</v>
+        <v>0.2771356143063628</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -7287,22 +7287,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6">
-      <c r="B36" s="371" t="s">
+      <c r="B36" s="374" t="s">
         <v>469</v>
       </c>
-      <c r="C36" s="371"/>
-      <c r="D36" s="371"/>
-      <c r="E36" s="371"/>
-      <c r="F36" s="371"/>
+      <c r="C36" s="374"/>
+      <c r="D36" s="374"/>
+      <c r="E36" s="374"/>
+      <c r="F36" s="374"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="372" t="s">
+      <c r="B37" s="377" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="372"/>
-      <c r="D37" s="372"/>
-      <c r="E37" s="372"/>
-      <c r="F37" s="372"/>
+      <c r="C37" s="377"/>
+      <c r="D37" s="377"/>
+      <c r="E37" s="377"/>
+      <c r="F37" s="377"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -7492,10 +7492,10 @@
       <c r="B61" s="370" t="s">
         <v>329</v>
       </c>
-      <c r="C61" s="373"/>
-      <c r="D61" s="373"/>
-      <c r="E61" s="373"/>
-      <c r="F61" s="373"/>
+      <c r="C61" s="376"/>
+      <c r="D61" s="376"/>
+      <c r="E61" s="376"/>
+      <c r="F61" s="376"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -7511,22 +7511,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="371" t="s">
+      <c r="B64" s="374" t="s">
         <v>334</v>
       </c>
-      <c r="C64" s="371"/>
-      <c r="D64" s="371"/>
-      <c r="E64" s="371"/>
-      <c r="F64" s="371"/>
+      <c r="C64" s="374"/>
+      <c r="D64" s="374"/>
+      <c r="E64" s="374"/>
+      <c r="F64" s="374"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="371" t="s">
+      <c r="B65" s="374" t="s">
         <v>348</v>
       </c>
-      <c r="C65" s="371"/>
-      <c r="D65" s="371"/>
-      <c r="E65" s="371"/>
-      <c r="F65" s="371"/>
+      <c r="C65" s="374"/>
+      <c r="D65" s="374"/>
+      <c r="E65" s="374"/>
+      <c r="F65" s="374"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -7560,7 +7560,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>8.1854774938882657E-2</v>
+        <v>8.0623876067621267E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -7570,7 +7570,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>0.10305343511450382</v>
+        <v>0.10150375939849623</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>424</v>
@@ -7661,22 +7661,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="371" t="s">
+      <c r="B80" s="374" t="s">
         <v>471</v>
       </c>
-      <c r="C80" s="371"/>
-      <c r="D80" s="371"/>
-      <c r="E80" s="371"/>
-      <c r="F80" s="371"/>
+      <c r="C80" s="374"/>
+      <c r="D80" s="374"/>
+      <c r="E80" s="374"/>
+      <c r="F80" s="374"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="372" t="s">
+      <c r="B81" s="377" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="372"/>
-      <c r="D81" s="372"/>
-      <c r="E81" s="372"/>
-      <c r="F81" s="372"/>
+      <c r="C81" s="377"/>
+      <c r="D81" s="377"/>
+      <c r="E81" s="377"/>
+      <c r="F81" s="377"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -7720,22 +7720,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="371" t="s">
+      <c r="B89" s="374" t="s">
         <v>349</v>
       </c>
-      <c r="C89" s="371"/>
-      <c r="D89" s="371"/>
-      <c r="E89" s="371"/>
-      <c r="F89" s="371"/>
+      <c r="C89" s="374"/>
+      <c r="D89" s="374"/>
+      <c r="E89" s="374"/>
+      <c r="F89" s="374"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="371" t="s">
+      <c r="B90" s="374" t="s">
         <v>350</v>
       </c>
-      <c r="C90" s="371"/>
-      <c r="D90" s="371"/>
-      <c r="E90" s="371"/>
-      <c r="F90" s="371"/>
+      <c r="C90" s="374"/>
+      <c r="D90" s="374"/>
+      <c r="E90" s="374"/>
+      <c r="F90" s="374"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -7772,13 +7772,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="371" t="s">
+      <c r="B97" s="374" t="s">
         <v>351</v>
       </c>
-      <c r="C97" s="371"/>
-      <c r="D97" s="371"/>
-      <c r="E97" s="371"/>
-      <c r="F97" s="371"/>
+      <c r="C97" s="374"/>
+      <c r="D97" s="374"/>
+      <c r="E97" s="374"/>
+      <c r="F97" s="374"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -7791,13 +7791,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="371" t="s">
+      <c r="B101" s="374" t="s">
         <v>335</v>
       </c>
-      <c r="C101" s="371"/>
-      <c r="D101" s="371"/>
-      <c r="E101" s="371"/>
-      <c r="F101" s="371"/>
+      <c r="C101" s="374"/>
+      <c r="D101" s="374"/>
+      <c r="E101" s="374"/>
+      <c r="F101" s="374"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -7919,13 +7919,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="371" t="s">
+      <c r="B116" s="374" t="s">
         <v>352</v>
       </c>
-      <c r="C116" s="371"/>
-      <c r="D116" s="371"/>
-      <c r="E116" s="371"/>
-      <c r="F116" s="371"/>
+      <c r="C116" s="374"/>
+      <c r="D116" s="374"/>
+      <c r="E116" s="374"/>
+      <c r="F116" s="374"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -8113,13 +8113,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="375" t="s">
+      <c r="B134" s="372" t="s">
         <v>474</v>
       </c>
-      <c r="C134" s="375"/>
-      <c r="D134" s="375"/>
-      <c r="E134" s="375"/>
-      <c r="F134" s="375"/>
+      <c r="C134" s="372"/>
+      <c r="D134" s="372"/>
+      <c r="E134" s="372"/>
+      <c r="F134" s="372"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -8132,22 +8132,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="376" t="s">
+      <c r="B138" s="373" t="s">
         <v>353</v>
       </c>
-      <c r="C138" s="376"/>
-      <c r="D138" s="376"/>
-      <c r="E138" s="376"/>
-      <c r="F138" s="376"/>
+      <c r="C138" s="373"/>
+      <c r="D138" s="373"/>
+      <c r="E138" s="373"/>
+      <c r="F138" s="373"/>
     </row>
     <row r="139" spans="1:6">
-      <c r="B139" s="371" t="s">
+      <c r="B139" s="374" t="s">
         <v>476</v>
       </c>
-      <c r="C139" s="371"/>
-      <c r="D139" s="371"/>
-      <c r="E139" s="371"/>
-      <c r="F139" s="371"/>
+      <c r="C139" s="374"/>
+      <c r="D139" s="374"/>
+      <c r="E139" s="374"/>
+      <c r="F139" s="374"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -8480,13 +8480,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="377" t="s">
+      <c r="B179" s="375" t="s">
         <v>477</v>
       </c>
-      <c r="C179" s="371"/>
-      <c r="D179" s="371"/>
-      <c r="E179" s="371"/>
-      <c r="F179" s="371"/>
+      <c r="C179" s="374"/>
+      <c r="D179" s="374"/>
+      <c r="E179" s="374"/>
+      <c r="F179" s="374"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -8494,13 +8494,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="373" t="s">
+      <c r="B182" s="376" t="s">
         <v>362</v>
       </c>
-      <c r="C182" s="373"/>
-      <c r="D182" s="373"/>
-      <c r="E182" s="373"/>
-      <c r="F182" s="373"/>
+      <c r="C182" s="376"/>
+      <c r="D182" s="376"/>
+      <c r="E182" s="376"/>
+      <c r="F182" s="376"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -8537,22 +8537,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="374" t="s">
+      <c r="B191" s="371" t="s">
         <v>363</v>
       </c>
-      <c r="C191" s="374"/>
-      <c r="D191" s="374"/>
-      <c r="E191" s="374"/>
-      <c r="F191" s="374"/>
+      <c r="C191" s="371"/>
+      <c r="D191" s="371"/>
+      <c r="E191" s="371"/>
+      <c r="F191" s="371"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="374" t="s">
+      <c r="B192" s="371" t="s">
         <v>364</v>
       </c>
-      <c r="C192" s="374"/>
-      <c r="D192" s="374"/>
-      <c r="E192" s="374"/>
-      <c r="F192" s="374"/>
+      <c r="C192" s="371"/>
+      <c r="D192" s="371"/>
+      <c r="E192" s="371"/>
+      <c r="F192" s="371"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -8576,17 +8576,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -8603,6 +8592,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -16146,20 +16146,20 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>0.10305343511450382</v>
+        <v>0.10150375939849623</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>0.10305343511450382</v>
+        <v>0.10150375939849623</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>9.6183206106870242E-2</v>
+        <v>9.4736842105263175E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>0.14770992366412217</v>
+        <v>0.14548872180451131</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
@@ -17345,50 +17345,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>8.1854774938882657E-2</v>
+        <v>8.0623876067621267E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>9.5518729353586435E-2</v>
+        <v>9.4082357483607701E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>0.1314397168516386</v>
+        <v>0.12946317975612526</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>0.2131685290307696</v>
+        <v>0.20996298724083323</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>0.17515138553631682</v>
+        <v>0.17251753011471807</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>6.2835266275187554E-2</v>
+        <v>6.1890375053004272E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>7.976846241953349E-2</v>
+        <v>7.8568936668863804E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>7.1023161774289842E-2</v>
+        <v>6.9955144303999767E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>6.7455618898125569E-2</v>
+        <v>6.6441248689131205E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>1.1940990189214101E-2</v>
+        <v>1.176142642697028E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>5.1728097207074178E-3</v>
+        <v>5.0950231083659522E-3</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -17402,43 +17402,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13606945596743306</v>
+        <v>0.13402329873484006</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.17250231098213115</v>
+        <v>0.1699082912681141</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.24801380245234422</v>
+        <v>0.24428427158839919</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.22947181585325091</v>
+        <v>0.22602111185545765</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.9011116896586348E-2</v>
+        <v>8.7672603860547454E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.8175796366888076E-2</v>
+        <v>8.6849844541822083E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.6360537348257257E-2</v>
+        <v>8.5061882651290971E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.8658830846590639E-2</v>
+        <v>8.7325615345138136E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.0721994038114299E-3</v>
+        <v>4.9959257285661449E-3</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-5.3339586597297171E-2</v>
+        <v>-5.2537487550721268E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -21388,7 +21388,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-2.62</v>
+        <v>-2.66</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -21628,7 +21628,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -22239,7 +22239,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.28412064787572122</v>
+        <v>0.2771356143063628</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/0639.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0639.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FC13866-967F-4659-9EF8-F6CF431566DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73135865-88F8-440F-B121-13CEC2472D0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="368" yWindow="368" windowWidth="12689" windowHeight="7642" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="投资主题" sheetId="12" r:id="rId1"/>
@@ -4759,6 +4759,15 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4768,16 +4777,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="C12" s="366">
         <f>Market_Price</f>
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C14" s="35">
         <f>投资主题!C12*Common_Shares/1000000</f>
-        <v>13542.234948200001</v>
+        <v>13593.145605899999</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",投资主题!D12*Common_Shares/1000000)</f>
@@ -5346,13 +5346,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="374" t="s">
+      <c r="B18" s="371" t="s">
         <v>489</v>
       </c>
-      <c r="C18" s="374"/>
-      <c r="D18" s="374"/>
-      <c r="E18" s="374"/>
-      <c r="F18" s="374"/>
+      <c r="C18" s="371"/>
+      <c r="D18" s="371"/>
+      <c r="E18" s="371"/>
+      <c r="F18" s="371"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -5443,7 +5443,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.2771356143063628</v>
+        <v>0.27541234630073297</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -5565,22 +5565,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="374" t="s">
+      <c r="B36" s="371" t="s">
         <v>492</v>
       </c>
-      <c r="C36" s="374"/>
-      <c r="D36" s="374"/>
-      <c r="E36" s="374"/>
-      <c r="F36" s="374"/>
+      <c r="C36" s="371"/>
+      <c r="D36" s="371"/>
+      <c r="E36" s="371"/>
+      <c r="F36" s="371"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="377" t="s">
+      <c r="B37" s="372" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="377"/>
-      <c r="D37" s="377"/>
-      <c r="E37" s="377"/>
-      <c r="F37" s="377"/>
+      <c r="C37" s="372"/>
+      <c r="D37" s="372"/>
+      <c r="E37" s="372"/>
+      <c r="F37" s="372"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -5770,10 +5770,10 @@
       <c r="B61" s="370" t="s">
         <v>499</v>
       </c>
-      <c r="C61" s="376"/>
-      <c r="D61" s="376"/>
-      <c r="E61" s="376"/>
-      <c r="F61" s="376"/>
+      <c r="C61" s="373"/>
+      <c r="D61" s="373"/>
+      <c r="E61" s="373"/>
+      <c r="F61" s="373"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -5789,22 +5789,22 @@
       </c>
     </row>
     <row r="64" spans="2:6">
-      <c r="B64" s="374" t="s">
+      <c r="B64" s="371" t="s">
         <v>500</v>
       </c>
-      <c r="C64" s="374"/>
-      <c r="D64" s="374"/>
-      <c r="E64" s="374"/>
-      <c r="F64" s="374"/>
+      <c r="C64" s="371"/>
+      <c r="D64" s="371"/>
+      <c r="E64" s="371"/>
+      <c r="F64" s="371"/>
     </row>
     <row r="65" spans="1:6">
-      <c r="B65" s="374" t="s">
+      <c r="B65" s="371" t="s">
         <v>501</v>
       </c>
-      <c r="C65" s="374"/>
-      <c r="D65" s="374"/>
-      <c r="E65" s="374"/>
-      <c r="F65" s="374"/>
+      <c r="C65" s="371"/>
+      <c r="D65" s="371"/>
+      <c r="E65" s="371"/>
+      <c r="F65" s="371"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -5838,7 +5838,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>8.0623876067621267E-2</v>
+        <v>8.0321913984971002E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -5848,7 +5848,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>0.10150375939849623</v>
+        <v>0.10112359550561799</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>503</v>
@@ -5939,22 +5939,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="374" t="s">
+      <c r="B80" s="371" t="s">
         <v>506</v>
       </c>
-      <c r="C80" s="374"/>
-      <c r="D80" s="374"/>
-      <c r="E80" s="374"/>
-      <c r="F80" s="374"/>
+      <c r="C80" s="371"/>
+      <c r="D80" s="371"/>
+      <c r="E80" s="371"/>
+      <c r="F80" s="371"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="377" t="s">
+      <c r="B81" s="372" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="377"/>
-      <c r="D81" s="377"/>
-      <c r="E81" s="377"/>
-      <c r="F81" s="377"/>
+      <c r="C81" s="372"/>
+      <c r="D81" s="372"/>
+      <c r="E81" s="372"/>
+      <c r="F81" s="372"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5998,22 +5998,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6">
-      <c r="B89" s="374" t="s">
+      <c r="B89" s="371" t="s">
         <v>507</v>
       </c>
-      <c r="C89" s="374"/>
-      <c r="D89" s="374"/>
-      <c r="E89" s="374"/>
-      <c r="F89" s="374"/>
+      <c r="C89" s="371"/>
+      <c r="D89" s="371"/>
+      <c r="E89" s="371"/>
+      <c r="F89" s="371"/>
     </row>
     <row r="90" spans="1:6">
-      <c r="B90" s="374" t="s">
+      <c r="B90" s="371" t="s">
         <v>508</v>
       </c>
-      <c r="C90" s="374"/>
-      <c r="D90" s="374"/>
-      <c r="E90" s="374"/>
-      <c r="F90" s="374"/>
+      <c r="C90" s="371"/>
+      <c r="D90" s="371"/>
+      <c r="E90" s="371"/>
+      <c r="F90" s="371"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -6050,13 +6050,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="374" t="s">
+      <c r="B97" s="371" t="s">
         <v>510</v>
       </c>
-      <c r="C97" s="374"/>
-      <c r="D97" s="374"/>
-      <c r="E97" s="374"/>
-      <c r="F97" s="374"/>
+      <c r="C97" s="371"/>
+      <c r="D97" s="371"/>
+      <c r="E97" s="371"/>
+      <c r="F97" s="371"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -6069,13 +6069,13 @@
       </c>
     </row>
     <row r="101" spans="2:6">
-      <c r="B101" s="374" t="s">
+      <c r="B101" s="371" t="s">
         <v>511</v>
       </c>
-      <c r="C101" s="374"/>
-      <c r="D101" s="374"/>
-      <c r="E101" s="374"/>
-      <c r="F101" s="374"/>
+      <c r="C101" s="371"/>
+      <c r="D101" s="371"/>
+      <c r="E101" s="371"/>
+      <c r="F101" s="371"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -6197,13 +6197,13 @@
       </c>
     </row>
     <row r="116" spans="1:6">
-      <c r="B116" s="374" t="s">
+      <c r="B116" s="371" t="s">
         <v>516</v>
       </c>
-      <c r="C116" s="374"/>
-      <c r="D116" s="374"/>
-      <c r="E116" s="374"/>
-      <c r="F116" s="374"/>
+      <c r="C116" s="371"/>
+      <c r="D116" s="371"/>
+      <c r="E116" s="371"/>
+      <c r="F116" s="371"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -6391,13 +6391,13 @@
       </c>
     </row>
     <row r="134" spans="1:6">
-      <c r="B134" s="372" t="s">
+      <c r="B134" s="375" t="s">
         <v>524</v>
       </c>
-      <c r="C134" s="372"/>
-      <c r="D134" s="372"/>
-      <c r="E134" s="372"/>
-      <c r="F134" s="372"/>
+      <c r="C134" s="375"/>
+      <c r="D134" s="375"/>
+      <c r="E134" s="375"/>
+      <c r="F134" s="375"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -6410,22 +6410,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="373" t="s">
+      <c r="B138" s="376" t="s">
         <v>526</v>
       </c>
-      <c r="C138" s="373"/>
-      <c r="D138" s="373"/>
-      <c r="E138" s="373"/>
-      <c r="F138" s="373"/>
+      <c r="C138" s="376"/>
+      <c r="D138" s="376"/>
+      <c r="E138" s="376"/>
+      <c r="F138" s="376"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="374" t="s">
+      <c r="B139" s="371" t="s">
         <v>527</v>
       </c>
-      <c r="C139" s="374"/>
-      <c r="D139" s="374"/>
-      <c r="E139" s="374"/>
-      <c r="F139" s="374"/>
+      <c r="C139" s="371"/>
+      <c r="D139" s="371"/>
+      <c r="E139" s="371"/>
+      <c r="F139" s="371"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -6758,13 +6758,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="375" t="s">
+      <c r="B179" s="377" t="s">
         <v>534</v>
       </c>
-      <c r="C179" s="374"/>
-      <c r="D179" s="374"/>
-      <c r="E179" s="374"/>
-      <c r="F179" s="374"/>
+      <c r="C179" s="371"/>
+      <c r="D179" s="371"/>
+      <c r="E179" s="371"/>
+      <c r="F179" s="371"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -6772,13 +6772,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="376" t="s">
+      <c r="B182" s="373" t="s">
         <v>536</v>
       </c>
-      <c r="C182" s="376"/>
-      <c r="D182" s="376"/>
-      <c r="E182" s="376"/>
-      <c r="F182" s="376"/>
+      <c r="C182" s="373"/>
+      <c r="D182" s="373"/>
+      <c r="E182" s="373"/>
+      <c r="F182" s="373"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -6815,22 +6815,22 @@
       </c>
     </row>
     <row r="191" spans="1:6">
-      <c r="B191" s="371" t="s">
+      <c r="B191" s="374" t="s">
         <v>543</v>
       </c>
-      <c r="C191" s="371"/>
-      <c r="D191" s="371"/>
-      <c r="E191" s="371"/>
-      <c r="F191" s="371"/>
+      <c r="C191" s="374"/>
+      <c r="D191" s="374"/>
+      <c r="E191" s="374"/>
+      <c r="F191" s="374"/>
     </row>
     <row r="192" spans="1:6">
-      <c r="B192" s="371" t="s">
+      <c r="B192" s="374" t="s">
         <v>544</v>
       </c>
-      <c r="C192" s="371"/>
-      <c r="D192" s="371"/>
-      <c r="E192" s="371"/>
-      <c r="F192" s="371"/>
+      <c r="C192" s="374"/>
+      <c r="D192" s="374"/>
+      <c r="E192" s="374"/>
+      <c r="F192" s="374"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -6854,12 +6854,15 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B47:F47"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B138:F138"/>
+    <mergeCell ref="B139:F139"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B182:F182"/>
     <mergeCell ref="B116:F116"/>
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B58:F58"/>
@@ -6872,15 +6875,12 @@
     <mergeCell ref="B90:F90"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B138:F138"/>
-    <mergeCell ref="B139:F139"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B43:F43"/>
   </mergeCells>
   <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">
@@ -7023,7 +7023,7 @@
         <v>463</v>
       </c>
       <c r="C12" s="50">
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -7044,7 +7044,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>13542.234948200001</v>
+        <v>13593.145605899999</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -7081,13 +7081,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="374" t="s">
+      <c r="B18" s="371" t="s">
         <v>468</v>
       </c>
-      <c r="C18" s="374"/>
-      <c r="D18" s="374"/>
-      <c r="E18" s="374"/>
-      <c r="F18" s="374"/>
+      <c r="C18" s="371"/>
+      <c r="D18" s="371"/>
+      <c r="E18" s="371"/>
+      <c r="F18" s="371"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -7170,7 +7170,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.2771356143063628</v>
+        <v>0.27541234630073297</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -7287,22 +7287,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6">
-      <c r="B36" s="374" t="s">
+      <c r="B36" s="371" t="s">
         <v>469</v>
       </c>
-      <c r="C36" s="374"/>
-      <c r="D36" s="374"/>
-      <c r="E36" s="374"/>
-      <c r="F36" s="374"/>
+      <c r="C36" s="371"/>
+      <c r="D36" s="371"/>
+      <c r="E36" s="371"/>
+      <c r="F36" s="371"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="377" t="s">
+      <c r="B37" s="372" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="377"/>
-      <c r="D37" s="377"/>
-      <c r="E37" s="377"/>
-      <c r="F37" s="377"/>
+      <c r="C37" s="372"/>
+      <c r="D37" s="372"/>
+      <c r="E37" s="372"/>
+      <c r="F37" s="372"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -7492,10 +7492,10 @@
       <c r="B61" s="370" t="s">
         <v>329</v>
       </c>
-      <c r="C61" s="376"/>
-      <c r="D61" s="376"/>
-      <c r="E61" s="376"/>
-      <c r="F61" s="376"/>
+      <c r="C61" s="373"/>
+      <c r="D61" s="373"/>
+      <c r="E61" s="373"/>
+      <c r="F61" s="373"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -7511,22 +7511,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="374" t="s">
+      <c r="B64" s="371" t="s">
         <v>334</v>
       </c>
-      <c r="C64" s="374"/>
-      <c r="D64" s="374"/>
-      <c r="E64" s="374"/>
-      <c r="F64" s="374"/>
+      <c r="C64" s="371"/>
+      <c r="D64" s="371"/>
+      <c r="E64" s="371"/>
+      <c r="F64" s="371"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="374" t="s">
+      <c r="B65" s="371" t="s">
         <v>348</v>
       </c>
-      <c r="C65" s="374"/>
-      <c r="D65" s="374"/>
-      <c r="E65" s="374"/>
-      <c r="F65" s="374"/>
+      <c r="C65" s="371"/>
+      <c r="D65" s="371"/>
+      <c r="E65" s="371"/>
+      <c r="F65" s="371"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -7560,7 +7560,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>8.0623876067621267E-2</v>
+        <v>8.0321913984971002E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -7570,7 +7570,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>0.10150375939849623</v>
+        <v>0.10112359550561799</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>424</v>
@@ -7661,22 +7661,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="374" t="s">
+      <c r="B80" s="371" t="s">
         <v>471</v>
       </c>
-      <c r="C80" s="374"/>
-      <c r="D80" s="374"/>
-      <c r="E80" s="374"/>
-      <c r="F80" s="374"/>
+      <c r="C80" s="371"/>
+      <c r="D80" s="371"/>
+      <c r="E80" s="371"/>
+      <c r="F80" s="371"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="377" t="s">
+      <c r="B81" s="372" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="377"/>
-      <c r="D81" s="377"/>
-      <c r="E81" s="377"/>
-      <c r="F81" s="377"/>
+      <c r="C81" s="372"/>
+      <c r="D81" s="372"/>
+      <c r="E81" s="372"/>
+      <c r="F81" s="372"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -7720,22 +7720,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="374" t="s">
+      <c r="B89" s="371" t="s">
         <v>349</v>
       </c>
-      <c r="C89" s="374"/>
-      <c r="D89" s="374"/>
-      <c r="E89" s="374"/>
-      <c r="F89" s="374"/>
+      <c r="C89" s="371"/>
+      <c r="D89" s="371"/>
+      <c r="E89" s="371"/>
+      <c r="F89" s="371"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="374" t="s">
+      <c r="B90" s="371" t="s">
         <v>350</v>
       </c>
-      <c r="C90" s="374"/>
-      <c r="D90" s="374"/>
-      <c r="E90" s="374"/>
-      <c r="F90" s="374"/>
+      <c r="C90" s="371"/>
+      <c r="D90" s="371"/>
+      <c r="E90" s="371"/>
+      <c r="F90" s="371"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -7772,13 +7772,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="374" t="s">
+      <c r="B97" s="371" t="s">
         <v>351</v>
       </c>
-      <c r="C97" s="374"/>
-      <c r="D97" s="374"/>
-      <c r="E97" s="374"/>
-      <c r="F97" s="374"/>
+      <c r="C97" s="371"/>
+      <c r="D97" s="371"/>
+      <c r="E97" s="371"/>
+      <c r="F97" s="371"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -7791,13 +7791,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="374" t="s">
+      <c r="B101" s="371" t="s">
         <v>335</v>
       </c>
-      <c r="C101" s="374"/>
-      <c r="D101" s="374"/>
-      <c r="E101" s="374"/>
-      <c r="F101" s="374"/>
+      <c r="C101" s="371"/>
+      <c r="D101" s="371"/>
+      <c r="E101" s="371"/>
+      <c r="F101" s="371"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -7919,13 +7919,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="374" t="s">
+      <c r="B116" s="371" t="s">
         <v>352</v>
       </c>
-      <c r="C116" s="374"/>
-      <c r="D116" s="374"/>
-      <c r="E116" s="374"/>
-      <c r="F116" s="374"/>
+      <c r="C116" s="371"/>
+      <c r="D116" s="371"/>
+      <c r="E116" s="371"/>
+      <c r="F116" s="371"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -8113,13 +8113,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="372" t="s">
+      <c r="B134" s="375" t="s">
         <v>474</v>
       </c>
-      <c r="C134" s="372"/>
-      <c r="D134" s="372"/>
-      <c r="E134" s="372"/>
-      <c r="F134" s="372"/>
+      <c r="C134" s="375"/>
+      <c r="D134" s="375"/>
+      <c r="E134" s="375"/>
+      <c r="F134" s="375"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -8132,22 +8132,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="373" t="s">
+      <c r="B138" s="376" t="s">
         <v>353</v>
       </c>
-      <c r="C138" s="373"/>
-      <c r="D138" s="373"/>
-      <c r="E138" s="373"/>
-      <c r="F138" s="373"/>
+      <c r="C138" s="376"/>
+      <c r="D138" s="376"/>
+      <c r="E138" s="376"/>
+      <c r="F138" s="376"/>
     </row>
     <row r="139" spans="1:6">
-      <c r="B139" s="374" t="s">
+      <c r="B139" s="371" t="s">
         <v>476</v>
       </c>
-      <c r="C139" s="374"/>
-      <c r="D139" s="374"/>
-      <c r="E139" s="374"/>
-      <c r="F139" s="374"/>
+      <c r="C139" s="371"/>
+      <c r="D139" s="371"/>
+      <c r="E139" s="371"/>
+      <c r="F139" s="371"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -8480,13 +8480,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="375" t="s">
+      <c r="B179" s="377" t="s">
         <v>477</v>
       </c>
-      <c r="C179" s="374"/>
-      <c r="D179" s="374"/>
-      <c r="E179" s="374"/>
-      <c r="F179" s="374"/>
+      <c r="C179" s="371"/>
+      <c r="D179" s="371"/>
+      <c r="E179" s="371"/>
+      <c r="F179" s="371"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -8494,13 +8494,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="376" t="s">
+      <c r="B182" s="373" t="s">
         <v>362</v>
       </c>
-      <c r="C182" s="376"/>
-      <c r="D182" s="376"/>
-      <c r="E182" s="376"/>
-      <c r="F182" s="376"/>
+      <c r="C182" s="373"/>
+      <c r="D182" s="373"/>
+      <c r="E182" s="373"/>
+      <c r="F182" s="373"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -8537,22 +8537,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="371" t="s">
+      <c r="B191" s="374" t="s">
         <v>363</v>
       </c>
-      <c r="C191" s="371"/>
-      <c r="D191" s="371"/>
-      <c r="E191" s="371"/>
-      <c r="F191" s="371"/>
+      <c r="C191" s="374"/>
+      <c r="D191" s="374"/>
+      <c r="E191" s="374"/>
+      <c r="F191" s="374"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="371" t="s">
+      <c r="B192" s="374" t="s">
         <v>364</v>
       </c>
-      <c r="C192" s="371"/>
-      <c r="D192" s="371"/>
-      <c r="E192" s="371"/>
-      <c r="F192" s="371"/>
+      <c r="C192" s="374"/>
+      <c r="D192" s="374"/>
+      <c r="E192" s="374"/>
+      <c r="F192" s="374"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -8576,6 +8576,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -8592,17 +8603,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -16146,20 +16146,20 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>0.10150375939849623</v>
+        <v>0.10112359550561799</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>0.10150375939849623</v>
+        <v>0.10112359550561799</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>9.4736842105263175E-2</v>
+        <v>9.4382022471910132E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>0.14548872180451131</v>
+        <v>0.14494382022471913</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
@@ -17345,50 +17345,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>8.0623876067621267E-2</v>
+        <v>8.0321913984971002E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>9.4082357483607701E-2</v>
+        <v>9.372998910351929E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>0.12946317975612526</v>
+        <v>0.12897829893306861</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>0.20996298724083323</v>
+        <v>0.20917660901146684</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>0.17251753011471807</v>
+        <v>0.17187139704312737</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>6.1890375053004272E-2</v>
+        <v>6.1658575895502395E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>7.8568936668863804E-2</v>
+        <v>7.8274670988456085E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>6.9955144303999767E-2</v>
+        <v>6.9693140018217012E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>6.6441248689131205E-2</v>
+        <v>6.6192405061082024E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>1.176142642697028E-2</v>
+        <v>1.1717376140726947E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>5.0950231083659522E-3</v>
+        <v>5.0759406248140201E-3</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -17402,43 +17402,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13402329873484006</v>
+        <v>0.13352133881448486</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1699082912681141</v>
+        <v>0.16927193062666052</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.24428427158839919</v>
+        <v>0.2433693492228996</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.22602111185545765</v>
+        <v>0.22517459083727243</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.7672603860547454E-2</v>
+        <v>8.7344242048335671E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.6849844541822083E-2</v>
+        <v>8.6524564225186049E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.5061882651290971E-2</v>
+        <v>8.4743298821136334E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.7325615345138136E-2</v>
+        <v>8.6998553115381072E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.9959257285661449E-3</v>
+        <v>4.9772143962494185E-3</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-5.2537487550721268E-2</v>
+        <v>-5.2340717934426434E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -21388,7 +21388,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-2.66</v>
+        <v>-2.67</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -21628,7 +21628,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -22239,7 +22239,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.2771356143063628</v>
+        <v>0.27541234630073297</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/0639.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0639.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73135865-88F8-440F-B121-13CEC2472D0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C574577B-7012-47A3-9971-64A6A86B9923}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4759,15 +4759,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4777,7 +4768,16 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="C12" s="366">
         <f>Market_Price</f>
-        <v>2.67</v>
+        <v>2.89</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C14" s="35">
         <f>投资主题!C12*Common_Shares/1000000</f>
-        <v>13593.145605899999</v>
+        <v>14713.180075300001</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",投资主题!D12*Common_Shares/1000000)</f>
@@ -5346,13 +5346,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="371" t="s">
+      <c r="B18" s="374" t="s">
         <v>489</v>
       </c>
-      <c r="C18" s="371"/>
-      <c r="D18" s="371"/>
-      <c r="E18" s="371"/>
-      <c r="F18" s="371"/>
+      <c r="C18" s="374"/>
+      <c r="D18" s="374"/>
+      <c r="E18" s="374"/>
+      <c r="F18" s="374"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -5443,7 +5443,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.27541234630073297</v>
+        <v>0.23964880679790124</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -5565,22 +5565,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="371" t="s">
+      <c r="B36" s="374" t="s">
         <v>492</v>
       </c>
-      <c r="C36" s="371"/>
-      <c r="D36" s="371"/>
-      <c r="E36" s="371"/>
-      <c r="F36" s="371"/>
+      <c r="C36" s="374"/>
+      <c r="D36" s="374"/>
+      <c r="E36" s="374"/>
+      <c r="F36" s="374"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="372" t="s">
+      <c r="B37" s="377" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="372"/>
-      <c r="D37" s="372"/>
-      <c r="E37" s="372"/>
-      <c r="F37" s="372"/>
+      <c r="C37" s="377"/>
+      <c r="D37" s="377"/>
+      <c r="E37" s="377"/>
+      <c r="F37" s="377"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -5770,10 +5770,10 @@
       <c r="B61" s="370" t="s">
         <v>499</v>
       </c>
-      <c r="C61" s="373"/>
-      <c r="D61" s="373"/>
-      <c r="E61" s="373"/>
-      <c r="F61" s="373"/>
+      <c r="C61" s="376"/>
+      <c r="D61" s="376"/>
+      <c r="E61" s="376"/>
+      <c r="F61" s="376"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -5789,22 +5789,22 @@
       </c>
     </row>
     <row r="64" spans="2:6">
-      <c r="B64" s="371" t="s">
+      <c r="B64" s="374" t="s">
         <v>500</v>
       </c>
-      <c r="C64" s="371"/>
-      <c r="D64" s="371"/>
-      <c r="E64" s="371"/>
-      <c r="F64" s="371"/>
+      <c r="C64" s="374"/>
+      <c r="D64" s="374"/>
+      <c r="E64" s="374"/>
+      <c r="F64" s="374"/>
     </row>
     <row r="65" spans="1:6">
-      <c r="B65" s="371" t="s">
+      <c r="B65" s="374" t="s">
         <v>501</v>
       </c>
-      <c r="C65" s="371"/>
-      <c r="D65" s="371"/>
-      <c r="E65" s="371"/>
-      <c r="F65" s="371"/>
+      <c r="C65" s="374"/>
+      <c r="D65" s="374"/>
+      <c r="E65" s="374"/>
+      <c r="F65" s="374"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -5838,7 +5838,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>8.0321913984971002E-2</v>
+        <v>7.4207443024177352E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -5848,7 +5848,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>0.10112359550561799</v>
+        <v>9.3425605536332182E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>503</v>
@@ -5939,22 +5939,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="371" t="s">
+      <c r="B80" s="374" t="s">
         <v>506</v>
       </c>
-      <c r="C80" s="371"/>
-      <c r="D80" s="371"/>
-      <c r="E80" s="371"/>
-      <c r="F80" s="371"/>
+      <c r="C80" s="374"/>
+      <c r="D80" s="374"/>
+      <c r="E80" s="374"/>
+      <c r="F80" s="374"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="372" t="s">
+      <c r="B81" s="377" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="372"/>
-      <c r="D81" s="372"/>
-      <c r="E81" s="372"/>
-      <c r="F81" s="372"/>
+      <c r="C81" s="377"/>
+      <c r="D81" s="377"/>
+      <c r="E81" s="377"/>
+      <c r="F81" s="377"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5998,22 +5998,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6">
-      <c r="B89" s="371" t="s">
+      <c r="B89" s="374" t="s">
         <v>507</v>
       </c>
-      <c r="C89" s="371"/>
-      <c r="D89" s="371"/>
-      <c r="E89" s="371"/>
-      <c r="F89" s="371"/>
+      <c r="C89" s="374"/>
+      <c r="D89" s="374"/>
+      <c r="E89" s="374"/>
+      <c r="F89" s="374"/>
     </row>
     <row r="90" spans="1:6">
-      <c r="B90" s="371" t="s">
+      <c r="B90" s="374" t="s">
         <v>508</v>
       </c>
-      <c r="C90" s="371"/>
-      <c r="D90" s="371"/>
-      <c r="E90" s="371"/>
-      <c r="F90" s="371"/>
+      <c r="C90" s="374"/>
+      <c r="D90" s="374"/>
+      <c r="E90" s="374"/>
+      <c r="F90" s="374"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -6050,13 +6050,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="371" t="s">
+      <c r="B97" s="374" t="s">
         <v>510</v>
       </c>
-      <c r="C97" s="371"/>
-      <c r="D97" s="371"/>
-      <c r="E97" s="371"/>
-      <c r="F97" s="371"/>
+      <c r="C97" s="374"/>
+      <c r="D97" s="374"/>
+      <c r="E97" s="374"/>
+      <c r="F97" s="374"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -6069,13 +6069,13 @@
       </c>
     </row>
     <row r="101" spans="2:6">
-      <c r="B101" s="371" t="s">
+      <c r="B101" s="374" t="s">
         <v>511</v>
       </c>
-      <c r="C101" s="371"/>
-      <c r="D101" s="371"/>
-      <c r="E101" s="371"/>
-      <c r="F101" s="371"/>
+      <c r="C101" s="374"/>
+      <c r="D101" s="374"/>
+      <c r="E101" s="374"/>
+      <c r="F101" s="374"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -6197,13 +6197,13 @@
       </c>
     </row>
     <row r="116" spans="1:6">
-      <c r="B116" s="371" t="s">
+      <c r="B116" s="374" t="s">
         <v>516</v>
       </c>
-      <c r="C116" s="371"/>
-      <c r="D116" s="371"/>
-      <c r="E116" s="371"/>
-      <c r="F116" s="371"/>
+      <c r="C116" s="374"/>
+      <c r="D116" s="374"/>
+      <c r="E116" s="374"/>
+      <c r="F116" s="374"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -6391,13 +6391,13 @@
       </c>
     </row>
     <row r="134" spans="1:6">
-      <c r="B134" s="375" t="s">
+      <c r="B134" s="372" t="s">
         <v>524</v>
       </c>
-      <c r="C134" s="375"/>
-      <c r="D134" s="375"/>
-      <c r="E134" s="375"/>
-      <c r="F134" s="375"/>
+      <c r="C134" s="372"/>
+      <c r="D134" s="372"/>
+      <c r="E134" s="372"/>
+      <c r="F134" s="372"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -6410,22 +6410,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="376" t="s">
+      <c r="B138" s="373" t="s">
         <v>526</v>
       </c>
-      <c r="C138" s="376"/>
-      <c r="D138" s="376"/>
-      <c r="E138" s="376"/>
-      <c r="F138" s="376"/>
+      <c r="C138" s="373"/>
+      <c r="D138" s="373"/>
+      <c r="E138" s="373"/>
+      <c r="F138" s="373"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="371" t="s">
+      <c r="B139" s="374" t="s">
         <v>527</v>
       </c>
-      <c r="C139" s="371"/>
-      <c r="D139" s="371"/>
-      <c r="E139" s="371"/>
-      <c r="F139" s="371"/>
+      <c r="C139" s="374"/>
+      <c r="D139" s="374"/>
+      <c r="E139" s="374"/>
+      <c r="F139" s="374"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -6758,13 +6758,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="377" t="s">
+      <c r="B179" s="375" t="s">
         <v>534</v>
       </c>
-      <c r="C179" s="371"/>
-      <c r="D179" s="371"/>
-      <c r="E179" s="371"/>
-      <c r="F179" s="371"/>
+      <c r="C179" s="374"/>
+      <c r="D179" s="374"/>
+      <c r="E179" s="374"/>
+      <c r="F179" s="374"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -6772,13 +6772,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="373" t="s">
+      <c r="B182" s="376" t="s">
         <v>536</v>
       </c>
-      <c r="C182" s="373"/>
-      <c r="D182" s="373"/>
-      <c r="E182" s="373"/>
-      <c r="F182" s="373"/>
+      <c r="C182" s="376"/>
+      <c r="D182" s="376"/>
+      <c r="E182" s="376"/>
+      <c r="F182" s="376"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -6815,22 +6815,22 @@
       </c>
     </row>
     <row r="191" spans="1:6">
-      <c r="B191" s="374" t="s">
+      <c r="B191" s="371" t="s">
         <v>543</v>
       </c>
-      <c r="C191" s="374"/>
-      <c r="D191" s="374"/>
-      <c r="E191" s="374"/>
-      <c r="F191" s="374"/>
+      <c r="C191" s="371"/>
+      <c r="D191" s="371"/>
+      <c r="E191" s="371"/>
+      <c r="F191" s="371"/>
     </row>
     <row r="192" spans="1:6">
-      <c r="B192" s="374" t="s">
+      <c r="B192" s="371" t="s">
         <v>544</v>
       </c>
-      <c r="C192" s="374"/>
-      <c r="D192" s="374"/>
-      <c r="E192" s="374"/>
-      <c r="F192" s="374"/>
+      <c r="C192" s="371"/>
+      <c r="D192" s="371"/>
+      <c r="E192" s="371"/>
+      <c r="F192" s="371"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -6854,15 +6854,12 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B138:F138"/>
-    <mergeCell ref="B139:F139"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B43:F43"/>
     <mergeCell ref="B116:F116"/>
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B58:F58"/>
@@ -6875,12 +6872,15 @@
     <mergeCell ref="B90:F90"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B47:F47"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B138:F138"/>
+    <mergeCell ref="B139:F139"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">
@@ -7023,7 +7023,7 @@
         <v>463</v>
       </c>
       <c r="C12" s="50">
-        <v>2.67</v>
+        <v>2.89</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -7044,7 +7044,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>13593.145605899999</v>
+        <v>14713.180075300001</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -7081,13 +7081,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="371" t="s">
+      <c r="B18" s="374" t="s">
         <v>468</v>
       </c>
-      <c r="C18" s="371"/>
-      <c r="D18" s="371"/>
-      <c r="E18" s="371"/>
-      <c r="F18" s="371"/>
+      <c r="C18" s="374"/>
+      <c r="D18" s="374"/>
+      <c r="E18" s="374"/>
+      <c r="F18" s="374"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -7170,7 +7170,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.27541234630073297</v>
+        <v>0.23964880679790124</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -7287,22 +7287,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6">
-      <c r="B36" s="371" t="s">
+      <c r="B36" s="374" t="s">
         <v>469</v>
       </c>
-      <c r="C36" s="371"/>
-      <c r="D36" s="371"/>
-      <c r="E36" s="371"/>
-      <c r="F36" s="371"/>
+      <c r="C36" s="374"/>
+      <c r="D36" s="374"/>
+      <c r="E36" s="374"/>
+      <c r="F36" s="374"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="372" t="s">
+      <c r="B37" s="377" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="372"/>
-      <c r="D37" s="372"/>
-      <c r="E37" s="372"/>
-      <c r="F37" s="372"/>
+      <c r="C37" s="377"/>
+      <c r="D37" s="377"/>
+      <c r="E37" s="377"/>
+      <c r="F37" s="377"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -7492,10 +7492,10 @@
       <c r="B61" s="370" t="s">
         <v>329</v>
       </c>
-      <c r="C61" s="373"/>
-      <c r="D61" s="373"/>
-      <c r="E61" s="373"/>
-      <c r="F61" s="373"/>
+      <c r="C61" s="376"/>
+      <c r="D61" s="376"/>
+      <c r="E61" s="376"/>
+      <c r="F61" s="376"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -7511,22 +7511,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="371" t="s">
+      <c r="B64" s="374" t="s">
         <v>334</v>
       </c>
-      <c r="C64" s="371"/>
-      <c r="D64" s="371"/>
-      <c r="E64" s="371"/>
-      <c r="F64" s="371"/>
+      <c r="C64" s="374"/>
+      <c r="D64" s="374"/>
+      <c r="E64" s="374"/>
+      <c r="F64" s="374"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="371" t="s">
+      <c r="B65" s="374" t="s">
         <v>348</v>
       </c>
-      <c r="C65" s="371"/>
-      <c r="D65" s="371"/>
-      <c r="E65" s="371"/>
-      <c r="F65" s="371"/>
+      <c r="C65" s="374"/>
+      <c r="D65" s="374"/>
+      <c r="E65" s="374"/>
+      <c r="F65" s="374"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -7560,7 +7560,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>8.0321913984971002E-2</v>
+        <v>7.4207443024177352E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -7570,7 +7570,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>0.10112359550561799</v>
+        <v>9.3425605536332182E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>424</v>
@@ -7661,22 +7661,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="371" t="s">
+      <c r="B80" s="374" t="s">
         <v>471</v>
       </c>
-      <c r="C80" s="371"/>
-      <c r="D80" s="371"/>
-      <c r="E80" s="371"/>
-      <c r="F80" s="371"/>
+      <c r="C80" s="374"/>
+      <c r="D80" s="374"/>
+      <c r="E80" s="374"/>
+      <c r="F80" s="374"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="372" t="s">
+      <c r="B81" s="377" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="372"/>
-      <c r="D81" s="372"/>
-      <c r="E81" s="372"/>
-      <c r="F81" s="372"/>
+      <c r="C81" s="377"/>
+      <c r="D81" s="377"/>
+      <c r="E81" s="377"/>
+      <c r="F81" s="377"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -7720,22 +7720,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="371" t="s">
+      <c r="B89" s="374" t="s">
         <v>349</v>
       </c>
-      <c r="C89" s="371"/>
-      <c r="D89" s="371"/>
-      <c r="E89" s="371"/>
-      <c r="F89" s="371"/>
+      <c r="C89" s="374"/>
+      <c r="D89" s="374"/>
+      <c r="E89" s="374"/>
+      <c r="F89" s="374"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="371" t="s">
+      <c r="B90" s="374" t="s">
         <v>350</v>
       </c>
-      <c r="C90" s="371"/>
-      <c r="D90" s="371"/>
-      <c r="E90" s="371"/>
-      <c r="F90" s="371"/>
+      <c r="C90" s="374"/>
+      <c r="D90" s="374"/>
+      <c r="E90" s="374"/>
+      <c r="F90" s="374"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -7772,13 +7772,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="371" t="s">
+      <c r="B97" s="374" t="s">
         <v>351</v>
       </c>
-      <c r="C97" s="371"/>
-      <c r="D97" s="371"/>
-      <c r="E97" s="371"/>
-      <c r="F97" s="371"/>
+      <c r="C97" s="374"/>
+      <c r="D97" s="374"/>
+      <c r="E97" s="374"/>
+      <c r="F97" s="374"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -7791,13 +7791,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="371" t="s">
+      <c r="B101" s="374" t="s">
         <v>335</v>
       </c>
-      <c r="C101" s="371"/>
-      <c r="D101" s="371"/>
-      <c r="E101" s="371"/>
-      <c r="F101" s="371"/>
+      <c r="C101" s="374"/>
+      <c r="D101" s="374"/>
+      <c r="E101" s="374"/>
+      <c r="F101" s="374"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -7919,13 +7919,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="371" t="s">
+      <c r="B116" s="374" t="s">
         <v>352</v>
       </c>
-      <c r="C116" s="371"/>
-      <c r="D116" s="371"/>
-      <c r="E116" s="371"/>
-      <c r="F116" s="371"/>
+      <c r="C116" s="374"/>
+      <c r="D116" s="374"/>
+      <c r="E116" s="374"/>
+      <c r="F116" s="374"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -8113,13 +8113,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="375" t="s">
+      <c r="B134" s="372" t="s">
         <v>474</v>
       </c>
-      <c r="C134" s="375"/>
-      <c r="D134" s="375"/>
-      <c r="E134" s="375"/>
-      <c r="F134" s="375"/>
+      <c r="C134" s="372"/>
+      <c r="D134" s="372"/>
+      <c r="E134" s="372"/>
+      <c r="F134" s="372"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -8132,22 +8132,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="376" t="s">
+      <c r="B138" s="373" t="s">
         <v>353</v>
       </c>
-      <c r="C138" s="376"/>
-      <c r="D138" s="376"/>
-      <c r="E138" s="376"/>
-      <c r="F138" s="376"/>
+      <c r="C138" s="373"/>
+      <c r="D138" s="373"/>
+      <c r="E138" s="373"/>
+      <c r="F138" s="373"/>
     </row>
     <row r="139" spans="1:6">
-      <c r="B139" s="371" t="s">
+      <c r="B139" s="374" t="s">
         <v>476</v>
       </c>
-      <c r="C139" s="371"/>
-      <c r="D139" s="371"/>
-      <c r="E139" s="371"/>
-      <c r="F139" s="371"/>
+      <c r="C139" s="374"/>
+      <c r="D139" s="374"/>
+      <c r="E139" s="374"/>
+      <c r="F139" s="374"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -8480,13 +8480,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="377" t="s">
+      <c r="B179" s="375" t="s">
         <v>477</v>
       </c>
-      <c r="C179" s="371"/>
-      <c r="D179" s="371"/>
-      <c r="E179" s="371"/>
-      <c r="F179" s="371"/>
+      <c r="C179" s="374"/>
+      <c r="D179" s="374"/>
+      <c r="E179" s="374"/>
+      <c r="F179" s="374"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -8494,13 +8494,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="373" t="s">
+      <c r="B182" s="376" t="s">
         <v>362</v>
       </c>
-      <c r="C182" s="373"/>
-      <c r="D182" s="373"/>
-      <c r="E182" s="373"/>
-      <c r="F182" s="373"/>
+      <c r="C182" s="376"/>
+      <c r="D182" s="376"/>
+      <c r="E182" s="376"/>
+      <c r="F182" s="376"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -8537,22 +8537,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="374" t="s">
+      <c r="B191" s="371" t="s">
         <v>363</v>
       </c>
-      <c r="C191" s="374"/>
-      <c r="D191" s="374"/>
-      <c r="E191" s="374"/>
-      <c r="F191" s="374"/>
+      <c r="C191" s="371"/>
+      <c r="D191" s="371"/>
+      <c r="E191" s="371"/>
+      <c r="F191" s="371"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="374" t="s">
+      <c r="B192" s="371" t="s">
         <v>364</v>
       </c>
-      <c r="C192" s="374"/>
-      <c r="D192" s="374"/>
-      <c r="E192" s="374"/>
-      <c r="F192" s="374"/>
+      <c r="C192" s="371"/>
+      <c r="D192" s="371"/>
+      <c r="E192" s="371"/>
+      <c r="F192" s="371"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -8576,17 +8576,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -8603,6 +8592,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -16146,20 +16146,20 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>0.10112359550561799</v>
+        <v>9.3425605536332182E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>0.10112359550561799</v>
+        <v>9.3425605536332182E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>9.4382022471910132E-2</v>
+        <v>8.7197231833910052E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>0.14494382022471913</v>
+        <v>0.13391003460207615</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
@@ -17345,50 +17345,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>8.0321913984971002E-2</v>
+        <v>7.4207443024177352E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>9.372998910351929E-2</v>
+        <v>8.6594834223666595E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>0.12897829893306861</v>
+        <v>0.11915988171325023</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>0.20917660901146684</v>
+        <v>0.19325313012478076</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>0.17187139704312737</v>
+        <v>0.15878776128205885</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>6.1658575895502395E-2</v>
+        <v>5.6964843474391479E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>7.8274670988456085E-2</v>
+        <v>7.2316045515286406E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>6.9693140018217012E-2</v>
+        <v>6.4387779878421939E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>6.6192405061082024E-2</v>
+        <v>6.1153536855740133E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>1.1717376140726947E-2</v>
+        <v>1.0825395950083373E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>5.0759406248140201E-3</v>
+        <v>4.6895368402261016E-3</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -17402,43 +17402,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13352133881448486</v>
+        <v>0.12335708464867631</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16927193062666052</v>
+        <v>0.15638617812220884</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.2433693492228996</v>
+        <v>0.22484296277686569</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.22517459083727243</v>
+        <v>0.2080332725036392</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.7344242048335671E-2</v>
+        <v>8.0695199401057516E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.6524564225186049E-2</v>
+        <v>7.9937919197663229E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.4743298821136334E-2</v>
+        <v>7.8292251852053282E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.6998553115381072E-2</v>
+        <v>8.037582588860466E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.9772143962494185E-3</v>
+        <v>4.5983261031093238E-3</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-5.2340717934426434E-2</v>
+        <v>-4.8356303420387048E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -21388,7 +21388,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-2.67</v>
+        <v>-2.89</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -21628,7 +21628,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>2.67</v>
+        <v>2.89</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>2.67</v>
+        <v>2.89</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -22239,7 +22239,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.27541234630073297</v>
+        <v>0.23964880679790124</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/0639.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0639.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C574577B-7012-47A3-9971-64A6A86B9923}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B975A3C-35D6-447E-8FE5-34A5923CEE3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4759,6 +4759,15 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4768,16 +4777,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="C12" s="366">
         <f>Market_Price</f>
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C14" s="35">
         <f>投资主题!C12*Common_Shares/1000000</f>
-        <v>14713.180075300001</v>
+        <v>14815.001390700001</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",投资主题!D12*Common_Shares/1000000)</f>
@@ -5346,13 +5346,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="374" t="s">
+      <c r="B18" s="371" t="s">
         <v>489</v>
       </c>
-      <c r="C18" s="374"/>
-      <c r="D18" s="374"/>
-      <c r="E18" s="374"/>
-      <c r="F18" s="374"/>
+      <c r="C18" s="371"/>
+      <c r="D18" s="371"/>
+      <c r="E18" s="371"/>
+      <c r="F18" s="371"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -5443,7 +5443,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.23964880679790124</v>
+        <v>0.23658707196826612</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -5565,22 +5565,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="374" t="s">
+      <c r="B36" s="371" t="s">
         <v>492</v>
       </c>
-      <c r="C36" s="374"/>
-      <c r="D36" s="374"/>
-      <c r="E36" s="374"/>
-      <c r="F36" s="374"/>
+      <c r="C36" s="371"/>
+      <c r="D36" s="371"/>
+      <c r="E36" s="371"/>
+      <c r="F36" s="371"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="377" t="s">
+      <c r="B37" s="372" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="377"/>
-      <c r="D37" s="377"/>
-      <c r="E37" s="377"/>
-      <c r="F37" s="377"/>
+      <c r="C37" s="372"/>
+      <c r="D37" s="372"/>
+      <c r="E37" s="372"/>
+      <c r="F37" s="372"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -5770,10 +5770,10 @@
       <c r="B61" s="370" t="s">
         <v>499</v>
       </c>
-      <c r="C61" s="376"/>
-      <c r="D61" s="376"/>
-      <c r="E61" s="376"/>
-      <c r="F61" s="376"/>
+      <c r="C61" s="373"/>
+      <c r="D61" s="373"/>
+      <c r="E61" s="373"/>
+      <c r="F61" s="373"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -5789,22 +5789,22 @@
       </c>
     </row>
     <row r="64" spans="2:6">
-      <c r="B64" s="374" t="s">
+      <c r="B64" s="371" t="s">
         <v>500</v>
       </c>
-      <c r="C64" s="374"/>
-      <c r="D64" s="374"/>
-      <c r="E64" s="374"/>
-      <c r="F64" s="374"/>
+      <c r="C64" s="371"/>
+      <c r="D64" s="371"/>
+      <c r="E64" s="371"/>
+      <c r="F64" s="371"/>
     </row>
     <row r="65" spans="1:6">
-      <c r="B65" s="374" t="s">
+      <c r="B65" s="371" t="s">
         <v>501</v>
       </c>
-      <c r="C65" s="374"/>
-      <c r="D65" s="374"/>
-      <c r="E65" s="374"/>
-      <c r="F65" s="374"/>
+      <c r="C65" s="371"/>
+      <c r="D65" s="371"/>
+      <c r="E65" s="371"/>
+      <c r="F65" s="371"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -5838,7 +5838,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>7.4207443024177352E-2</v>
+        <v>7.3697426233633179E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -5848,7 +5848,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>9.3425605536332182E-2</v>
+        <v>9.2783505154639179E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>503</v>
@@ -5939,22 +5939,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="374" t="s">
+      <c r="B80" s="371" t="s">
         <v>506</v>
       </c>
-      <c r="C80" s="374"/>
-      <c r="D80" s="374"/>
-      <c r="E80" s="374"/>
-      <c r="F80" s="374"/>
+      <c r="C80" s="371"/>
+      <c r="D80" s="371"/>
+      <c r="E80" s="371"/>
+      <c r="F80" s="371"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="377" t="s">
+      <c r="B81" s="372" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="377"/>
-      <c r="D81" s="377"/>
-      <c r="E81" s="377"/>
-      <c r="F81" s="377"/>
+      <c r="C81" s="372"/>
+      <c r="D81" s="372"/>
+      <c r="E81" s="372"/>
+      <c r="F81" s="372"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5998,22 +5998,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6">
-      <c r="B89" s="374" t="s">
+      <c r="B89" s="371" t="s">
         <v>507</v>
       </c>
-      <c r="C89" s="374"/>
-      <c r="D89" s="374"/>
-      <c r="E89" s="374"/>
-      <c r="F89" s="374"/>
+      <c r="C89" s="371"/>
+      <c r="D89" s="371"/>
+      <c r="E89" s="371"/>
+      <c r="F89" s="371"/>
     </row>
     <row r="90" spans="1:6">
-      <c r="B90" s="374" t="s">
+      <c r="B90" s="371" t="s">
         <v>508</v>
       </c>
-      <c r="C90" s="374"/>
-      <c r="D90" s="374"/>
-      <c r="E90" s="374"/>
-      <c r="F90" s="374"/>
+      <c r="C90" s="371"/>
+      <c r="D90" s="371"/>
+      <c r="E90" s="371"/>
+      <c r="F90" s="371"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -6050,13 +6050,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="374" t="s">
+      <c r="B97" s="371" t="s">
         <v>510</v>
       </c>
-      <c r="C97" s="374"/>
-      <c r="D97" s="374"/>
-      <c r="E97" s="374"/>
-      <c r="F97" s="374"/>
+      <c r="C97" s="371"/>
+      <c r="D97" s="371"/>
+      <c r="E97" s="371"/>
+      <c r="F97" s="371"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -6069,13 +6069,13 @@
       </c>
     </row>
     <row r="101" spans="2:6">
-      <c r="B101" s="374" t="s">
+      <c r="B101" s="371" t="s">
         <v>511</v>
       </c>
-      <c r="C101" s="374"/>
-      <c r="D101" s="374"/>
-      <c r="E101" s="374"/>
-      <c r="F101" s="374"/>
+      <c r="C101" s="371"/>
+      <c r="D101" s="371"/>
+      <c r="E101" s="371"/>
+      <c r="F101" s="371"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -6197,13 +6197,13 @@
       </c>
     </row>
     <row r="116" spans="1:6">
-      <c r="B116" s="374" t="s">
+      <c r="B116" s="371" t="s">
         <v>516</v>
       </c>
-      <c r="C116" s="374"/>
-      <c r="D116" s="374"/>
-      <c r="E116" s="374"/>
-      <c r="F116" s="374"/>
+      <c r="C116" s="371"/>
+      <c r="D116" s="371"/>
+      <c r="E116" s="371"/>
+      <c r="F116" s="371"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -6391,13 +6391,13 @@
       </c>
     </row>
     <row r="134" spans="1:6">
-      <c r="B134" s="372" t="s">
+      <c r="B134" s="375" t="s">
         <v>524</v>
       </c>
-      <c r="C134" s="372"/>
-      <c r="D134" s="372"/>
-      <c r="E134" s="372"/>
-      <c r="F134" s="372"/>
+      <c r="C134" s="375"/>
+      <c r="D134" s="375"/>
+      <c r="E134" s="375"/>
+      <c r="F134" s="375"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -6410,22 +6410,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="373" t="s">
+      <c r="B138" s="376" t="s">
         <v>526</v>
       </c>
-      <c r="C138" s="373"/>
-      <c r="D138" s="373"/>
-      <c r="E138" s="373"/>
-      <c r="F138" s="373"/>
+      <c r="C138" s="376"/>
+      <c r="D138" s="376"/>
+      <c r="E138" s="376"/>
+      <c r="F138" s="376"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="374" t="s">
+      <c r="B139" s="371" t="s">
         <v>527</v>
       </c>
-      <c r="C139" s="374"/>
-      <c r="D139" s="374"/>
-      <c r="E139" s="374"/>
-      <c r="F139" s="374"/>
+      <c r="C139" s="371"/>
+      <c r="D139" s="371"/>
+      <c r="E139" s="371"/>
+      <c r="F139" s="371"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -6758,13 +6758,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="375" t="s">
+      <c r="B179" s="377" t="s">
         <v>534</v>
       </c>
-      <c r="C179" s="374"/>
-      <c r="D179" s="374"/>
-      <c r="E179" s="374"/>
-      <c r="F179" s="374"/>
+      <c r="C179" s="371"/>
+      <c r="D179" s="371"/>
+      <c r="E179" s="371"/>
+      <c r="F179" s="371"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -6772,13 +6772,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="376" t="s">
+      <c r="B182" s="373" t="s">
         <v>536</v>
       </c>
-      <c r="C182" s="376"/>
-      <c r="D182" s="376"/>
-      <c r="E182" s="376"/>
-      <c r="F182" s="376"/>
+      <c r="C182" s="373"/>
+      <c r="D182" s="373"/>
+      <c r="E182" s="373"/>
+      <c r="F182" s="373"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -6815,22 +6815,22 @@
       </c>
     </row>
     <row r="191" spans="1:6">
-      <c r="B191" s="371" t="s">
+      <c r="B191" s="374" t="s">
         <v>543</v>
       </c>
-      <c r="C191" s="371"/>
-      <c r="D191" s="371"/>
-      <c r="E191" s="371"/>
-      <c r="F191" s="371"/>
+      <c r="C191" s="374"/>
+      <c r="D191" s="374"/>
+      <c r="E191" s="374"/>
+      <c r="F191" s="374"/>
     </row>
     <row r="192" spans="1:6">
-      <c r="B192" s="371" t="s">
+      <c r="B192" s="374" t="s">
         <v>544</v>
       </c>
-      <c r="C192" s="371"/>
-      <c r="D192" s="371"/>
-      <c r="E192" s="371"/>
-      <c r="F192" s="371"/>
+      <c r="C192" s="374"/>
+      <c r="D192" s="374"/>
+      <c r="E192" s="374"/>
+      <c r="F192" s="374"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -6854,12 +6854,15 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B47:F47"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B138:F138"/>
+    <mergeCell ref="B139:F139"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B182:F182"/>
     <mergeCell ref="B116:F116"/>
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B58:F58"/>
@@ -6872,15 +6875,12 @@
     <mergeCell ref="B90:F90"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B138:F138"/>
-    <mergeCell ref="B139:F139"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B43:F43"/>
   </mergeCells>
   <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">
@@ -7023,7 +7023,7 @@
         <v>463</v>
       </c>
       <c r="C12" s="50">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -7044,7 +7044,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>14713.180075300001</v>
+        <v>14815.001390700001</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -7081,13 +7081,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="374" t="s">
+      <c r="B18" s="371" t="s">
         <v>468</v>
       </c>
-      <c r="C18" s="374"/>
-      <c r="D18" s="374"/>
-      <c r="E18" s="374"/>
-      <c r="F18" s="374"/>
+      <c r="C18" s="371"/>
+      <c r="D18" s="371"/>
+      <c r="E18" s="371"/>
+      <c r="F18" s="371"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -7170,7 +7170,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.23964880679790124</v>
+        <v>0.23658707196826612</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -7287,22 +7287,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6">
-      <c r="B36" s="374" t="s">
+      <c r="B36" s="371" t="s">
         <v>469</v>
       </c>
-      <c r="C36" s="374"/>
-      <c r="D36" s="374"/>
-      <c r="E36" s="374"/>
-      <c r="F36" s="374"/>
+      <c r="C36" s="371"/>
+      <c r="D36" s="371"/>
+      <c r="E36" s="371"/>
+      <c r="F36" s="371"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="377" t="s">
+      <c r="B37" s="372" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="377"/>
-      <c r="D37" s="377"/>
-      <c r="E37" s="377"/>
-      <c r="F37" s="377"/>
+      <c r="C37" s="372"/>
+      <c r="D37" s="372"/>
+      <c r="E37" s="372"/>
+      <c r="F37" s="372"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -7492,10 +7492,10 @@
       <c r="B61" s="370" t="s">
         <v>329</v>
       </c>
-      <c r="C61" s="376"/>
-      <c r="D61" s="376"/>
-      <c r="E61" s="376"/>
-      <c r="F61" s="376"/>
+      <c r="C61" s="373"/>
+      <c r="D61" s="373"/>
+      <c r="E61" s="373"/>
+      <c r="F61" s="373"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -7511,22 +7511,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="374" t="s">
+      <c r="B64" s="371" t="s">
         <v>334</v>
       </c>
-      <c r="C64" s="374"/>
-      <c r="D64" s="374"/>
-      <c r="E64" s="374"/>
-      <c r="F64" s="374"/>
+      <c r="C64" s="371"/>
+      <c r="D64" s="371"/>
+      <c r="E64" s="371"/>
+      <c r="F64" s="371"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="374" t="s">
+      <c r="B65" s="371" t="s">
         <v>348</v>
       </c>
-      <c r="C65" s="374"/>
-      <c r="D65" s="374"/>
-      <c r="E65" s="374"/>
-      <c r="F65" s="374"/>
+      <c r="C65" s="371"/>
+      <c r="D65" s="371"/>
+      <c r="E65" s="371"/>
+      <c r="F65" s="371"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -7560,7 +7560,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>7.4207443024177352E-2</v>
+        <v>7.3697426233633179E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -7570,7 +7570,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>9.3425605536332182E-2</v>
+        <v>9.2783505154639179E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>424</v>
@@ -7661,22 +7661,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="374" t="s">
+      <c r="B80" s="371" t="s">
         <v>471</v>
       </c>
-      <c r="C80" s="374"/>
-      <c r="D80" s="374"/>
-      <c r="E80" s="374"/>
-      <c r="F80" s="374"/>
+      <c r="C80" s="371"/>
+      <c r="D80" s="371"/>
+      <c r="E80" s="371"/>
+      <c r="F80" s="371"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="377" t="s">
+      <c r="B81" s="372" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="377"/>
-      <c r="D81" s="377"/>
-      <c r="E81" s="377"/>
-      <c r="F81" s="377"/>
+      <c r="C81" s="372"/>
+      <c r="D81" s="372"/>
+      <c r="E81" s="372"/>
+      <c r="F81" s="372"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -7720,22 +7720,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="374" t="s">
+      <c r="B89" s="371" t="s">
         <v>349</v>
       </c>
-      <c r="C89" s="374"/>
-      <c r="D89" s="374"/>
-      <c r="E89" s="374"/>
-      <c r="F89" s="374"/>
+      <c r="C89" s="371"/>
+      <c r="D89" s="371"/>
+      <c r="E89" s="371"/>
+      <c r="F89" s="371"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="374" t="s">
+      <c r="B90" s="371" t="s">
         <v>350</v>
       </c>
-      <c r="C90" s="374"/>
-      <c r="D90" s="374"/>
-      <c r="E90" s="374"/>
-      <c r="F90" s="374"/>
+      <c r="C90" s="371"/>
+      <c r="D90" s="371"/>
+      <c r="E90" s="371"/>
+      <c r="F90" s="371"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -7772,13 +7772,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="374" t="s">
+      <c r="B97" s="371" t="s">
         <v>351</v>
       </c>
-      <c r="C97" s="374"/>
-      <c r="D97" s="374"/>
-      <c r="E97" s="374"/>
-      <c r="F97" s="374"/>
+      <c r="C97" s="371"/>
+      <c r="D97" s="371"/>
+      <c r="E97" s="371"/>
+      <c r="F97" s="371"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -7791,13 +7791,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="374" t="s">
+      <c r="B101" s="371" t="s">
         <v>335</v>
       </c>
-      <c r="C101" s="374"/>
-      <c r="D101" s="374"/>
-      <c r="E101" s="374"/>
-      <c r="F101" s="374"/>
+      <c r="C101" s="371"/>
+      <c r="D101" s="371"/>
+      <c r="E101" s="371"/>
+      <c r="F101" s="371"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -7919,13 +7919,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="374" t="s">
+      <c r="B116" s="371" t="s">
         <v>352</v>
       </c>
-      <c r="C116" s="374"/>
-      <c r="D116" s="374"/>
-      <c r="E116" s="374"/>
-      <c r="F116" s="374"/>
+      <c r="C116" s="371"/>
+      <c r="D116" s="371"/>
+      <c r="E116" s="371"/>
+      <c r="F116" s="371"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -8113,13 +8113,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="372" t="s">
+      <c r="B134" s="375" t="s">
         <v>474</v>
       </c>
-      <c r="C134" s="372"/>
-      <c r="D134" s="372"/>
-      <c r="E134" s="372"/>
-      <c r="F134" s="372"/>
+      <c r="C134" s="375"/>
+      <c r="D134" s="375"/>
+      <c r="E134" s="375"/>
+      <c r="F134" s="375"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -8132,22 +8132,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="373" t="s">
+      <c r="B138" s="376" t="s">
         <v>353</v>
       </c>
-      <c r="C138" s="373"/>
-      <c r="D138" s="373"/>
-      <c r="E138" s="373"/>
-      <c r="F138" s="373"/>
+      <c r="C138" s="376"/>
+      <c r="D138" s="376"/>
+      <c r="E138" s="376"/>
+      <c r="F138" s="376"/>
     </row>
     <row r="139" spans="1:6">
-      <c r="B139" s="374" t="s">
+      <c r="B139" s="371" t="s">
         <v>476</v>
       </c>
-      <c r="C139" s="374"/>
-      <c r="D139" s="374"/>
-      <c r="E139" s="374"/>
-      <c r="F139" s="374"/>
+      <c r="C139" s="371"/>
+      <c r="D139" s="371"/>
+      <c r="E139" s="371"/>
+      <c r="F139" s="371"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -8480,13 +8480,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="375" t="s">
+      <c r="B179" s="377" t="s">
         <v>477</v>
       </c>
-      <c r="C179" s="374"/>
-      <c r="D179" s="374"/>
-      <c r="E179" s="374"/>
-      <c r="F179" s="374"/>
+      <c r="C179" s="371"/>
+      <c r="D179" s="371"/>
+      <c r="E179" s="371"/>
+      <c r="F179" s="371"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -8494,13 +8494,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="376" t="s">
+      <c r="B182" s="373" t="s">
         <v>362</v>
       </c>
-      <c r="C182" s="376"/>
-      <c r="D182" s="376"/>
-      <c r="E182" s="376"/>
-      <c r="F182" s="376"/>
+      <c r="C182" s="373"/>
+      <c r="D182" s="373"/>
+      <c r="E182" s="373"/>
+      <c r="F182" s="373"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -8537,22 +8537,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="371" t="s">
+      <c r="B191" s="374" t="s">
         <v>363</v>
       </c>
-      <c r="C191" s="371"/>
-      <c r="D191" s="371"/>
-      <c r="E191" s="371"/>
-      <c r="F191" s="371"/>
+      <c r="C191" s="374"/>
+      <c r="D191" s="374"/>
+      <c r="E191" s="374"/>
+      <c r="F191" s="374"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="371" t="s">
+      <c r="B192" s="374" t="s">
         <v>364</v>
       </c>
-      <c r="C192" s="371"/>
-      <c r="D192" s="371"/>
-      <c r="E192" s="371"/>
-      <c r="F192" s="371"/>
+      <c r="C192" s="374"/>
+      <c r="D192" s="374"/>
+      <c r="E192" s="374"/>
+      <c r="F192" s="374"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -8576,6 +8576,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -8592,17 +8603,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -16146,20 +16146,20 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>9.3425605536332182E-2</v>
+        <v>9.2783505154639179E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>9.3425605536332182E-2</v>
+        <v>9.2783505154639179E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>8.7197231833910052E-2</v>
+        <v>8.6597938144329908E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>0.13391003460207615</v>
+        <v>0.13298969072164951</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
@@ -17345,50 +17345,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>7.4207443024177352E-2</v>
+        <v>7.3697426233633179E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>8.6594834223666595E-2</v>
+        <v>8.5999680723847588E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>0.11915988171325023</v>
+        <v>0.11834091345405263</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>0.19325313012478076</v>
+        <v>0.1919249299177376</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>0.15878776128205885</v>
+        <v>0.15769643646225087</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>5.6964843474391479E-2</v>
+        <v>5.6573332522677447E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>7.2316045515286406E-2</v>
+        <v>7.181902802033599E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>6.4387779878421939E-2</v>
+        <v>6.3945252181663026E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>6.1153536855740133E-2</v>
+        <v>6.0733237633363912E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>1.0825395950083373E-2</v>
+        <v>1.0750994603347403E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>4.6895368402261016E-3</v>
+        <v>4.657306346478843E-3</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -17402,43 +17402,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12335708464867631</v>
+        <v>0.12250926963390878</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15638617812220884</v>
+        <v>0.15531135902858542</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.22484296277686569</v>
+        <v>0.22329765031791815</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.2080332725036392</v>
+        <v>0.20660349056203345</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.0695199401057516E-2</v>
+        <v>8.0140593219606954E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.9937919197663229E-2</v>
+        <v>7.9388517691150073E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.8292251852053282E-2</v>
+        <v>7.7754160774032299E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.037582588860466E-2</v>
+        <v>7.9823414714112528E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.5983261031093238E-3</v>
+        <v>4.5667224872803936E-3</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-4.8356303420387048E-2</v>
+        <v>-4.8023957692411877E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -21388,7 +21388,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-2.89</v>
+        <v>-2.91</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -21628,7 +21628,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -22239,7 +22239,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.23964880679790124</v>
+        <v>0.23658707196826612</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/0639.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0639.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B975A3C-35D6-447E-8FE5-34A5923CEE3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E8DFB42-2361-4332-B954-736324706D7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4759,15 +4759,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4777,7 +4768,16 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="C12" s="366">
         <f>Market_Price</f>
-        <v>2.91</v>
+        <v>2.86</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C14" s="35">
         <f>投资主题!C12*Common_Shares/1000000</f>
-        <v>14815.001390700001</v>
+        <v>14560.448102199998</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",投资主题!D12*Common_Shares/1000000)</f>
@@ -5346,13 +5346,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="371" t="s">
+      <c r="B18" s="374" t="s">
         <v>489</v>
       </c>
-      <c r="C18" s="371"/>
-      <c r="D18" s="371"/>
-      <c r="E18" s="371"/>
-      <c r="F18" s="371"/>
+      <c r="C18" s="374"/>
+      <c r="D18" s="374"/>
+      <c r="E18" s="374"/>
+      <c r="F18" s="374"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -5443,7 +5443,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.23658707196826612</v>
+        <v>0.24429743578133856</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -5565,22 +5565,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="371" t="s">
+      <c r="B36" s="374" t="s">
         <v>492</v>
       </c>
-      <c r="C36" s="371"/>
-      <c r="D36" s="371"/>
-      <c r="E36" s="371"/>
-      <c r="F36" s="371"/>
+      <c r="C36" s="374"/>
+      <c r="D36" s="374"/>
+      <c r="E36" s="374"/>
+      <c r="F36" s="374"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="372" t="s">
+      <c r="B37" s="377" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="372"/>
-      <c r="D37" s="372"/>
-      <c r="E37" s="372"/>
-      <c r="F37" s="372"/>
+      <c r="C37" s="377"/>
+      <c r="D37" s="377"/>
+      <c r="E37" s="377"/>
+      <c r="F37" s="377"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -5770,10 +5770,10 @@
       <c r="B61" s="370" t="s">
         <v>499</v>
       </c>
-      <c r="C61" s="373"/>
-      <c r="D61" s="373"/>
-      <c r="E61" s="373"/>
-      <c r="F61" s="373"/>
+      <c r="C61" s="376"/>
+      <c r="D61" s="376"/>
+      <c r="E61" s="376"/>
+      <c r="F61" s="376"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -5789,22 +5789,22 @@
       </c>
     </row>
     <row r="64" spans="2:6">
-      <c r="B64" s="371" t="s">
+      <c r="B64" s="374" t="s">
         <v>500</v>
       </c>
-      <c r="C64" s="371"/>
-      <c r="D64" s="371"/>
-      <c r="E64" s="371"/>
-      <c r="F64" s="371"/>
+      <c r="C64" s="374"/>
+      <c r="D64" s="374"/>
+      <c r="E64" s="374"/>
+      <c r="F64" s="374"/>
     </row>
     <row r="65" spans="1:6">
-      <c r="B65" s="371" t="s">
+      <c r="B65" s="374" t="s">
         <v>501</v>
       </c>
-      <c r="C65" s="371"/>
-      <c r="D65" s="371"/>
-      <c r="E65" s="371"/>
-      <c r="F65" s="371"/>
+      <c r="C65" s="374"/>
+      <c r="D65" s="374"/>
+      <c r="E65" s="374"/>
+      <c r="F65" s="374"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -5838,7 +5838,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>7.3697426233633179E-2</v>
+        <v>7.4985842776179229E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -5848,7 +5848,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>9.2783505154639179E-2</v>
+        <v>9.4405594405594415E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>503</v>
@@ -5939,22 +5939,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="371" t="s">
+      <c r="B80" s="374" t="s">
         <v>506</v>
       </c>
-      <c r="C80" s="371"/>
-      <c r="D80" s="371"/>
-      <c r="E80" s="371"/>
-      <c r="F80" s="371"/>
+      <c r="C80" s="374"/>
+      <c r="D80" s="374"/>
+      <c r="E80" s="374"/>
+      <c r="F80" s="374"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="372" t="s">
+      <c r="B81" s="377" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="372"/>
-      <c r="D81" s="372"/>
-      <c r="E81" s="372"/>
-      <c r="F81" s="372"/>
+      <c r="C81" s="377"/>
+      <c r="D81" s="377"/>
+      <c r="E81" s="377"/>
+      <c r="F81" s="377"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5998,22 +5998,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6">
-      <c r="B89" s="371" t="s">
+      <c r="B89" s="374" t="s">
         <v>507</v>
       </c>
-      <c r="C89" s="371"/>
-      <c r="D89" s="371"/>
-      <c r="E89" s="371"/>
-      <c r="F89" s="371"/>
+      <c r="C89" s="374"/>
+      <c r="D89" s="374"/>
+      <c r="E89" s="374"/>
+      <c r="F89" s="374"/>
     </row>
     <row r="90" spans="1:6">
-      <c r="B90" s="371" t="s">
+      <c r="B90" s="374" t="s">
         <v>508</v>
       </c>
-      <c r="C90" s="371"/>
-      <c r="D90" s="371"/>
-      <c r="E90" s="371"/>
-      <c r="F90" s="371"/>
+      <c r="C90" s="374"/>
+      <c r="D90" s="374"/>
+      <c r="E90" s="374"/>
+      <c r="F90" s="374"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -6050,13 +6050,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="371" t="s">
+      <c r="B97" s="374" t="s">
         <v>510</v>
       </c>
-      <c r="C97" s="371"/>
-      <c r="D97" s="371"/>
-      <c r="E97" s="371"/>
-      <c r="F97" s="371"/>
+      <c r="C97" s="374"/>
+      <c r="D97" s="374"/>
+      <c r="E97" s="374"/>
+      <c r="F97" s="374"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -6069,13 +6069,13 @@
       </c>
     </row>
     <row r="101" spans="2:6">
-      <c r="B101" s="371" t="s">
+      <c r="B101" s="374" t="s">
         <v>511</v>
       </c>
-      <c r="C101" s="371"/>
-      <c r="D101" s="371"/>
-      <c r="E101" s="371"/>
-      <c r="F101" s="371"/>
+      <c r="C101" s="374"/>
+      <c r="D101" s="374"/>
+      <c r="E101" s="374"/>
+      <c r="F101" s="374"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -6197,13 +6197,13 @@
       </c>
     </row>
     <row r="116" spans="1:6">
-      <c r="B116" s="371" t="s">
+      <c r="B116" s="374" t="s">
         <v>516</v>
       </c>
-      <c r="C116" s="371"/>
-      <c r="D116" s="371"/>
-      <c r="E116" s="371"/>
-      <c r="F116" s="371"/>
+      <c r="C116" s="374"/>
+      <c r="D116" s="374"/>
+      <c r="E116" s="374"/>
+      <c r="F116" s="374"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -6391,13 +6391,13 @@
       </c>
     </row>
     <row r="134" spans="1:6">
-      <c r="B134" s="375" t="s">
+      <c r="B134" s="372" t="s">
         <v>524</v>
       </c>
-      <c r="C134" s="375"/>
-      <c r="D134" s="375"/>
-      <c r="E134" s="375"/>
-      <c r="F134" s="375"/>
+      <c r="C134" s="372"/>
+      <c r="D134" s="372"/>
+      <c r="E134" s="372"/>
+      <c r="F134" s="372"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -6410,22 +6410,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="376" t="s">
+      <c r="B138" s="373" t="s">
         <v>526</v>
       </c>
-      <c r="C138" s="376"/>
-      <c r="D138" s="376"/>
-      <c r="E138" s="376"/>
-      <c r="F138" s="376"/>
+      <c r="C138" s="373"/>
+      <c r="D138" s="373"/>
+      <c r="E138" s="373"/>
+      <c r="F138" s="373"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="371" t="s">
+      <c r="B139" s="374" t="s">
         <v>527</v>
       </c>
-      <c r="C139" s="371"/>
-      <c r="D139" s="371"/>
-      <c r="E139" s="371"/>
-      <c r="F139" s="371"/>
+      <c r="C139" s="374"/>
+      <c r="D139" s="374"/>
+      <c r="E139" s="374"/>
+      <c r="F139" s="374"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -6758,13 +6758,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="377" t="s">
+      <c r="B179" s="375" t="s">
         <v>534</v>
       </c>
-      <c r="C179" s="371"/>
-      <c r="D179" s="371"/>
-      <c r="E179" s="371"/>
-      <c r="F179" s="371"/>
+      <c r="C179" s="374"/>
+      <c r="D179" s="374"/>
+      <c r="E179" s="374"/>
+      <c r="F179" s="374"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -6772,13 +6772,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="373" t="s">
+      <c r="B182" s="376" t="s">
         <v>536</v>
       </c>
-      <c r="C182" s="373"/>
-      <c r="D182" s="373"/>
-      <c r="E182" s="373"/>
-      <c r="F182" s="373"/>
+      <c r="C182" s="376"/>
+      <c r="D182" s="376"/>
+      <c r="E182" s="376"/>
+      <c r="F182" s="376"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -6815,22 +6815,22 @@
       </c>
     </row>
     <row r="191" spans="1:6">
-      <c r="B191" s="374" t="s">
+      <c r="B191" s="371" t="s">
         <v>543</v>
       </c>
-      <c r="C191" s="374"/>
-      <c r="D191" s="374"/>
-      <c r="E191" s="374"/>
-      <c r="F191" s="374"/>
+      <c r="C191" s="371"/>
+      <c r="D191" s="371"/>
+      <c r="E191" s="371"/>
+      <c r="F191" s="371"/>
     </row>
     <row r="192" spans="1:6">
-      <c r="B192" s="374" t="s">
+      <c r="B192" s="371" t="s">
         <v>544</v>
       </c>
-      <c r="C192" s="374"/>
-      <c r="D192" s="374"/>
-      <c r="E192" s="374"/>
-      <c r="F192" s="374"/>
+      <c r="C192" s="371"/>
+      <c r="D192" s="371"/>
+      <c r="E192" s="371"/>
+      <c r="F192" s="371"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -6854,15 +6854,12 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B138:F138"/>
-    <mergeCell ref="B139:F139"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B43:F43"/>
     <mergeCell ref="B116:F116"/>
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B58:F58"/>
@@ -6875,12 +6872,15 @@
     <mergeCell ref="B90:F90"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B47:F47"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B138:F138"/>
+    <mergeCell ref="B139:F139"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">
@@ -7023,7 +7023,7 @@
         <v>463</v>
       </c>
       <c r="C12" s="50">
-        <v>2.91</v>
+        <v>2.86</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -7044,7 +7044,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>14815.001390700001</v>
+        <v>14560.448102199998</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -7081,13 +7081,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="371" t="s">
+      <c r="B18" s="374" t="s">
         <v>468</v>
       </c>
-      <c r="C18" s="371"/>
-      <c r="D18" s="371"/>
-      <c r="E18" s="371"/>
-      <c r="F18" s="371"/>
+      <c r="C18" s="374"/>
+      <c r="D18" s="374"/>
+      <c r="E18" s="374"/>
+      <c r="F18" s="374"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -7170,7 +7170,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.23658707196826612</v>
+        <v>0.24429743578133856</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -7287,22 +7287,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6">
-      <c r="B36" s="371" t="s">
+      <c r="B36" s="374" t="s">
         <v>469</v>
       </c>
-      <c r="C36" s="371"/>
-      <c r="D36" s="371"/>
-      <c r="E36" s="371"/>
-      <c r="F36" s="371"/>
+      <c r="C36" s="374"/>
+      <c r="D36" s="374"/>
+      <c r="E36" s="374"/>
+      <c r="F36" s="374"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="372" t="s">
+      <c r="B37" s="377" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="372"/>
-      <c r="D37" s="372"/>
-      <c r="E37" s="372"/>
-      <c r="F37" s="372"/>
+      <c r="C37" s="377"/>
+      <c r="D37" s="377"/>
+      <c r="E37" s="377"/>
+      <c r="F37" s="377"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -7492,10 +7492,10 @@
       <c r="B61" s="370" t="s">
         <v>329</v>
       </c>
-      <c r="C61" s="373"/>
-      <c r="D61" s="373"/>
-      <c r="E61" s="373"/>
-      <c r="F61" s="373"/>
+      <c r="C61" s="376"/>
+      <c r="D61" s="376"/>
+      <c r="E61" s="376"/>
+      <c r="F61" s="376"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -7511,22 +7511,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="371" t="s">
+      <c r="B64" s="374" t="s">
         <v>334</v>
       </c>
-      <c r="C64" s="371"/>
-      <c r="D64" s="371"/>
-      <c r="E64" s="371"/>
-      <c r="F64" s="371"/>
+      <c r="C64" s="374"/>
+      <c r="D64" s="374"/>
+      <c r="E64" s="374"/>
+      <c r="F64" s="374"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="371" t="s">
+      <c r="B65" s="374" t="s">
         <v>348</v>
       </c>
-      <c r="C65" s="371"/>
-      <c r="D65" s="371"/>
-      <c r="E65" s="371"/>
-      <c r="F65" s="371"/>
+      <c r="C65" s="374"/>
+      <c r="D65" s="374"/>
+      <c r="E65" s="374"/>
+      <c r="F65" s="374"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -7560,7 +7560,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>7.3697426233633179E-2</v>
+        <v>7.4985842776179229E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -7570,7 +7570,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>9.2783505154639179E-2</v>
+        <v>9.4405594405594415E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>424</v>
@@ -7661,22 +7661,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="371" t="s">
+      <c r="B80" s="374" t="s">
         <v>471</v>
       </c>
-      <c r="C80" s="371"/>
-      <c r="D80" s="371"/>
-      <c r="E80" s="371"/>
-      <c r="F80" s="371"/>
+      <c r="C80" s="374"/>
+      <c r="D80" s="374"/>
+      <c r="E80" s="374"/>
+      <c r="F80" s="374"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="372" t="s">
+      <c r="B81" s="377" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="372"/>
-      <c r="D81" s="372"/>
-      <c r="E81" s="372"/>
-      <c r="F81" s="372"/>
+      <c r="C81" s="377"/>
+      <c r="D81" s="377"/>
+      <c r="E81" s="377"/>
+      <c r="F81" s="377"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -7720,22 +7720,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="371" t="s">
+      <c r="B89" s="374" t="s">
         <v>349</v>
       </c>
-      <c r="C89" s="371"/>
-      <c r="D89" s="371"/>
-      <c r="E89" s="371"/>
-      <c r="F89" s="371"/>
+      <c r="C89" s="374"/>
+      <c r="D89" s="374"/>
+      <c r="E89" s="374"/>
+      <c r="F89" s="374"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="371" t="s">
+      <c r="B90" s="374" t="s">
         <v>350</v>
       </c>
-      <c r="C90" s="371"/>
-      <c r="D90" s="371"/>
-      <c r="E90" s="371"/>
-      <c r="F90" s="371"/>
+      <c r="C90" s="374"/>
+      <c r="D90" s="374"/>
+      <c r="E90" s="374"/>
+      <c r="F90" s="374"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -7772,13 +7772,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="371" t="s">
+      <c r="B97" s="374" t="s">
         <v>351</v>
       </c>
-      <c r="C97" s="371"/>
-      <c r="D97" s="371"/>
-      <c r="E97" s="371"/>
-      <c r="F97" s="371"/>
+      <c r="C97" s="374"/>
+      <c r="D97" s="374"/>
+      <c r="E97" s="374"/>
+      <c r="F97" s="374"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -7791,13 +7791,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="371" t="s">
+      <c r="B101" s="374" t="s">
         <v>335</v>
       </c>
-      <c r="C101" s="371"/>
-      <c r="D101" s="371"/>
-      <c r="E101" s="371"/>
-      <c r="F101" s="371"/>
+      <c r="C101" s="374"/>
+      <c r="D101" s="374"/>
+      <c r="E101" s="374"/>
+      <c r="F101" s="374"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -7919,13 +7919,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="371" t="s">
+      <c r="B116" s="374" t="s">
         <v>352</v>
       </c>
-      <c r="C116" s="371"/>
-      <c r="D116" s="371"/>
-      <c r="E116" s="371"/>
-      <c r="F116" s="371"/>
+      <c r="C116" s="374"/>
+      <c r="D116" s="374"/>
+      <c r="E116" s="374"/>
+      <c r="F116" s="374"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -8113,13 +8113,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="375" t="s">
+      <c r="B134" s="372" t="s">
         <v>474</v>
       </c>
-      <c r="C134" s="375"/>
-      <c r="D134" s="375"/>
-      <c r="E134" s="375"/>
-      <c r="F134" s="375"/>
+      <c r="C134" s="372"/>
+      <c r="D134" s="372"/>
+      <c r="E134" s="372"/>
+      <c r="F134" s="372"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -8132,22 +8132,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="376" t="s">
+      <c r="B138" s="373" t="s">
         <v>353</v>
       </c>
-      <c r="C138" s="376"/>
-      <c r="D138" s="376"/>
-      <c r="E138" s="376"/>
-      <c r="F138" s="376"/>
+      <c r="C138" s="373"/>
+      <c r="D138" s="373"/>
+      <c r="E138" s="373"/>
+      <c r="F138" s="373"/>
     </row>
     <row r="139" spans="1:6">
-      <c r="B139" s="371" t="s">
+      <c r="B139" s="374" t="s">
         <v>476</v>
       </c>
-      <c r="C139" s="371"/>
-      <c r="D139" s="371"/>
-      <c r="E139" s="371"/>
-      <c r="F139" s="371"/>
+      <c r="C139" s="374"/>
+      <c r="D139" s="374"/>
+      <c r="E139" s="374"/>
+      <c r="F139" s="374"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -8480,13 +8480,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="377" t="s">
+      <c r="B179" s="375" t="s">
         <v>477</v>
       </c>
-      <c r="C179" s="371"/>
-      <c r="D179" s="371"/>
-      <c r="E179" s="371"/>
-      <c r="F179" s="371"/>
+      <c r="C179" s="374"/>
+      <c r="D179" s="374"/>
+      <c r="E179" s="374"/>
+      <c r="F179" s="374"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -8494,13 +8494,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="373" t="s">
+      <c r="B182" s="376" t="s">
         <v>362</v>
       </c>
-      <c r="C182" s="373"/>
-      <c r="D182" s="373"/>
-      <c r="E182" s="373"/>
-      <c r="F182" s="373"/>
+      <c r="C182" s="376"/>
+      <c r="D182" s="376"/>
+      <c r="E182" s="376"/>
+      <c r="F182" s="376"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -8537,22 +8537,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="374" t="s">
+      <c r="B191" s="371" t="s">
         <v>363</v>
       </c>
-      <c r="C191" s="374"/>
-      <c r="D191" s="374"/>
-      <c r="E191" s="374"/>
-      <c r="F191" s="374"/>
+      <c r="C191" s="371"/>
+      <c r="D191" s="371"/>
+      <c r="E191" s="371"/>
+      <c r="F191" s="371"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="374" t="s">
+      <c r="B192" s="371" t="s">
         <v>364</v>
       </c>
-      <c r="C192" s="374"/>
-      <c r="D192" s="374"/>
-      <c r="E192" s="374"/>
-      <c r="F192" s="374"/>
+      <c r="C192" s="371"/>
+      <c r="D192" s="371"/>
+      <c r="E192" s="371"/>
+      <c r="F192" s="371"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -8576,17 +8576,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -8603,6 +8592,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -16146,20 +16146,20 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>9.2783505154639179E-2</v>
+        <v>9.4405594405594415E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>9.2783505154639179E-2</v>
+        <v>9.4405594405594415E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>8.6597938144329908E-2</v>
+        <v>8.8111888111888137E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>0.13298969072164951</v>
+        <v>0.13531468531468535</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
@@ -17345,50 +17345,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>7.3697426233633179E-2</v>
+        <v>7.4985842776179229E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>8.5999680723847588E-2</v>
+        <v>8.7503171645593181E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>0.11834091345405263</v>
+        <v>0.12040981054241021</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>0.1919249299177376</v>
+        <v>0.19528026086035541</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>0.15769643646225087</v>
+        <v>0.1604533671696329</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>5.6573332522677447E-2</v>
+        <v>5.7562376797549435E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>7.181902802033599E-2</v>
+        <v>7.3074605433278927E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>6.3945252181663026E-2</v>
+        <v>6.5063176170852943E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>6.0733237633363912E-2</v>
+        <v>6.1795007522059096E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>1.0750994603347403E-2</v>
+        <v>1.0938949054454876E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>4.657306346478843E-3</v>
+        <v>4.7387277861025996E-3</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -17402,43 +17402,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12250926963390878</v>
+        <v>0.12465104008205406</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15531135902858542</v>
+        <v>0.15802659257803622</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.22329765031791815</v>
+        <v>0.22720145539340628</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.20660349056203345</v>
+        <v>0.21021543969773335</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.0140593219606954E-2</v>
+        <v>8.1541652541628054E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.9388517691150073E-2</v>
+        <v>8.0776428839596764E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.7754160774032299E-2</v>
+        <v>7.9113499249102812E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.9823414714112528E-2</v>
+        <v>8.1218928957366252E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.5667224872803936E-3</v>
+        <v>4.6465602930020793E-3</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-4.8023957692411877E-2</v>
+        <v>-4.8863537372349157E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -21388,7 +21388,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-2.91</v>
+        <v>-2.86</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -21628,7 +21628,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>2.91</v>
+        <v>2.86</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>2.91</v>
+        <v>2.86</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -22239,7 +22239,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.23658707196826612</v>
+        <v>0.24429743578133856</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/0639.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0639.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E8DFB42-2361-4332-B954-736324706D7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBF46C29-E33E-4C64-869F-B02B747C9A87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4759,6 +4759,15 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4768,16 +4777,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="C12" s="366">
         <f>Market_Price</f>
-        <v>2.86</v>
+        <v>2.94</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C14" s="35">
         <f>投资主题!C12*Common_Shares/1000000</f>
-        <v>14560.448102199998</v>
+        <v>14967.7333638</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",投资主题!D12*Common_Shares/1000000)</f>
@@ -5346,13 +5346,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="374" t="s">
+      <c r="B18" s="371" t="s">
         <v>489</v>
       </c>
-      <c r="C18" s="374"/>
-      <c r="D18" s="374"/>
-      <c r="E18" s="374"/>
-      <c r="F18" s="374"/>
+      <c r="C18" s="371"/>
+      <c r="D18" s="371"/>
+      <c r="E18" s="371"/>
+      <c r="F18" s="371"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -5443,7 +5443,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.24429743578133856</v>
+        <v>0.23204925986510649</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -5565,22 +5565,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="374" t="s">
+      <c r="B36" s="371" t="s">
         <v>492</v>
       </c>
-      <c r="C36" s="374"/>
-      <c r="D36" s="374"/>
-      <c r="E36" s="374"/>
-      <c r="F36" s="374"/>
+      <c r="C36" s="371"/>
+      <c r="D36" s="371"/>
+      <c r="E36" s="371"/>
+      <c r="F36" s="371"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="377" t="s">
+      <c r="B37" s="372" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="377"/>
-      <c r="D37" s="377"/>
-      <c r="E37" s="377"/>
-      <c r="F37" s="377"/>
+      <c r="C37" s="372"/>
+      <c r="D37" s="372"/>
+      <c r="E37" s="372"/>
+      <c r="F37" s="372"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -5770,10 +5770,10 @@
       <c r="B61" s="370" t="s">
         <v>499</v>
       </c>
-      <c r="C61" s="376"/>
-      <c r="D61" s="376"/>
-      <c r="E61" s="376"/>
-      <c r="F61" s="376"/>
+      <c r="C61" s="373"/>
+      <c r="D61" s="373"/>
+      <c r="E61" s="373"/>
+      <c r="F61" s="373"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -5789,22 +5789,22 @@
       </c>
     </row>
     <row r="64" spans="2:6">
-      <c r="B64" s="374" t="s">
+      <c r="B64" s="371" t="s">
         <v>500</v>
       </c>
-      <c r="C64" s="374"/>
-      <c r="D64" s="374"/>
-      <c r="E64" s="374"/>
-      <c r="F64" s="374"/>
+      <c r="C64" s="371"/>
+      <c r="D64" s="371"/>
+      <c r="E64" s="371"/>
+      <c r="F64" s="371"/>
     </row>
     <row r="65" spans="1:6">
-      <c r="B65" s="374" t="s">
+      <c r="B65" s="371" t="s">
         <v>501</v>
       </c>
-      <c r="C65" s="374"/>
-      <c r="D65" s="374"/>
-      <c r="E65" s="374"/>
-      <c r="F65" s="374"/>
+      <c r="C65" s="371"/>
+      <c r="D65" s="371"/>
+      <c r="E65" s="371"/>
+      <c r="F65" s="371"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -5838,7 +5838,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>7.4985842776179229E-2</v>
+        <v>7.2945411680228764E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -5848,7 +5848,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>9.4405594405594415E-2</v>
+        <v>9.1836734693877556E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>503</v>
@@ -5939,22 +5939,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="374" t="s">
+      <c r="B80" s="371" t="s">
         <v>506</v>
       </c>
-      <c r="C80" s="374"/>
-      <c r="D80" s="374"/>
-      <c r="E80" s="374"/>
-      <c r="F80" s="374"/>
+      <c r="C80" s="371"/>
+      <c r="D80" s="371"/>
+      <c r="E80" s="371"/>
+      <c r="F80" s="371"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="377" t="s">
+      <c r="B81" s="372" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="377"/>
-      <c r="D81" s="377"/>
-      <c r="E81" s="377"/>
-      <c r="F81" s="377"/>
+      <c r="C81" s="372"/>
+      <c r="D81" s="372"/>
+      <c r="E81" s="372"/>
+      <c r="F81" s="372"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5998,22 +5998,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6">
-      <c r="B89" s="374" t="s">
+      <c r="B89" s="371" t="s">
         <v>507</v>
       </c>
-      <c r="C89" s="374"/>
-      <c r="D89" s="374"/>
-      <c r="E89" s="374"/>
-      <c r="F89" s="374"/>
+      <c r="C89" s="371"/>
+      <c r="D89" s="371"/>
+      <c r="E89" s="371"/>
+      <c r="F89" s="371"/>
     </row>
     <row r="90" spans="1:6">
-      <c r="B90" s="374" t="s">
+      <c r="B90" s="371" t="s">
         <v>508</v>
       </c>
-      <c r="C90" s="374"/>
-      <c r="D90" s="374"/>
-      <c r="E90" s="374"/>
-      <c r="F90" s="374"/>
+      <c r="C90" s="371"/>
+      <c r="D90" s="371"/>
+      <c r="E90" s="371"/>
+      <c r="F90" s="371"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -6050,13 +6050,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="374" t="s">
+      <c r="B97" s="371" t="s">
         <v>510</v>
       </c>
-      <c r="C97" s="374"/>
-      <c r="D97" s="374"/>
-      <c r="E97" s="374"/>
-      <c r="F97" s="374"/>
+      <c r="C97" s="371"/>
+      <c r="D97" s="371"/>
+      <c r="E97" s="371"/>
+      <c r="F97" s="371"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -6069,13 +6069,13 @@
       </c>
     </row>
     <row r="101" spans="2:6">
-      <c r="B101" s="374" t="s">
+      <c r="B101" s="371" t="s">
         <v>511</v>
       </c>
-      <c r="C101" s="374"/>
-      <c r="D101" s="374"/>
-      <c r="E101" s="374"/>
-      <c r="F101" s="374"/>
+      <c r="C101" s="371"/>
+      <c r="D101" s="371"/>
+      <c r="E101" s="371"/>
+      <c r="F101" s="371"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -6197,13 +6197,13 @@
       </c>
     </row>
     <row r="116" spans="1:6">
-      <c r="B116" s="374" t="s">
+      <c r="B116" s="371" t="s">
         <v>516</v>
       </c>
-      <c r="C116" s="374"/>
-      <c r="D116" s="374"/>
-      <c r="E116" s="374"/>
-      <c r="F116" s="374"/>
+      <c r="C116" s="371"/>
+      <c r="D116" s="371"/>
+      <c r="E116" s="371"/>
+      <c r="F116" s="371"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -6391,13 +6391,13 @@
       </c>
     </row>
     <row r="134" spans="1:6">
-      <c r="B134" s="372" t="s">
+      <c r="B134" s="375" t="s">
         <v>524</v>
       </c>
-      <c r="C134" s="372"/>
-      <c r="D134" s="372"/>
-      <c r="E134" s="372"/>
-      <c r="F134" s="372"/>
+      <c r="C134" s="375"/>
+      <c r="D134" s="375"/>
+      <c r="E134" s="375"/>
+      <c r="F134" s="375"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -6410,22 +6410,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="373" t="s">
+      <c r="B138" s="376" t="s">
         <v>526</v>
       </c>
-      <c r="C138" s="373"/>
-      <c r="D138" s="373"/>
-      <c r="E138" s="373"/>
-      <c r="F138" s="373"/>
+      <c r="C138" s="376"/>
+      <c r="D138" s="376"/>
+      <c r="E138" s="376"/>
+      <c r="F138" s="376"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="374" t="s">
+      <c r="B139" s="371" t="s">
         <v>527</v>
       </c>
-      <c r="C139" s="374"/>
-      <c r="D139" s="374"/>
-      <c r="E139" s="374"/>
-      <c r="F139" s="374"/>
+      <c r="C139" s="371"/>
+      <c r="D139" s="371"/>
+      <c r="E139" s="371"/>
+      <c r="F139" s="371"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -6758,13 +6758,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="375" t="s">
+      <c r="B179" s="377" t="s">
         <v>534</v>
       </c>
-      <c r="C179" s="374"/>
-      <c r="D179" s="374"/>
-      <c r="E179" s="374"/>
-      <c r="F179" s="374"/>
+      <c r="C179" s="371"/>
+      <c r="D179" s="371"/>
+      <c r="E179" s="371"/>
+      <c r="F179" s="371"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -6772,13 +6772,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="376" t="s">
+      <c r="B182" s="373" t="s">
         <v>536</v>
       </c>
-      <c r="C182" s="376"/>
-      <c r="D182" s="376"/>
-      <c r="E182" s="376"/>
-      <c r="F182" s="376"/>
+      <c r="C182" s="373"/>
+      <c r="D182" s="373"/>
+      <c r="E182" s="373"/>
+      <c r="F182" s="373"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -6815,22 +6815,22 @@
       </c>
     </row>
     <row r="191" spans="1:6">
-      <c r="B191" s="371" t="s">
+      <c r="B191" s="374" t="s">
         <v>543</v>
       </c>
-      <c r="C191" s="371"/>
-      <c r="D191" s="371"/>
-      <c r="E191" s="371"/>
-      <c r="F191" s="371"/>
+      <c r="C191" s="374"/>
+      <c r="D191" s="374"/>
+      <c r="E191" s="374"/>
+      <c r="F191" s="374"/>
     </row>
     <row r="192" spans="1:6">
-      <c r="B192" s="371" t="s">
+      <c r="B192" s="374" t="s">
         <v>544</v>
       </c>
-      <c r="C192" s="371"/>
-      <c r="D192" s="371"/>
-      <c r="E192" s="371"/>
-      <c r="F192" s="371"/>
+      <c r="C192" s="374"/>
+      <c r="D192" s="374"/>
+      <c r="E192" s="374"/>
+      <c r="F192" s="374"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -6854,12 +6854,15 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B47:F47"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B138:F138"/>
+    <mergeCell ref="B139:F139"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B182:F182"/>
     <mergeCell ref="B116:F116"/>
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B58:F58"/>
@@ -6872,15 +6875,12 @@
     <mergeCell ref="B90:F90"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B138:F138"/>
-    <mergeCell ref="B139:F139"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B43:F43"/>
   </mergeCells>
   <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">
@@ -7023,7 +7023,7 @@
         <v>463</v>
       </c>
       <c r="C12" s="50">
-        <v>2.86</v>
+        <v>2.94</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -7044,7 +7044,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>14560.448102199998</v>
+        <v>14967.7333638</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -7081,13 +7081,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="374" t="s">
+      <c r="B18" s="371" t="s">
         <v>468</v>
       </c>
-      <c r="C18" s="374"/>
-      <c r="D18" s="374"/>
-      <c r="E18" s="374"/>
-      <c r="F18" s="374"/>
+      <c r="C18" s="371"/>
+      <c r="D18" s="371"/>
+      <c r="E18" s="371"/>
+      <c r="F18" s="371"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -7170,7 +7170,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.24429743578133856</v>
+        <v>0.23204925986510649</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -7287,22 +7287,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6">
-      <c r="B36" s="374" t="s">
+      <c r="B36" s="371" t="s">
         <v>469</v>
       </c>
-      <c r="C36" s="374"/>
-      <c r="D36" s="374"/>
-      <c r="E36" s="374"/>
-      <c r="F36" s="374"/>
+      <c r="C36" s="371"/>
+      <c r="D36" s="371"/>
+      <c r="E36" s="371"/>
+      <c r="F36" s="371"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="377" t="s">
+      <c r="B37" s="372" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="377"/>
-      <c r="D37" s="377"/>
-      <c r="E37" s="377"/>
-      <c r="F37" s="377"/>
+      <c r="C37" s="372"/>
+      <c r="D37" s="372"/>
+      <c r="E37" s="372"/>
+      <c r="F37" s="372"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -7492,10 +7492,10 @@
       <c r="B61" s="370" t="s">
         <v>329</v>
       </c>
-      <c r="C61" s="376"/>
-      <c r="D61" s="376"/>
-      <c r="E61" s="376"/>
-      <c r="F61" s="376"/>
+      <c r="C61" s="373"/>
+      <c r="D61" s="373"/>
+      <c r="E61" s="373"/>
+      <c r="F61" s="373"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -7511,22 +7511,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="374" t="s">
+      <c r="B64" s="371" t="s">
         <v>334</v>
       </c>
-      <c r="C64" s="374"/>
-      <c r="D64" s="374"/>
-      <c r="E64" s="374"/>
-      <c r="F64" s="374"/>
+      <c r="C64" s="371"/>
+      <c r="D64" s="371"/>
+      <c r="E64" s="371"/>
+      <c r="F64" s="371"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="374" t="s">
+      <c r="B65" s="371" t="s">
         <v>348</v>
       </c>
-      <c r="C65" s="374"/>
-      <c r="D65" s="374"/>
-      <c r="E65" s="374"/>
-      <c r="F65" s="374"/>
+      <c r="C65" s="371"/>
+      <c r="D65" s="371"/>
+      <c r="E65" s="371"/>
+      <c r="F65" s="371"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -7560,7 +7560,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>7.4985842776179229E-2</v>
+        <v>7.2945411680228764E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -7570,7 +7570,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>9.4405594405594415E-2</v>
+        <v>9.1836734693877556E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>424</v>
@@ -7661,22 +7661,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="374" t="s">
+      <c r="B80" s="371" t="s">
         <v>471</v>
       </c>
-      <c r="C80" s="374"/>
-      <c r="D80" s="374"/>
-      <c r="E80" s="374"/>
-      <c r="F80" s="374"/>
+      <c r="C80" s="371"/>
+      <c r="D80" s="371"/>
+      <c r="E80" s="371"/>
+      <c r="F80" s="371"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="377" t="s">
+      <c r="B81" s="372" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="377"/>
-      <c r="D81" s="377"/>
-      <c r="E81" s="377"/>
-      <c r="F81" s="377"/>
+      <c r="C81" s="372"/>
+      <c r="D81" s="372"/>
+      <c r="E81" s="372"/>
+      <c r="F81" s="372"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -7720,22 +7720,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="374" t="s">
+      <c r="B89" s="371" t="s">
         <v>349</v>
       </c>
-      <c r="C89" s="374"/>
-      <c r="D89" s="374"/>
-      <c r="E89" s="374"/>
-      <c r="F89" s="374"/>
+      <c r="C89" s="371"/>
+      <c r="D89" s="371"/>
+      <c r="E89" s="371"/>
+      <c r="F89" s="371"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="374" t="s">
+      <c r="B90" s="371" t="s">
         <v>350</v>
       </c>
-      <c r="C90" s="374"/>
-      <c r="D90" s="374"/>
-      <c r="E90" s="374"/>
-      <c r="F90" s="374"/>
+      <c r="C90" s="371"/>
+      <c r="D90" s="371"/>
+      <c r="E90" s="371"/>
+      <c r="F90" s="371"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -7772,13 +7772,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="374" t="s">
+      <c r="B97" s="371" t="s">
         <v>351</v>
       </c>
-      <c r="C97" s="374"/>
-      <c r="D97" s="374"/>
-      <c r="E97" s="374"/>
-      <c r="F97" s="374"/>
+      <c r="C97" s="371"/>
+      <c r="D97" s="371"/>
+      <c r="E97" s="371"/>
+      <c r="F97" s="371"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -7791,13 +7791,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="374" t="s">
+      <c r="B101" s="371" t="s">
         <v>335</v>
       </c>
-      <c r="C101" s="374"/>
-      <c r="D101" s="374"/>
-      <c r="E101" s="374"/>
-      <c r="F101" s="374"/>
+      <c r="C101" s="371"/>
+      <c r="D101" s="371"/>
+      <c r="E101" s="371"/>
+      <c r="F101" s="371"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -7919,13 +7919,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="374" t="s">
+      <c r="B116" s="371" t="s">
         <v>352</v>
       </c>
-      <c r="C116" s="374"/>
-      <c r="D116" s="374"/>
-      <c r="E116" s="374"/>
-      <c r="F116" s="374"/>
+      <c r="C116" s="371"/>
+      <c r="D116" s="371"/>
+      <c r="E116" s="371"/>
+      <c r="F116" s="371"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -8113,13 +8113,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="372" t="s">
+      <c r="B134" s="375" t="s">
         <v>474</v>
       </c>
-      <c r="C134" s="372"/>
-      <c r="D134" s="372"/>
-      <c r="E134" s="372"/>
-      <c r="F134" s="372"/>
+      <c r="C134" s="375"/>
+      <c r="D134" s="375"/>
+      <c r="E134" s="375"/>
+      <c r="F134" s="375"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -8132,22 +8132,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="373" t="s">
+      <c r="B138" s="376" t="s">
         <v>353</v>
       </c>
-      <c r="C138" s="373"/>
-      <c r="D138" s="373"/>
-      <c r="E138" s="373"/>
-      <c r="F138" s="373"/>
+      <c r="C138" s="376"/>
+      <c r="D138" s="376"/>
+      <c r="E138" s="376"/>
+      <c r="F138" s="376"/>
     </row>
     <row r="139" spans="1:6">
-      <c r="B139" s="374" t="s">
+      <c r="B139" s="371" t="s">
         <v>476</v>
       </c>
-      <c r="C139" s="374"/>
-      <c r="D139" s="374"/>
-      <c r="E139" s="374"/>
-      <c r="F139" s="374"/>
+      <c r="C139" s="371"/>
+      <c r="D139" s="371"/>
+      <c r="E139" s="371"/>
+      <c r="F139" s="371"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -8480,13 +8480,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="375" t="s">
+      <c r="B179" s="377" t="s">
         <v>477</v>
       </c>
-      <c r="C179" s="374"/>
-      <c r="D179" s="374"/>
-      <c r="E179" s="374"/>
-      <c r="F179" s="374"/>
+      <c r="C179" s="371"/>
+      <c r="D179" s="371"/>
+      <c r="E179" s="371"/>
+      <c r="F179" s="371"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -8494,13 +8494,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="376" t="s">
+      <c r="B182" s="373" t="s">
         <v>362</v>
       </c>
-      <c r="C182" s="376"/>
-      <c r="D182" s="376"/>
-      <c r="E182" s="376"/>
-      <c r="F182" s="376"/>
+      <c r="C182" s="373"/>
+      <c r="D182" s="373"/>
+      <c r="E182" s="373"/>
+      <c r="F182" s="373"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -8537,22 +8537,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="371" t="s">
+      <c r="B191" s="374" t="s">
         <v>363</v>
       </c>
-      <c r="C191" s="371"/>
-      <c r="D191" s="371"/>
-      <c r="E191" s="371"/>
-      <c r="F191" s="371"/>
+      <c r="C191" s="374"/>
+      <c r="D191" s="374"/>
+      <c r="E191" s="374"/>
+      <c r="F191" s="374"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="371" t="s">
+      <c r="B192" s="374" t="s">
         <v>364</v>
       </c>
-      <c r="C192" s="371"/>
-      <c r="D192" s="371"/>
-      <c r="E192" s="371"/>
-      <c r="F192" s="371"/>
+      <c r="C192" s="374"/>
+      <c r="D192" s="374"/>
+      <c r="E192" s="374"/>
+      <c r="F192" s="374"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -8576,6 +8576,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -8592,17 +8603,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -16146,20 +16146,20 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>9.4405594405594415E-2</v>
+        <v>9.1836734693877556E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>9.4405594405594415E-2</v>
+        <v>9.1836734693877556E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>8.8111888111888137E-2</v>
+        <v>8.5714285714285729E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>0.13531468531468535</v>
+        <v>0.13163265306122451</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
@@ -17345,50 +17345,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>7.4985842776179229E-2</v>
+        <v>7.2945411680228764E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>8.7503171645593181E-2</v>
+        <v>8.5122132961359356E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>0.12040981054241021</v>
+        <v>0.11713335311268476</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>0.19528026086035541</v>
+        <v>0.18996651226551578</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>0.1604533671696329</v>
+        <v>0.1560872891514116</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>5.7562376797549435E-2</v>
+        <v>5.5996053619384825E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>7.3074605433278927E-2</v>
+        <v>7.1086180795638693E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>6.5063176170852943E-2</v>
+        <v>6.3292749608380758E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>6.1795007522059096E-2</v>
+        <v>6.0113510718737759E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>1.0938949054454876E-2</v>
+        <v>1.0641290576782635E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>4.7387277861025996E-3</v>
+        <v>4.6097828123311006E-3</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -17402,43 +17402,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12465104008205406</v>
+        <v>0.12125917504580769</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15802659257803622</v>
+        <v>0.15372654924257945</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.22720145539340628</v>
+        <v>0.22101910286569454</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.21021543969773335</v>
+        <v>0.20449529167874742</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.1541652541628054E-2</v>
+        <v>7.9322832064304849E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.0776428839596764E-2</v>
+        <v>7.8578430775934266E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.9113499249102812E-2</v>
+        <v>7.6960750970215652E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.1218928957366252E-2</v>
+        <v>7.9008890074172611E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.6465602930020793E-3</v>
+        <v>4.520123278226513E-3</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-4.8863537372349157E-2</v>
+        <v>-4.7533917307795437E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -21388,7 +21388,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-2.86</v>
+        <v>-2.94</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -21628,7 +21628,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>2.86</v>
+        <v>2.94</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>2.86</v>
+        <v>2.94</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -22239,7 +22239,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.24429743578133856</v>
+        <v>0.23204925986510649</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/0639.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0639.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBF46C29-E33E-4C64-869F-B02B747C9A87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13AD7FE2-8FDE-428E-88F5-E0DF1E8549B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4759,15 +4759,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4777,7 +4768,16 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
@@ -5346,13 +5346,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="371" t="s">
+      <c r="B18" s="374" t="s">
         <v>489</v>
       </c>
-      <c r="C18" s="371"/>
-      <c r="D18" s="371"/>
-      <c r="E18" s="371"/>
-      <c r="F18" s="371"/>
+      <c r="C18" s="374"/>
+      <c r="D18" s="374"/>
+      <c r="E18" s="374"/>
+      <c r="F18" s="374"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -5565,22 +5565,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="371" t="s">
+      <c r="B36" s="374" t="s">
         <v>492</v>
       </c>
-      <c r="C36" s="371"/>
-      <c r="D36" s="371"/>
-      <c r="E36" s="371"/>
-      <c r="F36" s="371"/>
+      <c r="C36" s="374"/>
+      <c r="D36" s="374"/>
+      <c r="E36" s="374"/>
+      <c r="F36" s="374"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="372" t="s">
+      <c r="B37" s="377" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="372"/>
-      <c r="D37" s="372"/>
-      <c r="E37" s="372"/>
-      <c r="F37" s="372"/>
+      <c r="C37" s="377"/>
+      <c r="D37" s="377"/>
+      <c r="E37" s="377"/>
+      <c r="F37" s="377"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -5770,10 +5770,10 @@
       <c r="B61" s="370" t="s">
         <v>499</v>
       </c>
-      <c r="C61" s="373"/>
-      <c r="D61" s="373"/>
-      <c r="E61" s="373"/>
-      <c r="F61" s="373"/>
+      <c r="C61" s="376"/>
+      <c r="D61" s="376"/>
+      <c r="E61" s="376"/>
+      <c r="F61" s="376"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -5789,22 +5789,22 @@
       </c>
     </row>
     <row r="64" spans="2:6">
-      <c r="B64" s="371" t="s">
+      <c r="B64" s="374" t="s">
         <v>500</v>
       </c>
-      <c r="C64" s="371"/>
-      <c r="D64" s="371"/>
-      <c r="E64" s="371"/>
-      <c r="F64" s="371"/>
+      <c r="C64" s="374"/>
+      <c r="D64" s="374"/>
+      <c r="E64" s="374"/>
+      <c r="F64" s="374"/>
     </row>
     <row r="65" spans="1:6">
-      <c r="B65" s="371" t="s">
+      <c r="B65" s="374" t="s">
         <v>501</v>
       </c>
-      <c r="C65" s="371"/>
-      <c r="D65" s="371"/>
-      <c r="E65" s="371"/>
-      <c r="F65" s="371"/>
+      <c r="C65" s="374"/>
+      <c r="D65" s="374"/>
+      <c r="E65" s="374"/>
+      <c r="F65" s="374"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -5939,22 +5939,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="371" t="s">
+      <c r="B80" s="374" t="s">
         <v>506</v>
       </c>
-      <c r="C80" s="371"/>
-      <c r="D80" s="371"/>
-      <c r="E80" s="371"/>
-      <c r="F80" s="371"/>
+      <c r="C80" s="374"/>
+      <c r="D80" s="374"/>
+      <c r="E80" s="374"/>
+      <c r="F80" s="374"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="372" t="s">
+      <c r="B81" s="377" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="372"/>
-      <c r="D81" s="372"/>
-      <c r="E81" s="372"/>
-      <c r="F81" s="372"/>
+      <c r="C81" s="377"/>
+      <c r="D81" s="377"/>
+      <c r="E81" s="377"/>
+      <c r="F81" s="377"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5998,22 +5998,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6">
-      <c r="B89" s="371" t="s">
+      <c r="B89" s="374" t="s">
         <v>507</v>
       </c>
-      <c r="C89" s="371"/>
-      <c r="D89" s="371"/>
-      <c r="E89" s="371"/>
-      <c r="F89" s="371"/>
+      <c r="C89" s="374"/>
+      <c r="D89" s="374"/>
+      <c r="E89" s="374"/>
+      <c r="F89" s="374"/>
     </row>
     <row r="90" spans="1:6">
-      <c r="B90" s="371" t="s">
+      <c r="B90" s="374" t="s">
         <v>508</v>
       </c>
-      <c r="C90" s="371"/>
-      <c r="D90" s="371"/>
-      <c r="E90" s="371"/>
-      <c r="F90" s="371"/>
+      <c r="C90" s="374"/>
+      <c r="D90" s="374"/>
+      <c r="E90" s="374"/>
+      <c r="F90" s="374"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -6050,13 +6050,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="371" t="s">
+      <c r="B97" s="374" t="s">
         <v>510</v>
       </c>
-      <c r="C97" s="371"/>
-      <c r="D97" s="371"/>
-      <c r="E97" s="371"/>
-      <c r="F97" s="371"/>
+      <c r="C97" s="374"/>
+      <c r="D97" s="374"/>
+      <c r="E97" s="374"/>
+      <c r="F97" s="374"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -6069,13 +6069,13 @@
       </c>
     </row>
     <row r="101" spans="2:6">
-      <c r="B101" s="371" t="s">
+      <c r="B101" s="374" t="s">
         <v>511</v>
       </c>
-      <c r="C101" s="371"/>
-      <c r="D101" s="371"/>
-      <c r="E101" s="371"/>
-      <c r="F101" s="371"/>
+      <c r="C101" s="374"/>
+      <c r="D101" s="374"/>
+      <c r="E101" s="374"/>
+      <c r="F101" s="374"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -6197,13 +6197,13 @@
       </c>
     </row>
     <row r="116" spans="1:6">
-      <c r="B116" s="371" t="s">
+      <c r="B116" s="374" t="s">
         <v>516</v>
       </c>
-      <c r="C116" s="371"/>
-      <c r="D116" s="371"/>
-      <c r="E116" s="371"/>
-      <c r="F116" s="371"/>
+      <c r="C116" s="374"/>
+      <c r="D116" s="374"/>
+      <c r="E116" s="374"/>
+      <c r="F116" s="374"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -6391,13 +6391,13 @@
       </c>
     </row>
     <row r="134" spans="1:6">
-      <c r="B134" s="375" t="s">
+      <c r="B134" s="372" t="s">
         <v>524</v>
       </c>
-      <c r="C134" s="375"/>
-      <c r="D134" s="375"/>
-      <c r="E134" s="375"/>
-      <c r="F134" s="375"/>
+      <c r="C134" s="372"/>
+      <c r="D134" s="372"/>
+      <c r="E134" s="372"/>
+      <c r="F134" s="372"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -6410,22 +6410,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="376" t="s">
+      <c r="B138" s="373" t="s">
         <v>526</v>
       </c>
-      <c r="C138" s="376"/>
-      <c r="D138" s="376"/>
-      <c r="E138" s="376"/>
-      <c r="F138" s="376"/>
+      <c r="C138" s="373"/>
+      <c r="D138" s="373"/>
+      <c r="E138" s="373"/>
+      <c r="F138" s="373"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="371" t="s">
+      <c r="B139" s="374" t="s">
         <v>527</v>
       </c>
-      <c r="C139" s="371"/>
-      <c r="D139" s="371"/>
-      <c r="E139" s="371"/>
-      <c r="F139" s="371"/>
+      <c r="C139" s="374"/>
+      <c r="D139" s="374"/>
+      <c r="E139" s="374"/>
+      <c r="F139" s="374"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -6758,13 +6758,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="377" t="s">
+      <c r="B179" s="375" t="s">
         <v>534</v>
       </c>
-      <c r="C179" s="371"/>
-      <c r="D179" s="371"/>
-      <c r="E179" s="371"/>
-      <c r="F179" s="371"/>
+      <c r="C179" s="374"/>
+      <c r="D179" s="374"/>
+      <c r="E179" s="374"/>
+      <c r="F179" s="374"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -6772,13 +6772,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="373" t="s">
+      <c r="B182" s="376" t="s">
         <v>536</v>
       </c>
-      <c r="C182" s="373"/>
-      <c r="D182" s="373"/>
-      <c r="E182" s="373"/>
-      <c r="F182" s="373"/>
+      <c r="C182" s="376"/>
+      <c r="D182" s="376"/>
+      <c r="E182" s="376"/>
+      <c r="F182" s="376"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -6815,22 +6815,22 @@
       </c>
     </row>
     <row r="191" spans="1:6">
-      <c r="B191" s="374" t="s">
+      <c r="B191" s="371" t="s">
         <v>543</v>
       </c>
-      <c r="C191" s="374"/>
-      <c r="D191" s="374"/>
-      <c r="E191" s="374"/>
-      <c r="F191" s="374"/>
+      <c r="C191" s="371"/>
+      <c r="D191" s="371"/>
+      <c r="E191" s="371"/>
+      <c r="F191" s="371"/>
     </row>
     <row r="192" spans="1:6">
-      <c r="B192" s="374" t="s">
+      <c r="B192" s="371" t="s">
         <v>544</v>
       </c>
-      <c r="C192" s="374"/>
-      <c r="D192" s="374"/>
-      <c r="E192" s="374"/>
-      <c r="F192" s="374"/>
+      <c r="C192" s="371"/>
+      <c r="D192" s="371"/>
+      <c r="E192" s="371"/>
+      <c r="F192" s="371"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -6854,15 +6854,12 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B138:F138"/>
-    <mergeCell ref="B139:F139"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B43:F43"/>
     <mergeCell ref="B116:F116"/>
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B58:F58"/>
@@ -6875,12 +6872,15 @@
     <mergeCell ref="B90:F90"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B47:F47"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B138:F138"/>
+    <mergeCell ref="B139:F139"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">
@@ -7081,13 +7081,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="371" t="s">
+      <c r="B18" s="374" t="s">
         <v>468</v>
       </c>
-      <c r="C18" s="371"/>
-      <c r="D18" s="371"/>
-      <c r="E18" s="371"/>
-      <c r="F18" s="371"/>
+      <c r="C18" s="374"/>
+      <c r="D18" s="374"/>
+      <c r="E18" s="374"/>
+      <c r="F18" s="374"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -7287,22 +7287,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6">
-      <c r="B36" s="371" t="s">
+      <c r="B36" s="374" t="s">
         <v>469</v>
       </c>
-      <c r="C36" s="371"/>
-      <c r="D36" s="371"/>
-      <c r="E36" s="371"/>
-      <c r="F36" s="371"/>
+      <c r="C36" s="374"/>
+      <c r="D36" s="374"/>
+      <c r="E36" s="374"/>
+      <c r="F36" s="374"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="372" t="s">
+      <c r="B37" s="377" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="372"/>
-      <c r="D37" s="372"/>
-      <c r="E37" s="372"/>
-      <c r="F37" s="372"/>
+      <c r="C37" s="377"/>
+      <c r="D37" s="377"/>
+      <c r="E37" s="377"/>
+      <c r="F37" s="377"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -7492,10 +7492,10 @@
       <c r="B61" s="370" t="s">
         <v>329</v>
       </c>
-      <c r="C61" s="373"/>
-      <c r="D61" s="373"/>
-      <c r="E61" s="373"/>
-      <c r="F61" s="373"/>
+      <c r="C61" s="376"/>
+      <c r="D61" s="376"/>
+      <c r="E61" s="376"/>
+      <c r="F61" s="376"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -7511,22 +7511,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="371" t="s">
+      <c r="B64" s="374" t="s">
         <v>334</v>
       </c>
-      <c r="C64" s="371"/>
-      <c r="D64" s="371"/>
-      <c r="E64" s="371"/>
-      <c r="F64" s="371"/>
+      <c r="C64" s="374"/>
+      <c r="D64" s="374"/>
+      <c r="E64" s="374"/>
+      <c r="F64" s="374"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="371" t="s">
+      <c r="B65" s="374" t="s">
         <v>348</v>
       </c>
-      <c r="C65" s="371"/>
-      <c r="D65" s="371"/>
-      <c r="E65" s="371"/>
-      <c r="F65" s="371"/>
+      <c r="C65" s="374"/>
+      <c r="D65" s="374"/>
+      <c r="E65" s="374"/>
+      <c r="F65" s="374"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -7661,22 +7661,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="371" t="s">
+      <c r="B80" s="374" t="s">
         <v>471</v>
       </c>
-      <c r="C80" s="371"/>
-      <c r="D80" s="371"/>
-      <c r="E80" s="371"/>
-      <c r="F80" s="371"/>
+      <c r="C80" s="374"/>
+      <c r="D80" s="374"/>
+      <c r="E80" s="374"/>
+      <c r="F80" s="374"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="372" t="s">
+      <c r="B81" s="377" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="372"/>
-      <c r="D81" s="372"/>
-      <c r="E81" s="372"/>
-      <c r="F81" s="372"/>
+      <c r="C81" s="377"/>
+      <c r="D81" s="377"/>
+      <c r="E81" s="377"/>
+      <c r="F81" s="377"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -7720,22 +7720,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="371" t="s">
+      <c r="B89" s="374" t="s">
         <v>349</v>
       </c>
-      <c r="C89" s="371"/>
-      <c r="D89" s="371"/>
-      <c r="E89" s="371"/>
-      <c r="F89" s="371"/>
+      <c r="C89" s="374"/>
+      <c r="D89" s="374"/>
+      <c r="E89" s="374"/>
+      <c r="F89" s="374"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="371" t="s">
+      <c r="B90" s="374" t="s">
         <v>350</v>
       </c>
-      <c r="C90" s="371"/>
-      <c r="D90" s="371"/>
-      <c r="E90" s="371"/>
-      <c r="F90" s="371"/>
+      <c r="C90" s="374"/>
+      <c r="D90" s="374"/>
+      <c r="E90" s="374"/>
+      <c r="F90" s="374"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -7772,13 +7772,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="371" t="s">
+      <c r="B97" s="374" t="s">
         <v>351</v>
       </c>
-      <c r="C97" s="371"/>
-      <c r="D97" s="371"/>
-      <c r="E97" s="371"/>
-      <c r="F97" s="371"/>
+      <c r="C97" s="374"/>
+      <c r="D97" s="374"/>
+      <c r="E97" s="374"/>
+      <c r="F97" s="374"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -7791,13 +7791,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="371" t="s">
+      <c r="B101" s="374" t="s">
         <v>335</v>
       </c>
-      <c r="C101" s="371"/>
-      <c r="D101" s="371"/>
-      <c r="E101" s="371"/>
-      <c r="F101" s="371"/>
+      <c r="C101" s="374"/>
+      <c r="D101" s="374"/>
+      <c r="E101" s="374"/>
+      <c r="F101" s="374"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -7919,13 +7919,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="371" t="s">
+      <c r="B116" s="374" t="s">
         <v>352</v>
       </c>
-      <c r="C116" s="371"/>
-      <c r="D116" s="371"/>
-      <c r="E116" s="371"/>
-      <c r="F116" s="371"/>
+      <c r="C116" s="374"/>
+      <c r="D116" s="374"/>
+      <c r="E116" s="374"/>
+      <c r="F116" s="374"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -8113,13 +8113,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="375" t="s">
+      <c r="B134" s="372" t="s">
         <v>474</v>
       </c>
-      <c r="C134" s="375"/>
-      <c r="D134" s="375"/>
-      <c r="E134" s="375"/>
-      <c r="F134" s="375"/>
+      <c r="C134" s="372"/>
+      <c r="D134" s="372"/>
+      <c r="E134" s="372"/>
+      <c r="F134" s="372"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -8132,22 +8132,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="376" t="s">
+      <c r="B138" s="373" t="s">
         <v>353</v>
       </c>
-      <c r="C138" s="376"/>
-      <c r="D138" s="376"/>
-      <c r="E138" s="376"/>
-      <c r="F138" s="376"/>
+      <c r="C138" s="373"/>
+      <c r="D138" s="373"/>
+      <c r="E138" s="373"/>
+      <c r="F138" s="373"/>
     </row>
     <row r="139" spans="1:6">
-      <c r="B139" s="371" t="s">
+      <c r="B139" s="374" t="s">
         <v>476</v>
       </c>
-      <c r="C139" s="371"/>
-      <c r="D139" s="371"/>
-      <c r="E139" s="371"/>
-      <c r="F139" s="371"/>
+      <c r="C139" s="374"/>
+      <c r="D139" s="374"/>
+      <c r="E139" s="374"/>
+      <c r="F139" s="374"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -8480,13 +8480,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="377" t="s">
+      <c r="B179" s="375" t="s">
         <v>477</v>
       </c>
-      <c r="C179" s="371"/>
-      <c r="D179" s="371"/>
-      <c r="E179" s="371"/>
-      <c r="F179" s="371"/>
+      <c r="C179" s="374"/>
+      <c r="D179" s="374"/>
+      <c r="E179" s="374"/>
+      <c r="F179" s="374"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -8494,13 +8494,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="373" t="s">
+      <c r="B182" s="376" t="s">
         <v>362</v>
       </c>
-      <c r="C182" s="373"/>
-      <c r="D182" s="373"/>
-      <c r="E182" s="373"/>
-      <c r="F182" s="373"/>
+      <c r="C182" s="376"/>
+      <c r="D182" s="376"/>
+      <c r="E182" s="376"/>
+      <c r="F182" s="376"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -8537,22 +8537,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="374" t="s">
+      <c r="B191" s="371" t="s">
         <v>363</v>
       </c>
-      <c r="C191" s="374"/>
-      <c r="D191" s="374"/>
-      <c r="E191" s="374"/>
-      <c r="F191" s="374"/>
+      <c r="C191" s="371"/>
+      <c r="D191" s="371"/>
+      <c r="E191" s="371"/>
+      <c r="F191" s="371"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="374" t="s">
+      <c r="B192" s="371" t="s">
         <v>364</v>
       </c>
-      <c r="C192" s="374"/>
-      <c r="D192" s="374"/>
-      <c r="E192" s="374"/>
-      <c r="F192" s="374"/>
+      <c r="C192" s="371"/>
+      <c r="D192" s="371"/>
+      <c r="E192" s="371"/>
+      <c r="F192" s="371"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -8576,17 +8576,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -8603,6 +8592,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">

--- a/financial_models/opportunities/0639.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0639.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13AD7FE2-8FDE-428E-88F5-E0DF1E8549B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6C850DD-D3FA-423F-858B-092A3761C121}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4759,6 +4759,15 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4768,16 +4777,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="C12" s="366">
         <f>Market_Price</f>
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C14" s="35">
         <f>投资主题!C12*Common_Shares/1000000</f>
-        <v>14967.7333638</v>
+        <v>14764.090733000001</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",投资主题!D12*Common_Shares/1000000)</f>
@@ -5346,13 +5346,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="374" t="s">
+      <c r="B18" s="371" t="s">
         <v>489</v>
       </c>
-      <c r="C18" s="374"/>
-      <c r="D18" s="374"/>
-      <c r="E18" s="374"/>
-      <c r="F18" s="374"/>
+      <c r="C18" s="371"/>
+      <c r="D18" s="371"/>
+      <c r="E18" s="371"/>
+      <c r="F18" s="371"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -5443,7 +5443,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.23204925986510649</v>
+        <v>0.23811424597741593</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -5565,22 +5565,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="374" t="s">
+      <c r="B36" s="371" t="s">
         <v>492</v>
       </c>
-      <c r="C36" s="374"/>
-      <c r="D36" s="374"/>
-      <c r="E36" s="374"/>
-      <c r="F36" s="374"/>
+      <c r="C36" s="371"/>
+      <c r="D36" s="371"/>
+      <c r="E36" s="371"/>
+      <c r="F36" s="371"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="377" t="s">
+      <c r="B37" s="372" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="377"/>
-      <c r="D37" s="377"/>
-      <c r="E37" s="377"/>
-      <c r="F37" s="377"/>
+      <c r="C37" s="372"/>
+      <c r="D37" s="372"/>
+      <c r="E37" s="372"/>
+      <c r="F37" s="372"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -5770,10 +5770,10 @@
       <c r="B61" s="370" t="s">
         <v>499</v>
       </c>
-      <c r="C61" s="376"/>
-      <c r="D61" s="376"/>
-      <c r="E61" s="376"/>
-      <c r="F61" s="376"/>
+      <c r="C61" s="373"/>
+      <c r="D61" s="373"/>
+      <c r="E61" s="373"/>
+      <c r="F61" s="373"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -5789,22 +5789,22 @@
       </c>
     </row>
     <row r="64" spans="2:6">
-      <c r="B64" s="374" t="s">
+      <c r="B64" s="371" t="s">
         <v>500</v>
       </c>
-      <c r="C64" s="374"/>
-      <c r="D64" s="374"/>
-      <c r="E64" s="374"/>
-      <c r="F64" s="374"/>
+      <c r="C64" s="371"/>
+      <c r="D64" s="371"/>
+      <c r="E64" s="371"/>
+      <c r="F64" s="371"/>
     </row>
     <row r="65" spans="1:6">
-      <c r="B65" s="374" t="s">
+      <c r="B65" s="371" t="s">
         <v>501</v>
       </c>
-      <c r="C65" s="374"/>
-      <c r="D65" s="374"/>
-      <c r="E65" s="374"/>
-      <c r="F65" s="374"/>
+      <c r="C65" s="371"/>
+      <c r="D65" s="371"/>
+      <c r="E65" s="371"/>
+      <c r="F65" s="371"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -5838,7 +5838,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>7.2945411680228764E-2</v>
+        <v>7.3951555289611226E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -5848,7 +5848,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>9.1836734693877556E-2</v>
+        <v>9.3103448275862075E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>503</v>
@@ -5939,22 +5939,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="374" t="s">
+      <c r="B80" s="371" t="s">
         <v>506</v>
       </c>
-      <c r="C80" s="374"/>
-      <c r="D80" s="374"/>
-      <c r="E80" s="374"/>
-      <c r="F80" s="374"/>
+      <c r="C80" s="371"/>
+      <c r="D80" s="371"/>
+      <c r="E80" s="371"/>
+      <c r="F80" s="371"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="377" t="s">
+      <c r="B81" s="372" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="377"/>
-      <c r="D81" s="377"/>
-      <c r="E81" s="377"/>
-      <c r="F81" s="377"/>
+      <c r="C81" s="372"/>
+      <c r="D81" s="372"/>
+      <c r="E81" s="372"/>
+      <c r="F81" s="372"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5998,22 +5998,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6">
-      <c r="B89" s="374" t="s">
+      <c r="B89" s="371" t="s">
         <v>507</v>
       </c>
-      <c r="C89" s="374"/>
-      <c r="D89" s="374"/>
-      <c r="E89" s="374"/>
-      <c r="F89" s="374"/>
+      <c r="C89" s="371"/>
+      <c r="D89" s="371"/>
+      <c r="E89" s="371"/>
+      <c r="F89" s="371"/>
     </row>
     <row r="90" spans="1:6">
-      <c r="B90" s="374" t="s">
+      <c r="B90" s="371" t="s">
         <v>508</v>
       </c>
-      <c r="C90" s="374"/>
-      <c r="D90" s="374"/>
-      <c r="E90" s="374"/>
-      <c r="F90" s="374"/>
+      <c r="C90" s="371"/>
+      <c r="D90" s="371"/>
+      <c r="E90" s="371"/>
+      <c r="F90" s="371"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -6050,13 +6050,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="374" t="s">
+      <c r="B97" s="371" t="s">
         <v>510</v>
       </c>
-      <c r="C97" s="374"/>
-      <c r="D97" s="374"/>
-      <c r="E97" s="374"/>
-      <c r="F97" s="374"/>
+      <c r="C97" s="371"/>
+      <c r="D97" s="371"/>
+      <c r="E97" s="371"/>
+      <c r="F97" s="371"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -6069,13 +6069,13 @@
       </c>
     </row>
     <row r="101" spans="2:6">
-      <c r="B101" s="374" t="s">
+      <c r="B101" s="371" t="s">
         <v>511</v>
       </c>
-      <c r="C101" s="374"/>
-      <c r="D101" s="374"/>
-      <c r="E101" s="374"/>
-      <c r="F101" s="374"/>
+      <c r="C101" s="371"/>
+      <c r="D101" s="371"/>
+      <c r="E101" s="371"/>
+      <c r="F101" s="371"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -6197,13 +6197,13 @@
       </c>
     </row>
     <row r="116" spans="1:6">
-      <c r="B116" s="374" t="s">
+      <c r="B116" s="371" t="s">
         <v>516</v>
       </c>
-      <c r="C116" s="374"/>
-      <c r="D116" s="374"/>
-      <c r="E116" s="374"/>
-      <c r="F116" s="374"/>
+      <c r="C116" s="371"/>
+      <c r="D116" s="371"/>
+      <c r="E116" s="371"/>
+      <c r="F116" s="371"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -6391,13 +6391,13 @@
       </c>
     </row>
     <row r="134" spans="1:6">
-      <c r="B134" s="372" t="s">
+      <c r="B134" s="375" t="s">
         <v>524</v>
       </c>
-      <c r="C134" s="372"/>
-      <c r="D134" s="372"/>
-      <c r="E134" s="372"/>
-      <c r="F134" s="372"/>
+      <c r="C134" s="375"/>
+      <c r="D134" s="375"/>
+      <c r="E134" s="375"/>
+      <c r="F134" s="375"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -6410,22 +6410,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="373" t="s">
+      <c r="B138" s="376" t="s">
         <v>526</v>
       </c>
-      <c r="C138" s="373"/>
-      <c r="D138" s="373"/>
-      <c r="E138" s="373"/>
-      <c r="F138" s="373"/>
+      <c r="C138" s="376"/>
+      <c r="D138" s="376"/>
+      <c r="E138" s="376"/>
+      <c r="F138" s="376"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="374" t="s">
+      <c r="B139" s="371" t="s">
         <v>527</v>
       </c>
-      <c r="C139" s="374"/>
-      <c r="D139" s="374"/>
-      <c r="E139" s="374"/>
-      <c r="F139" s="374"/>
+      <c r="C139" s="371"/>
+      <c r="D139" s="371"/>
+      <c r="E139" s="371"/>
+      <c r="F139" s="371"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -6758,13 +6758,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="375" t="s">
+      <c r="B179" s="377" t="s">
         <v>534</v>
       </c>
-      <c r="C179" s="374"/>
-      <c r="D179" s="374"/>
-      <c r="E179" s="374"/>
-      <c r="F179" s="374"/>
+      <c r="C179" s="371"/>
+      <c r="D179" s="371"/>
+      <c r="E179" s="371"/>
+      <c r="F179" s="371"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -6772,13 +6772,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="376" t="s">
+      <c r="B182" s="373" t="s">
         <v>536</v>
       </c>
-      <c r="C182" s="376"/>
-      <c r="D182" s="376"/>
-      <c r="E182" s="376"/>
-      <c r="F182" s="376"/>
+      <c r="C182" s="373"/>
+      <c r="D182" s="373"/>
+      <c r="E182" s="373"/>
+      <c r="F182" s="373"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -6815,22 +6815,22 @@
       </c>
     </row>
     <row r="191" spans="1:6">
-      <c r="B191" s="371" t="s">
+      <c r="B191" s="374" t="s">
         <v>543</v>
       </c>
-      <c r="C191" s="371"/>
-      <c r="D191" s="371"/>
-      <c r="E191" s="371"/>
-      <c r="F191" s="371"/>
+      <c r="C191" s="374"/>
+      <c r="D191" s="374"/>
+      <c r="E191" s="374"/>
+      <c r="F191" s="374"/>
     </row>
     <row r="192" spans="1:6">
-      <c r="B192" s="371" t="s">
+      <c r="B192" s="374" t="s">
         <v>544</v>
       </c>
-      <c r="C192" s="371"/>
-      <c r="D192" s="371"/>
-      <c r="E192" s="371"/>
-      <c r="F192" s="371"/>
+      <c r="C192" s="374"/>
+      <c r="D192" s="374"/>
+      <c r="E192" s="374"/>
+      <c r="F192" s="374"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -6854,12 +6854,15 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B47:F47"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B138:F138"/>
+    <mergeCell ref="B139:F139"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B182:F182"/>
     <mergeCell ref="B116:F116"/>
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B58:F58"/>
@@ -6872,15 +6875,12 @@
     <mergeCell ref="B90:F90"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B138:F138"/>
-    <mergeCell ref="B139:F139"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B43:F43"/>
   </mergeCells>
   <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">
@@ -7023,7 +7023,7 @@
         <v>463</v>
       </c>
       <c r="C12" s="50">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -7044,7 +7044,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>14967.7333638</v>
+        <v>14764.090733000001</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -7081,13 +7081,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="374" t="s">
+      <c r="B18" s="371" t="s">
         <v>468</v>
       </c>
-      <c r="C18" s="374"/>
-      <c r="D18" s="374"/>
-      <c r="E18" s="374"/>
-      <c r="F18" s="374"/>
+      <c r="C18" s="371"/>
+      <c r="D18" s="371"/>
+      <c r="E18" s="371"/>
+      <c r="F18" s="371"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -7170,7 +7170,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.23204925986510649</v>
+        <v>0.23811424597741593</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -7287,22 +7287,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6">
-      <c r="B36" s="374" t="s">
+      <c r="B36" s="371" t="s">
         <v>469</v>
       </c>
-      <c r="C36" s="374"/>
-      <c r="D36" s="374"/>
-      <c r="E36" s="374"/>
-      <c r="F36" s="374"/>
+      <c r="C36" s="371"/>
+      <c r="D36" s="371"/>
+      <c r="E36" s="371"/>
+      <c r="F36" s="371"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="377" t="s">
+      <c r="B37" s="372" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="377"/>
-      <c r="D37" s="377"/>
-      <c r="E37" s="377"/>
-      <c r="F37" s="377"/>
+      <c r="C37" s="372"/>
+      <c r="D37" s="372"/>
+      <c r="E37" s="372"/>
+      <c r="F37" s="372"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -7492,10 +7492,10 @@
       <c r="B61" s="370" t="s">
         <v>329</v>
       </c>
-      <c r="C61" s="376"/>
-      <c r="D61" s="376"/>
-      <c r="E61" s="376"/>
-      <c r="F61" s="376"/>
+      <c r="C61" s="373"/>
+      <c r="D61" s="373"/>
+      <c r="E61" s="373"/>
+      <c r="F61" s="373"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -7511,22 +7511,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="374" t="s">
+      <c r="B64" s="371" t="s">
         <v>334</v>
       </c>
-      <c r="C64" s="374"/>
-      <c r="D64" s="374"/>
-      <c r="E64" s="374"/>
-      <c r="F64" s="374"/>
+      <c r="C64" s="371"/>
+      <c r="D64" s="371"/>
+      <c r="E64" s="371"/>
+      <c r="F64" s="371"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="374" t="s">
+      <c r="B65" s="371" t="s">
         <v>348</v>
       </c>
-      <c r="C65" s="374"/>
-      <c r="D65" s="374"/>
-      <c r="E65" s="374"/>
-      <c r="F65" s="374"/>
+      <c r="C65" s="371"/>
+      <c r="D65" s="371"/>
+      <c r="E65" s="371"/>
+      <c r="F65" s="371"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -7560,7 +7560,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>7.2945411680228764E-2</v>
+        <v>7.3951555289611226E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -7570,7 +7570,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>9.1836734693877556E-2</v>
+        <v>9.3103448275862075E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>424</v>
@@ -7661,22 +7661,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="374" t="s">
+      <c r="B80" s="371" t="s">
         <v>471</v>
       </c>
-      <c r="C80" s="374"/>
-      <c r="D80" s="374"/>
-      <c r="E80" s="374"/>
-      <c r="F80" s="374"/>
+      <c r="C80" s="371"/>
+      <c r="D80" s="371"/>
+      <c r="E80" s="371"/>
+      <c r="F80" s="371"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="377" t="s">
+      <c r="B81" s="372" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="377"/>
-      <c r="D81" s="377"/>
-      <c r="E81" s="377"/>
-      <c r="F81" s="377"/>
+      <c r="C81" s="372"/>
+      <c r="D81" s="372"/>
+      <c r="E81" s="372"/>
+      <c r="F81" s="372"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -7720,22 +7720,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="374" t="s">
+      <c r="B89" s="371" t="s">
         <v>349</v>
       </c>
-      <c r="C89" s="374"/>
-      <c r="D89" s="374"/>
-      <c r="E89" s="374"/>
-      <c r="F89" s="374"/>
+      <c r="C89" s="371"/>
+      <c r="D89" s="371"/>
+      <c r="E89" s="371"/>
+      <c r="F89" s="371"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="374" t="s">
+      <c r="B90" s="371" t="s">
         <v>350</v>
       </c>
-      <c r="C90" s="374"/>
-      <c r="D90" s="374"/>
-      <c r="E90" s="374"/>
-      <c r="F90" s="374"/>
+      <c r="C90" s="371"/>
+      <c r="D90" s="371"/>
+      <c r="E90" s="371"/>
+      <c r="F90" s="371"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -7772,13 +7772,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="374" t="s">
+      <c r="B97" s="371" t="s">
         <v>351</v>
       </c>
-      <c r="C97" s="374"/>
-      <c r="D97" s="374"/>
-      <c r="E97" s="374"/>
-      <c r="F97" s="374"/>
+      <c r="C97" s="371"/>
+      <c r="D97" s="371"/>
+      <c r="E97" s="371"/>
+      <c r="F97" s="371"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -7791,13 +7791,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="374" t="s">
+      <c r="B101" s="371" t="s">
         <v>335</v>
       </c>
-      <c r="C101" s="374"/>
-      <c r="D101" s="374"/>
-      <c r="E101" s="374"/>
-      <c r="F101" s="374"/>
+      <c r="C101" s="371"/>
+      <c r="D101" s="371"/>
+      <c r="E101" s="371"/>
+      <c r="F101" s="371"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -7919,13 +7919,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="374" t="s">
+      <c r="B116" s="371" t="s">
         <v>352</v>
       </c>
-      <c r="C116" s="374"/>
-      <c r="D116" s="374"/>
-      <c r="E116" s="374"/>
-      <c r="F116" s="374"/>
+      <c r="C116" s="371"/>
+      <c r="D116" s="371"/>
+      <c r="E116" s="371"/>
+      <c r="F116" s="371"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -8113,13 +8113,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="372" t="s">
+      <c r="B134" s="375" t="s">
         <v>474</v>
       </c>
-      <c r="C134" s="372"/>
-      <c r="D134" s="372"/>
-      <c r="E134" s="372"/>
-      <c r="F134" s="372"/>
+      <c r="C134" s="375"/>
+      <c r="D134" s="375"/>
+      <c r="E134" s="375"/>
+      <c r="F134" s="375"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -8132,22 +8132,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="373" t="s">
+      <c r="B138" s="376" t="s">
         <v>353</v>
       </c>
-      <c r="C138" s="373"/>
-      <c r="D138" s="373"/>
-      <c r="E138" s="373"/>
-      <c r="F138" s="373"/>
+      <c r="C138" s="376"/>
+      <c r="D138" s="376"/>
+      <c r="E138" s="376"/>
+      <c r="F138" s="376"/>
     </row>
     <row r="139" spans="1:6">
-      <c r="B139" s="374" t="s">
+      <c r="B139" s="371" t="s">
         <v>476</v>
       </c>
-      <c r="C139" s="374"/>
-      <c r="D139" s="374"/>
-      <c r="E139" s="374"/>
-      <c r="F139" s="374"/>
+      <c r="C139" s="371"/>
+      <c r="D139" s="371"/>
+      <c r="E139" s="371"/>
+      <c r="F139" s="371"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -8480,13 +8480,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="375" t="s">
+      <c r="B179" s="377" t="s">
         <v>477</v>
       </c>
-      <c r="C179" s="374"/>
-      <c r="D179" s="374"/>
-      <c r="E179" s="374"/>
-      <c r="F179" s="374"/>
+      <c r="C179" s="371"/>
+      <c r="D179" s="371"/>
+      <c r="E179" s="371"/>
+      <c r="F179" s="371"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -8494,13 +8494,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="376" t="s">
+      <c r="B182" s="373" t="s">
         <v>362</v>
       </c>
-      <c r="C182" s="376"/>
-      <c r="D182" s="376"/>
-      <c r="E182" s="376"/>
-      <c r="F182" s="376"/>
+      <c r="C182" s="373"/>
+      <c r="D182" s="373"/>
+      <c r="E182" s="373"/>
+      <c r="F182" s="373"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -8537,22 +8537,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="371" t="s">
+      <c r="B191" s="374" t="s">
         <v>363</v>
       </c>
-      <c r="C191" s="371"/>
-      <c r="D191" s="371"/>
-      <c r="E191" s="371"/>
-      <c r="F191" s="371"/>
+      <c r="C191" s="374"/>
+      <c r="D191" s="374"/>
+      <c r="E191" s="374"/>
+      <c r="F191" s="374"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="371" t="s">
+      <c r="B192" s="374" t="s">
         <v>364</v>
       </c>
-      <c r="C192" s="371"/>
-      <c r="D192" s="371"/>
-      <c r="E192" s="371"/>
-      <c r="F192" s="371"/>
+      <c r="C192" s="374"/>
+      <c r="D192" s="374"/>
+      <c r="E192" s="374"/>
+      <c r="F192" s="374"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -8576,6 +8576,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -8592,17 +8603,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -16146,20 +16146,20 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>9.1836734693877556E-2</v>
+        <v>9.3103448275862075E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>9.1836734693877556E-2</v>
+        <v>9.3103448275862075E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>8.5714285714285729E-2</v>
+        <v>8.689655172413796E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>0.13163265306122451</v>
+        <v>0.133448275862069</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
@@ -17345,50 +17345,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>7.2945411680228764E-2</v>
+        <v>7.3951555289611226E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>8.5122132961359356E-2</v>
+        <v>8.6296231347033278E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>0.11713335311268476</v>
+        <v>0.11874898556941145</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>0.18996651226551578</v>
+        <v>0.19258674002090223</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>0.1560872891514116</v>
+        <v>0.15824021727763796</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>5.5996053619384825E-2</v>
+        <v>5.6768412979652204E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>7.1086180795638693E-2</v>
+        <v>7.2066679841095771E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>6.3292749608380758E-2</v>
+        <v>6.4165753051254965E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>6.0113510718737759E-2</v>
+        <v>6.0942662590720349E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>1.0641290576782635E-2</v>
+        <v>1.0788066998531361E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>4.6097828123311006E-3</v>
+        <v>4.6733660235356673E-3</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -17402,43 +17402,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12125917504580769</v>
+        <v>0.1229317153912671</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15372654924257945</v>
+        <v>0.15584691543902882</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.22101910286569454</v>
+        <v>0.22406764221556616</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.20449529167874742</v>
+        <v>0.20731591639155772</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.9322832064304849E-2</v>
+        <v>8.0416940092778014E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.8578430775934266E-2</v>
+        <v>7.9662271200429915E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.6960750970215652E-2</v>
+        <v>7.8022278569804829E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.9008890074172611E-2</v>
+        <v>8.0098667868299125E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.520123278226513E-3</v>
+        <v>4.5824698062020509E-3</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-4.7533917307795437E-2</v>
+        <v>-4.8189557546523647E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -21388,7 +21388,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-2.94</v>
+        <v>-2.9</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -21628,7 +21628,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -22239,7 +22239,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.23204925986510649</v>
+        <v>0.23811424597741593</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/0639.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0639.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6C850DD-D3FA-423F-858B-092A3761C121}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29B573A7-F1C5-40C7-8467-9472ECF90E75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2205" yWindow="2205" windowWidth="12690" windowHeight="7642" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="投资主题" sheetId="12" r:id="rId1"/>
@@ -4759,15 +4759,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4777,7 +4768,16 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="C12" s="366">
         <f>Market_Price</f>
-        <v>2.9</v>
+        <v>2.83</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C14" s="35">
         <f>投资主题!C12*Common_Shares/1000000</f>
-        <v>14764.090733000001</v>
+        <v>14407.716129100001</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",投资主题!D12*Common_Shares/1000000)</f>
@@ -5346,13 +5346,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="371" t="s">
+      <c r="B18" s="374" t="s">
         <v>489</v>
       </c>
-      <c r="C18" s="371"/>
-      <c r="D18" s="371"/>
-      <c r="E18" s="371"/>
-      <c r="F18" s="371"/>
+      <c r="C18" s="374"/>
+      <c r="D18" s="374"/>
+      <c r="E18" s="374"/>
+      <c r="F18" s="374"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -5443,7 +5443,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.23811424597741593</v>
+        <v>0.24901483038369632</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -5565,22 +5565,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="371" t="s">
+      <c r="B36" s="374" t="s">
         <v>492</v>
       </c>
-      <c r="C36" s="371"/>
-      <c r="D36" s="371"/>
-      <c r="E36" s="371"/>
-      <c r="F36" s="371"/>
+      <c r="C36" s="374"/>
+      <c r="D36" s="374"/>
+      <c r="E36" s="374"/>
+      <c r="F36" s="374"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="372" t="s">
+      <c r="B37" s="377" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="372"/>
-      <c r="D37" s="372"/>
-      <c r="E37" s="372"/>
-      <c r="F37" s="372"/>
+      <c r="C37" s="377"/>
+      <c r="D37" s="377"/>
+      <c r="E37" s="377"/>
+      <c r="F37" s="377"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -5770,10 +5770,10 @@
       <c r="B61" s="370" t="s">
         <v>499</v>
       </c>
-      <c r="C61" s="373"/>
-      <c r="D61" s="373"/>
-      <c r="E61" s="373"/>
-      <c r="F61" s="373"/>
+      <c r="C61" s="376"/>
+      <c r="D61" s="376"/>
+      <c r="E61" s="376"/>
+      <c r="F61" s="376"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -5789,22 +5789,22 @@
       </c>
     </row>
     <row r="64" spans="2:6">
-      <c r="B64" s="371" t="s">
+      <c r="B64" s="374" t="s">
         <v>500</v>
       </c>
-      <c r="C64" s="371"/>
-      <c r="D64" s="371"/>
-      <c r="E64" s="371"/>
-      <c r="F64" s="371"/>
+      <c r="C64" s="374"/>
+      <c r="D64" s="374"/>
+      <c r="E64" s="374"/>
+      <c r="F64" s="374"/>
     </row>
     <row r="65" spans="1:6">
-      <c r="B65" s="371" t="s">
+      <c r="B65" s="374" t="s">
         <v>501</v>
       </c>
-      <c r="C65" s="371"/>
-      <c r="D65" s="371"/>
-      <c r="E65" s="371"/>
-      <c r="F65" s="371"/>
+      <c r="C65" s="374"/>
+      <c r="D65" s="374"/>
+      <c r="E65" s="374"/>
+      <c r="F65" s="374"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -5838,7 +5838,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>7.3951555289611226E-2</v>
+        <v>7.5780745703135186E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -5848,7 +5848,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>9.3103448275862075E-2</v>
+        <v>9.5406360424028266E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>503</v>
@@ -5939,22 +5939,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="371" t="s">
+      <c r="B80" s="374" t="s">
         <v>506</v>
       </c>
-      <c r="C80" s="371"/>
-      <c r="D80" s="371"/>
-      <c r="E80" s="371"/>
-      <c r="F80" s="371"/>
+      <c r="C80" s="374"/>
+      <c r="D80" s="374"/>
+      <c r="E80" s="374"/>
+      <c r="F80" s="374"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="372" t="s">
+      <c r="B81" s="377" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="372"/>
-      <c r="D81" s="372"/>
-      <c r="E81" s="372"/>
-      <c r="F81" s="372"/>
+      <c r="C81" s="377"/>
+      <c r="D81" s="377"/>
+      <c r="E81" s="377"/>
+      <c r="F81" s="377"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5998,22 +5998,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6">
-      <c r="B89" s="371" t="s">
+      <c r="B89" s="374" t="s">
         <v>507</v>
       </c>
-      <c r="C89" s="371"/>
-      <c r="D89" s="371"/>
-      <c r="E89" s="371"/>
-      <c r="F89" s="371"/>
+      <c r="C89" s="374"/>
+      <c r="D89" s="374"/>
+      <c r="E89" s="374"/>
+      <c r="F89" s="374"/>
     </row>
     <row r="90" spans="1:6">
-      <c r="B90" s="371" t="s">
+      <c r="B90" s="374" t="s">
         <v>508</v>
       </c>
-      <c r="C90" s="371"/>
-      <c r="D90" s="371"/>
-      <c r="E90" s="371"/>
-      <c r="F90" s="371"/>
+      <c r="C90" s="374"/>
+      <c r="D90" s="374"/>
+      <c r="E90" s="374"/>
+      <c r="F90" s="374"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -6050,13 +6050,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="371" t="s">
+      <c r="B97" s="374" t="s">
         <v>510</v>
       </c>
-      <c r="C97" s="371"/>
-      <c r="D97" s="371"/>
-      <c r="E97" s="371"/>
-      <c r="F97" s="371"/>
+      <c r="C97" s="374"/>
+      <c r="D97" s="374"/>
+      <c r="E97" s="374"/>
+      <c r="F97" s="374"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -6069,13 +6069,13 @@
       </c>
     </row>
     <row r="101" spans="2:6">
-      <c r="B101" s="371" t="s">
+      <c r="B101" s="374" t="s">
         <v>511</v>
       </c>
-      <c r="C101" s="371"/>
-      <c r="D101" s="371"/>
-      <c r="E101" s="371"/>
-      <c r="F101" s="371"/>
+      <c r="C101" s="374"/>
+      <c r="D101" s="374"/>
+      <c r="E101" s="374"/>
+      <c r="F101" s="374"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -6197,13 +6197,13 @@
       </c>
     </row>
     <row r="116" spans="1:6">
-      <c r="B116" s="371" t="s">
+      <c r="B116" s="374" t="s">
         <v>516</v>
       </c>
-      <c r="C116" s="371"/>
-      <c r="D116" s="371"/>
-      <c r="E116" s="371"/>
-      <c r="F116" s="371"/>
+      <c r="C116" s="374"/>
+      <c r="D116" s="374"/>
+      <c r="E116" s="374"/>
+      <c r="F116" s="374"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -6391,13 +6391,13 @@
       </c>
     </row>
     <row r="134" spans="1:6">
-      <c r="B134" s="375" t="s">
+      <c r="B134" s="372" t="s">
         <v>524</v>
       </c>
-      <c r="C134" s="375"/>
-      <c r="D134" s="375"/>
-      <c r="E134" s="375"/>
-      <c r="F134" s="375"/>
+      <c r="C134" s="372"/>
+      <c r="D134" s="372"/>
+      <c r="E134" s="372"/>
+      <c r="F134" s="372"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -6410,22 +6410,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="376" t="s">
+      <c r="B138" s="373" t="s">
         <v>526</v>
       </c>
-      <c r="C138" s="376"/>
-      <c r="D138" s="376"/>
-      <c r="E138" s="376"/>
-      <c r="F138" s="376"/>
+      <c r="C138" s="373"/>
+      <c r="D138" s="373"/>
+      <c r="E138" s="373"/>
+      <c r="F138" s="373"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="371" t="s">
+      <c r="B139" s="374" t="s">
         <v>527</v>
       </c>
-      <c r="C139" s="371"/>
-      <c r="D139" s="371"/>
-      <c r="E139" s="371"/>
-      <c r="F139" s="371"/>
+      <c r="C139" s="374"/>
+      <c r="D139" s="374"/>
+      <c r="E139" s="374"/>
+      <c r="F139" s="374"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -6758,13 +6758,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="377" t="s">
+      <c r="B179" s="375" t="s">
         <v>534</v>
       </c>
-      <c r="C179" s="371"/>
-      <c r="D179" s="371"/>
-      <c r="E179" s="371"/>
-      <c r="F179" s="371"/>
+      <c r="C179" s="374"/>
+      <c r="D179" s="374"/>
+      <c r="E179" s="374"/>
+      <c r="F179" s="374"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -6772,13 +6772,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="373" t="s">
+      <c r="B182" s="376" t="s">
         <v>536</v>
       </c>
-      <c r="C182" s="373"/>
-      <c r="D182" s="373"/>
-      <c r="E182" s="373"/>
-      <c r="F182" s="373"/>
+      <c r="C182" s="376"/>
+      <c r="D182" s="376"/>
+      <c r="E182" s="376"/>
+      <c r="F182" s="376"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -6815,22 +6815,22 @@
       </c>
     </row>
     <row r="191" spans="1:6">
-      <c r="B191" s="374" t="s">
+      <c r="B191" s="371" t="s">
         <v>543</v>
       </c>
-      <c r="C191" s="374"/>
-      <c r="D191" s="374"/>
-      <c r="E191" s="374"/>
-      <c r="F191" s="374"/>
+      <c r="C191" s="371"/>
+      <c r="D191" s="371"/>
+      <c r="E191" s="371"/>
+      <c r="F191" s="371"/>
     </row>
     <row r="192" spans="1:6">
-      <c r="B192" s="374" t="s">
+      <c r="B192" s="371" t="s">
         <v>544</v>
       </c>
-      <c r="C192" s="374"/>
-      <c r="D192" s="374"/>
-      <c r="E192" s="374"/>
-      <c r="F192" s="374"/>
+      <c r="C192" s="371"/>
+      <c r="D192" s="371"/>
+      <c r="E192" s="371"/>
+      <c r="F192" s="371"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -6854,15 +6854,12 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B138:F138"/>
-    <mergeCell ref="B139:F139"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B43:F43"/>
     <mergeCell ref="B116:F116"/>
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B58:F58"/>
@@ -6875,12 +6872,15 @@
     <mergeCell ref="B90:F90"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B47:F47"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B138:F138"/>
+    <mergeCell ref="B139:F139"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">
@@ -7023,7 +7023,7 @@
         <v>463</v>
       </c>
       <c r="C12" s="50">
-        <v>2.9</v>
+        <v>2.83</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -7044,7 +7044,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>14764.090733000001</v>
+        <v>14407.716129100001</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -7081,13 +7081,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="371" t="s">
+      <c r="B18" s="374" t="s">
         <v>468</v>
       </c>
-      <c r="C18" s="371"/>
-      <c r="D18" s="371"/>
-      <c r="E18" s="371"/>
-      <c r="F18" s="371"/>
+      <c r="C18" s="374"/>
+      <c r="D18" s="374"/>
+      <c r="E18" s="374"/>
+      <c r="F18" s="374"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -7170,7 +7170,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.23811424597741593</v>
+        <v>0.24901483038369632</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -7287,22 +7287,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6">
-      <c r="B36" s="371" t="s">
+      <c r="B36" s="374" t="s">
         <v>469</v>
       </c>
-      <c r="C36" s="371"/>
-      <c r="D36" s="371"/>
-      <c r="E36" s="371"/>
-      <c r="F36" s="371"/>
+      <c r="C36" s="374"/>
+      <c r="D36" s="374"/>
+      <c r="E36" s="374"/>
+      <c r="F36" s="374"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="372" t="s">
+      <c r="B37" s="377" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="372"/>
-      <c r="D37" s="372"/>
-      <c r="E37" s="372"/>
-      <c r="F37" s="372"/>
+      <c r="C37" s="377"/>
+      <c r="D37" s="377"/>
+      <c r="E37" s="377"/>
+      <c r="F37" s="377"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -7492,10 +7492,10 @@
       <c r="B61" s="370" t="s">
         <v>329</v>
       </c>
-      <c r="C61" s="373"/>
-      <c r="D61" s="373"/>
-      <c r="E61" s="373"/>
-      <c r="F61" s="373"/>
+      <c r="C61" s="376"/>
+      <c r="D61" s="376"/>
+      <c r="E61" s="376"/>
+      <c r="F61" s="376"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -7511,22 +7511,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="371" t="s">
+      <c r="B64" s="374" t="s">
         <v>334</v>
       </c>
-      <c r="C64" s="371"/>
-      <c r="D64" s="371"/>
-      <c r="E64" s="371"/>
-      <c r="F64" s="371"/>
+      <c r="C64" s="374"/>
+      <c r="D64" s="374"/>
+      <c r="E64" s="374"/>
+      <c r="F64" s="374"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="371" t="s">
+      <c r="B65" s="374" t="s">
         <v>348</v>
       </c>
-      <c r="C65" s="371"/>
-      <c r="D65" s="371"/>
-      <c r="E65" s="371"/>
-      <c r="F65" s="371"/>
+      <c r="C65" s="374"/>
+      <c r="D65" s="374"/>
+      <c r="E65" s="374"/>
+      <c r="F65" s="374"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -7560,7 +7560,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>7.3951555289611226E-2</v>
+        <v>7.5780745703135186E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -7570,7 +7570,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>9.3103448275862075E-2</v>
+        <v>9.5406360424028266E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>424</v>
@@ -7661,22 +7661,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="371" t="s">
+      <c r="B80" s="374" t="s">
         <v>471</v>
       </c>
-      <c r="C80" s="371"/>
-      <c r="D80" s="371"/>
-      <c r="E80" s="371"/>
-      <c r="F80" s="371"/>
+      <c r="C80" s="374"/>
+      <c r="D80" s="374"/>
+      <c r="E80" s="374"/>
+      <c r="F80" s="374"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="372" t="s">
+      <c r="B81" s="377" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="372"/>
-      <c r="D81" s="372"/>
-      <c r="E81" s="372"/>
-      <c r="F81" s="372"/>
+      <c r="C81" s="377"/>
+      <c r="D81" s="377"/>
+      <c r="E81" s="377"/>
+      <c r="F81" s="377"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -7720,22 +7720,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="371" t="s">
+      <c r="B89" s="374" t="s">
         <v>349</v>
       </c>
-      <c r="C89" s="371"/>
-      <c r="D89" s="371"/>
-      <c r="E89" s="371"/>
-      <c r="F89" s="371"/>
+      <c r="C89" s="374"/>
+      <c r="D89" s="374"/>
+      <c r="E89" s="374"/>
+      <c r="F89" s="374"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="371" t="s">
+      <c r="B90" s="374" t="s">
         <v>350</v>
       </c>
-      <c r="C90" s="371"/>
-      <c r="D90" s="371"/>
-      <c r="E90" s="371"/>
-      <c r="F90" s="371"/>
+      <c r="C90" s="374"/>
+      <c r="D90" s="374"/>
+      <c r="E90" s="374"/>
+      <c r="F90" s="374"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -7772,13 +7772,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="371" t="s">
+      <c r="B97" s="374" t="s">
         <v>351</v>
       </c>
-      <c r="C97" s="371"/>
-      <c r="D97" s="371"/>
-      <c r="E97" s="371"/>
-      <c r="F97" s="371"/>
+      <c r="C97" s="374"/>
+      <c r="D97" s="374"/>
+      <c r="E97" s="374"/>
+      <c r="F97" s="374"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -7791,13 +7791,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="371" t="s">
+      <c r="B101" s="374" t="s">
         <v>335</v>
       </c>
-      <c r="C101" s="371"/>
-      <c r="D101" s="371"/>
-      <c r="E101" s="371"/>
-      <c r="F101" s="371"/>
+      <c r="C101" s="374"/>
+      <c r="D101" s="374"/>
+      <c r="E101" s="374"/>
+      <c r="F101" s="374"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -7919,13 +7919,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="371" t="s">
+      <c r="B116" s="374" t="s">
         <v>352</v>
       </c>
-      <c r="C116" s="371"/>
-      <c r="D116" s="371"/>
-      <c r="E116" s="371"/>
-      <c r="F116" s="371"/>
+      <c r="C116" s="374"/>
+      <c r="D116" s="374"/>
+      <c r="E116" s="374"/>
+      <c r="F116" s="374"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -8113,13 +8113,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="375" t="s">
+      <c r="B134" s="372" t="s">
         <v>474</v>
       </c>
-      <c r="C134" s="375"/>
-      <c r="D134" s="375"/>
-      <c r="E134" s="375"/>
-      <c r="F134" s="375"/>
+      <c r="C134" s="372"/>
+      <c r="D134" s="372"/>
+      <c r="E134" s="372"/>
+      <c r="F134" s="372"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -8132,22 +8132,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="376" t="s">
+      <c r="B138" s="373" t="s">
         <v>353</v>
       </c>
-      <c r="C138" s="376"/>
-      <c r="D138" s="376"/>
-      <c r="E138" s="376"/>
-      <c r="F138" s="376"/>
+      <c r="C138" s="373"/>
+      <c r="D138" s="373"/>
+      <c r="E138" s="373"/>
+      <c r="F138" s="373"/>
     </row>
     <row r="139" spans="1:6">
-      <c r="B139" s="371" t="s">
+      <c r="B139" s="374" t="s">
         <v>476</v>
       </c>
-      <c r="C139" s="371"/>
-      <c r="D139" s="371"/>
-      <c r="E139" s="371"/>
-      <c r="F139" s="371"/>
+      <c r="C139" s="374"/>
+      <c r="D139" s="374"/>
+      <c r="E139" s="374"/>
+      <c r="F139" s="374"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -8480,13 +8480,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="377" t="s">
+      <c r="B179" s="375" t="s">
         <v>477</v>
       </c>
-      <c r="C179" s="371"/>
-      <c r="D179" s="371"/>
-      <c r="E179" s="371"/>
-      <c r="F179" s="371"/>
+      <c r="C179" s="374"/>
+      <c r="D179" s="374"/>
+      <c r="E179" s="374"/>
+      <c r="F179" s="374"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -8494,13 +8494,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="373" t="s">
+      <c r="B182" s="376" t="s">
         <v>362</v>
       </c>
-      <c r="C182" s="373"/>
-      <c r="D182" s="373"/>
-      <c r="E182" s="373"/>
-      <c r="F182" s="373"/>
+      <c r="C182" s="376"/>
+      <c r="D182" s="376"/>
+      <c r="E182" s="376"/>
+      <c r="F182" s="376"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -8537,22 +8537,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="374" t="s">
+      <c r="B191" s="371" t="s">
         <v>363</v>
       </c>
-      <c r="C191" s="374"/>
-      <c r="D191" s="374"/>
-      <c r="E191" s="374"/>
-      <c r="F191" s="374"/>
+      <c r="C191" s="371"/>
+      <c r="D191" s="371"/>
+      <c r="E191" s="371"/>
+      <c r="F191" s="371"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="374" t="s">
+      <c r="B192" s="371" t="s">
         <v>364</v>
       </c>
-      <c r="C192" s="374"/>
-      <c r="D192" s="374"/>
-      <c r="E192" s="374"/>
-      <c r="F192" s="374"/>
+      <c r="C192" s="371"/>
+      <c r="D192" s="371"/>
+      <c r="E192" s="371"/>
+      <c r="F192" s="371"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -8576,17 +8576,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -8603,6 +8592,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -16146,20 +16146,20 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>9.3103448275862075E-2</v>
+        <v>9.5406360424028266E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>9.3103448275862075E-2</v>
+        <v>9.5406360424028266E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>8.689655172413796E-2</v>
+        <v>8.9045936395759737E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>0.133448275862069</v>
+        <v>0.13674911660777386</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
@@ -17345,50 +17345,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>7.3951555289611226E-2</v>
+        <v>7.5780745703135186E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>8.6296231347033278E-2</v>
+        <v>8.8430767104733743E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>0.11874898556941145</v>
+        <v>0.12168623962943222</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>0.19258674002090223</v>
+        <v>0.19735036963272665</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>0.15824021727763796</v>
+        <v>0.16215428625623676</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>5.6768412979652204E-2</v>
+        <v>5.8172578671728405E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>7.2066679841095771E-2</v>
+        <v>7.3849247893702383E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>6.4165753051254965E-2</v>
+        <v>6.5752891819307213E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>6.0942662590720349E-2</v>
+        <v>6.2450078273176321E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>1.0788066998531361E-2</v>
+        <v>1.1054909645138144E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>4.6733660235356673E-3</v>
+        <v>4.7889616495595177E-3</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -17402,43 +17402,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1229317153912671</v>
+        <v>0.12597242919953164</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15584691543902882</v>
+        <v>0.15970178613893413</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.22406764221556616</v>
+        <v>0.22960995138697593</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.20731591639155772</v>
+        <v>0.21244387192067751</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.0416940092778014E-2</v>
+        <v>8.240605168517888E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.9662271200429915E-2</v>
+        <v>8.1632716071111916E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.8022278569804829E-2</v>
+        <v>7.9952158251743469E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.0098667868299125E-2</v>
+        <v>8.2079907002850699E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.5824698062020509E-3</v>
+        <v>4.6958171158960936E-3</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-4.8189557546523647E-2</v>
+        <v>-4.9381525401031301E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -21388,7 +21388,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-2.9</v>
+        <v>-2.83</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -21628,7 +21628,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>2.9</v>
+        <v>2.83</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>2.9</v>
+        <v>2.83</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -22239,7 +22239,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.23811424597741593</v>
+        <v>0.24901483038369632</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/0639.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0639.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29B573A7-F1C5-40C7-8467-9472ECF90E75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81B77B36-119A-40A4-A45B-984A15A15207}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2205" yWindow="2205" windowWidth="12690" windowHeight="7642" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="735" yWindow="735" windowWidth="12690" windowHeight="7643" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="投资主题" sheetId="12" r:id="rId1"/>
@@ -4759,6 +4759,15 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4768,16 +4777,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="C12" s="366">
         <f>Market_Price</f>
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C14" s="35">
         <f>投资主题!C12*Common_Shares/1000000</f>
-        <v>14407.716129100001</v>
+        <v>14458.6267868</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",投资主题!D12*Common_Shares/1000000)</f>
@@ -5346,13 +5346,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="374" t="s">
+      <c r="B18" s="371" t="s">
         <v>489</v>
       </c>
-      <c r="C18" s="374"/>
-      <c r="D18" s="374"/>
-      <c r="E18" s="374"/>
-      <c r="F18" s="374"/>
+      <c r="C18" s="371"/>
+      <c r="D18" s="371"/>
+      <c r="E18" s="371"/>
+      <c r="F18" s="371"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -5443,7 +5443,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.24901483038369632</v>
+        <v>0.24743461613512951</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -5565,22 +5565,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="374" t="s">
+      <c r="B36" s="371" t="s">
         <v>492</v>
       </c>
-      <c r="C36" s="374"/>
-      <c r="D36" s="374"/>
-      <c r="E36" s="374"/>
-      <c r="F36" s="374"/>
+      <c r="C36" s="371"/>
+      <c r="D36" s="371"/>
+      <c r="E36" s="371"/>
+      <c r="F36" s="371"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="377" t="s">
+      <c r="B37" s="372" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="377"/>
-      <c r="D37" s="377"/>
-      <c r="E37" s="377"/>
-      <c r="F37" s="377"/>
+      <c r="C37" s="372"/>
+      <c r="D37" s="372"/>
+      <c r="E37" s="372"/>
+      <c r="F37" s="372"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -5770,10 +5770,10 @@
       <c r="B61" s="370" t="s">
         <v>499</v>
       </c>
-      <c r="C61" s="376"/>
-      <c r="D61" s="376"/>
-      <c r="E61" s="376"/>
-      <c r="F61" s="376"/>
+      <c r="C61" s="373"/>
+      <c r="D61" s="373"/>
+      <c r="E61" s="373"/>
+      <c r="F61" s="373"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -5789,22 +5789,22 @@
       </c>
     </row>
     <row r="64" spans="2:6">
-      <c r="B64" s="374" t="s">
+      <c r="B64" s="371" t="s">
         <v>500</v>
       </c>
-      <c r="C64" s="374"/>
-      <c r="D64" s="374"/>
-      <c r="E64" s="374"/>
-      <c r="F64" s="374"/>
+      <c r="C64" s="371"/>
+      <c r="D64" s="371"/>
+      <c r="E64" s="371"/>
+      <c r="F64" s="371"/>
     </row>
     <row r="65" spans="1:6">
-      <c r="B65" s="374" t="s">
+      <c r="B65" s="371" t="s">
         <v>501</v>
       </c>
-      <c r="C65" s="374"/>
-      <c r="D65" s="374"/>
-      <c r="E65" s="374"/>
-      <c r="F65" s="374"/>
+      <c r="C65" s="371"/>
+      <c r="D65" s="371"/>
+      <c r="E65" s="371"/>
+      <c r="F65" s="371"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -5838,7 +5838,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>7.5780745703135186E-2</v>
+        <v>7.5513912091504432E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -5848,7 +5848,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>9.5406360424028266E-2</v>
+        <v>9.507042253521128E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>503</v>
@@ -5939,22 +5939,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="374" t="s">
+      <c r="B80" s="371" t="s">
         <v>506</v>
       </c>
-      <c r="C80" s="374"/>
-      <c r="D80" s="374"/>
-      <c r="E80" s="374"/>
-      <c r="F80" s="374"/>
+      <c r="C80" s="371"/>
+      <c r="D80" s="371"/>
+      <c r="E80" s="371"/>
+      <c r="F80" s="371"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="377" t="s">
+      <c r="B81" s="372" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="377"/>
-      <c r="D81" s="377"/>
-      <c r="E81" s="377"/>
-      <c r="F81" s="377"/>
+      <c r="C81" s="372"/>
+      <c r="D81" s="372"/>
+      <c r="E81" s="372"/>
+      <c r="F81" s="372"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5998,22 +5998,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6">
-      <c r="B89" s="374" t="s">
+      <c r="B89" s="371" t="s">
         <v>507</v>
       </c>
-      <c r="C89" s="374"/>
-      <c r="D89" s="374"/>
-      <c r="E89" s="374"/>
-      <c r="F89" s="374"/>
+      <c r="C89" s="371"/>
+      <c r="D89" s="371"/>
+      <c r="E89" s="371"/>
+      <c r="F89" s="371"/>
     </row>
     <row r="90" spans="1:6">
-      <c r="B90" s="374" t="s">
+      <c r="B90" s="371" t="s">
         <v>508</v>
       </c>
-      <c r="C90" s="374"/>
-      <c r="D90" s="374"/>
-      <c r="E90" s="374"/>
-      <c r="F90" s="374"/>
+      <c r="C90" s="371"/>
+      <c r="D90" s="371"/>
+      <c r="E90" s="371"/>
+      <c r="F90" s="371"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -6050,13 +6050,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="374" t="s">
+      <c r="B97" s="371" t="s">
         <v>510</v>
       </c>
-      <c r="C97" s="374"/>
-      <c r="D97" s="374"/>
-      <c r="E97" s="374"/>
-      <c r="F97" s="374"/>
+      <c r="C97" s="371"/>
+      <c r="D97" s="371"/>
+      <c r="E97" s="371"/>
+      <c r="F97" s="371"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -6069,13 +6069,13 @@
       </c>
     </row>
     <row r="101" spans="2:6">
-      <c r="B101" s="374" t="s">
+      <c r="B101" s="371" t="s">
         <v>511</v>
       </c>
-      <c r="C101" s="374"/>
-      <c r="D101" s="374"/>
-      <c r="E101" s="374"/>
-      <c r="F101" s="374"/>
+      <c r="C101" s="371"/>
+      <c r="D101" s="371"/>
+      <c r="E101" s="371"/>
+      <c r="F101" s="371"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -6197,13 +6197,13 @@
       </c>
     </row>
     <row r="116" spans="1:6">
-      <c r="B116" s="374" t="s">
+      <c r="B116" s="371" t="s">
         <v>516</v>
       </c>
-      <c r="C116" s="374"/>
-      <c r="D116" s="374"/>
-      <c r="E116" s="374"/>
-      <c r="F116" s="374"/>
+      <c r="C116" s="371"/>
+      <c r="D116" s="371"/>
+      <c r="E116" s="371"/>
+      <c r="F116" s="371"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -6391,13 +6391,13 @@
       </c>
     </row>
     <row r="134" spans="1:6">
-      <c r="B134" s="372" t="s">
+      <c r="B134" s="375" t="s">
         <v>524</v>
       </c>
-      <c r="C134" s="372"/>
-      <c r="D134" s="372"/>
-      <c r="E134" s="372"/>
-      <c r="F134" s="372"/>
+      <c r="C134" s="375"/>
+      <c r="D134" s="375"/>
+      <c r="E134" s="375"/>
+      <c r="F134" s="375"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -6410,22 +6410,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="373" t="s">
+      <c r="B138" s="376" t="s">
         <v>526</v>
       </c>
-      <c r="C138" s="373"/>
-      <c r="D138" s="373"/>
-      <c r="E138" s="373"/>
-      <c r="F138" s="373"/>
+      <c r="C138" s="376"/>
+      <c r="D138" s="376"/>
+      <c r="E138" s="376"/>
+      <c r="F138" s="376"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="374" t="s">
+      <c r="B139" s="371" t="s">
         <v>527</v>
       </c>
-      <c r="C139" s="374"/>
-      <c r="D139" s="374"/>
-      <c r="E139" s="374"/>
-      <c r="F139" s="374"/>
+      <c r="C139" s="371"/>
+      <c r="D139" s="371"/>
+      <c r="E139" s="371"/>
+      <c r="F139" s="371"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -6758,13 +6758,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="375" t="s">
+      <c r="B179" s="377" t="s">
         <v>534</v>
       </c>
-      <c r="C179" s="374"/>
-      <c r="D179" s="374"/>
-      <c r="E179" s="374"/>
-      <c r="F179" s="374"/>
+      <c r="C179" s="371"/>
+      <c r="D179" s="371"/>
+      <c r="E179" s="371"/>
+      <c r="F179" s="371"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -6772,13 +6772,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="376" t="s">
+      <c r="B182" s="373" t="s">
         <v>536</v>
       </c>
-      <c r="C182" s="376"/>
-      <c r="D182" s="376"/>
-      <c r="E182" s="376"/>
-      <c r="F182" s="376"/>
+      <c r="C182" s="373"/>
+      <c r="D182" s="373"/>
+      <c r="E182" s="373"/>
+      <c r="F182" s="373"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -6815,22 +6815,22 @@
       </c>
     </row>
     <row r="191" spans="1:6">
-      <c r="B191" s="371" t="s">
+      <c r="B191" s="374" t="s">
         <v>543</v>
       </c>
-      <c r="C191" s="371"/>
-      <c r="D191" s="371"/>
-      <c r="E191" s="371"/>
-      <c r="F191" s="371"/>
+      <c r="C191" s="374"/>
+      <c r="D191" s="374"/>
+      <c r="E191" s="374"/>
+      <c r="F191" s="374"/>
     </row>
     <row r="192" spans="1:6">
-      <c r="B192" s="371" t="s">
+      <c r="B192" s="374" t="s">
         <v>544</v>
       </c>
-      <c r="C192" s="371"/>
-      <c r="D192" s="371"/>
-      <c r="E192" s="371"/>
-      <c r="F192" s="371"/>
+      <c r="C192" s="374"/>
+      <c r="D192" s="374"/>
+      <c r="E192" s="374"/>
+      <c r="F192" s="374"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -6854,12 +6854,15 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B47:F47"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B138:F138"/>
+    <mergeCell ref="B139:F139"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B182:F182"/>
     <mergeCell ref="B116:F116"/>
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B58:F58"/>
@@ -6872,15 +6875,12 @@
     <mergeCell ref="B90:F90"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B138:F138"/>
-    <mergeCell ref="B139:F139"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B43:F43"/>
   </mergeCells>
   <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">
@@ -7023,7 +7023,7 @@
         <v>463</v>
       </c>
       <c r="C12" s="50">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -7044,7 +7044,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>14407.716129100001</v>
+        <v>14458.6267868</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -7081,13 +7081,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="374" t="s">
+      <c r="B18" s="371" t="s">
         <v>468</v>
       </c>
-      <c r="C18" s="374"/>
-      <c r="D18" s="374"/>
-      <c r="E18" s="374"/>
-      <c r="F18" s="374"/>
+      <c r="C18" s="371"/>
+      <c r="D18" s="371"/>
+      <c r="E18" s="371"/>
+      <c r="F18" s="371"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -7170,7 +7170,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.24901483038369632</v>
+        <v>0.24743461613512951</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -7287,22 +7287,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6">
-      <c r="B36" s="374" t="s">
+      <c r="B36" s="371" t="s">
         <v>469</v>
       </c>
-      <c r="C36" s="374"/>
-      <c r="D36" s="374"/>
-      <c r="E36" s="374"/>
-      <c r="F36" s="374"/>
+      <c r="C36" s="371"/>
+      <c r="D36" s="371"/>
+      <c r="E36" s="371"/>
+      <c r="F36" s="371"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="377" t="s">
+      <c r="B37" s="372" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="377"/>
-      <c r="D37" s="377"/>
-      <c r="E37" s="377"/>
-      <c r="F37" s="377"/>
+      <c r="C37" s="372"/>
+      <c r="D37" s="372"/>
+      <c r="E37" s="372"/>
+      <c r="F37" s="372"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -7492,10 +7492,10 @@
       <c r="B61" s="370" t="s">
         <v>329</v>
       </c>
-      <c r="C61" s="376"/>
-      <c r="D61" s="376"/>
-      <c r="E61" s="376"/>
-      <c r="F61" s="376"/>
+      <c r="C61" s="373"/>
+      <c r="D61" s="373"/>
+      <c r="E61" s="373"/>
+      <c r="F61" s="373"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -7511,22 +7511,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="374" t="s">
+      <c r="B64" s="371" t="s">
         <v>334</v>
       </c>
-      <c r="C64" s="374"/>
-      <c r="D64" s="374"/>
-      <c r="E64" s="374"/>
-      <c r="F64" s="374"/>
+      <c r="C64" s="371"/>
+      <c r="D64" s="371"/>
+      <c r="E64" s="371"/>
+      <c r="F64" s="371"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="374" t="s">
+      <c r="B65" s="371" t="s">
         <v>348</v>
       </c>
-      <c r="C65" s="374"/>
-      <c r="D65" s="374"/>
-      <c r="E65" s="374"/>
-      <c r="F65" s="374"/>
+      <c r="C65" s="371"/>
+      <c r="D65" s="371"/>
+      <c r="E65" s="371"/>
+      <c r="F65" s="371"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -7560,7 +7560,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>7.5780745703135186E-2</v>
+        <v>7.5513912091504432E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -7570,7 +7570,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>9.5406360424028266E-2</v>
+        <v>9.507042253521128E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>424</v>
@@ -7661,22 +7661,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="374" t="s">
+      <c r="B80" s="371" t="s">
         <v>471</v>
       </c>
-      <c r="C80" s="374"/>
-      <c r="D80" s="374"/>
-      <c r="E80" s="374"/>
-      <c r="F80" s="374"/>
+      <c r="C80" s="371"/>
+      <c r="D80" s="371"/>
+      <c r="E80" s="371"/>
+      <c r="F80" s="371"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="377" t="s">
+      <c r="B81" s="372" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="377"/>
-      <c r="D81" s="377"/>
-      <c r="E81" s="377"/>
-      <c r="F81" s="377"/>
+      <c r="C81" s="372"/>
+      <c r="D81" s="372"/>
+      <c r="E81" s="372"/>
+      <c r="F81" s="372"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -7720,22 +7720,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="374" t="s">
+      <c r="B89" s="371" t="s">
         <v>349</v>
       </c>
-      <c r="C89" s="374"/>
-      <c r="D89" s="374"/>
-      <c r="E89" s="374"/>
-      <c r="F89" s="374"/>
+      <c r="C89" s="371"/>
+      <c r="D89" s="371"/>
+      <c r="E89" s="371"/>
+      <c r="F89" s="371"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="374" t="s">
+      <c r="B90" s="371" t="s">
         <v>350</v>
       </c>
-      <c r="C90" s="374"/>
-      <c r="D90" s="374"/>
-      <c r="E90" s="374"/>
-      <c r="F90" s="374"/>
+      <c r="C90" s="371"/>
+      <c r="D90" s="371"/>
+      <c r="E90" s="371"/>
+      <c r="F90" s="371"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -7772,13 +7772,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="374" t="s">
+      <c r="B97" s="371" t="s">
         <v>351</v>
       </c>
-      <c r="C97" s="374"/>
-      <c r="D97" s="374"/>
-      <c r="E97" s="374"/>
-      <c r="F97" s="374"/>
+      <c r="C97" s="371"/>
+      <c r="D97" s="371"/>
+      <c r="E97" s="371"/>
+      <c r="F97" s="371"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -7791,13 +7791,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="374" t="s">
+      <c r="B101" s="371" t="s">
         <v>335</v>
       </c>
-      <c r="C101" s="374"/>
-      <c r="D101" s="374"/>
-      <c r="E101" s="374"/>
-      <c r="F101" s="374"/>
+      <c r="C101" s="371"/>
+      <c r="D101" s="371"/>
+      <c r="E101" s="371"/>
+      <c r="F101" s="371"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -7919,13 +7919,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="374" t="s">
+      <c r="B116" s="371" t="s">
         <v>352</v>
       </c>
-      <c r="C116" s="374"/>
-      <c r="D116" s="374"/>
-      <c r="E116" s="374"/>
-      <c r="F116" s="374"/>
+      <c r="C116" s="371"/>
+      <c r="D116" s="371"/>
+      <c r="E116" s="371"/>
+      <c r="F116" s="371"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -8113,13 +8113,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="372" t="s">
+      <c r="B134" s="375" t="s">
         <v>474</v>
       </c>
-      <c r="C134" s="372"/>
-      <c r="D134" s="372"/>
-      <c r="E134" s="372"/>
-      <c r="F134" s="372"/>
+      <c r="C134" s="375"/>
+      <c r="D134" s="375"/>
+      <c r="E134" s="375"/>
+      <c r="F134" s="375"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -8132,22 +8132,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="373" t="s">
+      <c r="B138" s="376" t="s">
         <v>353</v>
       </c>
-      <c r="C138" s="373"/>
-      <c r="D138" s="373"/>
-      <c r="E138" s="373"/>
-      <c r="F138" s="373"/>
+      <c r="C138" s="376"/>
+      <c r="D138" s="376"/>
+      <c r="E138" s="376"/>
+      <c r="F138" s="376"/>
     </row>
     <row r="139" spans="1:6">
-      <c r="B139" s="374" t="s">
+      <c r="B139" s="371" t="s">
         <v>476</v>
       </c>
-      <c r="C139" s="374"/>
-      <c r="D139" s="374"/>
-      <c r="E139" s="374"/>
-      <c r="F139" s="374"/>
+      <c r="C139" s="371"/>
+      <c r="D139" s="371"/>
+      <c r="E139" s="371"/>
+      <c r="F139" s="371"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -8480,13 +8480,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="375" t="s">
+      <c r="B179" s="377" t="s">
         <v>477</v>
       </c>
-      <c r="C179" s="374"/>
-      <c r="D179" s="374"/>
-      <c r="E179" s="374"/>
-      <c r="F179" s="374"/>
+      <c r="C179" s="371"/>
+      <c r="D179" s="371"/>
+      <c r="E179" s="371"/>
+      <c r="F179" s="371"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -8494,13 +8494,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="376" t="s">
+      <c r="B182" s="373" t="s">
         <v>362</v>
       </c>
-      <c r="C182" s="376"/>
-      <c r="D182" s="376"/>
-      <c r="E182" s="376"/>
-      <c r="F182" s="376"/>
+      <c r="C182" s="373"/>
+      <c r="D182" s="373"/>
+      <c r="E182" s="373"/>
+      <c r="F182" s="373"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -8537,22 +8537,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="371" t="s">
+      <c r="B191" s="374" t="s">
         <v>363</v>
       </c>
-      <c r="C191" s="371"/>
-      <c r="D191" s="371"/>
-      <c r="E191" s="371"/>
-      <c r="F191" s="371"/>
+      <c r="C191" s="374"/>
+      <c r="D191" s="374"/>
+      <c r="E191" s="374"/>
+      <c r="F191" s="374"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="371" t="s">
+      <c r="B192" s="374" t="s">
         <v>364</v>
       </c>
-      <c r="C192" s="371"/>
-      <c r="D192" s="371"/>
-      <c r="E192" s="371"/>
-      <c r="F192" s="371"/>
+      <c r="C192" s="374"/>
+      <c r="D192" s="374"/>
+      <c r="E192" s="374"/>
+      <c r="F192" s="374"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -8576,6 +8576,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -8592,17 +8603,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -16146,20 +16146,20 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>9.5406360424028266E-2</v>
+        <v>9.507042253521128E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>9.5406360424028266E-2</v>
+        <v>9.507042253521128E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>8.9045936395759737E-2</v>
+        <v>8.8732394366197204E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>0.13674911660777386</v>
+        <v>0.13626760563380286</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
@@ -17345,50 +17345,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>7.5780745703135186E-2</v>
+        <v>7.5513912091504432E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>8.8430767104733743E-2</v>
+        <v>8.8119391164224126E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>0.12168623962943222</v>
+        <v>0.1212577669546807</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>0.19735036963272665</v>
+        <v>0.19665547396500579</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>0.16215428625623676</v>
+        <v>0.16158332045955989</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>5.8172578671728405E-2</v>
+        <v>5.7967745648236403E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>7.3849247893702383E-2</v>
+        <v>7.3589215330696386E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>6.5752891819307213E-2</v>
+        <v>6.5521367552337825E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>6.2450078273176321E-2</v>
+        <v>6.2230183631369368E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>1.1054909645138144E-2</v>
+        <v>1.1015983906951039E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>4.7889616495595177E-3</v>
+        <v>4.7720991085399419E-3</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -17402,43 +17402,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12597242919953164</v>
+        <v>0.12552886430798402</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15970178613893413</v>
+        <v>0.15913945590605055</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.22960995138697593</v>
+        <v>0.2288014656426556</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.21244387192067751</v>
+        <v>0.21169583011813992</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.240605168517888E-2</v>
+        <v>8.211588953135783E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.1632716071111916E-2</v>
+        <v>8.1345276930016461E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.9952158251743469E-2</v>
+        <v>7.9670636567758454E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.2079907002850699E-2</v>
+        <v>8.1790893245798413E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.6958171158960936E-3</v>
+        <v>4.6792825485866014E-3</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-4.9381525401031301E-2</v>
+        <v>-4.9207646790464292E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -21388,7 +21388,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-2.83</v>
+        <v>-2.84</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -21628,7 +21628,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -22239,7 +22239,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.24901483038369632</v>
+        <v>0.24743461613512951</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/0639.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0639.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81B77B36-119A-40A4-A45B-984A15A15207}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E56B9A1-D38A-46EF-87D3-355AEE47FE59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="735" yWindow="735" windowWidth="12690" windowHeight="7643" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1837" yWindow="1837" windowWidth="12691" windowHeight="7643" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="投资主题" sheetId="12" r:id="rId1"/>
@@ -4759,15 +4759,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4777,7 +4768,16 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="C12" s="366">
         <f>Market_Price</f>
-        <v>2.84</v>
+        <v>2.91</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C14" s="35">
         <f>投资主题!C12*Common_Shares/1000000</f>
-        <v>14458.6267868</v>
+        <v>14815.001390700001</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",投资主题!D12*Common_Shares/1000000)</f>
@@ -5346,13 +5346,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="371" t="s">
+      <c r="B18" s="374" t="s">
         <v>489</v>
       </c>
-      <c r="C18" s="371"/>
-      <c r="D18" s="371"/>
-      <c r="E18" s="371"/>
-      <c r="F18" s="371"/>
+      <c r="C18" s="374"/>
+      <c r="D18" s="374"/>
+      <c r="E18" s="374"/>
+      <c r="F18" s="374"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -5443,7 +5443,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.24743461613512951</v>
+        <v>0.23658707196826612</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -5565,22 +5565,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="371" t="s">
+      <c r="B36" s="374" t="s">
         <v>492</v>
       </c>
-      <c r="C36" s="371"/>
-      <c r="D36" s="371"/>
-      <c r="E36" s="371"/>
-      <c r="F36" s="371"/>
+      <c r="C36" s="374"/>
+      <c r="D36" s="374"/>
+      <c r="E36" s="374"/>
+      <c r="F36" s="374"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="372" t="s">
+      <c r="B37" s="377" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="372"/>
-      <c r="D37" s="372"/>
-      <c r="E37" s="372"/>
-      <c r="F37" s="372"/>
+      <c r="C37" s="377"/>
+      <c r="D37" s="377"/>
+      <c r="E37" s="377"/>
+      <c r="F37" s="377"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -5770,10 +5770,10 @@
       <c r="B61" s="370" t="s">
         <v>499</v>
       </c>
-      <c r="C61" s="373"/>
-      <c r="D61" s="373"/>
-      <c r="E61" s="373"/>
-      <c r="F61" s="373"/>
+      <c r="C61" s="376"/>
+      <c r="D61" s="376"/>
+      <c r="E61" s="376"/>
+      <c r="F61" s="376"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -5789,22 +5789,22 @@
       </c>
     </row>
     <row r="64" spans="2:6">
-      <c r="B64" s="371" t="s">
+      <c r="B64" s="374" t="s">
         <v>500</v>
       </c>
-      <c r="C64" s="371"/>
-      <c r="D64" s="371"/>
-      <c r="E64" s="371"/>
-      <c r="F64" s="371"/>
+      <c r="C64" s="374"/>
+      <c r="D64" s="374"/>
+      <c r="E64" s="374"/>
+      <c r="F64" s="374"/>
     </row>
     <row r="65" spans="1:6">
-      <c r="B65" s="371" t="s">
+      <c r="B65" s="374" t="s">
         <v>501</v>
       </c>
-      <c r="C65" s="371"/>
-      <c r="D65" s="371"/>
-      <c r="E65" s="371"/>
-      <c r="F65" s="371"/>
+      <c r="C65" s="374"/>
+      <c r="D65" s="374"/>
+      <c r="E65" s="374"/>
+      <c r="F65" s="374"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -5838,7 +5838,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>7.5513912091504432E-2</v>
+        <v>7.3697426233633179E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -5848,7 +5848,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>9.507042253521128E-2</v>
+        <v>9.2783505154639179E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>503</v>
@@ -5939,22 +5939,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="371" t="s">
+      <c r="B80" s="374" t="s">
         <v>506</v>
       </c>
-      <c r="C80" s="371"/>
-      <c r="D80" s="371"/>
-      <c r="E80" s="371"/>
-      <c r="F80" s="371"/>
+      <c r="C80" s="374"/>
+      <c r="D80" s="374"/>
+      <c r="E80" s="374"/>
+      <c r="F80" s="374"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="372" t="s">
+      <c r="B81" s="377" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="372"/>
-      <c r="D81" s="372"/>
-      <c r="E81" s="372"/>
-      <c r="F81" s="372"/>
+      <c r="C81" s="377"/>
+      <c r="D81" s="377"/>
+      <c r="E81" s="377"/>
+      <c r="F81" s="377"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5998,22 +5998,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6">
-      <c r="B89" s="371" t="s">
+      <c r="B89" s="374" t="s">
         <v>507</v>
       </c>
-      <c r="C89" s="371"/>
-      <c r="D89" s="371"/>
-      <c r="E89" s="371"/>
-      <c r="F89" s="371"/>
+      <c r="C89" s="374"/>
+      <c r="D89" s="374"/>
+      <c r="E89" s="374"/>
+      <c r="F89" s="374"/>
     </row>
     <row r="90" spans="1:6">
-      <c r="B90" s="371" t="s">
+      <c r="B90" s="374" t="s">
         <v>508</v>
       </c>
-      <c r="C90" s="371"/>
-      <c r="D90" s="371"/>
-      <c r="E90" s="371"/>
-      <c r="F90" s="371"/>
+      <c r="C90" s="374"/>
+      <c r="D90" s="374"/>
+      <c r="E90" s="374"/>
+      <c r="F90" s="374"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -6050,13 +6050,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="371" t="s">
+      <c r="B97" s="374" t="s">
         <v>510</v>
       </c>
-      <c r="C97" s="371"/>
-      <c r="D97" s="371"/>
-      <c r="E97" s="371"/>
-      <c r="F97" s="371"/>
+      <c r="C97" s="374"/>
+      <c r="D97" s="374"/>
+      <c r="E97" s="374"/>
+      <c r="F97" s="374"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -6069,13 +6069,13 @@
       </c>
     </row>
     <row r="101" spans="2:6">
-      <c r="B101" s="371" t="s">
+      <c r="B101" s="374" t="s">
         <v>511</v>
       </c>
-      <c r="C101" s="371"/>
-      <c r="D101" s="371"/>
-      <c r="E101" s="371"/>
-      <c r="F101" s="371"/>
+      <c r="C101" s="374"/>
+      <c r="D101" s="374"/>
+      <c r="E101" s="374"/>
+      <c r="F101" s="374"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -6197,13 +6197,13 @@
       </c>
     </row>
     <row r="116" spans="1:6">
-      <c r="B116" s="371" t="s">
+      <c r="B116" s="374" t="s">
         <v>516</v>
       </c>
-      <c r="C116" s="371"/>
-      <c r="D116" s="371"/>
-      <c r="E116" s="371"/>
-      <c r="F116" s="371"/>
+      <c r="C116" s="374"/>
+      <c r="D116" s="374"/>
+      <c r="E116" s="374"/>
+      <c r="F116" s="374"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -6391,13 +6391,13 @@
       </c>
     </row>
     <row r="134" spans="1:6">
-      <c r="B134" s="375" t="s">
+      <c r="B134" s="372" t="s">
         <v>524</v>
       </c>
-      <c r="C134" s="375"/>
-      <c r="D134" s="375"/>
-      <c r="E134" s="375"/>
-      <c r="F134" s="375"/>
+      <c r="C134" s="372"/>
+      <c r="D134" s="372"/>
+      <c r="E134" s="372"/>
+      <c r="F134" s="372"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -6410,22 +6410,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="376" t="s">
+      <c r="B138" s="373" t="s">
         <v>526</v>
       </c>
-      <c r="C138" s="376"/>
-      <c r="D138" s="376"/>
-      <c r="E138" s="376"/>
-      <c r="F138" s="376"/>
+      <c r="C138" s="373"/>
+      <c r="D138" s="373"/>
+      <c r="E138" s="373"/>
+      <c r="F138" s="373"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="371" t="s">
+      <c r="B139" s="374" t="s">
         <v>527</v>
       </c>
-      <c r="C139" s="371"/>
-      <c r="D139" s="371"/>
-      <c r="E139" s="371"/>
-      <c r="F139" s="371"/>
+      <c r="C139" s="374"/>
+      <c r="D139" s="374"/>
+      <c r="E139" s="374"/>
+      <c r="F139" s="374"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -6758,13 +6758,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="377" t="s">
+      <c r="B179" s="375" t="s">
         <v>534</v>
       </c>
-      <c r="C179" s="371"/>
-      <c r="D179" s="371"/>
-      <c r="E179" s="371"/>
-      <c r="F179" s="371"/>
+      <c r="C179" s="374"/>
+      <c r="D179" s="374"/>
+      <c r="E179" s="374"/>
+      <c r="F179" s="374"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -6772,13 +6772,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="373" t="s">
+      <c r="B182" s="376" t="s">
         <v>536</v>
       </c>
-      <c r="C182" s="373"/>
-      <c r="D182" s="373"/>
-      <c r="E182" s="373"/>
-      <c r="F182" s="373"/>
+      <c r="C182" s="376"/>
+      <c r="D182" s="376"/>
+      <c r="E182" s="376"/>
+      <c r="F182" s="376"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -6815,22 +6815,22 @@
       </c>
     </row>
     <row r="191" spans="1:6">
-      <c r="B191" s="374" t="s">
+      <c r="B191" s="371" t="s">
         <v>543</v>
       </c>
-      <c r="C191" s="374"/>
-      <c r="D191" s="374"/>
-      <c r="E191" s="374"/>
-      <c r="F191" s="374"/>
+      <c r="C191" s="371"/>
+      <c r="D191" s="371"/>
+      <c r="E191" s="371"/>
+      <c r="F191" s="371"/>
     </row>
     <row r="192" spans="1:6">
-      <c r="B192" s="374" t="s">
+      <c r="B192" s="371" t="s">
         <v>544</v>
       </c>
-      <c r="C192" s="374"/>
-      <c r="D192" s="374"/>
-      <c r="E192" s="374"/>
-      <c r="F192" s="374"/>
+      <c r="C192" s="371"/>
+      <c r="D192" s="371"/>
+      <c r="E192" s="371"/>
+      <c r="F192" s="371"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -6854,15 +6854,12 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B138:F138"/>
-    <mergeCell ref="B139:F139"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B43:F43"/>
     <mergeCell ref="B116:F116"/>
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B58:F58"/>
@@ -6875,12 +6872,15 @@
     <mergeCell ref="B90:F90"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B47:F47"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B138:F138"/>
+    <mergeCell ref="B139:F139"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">
@@ -7023,7 +7023,7 @@
         <v>463</v>
       </c>
       <c r="C12" s="50">
-        <v>2.84</v>
+        <v>2.91</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -7044,7 +7044,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>14458.6267868</v>
+        <v>14815.001390700001</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -7081,13 +7081,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="371" t="s">
+      <c r="B18" s="374" t="s">
         <v>468</v>
       </c>
-      <c r="C18" s="371"/>
-      <c r="D18" s="371"/>
-      <c r="E18" s="371"/>
-      <c r="F18" s="371"/>
+      <c r="C18" s="374"/>
+      <c r="D18" s="374"/>
+      <c r="E18" s="374"/>
+      <c r="F18" s="374"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -7170,7 +7170,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.24743461613512951</v>
+        <v>0.23658707196826612</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -7287,22 +7287,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6">
-      <c r="B36" s="371" t="s">
+      <c r="B36" s="374" t="s">
         <v>469</v>
       </c>
-      <c r="C36" s="371"/>
-      <c r="D36" s="371"/>
-      <c r="E36" s="371"/>
-      <c r="F36" s="371"/>
+      <c r="C36" s="374"/>
+      <c r="D36" s="374"/>
+      <c r="E36" s="374"/>
+      <c r="F36" s="374"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="372" t="s">
+      <c r="B37" s="377" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="372"/>
-      <c r="D37" s="372"/>
-      <c r="E37" s="372"/>
-      <c r="F37" s="372"/>
+      <c r="C37" s="377"/>
+      <c r="D37" s="377"/>
+      <c r="E37" s="377"/>
+      <c r="F37" s="377"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -7492,10 +7492,10 @@
       <c r="B61" s="370" t="s">
         <v>329</v>
       </c>
-      <c r="C61" s="373"/>
-      <c r="D61" s="373"/>
-      <c r="E61" s="373"/>
-      <c r="F61" s="373"/>
+      <c r="C61" s="376"/>
+      <c r="D61" s="376"/>
+      <c r="E61" s="376"/>
+      <c r="F61" s="376"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -7511,22 +7511,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="371" t="s">
+      <c r="B64" s="374" t="s">
         <v>334</v>
       </c>
-      <c r="C64" s="371"/>
-      <c r="D64" s="371"/>
-      <c r="E64" s="371"/>
-      <c r="F64" s="371"/>
+      <c r="C64" s="374"/>
+      <c r="D64" s="374"/>
+      <c r="E64" s="374"/>
+      <c r="F64" s="374"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="371" t="s">
+      <c r="B65" s="374" t="s">
         <v>348</v>
       </c>
-      <c r="C65" s="371"/>
-      <c r="D65" s="371"/>
-      <c r="E65" s="371"/>
-      <c r="F65" s="371"/>
+      <c r="C65" s="374"/>
+      <c r="D65" s="374"/>
+      <c r="E65" s="374"/>
+      <c r="F65" s="374"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -7560,7 +7560,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>7.5513912091504432E-2</v>
+        <v>7.3697426233633179E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -7570,7 +7570,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>9.507042253521128E-2</v>
+        <v>9.2783505154639179E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>424</v>
@@ -7661,22 +7661,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="371" t="s">
+      <c r="B80" s="374" t="s">
         <v>471</v>
       </c>
-      <c r="C80" s="371"/>
-      <c r="D80" s="371"/>
-      <c r="E80" s="371"/>
-      <c r="F80" s="371"/>
+      <c r="C80" s="374"/>
+      <c r="D80" s="374"/>
+      <c r="E80" s="374"/>
+      <c r="F80" s="374"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="372" t="s">
+      <c r="B81" s="377" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="372"/>
-      <c r="D81" s="372"/>
-      <c r="E81" s="372"/>
-      <c r="F81" s="372"/>
+      <c r="C81" s="377"/>
+      <c r="D81" s="377"/>
+      <c r="E81" s="377"/>
+      <c r="F81" s="377"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -7720,22 +7720,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="371" t="s">
+      <c r="B89" s="374" t="s">
         <v>349</v>
       </c>
-      <c r="C89" s="371"/>
-      <c r="D89" s="371"/>
-      <c r="E89" s="371"/>
-      <c r="F89" s="371"/>
+      <c r="C89" s="374"/>
+      <c r="D89" s="374"/>
+      <c r="E89" s="374"/>
+      <c r="F89" s="374"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="371" t="s">
+      <c r="B90" s="374" t="s">
         <v>350</v>
       </c>
-      <c r="C90" s="371"/>
-      <c r="D90" s="371"/>
-      <c r="E90" s="371"/>
-      <c r="F90" s="371"/>
+      <c r="C90" s="374"/>
+      <c r="D90" s="374"/>
+      <c r="E90" s="374"/>
+      <c r="F90" s="374"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -7772,13 +7772,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="371" t="s">
+      <c r="B97" s="374" t="s">
         <v>351</v>
       </c>
-      <c r="C97" s="371"/>
-      <c r="D97" s="371"/>
-      <c r="E97" s="371"/>
-      <c r="F97" s="371"/>
+      <c r="C97" s="374"/>
+      <c r="D97" s="374"/>
+      <c r="E97" s="374"/>
+      <c r="F97" s="374"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -7791,13 +7791,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="371" t="s">
+      <c r="B101" s="374" t="s">
         <v>335</v>
       </c>
-      <c r="C101" s="371"/>
-      <c r="D101" s="371"/>
-      <c r="E101" s="371"/>
-      <c r="F101" s="371"/>
+      <c r="C101" s="374"/>
+      <c r="D101" s="374"/>
+      <c r="E101" s="374"/>
+      <c r="F101" s="374"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -7919,13 +7919,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="371" t="s">
+      <c r="B116" s="374" t="s">
         <v>352</v>
       </c>
-      <c r="C116" s="371"/>
-      <c r="D116" s="371"/>
-      <c r="E116" s="371"/>
-      <c r="F116" s="371"/>
+      <c r="C116" s="374"/>
+      <c r="D116" s="374"/>
+      <c r="E116" s="374"/>
+      <c r="F116" s="374"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -8113,13 +8113,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="375" t="s">
+      <c r="B134" s="372" t="s">
         <v>474</v>
       </c>
-      <c r="C134" s="375"/>
-      <c r="D134" s="375"/>
-      <c r="E134" s="375"/>
-      <c r="F134" s="375"/>
+      <c r="C134" s="372"/>
+      <c r="D134" s="372"/>
+      <c r="E134" s="372"/>
+      <c r="F134" s="372"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -8132,22 +8132,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="376" t="s">
+      <c r="B138" s="373" t="s">
         <v>353</v>
       </c>
-      <c r="C138" s="376"/>
-      <c r="D138" s="376"/>
-      <c r="E138" s="376"/>
-      <c r="F138" s="376"/>
+      <c r="C138" s="373"/>
+      <c r="D138" s="373"/>
+      <c r="E138" s="373"/>
+      <c r="F138" s="373"/>
     </row>
     <row r="139" spans="1:6">
-      <c r="B139" s="371" t="s">
+      <c r="B139" s="374" t="s">
         <v>476</v>
       </c>
-      <c r="C139" s="371"/>
-      <c r="D139" s="371"/>
-      <c r="E139" s="371"/>
-      <c r="F139" s="371"/>
+      <c r="C139" s="374"/>
+      <c r="D139" s="374"/>
+      <c r="E139" s="374"/>
+      <c r="F139" s="374"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -8480,13 +8480,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="377" t="s">
+      <c r="B179" s="375" t="s">
         <v>477</v>
       </c>
-      <c r="C179" s="371"/>
-      <c r="D179" s="371"/>
-      <c r="E179" s="371"/>
-      <c r="F179" s="371"/>
+      <c r="C179" s="374"/>
+      <c r="D179" s="374"/>
+      <c r="E179" s="374"/>
+      <c r="F179" s="374"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -8494,13 +8494,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="373" t="s">
+      <c r="B182" s="376" t="s">
         <v>362</v>
       </c>
-      <c r="C182" s="373"/>
-      <c r="D182" s="373"/>
-      <c r="E182" s="373"/>
-      <c r="F182" s="373"/>
+      <c r="C182" s="376"/>
+      <c r="D182" s="376"/>
+      <c r="E182" s="376"/>
+      <c r="F182" s="376"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -8537,22 +8537,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="374" t="s">
+      <c r="B191" s="371" t="s">
         <v>363</v>
       </c>
-      <c r="C191" s="374"/>
-      <c r="D191" s="374"/>
-      <c r="E191" s="374"/>
-      <c r="F191" s="374"/>
+      <c r="C191" s="371"/>
+      <c r="D191" s="371"/>
+      <c r="E191" s="371"/>
+      <c r="F191" s="371"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="374" t="s">
+      <c r="B192" s="371" t="s">
         <v>364</v>
       </c>
-      <c r="C192" s="374"/>
-      <c r="D192" s="374"/>
-      <c r="E192" s="374"/>
-      <c r="F192" s="374"/>
+      <c r="C192" s="371"/>
+      <c r="D192" s="371"/>
+      <c r="E192" s="371"/>
+      <c r="F192" s="371"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -8576,17 +8576,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -8603,6 +8592,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -16146,20 +16146,20 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>9.507042253521128E-2</v>
+        <v>9.2783505154639179E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>9.507042253521128E-2</v>
+        <v>9.2783505154639179E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>8.8732394366197204E-2</v>
+        <v>8.6597938144329908E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>0.13626760563380286</v>
+        <v>0.13298969072164951</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
@@ -17345,50 +17345,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>7.5513912091504432E-2</v>
+        <v>7.3697426233633179E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>8.8119391164224126E-2</v>
+        <v>8.5999680723847588E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>0.1212577669546807</v>
+        <v>0.11834091345405263</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>0.19665547396500579</v>
+        <v>0.1919249299177376</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>0.16158332045955989</v>
+        <v>0.15769643646225087</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>5.7967745648236403E-2</v>
+        <v>5.6573332522677447E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>7.3589215330696386E-2</v>
+        <v>7.181902802033599E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>6.5521367552337825E-2</v>
+        <v>6.3945252181663026E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>6.2230183631369368E-2</v>
+        <v>6.0733237633363912E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>1.1015983906951039E-2</v>
+        <v>1.0750994603347403E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>4.7720991085399419E-3</v>
+        <v>4.657306346478843E-3</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -17402,43 +17402,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12552886430798402</v>
+        <v>0.12250926963390878</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15913945590605055</v>
+        <v>0.15531135902858542</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.2288014656426556</v>
+        <v>0.22329765031791815</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.21169583011813992</v>
+        <v>0.20660349056203345</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.211588953135783E-2</v>
+        <v>8.0140593219606954E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.1345276930016461E-2</v>
+        <v>7.9388517691150073E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.9670636567758454E-2</v>
+        <v>7.7754160774032299E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.1790893245798413E-2</v>
+        <v>7.9823414714112528E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.6792825485866014E-3</v>
+        <v>4.5667224872803936E-3</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-4.9207646790464292E-2</v>
+        <v>-4.8023957692411877E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -21388,7 +21388,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-2.84</v>
+        <v>-2.91</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -21628,7 +21628,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>2.84</v>
+        <v>2.91</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>2.84</v>
+        <v>2.91</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -22239,7 +22239,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.24743461613512951</v>
+        <v>0.23658707196826612</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/0639.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0639.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E56B9A1-D38A-46EF-87D3-355AEE47FE59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E58E32A-61A2-4A4D-B5CF-4E7797925EF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1837" yWindow="1837" windowWidth="12691" windowHeight="7643" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="投资主题" sheetId="12" r:id="rId1"/>
@@ -4759,6 +4759,15 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4768,16 +4777,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="C12" s="366">
         <f>Market_Price</f>
-        <v>2.91</v>
+        <v>2.94</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C14" s="35">
         <f>投资主题!C12*Common_Shares/1000000</f>
-        <v>14815.001390700001</v>
+        <v>14967.7333638</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",投资主题!D12*Common_Shares/1000000)</f>
@@ -5346,13 +5346,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="374" t="s">
+      <c r="B18" s="371" t="s">
         <v>489</v>
       </c>
-      <c r="C18" s="374"/>
-      <c r="D18" s="374"/>
-      <c r="E18" s="374"/>
-      <c r="F18" s="374"/>
+      <c r="C18" s="371"/>
+      <c r="D18" s="371"/>
+      <c r="E18" s="371"/>
+      <c r="F18" s="371"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -5443,7 +5443,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.23658707196826612</v>
+        <v>0.23204925986510649</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -5565,22 +5565,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="374" t="s">
+      <c r="B36" s="371" t="s">
         <v>492</v>
       </c>
-      <c r="C36" s="374"/>
-      <c r="D36" s="374"/>
-      <c r="E36" s="374"/>
-      <c r="F36" s="374"/>
+      <c r="C36" s="371"/>
+      <c r="D36" s="371"/>
+      <c r="E36" s="371"/>
+      <c r="F36" s="371"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="377" t="s">
+      <c r="B37" s="372" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="377"/>
-      <c r="D37" s="377"/>
-      <c r="E37" s="377"/>
-      <c r="F37" s="377"/>
+      <c r="C37" s="372"/>
+      <c r="D37" s="372"/>
+      <c r="E37" s="372"/>
+      <c r="F37" s="372"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -5770,10 +5770,10 @@
       <c r="B61" s="370" t="s">
         <v>499</v>
       </c>
-      <c r="C61" s="376"/>
-      <c r="D61" s="376"/>
-      <c r="E61" s="376"/>
-      <c r="F61" s="376"/>
+      <c r="C61" s="373"/>
+      <c r="D61" s="373"/>
+      <c r="E61" s="373"/>
+      <c r="F61" s="373"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -5789,22 +5789,22 @@
       </c>
     </row>
     <row r="64" spans="2:6">
-      <c r="B64" s="374" t="s">
+      <c r="B64" s="371" t="s">
         <v>500</v>
       </c>
-      <c r="C64" s="374"/>
-      <c r="D64" s="374"/>
-      <c r="E64" s="374"/>
-      <c r="F64" s="374"/>
+      <c r="C64" s="371"/>
+      <c r="D64" s="371"/>
+      <c r="E64" s="371"/>
+      <c r="F64" s="371"/>
     </row>
     <row r="65" spans="1:6">
-      <c r="B65" s="374" t="s">
+      <c r="B65" s="371" t="s">
         <v>501</v>
       </c>
-      <c r="C65" s="374"/>
-      <c r="D65" s="374"/>
-      <c r="E65" s="374"/>
-      <c r="F65" s="374"/>
+      <c r="C65" s="371"/>
+      <c r="D65" s="371"/>
+      <c r="E65" s="371"/>
+      <c r="F65" s="371"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -5838,7 +5838,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>7.3697426233633179E-2</v>
+        <v>7.2945411680228764E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -5848,7 +5848,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>9.2783505154639179E-2</v>
+        <v>9.1836734693877556E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>503</v>
@@ -5939,22 +5939,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="374" t="s">
+      <c r="B80" s="371" t="s">
         <v>506</v>
       </c>
-      <c r="C80" s="374"/>
-      <c r="D80" s="374"/>
-      <c r="E80" s="374"/>
-      <c r="F80" s="374"/>
+      <c r="C80" s="371"/>
+      <c r="D80" s="371"/>
+      <c r="E80" s="371"/>
+      <c r="F80" s="371"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="377" t="s">
+      <c r="B81" s="372" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="377"/>
-      <c r="D81" s="377"/>
-      <c r="E81" s="377"/>
-      <c r="F81" s="377"/>
+      <c r="C81" s="372"/>
+      <c r="D81" s="372"/>
+      <c r="E81" s="372"/>
+      <c r="F81" s="372"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5998,22 +5998,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6">
-      <c r="B89" s="374" t="s">
+      <c r="B89" s="371" t="s">
         <v>507</v>
       </c>
-      <c r="C89" s="374"/>
-      <c r="D89" s="374"/>
-      <c r="E89" s="374"/>
-      <c r="F89" s="374"/>
+      <c r="C89" s="371"/>
+      <c r="D89" s="371"/>
+      <c r="E89" s="371"/>
+      <c r="F89" s="371"/>
     </row>
     <row r="90" spans="1:6">
-      <c r="B90" s="374" t="s">
+      <c r="B90" s="371" t="s">
         <v>508</v>
       </c>
-      <c r="C90" s="374"/>
-      <c r="D90" s="374"/>
-      <c r="E90" s="374"/>
-      <c r="F90" s="374"/>
+      <c r="C90" s="371"/>
+      <c r="D90" s="371"/>
+      <c r="E90" s="371"/>
+      <c r="F90" s="371"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -6050,13 +6050,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="374" t="s">
+      <c r="B97" s="371" t="s">
         <v>510</v>
       </c>
-      <c r="C97" s="374"/>
-      <c r="D97" s="374"/>
-      <c r="E97" s="374"/>
-      <c r="F97" s="374"/>
+      <c r="C97" s="371"/>
+      <c r="D97" s="371"/>
+      <c r="E97" s="371"/>
+      <c r="F97" s="371"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -6069,13 +6069,13 @@
       </c>
     </row>
     <row r="101" spans="2:6">
-      <c r="B101" s="374" t="s">
+      <c r="B101" s="371" t="s">
         <v>511</v>
       </c>
-      <c r="C101" s="374"/>
-      <c r="D101" s="374"/>
-      <c r="E101" s="374"/>
-      <c r="F101" s="374"/>
+      <c r="C101" s="371"/>
+      <c r="D101" s="371"/>
+      <c r="E101" s="371"/>
+      <c r="F101" s="371"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -6197,13 +6197,13 @@
       </c>
     </row>
     <row r="116" spans="1:6">
-      <c r="B116" s="374" t="s">
+      <c r="B116" s="371" t="s">
         <v>516</v>
       </c>
-      <c r="C116" s="374"/>
-      <c r="D116" s="374"/>
-      <c r="E116" s="374"/>
-      <c r="F116" s="374"/>
+      <c r="C116" s="371"/>
+      <c r="D116" s="371"/>
+      <c r="E116" s="371"/>
+      <c r="F116" s="371"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -6391,13 +6391,13 @@
       </c>
     </row>
     <row r="134" spans="1:6">
-      <c r="B134" s="372" t="s">
+      <c r="B134" s="375" t="s">
         <v>524</v>
       </c>
-      <c r="C134" s="372"/>
-      <c r="D134" s="372"/>
-      <c r="E134" s="372"/>
-      <c r="F134" s="372"/>
+      <c r="C134" s="375"/>
+      <c r="D134" s="375"/>
+      <c r="E134" s="375"/>
+      <c r="F134" s="375"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -6410,22 +6410,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="373" t="s">
+      <c r="B138" s="376" t="s">
         <v>526</v>
       </c>
-      <c r="C138" s="373"/>
-      <c r="D138" s="373"/>
-      <c r="E138" s="373"/>
-      <c r="F138" s="373"/>
+      <c r="C138" s="376"/>
+      <c r="D138" s="376"/>
+      <c r="E138" s="376"/>
+      <c r="F138" s="376"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="374" t="s">
+      <c r="B139" s="371" t="s">
         <v>527</v>
       </c>
-      <c r="C139" s="374"/>
-      <c r="D139" s="374"/>
-      <c r="E139" s="374"/>
-      <c r="F139" s="374"/>
+      <c r="C139" s="371"/>
+      <c r="D139" s="371"/>
+      <c r="E139" s="371"/>
+      <c r="F139" s="371"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -6758,13 +6758,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="375" t="s">
+      <c r="B179" s="377" t="s">
         <v>534</v>
       </c>
-      <c r="C179" s="374"/>
-      <c r="D179" s="374"/>
-      <c r="E179" s="374"/>
-      <c r="F179" s="374"/>
+      <c r="C179" s="371"/>
+      <c r="D179" s="371"/>
+      <c r="E179" s="371"/>
+      <c r="F179" s="371"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -6772,13 +6772,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="376" t="s">
+      <c r="B182" s="373" t="s">
         <v>536</v>
       </c>
-      <c r="C182" s="376"/>
-      <c r="D182" s="376"/>
-      <c r="E182" s="376"/>
-      <c r="F182" s="376"/>
+      <c r="C182" s="373"/>
+      <c r="D182" s="373"/>
+      <c r="E182" s="373"/>
+      <c r="F182" s="373"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -6815,22 +6815,22 @@
       </c>
     </row>
     <row r="191" spans="1:6">
-      <c r="B191" s="371" t="s">
+      <c r="B191" s="374" t="s">
         <v>543</v>
       </c>
-      <c r="C191" s="371"/>
-      <c r="D191" s="371"/>
-      <c r="E191" s="371"/>
-      <c r="F191" s="371"/>
+      <c r="C191" s="374"/>
+      <c r="D191" s="374"/>
+      <c r="E191" s="374"/>
+      <c r="F191" s="374"/>
     </row>
     <row r="192" spans="1:6">
-      <c r="B192" s="371" t="s">
+      <c r="B192" s="374" t="s">
         <v>544</v>
       </c>
-      <c r="C192" s="371"/>
-      <c r="D192" s="371"/>
-      <c r="E192" s="371"/>
-      <c r="F192" s="371"/>
+      <c r="C192" s="374"/>
+      <c r="D192" s="374"/>
+      <c r="E192" s="374"/>
+      <c r="F192" s="374"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -6854,12 +6854,15 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B47:F47"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B138:F138"/>
+    <mergeCell ref="B139:F139"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B182:F182"/>
     <mergeCell ref="B116:F116"/>
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B58:F58"/>
@@ -6872,15 +6875,12 @@
     <mergeCell ref="B90:F90"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B138:F138"/>
-    <mergeCell ref="B139:F139"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B43:F43"/>
   </mergeCells>
   <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">
@@ -7023,7 +7023,7 @@
         <v>463</v>
       </c>
       <c r="C12" s="50">
-        <v>2.91</v>
+        <v>2.94</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -7044,7 +7044,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>14815.001390700001</v>
+        <v>14967.7333638</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -7081,13 +7081,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="374" t="s">
+      <c r="B18" s="371" t="s">
         <v>468</v>
       </c>
-      <c r="C18" s="374"/>
-      <c r="D18" s="374"/>
-      <c r="E18" s="374"/>
-      <c r="F18" s="374"/>
+      <c r="C18" s="371"/>
+      <c r="D18" s="371"/>
+      <c r="E18" s="371"/>
+      <c r="F18" s="371"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -7170,7 +7170,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.23658707196826612</v>
+        <v>0.23204925986510649</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -7287,22 +7287,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6">
-      <c r="B36" s="374" t="s">
+      <c r="B36" s="371" t="s">
         <v>469</v>
       </c>
-      <c r="C36" s="374"/>
-      <c r="D36" s="374"/>
-      <c r="E36" s="374"/>
-      <c r="F36" s="374"/>
+      <c r="C36" s="371"/>
+      <c r="D36" s="371"/>
+      <c r="E36" s="371"/>
+      <c r="F36" s="371"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="377" t="s">
+      <c r="B37" s="372" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="377"/>
-      <c r="D37" s="377"/>
-      <c r="E37" s="377"/>
-      <c r="F37" s="377"/>
+      <c r="C37" s="372"/>
+      <c r="D37" s="372"/>
+      <c r="E37" s="372"/>
+      <c r="F37" s="372"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -7492,10 +7492,10 @@
       <c r="B61" s="370" t="s">
         <v>329</v>
       </c>
-      <c r="C61" s="376"/>
-      <c r="D61" s="376"/>
-      <c r="E61" s="376"/>
-      <c r="F61" s="376"/>
+      <c r="C61" s="373"/>
+      <c r="D61" s="373"/>
+      <c r="E61" s="373"/>
+      <c r="F61" s="373"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -7511,22 +7511,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="374" t="s">
+      <c r="B64" s="371" t="s">
         <v>334</v>
       </c>
-      <c r="C64" s="374"/>
-      <c r="D64" s="374"/>
-      <c r="E64" s="374"/>
-      <c r="F64" s="374"/>
+      <c r="C64" s="371"/>
+      <c r="D64" s="371"/>
+      <c r="E64" s="371"/>
+      <c r="F64" s="371"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="374" t="s">
+      <c r="B65" s="371" t="s">
         <v>348</v>
       </c>
-      <c r="C65" s="374"/>
-      <c r="D65" s="374"/>
-      <c r="E65" s="374"/>
-      <c r="F65" s="374"/>
+      <c r="C65" s="371"/>
+      <c r="D65" s="371"/>
+      <c r="E65" s="371"/>
+      <c r="F65" s="371"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -7560,7 +7560,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>7.3697426233633179E-2</v>
+        <v>7.2945411680228764E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -7570,7 +7570,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>9.2783505154639179E-2</v>
+        <v>9.1836734693877556E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>424</v>
@@ -7661,22 +7661,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="374" t="s">
+      <c r="B80" s="371" t="s">
         <v>471</v>
       </c>
-      <c r="C80" s="374"/>
-      <c r="D80" s="374"/>
-      <c r="E80" s="374"/>
-      <c r="F80" s="374"/>
+      <c r="C80" s="371"/>
+      <c r="D80" s="371"/>
+      <c r="E80" s="371"/>
+      <c r="F80" s="371"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="377" t="s">
+      <c r="B81" s="372" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="377"/>
-      <c r="D81" s="377"/>
-      <c r="E81" s="377"/>
-      <c r="F81" s="377"/>
+      <c r="C81" s="372"/>
+      <c r="D81" s="372"/>
+      <c r="E81" s="372"/>
+      <c r="F81" s="372"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -7720,22 +7720,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="374" t="s">
+      <c r="B89" s="371" t="s">
         <v>349</v>
       </c>
-      <c r="C89" s="374"/>
-      <c r="D89" s="374"/>
-      <c r="E89" s="374"/>
-      <c r="F89" s="374"/>
+      <c r="C89" s="371"/>
+      <c r="D89" s="371"/>
+      <c r="E89" s="371"/>
+      <c r="F89" s="371"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="374" t="s">
+      <c r="B90" s="371" t="s">
         <v>350</v>
       </c>
-      <c r="C90" s="374"/>
-      <c r="D90" s="374"/>
-      <c r="E90" s="374"/>
-      <c r="F90" s="374"/>
+      <c r="C90" s="371"/>
+      <c r="D90" s="371"/>
+      <c r="E90" s="371"/>
+      <c r="F90" s="371"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -7772,13 +7772,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="374" t="s">
+      <c r="B97" s="371" t="s">
         <v>351</v>
       </c>
-      <c r="C97" s="374"/>
-      <c r="D97" s="374"/>
-      <c r="E97" s="374"/>
-      <c r="F97" s="374"/>
+      <c r="C97" s="371"/>
+      <c r="D97" s="371"/>
+      <c r="E97" s="371"/>
+      <c r="F97" s="371"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -7791,13 +7791,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="374" t="s">
+      <c r="B101" s="371" t="s">
         <v>335</v>
       </c>
-      <c r="C101" s="374"/>
-      <c r="D101" s="374"/>
-      <c r="E101" s="374"/>
-      <c r="F101" s="374"/>
+      <c r="C101" s="371"/>
+      <c r="D101" s="371"/>
+      <c r="E101" s="371"/>
+      <c r="F101" s="371"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -7919,13 +7919,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="374" t="s">
+      <c r="B116" s="371" t="s">
         <v>352</v>
       </c>
-      <c r="C116" s="374"/>
-      <c r="D116" s="374"/>
-      <c r="E116" s="374"/>
-      <c r="F116" s="374"/>
+      <c r="C116" s="371"/>
+      <c r="D116" s="371"/>
+      <c r="E116" s="371"/>
+      <c r="F116" s="371"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -8113,13 +8113,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="372" t="s">
+      <c r="B134" s="375" t="s">
         <v>474</v>
       </c>
-      <c r="C134" s="372"/>
-      <c r="D134" s="372"/>
-      <c r="E134" s="372"/>
-      <c r="F134" s="372"/>
+      <c r="C134" s="375"/>
+      <c r="D134" s="375"/>
+      <c r="E134" s="375"/>
+      <c r="F134" s="375"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -8132,22 +8132,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="373" t="s">
+      <c r="B138" s="376" t="s">
         <v>353</v>
       </c>
-      <c r="C138" s="373"/>
-      <c r="D138" s="373"/>
-      <c r="E138" s="373"/>
-      <c r="F138" s="373"/>
+      <c r="C138" s="376"/>
+      <c r="D138" s="376"/>
+      <c r="E138" s="376"/>
+      <c r="F138" s="376"/>
     </row>
     <row r="139" spans="1:6">
-      <c r="B139" s="374" t="s">
+      <c r="B139" s="371" t="s">
         <v>476</v>
       </c>
-      <c r="C139" s="374"/>
-      <c r="D139" s="374"/>
-      <c r="E139" s="374"/>
-      <c r="F139" s="374"/>
+      <c r="C139" s="371"/>
+      <c r="D139" s="371"/>
+      <c r="E139" s="371"/>
+      <c r="F139" s="371"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -8480,13 +8480,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="375" t="s">
+      <c r="B179" s="377" t="s">
         <v>477</v>
       </c>
-      <c r="C179" s="374"/>
-      <c r="D179" s="374"/>
-      <c r="E179" s="374"/>
-      <c r="F179" s="374"/>
+      <c r="C179" s="371"/>
+      <c r="D179" s="371"/>
+      <c r="E179" s="371"/>
+      <c r="F179" s="371"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -8494,13 +8494,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="376" t="s">
+      <c r="B182" s="373" t="s">
         <v>362</v>
       </c>
-      <c r="C182" s="376"/>
-      <c r="D182" s="376"/>
-      <c r="E182" s="376"/>
-      <c r="F182" s="376"/>
+      <c r="C182" s="373"/>
+      <c r="D182" s="373"/>
+      <c r="E182" s="373"/>
+      <c r="F182" s="373"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -8537,22 +8537,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="371" t="s">
+      <c r="B191" s="374" t="s">
         <v>363</v>
       </c>
-      <c r="C191" s="371"/>
-      <c r="D191" s="371"/>
-      <c r="E191" s="371"/>
-      <c r="F191" s="371"/>
+      <c r="C191" s="374"/>
+      <c r="D191" s="374"/>
+      <c r="E191" s="374"/>
+      <c r="F191" s="374"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="371" t="s">
+      <c r="B192" s="374" t="s">
         <v>364</v>
       </c>
-      <c r="C192" s="371"/>
-      <c r="D192" s="371"/>
-      <c r="E192" s="371"/>
-      <c r="F192" s="371"/>
+      <c r="C192" s="374"/>
+      <c r="D192" s="374"/>
+      <c r="E192" s="374"/>
+      <c r="F192" s="374"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -8576,6 +8576,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -8592,17 +8603,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -16146,20 +16146,20 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>9.2783505154639179E-2</v>
+        <v>9.1836734693877556E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>9.2783505154639179E-2</v>
+        <v>9.1836734693877556E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>8.6597938144329908E-2</v>
+        <v>8.5714285714285729E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>0.13298969072164951</v>
+        <v>0.13163265306122451</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
@@ -17345,50 +17345,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>7.3697426233633179E-2</v>
+        <v>7.2945411680228764E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>8.5999680723847588E-2</v>
+        <v>8.5122132961359356E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>0.11834091345405263</v>
+        <v>0.11713335311268476</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>0.1919249299177376</v>
+        <v>0.18996651226551578</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>0.15769643646225087</v>
+        <v>0.1560872891514116</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>5.6573332522677447E-2</v>
+        <v>5.5996053619384825E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>7.181902802033599E-2</v>
+        <v>7.1086180795638693E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>6.3945252181663026E-2</v>
+        <v>6.3292749608380758E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>6.0733237633363912E-2</v>
+        <v>6.0113510718737759E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>1.0750994603347403E-2</v>
+        <v>1.0641290576782635E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>4.657306346478843E-3</v>
+        <v>4.6097828123311006E-3</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -17402,43 +17402,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12250926963390878</v>
+        <v>0.12125917504580769</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15531135902858542</v>
+        <v>0.15372654924257945</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.22329765031791815</v>
+        <v>0.22101910286569454</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.20660349056203345</v>
+        <v>0.20449529167874742</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.0140593219606954E-2</v>
+        <v>7.9322832064304849E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.9388517691150073E-2</v>
+        <v>7.8578430775934266E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.7754160774032299E-2</v>
+        <v>7.6960750970215652E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.9823414714112528E-2</v>
+        <v>7.9008890074172611E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.5667224872803936E-3</v>
+        <v>4.520123278226513E-3</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-4.8023957692411877E-2</v>
+        <v>-4.7533917307795437E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -21388,7 +21388,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-2.91</v>
+        <v>-2.94</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -21628,7 +21628,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>2.91</v>
+        <v>2.94</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>2.91</v>
+        <v>2.94</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -22239,7 +22239,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.23658707196826612</v>
+        <v>0.23204925986510649</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/0639.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0639.HK_Valuation.xlsx
@@ -8,27 +8,27 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E58E32A-61A2-4A4D-B5CF-4E7797925EF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55A3B1C7-5A34-4A72-9935-C58B1AF26FF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="投资主题" sheetId="12" r:id="rId1"/>
-    <sheet name="Thesis" sheetId="6" r:id="rId2"/>
-    <sheet name="Data" sheetId="4" r:id="rId3"/>
-    <sheet name="BS" sheetId="3" r:id="rId4"/>
-    <sheet name="Normalized_FCF" sheetId="2" r:id="rId5"/>
-    <sheet name="DCF" sheetId="8" r:id="rId6"/>
-    <sheet name="DDM" sheetId="10" r:id="rId7"/>
-    <sheet name="Scenarios" sheetId="9" r:id="rId8"/>
+    <sheet name="Thesis" sheetId="6" r:id="rId1"/>
+    <sheet name="Data" sheetId="4" r:id="rId2"/>
+    <sheet name="BS" sheetId="3" r:id="rId3"/>
+    <sheet name="Normalized_FCF" sheetId="2" r:id="rId4"/>
+    <sheet name="DCF" sheetId="8" r:id="rId5"/>
+    <sheet name="DDM" sheetId="10" r:id="rId6"/>
+    <sheet name="Scenarios" sheetId="9" r:id="rId7"/>
+    <sheet name="投资主题" sheetId="12" r:id="rId8"/>
     <sheet name="Breakdown" sheetId="13" r:id="rId9"/>
   </sheets>
   <externalReferences>
     <externalReference r:id="rId10"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">DCF!$B$73:$H$73</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">DDM!$B$68:$H$68</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">DCF!$B$73:$H$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">DDM!$B$68:$H$68</definedName>
     <definedName name="Common_Shares" localSheetId="8">[1]Thesis!$C$6</definedName>
     <definedName name="Common_Shares">Thesis!$C$6</definedName>
     <definedName name="dividend_tax_rate" localSheetId="8">[1]Normalized_FCF!$C$93</definedName>
@@ -4751,31 +4751,26 @@
     <xf numFmtId="4" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="1" xfId="2"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4792,10 +4787,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="1" xfId="2"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="2" xr:uid="{C04B486E-6FC7-49BB-B6BA-011B4CED336A}"/>
+    <cellStyle name="常规 2" xfId="2" xr:uid="{20E05687-AD80-4962-8416-EB9A18D9162C}"/>
     <cellStyle name="常规 2 2" xfId="1" xr:uid="{A35F4541-DCCE-4554-A311-39480A36979A}"/>
   </cellStyles>
   <dxfs count="8">
@@ -4889,6 +4889,7 @@
       <xxl21:absoluteUrl r:id="rId2"/>
     </xxl21:alternateUrls>
     <sheetNames>
+      <sheetName val="投资主题"/>
       <sheetName val="Thesis"/>
       <sheetName val="Data"/>
       <sheetName val="BS"/>
@@ -4899,7 +4900,8 @@
       <sheetName val="Breakdown"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0">
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
         <row r="6">
           <cell r="C6">
             <v>5091065770</v>
@@ -4907,7 +4909,7 @@
         </row>
         <row r="12">
           <cell r="C12">
-            <v>2.62</v>
+            <v>2.94</v>
           </cell>
         </row>
         <row r="13">
@@ -4941,25 +4943,25 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1">
+      <sheetData sheetId="2">
         <row r="3">
           <cell r="C3">
             <v>1000</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3">
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4">
         <row r="93">
           <cell r="C93">
             <v>0.1</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="4"/>
       <sheetData sheetId="5"/>
       <sheetData sheetId="6"/>
       <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -5162,1749 +5164,6 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA287911-AF8F-41DE-9E8E-72556F041FFB}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:J197"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
-  <cols>
-    <col min="1" max="1" width="2.73046875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="32.73046875" style="1" customWidth="1"/>
-    <col min="3" max="4" width="25.73046875" style="1" customWidth="1"/>
-    <col min="5" max="6" width="15.73046875" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10">
-      <c r="B1" s="3" t="s">
-        <v>437</v>
-      </c>
-      <c r="C1" s="33">
-        <f>Thesis!C1</f>
-        <v>45807</v>
-      </c>
-      <c r="D1" s="358" t="str">
-        <f>Thesis!D1</f>
-        <v>INT</v>
-      </c>
-      <c r="E1" s="292" t="s">
-        <v>344</v>
-      </c>
-      <c r="F1" s="307" t="str">
-        <f>Thesis!F1</f>
-        <v>Y</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="13.9">
-      <c r="A2" s="222" t="s">
-        <v>438</v>
-      </c>
-      <c r="B2" s="36"/>
-      <c r="C2" s="36"/>
-      <c r="D2" s="36"/>
-      <c r="E2" s="36"/>
-      <c r="F2" s="36"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
-      <c r="I2" s="22"/>
-      <c r="J2" s="22"/>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="B4" s="45" t="s">
-        <v>439</v>
-      </c>
-      <c r="C4" s="46"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-    </row>
-    <row r="5" spans="1:10" ht="12.4">
-      <c r="B5" s="4" t="s">
-        <v>479</v>
-      </c>
-      <c r="C5" s="359" t="str">
-        <f>Thesis!C5</f>
-        <v>首钢资源</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="B6" s="4" t="s">
-        <v>480</v>
-      </c>
-      <c r="C6" s="34">
-        <f>Common_Shares</f>
-        <v>5091065770</v>
-      </c>
-      <c r="E6" s="48"/>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="B7" s="2" t="s">
-        <v>481</v>
-      </c>
-      <c r="C7" s="360">
-        <f>Thesis!C7</f>
-        <v>6</v>
-      </c>
-      <c r="D7" s="48"/>
-      <c r="E7" s="48"/>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="B8" s="1" t="s">
-        <v>482</v>
-      </c>
-      <c r="C8" s="33">
-        <f>EOMONTH(EDATE(BS!C1,C7+2),0)</f>
-        <v>45900</v>
-      </c>
-      <c r="E8" s="48"/>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="E9" s="34"/>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="B10" s="45" t="s">
-        <v>440</v>
-      </c>
-      <c r="C10" s="46"/>
-      <c r="E10" s="34"/>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="B11" s="1" t="s">
-        <v>483</v>
-      </c>
-      <c r="C11" s="365" t="str">
-        <f>Thesis!C11</f>
-        <v>0639.HK</v>
-      </c>
-      <c r="D11" s="49"/>
-      <c r="E11" s="34"/>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="B12" s="4" t="s">
-        <v>484</v>
-      </c>
-      <c r="C12" s="366">
-        <f>Market_Price</f>
-        <v>2.94</v>
-      </c>
-      <c r="D12" s="50"/>
-      <c r="E12" s="48"/>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="B13" s="1" t="s">
-        <v>485</v>
-      </c>
-      <c r="C13" s="32" t="str">
-        <f>Market_currency</f>
-        <v>HKD</v>
-      </c>
-      <c r="D13" s="48"/>
-      <c r="E13" s="5"/>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="B14" s="4" t="s">
-        <v>486</v>
-      </c>
-      <c r="C14" s="35">
-        <f>投资主题!C12*Common_Shares/1000000</f>
-        <v>14967.7333638</v>
-      </c>
-      <c r="D14" s="35" t="str">
-        <f>IF(D11="","",投资主题!D12*Common_Shares/1000000)</f>
-        <v/>
-      </c>
-      <c r="E14" s="5"/>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="B15" s="4" t="s">
-        <v>487</v>
-      </c>
-      <c r="C15" s="32" t="str">
-        <f>IF(C25=C13,C13,C25&amp;"/"&amp;C13)</f>
-        <v>HKD</v>
-      </c>
-      <c r="D15" s="32" t="str">
-        <f>IF(D11="","",IF(C25=D13,D13,C25&amp;"/"&amp;D13))</f>
-        <v/>
-      </c>
-      <c r="E15" s="5"/>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="B16" s="4" t="s">
-        <v>488</v>
-      </c>
-      <c r="C16" s="366">
-        <f>Exchange_Rate</f>
-        <v>1</v>
-      </c>
-      <c r="D16" s="50"/>
-      <c r="E16" s="5"/>
-    </row>
-    <row r="17" spans="2:6">
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-    </row>
-    <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="371" t="s">
-        <v>489</v>
-      </c>
-      <c r="C18" s="371"/>
-      <c r="D18" s="371"/>
-      <c r="E18" s="371"/>
-      <c r="F18" s="371"/>
-    </row>
-    <row r="20" spans="2:6">
-      <c r="B20" s="45" t="s">
-        <v>490</v>
-      </c>
-      <c r="C20" s="46"/>
-      <c r="D20" s="5"/>
-    </row>
-    <row r="21" spans="2:6">
-      <c r="B21" s="2" t="s">
-        <v>441</v>
-      </c>
-      <c r="C21" s="32" t="str">
-        <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
-        <v xml:space="preserve">Low Growth </v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="E21" s="363" t="str">
-        <f>valuation_method</f>
-        <v>DCF</v>
-      </c>
-    </row>
-    <row r="22" spans="2:6">
-      <c r="B22" s="2" t="s">
-        <v>442</v>
-      </c>
-      <c r="C22" s="32" t="str">
-        <f>Thesis!C22</f>
-        <v>MAT_01</v>
-      </c>
-      <c r="D22" s="1" t="str">
-        <f>IF(valuation_method="DDM","终值贴现率","")</f>
-        <v/>
-      </c>
-      <c r="E22" s="364">
-        <f>Thesis!E22</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="2:6">
-      <c r="B23" s="1" t="s">
-        <v>443</v>
-      </c>
-      <c r="C23" s="253" t="str">
-        <f>Thesis!C23</f>
-        <v>N</v>
-      </c>
-    </row>
-    <row r="24" spans="2:6">
-      <c r="B24" s="1" t="s">
-        <v>444</v>
-      </c>
-      <c r="C24" s="253" t="str">
-        <f>Thesis!C24</f>
-        <v>N</v>
-      </c>
-    </row>
-    <row r="25" spans="2:6">
-      <c r="B25" s="4" t="s">
-        <v>445</v>
-      </c>
-      <c r="C25" s="32" t="str">
-        <f>Reporting_currency</f>
-        <v>HKD</v>
-      </c>
-      <c r="D25" s="32" t="str">
-        <f>IF(D11="","",Market_currency&amp;"/"&amp;D13&amp;":")</f>
-        <v/>
-      </c>
-      <c r="E25" s="299" t="str">
-        <f>IF(D11="","",1/Exchange_Rate*D16)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" spans="2:6">
-      <c r="B26" s="1" t="str">
-        <f>"预期股权价值 ("&amp;C13&amp;") :"</f>
-        <v>预期股权价值 (HKD) :</v>
-      </c>
-      <c r="C26" s="304">
-        <f>C132</f>
-        <v>4.4858408799140586</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>446</v>
-      </c>
-      <c r="E26" s="301">
-        <f ca="1">Scenarios!C87</f>
-        <v>0.23204925986510649</v>
-      </c>
-    </row>
-    <row r="27" spans="2:6">
-      <c r="D27" s="5"/>
-      <c r="E27" s="5"/>
-    </row>
-    <row r="28" spans="2:6">
-      <c r="B28" s="45" t="s">
-        <v>448</v>
-      </c>
-      <c r="C28" s="309" t="str">
-        <f>C145&amp;" ("&amp;Market_currency&amp;")"</f>
-        <v>0639.HK (HKD)</v>
-      </c>
-      <c r="D28" s="309" t="str">
-        <f>IF(D11="","",D145&amp;" ("&amp;D13&amp;")")</f>
-        <v/>
-      </c>
-      <c r="E28" s="305" t="s">
-        <v>453</v>
-      </c>
-      <c r="F28" s="361">
-        <f>Thesis!F28</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="29" spans="2:6">
-      <c r="B29" s="1" t="s">
-        <v>449</v>
-      </c>
-      <c r="C29" s="310">
-        <f>C149</f>
-        <v>2.2811221378505544</v>
-      </c>
-      <c r="D29" s="310" t="str">
-        <f>D149</f>
-        <v/>
-      </c>
-      <c r="E29" s="306" t="s">
-        <v>455</v>
-      </c>
-      <c r="F29" s="362">
-        <f>Thesis!F29</f>
-        <v>0.35</v>
-      </c>
-    </row>
-    <row r="30" spans="2:6">
-      <c r="B30" s="1" t="s">
-        <v>450</v>
-      </c>
-      <c r="C30" s="311">
-        <f>C157</f>
-        <v>2.823790530515998</v>
-      </c>
-      <c r="D30" s="311" t="str">
-        <f>D157</f>
-        <v/>
-      </c>
-      <c r="E30" s="307" t="s">
-        <v>454</v>
-      </c>
-      <c r="F30" s="224">
-        <f>Thesis!F30</f>
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="31" spans="2:6">
-      <c r="B31" s="1" t="s">
-        <v>451</v>
-      </c>
-      <c r="C31" s="311">
-        <f>C165</f>
-        <v>4.3130669791905083</v>
-      </c>
-      <c r="D31" s="311" t="str">
-        <f>D165</f>
-        <v/>
-      </c>
-      <c r="E31" s="307" t="s">
-        <v>491</v>
-      </c>
-      <c r="F31" s="224">
-        <f>Thesis!F31</f>
-        <v>7.4999999999999997E-2</v>
-      </c>
-    </row>
-    <row r="32" spans="2:6">
-      <c r="B32" s="1" t="s">
-        <v>452</v>
-      </c>
-      <c r="C32" s="311">
-        <f>C173</f>
-        <v>3.8666759160925035</v>
-      </c>
-      <c r="D32" s="311" t="str">
-        <f>D173</f>
-        <v/>
-      </c>
-      <c r="E32" s="307" t="s">
-        <v>456</v>
-      </c>
-      <c r="F32" s="224">
-        <f>Thesis!F32</f>
-        <v>0.1174</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="D33" s="5"/>
-      <c r="E33" s="5"/>
-    </row>
-    <row r="34" spans="1:6" ht="13.9">
-      <c r="A34" s="222" t="s">
-        <v>457</v>
-      </c>
-      <c r="B34" s="36"/>
-      <c r="C34" s="36"/>
-      <c r="D34" s="36"/>
-      <c r="E34" s="36"/>
-      <c r="F34" s="36"/>
-    </row>
-    <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="371" t="s">
-        <v>492</v>
-      </c>
-      <c r="C36" s="371"/>
-      <c r="D36" s="371"/>
-      <c r="E36" s="371"/>
-      <c r="F36" s="371"/>
-    </row>
-    <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="372" t="s">
-        <v>330</v>
-      </c>
-      <c r="C37" s="372"/>
-      <c r="D37" s="372"/>
-      <c r="E37" s="372"/>
-      <c r="F37" s="372"/>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="B39" s="210" t="s">
-        <v>493</v>
-      </c>
-      <c r="C39" s="108">
-        <f>scaling_factor</f>
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="B40" s="370" t="s">
-        <v>494</v>
-      </c>
-      <c r="C40" s="370"/>
-      <c r="D40" s="370"/>
-      <c r="E40" s="370"/>
-      <c r="F40" s="370"/>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="B41" s="47" t="s">
-        <v>228</v>
-      </c>
-      <c r="C41" s="349">
-        <f>Normalized_FCF!C8</f>
-        <v>1880349.4511684938</v>
-      </c>
-      <c r="D41" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>HKD</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="B42" s="47"/>
-      <c r="C42" s="76"/>
-    </row>
-    <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="370" t="s">
-        <v>495</v>
-      </c>
-      <c r="C43" s="370"/>
-      <c r="D43" s="370"/>
-      <c r="E43" s="370"/>
-      <c r="F43" s="370"/>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="B44" s="47" t="s">
-        <v>230</v>
-      </c>
-      <c r="C44" s="349">
-        <f>Normalized_FCF!C9</f>
-        <v>0</v>
-      </c>
-      <c r="D44" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>HKD</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="B45" s="52" t="s">
-        <v>231</v>
-      </c>
-      <c r="C45" s="349">
-        <f>Normalized_FCF!C10</f>
-        <v>0</v>
-      </c>
-      <c r="D45" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>HKD</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
-      <c r="B47" s="370" t="s">
-        <v>496</v>
-      </c>
-      <c r="C47" s="370"/>
-      <c r="D47" s="370"/>
-      <c r="E47" s="370"/>
-      <c r="F47" s="370"/>
-    </row>
-    <row r="48" spans="1:6">
-      <c r="B48" s="47" t="s">
-        <v>233</v>
-      </c>
-      <c r="C48" s="349">
-        <f>Normalized_FCF!C11</f>
-        <v>0</v>
-      </c>
-      <c r="D48" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>HKD</v>
-      </c>
-    </row>
-    <row r="50" spans="2:6">
-      <c r="B50" s="370" t="s">
-        <v>497</v>
-      </c>
-      <c r="C50" s="370"/>
-      <c r="D50" s="370"/>
-      <c r="E50" s="370"/>
-      <c r="F50" s="370"/>
-    </row>
-    <row r="51" spans="2:6">
-      <c r="B51" s="47" t="s">
-        <v>331</v>
-      </c>
-      <c r="C51" s="350">
-        <f>Normalized_FCF!C48</f>
-        <v>20769.589399157529</v>
-      </c>
-      <c r="D51" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>HKD</v>
-      </c>
-      <c r="E51" s="286"/>
-      <c r="F51" s="286"/>
-    </row>
-    <row r="52" spans="2:6">
-      <c r="B52" s="47" t="s">
-        <v>332</v>
-      </c>
-      <c r="C52" s="350">
-        <f>Normalized_FCF!C47</f>
-        <v>-1746</v>
-      </c>
-      <c r="D52" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>HKD</v>
-      </c>
-      <c r="E52" s="286"/>
-      <c r="F52" s="286"/>
-    </row>
-    <row r="53" spans="2:6">
-      <c r="B53" s="47" t="s">
-        <v>234</v>
-      </c>
-      <c r="C53" s="349">
-        <f>Normalized_FCF!C12</f>
-        <v>19023.589399157529</v>
-      </c>
-      <c r="D53" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>HKD</v>
-      </c>
-    </row>
-    <row r="55" spans="2:6">
-      <c r="B55" s="1" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="56" spans="2:6">
-      <c r="B56" s="47" t="s">
-        <v>261</v>
-      </c>
-      <c r="C56" s="349">
-        <f>Normalized_FCF!C15</f>
-        <v>-332702.30828345218</v>
-      </c>
-      <c r="D56" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>HKD</v>
-      </c>
-    </row>
-    <row r="58" spans="2:6">
-      <c r="B58" s="370" t="s">
-        <v>237</v>
-      </c>
-      <c r="C58" s="370"/>
-      <c r="D58" s="370"/>
-      <c r="E58" s="370"/>
-      <c r="F58" s="370"/>
-    </row>
-    <row r="59" spans="2:6">
-      <c r="B59" s="47" t="s">
-        <v>235</v>
-      </c>
-      <c r="C59" s="349">
-        <f>Normalized_FCF!C14</f>
-        <v>-474843.26014191285</v>
-      </c>
-      <c r="D59" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>HKD</v>
-      </c>
-    </row>
-    <row r="61" spans="2:6">
-      <c r="B61" s="370" t="s">
-        <v>499</v>
-      </c>
-      <c r="C61" s="373"/>
-      <c r="D61" s="373"/>
-      <c r="E61" s="373"/>
-      <c r="F61" s="373"/>
-    </row>
-    <row r="62" spans="2:6">
-      <c r="B62" s="47" t="s">
-        <v>238</v>
-      </c>
-      <c r="C62" s="349">
-        <f>Normalized_FCF!C17</f>
-        <v>0</v>
-      </c>
-      <c r="D62" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>HKD</v>
-      </c>
-    </row>
-    <row r="64" spans="2:6">
-      <c r="B64" s="371" t="s">
-        <v>500</v>
-      </c>
-      <c r="C64" s="371"/>
-      <c r="D64" s="371"/>
-      <c r="E64" s="371"/>
-      <c r="F64" s="371"/>
-    </row>
-    <row r="65" spans="1:6">
-      <c r="B65" s="371" t="s">
-        <v>501</v>
-      </c>
-      <c r="C65" s="371"/>
-      <c r="D65" s="371"/>
-      <c r="E65" s="371"/>
-      <c r="F65" s="371"/>
-    </row>
-    <row r="67" spans="1:6">
-      <c r="B67" s="47" t="s">
-        <v>502</v>
-      </c>
-      <c r="C67" s="349">
-        <f>Normalized_FCF!G19</f>
-        <v>1274085.3895235579</v>
-      </c>
-      <c r="D67" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>HKD</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6">
-      <c r="B68" s="47" t="s">
-        <v>244</v>
-      </c>
-      <c r="C68" s="349">
-        <f>Normalized_FCF!C19</f>
-        <v>1091827.4721422864</v>
-      </c>
-      <c r="D68" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>HKD</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6">
-      <c r="B69" s="227" t="s">
-        <v>371</v>
-      </c>
-      <c r="C69" s="92">
-        <f>Normalized_FCF!C126</f>
-        <v>7.2945411680228764E-2</v>
-      </c>
-      <c r="F69" s="314"/>
-    </row>
-    <row r="70" spans="1:6">
-      <c r="B70" s="227" t="s">
-        <v>434</v>
-      </c>
-      <c r="C70" s="92">
-        <f>Normalized_FCF!C94</f>
-        <v>9.1836734693877556E-2</v>
-      </c>
-      <c r="E70" s="47" t="s">
-        <v>503</v>
-      </c>
-      <c r="F70" s="315">
-        <f>Normalized_FCF!C92</f>
-        <v>1.3988654526188369</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6">
-      <c r="B72" s="210" t="s">
-        <v>513</v>
-      </c>
-      <c r="C72" s="323" t="s">
-        <v>429</v>
-      </c>
-      <c r="D72" s="323" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6">
-      <c r="B73" s="47" t="s">
-        <v>428</v>
-      </c>
-      <c r="C73" s="92">
-        <f>Normalized_FCF!C121</f>
-        <v>0.10048924474005361</v>
-      </c>
-      <c r="D73" s="92">
-        <f>Normalized_FCF!G121</f>
-        <v>0.12199804433766272</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6">
-      <c r="B74" s="259" t="str">
-        <f>Normalized_FCF!B118</f>
-        <v>Pre-tax Profit/Sales</v>
-      </c>
-      <c r="C74" s="322">
-        <f>Normalized_FCF!C118</f>
-        <v>0.42143224397986156</v>
-      </c>
-      <c r="D74" s="322">
-        <f>Normalized_FCF!G118</f>
-        <v>0.45598504835348186</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6">
-      <c r="B75" s="259" t="str">
-        <f>Normalized_FCF!B119</f>
-        <v>Sales/Total Assets</v>
-      </c>
-      <c r="C75" s="324">
-        <f>Normalized_FCF!C119</f>
-        <v>0.19639123104483397</v>
-      </c>
-      <c r="D75" s="324">
-        <f>Normalized_FCF!G119</f>
-        <v>0.22035988512352028</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6">
-      <c r="B76" s="259" t="str">
-        <f>Normalized_FCF!B120</f>
-        <v>Total Assets/Equity</v>
-      </c>
-      <c r="C76" s="324">
-        <f>Normalized_FCF!C120</f>
-        <v>1.2141426890285656</v>
-      </c>
-      <c r="D76" s="324">
-        <f>Normalized_FCF!G120</f>
-        <v>1.2141426890285656</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" ht="13.9">
-      <c r="A78" s="222" t="s">
-        <v>505</v>
-      </c>
-      <c r="B78" s="36"/>
-      <c r="C78" s="36"/>
-      <c r="D78" s="36"/>
-      <c r="E78" s="36"/>
-      <c r="F78" s="36"/>
-    </row>
-    <row r="79" spans="1:6">
-      <c r="A79" s="209"/>
-    </row>
-    <row r="80" spans="1:6">
-      <c r="A80" s="17"/>
-      <c r="B80" s="371" t="s">
-        <v>506</v>
-      </c>
-      <c r="C80" s="371"/>
-      <c r="D80" s="371"/>
-      <c r="E80" s="371"/>
-      <c r="F80" s="371"/>
-    </row>
-    <row r="81" spans="1:6">
-      <c r="B81" s="372" t="s">
-        <v>248</v>
-      </c>
-      <c r="C81" s="372"/>
-      <c r="D81" s="372"/>
-      <c r="E81" s="372"/>
-      <c r="F81" s="372"/>
-    </row>
-    <row r="83" spans="1:6">
-      <c r="B83" s="210" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6">
-      <c r="B84" s="1" t="s">
-        <v>407</v>
-      </c>
-      <c r="C84" s="92">
-        <f>F31</f>
-        <v>7.4999999999999997E-2</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6">
-      <c r="B85" s="1" t="s">
-        <v>406</v>
-      </c>
-      <c r="C85" s="92">
-        <f>IF(C23="Y",1%,0)+IF(C24="Y",1%,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6">
-      <c r="B86" s="80" t="s">
-        <v>243</v>
-      </c>
-      <c r="C86" s="236">
-        <f>F31+C85</f>
-        <v>7.4999999999999997E-2</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6">
-      <c r="C87" s="121"/>
-    </row>
-    <row r="88" spans="1:6">
-      <c r="B88" s="293" t="s">
-        <v>512</v>
-      </c>
-      <c r="C88" s="121"/>
-    </row>
-    <row r="89" spans="1:6">
-      <c r="B89" s="371" t="s">
-        <v>507</v>
-      </c>
-      <c r="C89" s="371"/>
-      <c r="D89" s="371"/>
-      <c r="E89" s="371"/>
-      <c r="F89" s="371"/>
-    </row>
-    <row r="90" spans="1:6">
-      <c r="B90" s="371" t="s">
-        <v>508</v>
-      </c>
-      <c r="C90" s="371"/>
-      <c r="D90" s="371"/>
-      <c r="E90" s="371"/>
-      <c r="F90" s="371"/>
-    </row>
-    <row r="92" spans="1:6">
-      <c r="B92" s="47" t="s">
-        <v>247</v>
-      </c>
-      <c r="C92" s="236">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6">
-      <c r="B93" s="47" t="s">
-        <v>275</v>
-      </c>
-      <c r="C93" s="223">
-        <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>2.8594601378649682</v>
-      </c>
-      <c r="D93" s="1" t="str">
-        <f>Market_currency</f>
-        <v>HKD</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6" ht="13.9">
-      <c r="A95" s="222" t="s">
-        <v>509</v>
-      </c>
-      <c r="B95" s="36"/>
-      <c r="C95" s="36"/>
-      <c r="D95" s="36"/>
-      <c r="E95" s="36"/>
-      <c r="F95" s="36"/>
-    </row>
-    <row r="96" spans="1:6">
-      <c r="A96" s="209"/>
-    </row>
-    <row r="97" spans="2:6">
-      <c r="B97" s="371" t="s">
-        <v>510</v>
-      </c>
-      <c r="C97" s="371"/>
-      <c r="D97" s="371"/>
-      <c r="E97" s="371"/>
-      <c r="F97" s="371"/>
-    </row>
-    <row r="98" spans="2:6">
-      <c r="B98" s="1" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="100" spans="2:6">
-      <c r="B100" s="210" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="101" spans="2:6">
-      <c r="B101" s="371" t="s">
-        <v>511</v>
-      </c>
-      <c r="C101" s="371"/>
-      <c r="D101" s="371"/>
-      <c r="E101" s="371"/>
-      <c r="F101" s="371"/>
-    </row>
-    <row r="102" spans="2:6">
-      <c r="B102" s="47" t="s">
-        <v>251</v>
-      </c>
-      <c r="C102" s="349">
-        <f>DCF!C7</f>
-        <v>43677</v>
-      </c>
-      <c r="D102" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>HKD</v>
-      </c>
-    </row>
-    <row r="103" spans="2:6">
-      <c r="B103" s="47" t="s">
-        <v>276</v>
-      </c>
-      <c r="C103" s="223">
-        <f>C102*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>8.5791466803226933E-3</v>
-      </c>
-      <c r="D103" s="1" t="str">
-        <f>Market_currency</f>
-        <v>HKD</v>
-      </c>
-    </row>
-    <row r="104" spans="2:6">
-      <c r="B104" s="296" t="s">
-        <v>384</v>
-      </c>
-      <c r="C104" s="325">
-        <f>IF(BS!G31/BS!G27&gt;300%,"nm",BS!G31/BS!G27)</f>
-        <v>2.3107986944995245E-3</v>
-      </c>
-    </row>
-    <row r="105" spans="2:6">
-      <c r="B105" s="296" t="s">
-        <v>386</v>
-      </c>
-      <c r="C105" s="326">
-        <f>IF(BS!C50&gt;30,"nm",BS!C50)</f>
-        <v>2.3228129203780753E-2</v>
-      </c>
-    </row>
-    <row r="107" spans="2:6">
-      <c r="B107" s="1" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="108" spans="2:6">
-      <c r="B108" s="47" t="s">
-        <v>260</v>
-      </c>
-      <c r="C108" s="349">
-        <f>BS!C66</f>
-        <v>10118429</v>
-      </c>
-      <c r="D108" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>HKD</v>
-      </c>
-    </row>
-    <row r="109" spans="2:6">
-      <c r="B109" s="47" t="s">
-        <v>262</v>
-      </c>
-      <c r="C109" s="349">
-        <f>DCF!C8</f>
-        <v>8041470.060084247</v>
-      </c>
-      <c r="D109" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>HKD</v>
-      </c>
-    </row>
-    <row r="110" spans="2:6">
-      <c r="B110" s="47" t="s">
-        <v>277</v>
-      </c>
-      <c r="C110" s="223">
-        <f>C109*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.5795258642050989</v>
-      </c>
-      <c r="D110" s="1" t="str">
-        <f>Market_currency</f>
-        <v>HKD</v>
-      </c>
-    </row>
-    <row r="112" spans="2:6">
-      <c r="B112" s="1" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6">
-      <c r="B113" s="47" t="s">
-        <v>253</v>
-      </c>
-      <c r="C113" s="349">
-        <f>DCF!C9</f>
-        <v>263512.2</v>
-      </c>
-      <c r="D113" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>HKD</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6">
-      <c r="B114" s="47" t="s">
-        <v>278</v>
-      </c>
-      <c r="C114" s="223">
-        <f>C113*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>5.1759732029547124E-2</v>
-      </c>
-      <c r="D114" s="1" t="str">
-        <f>Market_currency</f>
-        <v>HKD</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6">
-      <c r="B116" s="371" t="s">
-        <v>516</v>
-      </c>
-      <c r="C116" s="371"/>
-      <c r="D116" s="371"/>
-      <c r="E116" s="371"/>
-      <c r="F116" s="371"/>
-    </row>
-    <row r="118" spans="1:6">
-      <c r="B118" s="47" t="s">
-        <v>517</v>
-      </c>
-      <c r="C118" s="223">
-        <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>4.4821665874192913</v>
-      </c>
-      <c r="D118" s="1" t="str">
-        <f>Market_currency</f>
-        <v>HKD</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6">
-      <c r="B119" s="296" t="s">
-        <v>550</v>
-      </c>
-      <c r="C119" s="223">
-        <f>BS!D47</f>
-        <v>0.79833937207218564</v>
-      </c>
-      <c r="D119" s="1" t="str">
-        <f>Market_currency</f>
-        <v>HKD</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6" ht="13.9">
-      <c r="A121" s="222" t="s">
-        <v>518</v>
-      </c>
-      <c r="B121" s="36"/>
-      <c r="C121" s="36"/>
-      <c r="D121" s="36"/>
-      <c r="E121" s="36"/>
-      <c r="F121" s="36"/>
-    </row>
-    <row r="123" spans="1:6">
-      <c r="B123" s="370" t="s">
-        <v>519</v>
-      </c>
-      <c r="C123" s="370"/>
-      <c r="D123" s="370"/>
-      <c r="E123" s="370"/>
-      <c r="F123" s="370"/>
-    </row>
-    <row r="125" spans="1:6" ht="12.4">
-      <c r="B125" s="233" t="s">
-        <v>520</v>
-      </c>
-      <c r="C125" s="233" t="s">
-        <v>521</v>
-      </c>
-      <c r="D125" s="233" t="s">
-        <v>108</v>
-      </c>
-      <c r="E125" s="233" t="s">
-        <v>522</v>
-      </c>
-      <c r="F125" s="233" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6">
-      <c r="B126" s="228" t="str">
-        <f>DCF!B74</f>
-        <v>Snowball Scenario</v>
-      </c>
-      <c r="C126" s="229">
-        <f>DCF!C74</f>
-        <v>0.04</v>
-      </c>
-      <c r="D126" s="230">
-        <f>DCF!D74</f>
-        <v>10</v>
-      </c>
-      <c r="E126" s="231" t="str">
-        <f>ROUND(IF(valuation_method="DCF",DCF!E74,DDM!E69),2)&amp;" "&amp;Market_currency</f>
-        <v>4.86 HKD</v>
-      </c>
-      <c r="F126" s="232">
-        <f>DCF!F74</f>
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6">
-      <c r="B127" s="218" t="str">
-        <f>DCF!B75</f>
-        <v>Optimistic</v>
-      </c>
-      <c r="C127" s="219">
-        <f>DCF!C75</f>
-        <v>0.02</v>
-      </c>
-      <c r="D127" s="220">
-        <f>DCF!D75</f>
-        <v>5</v>
-      </c>
-      <c r="E127" s="231" t="str">
-        <f>ROUND(IF(valuation_method="DCF",DCF!E75,DDM!E70),2)&amp;" "&amp;Market_currency</f>
-        <v>4.57 HKD</v>
-      </c>
-      <c r="F127" s="221">
-        <f>DCF!F75</f>
-        <v>0.18</v>
-      </c>
-    </row>
-    <row r="128" spans="1:6">
-      <c r="B128" s="218" t="str">
-        <f>DCF!B76</f>
-        <v>Base</v>
-      </c>
-      <c r="C128" s="219">
-        <f>DCF!C76</f>
-        <v>0</v>
-      </c>
-      <c r="D128" s="220">
-        <f>DCF!D76</f>
-        <v>5</v>
-      </c>
-      <c r="E128" s="231" t="str">
-        <f>ROUND(IF(valuation_method="DCF",DCF!E76,DDM!E71),2)&amp;" "&amp;Market_currency</f>
-        <v>4.48 HKD</v>
-      </c>
-      <c r="F128" s="221">
-        <f>DCF!F76</f>
-        <v>0.53999999999999992</v>
-      </c>
-    </row>
-    <row r="129" spans="1:6">
-      <c r="B129" s="218" t="str">
-        <f>DCF!B77</f>
-        <v>Pessimistic</v>
-      </c>
-      <c r="C129" s="219">
-        <f>DCF!C77</f>
-        <v>-0.02</v>
-      </c>
-      <c r="D129" s="220">
-        <f>DCF!D77</f>
-        <v>5</v>
-      </c>
-      <c r="E129" s="231" t="str">
-        <f>ROUND(IF(valuation_method="DCF",DCF!E77,DDM!E72),2)&amp;" "&amp;Market_currency</f>
-        <v>4.39 HKD</v>
-      </c>
-      <c r="F129" s="221">
-        <f>DCF!F77</f>
-        <v>0.18</v>
-      </c>
-    </row>
-    <row r="130" spans="1:6">
-      <c r="B130" s="218" t="str">
-        <f>DCF!B78</f>
-        <v>Devil's advocate</v>
-      </c>
-      <c r="C130" s="219">
-        <f>DCF!C78</f>
-        <v>-0.04</v>
-      </c>
-      <c r="D130" s="220">
-        <f>DCF!D78</f>
-        <v>10</v>
-      </c>
-      <c r="E130" s="231" t="str">
-        <f>ROUND(IF(valuation_method="DCF",DCF!E78,DDM!E73),2)&amp;" "&amp;Market_currency</f>
-        <v>4.17 HKD</v>
-      </c>
-      <c r="F130" s="221">
-        <f>DCF!F78</f>
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="132" spans="1:6">
-      <c r="B132" s="211" t="s">
-        <v>254</v>
-      </c>
-      <c r="C132" s="217">
-        <f>Scenarios!C60</f>
-        <v>4.4858408799140586</v>
-      </c>
-      <c r="D132" s="212" t="str">
-        <f>Market_currency</f>
-        <v>HKD</v>
-      </c>
-    </row>
-    <row r="134" spans="1:6">
-      <c r="B134" s="375" t="s">
-        <v>524</v>
-      </c>
-      <c r="C134" s="375"/>
-      <c r="D134" s="375"/>
-      <c r="E134" s="375"/>
-      <c r="F134" s="375"/>
-    </row>
-    <row r="136" spans="1:6" ht="13.9">
-      <c r="A136" s="222" t="s">
-        <v>525</v>
-      </c>
-      <c r="B136" s="36"/>
-      <c r="C136" s="36"/>
-      <c r="D136" s="36"/>
-      <c r="E136" s="36"/>
-      <c r="F136" s="36"/>
-    </row>
-    <row r="138" spans="1:6">
-      <c r="B138" s="376" t="s">
-        <v>526</v>
-      </c>
-      <c r="C138" s="376"/>
-      <c r="D138" s="376"/>
-      <c r="E138" s="376"/>
-      <c r="F138" s="376"/>
-    </row>
-    <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="371" t="s">
-        <v>527</v>
-      </c>
-      <c r="C139" s="371"/>
-      <c r="D139" s="371"/>
-      <c r="E139" s="371"/>
-      <c r="F139" s="371"/>
-    </row>
-    <row r="140" spans="1:6">
-      <c r="B140" s="210" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="141" spans="1:6">
-      <c r="B141" s="1" t="s">
-        <v>528</v>
-      </c>
-      <c r="C141" s="225">
-        <f>F28</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6">
-      <c r="B142" s="1" t="s">
-        <v>529</v>
-      </c>
-      <c r="C142" s="224">
-        <f>F29</f>
-        <v>0.35</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6">
-      <c r="B143" s="212" t="s">
-        <v>530</v>
-      </c>
-      <c r="C143" s="213">
-        <f>Scenarios!C77</f>
-        <v>0.27</v>
-      </c>
-      <c r="D143" s="212" t="str">
-        <f>Market_currency</f>
-        <v>HKD</v>
-      </c>
-    </row>
-    <row r="145" spans="2:4">
-      <c r="B145" s="210" t="s">
-        <v>531</v>
-      </c>
-      <c r="C145" s="241" t="str">
-        <f>C11</f>
-        <v>0639.HK</v>
-      </c>
-      <c r="D145" s="241" t="str">
-        <f>IF(D11="","",D11)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="146" spans="2:4">
-      <c r="B146" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="C146" s="297">
-        <f>F29</f>
-        <v>0.35</v>
-      </c>
-    </row>
-    <row r="147" spans="2:4">
-      <c r="B147" s="212" t="str">
-        <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
-        <v>PV(3 yrs of Dividends)</v>
-      </c>
-      <c r="C147" s="216">
-        <f>Scenarios!C81</f>
-        <v>0.45788751714677645</v>
-      </c>
-    </row>
-    <row r="148" spans="2:4">
-      <c r="B148" s="212" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
-        <v>+ PV(Equity Value realized at year 3)</v>
-      </c>
-      <c r="C148" s="216">
-        <f>Scenarios!C82</f>
-        <v>1.823234620703778</v>
-      </c>
-    </row>
-    <row r="149" spans="2:4">
-      <c r="B149" s="80" t="s">
-        <v>256</v>
-      </c>
-      <c r="C149" s="215">
-        <f>Scenarios!C83</f>
-        <v>2.2811221378505544</v>
-      </c>
-      <c r="D149" s="300" t="str">
-        <f>IF($D$11="","",C149*$E$25)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="150" spans="2:4">
-      <c r="B150" s="259" t="s">
-        <v>532</v>
-      </c>
-      <c r="C150" s="298" t="str">
-        <f>Market_currency</f>
-        <v>HKD</v>
-      </c>
-      <c r="D150" s="298" t="str">
-        <f>IF($D$11="","",D$13)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="151" spans="2:4">
-      <c r="B151" s="214" t="s">
-        <v>533</v>
-      </c>
-      <c r="C151" s="92">
-        <f>Scenarios!F83</f>
-        <v>0.49148393825902781</v>
-      </c>
-    </row>
-    <row r="153" spans="2:4">
-      <c r="B153" s="210" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="154" spans="2:4">
-      <c r="B154" s="1" t="s">
-        <v>390</v>
-      </c>
-      <c r="C154" s="297">
-        <f>Scenarios!C90</f>
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="155" spans="2:4">
-      <c r="B155" s="212" t="str">
-        <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
-        <v>PV(3 yrs of Dividends)</v>
-      </c>
-      <c r="C155" s="216">
-        <f>Scenarios!C91</f>
-        <v>0.52704000000000006</v>
-      </c>
-    </row>
-    <row r="156" spans="2:4">
-      <c r="B156" s="212" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
-        <v>+ PV(Equity Value realized at year 3)</v>
-      </c>
-      <c r="C156" s="216">
-        <f>Scenarios!C92</f>
-        <v>2.2967505305159981</v>
-      </c>
-    </row>
-    <row r="157" spans="2:4">
-      <c r="B157" s="80" t="s">
-        <v>256</v>
-      </c>
-      <c r="C157" s="215">
-        <f>Scenarios!C93</f>
-        <v>2.823790530515998</v>
-      </c>
-      <c r="D157" s="300" t="str">
-        <f>IF($D$11="","",C157*$E$25)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="158" spans="2:4">
-      <c r="B158" s="259" t="s">
-        <v>532</v>
-      </c>
-      <c r="C158" s="298" t="str">
-        <f>Market_currency</f>
-        <v>HKD</v>
-      </c>
-      <c r="D158" s="298" t="str">
-        <f>IF($D$11="","",D$13)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="159" spans="2:4">
-      <c r="B159" s="214" t="s">
-        <v>533</v>
-      </c>
-      <c r="C159" s="92">
-        <f>Scenarios!F93</f>
-        <v>0.37051032212045443</v>
-      </c>
-    </row>
-    <row r="161" spans="2:4">
-      <c r="B161" s="210" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="162" spans="2:4">
-      <c r="B162" s="1" t="s">
-        <v>389</v>
-      </c>
-      <c r="C162" s="92">
-        <f>Scenarios!C96</f>
-        <v>7.4999999999999997E-2</v>
-      </c>
-    </row>
-    <row r="163" spans="2:4">
-      <c r="B163" s="212" t="str">
-        <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
-        <v>PV(3 yrs of Dividends)</v>
-      </c>
-      <c r="C163" s="216">
-        <f>Scenarios!C97</f>
-        <v>0.70214194976542921</v>
-      </c>
-    </row>
-    <row r="164" spans="2:4">
-      <c r="B164" s="212" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
-        <v>+ PV(Equity Value realized at year 3)</v>
-      </c>
-      <c r="C164" s="216">
-        <f>Scenarios!C98</f>
-        <v>3.6109250294250792</v>
-      </c>
-    </row>
-    <row r="165" spans="2:4">
-      <c r="B165" s="80" t="s">
-        <v>382</v>
-      </c>
-      <c r="C165" s="215">
-        <f>Scenarios!C99</f>
-        <v>4.3130669791905083</v>
-      </c>
-      <c r="D165" s="300" t="str">
-        <f>IF($D$11="","",C165*$E$25)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="166" spans="2:4">
-      <c r="B166" s="259" t="s">
-        <v>532</v>
-      </c>
-      <c r="C166" s="298" t="str">
-        <f>Market_currency</f>
-        <v>HKD</v>
-      </c>
-      <c r="D166" s="298" t="str">
-        <f>IF($D$11="","",D$13)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="167" spans="2:4">
-      <c r="B167" s="214" t="s">
-        <v>533</v>
-      </c>
-      <c r="C167" s="92">
-        <f>Scenarios!F99</f>
-        <v>3.8515387716307137E-2</v>
-      </c>
-    </row>
-    <row r="169" spans="2:4">
-      <c r="B169" s="210" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="170" spans="2:4">
-      <c r="B170" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="C170" s="92">
-        <f>F32</f>
-        <v>0.1174</v>
-      </c>
-    </row>
-    <row r="171" spans="2:4">
-      <c r="B171" s="212" t="str">
-        <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
-        <v>PV(3 yrs of Dividends)</v>
-      </c>
-      <c r="C171" s="216">
-        <f>Scenarios!C103</f>
-        <v>0.65140284400343529</v>
-      </c>
-    </row>
-    <row r="172" spans="2:4">
-      <c r="B172" s="212" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
-        <v>+ PV(Equity Value realized at year 3)</v>
-      </c>
-      <c r="C172" s="216">
-        <f>Scenarios!C104</f>
-        <v>3.2152730720890683</v>
-      </c>
-    </row>
-    <row r="173" spans="2:4">
-      <c r="B173" s="80" t="s">
-        <v>382</v>
-      </c>
-      <c r="C173" s="215">
-        <f>Scenarios!C105</f>
-        <v>3.8666759160925035</v>
-      </c>
-      <c r="D173" s="300" t="str">
-        <f>IF($D$11="","",C173*$E$25)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="174" spans="2:4">
-      <c r="B174" s="259" t="s">
-        <v>532</v>
-      </c>
-      <c r="C174" s="298" t="str">
-        <f>Market_currency</f>
-        <v>HKD</v>
-      </c>
-      <c r="D174" s="298" t="str">
-        <f>IF($D$11="","",D$13)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="175" spans="2:4">
-      <c r="B175" s="214" t="s">
-        <v>533</v>
-      </c>
-      <c r="C175" s="92">
-        <f>Scenarios!F105</f>
-        <v>0.13842067503200794</v>
-      </c>
-    </row>
-    <row r="177" spans="1:6" ht="13.9">
-      <c r="A177" s="222" t="s">
-        <v>357</v>
-      </c>
-      <c r="B177" s="36"/>
-      <c r="C177" s="36"/>
-      <c r="D177" s="36"/>
-      <c r="E177" s="36"/>
-      <c r="F177" s="36"/>
-    </row>
-    <row r="179" spans="1:6">
-      <c r="B179" s="377" t="s">
-        <v>534</v>
-      </c>
-      <c r="C179" s="371"/>
-      <c r="D179" s="371"/>
-      <c r="E179" s="371"/>
-      <c r="F179" s="371"/>
-    </row>
-    <row r="181" spans="1:6">
-      <c r="B181" s="210" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="182" spans="1:6">
-      <c r="B182" s="373" t="s">
-        <v>536</v>
-      </c>
-      <c r="C182" s="373"/>
-      <c r="D182" s="373"/>
-      <c r="E182" s="373"/>
-      <c r="F182" s="373"/>
-    </row>
-    <row r="183" spans="1:6">
-      <c r="B183" s="214" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="184" spans="1:6">
-      <c r="B184" s="214" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="185" spans="1:6">
-      <c r="B185" s="214" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="187" spans="1:6">
-      <c r="B187" s="1" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="188" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B188" s="370" t="s">
-        <v>541</v>
-      </c>
-      <c r="C188" s="370"/>
-      <c r="D188" s="370"/>
-      <c r="E188" s="370"/>
-      <c r="F188" s="370"/>
-    </row>
-    <row r="190" spans="1:6">
-      <c r="B190" s="1" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="191" spans="1:6">
-      <c r="B191" s="374" t="s">
-        <v>543</v>
-      </c>
-      <c r="C191" s="374"/>
-      <c r="D191" s="374"/>
-      <c r="E191" s="374"/>
-      <c r="F191" s="374"/>
-    </row>
-    <row r="192" spans="1:6">
-      <c r="B192" s="374" t="s">
-        <v>544</v>
-      </c>
-      <c r="C192" s="374"/>
-      <c r="D192" s="374"/>
-      <c r="E192" s="374"/>
-      <c r="F192" s="374"/>
-    </row>
-    <row r="194" spans="2:2">
-      <c r="B194" s="1" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="195" spans="2:2">
-      <c r="B195" s="214" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="196" spans="2:2">
-      <c r="B196" s="214" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="197" spans="2:2">
-      <c r="B197" s="214" t="s">
-        <v>548</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="27">
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B138:F138"/>
-    <mergeCell ref="B139:F139"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B116:F116"/>
-    <mergeCell ref="B50:F50"/>
-    <mergeCell ref="B58:F58"/>
-    <mergeCell ref="B61:F61"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B65:F65"/>
-    <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B90:F90"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B47:F47"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B43:F43"/>
-  </mergeCells>
-  <dataValidations count="5">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">
-      <formula1>"INT,CN"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E21 E25" xr:uid="{0BE1D34E-D50B-41CB-99F3-E9F8694C38CA}">
-      <formula1>"DCF,DDM"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="C25:D25" xr:uid="{4F076B80-6574-480B-B48C-99BFFF6B4B13}">
-      <formula1>"HKD,USD,CNY,EUR"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C23:C24" xr:uid="{B605A743-B0FC-4D89-AD54-945707F01FA1}">
-      <formula1>"Y,N"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1" xr:uid="{CF966412-2762-45A3-9589-2A9D9DD6B905}">
-      <formula1>"Y, N"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="85" fitToHeight="0" orientation="portrait" verticalDpi="300" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E03CB28-CABF-4F73-9474-1674E7E6FB22}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -7081,13 +5340,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="371" t="s">
+      <c r="B18" s="367" t="s">
         <v>468</v>
       </c>
-      <c r="C18" s="371"/>
-      <c r="D18" s="371"/>
-      <c r="E18" s="371"/>
-      <c r="F18" s="371"/>
+      <c r="C18" s="367"/>
+      <c r="D18" s="367"/>
+      <c r="E18" s="367"/>
+      <c r="F18" s="367"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -7287,22 +5546,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6">
-      <c r="B36" s="371" t="s">
+      <c r="B36" s="367" t="s">
         <v>469</v>
       </c>
-      <c r="C36" s="371"/>
-      <c r="D36" s="371"/>
-      <c r="E36" s="371"/>
-      <c r="F36" s="371"/>
+      <c r="C36" s="367"/>
+      <c r="D36" s="367"/>
+      <c r="E36" s="367"/>
+      <c r="F36" s="367"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="372" t="s">
+      <c r="B37" s="369" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="372"/>
-      <c r="D37" s="372"/>
-      <c r="E37" s="372"/>
-      <c r="F37" s="372"/>
+      <c r="C37" s="369"/>
+      <c r="D37" s="369"/>
+      <c r="E37" s="369"/>
+      <c r="F37" s="369"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -7314,13 +5573,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="370" t="s">
+      <c r="B40" s="368" t="s">
         <v>227</v>
       </c>
-      <c r="C40" s="370"/>
-      <c r="D40" s="370"/>
-      <c r="E40" s="370"/>
-      <c r="F40" s="370"/>
+      <c r="C40" s="368"/>
+      <c r="D40" s="368"/>
+      <c r="E40" s="368"/>
+      <c r="F40" s="368"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -7340,13 +5599,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="370" t="s">
+      <c r="B43" s="368" t="s">
         <v>229</v>
       </c>
-      <c r="C43" s="370"/>
-      <c r="D43" s="370"/>
-      <c r="E43" s="370"/>
-      <c r="F43" s="370"/>
+      <c r="C43" s="368"/>
+      <c r="D43" s="368"/>
+      <c r="E43" s="368"/>
+      <c r="F43" s="368"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -7375,13 +5634,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="370" t="s">
+      <c r="B47" s="368" t="s">
         <v>232</v>
       </c>
-      <c r="C47" s="370"/>
-      <c r="D47" s="370"/>
-      <c r="E47" s="370"/>
-      <c r="F47" s="370"/>
+      <c r="C47" s="368"/>
+      <c r="D47" s="368"/>
+      <c r="E47" s="368"/>
+      <c r="F47" s="368"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -7397,13 +5656,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="370" t="s">
+      <c r="B50" s="368" t="s">
         <v>236</v>
       </c>
-      <c r="C50" s="370"/>
-      <c r="D50" s="370"/>
-      <c r="E50" s="370"/>
-      <c r="F50" s="370"/>
+      <c r="C50" s="368"/>
+      <c r="D50" s="368"/>
+      <c r="E50" s="368"/>
+      <c r="F50" s="368"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -7467,13 +5726,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="370" t="s">
+      <c r="B58" s="368" t="s">
         <v>237</v>
       </c>
-      <c r="C58" s="370"/>
-      <c r="D58" s="370"/>
-      <c r="E58" s="370"/>
-      <c r="F58" s="370"/>
+      <c r="C58" s="368"/>
+      <c r="D58" s="368"/>
+      <c r="E58" s="368"/>
+      <c r="F58" s="368"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -7489,13 +5748,13 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="370" t="s">
+      <c r="B61" s="368" t="s">
         <v>329</v>
       </c>
-      <c r="C61" s="373"/>
-      <c r="D61" s="373"/>
-      <c r="E61" s="373"/>
-      <c r="F61" s="373"/>
+      <c r="C61" s="371"/>
+      <c r="D61" s="371"/>
+      <c r="E61" s="371"/>
+      <c r="F61" s="371"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -7511,22 +5770,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="371" t="s">
+      <c r="B64" s="367" t="s">
         <v>334</v>
       </c>
-      <c r="C64" s="371"/>
-      <c r="D64" s="371"/>
-      <c r="E64" s="371"/>
-      <c r="F64" s="371"/>
+      <c r="C64" s="367"/>
+      <c r="D64" s="367"/>
+      <c r="E64" s="367"/>
+      <c r="F64" s="367"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="371" t="s">
+      <c r="B65" s="367" t="s">
         <v>348</v>
       </c>
-      <c r="C65" s="371"/>
-      <c r="D65" s="371"/>
-      <c r="E65" s="371"/>
-      <c r="F65" s="371"/>
+      <c r="C65" s="367"/>
+      <c r="D65" s="367"/>
+      <c r="E65" s="367"/>
+      <c r="F65" s="367"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -7661,22 +5920,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="371" t="s">
+      <c r="B80" s="367" t="s">
         <v>471</v>
       </c>
-      <c r="C80" s="371"/>
-      <c r="D80" s="371"/>
-      <c r="E80" s="371"/>
-      <c r="F80" s="371"/>
+      <c r="C80" s="367"/>
+      <c r="D80" s="367"/>
+      <c r="E80" s="367"/>
+      <c r="F80" s="367"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="372" t="s">
+      <c r="B81" s="369" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="372"/>
-      <c r="D81" s="372"/>
-      <c r="E81" s="372"/>
-      <c r="F81" s="372"/>
+      <c r="C81" s="369"/>
+      <c r="D81" s="369"/>
+      <c r="E81" s="369"/>
+      <c r="F81" s="369"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -7720,22 +5979,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="371" t="s">
+      <c r="B89" s="367" t="s">
         <v>349</v>
       </c>
-      <c r="C89" s="371"/>
-      <c r="D89" s="371"/>
-      <c r="E89" s="371"/>
-      <c r="F89" s="371"/>
+      <c r="C89" s="367"/>
+      <c r="D89" s="367"/>
+      <c r="E89" s="367"/>
+      <c r="F89" s="367"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="371" t="s">
+      <c r="B90" s="367" t="s">
         <v>350</v>
       </c>
-      <c r="C90" s="371"/>
-      <c r="D90" s="371"/>
-      <c r="E90" s="371"/>
-      <c r="F90" s="371"/>
+      <c r="C90" s="367"/>
+      <c r="D90" s="367"/>
+      <c r="E90" s="367"/>
+      <c r="F90" s="367"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -7772,13 +6031,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="371" t="s">
+      <c r="B97" s="367" t="s">
         <v>351</v>
       </c>
-      <c r="C97" s="371"/>
-      <c r="D97" s="371"/>
-      <c r="E97" s="371"/>
-      <c r="F97" s="371"/>
+      <c r="C97" s="367"/>
+      <c r="D97" s="367"/>
+      <c r="E97" s="367"/>
+      <c r="F97" s="367"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -7791,13 +6050,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="371" t="s">
+      <c r="B101" s="367" t="s">
         <v>335</v>
       </c>
-      <c r="C101" s="371"/>
-      <c r="D101" s="371"/>
-      <c r="E101" s="371"/>
-      <c r="F101" s="371"/>
+      <c r="C101" s="367"/>
+      <c r="D101" s="367"/>
+      <c r="E101" s="367"/>
+      <c r="F101" s="367"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -7919,13 +6178,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="371" t="s">
+      <c r="B116" s="367" t="s">
         <v>352</v>
       </c>
-      <c r="C116" s="371"/>
-      <c r="D116" s="371"/>
-      <c r="E116" s="371"/>
-      <c r="F116" s="371"/>
+      <c r="C116" s="367"/>
+      <c r="D116" s="367"/>
+      <c r="E116" s="367"/>
+      <c r="F116" s="367"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -7964,13 +6223,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="370" t="s">
+      <c r="B123" s="368" t="s">
         <v>473</v>
       </c>
-      <c r="C123" s="370"/>
-      <c r="D123" s="370"/>
-      <c r="E123" s="370"/>
-      <c r="F123" s="370"/>
+      <c r="C123" s="368"/>
+      <c r="D123" s="368"/>
+      <c r="E123" s="368"/>
+      <c r="F123" s="368"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -8113,13 +6372,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="375" t="s">
+      <c r="B134" s="372" t="s">
         <v>474</v>
       </c>
-      <c r="C134" s="375"/>
-      <c r="D134" s="375"/>
-      <c r="E134" s="375"/>
-      <c r="F134" s="375"/>
+      <c r="C134" s="372"/>
+      <c r="D134" s="372"/>
+      <c r="E134" s="372"/>
+      <c r="F134" s="372"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -8132,22 +6391,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="376" t="s">
+      <c r="B138" s="370" t="s">
         <v>353</v>
       </c>
-      <c r="C138" s="376"/>
-      <c r="D138" s="376"/>
-      <c r="E138" s="376"/>
-      <c r="F138" s="376"/>
+      <c r="C138" s="370"/>
+      <c r="D138" s="370"/>
+      <c r="E138" s="370"/>
+      <c r="F138" s="370"/>
     </row>
     <row r="139" spans="1:6">
-      <c r="B139" s="371" t="s">
+      <c r="B139" s="367" t="s">
         <v>476</v>
       </c>
-      <c r="C139" s="371"/>
-      <c r="D139" s="371"/>
-      <c r="E139" s="371"/>
-      <c r="F139" s="371"/>
+      <c r="C139" s="367"/>
+      <c r="D139" s="367"/>
+      <c r="E139" s="367"/>
+      <c r="F139" s="367"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -8480,13 +6739,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="377" t="s">
+      <c r="B179" s="374" t="s">
         <v>477</v>
       </c>
-      <c r="C179" s="371"/>
-      <c r="D179" s="371"/>
-      <c r="E179" s="371"/>
-      <c r="F179" s="371"/>
+      <c r="C179" s="367"/>
+      <c r="D179" s="367"/>
+      <c r="E179" s="367"/>
+      <c r="F179" s="367"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -8494,13 +6753,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="373" t="s">
+      <c r="B182" s="371" t="s">
         <v>362</v>
       </c>
-      <c r="C182" s="373"/>
-      <c r="D182" s="373"/>
-      <c r="E182" s="373"/>
-      <c r="F182" s="373"/>
+      <c r="C182" s="371"/>
+      <c r="D182" s="371"/>
+      <c r="E182" s="371"/>
+      <c r="F182" s="371"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -8523,13 +6782,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="34.35" customHeight="1">
-      <c r="B188" s="370" t="s">
+      <c r="B188" s="368" t="s">
         <v>478</v>
       </c>
-      <c r="C188" s="370"/>
-      <c r="D188" s="370"/>
-      <c r="E188" s="370"/>
-      <c r="F188" s="370"/>
+      <c r="C188" s="368"/>
+      <c r="D188" s="368"/>
+      <c r="E188" s="368"/>
+      <c r="F188" s="368"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -8537,22 +6796,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="374" t="s">
+      <c r="B191" s="373" t="s">
         <v>363</v>
       </c>
-      <c r="C191" s="374"/>
-      <c r="D191" s="374"/>
-      <c r="E191" s="374"/>
-      <c r="F191" s="374"/>
+      <c r="C191" s="373"/>
+      <c r="D191" s="373"/>
+      <c r="E191" s="373"/>
+      <c r="F191" s="373"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="374" t="s">
+      <c r="B192" s="373" t="s">
         <v>364</v>
       </c>
-      <c r="C192" s="374"/>
-      <c r="D192" s="374"/>
-      <c r="E192" s="374"/>
-      <c r="F192" s="374"/>
+      <c r="C192" s="373"/>
+      <c r="D192" s="373"/>
+      <c r="E192" s="373"/>
+      <c r="F192" s="373"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -8627,7 +6886,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48ED7348-D356-493F-B1FA-0B9102624322}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -11187,7 +9446,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet3">
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -12461,7 +10720,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2">
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -18142,7 +16401,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3EAD7ED-D484-47B2-9C7C-1D1BCBEAE5A9}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -18226,10 +16485,10 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E6" s="378" t="s">
+      <c r="E6" s="375" t="s">
         <v>245</v>
       </c>
-      <c r="F6" s="378"/>
+      <c r="F6" s="375"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8">
@@ -18244,8 +16503,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E7" s="378"/>
-      <c r="F7" s="378"/>
+      <c r="E7" s="375"/>
+      <c r="F7" s="375"/>
       <c r="H7" s="120"/>
     </row>
     <row r="8" spans="2:8">
@@ -18260,8 +16519,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E8" s="378"/>
-      <c r="F8" s="378"/>
+      <c r="E8" s="375"/>
+      <c r="F8" s="375"/>
       <c r="H8" s="120"/>
     </row>
     <row r="9" spans="2:8">
@@ -18276,8 +16535,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E9" s="378"/>
-      <c r="F9" s="378"/>
+      <c r="E9" s="375"/>
+      <c r="F9" s="375"/>
       <c r="H9" s="120"/>
     </row>
     <row r="10" spans="2:8" ht="13.15">
@@ -19902,7 +18161,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A27DB9BF-8D77-49A8-A09B-23E6CA7BEA90}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -19986,8 +18245,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E6" s="378"/>
-      <c r="F6" s="378"/>
+      <c r="E6" s="375"/>
+      <c r="F6" s="375"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8" ht="13.15">
@@ -21353,7 +19612,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
   <dimension ref="B2:I110"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
@@ -21452,11 +19711,11 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E7" s="380" t="str">
+      <c r="E7" s="377" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 5-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 10-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 首钢资源(0639.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="380"/>
+      <c r="F7" s="377"/>
       <c r="H7" s="247">
         <v>4</v>
       </c>
@@ -21477,8 +19736,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E8" s="380"/>
-      <c r="F8" s="380"/>
+      <c r="E8" s="377"/>
+      <c r="F8" s="377"/>
       <c r="H8" s="247">
         <v>5</v>
       </c>
@@ -21499,8 +19758,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E9" s="380"/>
-      <c r="F9" s="380"/>
+      <c r="E9" s="377"/>
+      <c r="F9" s="377"/>
       <c r="H9" s="247">
         <v>6</v>
       </c>
@@ -21510,8 +19769,8 @@
       </c>
     </row>
     <row r="10" spans="2:9">
-      <c r="E10" s="380"/>
-      <c r="F10" s="380"/>
+      <c r="E10" s="377"/>
+      <c r="F10" s="377"/>
       <c r="H10" s="247">
         <v>7</v>
       </c>
@@ -21524,8 +19783,8 @@
       <c r="B11" s="159" t="s">
         <v>423</v>
       </c>
-      <c r="E11" s="380"/>
-      <c r="F11" s="380"/>
+      <c r="E11" s="377"/>
+      <c r="F11" s="377"/>
       <c r="H11" s="247">
         <v>8</v>
       </c>
@@ -21543,8 +19802,8 @@
         <v>-0.1059288114314666</v>
       </c>
       <c r="D12" s="158"/>
-      <c r="E12" s="380"/>
-      <c r="F12" s="380"/>
+      <c r="E12" s="377"/>
+      <c r="F12" s="377"/>
       <c r="H12" s="247">
         <v>9</v>
       </c>
@@ -21561,8 +19820,8 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.1663504856430581</v>
       </c>
-      <c r="E13" s="380"/>
-      <c r="F13" s="380"/>
+      <c r="E13" s="377"/>
+      <c r="F13" s="377"/>
       <c r="H13" s="247">
         <v>10</v>
       </c>
@@ -21579,8 +19838,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.18299448813777219</v>
       </c>
-      <c r="E14" s="380"/>
-      <c r="F14" s="380"/>
+      <c r="E14" s="377"/>
+      <c r="F14" s="377"/>
     </row>
     <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
@@ -21606,21 +19865,21 @@
       <c r="C18" s="150">
         <v>5</v>
       </c>
-      <c r="E18" s="380" t="s">
+      <c r="E18" s="377" t="s">
         <v>321</v>
       </c>
-      <c r="F18" s="381"/>
+      <c r="F18" s="378"/>
     </row>
     <row r="19" spans="2:6">
-      <c r="E19" s="381"/>
-      <c r="F19" s="381"/>
+      <c r="E19" s="378"/>
+      <c r="F19" s="378"/>
     </row>
     <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="159" t="s">
         <v>298</v>
       </c>
-      <c r="E20" s="381"/>
-      <c r="F20" s="381"/>
+      <c r="E20" s="378"/>
+      <c r="F20" s="378"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
@@ -21634,8 +19893,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E21" s="381"/>
-      <c r="F21" s="381"/>
+      <c r="E21" s="378"/>
+      <c r="F21" s="378"/>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
@@ -21649,8 +19908,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E22" s="381"/>
-      <c r="F22" s="381"/>
+      <c r="E22" s="378"/>
+      <c r="F22" s="378"/>
     </row>
     <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="159" t="s">
@@ -21670,8 +19929,8 @@
         <v>5</v>
       </c>
       <c r="D25" s="163"/>
-      <c r="E25" s="379"/>
-      <c r="F25" s="379"/>
+      <c r="E25" s="376"/>
+      <c r="F25" s="376"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="118" t="s">
@@ -21681,8 +19940,8 @@
         <v>0</v>
       </c>
       <c r="D26" s="164"/>
-      <c r="E26" s="379"/>
-      <c r="F26" s="379"/>
+      <c r="E26" s="376"/>
+      <c r="F26" s="376"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
@@ -21696,8 +19955,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E27" s="379"/>
-      <c r="F27" s="379"/>
+      <c r="E27" s="376"/>
+      <c r="F27" s="376"/>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
@@ -21707,8 +19966,8 @@
         <v>0.6</v>
       </c>
       <c r="D28" s="165"/>
-      <c r="E28" s="379"/>
-      <c r="F28" s="379"/>
+      <c r="E28" s="376"/>
+      <c r="F28" s="376"/>
     </row>
     <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="159" t="s">
@@ -21728,8 +19987,8 @@
         <v>5</v>
       </c>
       <c r="D31" s="163"/>
-      <c r="E31" s="379"/>
-      <c r="F31" s="379"/>
+      <c r="E31" s="376"/>
+      <c r="F31" s="376"/>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="118" t="s">
@@ -21739,8 +19998,8 @@
         <v>-0.02</v>
       </c>
       <c r="D32" s="164"/>
-      <c r="E32" s="379"/>
-      <c r="F32" s="379"/>
+      <c r="E32" s="376"/>
+      <c r="F32" s="376"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
@@ -21754,8 +20013,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E33" s="379"/>
-      <c r="F33" s="379"/>
+      <c r="E33" s="376"/>
+      <c r="F33" s="376"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
@@ -21765,8 +20024,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="165"/>
-      <c r="E34" s="379"/>
-      <c r="F34" s="379"/>
+      <c r="E34" s="376"/>
+      <c r="F34" s="376"/>
     </row>
     <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="159" t="s">
@@ -21786,8 +20045,8 @@
         <v>5</v>
       </c>
       <c r="D37" s="163"/>
-      <c r="E37" s="379"/>
-      <c r="F37" s="379"/>
+      <c r="E37" s="376"/>
+      <c r="F37" s="376"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="118" t="s">
@@ -21797,8 +20056,8 @@
         <v>0.02</v>
       </c>
       <c r="D38" s="164"/>
-      <c r="E38" s="379"/>
-      <c r="F38" s="379"/>
+      <c r="E38" s="376"/>
+      <c r="F38" s="376"/>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
@@ -21812,8 +20071,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E39" s="379"/>
-      <c r="F39" s="379"/>
+      <c r="E39" s="376"/>
+      <c r="F39" s="376"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
@@ -21824,8 +20083,8 @@
         <v>0.2</v>
       </c>
       <c r="D40" s="165"/>
-      <c r="E40" s="379"/>
-      <c r="F40" s="379"/>
+      <c r="E40" s="376"/>
+      <c r="F40" s="376"/>
     </row>
     <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
@@ -21887,8 +20146,8 @@
         <v>10</v>
       </c>
       <c r="D49" s="163"/>
-      <c r="E49" s="379"/>
-      <c r="F49" s="379"/>
+      <c r="E49" s="376"/>
+      <c r="F49" s="376"/>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="118" t="s">
@@ -21898,8 +20157,8 @@
         <v>-0.04</v>
       </c>
       <c r="D50" s="164"/>
-      <c r="E50" s="379"/>
-      <c r="F50" s="379"/>
+      <c r="E50" s="376"/>
+      <c r="F50" s="376"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
@@ -21913,8 +20172,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E51" s="379"/>
-      <c r="F51" s="379"/>
+      <c r="E51" s="376"/>
+      <c r="F51" s="376"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
@@ -21924,8 +20183,8 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="165"/>
-      <c r="E52" s="379"/>
-      <c r="F52" s="379"/>
+      <c r="E52" s="376"/>
+      <c r="F52" s="376"/>
     </row>
     <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="159" t="s">
@@ -21945,8 +20204,8 @@
         <v>10</v>
       </c>
       <c r="D55" s="163"/>
-      <c r="E55" s="379"/>
-      <c r="F55" s="379"/>
+      <c r="E55" s="376"/>
+      <c r="F55" s="376"/>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="118" t="s">
@@ -21956,8 +20215,8 @@
         <v>0.04</v>
       </c>
       <c r="D56" s="164"/>
-      <c r="E56" s="379"/>
-      <c r="F56" s="379"/>
+      <c r="E56" s="376"/>
+      <c r="F56" s="376"/>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
@@ -21971,8 +20230,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E57" s="379"/>
-      <c r="F57" s="379"/>
+      <c r="E57" s="376"/>
+      <c r="F57" s="376"/>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
@@ -21982,8 +20241,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="165"/>
-      <c r="E58" s="379"/>
-      <c r="F58" s="379"/>
+      <c r="E58" s="376"/>
+      <c r="F58" s="376"/>
     </row>
     <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
@@ -22467,24 +20726,1767 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA287911-AF8F-41DE-9E8E-72556F041FFB}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:J197"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
+  <cols>
+    <col min="1" max="1" width="2.73046875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="32.73046875" style="1" customWidth="1"/>
+    <col min="3" max="4" width="25.73046875" style="1" customWidth="1"/>
+    <col min="5" max="6" width="15.73046875" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="B1" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="C1" s="33">
+        <f>Thesis!C1</f>
+        <v>45807</v>
+      </c>
+      <c r="D1" s="358" t="str">
+        <f>Thesis!D1</f>
+        <v>INT</v>
+      </c>
+      <c r="E1" s="292" t="s">
+        <v>344</v>
+      </c>
+      <c r="F1" s="307" t="str">
+        <f>Thesis!F1</f>
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="13.9">
+      <c r="A2" s="222" t="s">
+        <v>438</v>
+      </c>
+      <c r="B2" s="36"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="36"/>
+      <c r="F2" s="36"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
+      <c r="I2" s="22"/>
+      <c r="J2" s="22"/>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="B4" s="45" t="s">
+        <v>439</v>
+      </c>
+      <c r="C4" s="46"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+    </row>
+    <row r="5" spans="1:10" ht="12.4">
+      <c r="B5" s="4" t="s">
+        <v>479</v>
+      </c>
+      <c r="C5" s="359" t="str">
+        <f>Thesis!C5</f>
+        <v>首钢资源</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="B6" s="4" t="s">
+        <v>480</v>
+      </c>
+      <c r="C6" s="34">
+        <f>Common_Shares</f>
+        <v>5091065770</v>
+      </c>
+      <c r="E6" s="48"/>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="B7" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="C7" s="360">
+        <f>Thesis!C7</f>
+        <v>6</v>
+      </c>
+      <c r="D7" s="48"/>
+      <c r="E7" s="48"/>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="B8" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="C8" s="33">
+        <f>EOMONTH(EDATE(BS!C1,C7+2),0)</f>
+        <v>45900</v>
+      </c>
+      <c r="E8" s="48"/>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="E9" s="34"/>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="B10" s="45" t="s">
+        <v>440</v>
+      </c>
+      <c r="C10" s="46"/>
+      <c r="E10" s="34"/>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="B11" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="C11" s="365" t="str">
+        <f>Thesis!C11</f>
+        <v>0639.HK</v>
+      </c>
+      <c r="D11" s="49"/>
+      <c r="E11" s="34"/>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="B12" s="4" t="s">
+        <v>484</v>
+      </c>
+      <c r="C12" s="366">
+        <f>Market_Price</f>
+        <v>2.94</v>
+      </c>
+      <c r="D12" s="50"/>
+      <c r="E12" s="48"/>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="B13" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="C13" s="32" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+      <c r="D13" s="48"/>
+      <c r="E13" s="5"/>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="B14" s="4" t="s">
+        <v>486</v>
+      </c>
+      <c r="C14" s="35">
+        <f>投资主题!C12*Common_Shares/1000000</f>
+        <v>14967.7333638</v>
+      </c>
+      <c r="D14" s="35" t="str">
+        <f>IF(D11="","",投资主题!D12*Common_Shares/1000000)</f>
+        <v/>
+      </c>
+      <c r="E14" s="5"/>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="B15" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="C15" s="32" t="str">
+        <f>IF(C25=C13,C13,C25&amp;"/"&amp;C13)</f>
+        <v>HKD</v>
+      </c>
+      <c r="D15" s="32" t="str">
+        <f>IF(D11="","",IF(C25=D13,D13,C25&amp;"/"&amp;D13))</f>
+        <v/>
+      </c>
+      <c r="E15" s="5"/>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="B16" s="4" t="s">
+        <v>488</v>
+      </c>
+      <c r="C16" s="366">
+        <f>Exchange_Rate</f>
+        <v>1</v>
+      </c>
+      <c r="D16" s="50"/>
+      <c r="E16" s="5"/>
+    </row>
+    <row r="17" spans="2:6">
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+    </row>
+    <row r="18" spans="2:6" ht="24.6" customHeight="1">
+      <c r="B18" s="367" t="s">
+        <v>489</v>
+      </c>
+      <c r="C18" s="367"/>
+      <c r="D18" s="367"/>
+      <c r="E18" s="367"/>
+      <c r="F18" s="367"/>
+    </row>
+    <row r="20" spans="2:6">
+      <c r="B20" s="45" t="s">
+        <v>490</v>
+      </c>
+      <c r="C20" s="46"/>
+      <c r="D20" s="5"/>
+    </row>
+    <row r="21" spans="2:6">
+      <c r="B21" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="C21" s="32" t="str">
+        <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
+        <v xml:space="preserve">Low Growth </v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="E21" s="363" t="str">
+        <f>valuation_method</f>
+        <v>DCF</v>
+      </c>
+    </row>
+    <row r="22" spans="2:6">
+      <c r="B22" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="C22" s="32" t="str">
+        <f>Thesis!C22</f>
+        <v>MAT_01</v>
+      </c>
+      <c r="D22" s="1" t="str">
+        <f>IF(valuation_method="DDM","终值贴现率","")</f>
+        <v/>
+      </c>
+      <c r="E22" s="364">
+        <f>Thesis!E22</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="2:6">
+      <c r="B23" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="C23" s="253" t="str">
+        <f>Thesis!C23</f>
+        <v>N</v>
+      </c>
+    </row>
+    <row r="24" spans="2:6">
+      <c r="B24" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="C24" s="253" t="str">
+        <f>Thesis!C24</f>
+        <v>N</v>
+      </c>
+    </row>
+    <row r="25" spans="2:6">
+      <c r="B25" s="4" t="s">
+        <v>445</v>
+      </c>
+      <c r="C25" s="32" t="str">
+        <f>Reporting_currency</f>
+        <v>HKD</v>
+      </c>
+      <c r="D25" s="32" t="str">
+        <f>IF(D11="","",Market_currency&amp;"/"&amp;D13&amp;":")</f>
+        <v/>
+      </c>
+      <c r="E25" s="299" t="str">
+        <f>IF(D11="","",1/Exchange_Rate*D16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="2:6">
+      <c r="B26" s="1" t="str">
+        <f>"预期股权价值 ("&amp;C13&amp;") :"</f>
+        <v>预期股权价值 (HKD) :</v>
+      </c>
+      <c r="C26" s="304">
+        <f>C132</f>
+        <v>4.4858408799140586</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="E26" s="301">
+        <f ca="1">Scenarios!C87</f>
+        <v>0.23204925986510649</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6">
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+    </row>
+    <row r="28" spans="2:6">
+      <c r="B28" s="45" t="s">
+        <v>448</v>
+      </c>
+      <c r="C28" s="309" t="str">
+        <f>C145&amp;" ("&amp;Market_currency&amp;")"</f>
+        <v>0639.HK (HKD)</v>
+      </c>
+      <c r="D28" s="309" t="str">
+        <f>IF(D11="","",D145&amp;" ("&amp;D13&amp;")")</f>
+        <v/>
+      </c>
+      <c r="E28" s="305" t="s">
+        <v>453</v>
+      </c>
+      <c r="F28" s="361">
+        <f>Thesis!F28</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="2:6">
+      <c r="B29" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="C29" s="310">
+        <f>C149</f>
+        <v>2.2811221378505544</v>
+      </c>
+      <c r="D29" s="310" t="str">
+        <f>D149</f>
+        <v/>
+      </c>
+      <c r="E29" s="306" t="s">
+        <v>455</v>
+      </c>
+      <c r="F29" s="362">
+        <f>Thesis!F29</f>
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6">
+      <c r="B30" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="C30" s="311">
+        <f>C157</f>
+        <v>2.823790530515998</v>
+      </c>
+      <c r="D30" s="311" t="str">
+        <f>D157</f>
+        <v/>
+      </c>
+      <c r="E30" s="307" t="s">
+        <v>454</v>
+      </c>
+      <c r="F30" s="224">
+        <f>Thesis!F30</f>
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="31" spans="2:6">
+      <c r="B31" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="C31" s="311">
+        <f>C165</f>
+        <v>4.3130669791905083</v>
+      </c>
+      <c r="D31" s="311" t="str">
+        <f>D165</f>
+        <v/>
+      </c>
+      <c r="E31" s="307" t="s">
+        <v>491</v>
+      </c>
+      <c r="F31" s="224">
+        <f>Thesis!F31</f>
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="2:6">
+      <c r="B32" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="C32" s="311">
+        <f>C173</f>
+        <v>3.8666759160925035</v>
+      </c>
+      <c r="D32" s="311" t="str">
+        <f>D173</f>
+        <v/>
+      </c>
+      <c r="E32" s="307" t="s">
+        <v>456</v>
+      </c>
+      <c r="F32" s="224">
+        <f>Thesis!F32</f>
+        <v>0.1174</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="D33" s="5"/>
+      <c r="E33" s="5"/>
+    </row>
+    <row r="34" spans="1:6" ht="13.9">
+      <c r="A34" s="222" t="s">
+        <v>457</v>
+      </c>
+      <c r="B34" s="36"/>
+      <c r="C34" s="36"/>
+      <c r="D34" s="36"/>
+      <c r="E34" s="36"/>
+      <c r="F34" s="36"/>
+    </row>
+    <row r="36" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B36" s="367" t="s">
+        <v>492</v>
+      </c>
+      <c r="C36" s="367"/>
+      <c r="D36" s="367"/>
+      <c r="E36" s="367"/>
+      <c r="F36" s="367"/>
+    </row>
+    <row r="37" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B37" s="369" t="s">
+        <v>330</v>
+      </c>
+      <c r="C37" s="369"/>
+      <c r="D37" s="369"/>
+      <c r="E37" s="369"/>
+      <c r="F37" s="369"/>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="B39" s="210" t="s">
+        <v>493</v>
+      </c>
+      <c r="C39" s="108">
+        <f>scaling_factor</f>
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
+      <c r="B40" s="368" t="s">
+        <v>494</v>
+      </c>
+      <c r="C40" s="368"/>
+      <c r="D40" s="368"/>
+      <c r="E40" s="368"/>
+      <c r="F40" s="368"/>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="B41" s="47" t="s">
+        <v>228</v>
+      </c>
+      <c r="C41" s="349">
+        <f>Normalized_FCF!C8</f>
+        <v>1880349.4511684938</v>
+      </c>
+      <c r="D41" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
+      <c r="B42" s="47"/>
+      <c r="C42" s="76"/>
+    </row>
+    <row r="43" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B43" s="368" t="s">
+        <v>495</v>
+      </c>
+      <c r="C43" s="368"/>
+      <c r="D43" s="368"/>
+      <c r="E43" s="368"/>
+      <c r="F43" s="368"/>
+    </row>
+    <row r="44" spans="1:6">
+      <c r="B44" s="47" t="s">
+        <v>230</v>
+      </c>
+      <c r="C44" s="349">
+        <f>Normalized_FCF!C9</f>
+        <v>0</v>
+      </c>
+      <c r="D44" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6">
+      <c r="B45" s="52" t="s">
+        <v>231</v>
+      </c>
+      <c r="C45" s="349">
+        <f>Normalized_FCF!C10</f>
+        <v>0</v>
+      </c>
+      <c r="D45" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6">
+      <c r="B47" s="368" t="s">
+        <v>496</v>
+      </c>
+      <c r="C47" s="368"/>
+      <c r="D47" s="368"/>
+      <c r="E47" s="368"/>
+      <c r="F47" s="368"/>
+    </row>
+    <row r="48" spans="1:6">
+      <c r="B48" s="47" t="s">
+        <v>233</v>
+      </c>
+      <c r="C48" s="349">
+        <f>Normalized_FCF!C11</f>
+        <v>0</v>
+      </c>
+      <c r="D48" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="50" spans="2:6">
+      <c r="B50" s="368" t="s">
+        <v>497</v>
+      </c>
+      <c r="C50" s="368"/>
+      <c r="D50" s="368"/>
+      <c r="E50" s="368"/>
+      <c r="F50" s="368"/>
+    </row>
+    <row r="51" spans="2:6">
+      <c r="B51" s="47" t="s">
+        <v>331</v>
+      </c>
+      <c r="C51" s="350">
+        <f>Normalized_FCF!C48</f>
+        <v>20769.589399157529</v>
+      </c>
+      <c r="D51" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>HKD</v>
+      </c>
+      <c r="E51" s="286"/>
+      <c r="F51" s="286"/>
+    </row>
+    <row r="52" spans="2:6">
+      <c r="B52" s="47" t="s">
+        <v>332</v>
+      </c>
+      <c r="C52" s="350">
+        <f>Normalized_FCF!C47</f>
+        <v>-1746</v>
+      </c>
+      <c r="D52" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>HKD</v>
+      </c>
+      <c r="E52" s="286"/>
+      <c r="F52" s="286"/>
+    </row>
+    <row r="53" spans="2:6">
+      <c r="B53" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="C53" s="349">
+        <f>Normalized_FCF!C12</f>
+        <v>19023.589399157529</v>
+      </c>
+      <c r="D53" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="55" spans="2:6">
+      <c r="B55" s="1" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="56" spans="2:6">
+      <c r="B56" s="47" t="s">
+        <v>261</v>
+      </c>
+      <c r="C56" s="349">
+        <f>Normalized_FCF!C15</f>
+        <v>-332702.30828345218</v>
+      </c>
+      <c r="D56" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="58" spans="2:6">
+      <c r="B58" s="368" t="s">
+        <v>237</v>
+      </c>
+      <c r="C58" s="368"/>
+      <c r="D58" s="368"/>
+      <c r="E58" s="368"/>
+      <c r="F58" s="368"/>
+    </row>
+    <row r="59" spans="2:6">
+      <c r="B59" s="47" t="s">
+        <v>235</v>
+      </c>
+      <c r="C59" s="349">
+        <f>Normalized_FCF!C14</f>
+        <v>-474843.26014191285</v>
+      </c>
+      <c r="D59" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="61" spans="2:6">
+      <c r="B61" s="368" t="s">
+        <v>499</v>
+      </c>
+      <c r="C61" s="371"/>
+      <c r="D61" s="371"/>
+      <c r="E61" s="371"/>
+      <c r="F61" s="371"/>
+    </row>
+    <row r="62" spans="2:6">
+      <c r="B62" s="47" t="s">
+        <v>238</v>
+      </c>
+      <c r="C62" s="349">
+        <f>Normalized_FCF!C17</f>
+        <v>0</v>
+      </c>
+      <c r="D62" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="64" spans="2:6">
+      <c r="B64" s="367" t="s">
+        <v>500</v>
+      </c>
+      <c r="C64" s="367"/>
+      <c r="D64" s="367"/>
+      <c r="E64" s="367"/>
+      <c r="F64" s="367"/>
+    </row>
+    <row r="65" spans="1:6">
+      <c r="B65" s="367" t="s">
+        <v>501</v>
+      </c>
+      <c r="C65" s="367"/>
+      <c r="D65" s="367"/>
+      <c r="E65" s="367"/>
+      <c r="F65" s="367"/>
+    </row>
+    <row r="67" spans="1:6">
+      <c r="B67" s="47" t="s">
+        <v>502</v>
+      </c>
+      <c r="C67" s="349">
+        <f>Normalized_FCF!G19</f>
+        <v>1274085.3895235579</v>
+      </c>
+      <c r="D67" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6">
+      <c r="B68" s="47" t="s">
+        <v>244</v>
+      </c>
+      <c r="C68" s="349">
+        <f>Normalized_FCF!C19</f>
+        <v>1091827.4721422864</v>
+      </c>
+      <c r="D68" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6">
+      <c r="B69" s="227" t="s">
+        <v>371</v>
+      </c>
+      <c r="C69" s="92">
+        <f>Normalized_FCF!C126</f>
+        <v>7.2945411680228764E-2</v>
+      </c>
+      <c r="F69" s="314"/>
+    </row>
+    <row r="70" spans="1:6">
+      <c r="B70" s="227" t="s">
+        <v>434</v>
+      </c>
+      <c r="C70" s="92">
+        <f>Normalized_FCF!C94</f>
+        <v>9.1836734693877556E-2</v>
+      </c>
+      <c r="E70" s="47" t="s">
+        <v>503</v>
+      </c>
+      <c r="F70" s="315">
+        <f>Normalized_FCF!C92</f>
+        <v>1.3988654526188369</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6">
+      <c r="B72" s="210" t="s">
+        <v>513</v>
+      </c>
+      <c r="C72" s="323" t="s">
+        <v>429</v>
+      </c>
+      <c r="D72" s="323" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6">
+      <c r="B73" s="47" t="s">
+        <v>428</v>
+      </c>
+      <c r="C73" s="92">
+        <f>Normalized_FCF!C121</f>
+        <v>0.10048924474005361</v>
+      </c>
+      <c r="D73" s="92">
+        <f>Normalized_FCF!G121</f>
+        <v>0.12199804433766272</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6">
+      <c r="B74" s="259" t="str">
+        <f>Normalized_FCF!B118</f>
+        <v>Pre-tax Profit/Sales</v>
+      </c>
+      <c r="C74" s="322">
+        <f>Normalized_FCF!C118</f>
+        <v>0.42143224397986156</v>
+      </c>
+      <c r="D74" s="322">
+        <f>Normalized_FCF!G118</f>
+        <v>0.45598504835348186</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6">
+      <c r="B75" s="259" t="str">
+        <f>Normalized_FCF!B119</f>
+        <v>Sales/Total Assets</v>
+      </c>
+      <c r="C75" s="324">
+        <f>Normalized_FCF!C119</f>
+        <v>0.19639123104483397</v>
+      </c>
+      <c r="D75" s="324">
+        <f>Normalized_FCF!G119</f>
+        <v>0.22035988512352028</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6">
+      <c r="B76" s="259" t="str">
+        <f>Normalized_FCF!B120</f>
+        <v>Total Assets/Equity</v>
+      </c>
+      <c r="C76" s="324">
+        <f>Normalized_FCF!C120</f>
+        <v>1.2141426890285656</v>
+      </c>
+      <c r="D76" s="324">
+        <f>Normalized_FCF!G120</f>
+        <v>1.2141426890285656</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" ht="13.9">
+      <c r="A78" s="222" t="s">
+        <v>505</v>
+      </c>
+      <c r="B78" s="36"/>
+      <c r="C78" s="36"/>
+      <c r="D78" s="36"/>
+      <c r="E78" s="36"/>
+      <c r="F78" s="36"/>
+    </row>
+    <row r="79" spans="1:6">
+      <c r="A79" s="209"/>
+    </row>
+    <row r="80" spans="1:6">
+      <c r="A80" s="17"/>
+      <c r="B80" s="367" t="s">
+        <v>506</v>
+      </c>
+      <c r="C80" s="367"/>
+      <c r="D80" s="367"/>
+      <c r="E80" s="367"/>
+      <c r="F80" s="367"/>
+    </row>
+    <row r="81" spans="1:6">
+      <c r="B81" s="369" t="s">
+        <v>248</v>
+      </c>
+      <c r="C81" s="369"/>
+      <c r="D81" s="369"/>
+      <c r="E81" s="369"/>
+      <c r="F81" s="369"/>
+    </row>
+    <row r="83" spans="1:6">
+      <c r="B83" s="210" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6">
+      <c r="B84" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="C84" s="92">
+        <f>F31</f>
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6">
+      <c r="B85" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="C85" s="92">
+        <f>IF(C23="Y",1%,0)+IF(C24="Y",1%,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6">
+      <c r="B86" s="80" t="s">
+        <v>243</v>
+      </c>
+      <c r="C86" s="236">
+        <f>F31+C85</f>
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6">
+      <c r="C87" s="121"/>
+    </row>
+    <row r="88" spans="1:6">
+      <c r="B88" s="293" t="s">
+        <v>512</v>
+      </c>
+      <c r="C88" s="121"/>
+    </row>
+    <row r="89" spans="1:6">
+      <c r="B89" s="367" t="s">
+        <v>507</v>
+      </c>
+      <c r="C89" s="367"/>
+      <c r="D89" s="367"/>
+      <c r="E89" s="367"/>
+      <c r="F89" s="367"/>
+    </row>
+    <row r="90" spans="1:6">
+      <c r="B90" s="367" t="s">
+        <v>508</v>
+      </c>
+      <c r="C90" s="367"/>
+      <c r="D90" s="367"/>
+      <c r="E90" s="367"/>
+      <c r="F90" s="367"/>
+    </row>
+    <row r="92" spans="1:6">
+      <c r="B92" s="47" t="s">
+        <v>247</v>
+      </c>
+      <c r="C92" s="236">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6">
+      <c r="B93" s="47" t="s">
+        <v>275</v>
+      </c>
+      <c r="C93" s="223">
+        <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <v>2.8594601378649682</v>
+      </c>
+      <c r="D93" s="1" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" ht="13.9">
+      <c r="A95" s="222" t="s">
+        <v>509</v>
+      </c>
+      <c r="B95" s="36"/>
+      <c r="C95" s="36"/>
+      <c r="D95" s="36"/>
+      <c r="E95" s="36"/>
+      <c r="F95" s="36"/>
+    </row>
+    <row r="96" spans="1:6">
+      <c r="A96" s="209"/>
+    </row>
+    <row r="97" spans="2:6">
+      <c r="B97" s="367" t="s">
+        <v>510</v>
+      </c>
+      <c r="C97" s="367"/>
+      <c r="D97" s="367"/>
+      <c r="E97" s="367"/>
+      <c r="F97" s="367"/>
+    </row>
+    <row r="98" spans="2:6">
+      <c r="B98" s="1" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="100" spans="2:6">
+      <c r="B100" s="210" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="101" spans="2:6">
+      <c r="B101" s="367" t="s">
+        <v>511</v>
+      </c>
+      <c r="C101" s="367"/>
+      <c r="D101" s="367"/>
+      <c r="E101" s="367"/>
+      <c r="F101" s="367"/>
+    </row>
+    <row r="102" spans="2:6">
+      <c r="B102" s="47" t="s">
+        <v>251</v>
+      </c>
+      <c r="C102" s="349">
+        <f>DCF!C7</f>
+        <v>43677</v>
+      </c>
+      <c r="D102" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="103" spans="2:6">
+      <c r="B103" s="47" t="s">
+        <v>276</v>
+      </c>
+      <c r="C103" s="223">
+        <f>C102*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <v>8.5791466803226933E-3</v>
+      </c>
+      <c r="D103" s="1" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="104" spans="2:6">
+      <c r="B104" s="296" t="s">
+        <v>384</v>
+      </c>
+      <c r="C104" s="325">
+        <f>IF(BS!G31/BS!G27&gt;300%,"nm",BS!G31/BS!G27)</f>
+        <v>2.3107986944995245E-3</v>
+      </c>
+    </row>
+    <row r="105" spans="2:6">
+      <c r="B105" s="296" t="s">
+        <v>386</v>
+      </c>
+      <c r="C105" s="326">
+        <f>IF(BS!C50&gt;30,"nm",BS!C50)</f>
+        <v>2.3228129203780753E-2</v>
+      </c>
+    </row>
+    <row r="107" spans="2:6">
+      <c r="B107" s="1" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="108" spans="2:6">
+      <c r="B108" s="47" t="s">
+        <v>260</v>
+      </c>
+      <c r="C108" s="349">
+        <f>BS!C66</f>
+        <v>10118429</v>
+      </c>
+      <c r="D108" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="109" spans="2:6">
+      <c r="B109" s="47" t="s">
+        <v>262</v>
+      </c>
+      <c r="C109" s="349">
+        <f>DCF!C8</f>
+        <v>8041470.060084247</v>
+      </c>
+      <c r="D109" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="110" spans="2:6">
+      <c r="B110" s="47" t="s">
+        <v>277</v>
+      </c>
+      <c r="C110" s="223">
+        <f>C109*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <v>1.5795258642050989</v>
+      </c>
+      <c r="D110" s="1" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="112" spans="2:6">
+      <c r="B112" s="1" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6">
+      <c r="B113" s="47" t="s">
+        <v>253</v>
+      </c>
+      <c r="C113" s="349">
+        <f>DCF!C9</f>
+        <v>263512.2</v>
+      </c>
+      <c r="D113" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6">
+      <c r="B114" s="47" t="s">
+        <v>278</v>
+      </c>
+      <c r="C114" s="223">
+        <f>C113*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <v>5.1759732029547124E-2</v>
+      </c>
+      <c r="D114" s="1" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6">
+      <c r="B116" s="367" t="s">
+        <v>516</v>
+      </c>
+      <c r="C116" s="367"/>
+      <c r="D116" s="367"/>
+      <c r="E116" s="367"/>
+      <c r="F116" s="367"/>
+    </row>
+    <row r="118" spans="1:6">
+      <c r="B118" s="47" t="s">
+        <v>517</v>
+      </c>
+      <c r="C118" s="223">
+        <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
+        <v>4.4821665874192913</v>
+      </c>
+      <c r="D118" s="1" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6">
+      <c r="B119" s="296" t="s">
+        <v>550</v>
+      </c>
+      <c r="C119" s="223">
+        <f>BS!D47</f>
+        <v>0.79833937207218564</v>
+      </c>
+      <c r="D119" s="1" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" ht="13.9">
+      <c r="A121" s="222" t="s">
+        <v>518</v>
+      </c>
+      <c r="B121" s="36"/>
+      <c r="C121" s="36"/>
+      <c r="D121" s="36"/>
+      <c r="E121" s="36"/>
+      <c r="F121" s="36"/>
+    </row>
+    <row r="123" spans="1:6">
+      <c r="B123" s="368" t="s">
+        <v>519</v>
+      </c>
+      <c r="C123" s="368"/>
+      <c r="D123" s="368"/>
+      <c r="E123" s="368"/>
+      <c r="F123" s="368"/>
+    </row>
+    <row r="125" spans="1:6" ht="12.4">
+      <c r="B125" s="233" t="s">
+        <v>520</v>
+      </c>
+      <c r="C125" s="233" t="s">
+        <v>521</v>
+      </c>
+      <c r="D125" s="233" t="s">
+        <v>108</v>
+      </c>
+      <c r="E125" s="233" t="s">
+        <v>522</v>
+      </c>
+      <c r="F125" s="233" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6">
+      <c r="B126" s="228" t="str">
+        <f>DCF!B74</f>
+        <v>Snowball Scenario</v>
+      </c>
+      <c r="C126" s="229">
+        <f>DCF!C74</f>
+        <v>0.04</v>
+      </c>
+      <c r="D126" s="230">
+        <f>DCF!D74</f>
+        <v>10</v>
+      </c>
+      <c r="E126" s="231" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E74,DDM!E69),2)&amp;" "&amp;Market_currency</f>
+        <v>4.86 HKD</v>
+      </c>
+      <c r="F126" s="232">
+        <f>DCF!F74</f>
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6">
+      <c r="B127" s="218" t="str">
+        <f>DCF!B75</f>
+        <v>Optimistic</v>
+      </c>
+      <c r="C127" s="219">
+        <f>DCF!C75</f>
+        <v>0.02</v>
+      </c>
+      <c r="D127" s="220">
+        <f>DCF!D75</f>
+        <v>5</v>
+      </c>
+      <c r="E127" s="231" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E75,DDM!E70),2)&amp;" "&amp;Market_currency</f>
+        <v>4.57 HKD</v>
+      </c>
+      <c r="F127" s="221">
+        <f>DCF!F75</f>
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6">
+      <c r="B128" s="218" t="str">
+        <f>DCF!B76</f>
+        <v>Base</v>
+      </c>
+      <c r="C128" s="219">
+        <f>DCF!C76</f>
+        <v>0</v>
+      </c>
+      <c r="D128" s="220">
+        <f>DCF!D76</f>
+        <v>5</v>
+      </c>
+      <c r="E128" s="231" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E76,DDM!E71),2)&amp;" "&amp;Market_currency</f>
+        <v>4.48 HKD</v>
+      </c>
+      <c r="F128" s="221">
+        <f>DCF!F76</f>
+        <v>0.53999999999999992</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6">
+      <c r="B129" s="218" t="str">
+        <f>DCF!B77</f>
+        <v>Pessimistic</v>
+      </c>
+      <c r="C129" s="219">
+        <f>DCF!C77</f>
+        <v>-0.02</v>
+      </c>
+      <c r="D129" s="220">
+        <f>DCF!D77</f>
+        <v>5</v>
+      </c>
+      <c r="E129" s="231" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E77,DDM!E72),2)&amp;" "&amp;Market_currency</f>
+        <v>4.39 HKD</v>
+      </c>
+      <c r="F129" s="221">
+        <f>DCF!F77</f>
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6">
+      <c r="B130" s="218" t="str">
+        <f>DCF!B78</f>
+        <v>Devil's advocate</v>
+      </c>
+      <c r="C130" s="219">
+        <f>DCF!C78</f>
+        <v>-0.04</v>
+      </c>
+      <c r="D130" s="220">
+        <f>DCF!D78</f>
+        <v>10</v>
+      </c>
+      <c r="E130" s="231" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E78,DDM!E73),2)&amp;" "&amp;Market_currency</f>
+        <v>4.17 HKD</v>
+      </c>
+      <c r="F130" s="221">
+        <f>DCF!F78</f>
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6">
+      <c r="B132" s="211" t="s">
+        <v>254</v>
+      </c>
+      <c r="C132" s="217">
+        <f>Scenarios!C60</f>
+        <v>4.4858408799140586</v>
+      </c>
+      <c r="D132" s="212" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6">
+      <c r="B134" s="372" t="s">
+        <v>524</v>
+      </c>
+      <c r="C134" s="372"/>
+      <c r="D134" s="372"/>
+      <c r="E134" s="372"/>
+      <c r="F134" s="372"/>
+    </row>
+    <row r="136" spans="1:6" ht="13.9">
+      <c r="A136" s="222" t="s">
+        <v>525</v>
+      </c>
+      <c r="B136" s="36"/>
+      <c r="C136" s="36"/>
+      <c r="D136" s="36"/>
+      <c r="E136" s="36"/>
+      <c r="F136" s="36"/>
+    </row>
+    <row r="138" spans="1:6">
+      <c r="B138" s="370" t="s">
+        <v>526</v>
+      </c>
+      <c r="C138" s="370"/>
+      <c r="D138" s="370"/>
+      <c r="E138" s="370"/>
+      <c r="F138" s="370"/>
+    </row>
+    <row r="139" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B139" s="367" t="s">
+        <v>527</v>
+      </c>
+      <c r="C139" s="367"/>
+      <c r="D139" s="367"/>
+      <c r="E139" s="367"/>
+      <c r="F139" s="367"/>
+    </row>
+    <row r="140" spans="1:6">
+      <c r="B140" s="210" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6">
+      <c r="B141" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="C141" s="225">
+        <f>F28</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6">
+      <c r="B142" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="C142" s="224">
+        <f>F29</f>
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6">
+      <c r="B143" s="212" t="s">
+        <v>530</v>
+      </c>
+      <c r="C143" s="213">
+        <f>Scenarios!C77</f>
+        <v>0.27</v>
+      </c>
+      <c r="D143" s="212" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="145" spans="2:4">
+      <c r="B145" s="210" t="s">
+        <v>531</v>
+      </c>
+      <c r="C145" s="241" t="str">
+        <f>C11</f>
+        <v>0639.HK</v>
+      </c>
+      <c r="D145" s="241" t="str">
+        <f>IF(D11="","",D11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="146" spans="2:4">
+      <c r="B146" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="C146" s="297">
+        <f>F29</f>
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="147" spans="2:4">
+      <c r="B147" s="212" t="str">
+        <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
+        <v>PV(3 yrs of Dividends)</v>
+      </c>
+      <c r="C147" s="216">
+        <f>Scenarios!C81</f>
+        <v>0.45788751714677645</v>
+      </c>
+    </row>
+    <row r="148" spans="2:4">
+      <c r="B148" s="212" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
+        <v>+ PV(Equity Value realized at year 3)</v>
+      </c>
+      <c r="C148" s="216">
+        <f>Scenarios!C82</f>
+        <v>1.823234620703778</v>
+      </c>
+    </row>
+    <row r="149" spans="2:4">
+      <c r="B149" s="80" t="s">
+        <v>256</v>
+      </c>
+      <c r="C149" s="215">
+        <f>Scenarios!C83</f>
+        <v>2.2811221378505544</v>
+      </c>
+      <c r="D149" s="300" t="str">
+        <f>IF($D$11="","",C149*$E$25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="150" spans="2:4">
+      <c r="B150" s="259" t="s">
+        <v>532</v>
+      </c>
+      <c r="C150" s="298" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+      <c r="D150" s="298" t="str">
+        <f>IF($D$11="","",D$13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="151" spans="2:4">
+      <c r="B151" s="214" t="s">
+        <v>533</v>
+      </c>
+      <c r="C151" s="92">
+        <f>Scenarios!F83</f>
+        <v>0.49148393825902781</v>
+      </c>
+    </row>
+    <row r="153" spans="2:4">
+      <c r="B153" s="210" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="154" spans="2:4">
+      <c r="B154" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="C154" s="297">
+        <f>Scenarios!C90</f>
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="155" spans="2:4">
+      <c r="B155" s="212" t="str">
+        <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
+        <v>PV(3 yrs of Dividends)</v>
+      </c>
+      <c r="C155" s="216">
+        <f>Scenarios!C91</f>
+        <v>0.52704000000000006</v>
+      </c>
+    </row>
+    <row r="156" spans="2:4">
+      <c r="B156" s="212" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
+        <v>+ PV(Equity Value realized at year 3)</v>
+      </c>
+      <c r="C156" s="216">
+        <f>Scenarios!C92</f>
+        <v>2.2967505305159981</v>
+      </c>
+    </row>
+    <row r="157" spans="2:4">
+      <c r="B157" s="80" t="s">
+        <v>256</v>
+      </c>
+      <c r="C157" s="215">
+        <f>Scenarios!C93</f>
+        <v>2.823790530515998</v>
+      </c>
+      <c r="D157" s="300" t="str">
+        <f>IF($D$11="","",C157*$E$25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="158" spans="2:4">
+      <c r="B158" s="259" t="s">
+        <v>532</v>
+      </c>
+      <c r="C158" s="298" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+      <c r="D158" s="298" t="str">
+        <f>IF($D$11="","",D$13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="159" spans="2:4">
+      <c r="B159" s="214" t="s">
+        <v>533</v>
+      </c>
+      <c r="C159" s="92">
+        <f>Scenarios!F93</f>
+        <v>0.37051032212045443</v>
+      </c>
+    </row>
+    <row r="161" spans="2:4">
+      <c r="B161" s="210" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="162" spans="2:4">
+      <c r="B162" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="C162" s="92">
+        <f>Scenarios!C96</f>
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="163" spans="2:4">
+      <c r="B163" s="212" t="str">
+        <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
+        <v>PV(3 yrs of Dividends)</v>
+      </c>
+      <c r="C163" s="216">
+        <f>Scenarios!C97</f>
+        <v>0.70214194976542921</v>
+      </c>
+    </row>
+    <row r="164" spans="2:4">
+      <c r="B164" s="212" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
+        <v>+ PV(Equity Value realized at year 3)</v>
+      </c>
+      <c r="C164" s="216">
+        <f>Scenarios!C98</f>
+        <v>3.6109250294250792</v>
+      </c>
+    </row>
+    <row r="165" spans="2:4">
+      <c r="B165" s="80" t="s">
+        <v>382</v>
+      </c>
+      <c r="C165" s="215">
+        <f>Scenarios!C99</f>
+        <v>4.3130669791905083</v>
+      </c>
+      <c r="D165" s="300" t="str">
+        <f>IF($D$11="","",C165*$E$25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="166" spans="2:4">
+      <c r="B166" s="259" t="s">
+        <v>532</v>
+      </c>
+      <c r="C166" s="298" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+      <c r="D166" s="298" t="str">
+        <f>IF($D$11="","",D$13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="167" spans="2:4">
+      <c r="B167" s="214" t="s">
+        <v>533</v>
+      </c>
+      <c r="C167" s="92">
+        <f>Scenarios!F99</f>
+        <v>3.8515387716307137E-2</v>
+      </c>
+    </row>
+    <row r="169" spans="2:4">
+      <c r="B169" s="210" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="170" spans="2:4">
+      <c r="B170" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="C170" s="92">
+        <f>F32</f>
+        <v>0.1174</v>
+      </c>
+    </row>
+    <row r="171" spans="2:4">
+      <c r="B171" s="212" t="str">
+        <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
+        <v>PV(3 yrs of Dividends)</v>
+      </c>
+      <c r="C171" s="216">
+        <f>Scenarios!C103</f>
+        <v>0.65140284400343529</v>
+      </c>
+    </row>
+    <row r="172" spans="2:4">
+      <c r="B172" s="212" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
+        <v>+ PV(Equity Value realized at year 3)</v>
+      </c>
+      <c r="C172" s="216">
+        <f>Scenarios!C104</f>
+        <v>3.2152730720890683</v>
+      </c>
+    </row>
+    <row r="173" spans="2:4">
+      <c r="B173" s="80" t="s">
+        <v>382</v>
+      </c>
+      <c r="C173" s="215">
+        <f>Scenarios!C105</f>
+        <v>3.8666759160925035</v>
+      </c>
+      <c r="D173" s="300" t="str">
+        <f>IF($D$11="","",C173*$E$25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="174" spans="2:4">
+      <c r="B174" s="259" t="s">
+        <v>532</v>
+      </c>
+      <c r="C174" s="298" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+      <c r="D174" s="298" t="str">
+        <f>IF($D$11="","",D$13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="175" spans="2:4">
+      <c r="B175" s="214" t="s">
+        <v>533</v>
+      </c>
+      <c r="C175" s="92">
+        <f>Scenarios!F105</f>
+        <v>0.13842067503200794</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6" ht="13.9">
+      <c r="A177" s="222" t="s">
+        <v>357</v>
+      </c>
+      <c r="B177" s="36"/>
+      <c r="C177" s="36"/>
+      <c r="D177" s="36"/>
+      <c r="E177" s="36"/>
+      <c r="F177" s="36"/>
+    </row>
+    <row r="179" spans="1:6">
+      <c r="B179" s="374" t="s">
+        <v>534</v>
+      </c>
+      <c r="C179" s="367"/>
+      <c r="D179" s="367"/>
+      <c r="E179" s="367"/>
+      <c r="F179" s="367"/>
+    </row>
+    <row r="181" spans="1:6">
+      <c r="B181" s="210" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6">
+      <c r="B182" s="371" t="s">
+        <v>536</v>
+      </c>
+      <c r="C182" s="371"/>
+      <c r="D182" s="371"/>
+      <c r="E182" s="371"/>
+      <c r="F182" s="371"/>
+    </row>
+    <row r="183" spans="1:6">
+      <c r="B183" s="214" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6">
+      <c r="B184" s="214" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6">
+      <c r="B185" s="214" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6">
+      <c r="B187" s="1" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B188" s="368" t="s">
+        <v>541</v>
+      </c>
+      <c r="C188" s="368"/>
+      <c r="D188" s="368"/>
+      <c r="E188" s="368"/>
+      <c r="F188" s="368"/>
+    </row>
+    <row r="190" spans="1:6">
+      <c r="B190" s="1" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6">
+      <c r="B191" s="373" t="s">
+        <v>543</v>
+      </c>
+      <c r="C191" s="373"/>
+      <c r="D191" s="373"/>
+      <c r="E191" s="373"/>
+      <c r="F191" s="373"/>
+    </row>
+    <row r="192" spans="1:6">
+      <c r="B192" s="373" t="s">
+        <v>544</v>
+      </c>
+      <c r="C192" s="373"/>
+      <c r="D192" s="373"/>
+      <c r="E192" s="373"/>
+      <c r="F192" s="373"/>
+    </row>
+    <row r="194" spans="2:2">
+      <c r="B194" s="1" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="195" spans="2:2">
+      <c r="B195" s="214" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="196" spans="2:2">
+      <c r="B196" s="214" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="197" spans="2:2">
+      <c r="B197" s="214" t="s">
+        <v>548</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="27">
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B138:F138"/>
+    <mergeCell ref="B139:F139"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B116:F116"/>
+    <mergeCell ref="B50:F50"/>
+    <mergeCell ref="B58:F58"/>
+    <mergeCell ref="B61:F61"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B65:F65"/>
+    <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B90:F90"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B43:F43"/>
+  </mergeCells>
+  <dataValidations count="5">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">
+      <formula1>"INT,CN"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E21 E25" xr:uid="{0BE1D34E-D50B-41CB-99F3-E9F8694C38CA}">
+      <formula1>"DCF,DDM"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="C25:D25" xr:uid="{4F076B80-6574-480B-B48C-99BFFF6B4B13}">
+      <formula1>"HKD,USD,CNY,EUR"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C23:C24" xr:uid="{B605A743-B0FC-4D89-AD54-945707F01FA1}">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1" xr:uid="{CF966412-2762-45A3-9589-2A9D9DD6B905}">
+      <formula1>"Y, N"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="85" fitToHeight="0" orientation="portrait" verticalDpi="300" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1687E01B-0970-4659-AAA7-C41D486D7CC3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4598C18A-B422-4B33-9718-91EF341533D1}">
   <dimension ref="B2:E2"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="2.59765625" style="369" customWidth="1"/>
-    <col min="2" max="2" width="22.73046875" style="369" customWidth="1"/>
-    <col min="3" max="5" width="20.73046875" style="369" customWidth="1"/>
-    <col min="6" max="16384" width="9.06640625" style="369"/>
+    <col min="1" max="1" width="2.59765625" style="381" customWidth="1"/>
+    <col min="2" max="2" width="22.73046875" style="381" customWidth="1"/>
+    <col min="3" max="5" width="20.73046875" style="381" customWidth="1"/>
+    <col min="6" max="16384" width="9.06640625" style="381"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:5" ht="13.9">
-      <c r="B2" s="367" t="s">
+      <c r="B2" s="379" t="s">
         <v>436</v>
       </c>
-      <c r="C2" s="368"/>
-      <c r="D2" s="368"/>
-      <c r="E2" s="368"/>
+      <c r="C2" s="380"/>
+      <c r="D2" s="380"/>
+      <c r="E2" s="380"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/financial_models/opportunities/0639.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0639.HK_Valuation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55A3B1C7-5A34-4A72-9935-C58B1AF26FF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DD414D0-28A9-46E6-B859-60BBC6EF11F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2205" yWindow="2205" windowWidth="12690" windowHeight="7642" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4751,29 +4751,34 @@
     <xf numFmtId="4" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="1" xfId="2"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4787,11 +4792,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="1" xfId="2"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -5282,7 +5282,7 @@
         <v>463</v>
       </c>
       <c r="C12" s="50">
-        <v>2.94</v>
+        <v>2.99</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -5303,7 +5303,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>14967.7333638</v>
+        <v>15222.286652300001</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -5340,13 +5340,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="367" t="s">
+      <c r="B18" s="372" t="s">
         <v>468</v>
       </c>
-      <c r="C18" s="367"/>
-      <c r="D18" s="367"/>
-      <c r="E18" s="367"/>
-      <c r="F18" s="367"/>
+      <c r="C18" s="372"/>
+      <c r="D18" s="372"/>
+      <c r="E18" s="372"/>
+      <c r="F18" s="372"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -5429,7 +5429,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.23204925986510649</v>
+        <v>0.22462837980630135</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -5546,22 +5546,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6">
-      <c r="B36" s="367" t="s">
+      <c r="B36" s="372" t="s">
         <v>469</v>
       </c>
-      <c r="C36" s="367"/>
-      <c r="D36" s="367"/>
-      <c r="E36" s="367"/>
-      <c r="F36" s="367"/>
+      <c r="C36" s="372"/>
+      <c r="D36" s="372"/>
+      <c r="E36" s="372"/>
+      <c r="F36" s="372"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="369" t="s">
+      <c r="B37" s="375" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="369"/>
-      <c r="D37" s="369"/>
-      <c r="E37" s="369"/>
-      <c r="F37" s="369"/>
+      <c r="C37" s="375"/>
+      <c r="D37" s="375"/>
+      <c r="E37" s="375"/>
+      <c r="F37" s="375"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -5573,13 +5573,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="368" t="s">
+      <c r="B40" s="373" t="s">
         <v>227</v>
       </c>
-      <c r="C40" s="368"/>
-      <c r="D40" s="368"/>
-      <c r="E40" s="368"/>
-      <c r="F40" s="368"/>
+      <c r="C40" s="373"/>
+      <c r="D40" s="373"/>
+      <c r="E40" s="373"/>
+      <c r="F40" s="373"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -5599,13 +5599,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="368" t="s">
+      <c r="B43" s="373" t="s">
         <v>229</v>
       </c>
-      <c r="C43" s="368"/>
-      <c r="D43" s="368"/>
-      <c r="E43" s="368"/>
-      <c r="F43" s="368"/>
+      <c r="C43" s="373"/>
+      <c r="D43" s="373"/>
+      <c r="E43" s="373"/>
+      <c r="F43" s="373"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -5634,13 +5634,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="368" t="s">
+      <c r="B47" s="373" t="s">
         <v>232</v>
       </c>
-      <c r="C47" s="368"/>
-      <c r="D47" s="368"/>
-      <c r="E47" s="368"/>
-      <c r="F47" s="368"/>
+      <c r="C47" s="373"/>
+      <c r="D47" s="373"/>
+      <c r="E47" s="373"/>
+      <c r="F47" s="373"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -5656,13 +5656,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="368" t="s">
+      <c r="B50" s="373" t="s">
         <v>236</v>
       </c>
-      <c r="C50" s="368"/>
-      <c r="D50" s="368"/>
-      <c r="E50" s="368"/>
-      <c r="F50" s="368"/>
+      <c r="C50" s="373"/>
+      <c r="D50" s="373"/>
+      <c r="E50" s="373"/>
+      <c r="F50" s="373"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -5726,13 +5726,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="368" t="s">
+      <c r="B58" s="373" t="s">
         <v>237</v>
       </c>
-      <c r="C58" s="368"/>
-      <c r="D58" s="368"/>
-      <c r="E58" s="368"/>
-      <c r="F58" s="368"/>
+      <c r="C58" s="373"/>
+      <c r="D58" s="373"/>
+      <c r="E58" s="373"/>
+      <c r="F58" s="373"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -5748,13 +5748,13 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="368" t="s">
+      <c r="B61" s="373" t="s">
         <v>329</v>
       </c>
-      <c r="C61" s="371"/>
-      <c r="D61" s="371"/>
-      <c r="E61" s="371"/>
-      <c r="F61" s="371"/>
+      <c r="C61" s="374"/>
+      <c r="D61" s="374"/>
+      <c r="E61" s="374"/>
+      <c r="F61" s="374"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -5770,22 +5770,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="367" t="s">
+      <c r="B64" s="372" t="s">
         <v>334</v>
       </c>
-      <c r="C64" s="367"/>
-      <c r="D64" s="367"/>
-      <c r="E64" s="367"/>
-      <c r="F64" s="367"/>
+      <c r="C64" s="372"/>
+      <c r="D64" s="372"/>
+      <c r="E64" s="372"/>
+      <c r="F64" s="372"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="367" t="s">
+      <c r="B65" s="372" t="s">
         <v>348</v>
       </c>
-      <c r="C65" s="367"/>
-      <c r="D65" s="367"/>
-      <c r="E65" s="367"/>
-      <c r="F65" s="367"/>
+      <c r="C65" s="372"/>
+      <c r="D65" s="372"/>
+      <c r="E65" s="372"/>
+      <c r="F65" s="372"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -5819,7 +5819,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>7.2945411680228764E-2</v>
+        <v>7.1725588742432289E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -5829,7 +5829,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>9.1836734693877556E-2</v>
+        <v>9.0301003344481601E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>424</v>
@@ -5920,22 +5920,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="367" t="s">
+      <c r="B80" s="372" t="s">
         <v>471</v>
       </c>
-      <c r="C80" s="367"/>
-      <c r="D80" s="367"/>
-      <c r="E80" s="367"/>
-      <c r="F80" s="367"/>
+      <c r="C80" s="372"/>
+      <c r="D80" s="372"/>
+      <c r="E80" s="372"/>
+      <c r="F80" s="372"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="369" t="s">
+      <c r="B81" s="375" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="369"/>
-      <c r="D81" s="369"/>
-      <c r="E81" s="369"/>
-      <c r="F81" s="369"/>
+      <c r="C81" s="375"/>
+      <c r="D81" s="375"/>
+      <c r="E81" s="375"/>
+      <c r="F81" s="375"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5979,22 +5979,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="367" t="s">
+      <c r="B89" s="372" t="s">
         <v>349</v>
       </c>
-      <c r="C89" s="367"/>
-      <c r="D89" s="367"/>
-      <c r="E89" s="367"/>
-      <c r="F89" s="367"/>
+      <c r="C89" s="372"/>
+      <c r="D89" s="372"/>
+      <c r="E89" s="372"/>
+      <c r="F89" s="372"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="367" t="s">
+      <c r="B90" s="372" t="s">
         <v>350</v>
       </c>
-      <c r="C90" s="367"/>
-      <c r="D90" s="367"/>
-      <c r="E90" s="367"/>
-      <c r="F90" s="367"/>
+      <c r="C90" s="372"/>
+      <c r="D90" s="372"/>
+      <c r="E90" s="372"/>
+      <c r="F90" s="372"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -6031,13 +6031,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="367" t="s">
+      <c r="B97" s="372" t="s">
         <v>351</v>
       </c>
-      <c r="C97" s="367"/>
-      <c r="D97" s="367"/>
-      <c r="E97" s="367"/>
-      <c r="F97" s="367"/>
+      <c r="C97" s="372"/>
+      <c r="D97" s="372"/>
+      <c r="E97" s="372"/>
+      <c r="F97" s="372"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -6050,13 +6050,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="367" t="s">
+      <c r="B101" s="372" t="s">
         <v>335</v>
       </c>
-      <c r="C101" s="367"/>
-      <c r="D101" s="367"/>
-      <c r="E101" s="367"/>
-      <c r="F101" s="367"/>
+      <c r="C101" s="372"/>
+      <c r="D101" s="372"/>
+      <c r="E101" s="372"/>
+      <c r="F101" s="372"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -6178,13 +6178,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="367" t="s">
+      <c r="B116" s="372" t="s">
         <v>352</v>
       </c>
-      <c r="C116" s="367"/>
-      <c r="D116" s="367"/>
-      <c r="E116" s="367"/>
-      <c r="F116" s="367"/>
+      <c r="C116" s="372"/>
+      <c r="D116" s="372"/>
+      <c r="E116" s="372"/>
+      <c r="F116" s="372"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -6223,13 +6223,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="368" t="s">
+      <c r="B123" s="373" t="s">
         <v>473</v>
       </c>
-      <c r="C123" s="368"/>
-      <c r="D123" s="368"/>
-      <c r="E123" s="368"/>
-      <c r="F123" s="368"/>
+      <c r="C123" s="373"/>
+      <c r="D123" s="373"/>
+      <c r="E123" s="373"/>
+      <c r="F123" s="373"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -6372,13 +6372,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="372" t="s">
+      <c r="B134" s="376" t="s">
         <v>474</v>
       </c>
-      <c r="C134" s="372"/>
-      <c r="D134" s="372"/>
-      <c r="E134" s="372"/>
-      <c r="F134" s="372"/>
+      <c r="C134" s="376"/>
+      <c r="D134" s="376"/>
+      <c r="E134" s="376"/>
+      <c r="F134" s="376"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -6391,22 +6391,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="370" t="s">
+      <c r="B138" s="377" t="s">
         <v>353</v>
       </c>
-      <c r="C138" s="370"/>
-      <c r="D138" s="370"/>
-      <c r="E138" s="370"/>
-      <c r="F138" s="370"/>
+      <c r="C138" s="377"/>
+      <c r="D138" s="377"/>
+      <c r="E138" s="377"/>
+      <c r="F138" s="377"/>
     </row>
     <row r="139" spans="1:6">
-      <c r="B139" s="367" t="s">
+      <c r="B139" s="372" t="s">
         <v>476</v>
       </c>
-      <c r="C139" s="367"/>
-      <c r="D139" s="367"/>
-      <c r="E139" s="367"/>
-      <c r="F139" s="367"/>
+      <c r="C139" s="372"/>
+      <c r="D139" s="372"/>
+      <c r="E139" s="372"/>
+      <c r="F139" s="372"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -6739,13 +6739,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="374" t="s">
+      <c r="B179" s="371" t="s">
         <v>477</v>
       </c>
-      <c r="C179" s="367"/>
-      <c r="D179" s="367"/>
-      <c r="E179" s="367"/>
-      <c r="F179" s="367"/>
+      <c r="C179" s="372"/>
+      <c r="D179" s="372"/>
+      <c r="E179" s="372"/>
+      <c r="F179" s="372"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -6753,13 +6753,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="371" t="s">
+      <c r="B182" s="374" t="s">
         <v>362</v>
       </c>
-      <c r="C182" s="371"/>
-      <c r="D182" s="371"/>
-      <c r="E182" s="371"/>
-      <c r="F182" s="371"/>
+      <c r="C182" s="374"/>
+      <c r="D182" s="374"/>
+      <c r="E182" s="374"/>
+      <c r="F182" s="374"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -6782,13 +6782,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="34.35" customHeight="1">
-      <c r="B188" s="368" t="s">
+      <c r="B188" s="373" t="s">
         <v>478</v>
       </c>
-      <c r="C188" s="368"/>
-      <c r="D188" s="368"/>
-      <c r="E188" s="368"/>
-      <c r="F188" s="368"/>
+      <c r="C188" s="373"/>
+      <c r="D188" s="373"/>
+      <c r="E188" s="373"/>
+      <c r="F188" s="373"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -6796,22 +6796,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="373" t="s">
+      <c r="B191" s="370" t="s">
         <v>363</v>
       </c>
-      <c r="C191" s="373"/>
-      <c r="D191" s="373"/>
-      <c r="E191" s="373"/>
-      <c r="F191" s="373"/>
+      <c r="C191" s="370"/>
+      <c r="D191" s="370"/>
+      <c r="E191" s="370"/>
+      <c r="F191" s="370"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="373" t="s">
+      <c r="B192" s="370" t="s">
         <v>364</v>
       </c>
-      <c r="C192" s="373"/>
-      <c r="D192" s="373"/>
-      <c r="E192" s="373"/>
-      <c r="F192" s="373"/>
+      <c r="C192" s="370"/>
+      <c r="D192" s="370"/>
+      <c r="E192" s="370"/>
+      <c r="F192" s="370"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -6835,17 +6835,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -6862,6 +6851,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -14405,20 +14405,20 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>9.1836734693877556E-2</v>
+        <v>9.0301003344481601E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>9.1836734693877556E-2</v>
+        <v>9.0301003344481601E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>8.5714285714285729E-2</v>
+        <v>8.4280936454849506E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>0.13163265306122451</v>
+        <v>0.12943143812709032</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
@@ -15604,50 +15604,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>7.2945411680228764E-2</v>
+        <v>7.1725588742432289E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>8.5122132961359356E-2</v>
+        <v>8.3698685921871727E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>0.11713335311268476</v>
+        <v>0.11517460138839236</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>0.18996651226551578</v>
+        <v>0.1867898147359921</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>0.1560872891514116</v>
+        <v>0.15347713381443145</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>5.5996053619384825E-2</v>
+        <v>5.505966476287337E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>7.1086180795638693E-2</v>
+        <v>6.9897448675310281E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>6.3292749608380758E-2</v>
+        <v>6.2234342424294112E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>6.0113510718737759E-2</v>
+        <v>5.9108268064578258E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>1.0641290576782635E-2</v>
+        <v>1.0463342573826404E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>4.6097828123311006E-3</v>
+        <v>4.5326961432285732E-3</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -15661,43 +15661,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12125917504580769</v>
+        <v>0.11923142964370387</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15372654924257945</v>
+        <v>0.15115587116159984</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.22101910286569454</v>
+        <v>0.21732313124586683</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.20449529167874742</v>
+        <v>0.20107563797174491</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.9322832064304849E-2</v>
+        <v>7.7996363300687696E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.8578430775934266E-2</v>
+        <v>7.7264410194396893E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.6960750970215652E-2</v>
+        <v>7.5673781890446157E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.9008890074172611E-2</v>
+        <v>7.7687671176611184E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.520123278226513E-3</v>
+        <v>4.4445359324367713E-3</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-4.7533917307795437E-2</v>
+        <v>-4.6739035747464401E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16485,10 +16485,10 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E6" s="375" t="s">
+      <c r="E6" s="378" t="s">
         <v>245</v>
       </c>
-      <c r="F6" s="375"/>
+      <c r="F6" s="378"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8">
@@ -16503,8 +16503,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E7" s="375"/>
-      <c r="F7" s="375"/>
+      <c r="E7" s="378"/>
+      <c r="F7" s="378"/>
       <c r="H7" s="120"/>
     </row>
     <row r="8" spans="2:8">
@@ -16519,8 +16519,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E8" s="375"/>
-      <c r="F8" s="375"/>
+      <c r="E8" s="378"/>
+      <c r="F8" s="378"/>
       <c r="H8" s="120"/>
     </row>
     <row r="9" spans="2:8">
@@ -16535,8 +16535,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E9" s="375"/>
-      <c r="F9" s="375"/>
+      <c r="E9" s="378"/>
+      <c r="F9" s="378"/>
       <c r="H9" s="120"/>
     </row>
     <row r="10" spans="2:8" ht="13.15">
@@ -18245,8 +18245,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E6" s="375"/>
-      <c r="F6" s="375"/>
+      <c r="E6" s="378"/>
+      <c r="F6" s="378"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8" ht="13.15">
@@ -19647,7 +19647,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-2.94</v>
+        <v>-2.99</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -19711,11 +19711,11 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E7" s="377" t="str">
+      <c r="E7" s="380" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 5-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 10-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 首钢资源(0639.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="377"/>
+      <c r="F7" s="380"/>
       <c r="H7" s="247">
         <v>4</v>
       </c>
@@ -19736,8 +19736,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E8" s="377"/>
-      <c r="F8" s="377"/>
+      <c r="E8" s="380"/>
+      <c r="F8" s="380"/>
       <c r="H8" s="247">
         <v>5</v>
       </c>
@@ -19758,8 +19758,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E9" s="377"/>
-      <c r="F9" s="377"/>
+      <c r="E9" s="380"/>
+      <c r="F9" s="380"/>
       <c r="H9" s="247">
         <v>6</v>
       </c>
@@ -19769,8 +19769,8 @@
       </c>
     </row>
     <row r="10" spans="2:9">
-      <c r="E10" s="377"/>
-      <c r="F10" s="377"/>
+      <c r="E10" s="380"/>
+      <c r="F10" s="380"/>
       <c r="H10" s="247">
         <v>7</v>
       </c>
@@ -19783,8 +19783,8 @@
       <c r="B11" s="159" t="s">
         <v>423</v>
       </c>
-      <c r="E11" s="377"/>
-      <c r="F11" s="377"/>
+      <c r="E11" s="380"/>
+      <c r="F11" s="380"/>
       <c r="H11" s="247">
         <v>8</v>
       </c>
@@ -19802,8 +19802,8 @@
         <v>-0.1059288114314666</v>
       </c>
       <c r="D12" s="158"/>
-      <c r="E12" s="377"/>
-      <c r="F12" s="377"/>
+      <c r="E12" s="380"/>
+      <c r="F12" s="380"/>
       <c r="H12" s="247">
         <v>9</v>
       </c>
@@ -19820,8 +19820,8 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.1663504856430581</v>
       </c>
-      <c r="E13" s="377"/>
-      <c r="F13" s="377"/>
+      <c r="E13" s="380"/>
+      <c r="F13" s="380"/>
       <c r="H13" s="247">
         <v>10</v>
       </c>
@@ -19838,8 +19838,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.18299448813777219</v>
       </c>
-      <c r="E14" s="377"/>
-      <c r="F14" s="377"/>
+      <c r="E14" s="380"/>
+      <c r="F14" s="380"/>
     </row>
     <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
@@ -19865,21 +19865,21 @@
       <c r="C18" s="150">
         <v>5</v>
       </c>
-      <c r="E18" s="377" t="s">
+      <c r="E18" s="380" t="s">
         <v>321</v>
       </c>
-      <c r="F18" s="378"/>
+      <c r="F18" s="381"/>
     </row>
     <row r="19" spans="2:6">
-      <c r="E19" s="378"/>
-      <c r="F19" s="378"/>
+      <c r="E19" s="381"/>
+      <c r="F19" s="381"/>
     </row>
     <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="159" t="s">
         <v>298</v>
       </c>
-      <c r="E20" s="378"/>
-      <c r="F20" s="378"/>
+      <c r="E20" s="381"/>
+      <c r="F20" s="381"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
@@ -19887,14 +19887,14 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>2.94</v>
+        <v>2.99</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E21" s="378"/>
-      <c r="F21" s="378"/>
+      <c r="E21" s="381"/>
+      <c r="F21" s="381"/>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
@@ -19908,8 +19908,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E22" s="378"/>
-      <c r="F22" s="378"/>
+      <c r="E22" s="381"/>
+      <c r="F22" s="381"/>
     </row>
     <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="159" t="s">
@@ -19929,8 +19929,8 @@
         <v>5</v>
       </c>
       <c r="D25" s="163"/>
-      <c r="E25" s="376"/>
-      <c r="F25" s="376"/>
+      <c r="E25" s="379"/>
+      <c r="F25" s="379"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="118" t="s">
@@ -19940,8 +19940,8 @@
         <v>0</v>
       </c>
       <c r="D26" s="164"/>
-      <c r="E26" s="376"/>
-      <c r="F26" s="376"/>
+      <c r="E26" s="379"/>
+      <c r="F26" s="379"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
@@ -19955,8 +19955,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E27" s="376"/>
-      <c r="F27" s="376"/>
+      <c r="E27" s="379"/>
+      <c r="F27" s="379"/>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
@@ -19966,8 +19966,8 @@
         <v>0.6</v>
       </c>
       <c r="D28" s="165"/>
-      <c r="E28" s="376"/>
-      <c r="F28" s="376"/>
+      <c r="E28" s="379"/>
+      <c r="F28" s="379"/>
     </row>
     <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="159" t="s">
@@ -19987,8 +19987,8 @@
         <v>5</v>
       </c>
       <c r="D31" s="163"/>
-      <c r="E31" s="376"/>
-      <c r="F31" s="376"/>
+      <c r="E31" s="379"/>
+      <c r="F31" s="379"/>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="118" t="s">
@@ -19998,8 +19998,8 @@
         <v>-0.02</v>
       </c>
       <c r="D32" s="164"/>
-      <c r="E32" s="376"/>
-      <c r="F32" s="376"/>
+      <c r="E32" s="379"/>
+      <c r="F32" s="379"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
@@ -20013,8 +20013,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E33" s="376"/>
-      <c r="F33" s="376"/>
+      <c r="E33" s="379"/>
+      <c r="F33" s="379"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
@@ -20024,8 +20024,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="165"/>
-      <c r="E34" s="376"/>
-      <c r="F34" s="376"/>
+      <c r="E34" s="379"/>
+      <c r="F34" s="379"/>
     </row>
     <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="159" t="s">
@@ -20045,8 +20045,8 @@
         <v>5</v>
       </c>
       <c r="D37" s="163"/>
-      <c r="E37" s="376"/>
-      <c r="F37" s="376"/>
+      <c r="E37" s="379"/>
+      <c r="F37" s="379"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="118" t="s">
@@ -20056,8 +20056,8 @@
         <v>0.02</v>
       </c>
       <c r="D38" s="164"/>
-      <c r="E38" s="376"/>
-      <c r="F38" s="376"/>
+      <c r="E38" s="379"/>
+      <c r="F38" s="379"/>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
@@ -20071,8 +20071,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E39" s="376"/>
-      <c r="F39" s="376"/>
+      <c r="E39" s="379"/>
+      <c r="F39" s="379"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
@@ -20083,8 +20083,8 @@
         <v>0.2</v>
       </c>
       <c r="D40" s="165"/>
-      <c r="E40" s="376"/>
-      <c r="F40" s="376"/>
+      <c r="E40" s="379"/>
+      <c r="F40" s="379"/>
     </row>
     <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
@@ -20146,8 +20146,8 @@
         <v>10</v>
       </c>
       <c r="D49" s="163"/>
-      <c r="E49" s="376"/>
-      <c r="F49" s="376"/>
+      <c r="E49" s="379"/>
+      <c r="F49" s="379"/>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="118" t="s">
@@ -20157,8 +20157,8 @@
         <v>-0.04</v>
       </c>
       <c r="D50" s="164"/>
-      <c r="E50" s="376"/>
-      <c r="F50" s="376"/>
+      <c r="E50" s="379"/>
+      <c r="F50" s="379"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
@@ -20172,8 +20172,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E51" s="376"/>
-      <c r="F51" s="376"/>
+      <c r="E51" s="379"/>
+      <c r="F51" s="379"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
@@ -20183,8 +20183,8 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="165"/>
-      <c r="E52" s="376"/>
-      <c r="F52" s="376"/>
+      <c r="E52" s="379"/>
+      <c r="F52" s="379"/>
     </row>
     <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="159" t="s">
@@ -20204,8 +20204,8 @@
         <v>10</v>
       </c>
       <c r="D55" s="163"/>
-      <c r="E55" s="376"/>
-      <c r="F55" s="376"/>
+      <c r="E55" s="379"/>
+      <c r="F55" s="379"/>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="118" t="s">
@@ -20215,8 +20215,8 @@
         <v>0.04</v>
       </c>
       <c r="D56" s="164"/>
-      <c r="E56" s="376"/>
-      <c r="F56" s="376"/>
+      <c r="E56" s="379"/>
+      <c r="F56" s="379"/>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
@@ -20230,8 +20230,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E57" s="376"/>
-      <c r="F57" s="376"/>
+      <c r="E57" s="379"/>
+      <c r="F57" s="379"/>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
@@ -20241,8 +20241,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="165"/>
-      <c r="E58" s="376"/>
-      <c r="F58" s="376"/>
+      <c r="E58" s="379"/>
+      <c r="F58" s="379"/>
     </row>
     <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
@@ -20485,7 +20485,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>2.94</v>
+        <v>2.99</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -20498,7 +20498,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.23204925986510649</v>
+        <v>0.22462837980630135</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -20851,7 +20851,7 @@
       </c>
       <c r="C12" s="366">
         <f>Market_Price</f>
-        <v>2.94</v>
+        <v>2.99</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -20873,7 +20873,7 @@
       </c>
       <c r="C14" s="35">
         <f>投资主题!C12*Common_Shares/1000000</f>
-        <v>14967.7333638</v>
+        <v>15222.286652300001</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",投资主题!D12*Common_Shares/1000000)</f>
@@ -20911,13 +20911,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="367" t="s">
+      <c r="B18" s="372" t="s">
         <v>489</v>
       </c>
-      <c r="C18" s="367"/>
-      <c r="D18" s="367"/>
-      <c r="E18" s="367"/>
-      <c r="F18" s="367"/>
+      <c r="C18" s="372"/>
+      <c r="D18" s="372"/>
+      <c r="E18" s="372"/>
+      <c r="F18" s="372"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -21008,7 +21008,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.23204925986510649</v>
+        <v>0.22462837980630135</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -21130,22 +21130,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="367" t="s">
+      <c r="B36" s="372" t="s">
         <v>492</v>
       </c>
-      <c r="C36" s="367"/>
-      <c r="D36" s="367"/>
-      <c r="E36" s="367"/>
-      <c r="F36" s="367"/>
+      <c r="C36" s="372"/>
+      <c r="D36" s="372"/>
+      <c r="E36" s="372"/>
+      <c r="F36" s="372"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="369" t="s">
+      <c r="B37" s="375" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="369"/>
-      <c r="D37" s="369"/>
-      <c r="E37" s="369"/>
-      <c r="F37" s="369"/>
+      <c r="C37" s="375"/>
+      <c r="D37" s="375"/>
+      <c r="E37" s="375"/>
+      <c r="F37" s="375"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -21157,13 +21157,13 @@
       </c>
     </row>
     <row r="40" spans="1:6">
-      <c r="B40" s="368" t="s">
+      <c r="B40" s="373" t="s">
         <v>494</v>
       </c>
-      <c r="C40" s="368"/>
-      <c r="D40" s="368"/>
-      <c r="E40" s="368"/>
-      <c r="F40" s="368"/>
+      <c r="C40" s="373"/>
+      <c r="D40" s="373"/>
+      <c r="E40" s="373"/>
+      <c r="F40" s="373"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -21183,13 +21183,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="368" t="s">
+      <c r="B43" s="373" t="s">
         <v>495</v>
       </c>
-      <c r="C43" s="368"/>
-      <c r="D43" s="368"/>
-      <c r="E43" s="368"/>
-      <c r="F43" s="368"/>
+      <c r="C43" s="373"/>
+      <c r="D43" s="373"/>
+      <c r="E43" s="373"/>
+      <c r="F43" s="373"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -21218,13 +21218,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="368" t="s">
+      <c r="B47" s="373" t="s">
         <v>496</v>
       </c>
-      <c r="C47" s="368"/>
-      <c r="D47" s="368"/>
-      <c r="E47" s="368"/>
-      <c r="F47" s="368"/>
+      <c r="C47" s="373"/>
+      <c r="D47" s="373"/>
+      <c r="E47" s="373"/>
+      <c r="F47" s="373"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -21240,13 +21240,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="368" t="s">
+      <c r="B50" s="373" t="s">
         <v>497</v>
       </c>
-      <c r="C50" s="368"/>
-      <c r="D50" s="368"/>
-      <c r="E50" s="368"/>
-      <c r="F50" s="368"/>
+      <c r="C50" s="373"/>
+      <c r="D50" s="373"/>
+      <c r="E50" s="373"/>
+      <c r="F50" s="373"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -21310,13 +21310,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="368" t="s">
+      <c r="B58" s="373" t="s">
         <v>237</v>
       </c>
-      <c r="C58" s="368"/>
-      <c r="D58" s="368"/>
-      <c r="E58" s="368"/>
-      <c r="F58" s="368"/>
+      <c r="C58" s="373"/>
+      <c r="D58" s="373"/>
+      <c r="E58" s="373"/>
+      <c r="F58" s="373"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -21332,13 +21332,13 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="368" t="s">
+      <c r="B61" s="373" t="s">
         <v>499</v>
       </c>
-      <c r="C61" s="371"/>
-      <c r="D61" s="371"/>
-      <c r="E61" s="371"/>
-      <c r="F61" s="371"/>
+      <c r="C61" s="374"/>
+      <c r="D61" s="374"/>
+      <c r="E61" s="374"/>
+      <c r="F61" s="374"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -21354,22 +21354,22 @@
       </c>
     </row>
     <row r="64" spans="2:6">
-      <c r="B64" s="367" t="s">
+      <c r="B64" s="372" t="s">
         <v>500</v>
       </c>
-      <c r="C64" s="367"/>
-      <c r="D64" s="367"/>
-      <c r="E64" s="367"/>
-      <c r="F64" s="367"/>
+      <c r="C64" s="372"/>
+      <c r="D64" s="372"/>
+      <c r="E64" s="372"/>
+      <c r="F64" s="372"/>
     </row>
     <row r="65" spans="1:6">
-      <c r="B65" s="367" t="s">
+      <c r="B65" s="372" t="s">
         <v>501</v>
       </c>
-      <c r="C65" s="367"/>
-      <c r="D65" s="367"/>
-      <c r="E65" s="367"/>
-      <c r="F65" s="367"/>
+      <c r="C65" s="372"/>
+      <c r="D65" s="372"/>
+      <c r="E65" s="372"/>
+      <c r="F65" s="372"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -21403,7 +21403,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>7.2945411680228764E-2</v>
+        <v>7.1725588742432289E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -21413,7 +21413,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>9.1836734693877556E-2</v>
+        <v>9.0301003344481601E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>503</v>
@@ -21504,22 +21504,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="367" t="s">
+      <c r="B80" s="372" t="s">
         <v>506</v>
       </c>
-      <c r="C80" s="367"/>
-      <c r="D80" s="367"/>
-      <c r="E80" s="367"/>
-      <c r="F80" s="367"/>
+      <c r="C80" s="372"/>
+      <c r="D80" s="372"/>
+      <c r="E80" s="372"/>
+      <c r="F80" s="372"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="369" t="s">
+      <c r="B81" s="375" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="369"/>
-      <c r="D81" s="369"/>
-      <c r="E81" s="369"/>
-      <c r="F81" s="369"/>
+      <c r="C81" s="375"/>
+      <c r="D81" s="375"/>
+      <c r="E81" s="375"/>
+      <c r="F81" s="375"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -21563,22 +21563,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6">
-      <c r="B89" s="367" t="s">
+      <c r="B89" s="372" t="s">
         <v>507</v>
       </c>
-      <c r="C89" s="367"/>
-      <c r="D89" s="367"/>
-      <c r="E89" s="367"/>
-      <c r="F89" s="367"/>
+      <c r="C89" s="372"/>
+      <c r="D89" s="372"/>
+      <c r="E89" s="372"/>
+      <c r="F89" s="372"/>
     </row>
     <row r="90" spans="1:6">
-      <c r="B90" s="367" t="s">
+      <c r="B90" s="372" t="s">
         <v>508</v>
       </c>
-      <c r="C90" s="367"/>
-      <c r="D90" s="367"/>
-      <c r="E90" s="367"/>
-      <c r="F90" s="367"/>
+      <c r="C90" s="372"/>
+      <c r="D90" s="372"/>
+      <c r="E90" s="372"/>
+      <c r="F90" s="372"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -21615,13 +21615,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="367" t="s">
+      <c r="B97" s="372" t="s">
         <v>510</v>
       </c>
-      <c r="C97" s="367"/>
-      <c r="D97" s="367"/>
-      <c r="E97" s="367"/>
-      <c r="F97" s="367"/>
+      <c r="C97" s="372"/>
+      <c r="D97" s="372"/>
+      <c r="E97" s="372"/>
+      <c r="F97" s="372"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -21634,13 +21634,13 @@
       </c>
     </row>
     <row r="101" spans="2:6">
-      <c r="B101" s="367" t="s">
+      <c r="B101" s="372" t="s">
         <v>511</v>
       </c>
-      <c r="C101" s="367"/>
-      <c r="D101" s="367"/>
-      <c r="E101" s="367"/>
-      <c r="F101" s="367"/>
+      <c r="C101" s="372"/>
+      <c r="D101" s="372"/>
+      <c r="E101" s="372"/>
+      <c r="F101" s="372"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -21762,13 +21762,13 @@
       </c>
     </row>
     <row r="116" spans="1:6">
-      <c r="B116" s="367" t="s">
+      <c r="B116" s="372" t="s">
         <v>516</v>
       </c>
-      <c r="C116" s="367"/>
-      <c r="D116" s="367"/>
-      <c r="E116" s="367"/>
-      <c r="F116" s="367"/>
+      <c r="C116" s="372"/>
+      <c r="D116" s="372"/>
+      <c r="E116" s="372"/>
+      <c r="F116" s="372"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -21807,13 +21807,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="368" t="s">
+      <c r="B123" s="373" t="s">
         <v>519</v>
       </c>
-      <c r="C123" s="368"/>
-      <c r="D123" s="368"/>
-      <c r="E123" s="368"/>
-      <c r="F123" s="368"/>
+      <c r="C123" s="373"/>
+      <c r="D123" s="373"/>
+      <c r="E123" s="373"/>
+      <c r="F123" s="373"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -21956,13 +21956,13 @@
       </c>
     </row>
     <row r="134" spans="1:6">
-      <c r="B134" s="372" t="s">
+      <c r="B134" s="376" t="s">
         <v>524</v>
       </c>
-      <c r="C134" s="372"/>
-      <c r="D134" s="372"/>
-      <c r="E134" s="372"/>
-      <c r="F134" s="372"/>
+      <c r="C134" s="376"/>
+      <c r="D134" s="376"/>
+      <c r="E134" s="376"/>
+      <c r="F134" s="376"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -21975,22 +21975,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="370" t="s">
+      <c r="B138" s="377" t="s">
         <v>526</v>
       </c>
-      <c r="C138" s="370"/>
-      <c r="D138" s="370"/>
-      <c r="E138" s="370"/>
-      <c r="F138" s="370"/>
+      <c r="C138" s="377"/>
+      <c r="D138" s="377"/>
+      <c r="E138" s="377"/>
+      <c r="F138" s="377"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="367" t="s">
+      <c r="B139" s="372" t="s">
         <v>527</v>
       </c>
-      <c r="C139" s="367"/>
-      <c r="D139" s="367"/>
-      <c r="E139" s="367"/>
-      <c r="F139" s="367"/>
+      <c r="C139" s="372"/>
+      <c r="D139" s="372"/>
+      <c r="E139" s="372"/>
+      <c r="F139" s="372"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -22323,13 +22323,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="374" t="s">
+      <c r="B179" s="371" t="s">
         <v>534</v>
       </c>
-      <c r="C179" s="367"/>
-      <c r="D179" s="367"/>
-      <c r="E179" s="367"/>
-      <c r="F179" s="367"/>
+      <c r="C179" s="372"/>
+      <c r="D179" s="372"/>
+      <c r="E179" s="372"/>
+      <c r="F179" s="372"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -22337,13 +22337,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="371" t="s">
+      <c r="B182" s="374" t="s">
         <v>536</v>
       </c>
-      <c r="C182" s="371"/>
-      <c r="D182" s="371"/>
-      <c r="E182" s="371"/>
-      <c r="F182" s="371"/>
+      <c r="C182" s="374"/>
+      <c r="D182" s="374"/>
+      <c r="E182" s="374"/>
+      <c r="F182" s="374"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -22366,13 +22366,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B188" s="368" t="s">
+      <c r="B188" s="373" t="s">
         <v>541</v>
       </c>
-      <c r="C188" s="368"/>
-      <c r="D188" s="368"/>
-      <c r="E188" s="368"/>
-      <c r="F188" s="368"/>
+      <c r="C188" s="373"/>
+      <c r="D188" s="373"/>
+      <c r="E188" s="373"/>
+      <c r="F188" s="373"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -22380,22 +22380,22 @@
       </c>
     </row>
     <row r="191" spans="1:6">
-      <c r="B191" s="373" t="s">
+      <c r="B191" s="370" t="s">
         <v>543</v>
       </c>
-      <c r="C191" s="373"/>
-      <c r="D191" s="373"/>
-      <c r="E191" s="373"/>
-      <c r="F191" s="373"/>
+      <c r="C191" s="370"/>
+      <c r="D191" s="370"/>
+      <c r="E191" s="370"/>
+      <c r="F191" s="370"/>
     </row>
     <row r="192" spans="1:6">
-      <c r="B192" s="373" t="s">
+      <c r="B192" s="370" t="s">
         <v>544</v>
       </c>
-      <c r="C192" s="373"/>
-      <c r="D192" s="373"/>
-      <c r="E192" s="373"/>
-      <c r="F192" s="373"/>
+      <c r="C192" s="370"/>
+      <c r="D192" s="370"/>
+      <c r="E192" s="370"/>
+      <c r="F192" s="370"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -22419,15 +22419,12 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B138:F138"/>
-    <mergeCell ref="B139:F139"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B43:F43"/>
     <mergeCell ref="B116:F116"/>
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B58:F58"/>
@@ -22440,12 +22437,15 @@
     <mergeCell ref="B90:F90"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B47:F47"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B138:F138"/>
+    <mergeCell ref="B139:F139"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">
@@ -22474,19 +22474,19 @@
   <dimension ref="B2:E2"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="2.59765625" style="381" customWidth="1"/>
-    <col min="2" max="2" width="22.73046875" style="381" customWidth="1"/>
-    <col min="3" max="5" width="20.73046875" style="381" customWidth="1"/>
-    <col min="6" max="16384" width="9.06640625" style="381"/>
+    <col min="1" max="1" width="2.59765625" style="369" customWidth="1"/>
+    <col min="2" max="2" width="22.73046875" style="369" customWidth="1"/>
+    <col min="3" max="5" width="20.73046875" style="369" customWidth="1"/>
+    <col min="6" max="16384" width="9.06640625" style="369"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:5" ht="13.9">
-      <c r="B2" s="379" t="s">
+      <c r="B2" s="367" t="s">
         <v>436</v>
       </c>
-      <c r="C2" s="380"/>
-      <c r="D2" s="380"/>
-      <c r="E2" s="380"/>
+      <c r="C2" s="368"/>
+      <c r="D2" s="368"/>
+      <c r="E2" s="368"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/financial_models/opportunities/0639.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0639.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DD414D0-28A9-46E6-B859-60BBC6EF11F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B82FE594-6C55-46C8-A352-C2B339E8885D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2205" yWindow="2205" windowWidth="12690" windowHeight="7642" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4756,29 +4756,29 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="59" fillId="0" borderId="1" xfId="2"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -5282,7 +5282,7 @@
         <v>463</v>
       </c>
       <c r="C12" s="50">
-        <v>2.99</v>
+        <v>2.92</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -5303,7 +5303,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>15222.286652300001</v>
+        <v>14865.9120484</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -5340,13 +5340,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="372" t="s">
+      <c r="B18" s="370" t="s">
         <v>468</v>
       </c>
-      <c r="C18" s="372"/>
-      <c r="D18" s="372"/>
-      <c r="E18" s="372"/>
-      <c r="F18" s="372"/>
+      <c r="C18" s="370"/>
+      <c r="D18" s="370"/>
+      <c r="E18" s="370"/>
+      <c r="F18" s="370"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -5429,7 +5429,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.22462837980630135</v>
+        <v>0.23506722331508234</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -5546,22 +5546,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6">
-      <c r="B36" s="372" t="s">
+      <c r="B36" s="370" t="s">
         <v>469</v>
       </c>
-      <c r="C36" s="372"/>
-      <c r="D36" s="372"/>
-      <c r="E36" s="372"/>
-      <c r="F36" s="372"/>
+      <c r="C36" s="370"/>
+      <c r="D36" s="370"/>
+      <c r="E36" s="370"/>
+      <c r="F36" s="370"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="375" t="s">
+      <c r="B37" s="372" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="375"/>
-      <c r="D37" s="375"/>
-      <c r="E37" s="375"/>
-      <c r="F37" s="375"/>
+      <c r="C37" s="372"/>
+      <c r="D37" s="372"/>
+      <c r="E37" s="372"/>
+      <c r="F37" s="372"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -5573,13 +5573,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="373" t="s">
+      <c r="B40" s="371" t="s">
         <v>227</v>
       </c>
-      <c r="C40" s="373"/>
-      <c r="D40" s="373"/>
-      <c r="E40" s="373"/>
-      <c r="F40" s="373"/>
+      <c r="C40" s="371"/>
+      <c r="D40" s="371"/>
+      <c r="E40" s="371"/>
+      <c r="F40" s="371"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -5599,13 +5599,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="373" t="s">
+      <c r="B43" s="371" t="s">
         <v>229</v>
       </c>
-      <c r="C43" s="373"/>
-      <c r="D43" s="373"/>
-      <c r="E43" s="373"/>
-      <c r="F43" s="373"/>
+      <c r="C43" s="371"/>
+      <c r="D43" s="371"/>
+      <c r="E43" s="371"/>
+      <c r="F43" s="371"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -5634,13 +5634,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="373" t="s">
+      <c r="B47" s="371" t="s">
         <v>232</v>
       </c>
-      <c r="C47" s="373"/>
-      <c r="D47" s="373"/>
-      <c r="E47" s="373"/>
-      <c r="F47" s="373"/>
+      <c r="C47" s="371"/>
+      <c r="D47" s="371"/>
+      <c r="E47" s="371"/>
+      <c r="F47" s="371"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -5656,13 +5656,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="373" t="s">
+      <c r="B50" s="371" t="s">
         <v>236</v>
       </c>
-      <c r="C50" s="373"/>
-      <c r="D50" s="373"/>
-      <c r="E50" s="373"/>
-      <c r="F50" s="373"/>
+      <c r="C50" s="371"/>
+      <c r="D50" s="371"/>
+      <c r="E50" s="371"/>
+      <c r="F50" s="371"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -5726,13 +5726,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="373" t="s">
+      <c r="B58" s="371" t="s">
         <v>237</v>
       </c>
-      <c r="C58" s="373"/>
-      <c r="D58" s="373"/>
-      <c r="E58" s="373"/>
-      <c r="F58" s="373"/>
+      <c r="C58" s="371"/>
+      <c r="D58" s="371"/>
+      <c r="E58" s="371"/>
+      <c r="F58" s="371"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -5748,7 +5748,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="373" t="s">
+      <c r="B61" s="371" t="s">
         <v>329</v>
       </c>
       <c r="C61" s="374"/>
@@ -5770,22 +5770,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="372" t="s">
+      <c r="B64" s="370" t="s">
         <v>334</v>
       </c>
-      <c r="C64" s="372"/>
-      <c r="D64" s="372"/>
-      <c r="E64" s="372"/>
-      <c r="F64" s="372"/>
+      <c r="C64" s="370"/>
+      <c r="D64" s="370"/>
+      <c r="E64" s="370"/>
+      <c r="F64" s="370"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="372" t="s">
+      <c r="B65" s="370" t="s">
         <v>348</v>
       </c>
-      <c r="C65" s="372"/>
-      <c r="D65" s="372"/>
-      <c r="E65" s="372"/>
-      <c r="F65" s="372"/>
+      <c r="C65" s="370"/>
+      <c r="D65" s="370"/>
+      <c r="E65" s="370"/>
+      <c r="F65" s="370"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -5819,7 +5819,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>7.1725588742432289E-2</v>
+        <v>7.3445037787627593E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -5829,7 +5829,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>9.0301003344481601E-2</v>
+        <v>9.2465753424657543E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>424</v>
@@ -5920,22 +5920,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="372" t="s">
+      <c r="B80" s="370" t="s">
         <v>471</v>
       </c>
-      <c r="C80" s="372"/>
-      <c r="D80" s="372"/>
-      <c r="E80" s="372"/>
-      <c r="F80" s="372"/>
+      <c r="C80" s="370"/>
+      <c r="D80" s="370"/>
+      <c r="E80" s="370"/>
+      <c r="F80" s="370"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="375" t="s">
+      <c r="B81" s="372" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="375"/>
-      <c r="D81" s="375"/>
-      <c r="E81" s="375"/>
-      <c r="F81" s="375"/>
+      <c r="C81" s="372"/>
+      <c r="D81" s="372"/>
+      <c r="E81" s="372"/>
+      <c r="F81" s="372"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5979,22 +5979,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="372" t="s">
+      <c r="B89" s="370" t="s">
         <v>349</v>
       </c>
-      <c r="C89" s="372"/>
-      <c r="D89" s="372"/>
-      <c r="E89" s="372"/>
-      <c r="F89" s="372"/>
+      <c r="C89" s="370"/>
+      <c r="D89" s="370"/>
+      <c r="E89" s="370"/>
+      <c r="F89" s="370"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="372" t="s">
+      <c r="B90" s="370" t="s">
         <v>350</v>
       </c>
-      <c r="C90" s="372"/>
-      <c r="D90" s="372"/>
-      <c r="E90" s="372"/>
-      <c r="F90" s="372"/>
+      <c r="C90" s="370"/>
+      <c r="D90" s="370"/>
+      <c r="E90" s="370"/>
+      <c r="F90" s="370"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -6031,13 +6031,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="372" t="s">
+      <c r="B97" s="370" t="s">
         <v>351</v>
       </c>
-      <c r="C97" s="372"/>
-      <c r="D97" s="372"/>
-      <c r="E97" s="372"/>
-      <c r="F97" s="372"/>
+      <c r="C97" s="370"/>
+      <c r="D97" s="370"/>
+      <c r="E97" s="370"/>
+      <c r="F97" s="370"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -6050,13 +6050,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="372" t="s">
+      <c r="B101" s="370" t="s">
         <v>335</v>
       </c>
-      <c r="C101" s="372"/>
-      <c r="D101" s="372"/>
-      <c r="E101" s="372"/>
-      <c r="F101" s="372"/>
+      <c r="C101" s="370"/>
+      <c r="D101" s="370"/>
+      <c r="E101" s="370"/>
+      <c r="F101" s="370"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -6178,13 +6178,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="372" t="s">
+      <c r="B116" s="370" t="s">
         <v>352</v>
       </c>
-      <c r="C116" s="372"/>
-      <c r="D116" s="372"/>
-      <c r="E116" s="372"/>
-      <c r="F116" s="372"/>
+      <c r="C116" s="370"/>
+      <c r="D116" s="370"/>
+      <c r="E116" s="370"/>
+      <c r="F116" s="370"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -6223,13 +6223,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="373" t="s">
+      <c r="B123" s="371" t="s">
         <v>473</v>
       </c>
-      <c r="C123" s="373"/>
-      <c r="D123" s="373"/>
-      <c r="E123" s="373"/>
-      <c r="F123" s="373"/>
+      <c r="C123" s="371"/>
+      <c r="D123" s="371"/>
+      <c r="E123" s="371"/>
+      <c r="F123" s="371"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -6372,13 +6372,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="376" t="s">
+      <c r="B134" s="375" t="s">
         <v>474</v>
       </c>
-      <c r="C134" s="376"/>
-      <c r="D134" s="376"/>
-      <c r="E134" s="376"/>
-      <c r="F134" s="376"/>
+      <c r="C134" s="375"/>
+      <c r="D134" s="375"/>
+      <c r="E134" s="375"/>
+      <c r="F134" s="375"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -6391,22 +6391,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="377" t="s">
+      <c r="B138" s="373" t="s">
         <v>353</v>
       </c>
-      <c r="C138" s="377"/>
-      <c r="D138" s="377"/>
-      <c r="E138" s="377"/>
-      <c r="F138" s="377"/>
+      <c r="C138" s="373"/>
+      <c r="D138" s="373"/>
+      <c r="E138" s="373"/>
+      <c r="F138" s="373"/>
     </row>
     <row r="139" spans="1:6">
-      <c r="B139" s="372" t="s">
+      <c r="B139" s="370" t="s">
         <v>476</v>
       </c>
-      <c r="C139" s="372"/>
-      <c r="D139" s="372"/>
-      <c r="E139" s="372"/>
-      <c r="F139" s="372"/>
+      <c r="C139" s="370"/>
+      <c r="D139" s="370"/>
+      <c r="E139" s="370"/>
+      <c r="F139" s="370"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -6739,13 +6739,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="371" t="s">
+      <c r="B179" s="377" t="s">
         <v>477</v>
       </c>
-      <c r="C179" s="372"/>
-      <c r="D179" s="372"/>
-      <c r="E179" s="372"/>
-      <c r="F179" s="372"/>
+      <c r="C179" s="370"/>
+      <c r="D179" s="370"/>
+      <c r="E179" s="370"/>
+      <c r="F179" s="370"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -6782,13 +6782,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="34.35" customHeight="1">
-      <c r="B188" s="373" t="s">
+      <c r="B188" s="371" t="s">
         <v>478</v>
       </c>
-      <c r="C188" s="373"/>
-      <c r="D188" s="373"/>
-      <c r="E188" s="373"/>
-      <c r="F188" s="373"/>
+      <c r="C188" s="371"/>
+      <c r="D188" s="371"/>
+      <c r="E188" s="371"/>
+      <c r="F188" s="371"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -6796,22 +6796,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="370" t="s">
+      <c r="B191" s="376" t="s">
         <v>363</v>
       </c>
-      <c r="C191" s="370"/>
-      <c r="D191" s="370"/>
-      <c r="E191" s="370"/>
-      <c r="F191" s="370"/>
+      <c r="C191" s="376"/>
+      <c r="D191" s="376"/>
+      <c r="E191" s="376"/>
+      <c r="F191" s="376"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="370" t="s">
+      <c r="B192" s="376" t="s">
         <v>364</v>
       </c>
-      <c r="C192" s="370"/>
-      <c r="D192" s="370"/>
-      <c r="E192" s="370"/>
-      <c r="F192" s="370"/>
+      <c r="C192" s="376"/>
+      <c r="D192" s="376"/>
+      <c r="E192" s="376"/>
+      <c r="F192" s="376"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -6835,6 +6835,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -6851,17 +6862,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -14405,20 +14405,20 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>9.0301003344481601E-2</v>
+        <v>9.2465753424657543E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>9.0301003344481601E-2</v>
+        <v>9.2465753424657543E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>8.4280936454849506E-2</v>
+        <v>8.6301369863013719E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>0.12943143812709032</v>
+        <v>0.13253424657534249</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
@@ -15604,50 +15604,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>7.1725588742432289E-2</v>
+        <v>7.3445037787627593E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>8.3698685921871727E-2</v>
+        <v>8.5705161269313865E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>0.11517460138839236</v>
+        <v>0.1179356363531826</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>0.1867898147359921</v>
+        <v>0.19126765276048507</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>0.15347713381443145</v>
+        <v>0.1571563801729966</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>5.505966476287337E-2</v>
+        <v>5.6379588233216225E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>6.9897448675310281E-2</v>
+        <v>7.1573072444923891E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>6.2234342424294112E-2</v>
+        <v>6.3726261591999803E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>5.9108268064578258E-2</v>
+        <v>6.0525247093523631E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>1.0463342573826404E-2</v>
+        <v>1.0714176128678407E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>4.5326961432285732E-3</v>
+        <v>4.6413566672100807E-3</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -15661,43 +15661,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11923142964370387</v>
+        <v>0.12208971734064199</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15115587116159984</v>
+        <v>0.1547794708127341</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.21732313124586683</v>
+        <v>0.22253293233737736</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.20107563797174491</v>
+        <v>0.20589594436147857</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.7996363300687696E-2</v>
+        <v>7.9866139133238437E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.7264410194396893E-2</v>
+        <v>7.9116639205906419E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.5673781890446157E-2</v>
+        <v>7.7487879401518495E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.7687671176611184E-2</v>
+        <v>7.9550046855502557E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.4445359324367713E-3</v>
+        <v>4.5510830267075164E-3</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-4.6739035747464401E-2</v>
+        <v>-4.7859492083876229E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -19647,7 +19647,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-2.99</v>
+        <v>-2.92</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -19887,7 +19887,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>2.99</v>
+        <v>2.92</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -20485,7 +20485,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>2.99</v>
+        <v>2.92</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -20498,7 +20498,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.22462837980630135</v>
+        <v>0.23506722331508234</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -20851,7 +20851,7 @@
       </c>
       <c r="C12" s="366">
         <f>Market_Price</f>
-        <v>2.99</v>
+        <v>2.92</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -20873,7 +20873,7 @@
       </c>
       <c r="C14" s="35">
         <f>投资主题!C12*Common_Shares/1000000</f>
-        <v>15222.286652300001</v>
+        <v>14865.9120484</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",投资主题!D12*Common_Shares/1000000)</f>
@@ -20911,13 +20911,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="372" t="s">
+      <c r="B18" s="370" t="s">
         <v>489</v>
       </c>
-      <c r="C18" s="372"/>
-      <c r="D18" s="372"/>
-      <c r="E18" s="372"/>
-      <c r="F18" s="372"/>
+      <c r="C18" s="370"/>
+      <c r="D18" s="370"/>
+      <c r="E18" s="370"/>
+      <c r="F18" s="370"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -21008,7 +21008,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.22462837980630135</v>
+        <v>0.23506722331508234</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -21130,22 +21130,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="372" t="s">
+      <c r="B36" s="370" t="s">
         <v>492</v>
       </c>
-      <c r="C36" s="372"/>
-      <c r="D36" s="372"/>
-      <c r="E36" s="372"/>
-      <c r="F36" s="372"/>
+      <c r="C36" s="370"/>
+      <c r="D36" s="370"/>
+      <c r="E36" s="370"/>
+      <c r="F36" s="370"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="375" t="s">
+      <c r="B37" s="372" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="375"/>
-      <c r="D37" s="375"/>
-      <c r="E37" s="375"/>
-      <c r="F37" s="375"/>
+      <c r="C37" s="372"/>
+      <c r="D37" s="372"/>
+      <c r="E37" s="372"/>
+      <c r="F37" s="372"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -21157,13 +21157,13 @@
       </c>
     </row>
     <row r="40" spans="1:6">
-      <c r="B40" s="373" t="s">
+      <c r="B40" s="371" t="s">
         <v>494</v>
       </c>
-      <c r="C40" s="373"/>
-      <c r="D40" s="373"/>
-      <c r="E40" s="373"/>
-      <c r="F40" s="373"/>
+      <c r="C40" s="371"/>
+      <c r="D40" s="371"/>
+      <c r="E40" s="371"/>
+      <c r="F40" s="371"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -21183,13 +21183,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="373" t="s">
+      <c r="B43" s="371" t="s">
         <v>495</v>
       </c>
-      <c r="C43" s="373"/>
-      <c r="D43" s="373"/>
-      <c r="E43" s="373"/>
-      <c r="F43" s="373"/>
+      <c r="C43" s="371"/>
+      <c r="D43" s="371"/>
+      <c r="E43" s="371"/>
+      <c r="F43" s="371"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -21218,13 +21218,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="373" t="s">
+      <c r="B47" s="371" t="s">
         <v>496</v>
       </c>
-      <c r="C47" s="373"/>
-      <c r="D47" s="373"/>
-      <c r="E47" s="373"/>
-      <c r="F47" s="373"/>
+      <c r="C47" s="371"/>
+      <c r="D47" s="371"/>
+      <c r="E47" s="371"/>
+      <c r="F47" s="371"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -21240,13 +21240,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="373" t="s">
+      <c r="B50" s="371" t="s">
         <v>497</v>
       </c>
-      <c r="C50" s="373"/>
-      <c r="D50" s="373"/>
-      <c r="E50" s="373"/>
-      <c r="F50" s="373"/>
+      <c r="C50" s="371"/>
+      <c r="D50" s="371"/>
+      <c r="E50" s="371"/>
+      <c r="F50" s="371"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -21310,13 +21310,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="373" t="s">
+      <c r="B58" s="371" t="s">
         <v>237</v>
       </c>
-      <c r="C58" s="373"/>
-      <c r="D58" s="373"/>
-      <c r="E58" s="373"/>
-      <c r="F58" s="373"/>
+      <c r="C58" s="371"/>
+      <c r="D58" s="371"/>
+      <c r="E58" s="371"/>
+      <c r="F58" s="371"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -21332,7 +21332,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="373" t="s">
+      <c r="B61" s="371" t="s">
         <v>499</v>
       </c>
       <c r="C61" s="374"/>
@@ -21354,22 +21354,22 @@
       </c>
     </row>
     <row r="64" spans="2:6">
-      <c r="B64" s="372" t="s">
+      <c r="B64" s="370" t="s">
         <v>500</v>
       </c>
-      <c r="C64" s="372"/>
-      <c r="D64" s="372"/>
-      <c r="E64" s="372"/>
-      <c r="F64" s="372"/>
+      <c r="C64" s="370"/>
+      <c r="D64" s="370"/>
+      <c r="E64" s="370"/>
+      <c r="F64" s="370"/>
     </row>
     <row r="65" spans="1:6">
-      <c r="B65" s="372" t="s">
+      <c r="B65" s="370" t="s">
         <v>501</v>
       </c>
-      <c r="C65" s="372"/>
-      <c r="D65" s="372"/>
-      <c r="E65" s="372"/>
-      <c r="F65" s="372"/>
+      <c r="C65" s="370"/>
+      <c r="D65" s="370"/>
+      <c r="E65" s="370"/>
+      <c r="F65" s="370"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -21403,7 +21403,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>7.1725588742432289E-2</v>
+        <v>7.3445037787627593E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -21413,7 +21413,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>9.0301003344481601E-2</v>
+        <v>9.2465753424657543E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>503</v>
@@ -21504,22 +21504,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="372" t="s">
+      <c r="B80" s="370" t="s">
         <v>506</v>
       </c>
-      <c r="C80" s="372"/>
-      <c r="D80" s="372"/>
-      <c r="E80" s="372"/>
-      <c r="F80" s="372"/>
+      <c r="C80" s="370"/>
+      <c r="D80" s="370"/>
+      <c r="E80" s="370"/>
+      <c r="F80" s="370"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="375" t="s">
+      <c r="B81" s="372" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="375"/>
-      <c r="D81" s="375"/>
-      <c r="E81" s="375"/>
-      <c r="F81" s="375"/>
+      <c r="C81" s="372"/>
+      <c r="D81" s="372"/>
+      <c r="E81" s="372"/>
+      <c r="F81" s="372"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -21563,22 +21563,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6">
-      <c r="B89" s="372" t="s">
+      <c r="B89" s="370" t="s">
         <v>507</v>
       </c>
-      <c r="C89" s="372"/>
-      <c r="D89" s="372"/>
-      <c r="E89" s="372"/>
-      <c r="F89" s="372"/>
+      <c r="C89" s="370"/>
+      <c r="D89" s="370"/>
+      <c r="E89" s="370"/>
+      <c r="F89" s="370"/>
     </row>
     <row r="90" spans="1:6">
-      <c r="B90" s="372" t="s">
+      <c r="B90" s="370" t="s">
         <v>508</v>
       </c>
-      <c r="C90" s="372"/>
-      <c r="D90" s="372"/>
-      <c r="E90" s="372"/>
-      <c r="F90" s="372"/>
+      <c r="C90" s="370"/>
+      <c r="D90" s="370"/>
+      <c r="E90" s="370"/>
+      <c r="F90" s="370"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -21615,13 +21615,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="372" t="s">
+      <c r="B97" s="370" t="s">
         <v>510</v>
       </c>
-      <c r="C97" s="372"/>
-      <c r="D97" s="372"/>
-      <c r="E97" s="372"/>
-      <c r="F97" s="372"/>
+      <c r="C97" s="370"/>
+      <c r="D97" s="370"/>
+      <c r="E97" s="370"/>
+      <c r="F97" s="370"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -21634,13 +21634,13 @@
       </c>
     </row>
     <row r="101" spans="2:6">
-      <c r="B101" s="372" t="s">
+      <c r="B101" s="370" t="s">
         <v>511</v>
       </c>
-      <c r="C101" s="372"/>
-      <c r="D101" s="372"/>
-      <c r="E101" s="372"/>
-      <c r="F101" s="372"/>
+      <c r="C101" s="370"/>
+      <c r="D101" s="370"/>
+      <c r="E101" s="370"/>
+      <c r="F101" s="370"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -21762,13 +21762,13 @@
       </c>
     </row>
     <row r="116" spans="1:6">
-      <c r="B116" s="372" t="s">
+      <c r="B116" s="370" t="s">
         <v>516</v>
       </c>
-      <c r="C116" s="372"/>
-      <c r="D116" s="372"/>
-      <c r="E116" s="372"/>
-      <c r="F116" s="372"/>
+      <c r="C116" s="370"/>
+      <c r="D116" s="370"/>
+      <c r="E116" s="370"/>
+      <c r="F116" s="370"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -21807,13 +21807,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="373" t="s">
+      <c r="B123" s="371" t="s">
         <v>519</v>
       </c>
-      <c r="C123" s="373"/>
-      <c r="D123" s="373"/>
-      <c r="E123" s="373"/>
-      <c r="F123" s="373"/>
+      <c r="C123" s="371"/>
+      <c r="D123" s="371"/>
+      <c r="E123" s="371"/>
+      <c r="F123" s="371"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -21956,13 +21956,13 @@
       </c>
     </row>
     <row r="134" spans="1:6">
-      <c r="B134" s="376" t="s">
+      <c r="B134" s="375" t="s">
         <v>524</v>
       </c>
-      <c r="C134" s="376"/>
-      <c r="D134" s="376"/>
-      <c r="E134" s="376"/>
-      <c r="F134" s="376"/>
+      <c r="C134" s="375"/>
+      <c r="D134" s="375"/>
+      <c r="E134" s="375"/>
+      <c r="F134" s="375"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -21975,22 +21975,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="377" t="s">
+      <c r="B138" s="373" t="s">
         <v>526</v>
       </c>
-      <c r="C138" s="377"/>
-      <c r="D138" s="377"/>
-      <c r="E138" s="377"/>
-      <c r="F138" s="377"/>
+      <c r="C138" s="373"/>
+      <c r="D138" s="373"/>
+      <c r="E138" s="373"/>
+      <c r="F138" s="373"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="372" t="s">
+      <c r="B139" s="370" t="s">
         <v>527</v>
       </c>
-      <c r="C139" s="372"/>
-      <c r="D139" s="372"/>
-      <c r="E139" s="372"/>
-      <c r="F139" s="372"/>
+      <c r="C139" s="370"/>
+      <c r="D139" s="370"/>
+      <c r="E139" s="370"/>
+      <c r="F139" s="370"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -22323,13 +22323,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="371" t="s">
+      <c r="B179" s="377" t="s">
         <v>534</v>
       </c>
-      <c r="C179" s="372"/>
-      <c r="D179" s="372"/>
-      <c r="E179" s="372"/>
-      <c r="F179" s="372"/>
+      <c r="C179" s="370"/>
+      <c r="D179" s="370"/>
+      <c r="E179" s="370"/>
+      <c r="F179" s="370"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -22366,13 +22366,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B188" s="373" t="s">
+      <c r="B188" s="371" t="s">
         <v>541</v>
       </c>
-      <c r="C188" s="373"/>
-      <c r="D188" s="373"/>
-      <c r="E188" s="373"/>
-      <c r="F188" s="373"/>
+      <c r="C188" s="371"/>
+      <c r="D188" s="371"/>
+      <c r="E188" s="371"/>
+      <c r="F188" s="371"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -22380,22 +22380,22 @@
       </c>
     </row>
     <row r="191" spans="1:6">
-      <c r="B191" s="370" t="s">
+      <c r="B191" s="376" t="s">
         <v>543</v>
       </c>
-      <c r="C191" s="370"/>
-      <c r="D191" s="370"/>
-      <c r="E191" s="370"/>
-      <c r="F191" s="370"/>
+      <c r="C191" s="376"/>
+      <c r="D191" s="376"/>
+      <c r="E191" s="376"/>
+      <c r="F191" s="376"/>
     </row>
     <row r="192" spans="1:6">
-      <c r="B192" s="370" t="s">
+      <c r="B192" s="376" t="s">
         <v>544</v>
       </c>
-      <c r="C192" s="370"/>
-      <c r="D192" s="370"/>
-      <c r="E192" s="370"/>
-      <c r="F192" s="370"/>
+      <c r="C192" s="376"/>
+      <c r="D192" s="376"/>
+      <c r="E192" s="376"/>
+      <c r="F192" s="376"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -22419,12 +22419,15 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B47:F47"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B138:F138"/>
+    <mergeCell ref="B139:F139"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B182:F182"/>
     <mergeCell ref="B116:F116"/>
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B58:F58"/>
@@ -22437,15 +22440,12 @@
     <mergeCell ref="B90:F90"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B138:F138"/>
-    <mergeCell ref="B139:F139"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B43:F43"/>
   </mergeCells>
   <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0639.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0639.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B82FE594-6C55-46C8-A352-C2B339E8885D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AF234F3-DB9A-4BA0-841B-D47A883C2353}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4756,29 +4756,29 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="59" fillId="0" borderId="1" xfId="2"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -5282,7 +5282,7 @@
         <v>463</v>
       </c>
       <c r="C12" s="50">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -5303,7 +5303,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>14865.9120484</v>
+        <v>15171.375994600001</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -5340,13 +5340,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="370" t="s">
+      <c r="B18" s="372" t="s">
         <v>468</v>
       </c>
-      <c r="C18" s="370"/>
-      <c r="D18" s="370"/>
-      <c r="E18" s="370"/>
-      <c r="F18" s="370"/>
+      <c r="C18" s="372"/>
+      <c r="D18" s="372"/>
+      <c r="E18" s="372"/>
+      <c r="F18" s="372"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -5429,7 +5429,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.23506722331508234</v>
+        <v>0.22609861224828309</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -5546,22 +5546,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6">
-      <c r="B36" s="370" t="s">
+      <c r="B36" s="372" t="s">
         <v>469</v>
       </c>
-      <c r="C36" s="370"/>
-      <c r="D36" s="370"/>
-      <c r="E36" s="370"/>
-      <c r="F36" s="370"/>
+      <c r="C36" s="372"/>
+      <c r="D36" s="372"/>
+      <c r="E36" s="372"/>
+      <c r="F36" s="372"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="372" t="s">
+      <c r="B37" s="375" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="372"/>
-      <c r="D37" s="372"/>
-      <c r="E37" s="372"/>
-      <c r="F37" s="372"/>
+      <c r="C37" s="375"/>
+      <c r="D37" s="375"/>
+      <c r="E37" s="375"/>
+      <c r="F37" s="375"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -5573,13 +5573,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="371" t="s">
+      <c r="B40" s="373" t="s">
         <v>227</v>
       </c>
-      <c r="C40" s="371"/>
-      <c r="D40" s="371"/>
-      <c r="E40" s="371"/>
-      <c r="F40" s="371"/>
+      <c r="C40" s="373"/>
+      <c r="D40" s="373"/>
+      <c r="E40" s="373"/>
+      <c r="F40" s="373"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -5599,13 +5599,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="371" t="s">
+      <c r="B43" s="373" t="s">
         <v>229</v>
       </c>
-      <c r="C43" s="371"/>
-      <c r="D43" s="371"/>
-      <c r="E43" s="371"/>
-      <c r="F43" s="371"/>
+      <c r="C43" s="373"/>
+      <c r="D43" s="373"/>
+      <c r="E43" s="373"/>
+      <c r="F43" s="373"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -5634,13 +5634,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="371" t="s">
+      <c r="B47" s="373" t="s">
         <v>232</v>
       </c>
-      <c r="C47" s="371"/>
-      <c r="D47" s="371"/>
-      <c r="E47" s="371"/>
-      <c r="F47" s="371"/>
+      <c r="C47" s="373"/>
+      <c r="D47" s="373"/>
+      <c r="E47" s="373"/>
+      <c r="F47" s="373"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -5656,13 +5656,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="371" t="s">
+      <c r="B50" s="373" t="s">
         <v>236</v>
       </c>
-      <c r="C50" s="371"/>
-      <c r="D50" s="371"/>
-      <c r="E50" s="371"/>
-      <c r="F50" s="371"/>
+      <c r="C50" s="373"/>
+      <c r="D50" s="373"/>
+      <c r="E50" s="373"/>
+      <c r="F50" s="373"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -5726,13 +5726,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="371" t="s">
+      <c r="B58" s="373" t="s">
         <v>237</v>
       </c>
-      <c r="C58" s="371"/>
-      <c r="D58" s="371"/>
-      <c r="E58" s="371"/>
-      <c r="F58" s="371"/>
+      <c r="C58" s="373"/>
+      <c r="D58" s="373"/>
+      <c r="E58" s="373"/>
+      <c r="F58" s="373"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -5748,7 +5748,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="371" t="s">
+      <c r="B61" s="373" t="s">
         <v>329</v>
       </c>
       <c r="C61" s="374"/>
@@ -5770,22 +5770,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="370" t="s">
+      <c r="B64" s="372" t="s">
         <v>334</v>
       </c>
-      <c r="C64" s="370"/>
-      <c r="D64" s="370"/>
-      <c r="E64" s="370"/>
-      <c r="F64" s="370"/>
+      <c r="C64" s="372"/>
+      <c r="D64" s="372"/>
+      <c r="E64" s="372"/>
+      <c r="F64" s="372"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="370" t="s">
+      <c r="B65" s="372" t="s">
         <v>348</v>
       </c>
-      <c r="C65" s="370"/>
-      <c r="D65" s="370"/>
-      <c r="E65" s="370"/>
-      <c r="F65" s="370"/>
+      <c r="C65" s="372"/>
+      <c r="D65" s="372"/>
+      <c r="E65" s="372"/>
+      <c r="F65" s="372"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -5819,7 +5819,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>7.3445037787627593E-2</v>
+        <v>7.1966278637541126E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -5829,7 +5829,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>9.2465753424657543E-2</v>
+        <v>9.0604026845637592E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>424</v>
@@ -5920,22 +5920,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="370" t="s">
+      <c r="B80" s="372" t="s">
         <v>471</v>
       </c>
-      <c r="C80" s="370"/>
-      <c r="D80" s="370"/>
-      <c r="E80" s="370"/>
-      <c r="F80" s="370"/>
+      <c r="C80" s="372"/>
+      <c r="D80" s="372"/>
+      <c r="E80" s="372"/>
+      <c r="F80" s="372"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="372" t="s">
+      <c r="B81" s="375" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="372"/>
-      <c r="D81" s="372"/>
-      <c r="E81" s="372"/>
-      <c r="F81" s="372"/>
+      <c r="C81" s="375"/>
+      <c r="D81" s="375"/>
+      <c r="E81" s="375"/>
+      <c r="F81" s="375"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5979,22 +5979,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="370" t="s">
+      <c r="B89" s="372" t="s">
         <v>349</v>
       </c>
-      <c r="C89" s="370"/>
-      <c r="D89" s="370"/>
-      <c r="E89" s="370"/>
-      <c r="F89" s="370"/>
+      <c r="C89" s="372"/>
+      <c r="D89" s="372"/>
+      <c r="E89" s="372"/>
+      <c r="F89" s="372"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="370" t="s">
+      <c r="B90" s="372" t="s">
         <v>350</v>
       </c>
-      <c r="C90" s="370"/>
-      <c r="D90" s="370"/>
-      <c r="E90" s="370"/>
-      <c r="F90" s="370"/>
+      <c r="C90" s="372"/>
+      <c r="D90" s="372"/>
+      <c r="E90" s="372"/>
+      <c r="F90" s="372"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -6031,13 +6031,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="370" t="s">
+      <c r="B97" s="372" t="s">
         <v>351</v>
       </c>
-      <c r="C97" s="370"/>
-      <c r="D97" s="370"/>
-      <c r="E97" s="370"/>
-      <c r="F97" s="370"/>
+      <c r="C97" s="372"/>
+      <c r="D97" s="372"/>
+      <c r="E97" s="372"/>
+      <c r="F97" s="372"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -6050,13 +6050,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="370" t="s">
+      <c r="B101" s="372" t="s">
         <v>335</v>
       </c>
-      <c r="C101" s="370"/>
-      <c r="D101" s="370"/>
-      <c r="E101" s="370"/>
-      <c r="F101" s="370"/>
+      <c r="C101" s="372"/>
+      <c r="D101" s="372"/>
+      <c r="E101" s="372"/>
+      <c r="F101" s="372"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -6178,13 +6178,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="370" t="s">
+      <c r="B116" s="372" t="s">
         <v>352</v>
       </c>
-      <c r="C116" s="370"/>
-      <c r="D116" s="370"/>
-      <c r="E116" s="370"/>
-      <c r="F116" s="370"/>
+      <c r="C116" s="372"/>
+      <c r="D116" s="372"/>
+      <c r="E116" s="372"/>
+      <c r="F116" s="372"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -6223,13 +6223,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="371" t="s">
+      <c r="B123" s="373" t="s">
         <v>473</v>
       </c>
-      <c r="C123" s="371"/>
-      <c r="D123" s="371"/>
-      <c r="E123" s="371"/>
-      <c r="F123" s="371"/>
+      <c r="C123" s="373"/>
+      <c r="D123" s="373"/>
+      <c r="E123" s="373"/>
+      <c r="F123" s="373"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -6372,13 +6372,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="375" t="s">
+      <c r="B134" s="376" t="s">
         <v>474</v>
       </c>
-      <c r="C134" s="375"/>
-      <c r="D134" s="375"/>
-      <c r="E134" s="375"/>
-      <c r="F134" s="375"/>
+      <c r="C134" s="376"/>
+      <c r="D134" s="376"/>
+      <c r="E134" s="376"/>
+      <c r="F134" s="376"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -6391,22 +6391,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="373" t="s">
+      <c r="B138" s="377" t="s">
         <v>353</v>
       </c>
-      <c r="C138" s="373"/>
-      <c r="D138" s="373"/>
-      <c r="E138" s="373"/>
-      <c r="F138" s="373"/>
+      <c r="C138" s="377"/>
+      <c r="D138" s="377"/>
+      <c r="E138" s="377"/>
+      <c r="F138" s="377"/>
     </row>
     <row r="139" spans="1:6">
-      <c r="B139" s="370" t="s">
+      <c r="B139" s="372" t="s">
         <v>476</v>
       </c>
-      <c r="C139" s="370"/>
-      <c r="D139" s="370"/>
-      <c r="E139" s="370"/>
-      <c r="F139" s="370"/>
+      <c r="C139" s="372"/>
+      <c r="D139" s="372"/>
+      <c r="E139" s="372"/>
+      <c r="F139" s="372"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -6739,13 +6739,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="377" t="s">
+      <c r="B179" s="371" t="s">
         <v>477</v>
       </c>
-      <c r="C179" s="370"/>
-      <c r="D179" s="370"/>
-      <c r="E179" s="370"/>
-      <c r="F179" s="370"/>
+      <c r="C179" s="372"/>
+      <c r="D179" s="372"/>
+      <c r="E179" s="372"/>
+      <c r="F179" s="372"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -6782,13 +6782,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="34.35" customHeight="1">
-      <c r="B188" s="371" t="s">
+      <c r="B188" s="373" t="s">
         <v>478</v>
       </c>
-      <c r="C188" s="371"/>
-      <c r="D188" s="371"/>
-      <c r="E188" s="371"/>
-      <c r="F188" s="371"/>
+      <c r="C188" s="373"/>
+      <c r="D188" s="373"/>
+      <c r="E188" s="373"/>
+      <c r="F188" s="373"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -6796,22 +6796,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="376" t="s">
+      <c r="B191" s="370" t="s">
         <v>363</v>
       </c>
-      <c r="C191" s="376"/>
-      <c r="D191" s="376"/>
-      <c r="E191" s="376"/>
-      <c r="F191" s="376"/>
+      <c r="C191" s="370"/>
+      <c r="D191" s="370"/>
+      <c r="E191" s="370"/>
+      <c r="F191" s="370"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="376" t="s">
+      <c r="B192" s="370" t="s">
         <v>364</v>
       </c>
-      <c r="C192" s="376"/>
-      <c r="D192" s="376"/>
-      <c r="E192" s="376"/>
-      <c r="F192" s="376"/>
+      <c r="C192" s="370"/>
+      <c r="D192" s="370"/>
+      <c r="E192" s="370"/>
+      <c r="F192" s="370"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -6835,17 +6835,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -6862,6 +6851,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -14405,20 +14405,20 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>9.2465753424657543E-2</v>
+        <v>9.0604026845637592E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>9.2465753424657543E-2</v>
+        <v>9.0604026845637592E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>8.6301369863013719E-2</v>
+        <v>8.4563758389261764E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>0.13253424657534249</v>
+        <v>0.12986577181208056</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
@@ -15604,50 +15604,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>7.3445037787627593E-2</v>
+        <v>7.1966278637541126E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>8.5705161269313865E-2</v>
+        <v>8.3979553995435066E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>0.1179356363531826</v>
+        <v>0.11556109333936013</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>0.19126765276048507</v>
+        <v>0.18741662619483773</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>0.1571563801729966</v>
+        <v>0.15399215775340608</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>5.6379588233216225E-2</v>
+        <v>5.524442873858771E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>7.1573072444923891E-2</v>
+        <v>7.0132003872207291E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>6.3726261591999803E-2</v>
+        <v>6.2443182499543427E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>6.0525247093523631E-2</v>
+        <v>5.9306617957412419E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>1.0714176128678407E-2</v>
+        <v>1.0498454461658036E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>4.6413566672100807E-3</v>
+        <v>4.5479065329709512E-3</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -15661,43 +15661,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12208971734064199</v>
+        <v>0.1196315351123069</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1547794708127341</v>
+        <v>0.15166310562858509</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.22253293233737736</v>
+        <v>0.21805240349836974</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.20589594436147857</v>
+        <v>0.20175038843473736</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.9866139133238437E-2</v>
+        <v>7.8258096063441682E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.9116639205906419E-2</v>
+        <v>7.7523686738673395E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.7487879401518495E-2</v>
+        <v>7.5927720755850331E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.9550046855502557E-2</v>
+        <v>7.7948368059754178E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.5510830267075164E-3</v>
+        <v>4.4594504825456191E-3</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-4.7859492083876229E-2</v>
+        <v>-4.6895878149301538E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -19647,7 +19647,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-2.92</v>
+        <v>-2.98</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -19887,7 +19887,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -20485,7 +20485,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -20498,7 +20498,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.23506722331508234</v>
+        <v>0.22609861224828309</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -20851,7 +20851,7 @@
       </c>
       <c r="C12" s="366">
         <f>Market_Price</f>
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -20873,7 +20873,7 @@
       </c>
       <c r="C14" s="35">
         <f>投资主题!C12*Common_Shares/1000000</f>
-        <v>14865.9120484</v>
+        <v>15171.375994600001</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",投资主题!D12*Common_Shares/1000000)</f>
@@ -20911,13 +20911,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="370" t="s">
+      <c r="B18" s="372" t="s">
         <v>489</v>
       </c>
-      <c r="C18" s="370"/>
-      <c r="D18" s="370"/>
-      <c r="E18" s="370"/>
-      <c r="F18" s="370"/>
+      <c r="C18" s="372"/>
+      <c r="D18" s="372"/>
+      <c r="E18" s="372"/>
+      <c r="F18" s="372"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -21008,7 +21008,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.23506722331508234</v>
+        <v>0.22609861224828309</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -21130,22 +21130,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="370" t="s">
+      <c r="B36" s="372" t="s">
         <v>492</v>
       </c>
-      <c r="C36" s="370"/>
-      <c r="D36" s="370"/>
-      <c r="E36" s="370"/>
-      <c r="F36" s="370"/>
+      <c r="C36" s="372"/>
+      <c r="D36" s="372"/>
+      <c r="E36" s="372"/>
+      <c r="F36" s="372"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="372" t="s">
+      <c r="B37" s="375" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="372"/>
-      <c r="D37" s="372"/>
-      <c r="E37" s="372"/>
-      <c r="F37" s="372"/>
+      <c r="C37" s="375"/>
+      <c r="D37" s="375"/>
+      <c r="E37" s="375"/>
+      <c r="F37" s="375"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -21157,13 +21157,13 @@
       </c>
     </row>
     <row r="40" spans="1:6">
-      <c r="B40" s="371" t="s">
+      <c r="B40" s="373" t="s">
         <v>494</v>
       </c>
-      <c r="C40" s="371"/>
-      <c r="D40" s="371"/>
-      <c r="E40" s="371"/>
-      <c r="F40" s="371"/>
+      <c r="C40" s="373"/>
+      <c r="D40" s="373"/>
+      <c r="E40" s="373"/>
+      <c r="F40" s="373"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -21183,13 +21183,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="371" t="s">
+      <c r="B43" s="373" t="s">
         <v>495</v>
       </c>
-      <c r="C43" s="371"/>
-      <c r="D43" s="371"/>
-      <c r="E43" s="371"/>
-      <c r="F43" s="371"/>
+      <c r="C43" s="373"/>
+      <c r="D43" s="373"/>
+      <c r="E43" s="373"/>
+      <c r="F43" s="373"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -21218,13 +21218,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="371" t="s">
+      <c r="B47" s="373" t="s">
         <v>496</v>
       </c>
-      <c r="C47" s="371"/>
-      <c r="D47" s="371"/>
-      <c r="E47" s="371"/>
-      <c r="F47" s="371"/>
+      <c r="C47" s="373"/>
+      <c r="D47" s="373"/>
+      <c r="E47" s="373"/>
+      <c r="F47" s="373"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -21240,13 +21240,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="371" t="s">
+      <c r="B50" s="373" t="s">
         <v>497</v>
       </c>
-      <c r="C50" s="371"/>
-      <c r="D50" s="371"/>
-      <c r="E50" s="371"/>
-      <c r="F50" s="371"/>
+      <c r="C50" s="373"/>
+      <c r="D50" s="373"/>
+      <c r="E50" s="373"/>
+      <c r="F50" s="373"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -21310,13 +21310,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="371" t="s">
+      <c r="B58" s="373" t="s">
         <v>237</v>
       </c>
-      <c r="C58" s="371"/>
-      <c r="D58" s="371"/>
-      <c r="E58" s="371"/>
-      <c r="F58" s="371"/>
+      <c r="C58" s="373"/>
+      <c r="D58" s="373"/>
+      <c r="E58" s="373"/>
+      <c r="F58" s="373"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -21332,7 +21332,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="371" t="s">
+      <c r="B61" s="373" t="s">
         <v>499</v>
       </c>
       <c r="C61" s="374"/>
@@ -21354,22 +21354,22 @@
       </c>
     </row>
     <row r="64" spans="2:6">
-      <c r="B64" s="370" t="s">
+      <c r="B64" s="372" t="s">
         <v>500</v>
       </c>
-      <c r="C64" s="370"/>
-      <c r="D64" s="370"/>
-      <c r="E64" s="370"/>
-      <c r="F64" s="370"/>
+      <c r="C64" s="372"/>
+      <c r="D64" s="372"/>
+      <c r="E64" s="372"/>
+      <c r="F64" s="372"/>
     </row>
     <row r="65" spans="1:6">
-      <c r="B65" s="370" t="s">
+      <c r="B65" s="372" t="s">
         <v>501</v>
       </c>
-      <c r="C65" s="370"/>
-      <c r="D65" s="370"/>
-      <c r="E65" s="370"/>
-      <c r="F65" s="370"/>
+      <c r="C65" s="372"/>
+      <c r="D65" s="372"/>
+      <c r="E65" s="372"/>
+      <c r="F65" s="372"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -21403,7 +21403,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>7.3445037787627593E-2</v>
+        <v>7.1966278637541126E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -21413,7 +21413,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>9.2465753424657543E-2</v>
+        <v>9.0604026845637592E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>503</v>
@@ -21504,22 +21504,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="370" t="s">
+      <c r="B80" s="372" t="s">
         <v>506</v>
       </c>
-      <c r="C80" s="370"/>
-      <c r="D80" s="370"/>
-      <c r="E80" s="370"/>
-      <c r="F80" s="370"/>
+      <c r="C80" s="372"/>
+      <c r="D80" s="372"/>
+      <c r="E80" s="372"/>
+      <c r="F80" s="372"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="372" t="s">
+      <c r="B81" s="375" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="372"/>
-      <c r="D81" s="372"/>
-      <c r="E81" s="372"/>
-      <c r="F81" s="372"/>
+      <c r="C81" s="375"/>
+      <c r="D81" s="375"/>
+      <c r="E81" s="375"/>
+      <c r="F81" s="375"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -21563,22 +21563,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6">
-      <c r="B89" s="370" t="s">
+      <c r="B89" s="372" t="s">
         <v>507</v>
       </c>
-      <c r="C89" s="370"/>
-      <c r="D89" s="370"/>
-      <c r="E89" s="370"/>
-      <c r="F89" s="370"/>
+      <c r="C89" s="372"/>
+      <c r="D89" s="372"/>
+      <c r="E89" s="372"/>
+      <c r="F89" s="372"/>
     </row>
     <row r="90" spans="1:6">
-      <c r="B90" s="370" t="s">
+      <c r="B90" s="372" t="s">
         <v>508</v>
       </c>
-      <c r="C90" s="370"/>
-      <c r="D90" s="370"/>
-      <c r="E90" s="370"/>
-      <c r="F90" s="370"/>
+      <c r="C90" s="372"/>
+      <c r="D90" s="372"/>
+      <c r="E90" s="372"/>
+      <c r="F90" s="372"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -21615,13 +21615,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="370" t="s">
+      <c r="B97" s="372" t="s">
         <v>510</v>
       </c>
-      <c r="C97" s="370"/>
-      <c r="D97" s="370"/>
-      <c r="E97" s="370"/>
-      <c r="F97" s="370"/>
+      <c r="C97" s="372"/>
+      <c r="D97" s="372"/>
+      <c r="E97" s="372"/>
+      <c r="F97" s="372"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -21634,13 +21634,13 @@
       </c>
     </row>
     <row r="101" spans="2:6">
-      <c r="B101" s="370" t="s">
+      <c r="B101" s="372" t="s">
         <v>511</v>
       </c>
-      <c r="C101" s="370"/>
-      <c r="D101" s="370"/>
-      <c r="E101" s="370"/>
-      <c r="F101" s="370"/>
+      <c r="C101" s="372"/>
+      <c r="D101" s="372"/>
+      <c r="E101" s="372"/>
+      <c r="F101" s="372"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -21762,13 +21762,13 @@
       </c>
     </row>
     <row r="116" spans="1:6">
-      <c r="B116" s="370" t="s">
+      <c r="B116" s="372" t="s">
         <v>516</v>
       </c>
-      <c r="C116" s="370"/>
-      <c r="D116" s="370"/>
-      <c r="E116" s="370"/>
-      <c r="F116" s="370"/>
+      <c r="C116" s="372"/>
+      <c r="D116" s="372"/>
+      <c r="E116" s="372"/>
+      <c r="F116" s="372"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -21807,13 +21807,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="371" t="s">
+      <c r="B123" s="373" t="s">
         <v>519</v>
       </c>
-      <c r="C123" s="371"/>
-      <c r="D123" s="371"/>
-      <c r="E123" s="371"/>
-      <c r="F123" s="371"/>
+      <c r="C123" s="373"/>
+      <c r="D123" s="373"/>
+      <c r="E123" s="373"/>
+      <c r="F123" s="373"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -21956,13 +21956,13 @@
       </c>
     </row>
     <row r="134" spans="1:6">
-      <c r="B134" s="375" t="s">
+      <c r="B134" s="376" t="s">
         <v>524</v>
       </c>
-      <c r="C134" s="375"/>
-      <c r="D134" s="375"/>
-      <c r="E134" s="375"/>
-      <c r="F134" s="375"/>
+      <c r="C134" s="376"/>
+      <c r="D134" s="376"/>
+      <c r="E134" s="376"/>
+      <c r="F134" s="376"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -21975,22 +21975,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="373" t="s">
+      <c r="B138" s="377" t="s">
         <v>526</v>
       </c>
-      <c r="C138" s="373"/>
-      <c r="D138" s="373"/>
-      <c r="E138" s="373"/>
-      <c r="F138" s="373"/>
+      <c r="C138" s="377"/>
+      <c r="D138" s="377"/>
+      <c r="E138" s="377"/>
+      <c r="F138" s="377"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="370" t="s">
+      <c r="B139" s="372" t="s">
         <v>527</v>
       </c>
-      <c r="C139" s="370"/>
-      <c r="D139" s="370"/>
-      <c r="E139" s="370"/>
-      <c r="F139" s="370"/>
+      <c r="C139" s="372"/>
+      <c r="D139" s="372"/>
+      <c r="E139" s="372"/>
+      <c r="F139" s="372"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -22323,13 +22323,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="377" t="s">
+      <c r="B179" s="371" t="s">
         <v>534</v>
       </c>
-      <c r="C179" s="370"/>
-      <c r="D179" s="370"/>
-      <c r="E179" s="370"/>
-      <c r="F179" s="370"/>
+      <c r="C179" s="372"/>
+      <c r="D179" s="372"/>
+      <c r="E179" s="372"/>
+      <c r="F179" s="372"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -22366,13 +22366,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B188" s="371" t="s">
+      <c r="B188" s="373" t="s">
         <v>541</v>
       </c>
-      <c r="C188" s="371"/>
-      <c r="D188" s="371"/>
-      <c r="E188" s="371"/>
-      <c r="F188" s="371"/>
+      <c r="C188" s="373"/>
+      <c r="D188" s="373"/>
+      <c r="E188" s="373"/>
+      <c r="F188" s="373"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -22380,22 +22380,22 @@
       </c>
     </row>
     <row r="191" spans="1:6">
-      <c r="B191" s="376" t="s">
+      <c r="B191" s="370" t="s">
         <v>543</v>
       </c>
-      <c r="C191" s="376"/>
-      <c r="D191" s="376"/>
-      <c r="E191" s="376"/>
-      <c r="F191" s="376"/>
+      <c r="C191" s="370"/>
+      <c r="D191" s="370"/>
+      <c r="E191" s="370"/>
+      <c r="F191" s="370"/>
     </row>
     <row r="192" spans="1:6">
-      <c r="B192" s="376" t="s">
+      <c r="B192" s="370" t="s">
         <v>544</v>
       </c>
-      <c r="C192" s="376"/>
-      <c r="D192" s="376"/>
-      <c r="E192" s="376"/>
-      <c r="F192" s="376"/>
+      <c r="C192" s="370"/>
+      <c r="D192" s="370"/>
+      <c r="E192" s="370"/>
+      <c r="F192" s="370"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -22419,15 +22419,12 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B138:F138"/>
-    <mergeCell ref="B139:F139"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B43:F43"/>
     <mergeCell ref="B116:F116"/>
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B58:F58"/>
@@ -22440,12 +22437,15 @@
     <mergeCell ref="B90:F90"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B47:F47"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B138:F138"/>
+    <mergeCell ref="B139:F139"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0639.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0639.HK_Valuation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamanl/PycharmProjects/Invest_Proc/financial_models/opportunities/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AF234F3-DB9A-4BA0-841B-D47A883C2353}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CDEB771-00D2-CA43-8D92-14F696169E95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="17120" windowHeight="10760" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -54,6 +54,17 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion1">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId11" roundtripDataSignature="AMtx7mi73Cg0ax9bLfpeUuF69nNRn7idDQ=="/>
@@ -3321,7 +3332,7 @@
     <numFmt numFmtId="180" formatCode="0.000000000000000%"/>
     <numFmt numFmtId="181" formatCode="#,##0_);\(#,##0\);0;@"/>
   </numFmts>
-  <fonts count="60">
+  <fonts count="60" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -3765,6 +3776,7 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -4756,29 +4768,29 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="59" fillId="0" borderId="1" xfId="2"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4794,7 +4806,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="常规 2" xfId="2" xr:uid="{20E05687-AD80-4962-8416-EB9A18D9162C}"/>
     <cellStyle name="常规 2 2" xfId="1" xr:uid="{A35F4541-DCCE-4554-A311-39480A36979A}"/>
   </cellStyles>
@@ -5169,16 +5181,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J197"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.73046875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="32.73046875" style="1" customWidth="1"/>
-    <col min="3" max="4" width="25.73046875" style="1" customWidth="1"/>
-    <col min="5" max="6" width="15.73046875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="32.6640625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="25.6640625" style="1" customWidth="1"/>
+    <col min="5" max="6" width="15.6640625" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B1" s="3" t="s">
         <v>39</v>
       </c>
@@ -5195,7 +5207,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="13.9">
+    <row r="2" spans="1:10" ht="16" x14ac:dyDescent="0.25">
       <c r="A2" s="222" t="s">
         <v>263</v>
       </c>
@@ -5209,7 +5221,7 @@
       <c r="I2" s="22"/>
       <c r="J2" s="22"/>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B4" s="45" t="s">
         <v>394</v>
       </c>
@@ -5218,7 +5230,7 @@
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
     </row>
-    <row r="5" spans="1:10" ht="12.4">
+    <row r="5" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="B5" s="4" t="s">
         <v>458</v>
       </c>
@@ -5226,7 +5238,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B6" s="4" t="s">
         <v>459</v>
       </c>
@@ -5235,7 +5247,7 @@
       </c>
       <c r="E6" s="48"/>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B7" s="2" t="s">
         <v>460</v>
       </c>
@@ -5245,7 +5257,7 @@
       <c r="D7" s="48"/>
       <c r="E7" s="48"/>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B8" s="1" t="s">
         <v>461</v>
       </c>
@@ -5255,17 +5267,17 @@
       </c>
       <c r="E8" s="48"/>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
       <c r="E9" s="34"/>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B10" s="45" t="s">
         <v>396</v>
       </c>
       <c r="C10" s="46"/>
       <c r="E10" s="34"/>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B11" s="1" t="s">
         <v>462</v>
       </c>
@@ -5277,17 +5289,17 @@
       </c>
       <c r="E11" s="34"/>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B12" s="4" t="s">
         <v>463</v>
       </c>
       <c r="C12" s="50">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B13" s="1" t="s">
         <v>464</v>
       </c>
@@ -5297,13 +5309,13 @@
       <c r="D13" s="48"/>
       <c r="E13" s="5"/>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B14" s="4" t="s">
         <v>465</v>
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>15171.375994600001</v>
+        <v>14967.7333638</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -5311,7 +5323,7 @@
       </c>
       <c r="E14" s="5"/>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B15" s="4" t="s">
         <v>466</v>
       </c>
@@ -5325,7 +5337,7 @@
       </c>
       <c r="E15" s="5"/>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B16" s="4" t="s">
         <v>467</v>
       </c>
@@ -5335,27 +5347,27 @@
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
     </row>
-    <row r="17" spans="2:6">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.15">
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
     </row>
-    <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="372" t="s">
+    <row r="18" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B18" s="370" t="s">
         <v>468</v>
       </c>
-      <c r="C18" s="372"/>
-      <c r="D18" s="372"/>
-      <c r="E18" s="372"/>
-      <c r="F18" s="372"/>
-    </row>
-    <row r="20" spans="2:6">
+      <c r="C18" s="370"/>
+      <c r="D18" s="370"/>
+      <c r="E18" s="370"/>
+      <c r="F18" s="370"/>
+    </row>
+    <row r="20" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B20" s="45" t="s">
         <v>301</v>
       </c>
       <c r="C20" s="46"/>
       <c r="D20" s="5"/>
     </row>
-    <row r="21" spans="2:6">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B21" s="2" t="s">
         <v>339</v>
       </c>
@@ -5370,7 +5382,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="22" spans="2:6">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B22" s="2" t="s">
         <v>54</v>
       </c>
@@ -5383,7 +5395,7 @@
       </c>
       <c r="E22" s="313"/>
     </row>
-    <row r="23" spans="2:6">
+    <row r="23" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B23" s="1" t="s">
         <v>410</v>
       </c>
@@ -5391,7 +5403,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="24" spans="2:6">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B24" s="1" t="s">
         <v>411</v>
       </c>
@@ -5399,7 +5411,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="25" spans="2:6">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B25" s="4" t="s">
         <v>338</v>
       </c>
@@ -5415,7 +5427,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="2:6">
+    <row r="26" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B26" s="1" t="str">
         <f>"Expected Equity Value ("&amp;C13&amp;") :"</f>
         <v>Expected Equity Value (HKD) :</v>
@@ -5429,14 +5441,14 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.22609861224828309</v>
-      </c>
-    </row>
-    <row r="27" spans="2:6">
+        <v>0.23204925986510649</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6" x14ac:dyDescent="0.15">
       <c r="D27" s="5"/>
       <c r="E27" s="5"/>
     </row>
-    <row r="28" spans="2:6">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B28" s="45" t="s">
         <v>409</v>
       </c>
@@ -5455,7 +5467,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="2:6">
+    <row r="29" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B29" s="1" t="s">
         <v>401</v>
       </c>
@@ -5474,7 +5486,7 @@
         <v>0.35</v>
       </c>
     </row>
-    <row r="30" spans="2:6">
+    <row r="30" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B30" s="1" t="s">
         <v>402</v>
       </c>
@@ -5493,7 +5505,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="31" spans="2:6">
+    <row r="31" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B31" s="1" t="s">
         <v>403</v>
       </c>
@@ -5512,7 +5524,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
-    <row r="32" spans="2:6">
+    <row r="32" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B32" s="1" t="s">
         <v>404</v>
       </c>
@@ -5531,11 +5543,11 @@
         <v>0.1174</v>
       </c>
     </row>
-    <row r="33" spans="1:6">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.15">
       <c r="D33" s="5"/>
       <c r="E33" s="5"/>
     </row>
-    <row r="34" spans="1:6" ht="13.9">
+    <row r="34" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A34" s="222" t="s">
         <v>345</v>
       </c>
@@ -5545,25 +5557,25 @@
       <c r="E34" s="36"/>
       <c r="F34" s="36"/>
     </row>
-    <row r="36" spans="1:6">
-      <c r="B36" s="372" t="s">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B36" s="370" t="s">
         <v>469</v>
       </c>
-      <c r="C36" s="372"/>
-      <c r="D36" s="372"/>
-      <c r="E36" s="372"/>
-      <c r="F36" s="372"/>
-    </row>
-    <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="375" t="s">
+      <c r="C36" s="370"/>
+      <c r="D36" s="370"/>
+      <c r="E36" s="370"/>
+      <c r="F36" s="370"/>
+    </row>
+    <row r="37" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B37" s="372" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="375"/>
-      <c r="D37" s="375"/>
-      <c r="E37" s="375"/>
-      <c r="F37" s="375"/>
-    </row>
-    <row r="39" spans="1:6">
+      <c r="C37" s="372"/>
+      <c r="D37" s="372"/>
+      <c r="E37" s="372"/>
+      <c r="F37" s="372"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B39" s="210" t="s">
         <v>226</v>
       </c>
@@ -5572,16 +5584,16 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="373" t="s">
+    <row r="40" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B40" s="371" t="s">
         <v>227</v>
       </c>
-      <c r="C40" s="373"/>
-      <c r="D40" s="373"/>
-      <c r="E40" s="373"/>
-      <c r="F40" s="373"/>
-    </row>
-    <row r="41" spans="1:6">
+      <c r="C40" s="371"/>
+      <c r="D40" s="371"/>
+      <c r="E40" s="371"/>
+      <c r="F40" s="371"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B41" s="47" t="s">
         <v>228</v>
       </c>
@@ -5594,20 +5606,20 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="42" spans="1:6">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B42" s="47"/>
       <c r="C42" s="76"/>
     </row>
-    <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="373" t="s">
+    <row r="43" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B43" s="371" t="s">
         <v>229</v>
       </c>
-      <c r="C43" s="373"/>
-      <c r="D43" s="373"/>
-      <c r="E43" s="373"/>
-      <c r="F43" s="373"/>
-    </row>
-    <row r="44" spans="1:6">
+      <c r="C43" s="371"/>
+      <c r="D43" s="371"/>
+      <c r="E43" s="371"/>
+      <c r="F43" s="371"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B44" s="47" t="s">
         <v>230</v>
       </c>
@@ -5620,7 +5632,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="45" spans="1:6">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B45" s="52" t="s">
         <v>231</v>
       </c>
@@ -5633,16 +5645,16 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="47" spans="1:6">
-      <c r="B47" s="373" t="s">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B47" s="371" t="s">
         <v>232</v>
       </c>
-      <c r="C47" s="373"/>
-      <c r="D47" s="373"/>
-      <c r="E47" s="373"/>
-      <c r="F47" s="373"/>
-    </row>
-    <row r="48" spans="1:6">
+      <c r="C47" s="371"/>
+      <c r="D47" s="371"/>
+      <c r="E47" s="371"/>
+      <c r="F47" s="371"/>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B48" s="47" t="s">
         <v>233</v>
       </c>
@@ -5655,16 +5667,16 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="50" spans="2:6">
-      <c r="B50" s="373" t="s">
+    <row r="50" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B50" s="371" t="s">
         <v>236</v>
       </c>
-      <c r="C50" s="373"/>
-      <c r="D50" s="373"/>
-      <c r="E50" s="373"/>
-      <c r="F50" s="373"/>
-    </row>
-    <row r="51" spans="2:6">
+      <c r="C50" s="371"/>
+      <c r="D50" s="371"/>
+      <c r="E50" s="371"/>
+      <c r="F50" s="371"/>
+    </row>
+    <row r="51" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B51" s="47" t="s">
         <v>331</v>
       </c>
@@ -5679,7 +5691,7 @@
       <c r="E51" s="286"/>
       <c r="F51" s="286"/>
     </row>
-    <row r="52" spans="2:6">
+    <row r="52" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B52" s="47" t="s">
         <v>332</v>
       </c>
@@ -5694,7 +5706,7 @@
       <c r="E52" s="286"/>
       <c r="F52" s="286"/>
     </row>
-    <row r="53" spans="2:6">
+    <row r="53" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B53" s="47" t="s">
         <v>234</v>
       </c>
@@ -5707,12 +5719,12 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="55" spans="2:6">
+    <row r="55" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B55" s="1" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="56" spans="2:6">
+    <row r="56" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B56" s="47" t="s">
         <v>261</v>
       </c>
@@ -5725,16 +5737,16 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="58" spans="2:6">
-      <c r="B58" s="373" t="s">
+    <row r="58" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B58" s="371" t="s">
         <v>237</v>
       </c>
-      <c r="C58" s="373"/>
-      <c r="D58" s="373"/>
-      <c r="E58" s="373"/>
-      <c r="F58" s="373"/>
-    </row>
-    <row r="59" spans="2:6">
+      <c r="C58" s="371"/>
+      <c r="D58" s="371"/>
+      <c r="E58" s="371"/>
+      <c r="F58" s="371"/>
+    </row>
+    <row r="59" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B59" s="47" t="s">
         <v>235</v>
       </c>
@@ -5747,8 +5759,8 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="61" spans="2:6">
-      <c r="B61" s="373" t="s">
+    <row r="61" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B61" s="371" t="s">
         <v>329</v>
       </c>
       <c r="C61" s="374"/>
@@ -5756,7 +5768,7 @@
       <c r="E61" s="374"/>
       <c r="F61" s="374"/>
     </row>
-    <row r="62" spans="2:6">
+    <row r="62" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B62" s="47" t="s">
         <v>238</v>
       </c>
@@ -5769,25 +5781,25 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="372" t="s">
+    <row r="64" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B64" s="370" t="s">
         <v>334</v>
       </c>
-      <c r="C64" s="372"/>
-      <c r="D64" s="372"/>
-      <c r="E64" s="372"/>
-      <c r="F64" s="372"/>
-    </row>
-    <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="372" t="s">
+      <c r="C64" s="370"/>
+      <c r="D64" s="370"/>
+      <c r="E64" s="370"/>
+      <c r="F64" s="370"/>
+    </row>
+    <row r="65" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B65" s="370" t="s">
         <v>348</v>
       </c>
-      <c r="C65" s="372"/>
-      <c r="D65" s="372"/>
-      <c r="E65" s="372"/>
-      <c r="F65" s="372"/>
-    </row>
-    <row r="67" spans="1:6">
+      <c r="C65" s="370"/>
+      <c r="D65" s="370"/>
+      <c r="E65" s="370"/>
+      <c r="F65" s="370"/>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B67" s="47" t="s">
         <v>265</v>
       </c>
@@ -5800,7 +5812,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="68" spans="1:6">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B68" s="47" t="s">
         <v>244</v>
       </c>
@@ -5813,23 +5825,23 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="69" spans="1:6">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B69" s="227" t="s">
         <v>371</v>
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>7.1966278637541126E-2</v>
+        <v>7.2945411680228764E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
-    <row r="70" spans="1:6">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B70" s="227" t="s">
         <v>434</v>
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>9.0604026845637592E-2</v>
+        <v>9.1836734693877556E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>424</v>
@@ -5839,7 +5851,7 @@
         <v>1.3988654526188369</v>
       </c>
     </row>
-    <row r="72" spans="1:6">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B72" s="210" t="s">
         <v>427</v>
       </c>
@@ -5850,7 +5862,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="73" spans="1:6">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B73" s="47" t="s">
         <v>428</v>
       </c>
@@ -5863,7 +5875,7 @@
         <v>0.12199804433766272</v>
       </c>
     </row>
-    <row r="74" spans="1:6">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B74" s="259" t="str">
         <f>Normalized_FCF!B118</f>
         <v>Pre-tax Profit/Sales</v>
@@ -5877,7 +5889,7 @@
         <v>0.45598504835348186</v>
       </c>
     </row>
-    <row r="75" spans="1:6">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B75" s="259" t="str">
         <f>Normalized_FCF!B119</f>
         <v>Sales/Total Assets</v>
@@ -5891,7 +5903,7 @@
         <v>0.22035988512352028</v>
       </c>
     </row>
-    <row r="76" spans="1:6">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B76" s="259" t="str">
         <f>Normalized_FCF!B120</f>
         <v>Total Assets/Equity</v>
@@ -5905,7 +5917,7 @@
         <v>1.2141426890285656</v>
       </c>
     </row>
-    <row r="78" spans="1:6" ht="13.9">
+    <row r="78" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A78" s="222" t="s">
         <v>470</v>
       </c>
@@ -5915,34 +5927,34 @@
       <c r="E78" s="36"/>
       <c r="F78" s="36"/>
     </row>
-    <row r="79" spans="1:6">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A79" s="209"/>
     </row>
-    <row r="80" spans="1:6">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A80" s="17"/>
-      <c r="B80" s="372" t="s">
+      <c r="B80" s="370" t="s">
         <v>471</v>
       </c>
-      <c r="C80" s="372"/>
-      <c r="D80" s="372"/>
-      <c r="E80" s="372"/>
-      <c r="F80" s="372"/>
-    </row>
-    <row r="81" spans="1:6">
-      <c r="B81" s="375" t="s">
+      <c r="C80" s="370"/>
+      <c r="D80" s="370"/>
+      <c r="E80" s="370"/>
+      <c r="F80" s="370"/>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B81" s="372" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="375"/>
-      <c r="D81" s="375"/>
-      <c r="E81" s="375"/>
-      <c r="F81" s="375"/>
-    </row>
-    <row r="83" spans="1:6">
+      <c r="C81" s="372"/>
+      <c r="D81" s="372"/>
+      <c r="E81" s="372"/>
+      <c r="F81" s="372"/>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B83" s="210" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="84" spans="1:6">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B84" s="1" t="s">
         <v>407</v>
       </c>
@@ -5951,7 +5963,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
-    <row r="85" spans="1:6">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B85" s="1" t="s">
         <v>406</v>
       </c>
@@ -5960,7 +5972,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:6">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B86" s="80" t="s">
         <v>243</v>
       </c>
@@ -5969,34 +5981,34 @@
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
-    <row r="87" spans="1:6">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.15">
       <c r="C87" s="121"/>
     </row>
-    <row r="88" spans="1:6">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B88" s="293" t="s">
         <v>346</v>
       </c>
       <c r="C88" s="121"/>
     </row>
-    <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="372" t="s">
+    <row r="89" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B89" s="370" t="s">
         <v>349</v>
       </c>
-      <c r="C89" s="372"/>
-      <c r="D89" s="372"/>
-      <c r="E89" s="372"/>
-      <c r="F89" s="372"/>
-    </row>
-    <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="372" t="s">
+      <c r="C89" s="370"/>
+      <c r="D89" s="370"/>
+      <c r="E89" s="370"/>
+      <c r="F89" s="370"/>
+    </row>
+    <row r="90" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B90" s="370" t="s">
         <v>350</v>
       </c>
-      <c r="C90" s="372"/>
-      <c r="D90" s="372"/>
-      <c r="E90" s="372"/>
-      <c r="F90" s="372"/>
-    </row>
-    <row r="92" spans="1:6">
+      <c r="C90" s="370"/>
+      <c r="D90" s="370"/>
+      <c r="E90" s="370"/>
+      <c r="F90" s="370"/>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B92" s="47" t="s">
         <v>247</v>
       </c>
@@ -6004,7 +6016,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:6">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B93" s="47" t="s">
         <v>275</v>
       </c>
@@ -6017,7 +6029,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="95" spans="1:6" ht="13.9">
+    <row r="95" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A95" s="222" t="s">
         <v>347</v>
       </c>
@@ -6027,38 +6039,38 @@
       <c r="E95" s="36"/>
       <c r="F95" s="36"/>
     </row>
-    <row r="96" spans="1:6">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A96" s="209"/>
     </row>
-    <row r="97" spans="2:6">
-      <c r="B97" s="372" t="s">
+    <row r="97" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B97" s="370" t="s">
         <v>351</v>
       </c>
-      <c r="C97" s="372"/>
-      <c r="D97" s="372"/>
-      <c r="E97" s="372"/>
-      <c r="F97" s="372"/>
-    </row>
-    <row r="98" spans="2:6">
+      <c r="C97" s="370"/>
+      <c r="D97" s="370"/>
+      <c r="E97" s="370"/>
+      <c r="F97" s="370"/>
+    </row>
+    <row r="98" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B98" s="1" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="100" spans="2:6">
+    <row r="100" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B100" s="210" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="372" t="s">
+    <row r="101" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B101" s="370" t="s">
         <v>335</v>
       </c>
-      <c r="C101" s="372"/>
-      <c r="D101" s="372"/>
-      <c r="E101" s="372"/>
-      <c r="F101" s="372"/>
-    </row>
-    <row r="102" spans="2:6">
+      <c r="C101" s="370"/>
+      <c r="D101" s="370"/>
+      <c r="E101" s="370"/>
+      <c r="F101" s="370"/>
+    </row>
+    <row r="102" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B102" s="47" t="s">
         <v>251</v>
       </c>
@@ -6071,7 +6083,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="103" spans="2:6">
+    <row r="103" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B103" s="47" t="s">
         <v>276</v>
       </c>
@@ -6084,7 +6096,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="104" spans="2:6">
+    <row r="104" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B104" s="296" t="s">
         <v>384</v>
       </c>
@@ -6093,7 +6105,7 @@
         <v>2.3107986944995245E-3</v>
       </c>
     </row>
-    <row r="105" spans="2:6">
+    <row r="105" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B105" s="296" t="s">
         <v>386</v>
       </c>
@@ -6102,12 +6114,12 @@
         <v>2.3228129203780753E-2</v>
       </c>
     </row>
-    <row r="107" spans="2:6">
+    <row r="107" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B107" s="1" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="108" spans="2:6">
+    <row r="108" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B108" s="47" t="s">
         <v>260</v>
       </c>
@@ -6120,7 +6132,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="109" spans="2:6">
+    <row r="109" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B109" s="47" t="s">
         <v>262</v>
       </c>
@@ -6133,7 +6145,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="110" spans="2:6">
+    <row r="110" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B110" s="47" t="s">
         <v>277</v>
       </c>
@@ -6146,12 +6158,12 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="112" spans="2:6">
+    <row r="112" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B112" s="1" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="113" spans="1:6">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B113" s="47" t="s">
         <v>253</v>
       </c>
@@ -6164,7 +6176,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="114" spans="1:6">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B114" s="47" t="s">
         <v>278</v>
       </c>
@@ -6177,16 +6189,16 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="372" t="s">
+    <row r="116" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B116" s="370" t="s">
         <v>352</v>
       </c>
-      <c r="C116" s="372"/>
-      <c r="D116" s="372"/>
-      <c r="E116" s="372"/>
-      <c r="F116" s="372"/>
-    </row>
-    <row r="118" spans="1:6">
+      <c r="C116" s="370"/>
+      <c r="D116" s="370"/>
+      <c r="E116" s="370"/>
+      <c r="F116" s="370"/>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B118" s="47" t="s">
         <v>425</v>
       </c>
@@ -6199,7 +6211,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="119" spans="1:6">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B119" s="296" t="s">
         <v>549</v>
       </c>
@@ -6212,7 +6224,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="121" spans="1:6" ht="13.9">
+    <row r="121" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A121" s="222" t="s">
         <v>472</v>
       </c>
@@ -6222,16 +6234,16 @@
       <c r="E121" s="36"/>
       <c r="F121" s="36"/>
     </row>
-    <row r="123" spans="1:6">
-      <c r="B123" s="373" t="s">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B123" s="371" t="s">
         <v>473</v>
       </c>
-      <c r="C123" s="373"/>
-      <c r="D123" s="373"/>
-      <c r="E123" s="373"/>
-      <c r="F123" s="373"/>
-    </row>
-    <row r="125" spans="1:6" ht="12.4">
+      <c r="C123" s="371"/>
+      <c r="D123" s="371"/>
+      <c r="E123" s="371"/>
+      <c r="F123" s="371"/>
+    </row>
+    <row r="125" spans="1:6" ht="14" x14ac:dyDescent="0.2">
       <c r="B125" s="233" t="s">
         <v>113</v>
       </c>
@@ -6248,7 +6260,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="126" spans="1:6">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B126" s="228" t="str">
         <f>DCF!B74</f>
         <v>Snowball Scenario</v>
@@ -6270,7 +6282,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="127" spans="1:6">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B127" s="218" t="str">
         <f>DCF!B75</f>
         <v>Optimistic</v>
@@ -6292,7 +6304,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="128" spans="1:6">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B128" s="218" t="str">
         <f>DCF!B76</f>
         <v>Base</v>
@@ -6314,7 +6326,7 @@
         <v>0.53999999999999992</v>
       </c>
     </row>
-    <row r="129" spans="1:6">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B129" s="218" t="str">
         <f>DCF!B77</f>
         <v>Pessimistic</v>
@@ -6336,7 +6348,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="130" spans="1:6">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B130" s="218" t="str">
         <f>DCF!B78</f>
         <v>Devil's advocate</v>
@@ -6358,7 +6370,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="132" spans="1:6">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B132" s="211" t="s">
         <v>254</v>
       </c>
@@ -6371,16 +6383,16 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="376" t="s">
+    <row r="134" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B134" s="375" t="s">
         <v>474</v>
       </c>
-      <c r="C134" s="376"/>
-      <c r="D134" s="376"/>
-      <c r="E134" s="376"/>
-      <c r="F134" s="376"/>
-    </row>
-    <row r="136" spans="1:6" ht="13.9">
+      <c r="C134" s="375"/>
+      <c r="D134" s="375"/>
+      <c r="E134" s="375"/>
+      <c r="F134" s="375"/>
+    </row>
+    <row r="136" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A136" s="222" t="s">
         <v>475</v>
       </c>
@@ -6390,30 +6402,30 @@
       <c r="E136" s="36"/>
       <c r="F136" s="36"/>
     </row>
-    <row r="138" spans="1:6">
-      <c r="B138" s="377" t="s">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B138" s="373" t="s">
         <v>353</v>
       </c>
-      <c r="C138" s="377"/>
-      <c r="D138" s="377"/>
-      <c r="E138" s="377"/>
-      <c r="F138" s="377"/>
-    </row>
-    <row r="139" spans="1:6">
-      <c r="B139" s="372" t="s">
+      <c r="C138" s="373"/>
+      <c r="D138" s="373"/>
+      <c r="E138" s="373"/>
+      <c r="F138" s="373"/>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B139" s="370" t="s">
         <v>476</v>
       </c>
-      <c r="C139" s="372"/>
-      <c r="D139" s="372"/>
-      <c r="E139" s="372"/>
-      <c r="F139" s="372"/>
-    </row>
-    <row r="140" spans="1:6">
+      <c r="C139" s="370"/>
+      <c r="D139" s="370"/>
+      <c r="E139" s="370"/>
+      <c r="F139" s="370"/>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B140" s="210" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="141" spans="1:6">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B141" s="1" t="s">
         <v>259</v>
       </c>
@@ -6422,7 +6434,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="142" spans="1:6">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B142" s="1" t="s">
         <v>271</v>
       </c>
@@ -6431,7 +6443,7 @@
         <v>0.35</v>
       </c>
     </row>
-    <row r="143" spans="1:6">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B143" s="212" t="s">
         <v>257</v>
       </c>
@@ -6444,7 +6456,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="145" spans="2:4">
+    <row r="145" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B145" s="210" t="s">
         <v>388</v>
       </c>
@@ -6457,7 +6469,7 @@
         <v/>
       </c>
     </row>
-    <row r="146" spans="2:4">
+    <row r="146" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B146" s="1" t="s">
         <v>387</v>
       </c>
@@ -6466,7 +6478,7 @@
         <v>0.35</v>
       </c>
     </row>
-    <row r="147" spans="2:4">
+    <row r="147" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B147" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -6476,7 +6488,7 @@
         <v>0.45788751714677645</v>
       </c>
     </row>
-    <row r="148" spans="2:4">
+    <row r="148" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B148" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -6486,7 +6498,7 @@
         <v>1.823234620703778</v>
       </c>
     </row>
-    <row r="149" spans="2:4">
+    <row r="149" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B149" s="80" t="s">
         <v>256</v>
       </c>
@@ -6499,7 +6511,7 @@
         <v/>
       </c>
     </row>
-    <row r="150" spans="2:4">
+    <row r="150" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B150" s="259" t="s">
         <v>395</v>
       </c>
@@ -6512,7 +6524,7 @@
         <v/>
       </c>
     </row>
-    <row r="151" spans="2:4">
+    <row r="151" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B151" s="214" t="s">
         <v>258</v>
       </c>
@@ -6521,12 +6533,12 @@
         <v>0.49148393825902781</v>
       </c>
     </row>
-    <row r="153" spans="2:4">
+    <row r="153" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B153" s="210" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="154" spans="2:4">
+    <row r="154" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B154" s="1" t="s">
         <v>390</v>
       </c>
@@ -6535,7 +6547,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="155" spans="2:4">
+    <row r="155" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B155" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -6545,7 +6557,7 @@
         <v>0.52704000000000006</v>
       </c>
     </row>
-    <row r="156" spans="2:4">
+    <row r="156" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B156" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -6555,7 +6567,7 @@
         <v>2.2967505305159981</v>
       </c>
     </row>
-    <row r="157" spans="2:4">
+    <row r="157" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B157" s="80" t="s">
         <v>256</v>
       </c>
@@ -6568,7 +6580,7 @@
         <v/>
       </c>
     </row>
-    <row r="158" spans="2:4">
+    <row r="158" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B158" s="259" t="s">
         <v>395</v>
       </c>
@@ -6581,7 +6593,7 @@
         <v/>
       </c>
     </row>
-    <row r="159" spans="2:4">
+    <row r="159" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B159" s="214" t="s">
         <v>258</v>
       </c>
@@ -6590,12 +6602,12 @@
         <v>0.37051032212045443</v>
       </c>
     </row>
-    <row r="161" spans="2:4">
+    <row r="161" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B161" s="210" t="s">
         <v>381</v>
       </c>
     </row>
-    <row r="162" spans="2:4">
+    <row r="162" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B162" s="1" t="s">
         <v>389</v>
       </c>
@@ -6604,7 +6616,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
-    <row r="163" spans="2:4">
+    <row r="163" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B163" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -6614,7 +6626,7 @@
         <v>0.70214194976542921</v>
       </c>
     </row>
-    <row r="164" spans="2:4">
+    <row r="164" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B164" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -6624,7 +6636,7 @@
         <v>3.6109250294250792</v>
       </c>
     </row>
-    <row r="165" spans="2:4">
+    <row r="165" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B165" s="80" t="s">
         <v>382</v>
       </c>
@@ -6637,7 +6649,7 @@
         <v/>
       </c>
     </row>
-    <row r="166" spans="2:4">
+    <row r="166" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B166" s="259" t="s">
         <v>395</v>
       </c>
@@ -6650,7 +6662,7 @@
         <v/>
       </c>
     </row>
-    <row r="167" spans="2:4">
+    <row r="167" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B167" s="214" t="s">
         <v>258</v>
       </c>
@@ -6659,12 +6671,12 @@
         <v>3.8515387716307137E-2</v>
       </c>
     </row>
-    <row r="169" spans="2:4">
+    <row r="169" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B169" s="210" t="s">
         <v>408</v>
       </c>
     </row>
-    <row r="170" spans="2:4">
+    <row r="170" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B170" s="1" t="s">
         <v>399</v>
       </c>
@@ -6673,7 +6685,7 @@
         <v>0.1174</v>
       </c>
     </row>
-    <row r="171" spans="2:4">
+    <row r="171" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B171" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -6683,7 +6695,7 @@
         <v>0.65140284400343529</v>
       </c>
     </row>
-    <row r="172" spans="2:4">
+    <row r="172" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B172" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -6693,7 +6705,7 @@
         <v>3.2152730720890683</v>
       </c>
     </row>
-    <row r="173" spans="2:4">
+    <row r="173" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B173" s="80" t="s">
         <v>382</v>
       </c>
@@ -6706,7 +6718,7 @@
         <v/>
       </c>
     </row>
-    <row r="174" spans="2:4">
+    <row r="174" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B174" s="259" t="s">
         <v>395</v>
       </c>
@@ -6719,7 +6731,7 @@
         <v/>
       </c>
     </row>
-    <row r="175" spans="2:4">
+    <row r="175" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B175" s="214" t="s">
         <v>258</v>
       </c>
@@ -6728,7 +6740,7 @@
         <v>0.13842067503200794</v>
       </c>
     </row>
-    <row r="177" spans="1:6" ht="13.9">
+    <row r="177" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A177" s="222" t="s">
         <v>357</v>
       </c>
@@ -6738,21 +6750,21 @@
       <c r="E177" s="36"/>
       <c r="F177" s="36"/>
     </row>
-    <row r="179" spans="1:6">
-      <c r="B179" s="371" t="s">
+    <row r="179" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B179" s="377" t="s">
         <v>477</v>
       </c>
-      <c r="C179" s="372"/>
-      <c r="D179" s="372"/>
-      <c r="E179" s="372"/>
-      <c r="F179" s="372"/>
-    </row>
-    <row r="181" spans="1:6">
+      <c r="C179" s="370"/>
+      <c r="D179" s="370"/>
+      <c r="E179" s="370"/>
+      <c r="F179" s="370"/>
+    </row>
+    <row r="181" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B181" s="210" t="s">
         <v>358</v>
       </c>
     </row>
-    <row r="182" spans="1:6">
+    <row r="182" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B182" s="374" t="s">
         <v>362</v>
       </c>
@@ -6761,80 +6773,91 @@
       <c r="E182" s="374"/>
       <c r="F182" s="374"/>
     </row>
-    <row r="183" spans="1:6">
+    <row r="183" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B183" s="214" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="184" spans="1:6">
+    <row r="184" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B184" s="214" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="185" spans="1:6">
+    <row r="185" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B185" s="214" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="187" spans="1:6">
+    <row r="187" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B187" s="1" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="188" spans="1:6" ht="34.35" customHeight="1">
-      <c r="B188" s="373" t="s">
+    <row r="188" spans="1:6" ht="34.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B188" s="371" t="s">
         <v>478</v>
       </c>
-      <c r="C188" s="373"/>
-      <c r="D188" s="373"/>
-      <c r="E188" s="373"/>
-      <c r="F188" s="373"/>
-    </row>
-    <row r="190" spans="1:6">
+      <c r="C188" s="371"/>
+      <c r="D188" s="371"/>
+      <c r="E188" s="371"/>
+      <c r="F188" s="371"/>
+    </row>
+    <row r="190" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B190" s="1" t="s">
         <v>366</v>
       </c>
     </row>
-    <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="370" t="s">
+    <row r="191" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B191" s="376" t="s">
         <v>363</v>
       </c>
-      <c r="C191" s="370"/>
-      <c r="D191" s="370"/>
-      <c r="E191" s="370"/>
-      <c r="F191" s="370"/>
-    </row>
-    <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="370" t="s">
+      <c r="C191" s="376"/>
+      <c r="D191" s="376"/>
+      <c r="E191" s="376"/>
+      <c r="F191" s="376"/>
+    </row>
+    <row r="192" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B192" s="376" t="s">
         <v>364</v>
       </c>
-      <c r="C192" s="370"/>
-      <c r="D192" s="370"/>
-      <c r="E192" s="370"/>
-      <c r="F192" s="370"/>
-    </row>
-    <row r="194" spans="2:2">
+      <c r="C192" s="376"/>
+      <c r="D192" s="376"/>
+      <c r="E192" s="376"/>
+      <c r="F192" s="376"/>
+    </row>
+    <row r="194" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B194" s="1" t="s">
         <v>370</v>
       </c>
     </row>
-    <row r="195" spans="2:2">
+    <row r="195" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B195" s="214" t="s">
         <v>367</v>
       </c>
     </row>
-    <row r="196" spans="2:2">
+    <row r="196" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B196" s="214" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="197" spans="2:2">
+    <row r="197" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B197" s="214" t="s">
         <v>369</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -6851,17 +6874,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -6892,15 +6904,15 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:M80"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="11.65"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
-    <col min="2" max="2" width="27.265625" style="1" customWidth="1"/>
-    <col min="3" max="13" width="20.73046875" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.86328125" style="1"/>
+    <col min="2" max="2" width="27.33203125" style="1" customWidth="1"/>
+    <col min="3" max="13" width="20.6640625" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13">
+    <row r="1" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B1" s="90" t="str">
         <f>Thesis!C25</f>
         <v>HKD</v>
@@ -6949,7 +6961,7 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="2:13" ht="13.9">
+    <row r="2" spans="2:13" ht="16" x14ac:dyDescent="0.25">
       <c r="B2" s="36" t="s">
         <v>94</v>
       </c>
@@ -6965,7 +6977,7 @@
       <c r="L2" s="37"/>
       <c r="M2" s="37"/>
     </row>
-    <row r="3" spans="2:13">
+    <row r="3" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B3" s="16" t="s">
         <v>25</v>
       </c>
@@ -6973,7 +6985,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="4" spans="2:13">
+    <row r="4" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B4" s="32" t="s">
         <v>0</v>
       </c>
@@ -7009,7 +7021,7 @@
       </c>
       <c r="M4" s="351"/>
     </row>
-    <row r="5" spans="2:13">
+    <row r="5" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B5" s="40" t="s">
         <v>41</v>
       </c>
@@ -7045,7 +7057,7 @@
       </c>
       <c r="M5" s="351"/>
     </row>
-    <row r="6" spans="2:13">
+    <row r="6" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B6" s="40" t="s">
         <v>52</v>
       </c>
@@ -7081,7 +7093,7 @@
       </c>
       <c r="M6" s="351"/>
     </row>
-    <row r="7" spans="2:13">
+    <row r="7" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B7" s="69" t="s">
         <v>59</v>
       </c>
@@ -7117,7 +7129,7 @@
       </c>
       <c r="M7" s="352"/>
     </row>
-    <row r="8" spans="2:13">
+    <row r="8" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B8" s="40" t="s">
         <v>47</v>
       </c>
@@ -7133,7 +7145,7 @@
       <c r="L8" s="351"/>
       <c r="M8" s="351"/>
     </row>
-    <row r="9" spans="2:13">
+    <row r="9" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B9" s="40" t="s">
         <v>155</v>
       </c>
@@ -7149,7 +7161,7 @@
       <c r="L9" s="351"/>
       <c r="M9" s="351"/>
     </row>
-    <row r="10" spans="2:13">
+    <row r="10" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B10" s="40" t="s">
         <v>163</v>
       </c>
@@ -7165,7 +7177,7 @@
       <c r="L10" s="351"/>
       <c r="M10" s="351"/>
     </row>
-    <row r="11" spans="2:13">
+    <row r="11" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B11" s="40" t="s">
         <v>154</v>
       </c>
@@ -7181,7 +7193,7 @@
       <c r="L11" s="351"/>
       <c r="M11" s="351"/>
     </row>
-    <row r="12" spans="2:13">
+    <row r="12" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B12" s="40" t="s">
         <v>37</v>
       </c>
@@ -7205,7 +7217,7 @@
       <c r="L12" s="351"/>
       <c r="M12" s="351"/>
     </row>
-    <row r="13" spans="2:13">
+    <row r="13" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B13" s="40" t="s">
         <v>65</v>
       </c>
@@ -7229,7 +7241,7 @@
       <c r="L13" s="351"/>
       <c r="M13" s="351"/>
     </row>
-    <row r="14" spans="2:13">
+    <row r="14" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B14" s="40" t="s">
         <v>48</v>
       </c>
@@ -7265,7 +7277,7 @@
       </c>
       <c r="M14" s="351"/>
     </row>
-    <row r="15" spans="2:13">
+    <row r="15" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B15" s="43" t="s">
         <v>40</v>
       </c>
@@ -7301,7 +7313,7 @@
       </c>
       <c r="M15" s="353"/>
     </row>
-    <row r="16" spans="2:13">
+    <row r="16" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B16" s="28" t="s">
         <v>42</v>
       </c>
@@ -7337,13 +7349,13 @@
       </c>
       <c r="M16" s="351"/>
     </row>
-    <row r="18" spans="2:13">
+    <row r="18" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B18" s="16" t="s">
         <v>49</v>
       </c>
       <c r="C18" s="9"/>
     </row>
-    <row r="19" spans="2:13">
+    <row r="19" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B19" s="27" t="s">
         <v>45</v>
       </c>
@@ -7359,7 +7371,7 @@
       <c r="L19" s="351"/>
       <c r="M19" s="351"/>
     </row>
-    <row r="20" spans="2:13">
+    <row r="20" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B20" s="27" t="s">
         <v>51</v>
       </c>
@@ -7375,7 +7387,7 @@
       <c r="L20" s="351"/>
       <c r="M20" s="351"/>
     </row>
-    <row r="21" spans="2:13">
+    <row r="21" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B21" s="27" t="s">
         <v>50</v>
       </c>
@@ -7391,7 +7403,7 @@
       <c r="L21" s="351"/>
       <c r="M21" s="351"/>
     </row>
-    <row r="22" spans="2:13">
+    <row r="22" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B22" s="27" t="s">
         <v>354</v>
       </c>
@@ -7427,7 +7439,7 @@
       </c>
       <c r="M22" s="351"/>
     </row>
-    <row r="23" spans="2:13">
+    <row r="23" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B23" s="27" t="s">
         <v>356</v>
       </c>
@@ -7463,7 +7475,7 @@
       </c>
       <c r="M23" s="351"/>
     </row>
-    <row r="24" spans="2:13">
+    <row r="24" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B24" s="27" t="s">
         <v>355</v>
       </c>
@@ -7499,7 +7511,7 @@
       </c>
       <c r="M24" s="351"/>
     </row>
-    <row r="25" spans="2:13">
+    <row r="25" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B25" s="24" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
         <v>Dividend per share (HKD)</v>
@@ -7525,7 +7537,7 @@
       <c r="L25" s="39"/>
       <c r="M25" s="39"/>
     </row>
-    <row r="27" spans="2:13">
+    <row r="27" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B27" s="16" t="s">
         <v>26</v>
       </c>
@@ -7533,7 +7545,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="28" spans="2:13">
+    <row r="28" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B28" s="26" t="s">
         <v>22</v>
       </c>
@@ -7570,7 +7582,7 @@
       </c>
       <c r="M28" s="351"/>
     </row>
-    <row r="29" spans="2:13">
+    <row r="29" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B29" s="26" t="s">
         <v>30</v>
       </c>
@@ -7607,7 +7619,7 @@
       </c>
       <c r="M29" s="351"/>
     </row>
-    <row r="30" spans="2:13">
+    <row r="30" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B30" s="29" t="s">
         <v>38</v>
       </c>
@@ -7644,7 +7656,7 @@
       </c>
       <c r="M30" s="353"/>
     </row>
-    <row r="31" spans="2:13">
+    <row r="31" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B31" s="29" t="s">
         <v>28</v>
       </c>
@@ -7681,7 +7693,7 @@
       </c>
       <c r="M31" s="353"/>
     </row>
-    <row r="32" spans="2:13">
+    <row r="32" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B32" s="26" t="s">
         <v>168</v>
       </c>
@@ -7718,7 +7730,7 @@
       </c>
       <c r="M32" s="351"/>
     </row>
-    <row r="34" spans="2:13" ht="13.9">
+    <row r="34" spans="2:13" ht="16" x14ac:dyDescent="0.25">
       <c r="B34" s="36" t="s">
         <v>79</v>
       </c>
@@ -7734,12 +7746,12 @@
       <c r="L34" s="37"/>
       <c r="M34" s="37"/>
     </row>
-    <row r="35" spans="2:13">
+    <row r="35" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B35" s="16" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="36" spans="2:13">
+    <row r="36" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B36" s="32" t="s">
         <v>0</v>
       </c>
@@ -7788,7 +7800,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="2:13">
+    <row r="37" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B37" s="40" t="s">
         <v>41</v>
       </c>
@@ -7837,7 +7849,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="2:13">
+    <row r="38" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B38" s="31" t="s">
         <v>56</v>
       </c>
@@ -7886,7 +7898,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="2:13">
+    <row r="39" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B39" s="40" t="s">
         <v>52</v>
       </c>
@@ -7935,7 +7947,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="2:13">
+    <row r="40" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B40" s="69" t="s">
         <v>59</v>
       </c>
@@ -7984,7 +7996,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="2:13">
+    <row r="41" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B41" s="69" t="s">
         <v>62</v>
       </c>
@@ -8033,7 +8045,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="2:13">
+    <row r="42" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B42" s="40" t="s">
         <v>47</v>
       </c>
@@ -8082,7 +8094,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="2:13">
+    <row r="43" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B43" s="43" t="s">
         <v>148</v>
       </c>
@@ -8131,7 +8143,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="2:13">
+    <row r="44" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B44" s="43" t="s">
         <v>164</v>
       </c>
@@ -8180,7 +8192,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" spans="2:13">
+    <row r="45" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B45" s="40" t="s">
         <v>66</v>
       </c>
@@ -8229,7 +8241,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="2:13">
+    <row r="46" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B46" s="40" t="s">
         <v>48</v>
       </c>
@@ -8278,7 +8290,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="2:13">
+    <row r="47" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B47" s="43" t="s">
         <v>40</v>
       </c>
@@ -8327,7 +8339,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="2:13">
+    <row r="48" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B48" s="28" t="s">
         <v>42</v>
       </c>
@@ -8376,12 +8388,12 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="2:13">
+    <row r="50" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B50" s="16" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="51" spans="2:13">
+    <row r="51" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B51" s="40" t="s">
         <v>37</v>
       </c>
@@ -8430,7 +8442,7 @@
         <v/>
       </c>
     </row>
-    <row r="52" spans="2:13">
+    <row r="52" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B52" s="40" t="s">
         <v>65</v>
       </c>
@@ -8479,12 +8491,12 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="2:13">
+    <row r="54" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B54" s="174" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="55" spans="2:13">
+    <row r="55" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B55" s="40" t="s">
         <v>155</v>
       </c>
@@ -8533,7 +8545,7 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="2:13">
+    <row r="56" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B56" s="40" t="s">
         <v>163</v>
       </c>
@@ -8582,7 +8594,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="2:13">
+    <row r="57" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B57" s="40" t="s">
         <v>154</v>
       </c>
@@ -8631,7 +8643,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="2:13">
+    <row r="58" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B58" s="40" t="s">
         <v>156</v>
       </c>
@@ -8680,13 +8692,13 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="2:13">
+    <row r="60" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B60" s="16" t="s">
         <v>49</v>
       </c>
       <c r="C60" s="9"/>
     </row>
-    <row r="61" spans="2:13">
+    <row r="61" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B61" s="27" t="s">
         <v>45</v>
       </c>
@@ -8735,7 +8747,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="2:13">
+    <row r="62" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B62" s="27" t="s">
         <v>51</v>
       </c>
@@ -8784,7 +8796,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="2:13">
+    <row r="63" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B63" s="27" t="s">
         <v>50</v>
       </c>
@@ -8833,7 +8845,7 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="2:13">
+    <row r="64" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B64" s="27" t="s">
         <v>374</v>
       </c>
@@ -8882,7 +8894,7 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="2:13">
+    <row r="65" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B65" s="24" t="s">
         <v>34</v>
       </c>
@@ -8931,12 +8943,12 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="2:13">
+    <row r="67" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B67" s="91" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="68" spans="2:13">
+    <row r="68" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B68" s="1" t="str">
         <f>B36</f>
         <v>Sales</v>
@@ -8986,7 +8998,7 @@
         <v/>
       </c>
     </row>
-    <row r="69" spans="2:13">
+    <row r="69" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B69" s="31" t="s">
         <v>56</v>
       </c>
@@ -9035,7 +9047,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="2:13">
+    <row r="70" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B70" s="80" t="str">
         <f>B43</f>
         <v>Operating EBIT</v>
@@ -9085,7 +9097,7 @@
         <v/>
       </c>
     </row>
-    <row r="71" spans="2:13">
+    <row r="71" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B71" s="43" t="s">
         <v>164</v>
       </c>
@@ -9134,7 +9146,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="2:13">
+    <row r="72" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B72" s="80" t="str">
         <f>B47</f>
         <v>Reported Net Income</v>
@@ -9184,7 +9196,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="2:13" ht="13.9">
+    <row r="74" spans="2:13" ht="16" x14ac:dyDescent="0.25">
       <c r="B74" s="36" t="s">
         <v>80</v>
       </c>
@@ -9200,13 +9212,13 @@
       <c r="L74" s="37"/>
       <c r="M74" s="37"/>
     </row>
-    <row r="75" spans="2:13">
+    <row r="75" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B75" s="16" t="s">
         <v>26</v>
       </c>
       <c r="C75" s="9"/>
     </row>
-    <row r="76" spans="2:13">
+    <row r="76" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B76" s="26" t="s">
         <v>1</v>
       </c>
@@ -9255,7 +9267,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="2:13">
+    <row r="77" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B77" s="93" t="s">
         <v>83</v>
       </c>
@@ -9289,7 +9301,7 @@
       <c r="L77" s="355"/>
       <c r="M77" s="355"/>
     </row>
-    <row r="78" spans="2:13">
+    <row r="78" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B78" s="93" t="s">
         <v>84</v>
       </c>
@@ -9323,7 +9335,7 @@
       <c r="L78" s="355"/>
       <c r="M78" s="355"/>
     </row>
-    <row r="79" spans="2:13">
+    <row r="79" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B79" s="26" t="s">
         <v>38</v>
       </c>
@@ -9372,7 +9384,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="2:13">
+    <row r="80" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B80" s="26" t="s">
         <v>28</v>
       </c>
@@ -9453,18 +9465,18 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:H89"/>
-  <sheetFormatPr defaultColWidth="12.265625" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.265625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2.33203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="34" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="18.73046875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="5.73046875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="25.265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="18.73046875" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="12.265625" style="1"/>
+    <col min="3" max="4" width="18.6640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="5.6640625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="25.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="18.6640625" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="12.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="15" customHeight="1">
+    <row r="1" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B1" s="18" t="s">
         <v>35</v>
       </c>
@@ -9480,7 +9492,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="2" spans="2:8" ht="15" customHeight="1">
+    <row r="2" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B2" s="79" t="s">
         <v>152</v>
       </c>
@@ -9491,7 +9503,7 @@
       <c r="G2" s="37"/>
       <c r="H2" s="37"/>
     </row>
-    <row r="3" spans="2:8" ht="15" customHeight="1">
+    <row r="3" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B3" s="16" t="s">
         <v>180</v>
       </c>
@@ -9511,7 +9523,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="15" customHeight="1">
+    <row r="4" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B4" s="4" t="s">
         <v>22</v>
       </c>
@@ -9534,7 +9546,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="15" customHeight="1">
+    <row r="5" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B5" s="1" t="s">
         <v>31</v>
       </c>
@@ -9555,7 +9567,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="15" customHeight="1">
+    <row r="6" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B6" s="4" t="s">
         <v>8</v>
       </c>
@@ -9576,7 +9588,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="15" customHeight="1">
+    <row r="7" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B7" s="1" t="s">
         <v>67</v>
       </c>
@@ -9597,7 +9609,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="15" customHeight="1">
+    <row r="8" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B8" s="1" t="s">
         <v>169</v>
       </c>
@@ -9618,7 +9630,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="9" spans="2:8" ht="15" customHeight="1">
+    <row r="9" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B9" s="4" t="s">
         <v>23</v>
       </c>
@@ -9639,7 +9651,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="10" spans="2:8" ht="15" customHeight="1">
+    <row r="10" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B10" s="4" t="s">
         <v>9</v>
       </c>
@@ -9651,7 +9663,7 @@
       </c>
       <c r="H10" s="262"/>
     </row>
-    <row r="11" spans="2:8" ht="15" customHeight="1">
+    <row r="11" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B11" s="4" t="s">
         <v>10</v>
       </c>
@@ -9663,7 +9675,7 @@
       </c>
       <c r="H11" s="262"/>
     </row>
-    <row r="12" spans="2:8" ht="15" customHeight="1">
+    <row r="12" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B12" s="80" t="s">
         <v>70</v>
       </c>
@@ -9687,12 +9699,12 @@
         <v>8919164.6999999993</v>
       </c>
     </row>
-    <row r="13" spans="2:8" ht="15" customHeight="1">
+    <row r="13" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F13" s="80"/>
       <c r="G13" s="81"/>
       <c r="H13" s="20"/>
     </row>
-    <row r="14" spans="2:8" ht="15" customHeight="1">
+    <row r="14" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B14" s="16" t="s">
         <v>179</v>
       </c>
@@ -9712,7 +9724,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="15" spans="2:8" ht="15" customHeight="1">
+    <row r="15" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B15" s="4" t="s">
         <v>431</v>
       </c>
@@ -9732,7 +9744,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="16" spans="2:8" ht="15" customHeight="1">
+    <row r="16" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B16" s="1" t="s">
         <v>32</v>
       </c>
@@ -9752,7 +9764,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="17" spans="2:8" ht="15" customHeight="1">
+    <row r="17" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="1" t="s">
         <v>67</v>
       </c>
@@ -9773,7 +9785,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="18" spans="2:8" ht="15" customHeight="1">
+    <row r="18" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="4" t="s">
         <v>169</v>
       </c>
@@ -9793,7 +9805,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="19" spans="2:8" ht="15" customHeight="1">
+    <row r="19" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B19" s="4" t="s">
         <v>24</v>
       </c>
@@ -9814,7 +9826,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="20" spans="2:8" ht="15" customHeight="1">
+    <row r="20" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B20" s="4" t="s">
         <v>16</v>
       </c>
@@ -9834,7 +9846,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="21" spans="2:8" ht="15" customHeight="1">
+    <row r="21" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B21" s="4" t="s">
         <v>17</v>
       </c>
@@ -9854,7 +9866,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="22" spans="2:8" ht="15" customHeight="1">
+    <row r="22" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B22" s="4" t="s">
         <v>18</v>
       </c>
@@ -9866,7 +9878,7 @@
       </c>
       <c r="H22" s="262"/>
     </row>
-    <row r="23" spans="2:8" ht="15" customHeight="1">
+    <row r="23" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B23" s="4" t="s">
         <v>19</v>
       </c>
@@ -9879,7 +9891,7 @@
       </c>
       <c r="H23" s="262"/>
     </row>
-    <row r="24" spans="2:8" ht="15" customHeight="1">
+    <row r="24" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B24" s="80" t="s">
         <v>71</v>
       </c>
@@ -9903,7 +9915,7 @@
         <v>263512.2</v>
       </c>
     </row>
-    <row r="26" spans="2:8" ht="15" customHeight="1">
+    <row r="26" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B26" s="16" t="s">
         <v>196</v>
       </c>
@@ -9920,7 +9932,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="27" spans="2:8" ht="15" customHeight="1">
+    <row r="27" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B27" s="4" t="s">
         <v>3</v>
       </c>
@@ -9939,7 +9951,7 @@
         <v>6485581.2499999981</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="15" customHeight="1">
+    <row r="28" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B28" s="4" t="s">
         <v>4</v>
       </c>
@@ -9954,7 +9966,7 @@
       </c>
       <c r="H28" s="188"/>
     </row>
-    <row r="29" spans="2:8" ht="15" customHeight="1">
+    <row r="29" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B29" s="4" t="s">
         <v>5</v>
       </c>
@@ -9973,7 +9985,7 @@
         <v>4064398.2499999981</v>
       </c>
     </row>
-    <row r="30" spans="2:8" ht="15" customHeight="1">
+    <row r="30" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B30" s="2" t="s">
         <v>6</v>
       </c>
@@ -9989,7 +10001,7 @@
       </c>
       <c r="H30" s="188"/>
     </row>
-    <row r="31" spans="2:8" ht="15" customHeight="1">
+    <row r="31" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B31" s="80" t="s">
         <v>199</v>
       </c>
@@ -10006,7 +10018,7 @@
       </c>
       <c r="H31" s="188"/>
     </row>
-    <row r="32" spans="2:8" ht="15" customHeight="1">
+    <row r="32" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B32" s="4" t="s">
         <v>7</v>
       </c>
@@ -10026,7 +10038,7 @@
         <v>10533147.249999998</v>
       </c>
     </row>
-    <row r="33" spans="2:8" ht="15" customHeight="1">
+    <row r="33" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B33" s="83" t="s">
         <v>2</v>
       </c>
@@ -10037,7 +10049,7 @@
       <c r="G33" s="2"/>
       <c r="H33" s="195"/>
     </row>
-    <row r="34" spans="2:8" ht="15" customHeight="1">
+    <row r="34" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B34" s="83"/>
       <c r="C34" s="84"/>
       <c r="F34" s="196" t="s">
@@ -10050,7 +10062,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="2:8" ht="15" customHeight="1">
+    <row r="35" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B35" s="16" t="s">
         <v>197</v>
       </c>
@@ -10069,7 +10081,7 @@
         <v>1350470.3499999999</v>
       </c>
     </row>
-    <row r="36" spans="2:8" ht="15" customHeight="1">
+    <row r="36" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B36" s="4" t="s">
         <v>11</v>
       </c>
@@ -10085,7 +10097,7 @@
       </c>
       <c r="H36" s="195"/>
     </row>
-    <row r="37" spans="2:8" ht="15" customHeight="1">
+    <row r="37" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B37" s="4" t="s">
         <v>12</v>
       </c>
@@ -10101,7 +10113,7 @@
       </c>
       <c r="H37" s="195"/>
     </row>
-    <row r="38" spans="2:8" ht="15" customHeight="1">
+    <row r="38" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B38" s="4" t="s">
         <v>13</v>
       </c>
@@ -10117,7 +10129,7 @@
       </c>
       <c r="H38" s="195"/>
     </row>
-    <row r="39" spans="2:8" ht="15" customHeight="1">
+    <row r="39" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B39" s="2" t="s">
         <v>14</v>
       </c>
@@ -10136,7 +10148,7 @@
         <v>382021.2</v>
       </c>
     </row>
-    <row r="40" spans="2:8" ht="15" customHeight="1">
+    <row r="40" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B40" s="80" t="s">
         <v>200</v>
       </c>
@@ -10156,7 +10168,7 @@
         <v>9182676.8999999985</v>
       </c>
     </row>
-    <row r="41" spans="2:8" ht="15" customHeight="1">
+    <row r="41" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B41" s="4" t="s">
         <v>15</v>
       </c>
@@ -10176,7 +10188,7 @@
         <v>8919164.6999999993</v>
       </c>
     </row>
-    <row r="42" spans="2:8" ht="15" customHeight="1">
+    <row r="42" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B42" s="83" t="s">
         <v>20</v>
       </c>
@@ -10195,7 +10207,7 @@
         <v>263512.2</v>
       </c>
     </row>
-    <row r="44" spans="2:8" ht="15" customHeight="1">
+    <row r="44" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B44" s="79" t="s">
         <v>93</v>
       </c>
@@ -10206,7 +10218,7 @@
       <c r="G44" s="37"/>
       <c r="H44" s="37"/>
     </row>
-    <row r="45" spans="2:8" ht="15" customHeight="1">
+    <row r="45" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B45" s="16" t="s">
         <v>266</v>
       </c>
@@ -10220,7 +10232,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="46" spans="2:8" ht="15" customHeight="1">
+    <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B46" s="1" t="s">
         <v>268</v>
       </c>
@@ -10234,7 +10246,7 @@
       </c>
       <c r="F46" s="253"/>
     </row>
-    <row r="47" spans="2:8" ht="15" customHeight="1">
+    <row r="47" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B47" s="1" t="str">
         <f>"Equity per share ("&amp;Market_currency&amp;")"</f>
         <v>Equity per share (HKD)</v>
@@ -10249,10 +10261,10 @@
       </c>
       <c r="F47" s="253"/>
     </row>
-    <row r="48" spans="2:8" ht="15" customHeight="1">
+    <row r="48" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F48" s="253"/>
     </row>
-    <row r="49" spans="2:8" ht="15" customHeight="1">
+    <row r="49" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B49" s="157" t="s">
         <v>139</v>
       </c>
@@ -10265,7 +10277,7 @@
       <c r="E49" s="2"/>
       <c r="F49" s="253"/>
     </row>
-    <row r="50" spans="2:8" ht="15" customHeight="1">
+    <row r="50" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B50" s="8" t="s">
         <v>91</v>
       </c>
@@ -10279,7 +10291,7 @@
       </c>
       <c r="F50" s="253"/>
     </row>
-    <row r="51" spans="2:8" ht="15" customHeight="1">
+    <row r="51" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B51" s="1" t="s">
         <v>172</v>
       </c>
@@ -10290,10 +10302,10 @@
       </c>
       <c r="F51" s="253"/>
     </row>
-    <row r="52" spans="2:8" ht="15" customHeight="1">
+    <row r="52" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F52" s="253"/>
     </row>
-    <row r="53" spans="2:8" ht="15" customHeight="1">
+    <row r="53" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B53" s="157" t="s">
         <v>138</v>
       </c>
@@ -10305,7 +10317,7 @@
       </c>
       <c r="F53" s="253"/>
     </row>
-    <row r="54" spans="2:8" ht="15" customHeight="1">
+    <row r="54" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B54" s="1" t="s">
         <v>135</v>
       </c>
@@ -10319,7 +10331,7 @@
       </c>
       <c r="F54" s="253"/>
     </row>
-    <row r="55" spans="2:8" ht="15" customHeight="1">
+    <row r="55" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B55" s="1" t="s">
         <v>137</v>
       </c>
@@ -10333,10 +10345,10 @@
       </c>
       <c r="F55" s="253"/>
     </row>
-    <row r="56" spans="2:8" ht="15" customHeight="1">
+    <row r="56" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F56" s="253"/>
     </row>
-    <row r="57" spans="2:8" ht="15" customHeight="1">
+    <row r="57" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B57" s="157" t="s">
         <v>171</v>
       </c>
@@ -10348,7 +10360,7 @@
       </c>
       <c r="F57" s="253"/>
     </row>
-    <row r="58" spans="2:8" ht="15" customHeight="1">
+    <row r="58" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B58" s="2" t="s">
         <v>87</v>
       </c>
@@ -10359,7 +10371,7 @@
       </c>
       <c r="F58" s="5"/>
     </row>
-    <row r="59" spans="2:8" ht="15" customHeight="1">
+    <row r="59" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B59" s="1" t="s">
         <v>90</v>
       </c>
@@ -10370,10 +10382,10 @@
       </c>
       <c r="F59" s="253"/>
     </row>
-    <row r="60" spans="2:8" ht="15" customHeight="1">
+    <row r="60" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F60" s="253"/>
     </row>
-    <row r="61" spans="2:8" ht="15" customHeight="1">
+    <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B61" s="157" t="s">
         <v>269</v>
       </c>
@@ -10385,7 +10397,7 @@
       </c>
       <c r="F61" s="253"/>
     </row>
-    <row r="62" spans="2:8" ht="15" customHeight="1">
+    <row r="62" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B62" s="1" t="s">
         <v>241</v>
       </c>
@@ -10401,7 +10413,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="64" spans="2:8" ht="15" customHeight="1">
+    <row r="64" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B64" s="79" t="s">
         <v>189</v>
       </c>
@@ -10412,7 +10424,7 @@
       <c r="G64" s="37"/>
       <c r="H64" s="37"/>
     </row>
-    <row r="65" spans="2:6" ht="15" customHeight="1">
+    <row r="65" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B65" s="16" t="s">
         <v>184</v>
       </c>
@@ -10426,7 +10438,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="66" spans="2:6" ht="15" customHeight="1">
+    <row r="66" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B66" s="105" t="s">
         <v>183</v>
       </c>
@@ -10442,7 +10454,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="67" spans="2:6" ht="15" customHeight="1">
+    <row r="67" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B67" s="105" t="s">
         <v>173</v>
       </c>
@@ -10452,7 +10464,7 @@
       </c>
       <c r="F67" s="253"/>
     </row>
-    <row r="68" spans="2:6" ht="15" customHeight="1">
+    <row r="68" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B68" s="105" t="s">
         <v>177</v>
       </c>
@@ -10462,7 +10474,7 @@
       </c>
       <c r="F68" s="253"/>
     </row>
-    <row r="69" spans="2:6" ht="15" customHeight="1">
+    <row r="69" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B69" s="105" t="s">
         <v>175</v>
       </c>
@@ -10472,7 +10484,7 @@
       </c>
       <c r="F69" s="253"/>
     </row>
-    <row r="70" spans="2:6" ht="15" customHeight="1">
+    <row r="70" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B70" s="80" t="s">
         <v>184</v>
       </c>
@@ -10482,10 +10494,10 @@
       </c>
       <c r="F70" s="253"/>
     </row>
-    <row r="71" spans="2:6" ht="15" customHeight="1">
+    <row r="71" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F71" s="253"/>
     </row>
-    <row r="72" spans="2:6" ht="15" customHeight="1">
+    <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B72" s="255" t="s">
         <v>309</v>
       </c>
@@ -10497,7 +10509,7 @@
       </c>
       <c r="F72" s="253"/>
     </row>
-    <row r="73" spans="2:6" ht="15" customHeight="1">
+    <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B73" s="105" t="s">
         <v>308</v>
       </c>
@@ -10513,7 +10525,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="74" spans="2:6" ht="15" customHeight="1">
+    <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B74" s="257" t="s">
         <v>312</v>
       </c>
@@ -10529,7 +10541,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="75" spans="2:6" ht="15" customHeight="1">
+    <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B75" s="80" t="s">
         <v>311</v>
       </c>
@@ -10542,7 +10554,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="76" spans="2:6" ht="15" customHeight="1">
+    <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B76" s="259" t="s">
         <v>313</v>
       </c>
@@ -10555,10 +10567,10 @@
         <v>314</v>
       </c>
     </row>
-    <row r="77" spans="2:6" ht="15" customHeight="1">
+    <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F77" s="253"/>
     </row>
-    <row r="78" spans="2:6" ht="15" customHeight="1">
+    <row r="78" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B78" s="16" t="s">
         <v>185</v>
       </c>
@@ -10570,7 +10582,7 @@
       </c>
       <c r="F78" s="253"/>
     </row>
-    <row r="79" spans="2:6" ht="15" customHeight="1">
+    <row r="79" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B79" s="105" t="s">
         <v>174</v>
       </c>
@@ -10584,7 +10596,7 @@
       </c>
       <c r="F79" s="253"/>
     </row>
-    <row r="80" spans="2:6" ht="15" customHeight="1">
+    <row r="80" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B80" s="105" t="s">
         <v>178</v>
       </c>
@@ -10598,7 +10610,7 @@
       </c>
       <c r="F80" s="253"/>
     </row>
-    <row r="81" spans="2:8" ht="15" customHeight="1">
+    <row r="81" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B81" s="105" t="s">
         <v>176</v>
       </c>
@@ -10612,7 +10624,7 @@
       </c>
       <c r="F81" s="253"/>
     </row>
-    <row r="82" spans="2:8" ht="15" customHeight="1">
+    <row r="82" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B82" s="80" t="s">
         <v>185</v>
       </c>
@@ -10626,7 +10638,7 @@
       </c>
       <c r="F82" s="253"/>
     </row>
-    <row r="84" spans="2:8" ht="15" customHeight="1">
+    <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B84" s="79" t="s">
         <v>283</v>
       </c>
@@ -10637,7 +10649,7 @@
       <c r="G84" s="37"/>
       <c r="H84" s="37"/>
     </row>
-    <row r="85" spans="2:8" ht="15" customHeight="1">
+    <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B85" s="16" t="s">
         <v>284</v>
       </c>
@@ -10645,7 +10657,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="86" spans="2:8" ht="15" customHeight="1">
+    <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B86" s="238" t="s">
         <v>281</v>
       </c>
@@ -10662,7 +10674,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="87" spans="2:8" ht="15" customHeight="1">
+    <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B87" s="238" t="s">
         <v>282</v>
       </c>
@@ -10679,7 +10691,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="88" spans="2:8" ht="15" customHeight="1">
+    <row r="88" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B88" s="239" t="s">
         <v>185</v>
       </c>
@@ -10696,7 +10708,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="89" spans="2:8" ht="15" customHeight="1">
+    <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B89" s="80" t="s">
         <v>286</v>
       </c>
@@ -10727,19 +10739,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q809"/>
-  <sheetFormatPr defaultColWidth="12.265625" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="1.265625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="26.265625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="20.73046875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="2.73046875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="25.1328125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="2.73046875" style="2" customWidth="1"/>
-    <col min="7" max="17" width="20.73046875" style="2" customWidth="1"/>
-    <col min="18" max="16384" width="12.265625" style="2"/>
+    <col min="1" max="1" width="1.33203125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="26.33203125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="20.6640625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="2.6640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="25.1640625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="2.6640625" style="2" customWidth="1"/>
+    <col min="7" max="17" width="20.6640625" style="2" customWidth="1"/>
+    <col min="18" max="16384" width="12.33203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.75" customHeight="1">
+    <row r="1" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="3"/>
       <c r="B1" s="90" t="str">
         <f>Thesis!C25</f>
@@ -10796,7 +10808,7 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="15.75" customHeight="1">
+    <row r="2" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="54" t="s">
         <v>96</v>
@@ -10819,7 +10831,7 @@
       <c r="P2" s="37"/>
       <c r="Q2" s="37"/>
     </row>
-    <row r="3" spans="1:17" ht="15.75" customHeight="1">
+    <row r="3" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="10"/>
       <c r="B3" s="16" t="s">
         <v>64</v>
@@ -10833,7 +10845,7 @@
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
     </row>
-    <row r="4" spans="1:17" ht="15.75" customHeight="1">
+    <row r="4" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="10"/>
       <c r="B4" s="26" t="s">
         <v>0</v>
@@ -10890,7 +10902,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="15.75" customHeight="1">
+    <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="10"/>
       <c r="B5" s="2" t="s">
         <v>44</v>
@@ -10945,7 +10957,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="15.75" customHeight="1">
+    <row r="6" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="10"/>
       <c r="B6" s="31" t="s">
         <v>46</v>
@@ -11000,7 +11012,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="15.75" customHeight="1">
+    <row r="7" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="10"/>
       <c r="B7" s="8" t="s">
         <v>43</v>
@@ -11055,7 +11067,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="15.75" customHeight="1">
+    <row r="8" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="10"/>
       <c r="B8" s="29" t="s">
         <v>148</v>
@@ -11112,7 +11124,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="15.75" customHeight="1">
+    <row r="9" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="10"/>
       <c r="B9" s="2" t="s">
         <v>63</v>
@@ -11167,7 +11179,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="15.75" customHeight="1">
+    <row r="10" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="10"/>
       <c r="B10" s="2" t="s">
         <v>78</v>
@@ -11222,7 +11234,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="15.75" customHeight="1">
+    <row r="11" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="10"/>
       <c r="B11" s="31" t="s">
         <v>190</v>
@@ -11279,7 +11291,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="15.75" customHeight="1">
+    <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="10"/>
       <c r="B12" s="2" t="s">
         <v>66</v>
@@ -11334,7 +11346,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="15.75" customHeight="1">
+    <row r="13" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="10"/>
       <c r="B13" s="70" t="s">
         <v>160</v>
@@ -11389,7 +11401,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="15.75" customHeight="1">
+    <row r="14" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="10"/>
       <c r="B14" s="2" t="s">
         <v>61</v>
@@ -11444,7 +11456,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="15.75" customHeight="1">
+    <row r="15" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="10"/>
       <c r="B15" s="40" t="s">
         <v>239</v>
@@ -11501,7 +11513,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="15.75" customHeight="1">
+    <row r="16" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="10"/>
       <c r="B16" s="41" t="s">
         <v>150</v>
@@ -11558,7 +11570,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="15.75" customHeight="1">
+    <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="10"/>
       <c r="B17" s="27" t="s">
         <v>50</v>
@@ -11584,7 +11596,7 @@
       <c r="P17" s="335"/>
       <c r="Q17" s="335"/>
     </row>
-    <row r="18" spans="1:17" ht="15.75" customHeight="1">
+    <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="10"/>
       <c r="B18" s="27" t="s">
         <v>95</v>
@@ -11609,7 +11621,7 @@
       <c r="P18" s="336"/>
       <c r="Q18" s="336"/>
     </row>
-    <row r="19" spans="1:17" ht="15.75" customHeight="1">
+    <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="10"/>
       <c r="B19" s="31" t="s">
         <v>64</v>
@@ -11666,7 +11678,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="15.75" customHeight="1">
+    <row r="20" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="10"/>
       <c r="B20" s="27"/>
       <c r="C20" s="62"/>
@@ -11685,7 +11697,7 @@
       <c r="P20" s="12"/>
       <c r="Q20" s="12"/>
     </row>
-    <row r="21" spans="1:17" ht="15.75" customHeight="1">
+    <row r="21" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="10"/>
       <c r="B21" s="54" t="s">
         <v>201</v>
@@ -11708,7 +11720,7 @@
       <c r="P21" s="37"/>
       <c r="Q21" s="37"/>
     </row>
-    <row r="22" spans="1:17" ht="15.75" customHeight="1">
+    <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="10"/>
       <c r="B22" s="64" t="s">
         <v>44</v>
@@ -11729,7 +11741,7 @@
       <c r="P22" s="12"/>
       <c r="Q22" s="12"/>
     </row>
-    <row r="23" spans="1:17" ht="15.75" customHeight="1">
+    <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="10"/>
       <c r="B23" s="27" t="s">
         <v>41</v>
@@ -11786,7 +11798,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="15.75" customHeight="1">
+    <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="10"/>
       <c r="B24" s="68" t="s">
         <v>60</v>
@@ -11843,7 +11855,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="15.75" customHeight="1">
+    <row r="25" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="10"/>
       <c r="B25" s="70" t="s">
         <v>44</v>
@@ -11900,18 +11912,18 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="15.75" customHeight="1">
+    <row r="26" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="10"/>
       <c r="E26" s="268"/>
     </row>
-    <row r="27" spans="1:17" ht="15.75" customHeight="1">
+    <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="10"/>
       <c r="B27" s="64" t="s">
         <v>202</v>
       </c>
       <c r="E27" s="268"/>
     </row>
-    <row r="28" spans="1:17" ht="15.75" customHeight="1">
+    <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="10"/>
       <c r="B28" s="26" t="s">
         <v>41</v>
@@ -11970,7 +11982,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:17" ht="15.75" customHeight="1">
+    <row r="29" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="10"/>
       <c r="B29" s="68" t="str">
         <f>B24</f>
@@ -12030,7 +12042,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="15.75" customHeight="1">
+    <row r="30" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="10"/>
       <c r="B30" s="70" t="s">
         <v>44</v>
@@ -12085,18 +12097,18 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="15.75" customHeight="1">
+    <row r="31" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="10"/>
       <c r="E31" s="268"/>
     </row>
-    <row r="32" spans="1:17" ht="15.75" customHeight="1">
+    <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="10"/>
       <c r="B32" s="64" t="s">
         <v>43</v>
       </c>
       <c r="E32" s="268"/>
     </row>
-    <row r="33" spans="1:17" ht="15.75" customHeight="1">
+    <row r="33" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="10"/>
       <c r="B33" s="8" t="s">
         <v>170</v>
@@ -12153,7 +12165,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:17" ht="15.75" customHeight="1">
+    <row r="34" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="10"/>
       <c r="B34" s="27" t="s">
         <v>47</v>
@@ -12212,7 +12224,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:17" ht="15.75" customHeight="1">
+    <row r="35" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="10"/>
       <c r="B35" s="70" t="s">
         <v>43</v>
@@ -12269,18 +12281,18 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="15.75" customHeight="1">
+    <row r="36" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="10"/>
       <c r="E36" s="268"/>
     </row>
-    <row r="37" spans="1:17" ht="15.75" customHeight="1">
+    <row r="37" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="10"/>
       <c r="B37" s="64" t="s">
         <v>203</v>
       </c>
       <c r="E37" s="268"/>
     </row>
-    <row r="38" spans="1:17" ht="15.75" customHeight="1">
+    <row r="38" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="10"/>
       <c r="B38" s="2" t="str">
         <f>B33</f>
@@ -12338,7 +12350,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:17" ht="15.75" customHeight="1">
+    <row r="39" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="10"/>
       <c r="B39" s="27" t="str">
         <f>B34</f>
@@ -12396,7 +12408,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="1:17" ht="15.75" customHeight="1">
+    <row r="40" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="10"/>
       <c r="B40" s="70" t="s">
         <v>43</v>
@@ -12451,18 +12463,18 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="1:17" ht="15.75" customHeight="1">
+    <row r="41" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="10"/>
       <c r="E41" s="268"/>
     </row>
-    <row r="42" spans="1:17" ht="15.75" customHeight="1">
+    <row r="42" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="10"/>
       <c r="B42" s="64" t="s">
         <v>204</v>
       </c>
       <c r="E42" s="268"/>
     </row>
-    <row r="43" spans="1:17" ht="15.75" customHeight="1">
+    <row r="43" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
         <v>167</v>
@@ -12520,10 +12532,10 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="1:17" ht="15.75" customHeight="1">
+    <row r="44" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="10"/>
     </row>
-    <row r="45" spans="1:17" ht="15.75" customHeight="1">
+    <row r="45" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="10"/>
       <c r="B45" s="54" t="s">
         <v>205</v>
@@ -12546,14 +12558,14 @@
       <c r="P45" s="37"/>
       <c r="Q45" s="37"/>
     </row>
-    <row r="46" spans="1:17" ht="15.75" customHeight="1">
+    <row r="46" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="10"/>
       <c r="B46" s="64" t="s">
         <v>58</v>
       </c>
       <c r="E46" s="268"/>
     </row>
-    <row r="47" spans="1:17" ht="15.75" customHeight="1">
+    <row r="47" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="10"/>
       <c r="B47" s="2" t="s">
         <v>37</v>
@@ -12608,7 +12620,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:17" ht="15.75" customHeight="1">
+    <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
         <v>336</v>
@@ -12663,7 +12675,7 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:17" ht="15.75" customHeight="1">
+    <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="10"/>
       <c r="B49" s="287" t="s">
         <v>333</v>
@@ -12720,7 +12732,7 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="1:17" ht="15.75" customHeight="1">
+    <row r="50" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="10"/>
       <c r="B50" s="70" t="s">
         <v>66</v>
@@ -12775,11 +12787,11 @@
         <v/>
       </c>
     </row>
-    <row r="51" spans="1:17" ht="15.75" customHeight="1">
+    <row r="51" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="10"/>
       <c r="E51" s="268"/>
     </row>
-    <row r="52" spans="1:17" ht="15.75" customHeight="1">
+    <row r="52" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" s="10"/>
       <c r="B52" s="72" t="s">
         <v>151</v>
@@ -12789,7 +12801,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="53" spans="1:17" ht="15.75" customHeight="1">
+    <row r="53" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" s="10"/>
       <c r="B53" s="8" t="s">
         <v>86</v>
@@ -12815,7 +12827,7 @@
       <c r="P53" s="169"/>
       <c r="Q53" s="169"/>
     </row>
-    <row r="54" spans="1:17" ht="15.75" customHeight="1">
+    <row r="54" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A54" s="10"/>
       <c r="B54" s="8" t="s">
         <v>85</v>
@@ -12842,7 +12854,7 @@
       <c r="P54" s="169"/>
       <c r="Q54" s="169"/>
     </row>
-    <row r="55" spans="1:17" ht="15.75" customHeight="1">
+    <row r="55" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A55" s="10"/>
       <c r="B55" s="26" t="s">
         <v>88</v>
@@ -12897,11 +12909,11 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="1:17" ht="15.75" customHeight="1">
+    <row r="56" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A56" s="10"/>
       <c r="E56" s="268"/>
     </row>
-    <row r="57" spans="1:17" ht="15.75" customHeight="1">
+    <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A57" s="10"/>
       <c r="B57" s="64" t="s">
         <v>164</v>
@@ -12911,7 +12923,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="58" spans="1:17" ht="15.75" customHeight="1">
+    <row r="58" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="10"/>
       <c r="B58" s="40" t="s">
         <v>163</v>
@@ -12966,7 +12978,7 @@
         <v/>
       </c>
     </row>
-    <row r="59" spans="1:17" ht="15.75" customHeight="1">
+    <row r="59" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A59" s="10"/>
       <c r="B59" s="40" t="s">
         <v>155</v>
@@ -13021,7 +13033,7 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="1:17" ht="15.75" customHeight="1">
+    <row r="60" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="10"/>
       <c r="B60" s="40" t="s">
         <v>154</v>
@@ -13076,7 +13088,7 @@
         <v/>
       </c>
     </row>
-    <row r="61" spans="1:17" ht="15.75" customHeight="1">
+    <row r="61" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A61" s="10"/>
       <c r="B61" s="31" t="s">
         <v>190</v>
@@ -13131,7 +13143,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="1:17" ht="15.75" customHeight="1">
+    <row r="62" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A62" s="10"/>
       <c r="B62" s="40" t="s">
         <v>156</v>
@@ -13187,7 +13199,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="1:17" ht="15.75" customHeight="1">
+    <row r="63" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A63" s="10"/>
       <c r="B63" s="31" t="s">
         <v>191</v>
@@ -13242,11 +13254,11 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="1:17" ht="15.75" customHeight="1">
+    <row r="64" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A64" s="10"/>
       <c r="E64" s="268"/>
     </row>
-    <row r="65" spans="1:17" ht="15.75" customHeight="1">
+    <row r="65" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A65" s="10"/>
       <c r="B65" s="96" t="s">
         <v>165</v>
@@ -13256,7 +13268,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="66" spans="1:17" ht="15.75" customHeight="1">
+    <row r="66" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A66" s="10"/>
       <c r="B66" s="40" t="s">
         <v>163</v>
@@ -13281,7 +13293,7 @@
       <c r="P66" s="175"/>
       <c r="Q66" s="175"/>
     </row>
-    <row r="67" spans="1:17" ht="15.75" customHeight="1">
+    <row r="67" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A67" s="10"/>
       <c r="B67" s="105" t="s">
         <v>153</v>
@@ -13306,7 +13318,7 @@
       <c r="P67" s="175"/>
       <c r="Q67" s="175"/>
     </row>
-    <row r="68" spans="1:17" ht="15.75" customHeight="1">
+    <row r="68" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A68" s="10"/>
       <c r="B68" s="105" t="s">
         <v>154</v>
@@ -13331,7 +13343,7 @@
       <c r="P68" s="175"/>
       <c r="Q68" s="175"/>
     </row>
-    <row r="69" spans="1:17" ht="15.75" customHeight="1">
+    <row r="69" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A69" s="10"/>
       <c r="B69" s="31" t="s">
         <v>190</v>
@@ -13358,10 +13370,10 @@
       <c r="P69" s="175"/>
       <c r="Q69" s="175"/>
     </row>
-    <row r="70" spans="1:17" ht="15.75" customHeight="1">
+    <row r="70" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A70" s="10"/>
     </row>
-    <row r="71" spans="1:17" ht="15.75" customHeight="1">
+    <row r="71" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="10"/>
       <c r="B71" s="54" t="s">
         <v>208</v>
@@ -13384,7 +13396,7 @@
       <c r="P71" s="37"/>
       <c r="Q71" s="37"/>
     </row>
-    <row r="72" spans="1:17" ht="15.75" customHeight="1">
+    <row r="72" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A72" s="10"/>
       <c r="B72" s="72" t="s">
         <v>212</v>
@@ -13405,7 +13417,7 @@
       <c r="P72" s="12"/>
       <c r="Q72" s="12"/>
     </row>
-    <row r="73" spans="1:17" ht="15.75" customHeight="1">
+    <row r="73" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A73" s="10"/>
       <c r="B73" s="2" t="s">
         <v>44</v>
@@ -13462,7 +13474,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="1:17" ht="15.75" customHeight="1">
+    <row r="74" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A74" s="10"/>
       <c r="B74" s="31" t="s">
         <v>46</v>
@@ -13519,7 +13531,7 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="1:17" ht="15.75" customHeight="1">
+    <row r="75" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A75" s="10"/>
       <c r="B75" s="8" t="s">
         <v>43</v>
@@ -13576,7 +13588,7 @@
         <v/>
       </c>
     </row>
-    <row r="76" spans="1:17" ht="15.75" customHeight="1">
+    <row r="76" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A76" s="10"/>
       <c r="B76" s="29" t="s">
         <v>148</v>
@@ -13633,7 +13645,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="1:17" ht="15.75" customHeight="1">
+    <row r="77" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A77" s="10"/>
       <c r="B77" s="2" t="s">
         <v>63</v>
@@ -13690,7 +13702,7 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="1:17" ht="15.75" customHeight="1">
+    <row r="78" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A78" s="10"/>
       <c r="B78" s="2" t="s">
         <v>78</v>
@@ -13749,7 +13761,7 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="1:17" ht="15.75" customHeight="1">
+    <row r="79" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A79" s="10"/>
       <c r="B79" s="31" t="s">
         <v>149</v>
@@ -13806,7 +13818,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="1:17" ht="15.75" customHeight="1">
+    <row r="80" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A80" s="10"/>
       <c r="B80" s="2" t="s">
         <v>66</v>
@@ -13863,7 +13875,7 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="1:17" ht="15.75" customHeight="1">
+    <row r="81" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A81" s="10"/>
       <c r="B81" s="70" t="s">
         <v>160</v>
@@ -13920,7 +13932,7 @@
         <v/>
       </c>
     </row>
-    <row r="82" spans="1:17" ht="15.75" customHeight="1">
+    <row r="82" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A82" s="10"/>
       <c r="B82" s="2" t="s">
         <v>61</v>
@@ -13977,7 +13989,7 @@
         <v/>
       </c>
     </row>
-    <row r="83" spans="1:17" ht="15.75" customHeight="1">
+    <row r="83" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A83" s="10"/>
       <c r="B83" s="40" t="str">
         <f>B15</f>
@@ -14035,7 +14047,7 @@
         <v/>
       </c>
     </row>
-    <row r="84" spans="1:17" ht="15.75" customHeight="1">
+    <row r="84" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A84" s="10"/>
       <c r="B84" s="41" t="s">
         <v>150</v>
@@ -14092,7 +14104,7 @@
         <v/>
       </c>
     </row>
-    <row r="85" spans="1:17" ht="15.75" customHeight="1">
+    <row r="85" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A85" s="10"/>
       <c r="B85" s="27" t="s">
         <v>50</v>
@@ -14118,7 +14130,7 @@
       <c r="P85" s="226"/>
       <c r="Q85" s="226"/>
     </row>
-    <row r="86" spans="1:17" ht="15.75" customHeight="1">
+    <row r="86" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A86" s="10"/>
       <c r="B86" s="8" t="s">
         <v>95</v>
@@ -14142,7 +14154,7 @@
       <c r="P86" s="169"/>
       <c r="Q86" s="169"/>
     </row>
-    <row r="87" spans="1:17" ht="15.75" customHeight="1">
+    <row r="87" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A87" s="10"/>
       <c r="B87" s="31" t="s">
         <v>136</v>
@@ -14199,18 +14211,18 @@
         <v/>
       </c>
     </row>
-    <row r="88" spans="1:17" ht="15.75" customHeight="1">
+    <row r="88" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A88" s="10"/>
       <c r="E88" s="268"/>
     </row>
-    <row r="89" spans="1:17" ht="15.75" customHeight="1">
+    <row r="89" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A89" s="10"/>
       <c r="B89" s="64" t="s">
         <v>210</v>
       </c>
       <c r="E89" s="268"/>
     </row>
-    <row r="90" spans="1:17" ht="15.75" customHeight="1">
+    <row r="90" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A90" s="10"/>
       <c r="B90" s="2" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
@@ -14266,7 +14278,7 @@
         <v/>
       </c>
     </row>
-    <row r="91" spans="1:17" ht="15.75" customHeight="1">
+    <row r="91" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A91" s="10"/>
       <c r="B91" s="2" t="str">
         <f>"Dividend ("&amp;Market_currency&amp;")"</f>
@@ -14322,7 +14334,7 @@
         <v/>
       </c>
     </row>
-    <row r="92" spans="1:17" ht="15.75" customHeight="1">
+    <row r="92" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A92" s="10"/>
       <c r="B92" s="2" t="s">
         <v>209</v>
@@ -14377,7 +14389,7 @@
         <v/>
       </c>
     </row>
-    <row r="93" spans="1:17" ht="15.75" customHeight="1">
+    <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
         <v>433</v>
@@ -14398,27 +14410,27 @@
       <c r="P93" s="357"/>
       <c r="Q93" s="357"/>
     </row>
-    <row r="94" spans="1:17" ht="15.75" customHeight="1">
+    <row r="94" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A94" s="10"/>
       <c r="B94" s="2" t="s">
         <v>432</v>
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>9.0604026845637592E-2</v>
+        <v>9.1836734693877556E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>9.0604026845637592E-2</v>
+        <v>9.1836734693877556E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>8.4563758389261764E-2</v>
+        <v>8.5714285714285729E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>0.12986577181208056</v>
+        <v>0.13163265306122451</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
@@ -14453,11 +14465,11 @@
         <v/>
       </c>
     </row>
-    <row r="95" spans="1:17" ht="15.75" customHeight="1">
+    <row r="95" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A95" s="10"/>
       <c r="E95" s="268"/>
     </row>
-    <row r="96" spans="1:17" ht="15.75" customHeight="1">
+    <row r="96" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A96" s="10"/>
       <c r="B96" s="157" t="s">
         <v>82</v>
@@ -14478,7 +14490,7 @@
       <c r="P96" s="12"/>
       <c r="Q96" s="12"/>
     </row>
-    <row r="97" spans="1:17" ht="15.75" customHeight="1">
+    <row r="97" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A97" s="10"/>
       <c r="B97" s="27" t="s">
         <v>140</v>
@@ -14535,7 +14547,7 @@
         <v/>
       </c>
     </row>
-    <row r="98" spans="1:17" ht="15.75" customHeight="1">
+    <row r="98" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A98" s="10"/>
       <c r="B98" s="70" t="s">
         <v>160</v>
@@ -14592,10 +14604,10 @@
         <v/>
       </c>
     </row>
-    <row r="99" spans="1:17" ht="15.75" customHeight="1">
+    <row r="99" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A99" s="10"/>
     </row>
-    <row r="100" spans="1:17" ht="15.75" customHeight="1">
+    <row r="100" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="3"/>
       <c r="B100" s="54" t="s">
         <v>211</v>
@@ -14618,7 +14630,7 @@
       <c r="P100" s="37"/>
       <c r="Q100" s="37"/>
     </row>
-    <row r="101" spans="1:17" ht="15.75" customHeight="1">
+    <row r="101" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A101" s="10"/>
       <c r="B101" s="64" t="s">
         <v>26</v>
@@ -14628,7 +14640,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="102" spans="1:17" ht="15.75" customHeight="1">
+    <row r="102" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A102" s="10"/>
       <c r="B102" s="26" t="s">
         <v>1</v>
@@ -14685,7 +14697,7 @@
         <v/>
       </c>
     </row>
-    <row r="103" spans="1:17" ht="15.75" customHeight="1">
+    <row r="103" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A103" s="10"/>
       <c r="B103" s="93" t="s">
         <v>206</v>
@@ -14742,7 +14754,7 @@
         <v/>
       </c>
     </row>
-    <row r="104" spans="1:17" ht="15.75" customHeight="1">
+    <row r="104" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A104" s="10"/>
       <c r="B104" s="93" t="s">
         <v>207</v>
@@ -14799,7 +14811,7 @@
         <v/>
       </c>
     </row>
-    <row r="105" spans="1:17" ht="15.75" customHeight="1">
+    <row r="105" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A105" s="10"/>
       <c r="B105" s="26" t="s">
         <v>38</v>
@@ -14856,7 +14868,7 @@
         <v/>
       </c>
     </row>
-    <row r="106" spans="1:17" ht="15.75" customHeight="1">
+    <row r="106" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A106" s="10"/>
       <c r="B106" s="26" t="s">
         <v>28</v>
@@ -14913,11 +14925,11 @@
         <v/>
       </c>
     </row>
-    <row r="107" spans="1:17" ht="15.75" customHeight="1">
+    <row r="107" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A107" s="10"/>
       <c r="E107" s="268"/>
     </row>
-    <row r="108" spans="1:17" ht="15.75" customHeight="1">
+    <row r="108" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A108" s="10"/>
       <c r="B108" s="91" t="s">
         <v>216</v>
@@ -14940,7 +14952,7 @@
       <c r="P108" s="12"/>
       <c r="Q108" s="12"/>
     </row>
-    <row r="109" spans="1:17" ht="15.75" customHeight="1">
+    <row r="109" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A109" s="10"/>
       <c r="B109" s="26" t="s">
         <v>213</v>
@@ -14997,7 +15009,7 @@
         <v/>
       </c>
     </row>
-    <row r="110" spans="1:17" ht="15.75" customHeight="1">
+    <row r="110" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A110" s="10"/>
       <c r="B110" s="26" t="s">
         <v>214</v>
@@ -15054,7 +15066,7 @@
         <v/>
       </c>
     </row>
-    <row r="111" spans="1:17" ht="15.75" customHeight="1">
+    <row r="111" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A111" s="10"/>
       <c r="B111" s="26" t="s">
         <v>67</v>
@@ -15081,18 +15093,18 @@
       <c r="P111" s="204"/>
       <c r="Q111" s="204"/>
     </row>
-    <row r="112" spans="1:17" ht="15.75" customHeight="1">
+    <row r="112" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A112" s="10"/>
       <c r="E112" s="268"/>
     </row>
-    <row r="113" spans="1:17" ht="15.75" customHeight="1">
+    <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A113" s="10"/>
       <c r="B113" s="64" t="s">
         <v>49</v>
       </c>
       <c r="E113" s="268"/>
     </row>
-    <row r="114" spans="1:17" ht="15.75" customHeight="1">
+    <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
         <v>372</v>
@@ -15144,7 +15156,7 @@
         <v/>
       </c>
     </row>
-    <row r="115" spans="1:17" ht="15.75" customHeight="1">
+    <row r="115" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A115" s="10"/>
       <c r="B115" s="2" t="s">
         <v>373</v>
@@ -15196,11 +15208,11 @@
         <v/>
       </c>
     </row>
-    <row r="116" spans="1:17" ht="15.75" customHeight="1">
+    <row r="116" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A116" s="10"/>
       <c r="E116" s="268"/>
     </row>
-    <row r="117" spans="1:17" ht="15.75" customHeight="1">
+    <row r="117" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A117" s="10"/>
       <c r="B117" s="91" t="s">
         <v>36</v>
@@ -15254,7 +15266,7 @@
         <v/>
       </c>
     </row>
-    <row r="118" spans="1:17" ht="15.75" customHeight="1">
+    <row r="118" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A118" s="10"/>
       <c r="B118" s="7" t="s">
         <v>217</v>
@@ -15309,7 +15321,7 @@
         <v/>
       </c>
     </row>
-    <row r="119" spans="1:17" ht="15.75" customHeight="1">
+    <row r="119" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B119" s="7" t="s">
         <v>81</v>
       </c>
@@ -15363,7 +15375,7 @@
         <v/>
       </c>
     </row>
-    <row r="120" spans="1:17" ht="15.75" customHeight="1">
+    <row r="120" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B120" s="7" t="s">
         <v>89</v>
       </c>
@@ -15419,7 +15431,7 @@
         <v/>
       </c>
     </row>
-    <row r="121" spans="1:17" ht="15.75" customHeight="1">
+    <row r="121" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A121" s="10"/>
       <c r="B121" s="70" t="s">
         <v>218</v>
@@ -15476,7 +15488,7 @@
         <v/>
       </c>
     </row>
-    <row r="122" spans="1:17" ht="15.75" customHeight="1">
+    <row r="122" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A122" s="10"/>
       <c r="B122" s="27"/>
       <c r="C122" s="62"/>
@@ -15495,7 +15507,7 @@
       <c r="P122" s="12"/>
       <c r="Q122" s="12"/>
     </row>
-    <row r="123" spans="1:17" ht="15.75" customHeight="1">
+    <row r="123" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="10"/>
       <c r="B123" s="54" t="s">
         <v>219</v>
@@ -15518,7 +15530,7 @@
       <c r="P123" s="37"/>
       <c r="Q123" s="37"/>
     </row>
-    <row r="124" spans="1:17" ht="15.75" customHeight="1">
+    <row r="124" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A124" s="10"/>
       <c r="B124" s="178" t="s">
         <v>166</v>
@@ -15539,7 +15551,7 @@
       <c r="P124" s="12"/>
       <c r="Q124" s="12"/>
     </row>
-    <row r="125" spans="1:17" ht="15.75" customHeight="1">
+    <row r="125" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A125" s="10"/>
       <c r="B125" s="27" t="str">
         <f>"FCFE per share ("&amp;Market_currency&amp;")"</f>
@@ -15597,795 +15609,795 @@
         <v/>
       </c>
     </row>
-    <row r="126" spans="1:17" ht="15.75" customHeight="1">
+    <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A126" s="10"/>
       <c r="B126" s="27" t="s">
         <v>264</v>
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>7.1966278637541126E-2</v>
+        <v>7.2945411680228764E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>8.3979553995435066E-2</v>
+        <v>8.5122132961359356E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>0.11556109333936013</v>
+        <v>0.11713335311268476</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>0.18741662619483773</v>
+        <v>0.18996651226551578</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>0.15399215775340608</v>
+        <v>0.1560872891514116</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>5.524442873858771E-2</v>
+        <v>5.5996053619384825E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>7.0132003872207291E-2</v>
+        <v>7.1086180795638693E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>6.2443182499543427E-2</v>
+        <v>6.3292749608380758E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>5.9306617957412419E-2</v>
+        <v>6.0113510718737759E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>1.0498454461658036E-2</v>
+        <v>1.0641290576782635E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>4.5479065329709512E-3</v>
+        <v>4.6097828123311006E-3</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
         <v/>
       </c>
     </row>
-    <row r="127" spans="1:17" ht="15.75" customHeight="1">
+    <row r="127" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B127" s="2" t="s">
         <v>375</v>
       </c>
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1196315351123069</v>
+        <v>0.12125917504580769</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15166310562858509</v>
+        <v>0.15372654924257945</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.21805240349836974</v>
+        <v>0.22101910286569454</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.20175038843473736</v>
+        <v>0.20449529167874742</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.8258096063441682E-2</v>
+        <v>7.9322832064304849E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.7523686738673395E-2</v>
+        <v>7.8578430775934266E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.5927720755850331E-2</v>
+        <v>7.6960750970215652E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.7948368059754178E-2</v>
+        <v>7.9008890074172611E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.4594504825456191E-3</v>
+        <v>4.520123278226513E-3</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-4.6895878149301538E-2</v>
+        <v>-4.7533917307795437E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
         <v/>
       </c>
     </row>
-    <row r="128" spans="1:17" ht="15.75" customHeight="1"/>
-    <row r="129" ht="15.75" customHeight="1"/>
-    <row r="130" ht="15.75" customHeight="1"/>
-    <row r="131" ht="15.75" customHeight="1"/>
-    <row r="132" ht="15.75" customHeight="1"/>
-    <row r="133" ht="15.75" customHeight="1"/>
-    <row r="134" ht="15.75" customHeight="1"/>
-    <row r="135" ht="15.75" customHeight="1"/>
-    <row r="136" ht="15.75" customHeight="1"/>
-    <row r="137" ht="15.75" customHeight="1"/>
-    <row r="138" ht="15.75" customHeight="1"/>
-    <row r="139" ht="15.75" customHeight="1"/>
-    <row r="140" ht="15.75" customHeight="1"/>
-    <row r="141" ht="15.75" customHeight="1"/>
-    <row r="142" ht="15.75" customHeight="1"/>
-    <row r="143" ht="15.75" customHeight="1"/>
-    <row r="144" ht="15.75" customHeight="1"/>
-    <row r="145" ht="15.75" customHeight="1"/>
-    <row r="146" ht="15.75" customHeight="1"/>
-    <row r="147" ht="15.75" customHeight="1"/>
-    <row r="148" ht="15.75" customHeight="1"/>
-    <row r="149" ht="15.75" customHeight="1"/>
-    <row r="150" ht="15.75" customHeight="1"/>
-    <row r="151" ht="15.75" customHeight="1"/>
-    <row r="152" ht="15.75" customHeight="1"/>
-    <row r="153" ht="15.75" customHeight="1"/>
-    <row r="154" ht="15.75" customHeight="1"/>
-    <row r="155" ht="15.75" customHeight="1"/>
-    <row r="156" ht="15.75" customHeight="1"/>
-    <row r="157" ht="15.75" customHeight="1"/>
-    <row r="158" ht="15.75" customHeight="1"/>
-    <row r="159" ht="15.75" customHeight="1"/>
-    <row r="160" ht="15.75" customHeight="1"/>
-    <row r="161" ht="15.75" customHeight="1"/>
-    <row r="162" ht="15.75" customHeight="1"/>
-    <row r="163" ht="15.75" customHeight="1"/>
-    <row r="164" ht="15.75" customHeight="1"/>
-    <row r="165" ht="15.75" customHeight="1"/>
-    <row r="166" ht="15.75" customHeight="1"/>
-    <row r="167" ht="15.75" customHeight="1"/>
-    <row r="168" ht="15.75" customHeight="1"/>
-    <row r="169" ht="15.75" customHeight="1"/>
-    <row r="170" ht="15.75" customHeight="1"/>
-    <row r="171" ht="15.75" customHeight="1"/>
-    <row r="172" ht="15.75" customHeight="1"/>
-    <row r="173" ht="15.75" customHeight="1"/>
-    <row r="174" ht="15.75" customHeight="1"/>
-    <row r="175" ht="15.75" customHeight="1"/>
-    <row r="176" ht="15.75" customHeight="1"/>
-    <row r="177" ht="15.75" customHeight="1"/>
-    <row r="178" ht="15.75" customHeight="1"/>
-    <row r="179" ht="15.75" customHeight="1"/>
-    <row r="180" ht="15.75" customHeight="1"/>
-    <row r="181" ht="15.75" customHeight="1"/>
-    <row r="182" ht="15.75" customHeight="1"/>
-    <row r="183" ht="15.75" customHeight="1"/>
-    <row r="184" ht="15.75" customHeight="1"/>
-    <row r="185" ht="15.75" customHeight="1"/>
-    <row r="186" ht="15.75" customHeight="1"/>
-    <row r="187" ht="15.75" customHeight="1"/>
-    <row r="188" ht="15.75" customHeight="1"/>
-    <row r="189" ht="15.75" customHeight="1"/>
-    <row r="190" ht="15.75" customHeight="1"/>
-    <row r="191" ht="15.75" customHeight="1"/>
-    <row r="192" ht="15.75" customHeight="1"/>
-    <row r="193" ht="15.75" customHeight="1"/>
-    <row r="194" ht="15.75" customHeight="1"/>
-    <row r="195" ht="15.75" customHeight="1"/>
-    <row r="196" ht="15.75" customHeight="1"/>
-    <row r="197" ht="15.75" customHeight="1"/>
-    <row r="198" ht="15.75" customHeight="1"/>
-    <row r="199" ht="15.75" customHeight="1"/>
-    <row r="200" ht="15.75" customHeight="1"/>
-    <row r="201" ht="15.75" customHeight="1"/>
-    <row r="202" ht="15.75" customHeight="1"/>
-    <row r="203" ht="15.75" customHeight="1"/>
-    <row r="204" ht="15.75" customHeight="1"/>
-    <row r="205" ht="15.75" customHeight="1"/>
-    <row r="206" ht="15.75" customHeight="1"/>
-    <row r="207" ht="15.75" customHeight="1"/>
-    <row r="208" ht="15.75" customHeight="1"/>
-    <row r="209" ht="15.75" customHeight="1"/>
-    <row r="210" ht="15.75" customHeight="1"/>
-    <row r="211" ht="15.75" customHeight="1"/>
-    <row r="212" ht="15.75" customHeight="1"/>
-    <row r="213" ht="15.75" customHeight="1"/>
-    <row r="214" ht="15.75" customHeight="1"/>
-    <row r="215" ht="15.75" customHeight="1"/>
-    <row r="216" ht="15.75" customHeight="1"/>
-    <row r="217" ht="15.75" customHeight="1"/>
-    <row r="218" ht="15.75" customHeight="1"/>
-    <row r="219" ht="15.75" customHeight="1"/>
-    <row r="220" ht="15.75" customHeight="1"/>
-    <row r="221" ht="15.75" customHeight="1"/>
-    <row r="222" ht="15.75" customHeight="1"/>
-    <row r="223" ht="15.75" customHeight="1"/>
-    <row r="224" ht="15.75" customHeight="1"/>
-    <row r="225" ht="15.75" customHeight="1"/>
-    <row r="226" ht="15.75" customHeight="1"/>
-    <row r="227" ht="15.75" customHeight="1"/>
-    <row r="228" ht="15.75" customHeight="1"/>
-    <row r="229" ht="15.75" customHeight="1"/>
-    <row r="230" ht="15.75" customHeight="1"/>
-    <row r="231" ht="15.75" customHeight="1"/>
-    <row r="232" ht="15.75" customHeight="1"/>
-    <row r="233" ht="15.75" customHeight="1"/>
-    <row r="234" ht="15.75" customHeight="1"/>
-    <row r="235" ht="15.75" customHeight="1"/>
-    <row r="236" ht="15.75" customHeight="1"/>
-    <row r="237" ht="15.75" customHeight="1"/>
-    <row r="238" ht="15.75" customHeight="1"/>
-    <row r="239" ht="15.75" customHeight="1"/>
-    <row r="240" ht="15.75" customHeight="1"/>
-    <row r="241" ht="15.75" customHeight="1"/>
-    <row r="242" ht="15.75" customHeight="1"/>
-    <row r="243" ht="15.75" customHeight="1"/>
-    <row r="244" ht="15.75" customHeight="1"/>
-    <row r="245" ht="15.75" customHeight="1"/>
-    <row r="246" ht="15.75" customHeight="1"/>
-    <row r="247" ht="15.75" customHeight="1"/>
-    <row r="248" ht="15.75" customHeight="1"/>
-    <row r="249" ht="15.75" customHeight="1"/>
-    <row r="250" ht="15.75" customHeight="1"/>
-    <row r="251" ht="15.75" customHeight="1"/>
-    <row r="252" ht="15.75" customHeight="1"/>
-    <row r="253" ht="15.75" customHeight="1"/>
-    <row r="254" ht="15.75" customHeight="1"/>
-    <row r="255" ht="15.75" customHeight="1"/>
-    <row r="256" ht="15.75" customHeight="1"/>
-    <row r="257" ht="15.75" customHeight="1"/>
-    <row r="258" ht="15.75" customHeight="1"/>
-    <row r="259" ht="15.75" customHeight="1"/>
-    <row r="260" ht="15.75" customHeight="1"/>
-    <row r="261" ht="15.75" customHeight="1"/>
-    <row r="262" ht="15.75" customHeight="1"/>
-    <row r="263" ht="15.75" customHeight="1"/>
-    <row r="264" ht="15.75" customHeight="1"/>
-    <row r="265" ht="15.75" customHeight="1"/>
-    <row r="266" ht="15.75" customHeight="1"/>
-    <row r="267" ht="15.75" customHeight="1"/>
-    <row r="268" ht="15.75" customHeight="1"/>
-    <row r="269" ht="15.75" customHeight="1"/>
-    <row r="270" ht="15.75" customHeight="1"/>
-    <row r="271" ht="15.75" customHeight="1"/>
-    <row r="272" ht="15.75" customHeight="1"/>
-    <row r="273" ht="15.75" customHeight="1"/>
-    <row r="274" ht="15.75" customHeight="1"/>
-    <row r="275" ht="15.75" customHeight="1"/>
-    <row r="276" ht="15.75" customHeight="1"/>
-    <row r="277" ht="15.75" customHeight="1"/>
-    <row r="278" ht="15.75" customHeight="1"/>
-    <row r="279" ht="15.75" customHeight="1"/>
-    <row r="280" ht="15.75" customHeight="1"/>
-    <row r="281" ht="15.75" customHeight="1"/>
-    <row r="282" ht="15.75" customHeight="1"/>
-    <row r="283" ht="15.75" customHeight="1"/>
-    <row r="284" ht="15.75" customHeight="1"/>
-    <row r="285" ht="15.75" customHeight="1"/>
-    <row r="286" ht="15.75" customHeight="1"/>
-    <row r="287" ht="15.75" customHeight="1"/>
-    <row r="288" ht="15.75" customHeight="1"/>
-    <row r="289" ht="15.75" customHeight="1"/>
-    <row r="290" ht="15.75" customHeight="1"/>
-    <row r="291" ht="15.75" customHeight="1"/>
-    <row r="292" ht="15.75" customHeight="1"/>
-    <row r="293" ht="15.75" customHeight="1"/>
-    <row r="294" ht="15.75" customHeight="1"/>
-    <row r="295" ht="15.75" customHeight="1"/>
-    <row r="296" ht="15.75" customHeight="1"/>
-    <row r="297" ht="15.75" customHeight="1"/>
-    <row r="298" ht="15.75" customHeight="1"/>
-    <row r="299" ht="15.75" customHeight="1"/>
-    <row r="300" ht="15.75" customHeight="1"/>
-    <row r="301" ht="15.75" customHeight="1"/>
-    <row r="302" ht="15.75" customHeight="1"/>
-    <row r="303" ht="15.75" customHeight="1"/>
-    <row r="304" ht="15.75" customHeight="1"/>
-    <row r="305" ht="15.75" customHeight="1"/>
-    <row r="306" ht="15.75" customHeight="1"/>
-    <row r="307" ht="15.75" customHeight="1"/>
-    <row r="308" ht="15.75" customHeight="1"/>
-    <row r="309" ht="15.75" customHeight="1"/>
-    <row r="310" ht="15.75" customHeight="1"/>
-    <row r="311" ht="15.75" customHeight="1"/>
-    <row r="312" ht="15.75" customHeight="1"/>
-    <row r="313" ht="15.75" customHeight="1"/>
-    <row r="314" ht="15.75" customHeight="1"/>
-    <row r="315" ht="15.75" customHeight="1"/>
-    <row r="316" ht="15.75" customHeight="1"/>
-    <row r="317" ht="15.75" customHeight="1"/>
-    <row r="318" ht="15.75" customHeight="1"/>
-    <row r="319" ht="15.75" customHeight="1"/>
-    <row r="320" ht="15.75" customHeight="1"/>
-    <row r="321" ht="15.75" customHeight="1"/>
-    <row r="322" ht="15.75" customHeight="1"/>
-    <row r="323" ht="15.75" customHeight="1"/>
-    <row r="324" ht="15.75" customHeight="1"/>
-    <row r="325" ht="15.75" customHeight="1"/>
-    <row r="326" ht="15.75" customHeight="1"/>
-    <row r="327" ht="15.75" customHeight="1"/>
-    <row r="328" ht="15.75" customHeight="1"/>
-    <row r="329" ht="15.75" customHeight="1"/>
-    <row r="330" ht="15.75" customHeight="1"/>
-    <row r="331" ht="15.75" customHeight="1"/>
-    <row r="332" ht="15.75" customHeight="1"/>
-    <row r="333" ht="15.75" customHeight="1"/>
-    <row r="334" ht="15.75" customHeight="1"/>
-    <row r="335" ht="15.75" customHeight="1"/>
-    <row r="336" ht="15.75" customHeight="1"/>
-    <row r="337" ht="15.75" customHeight="1"/>
-    <row r="338" ht="15.75" customHeight="1"/>
-    <row r="339" ht="15.75" customHeight="1"/>
-    <row r="340" ht="15.75" customHeight="1"/>
-    <row r="341" ht="15.75" customHeight="1"/>
-    <row r="342" ht="15.75" customHeight="1"/>
-    <row r="343" ht="15.75" customHeight="1"/>
-    <row r="344" ht="15.75" customHeight="1"/>
-    <row r="345" ht="15.75" customHeight="1"/>
-    <row r="346" ht="15.75" customHeight="1"/>
-    <row r="347" ht="15.75" customHeight="1"/>
-    <row r="348" ht="15.75" customHeight="1"/>
-    <row r="349" ht="15.75" customHeight="1"/>
-    <row r="350" ht="15.75" customHeight="1"/>
-    <row r="351" ht="15.75" customHeight="1"/>
-    <row r="352" ht="15.75" customHeight="1"/>
-    <row r="353" ht="15.75" customHeight="1"/>
-    <row r="354" ht="15.75" customHeight="1"/>
-    <row r="355" ht="15.75" customHeight="1"/>
-    <row r="356" ht="15.75" customHeight="1"/>
-    <row r="357" ht="15.75" customHeight="1"/>
-    <row r="358" ht="15.75" customHeight="1"/>
-    <row r="359" ht="15.75" customHeight="1"/>
-    <row r="360" ht="15.75" customHeight="1"/>
-    <row r="361" ht="15.75" customHeight="1"/>
-    <row r="362" ht="15.75" customHeight="1"/>
-    <row r="363" ht="15.75" customHeight="1"/>
-    <row r="364" ht="15.75" customHeight="1"/>
-    <row r="365" ht="15.75" customHeight="1"/>
-    <row r="366" ht="15.75" customHeight="1"/>
-    <row r="367" ht="15.75" customHeight="1"/>
-    <row r="368" ht="15.75" customHeight="1"/>
-    <row r="369" ht="15.75" customHeight="1"/>
-    <row r="370" ht="15.75" customHeight="1"/>
-    <row r="371" ht="15.75" customHeight="1"/>
-    <row r="372" ht="15.75" customHeight="1"/>
-    <row r="373" ht="15.75" customHeight="1"/>
-    <row r="374" ht="15.75" customHeight="1"/>
-    <row r="375" ht="15.75" customHeight="1"/>
-    <row r="376" ht="15.75" customHeight="1"/>
-    <row r="377" ht="15.75" customHeight="1"/>
-    <row r="378" ht="15.75" customHeight="1"/>
-    <row r="379" ht="15.75" customHeight="1"/>
-    <row r="380" ht="15.75" customHeight="1"/>
-    <row r="381" ht="15.75" customHeight="1"/>
-    <row r="382" ht="15.75" customHeight="1"/>
-    <row r="383" ht="15.75" customHeight="1"/>
-    <row r="384" ht="15.75" customHeight="1"/>
-    <row r="385" ht="15.75" customHeight="1"/>
-    <row r="386" ht="15.75" customHeight="1"/>
-    <row r="387" ht="15.75" customHeight="1"/>
-    <row r="388" ht="15.75" customHeight="1"/>
-    <row r="389" ht="15.75" customHeight="1"/>
-    <row r="390" ht="15.75" customHeight="1"/>
-    <row r="391" ht="15.75" customHeight="1"/>
-    <row r="392" ht="15.75" customHeight="1"/>
-    <row r="393" ht="15.75" customHeight="1"/>
-    <row r="394" ht="15.75" customHeight="1"/>
-    <row r="395" ht="15.75" customHeight="1"/>
-    <row r="396" ht="15.75" customHeight="1"/>
-    <row r="397" ht="15.75" customHeight="1"/>
-    <row r="398" ht="15.75" customHeight="1"/>
-    <row r="399" ht="15.75" customHeight="1"/>
-    <row r="400" ht="15.75" customHeight="1"/>
-    <row r="401" ht="15.75" customHeight="1"/>
-    <row r="402" ht="15.75" customHeight="1"/>
-    <row r="403" ht="15.75" customHeight="1"/>
-    <row r="404" ht="15.75" customHeight="1"/>
-    <row r="405" ht="15.75" customHeight="1"/>
-    <row r="406" ht="15.75" customHeight="1"/>
-    <row r="407" ht="15.75" customHeight="1"/>
-    <row r="408" ht="15.75" customHeight="1"/>
-    <row r="409" ht="15.75" customHeight="1"/>
-    <row r="410" ht="15.75" customHeight="1"/>
-    <row r="411" ht="15.75" customHeight="1"/>
-    <row r="412" ht="15.75" customHeight="1"/>
-    <row r="413" ht="15.75" customHeight="1"/>
-    <row r="414" ht="15.75" customHeight="1"/>
-    <row r="415" ht="15.75" customHeight="1"/>
-    <row r="416" ht="15.75" customHeight="1"/>
-    <row r="417" ht="15.75" customHeight="1"/>
-    <row r="418" ht="15.75" customHeight="1"/>
-    <row r="419" ht="15.75" customHeight="1"/>
-    <row r="420" ht="15.75" customHeight="1"/>
-    <row r="421" ht="15.75" customHeight="1"/>
-    <row r="422" ht="15.75" customHeight="1"/>
-    <row r="423" ht="15.75" customHeight="1"/>
-    <row r="424" ht="15.75" customHeight="1"/>
-    <row r="425" ht="15.75" customHeight="1"/>
-    <row r="426" ht="15.75" customHeight="1"/>
-    <row r="427" ht="15.75" customHeight="1"/>
-    <row r="428" ht="15.75" customHeight="1"/>
-    <row r="429" ht="15.75" customHeight="1"/>
-    <row r="430" ht="15.75" customHeight="1"/>
-    <row r="431" ht="15.75" customHeight="1"/>
-    <row r="432" ht="15.75" customHeight="1"/>
-    <row r="433" ht="15.75" customHeight="1"/>
-    <row r="434" ht="15.75" customHeight="1"/>
-    <row r="435" ht="15.75" customHeight="1"/>
-    <row r="436" ht="15.75" customHeight="1"/>
-    <row r="437" ht="15.75" customHeight="1"/>
-    <row r="438" ht="15.75" customHeight="1"/>
-    <row r="439" ht="15.75" customHeight="1"/>
-    <row r="440" ht="15.75" customHeight="1"/>
-    <row r="441" ht="15.75" customHeight="1"/>
-    <row r="442" ht="15.75" customHeight="1"/>
-    <row r="443" ht="15.75" customHeight="1"/>
-    <row r="444" ht="15.75" customHeight="1"/>
-    <row r="445" ht="15.75" customHeight="1"/>
-    <row r="446" ht="15.75" customHeight="1"/>
-    <row r="447" ht="15.75" customHeight="1"/>
-    <row r="448" ht="15.75" customHeight="1"/>
-    <row r="449" ht="15.75" customHeight="1"/>
-    <row r="450" ht="15.75" customHeight="1"/>
-    <row r="451" ht="15.75" customHeight="1"/>
-    <row r="452" ht="15.75" customHeight="1"/>
-    <row r="453" ht="15.75" customHeight="1"/>
-    <row r="454" ht="15.75" customHeight="1"/>
-    <row r="455" ht="15.75" customHeight="1"/>
-    <row r="456" ht="15.75" customHeight="1"/>
-    <row r="457" ht="15.75" customHeight="1"/>
-    <row r="458" ht="15.75" customHeight="1"/>
-    <row r="459" ht="15.75" customHeight="1"/>
-    <row r="460" ht="15.75" customHeight="1"/>
-    <row r="461" ht="15.75" customHeight="1"/>
-    <row r="462" ht="15.75" customHeight="1"/>
-    <row r="463" ht="15.75" customHeight="1"/>
-    <row r="464" ht="15.75" customHeight="1"/>
-    <row r="465" ht="15.75" customHeight="1"/>
-    <row r="466" ht="15.75" customHeight="1"/>
-    <row r="467" ht="15.75" customHeight="1"/>
-    <row r="468" ht="15.75" customHeight="1"/>
-    <row r="469" ht="15.75" customHeight="1"/>
-    <row r="470" ht="15.75" customHeight="1"/>
-    <row r="471" ht="15.75" customHeight="1"/>
-    <row r="472" ht="15.75" customHeight="1"/>
-    <row r="473" ht="15.75" customHeight="1"/>
-    <row r="474" ht="15.75" customHeight="1"/>
-    <row r="475" ht="15.75" customHeight="1"/>
-    <row r="476" ht="15.75" customHeight="1"/>
-    <row r="477" ht="15.75" customHeight="1"/>
-    <row r="478" ht="15.75" customHeight="1"/>
-    <row r="479" ht="15.75" customHeight="1"/>
-    <row r="480" ht="15.75" customHeight="1"/>
-    <row r="481" ht="15.75" customHeight="1"/>
-    <row r="482" ht="15.75" customHeight="1"/>
-    <row r="483" ht="15.75" customHeight="1"/>
-    <row r="484" ht="15.75" customHeight="1"/>
-    <row r="485" ht="15.75" customHeight="1"/>
-    <row r="486" ht="15.75" customHeight="1"/>
-    <row r="487" ht="15.75" customHeight="1"/>
-    <row r="488" ht="15.75" customHeight="1"/>
-    <row r="489" ht="15.75" customHeight="1"/>
-    <row r="490" ht="15.75" customHeight="1"/>
-    <row r="491" ht="15.75" customHeight="1"/>
-    <row r="492" ht="15.75" customHeight="1"/>
-    <row r="493" ht="15.75" customHeight="1"/>
-    <row r="494" ht="15.75" customHeight="1"/>
-    <row r="495" ht="15.75" customHeight="1"/>
-    <row r="496" ht="15.75" customHeight="1"/>
-    <row r="497" ht="15.75" customHeight="1"/>
-    <row r="498" ht="15.75" customHeight="1"/>
-    <row r="499" ht="15.75" customHeight="1"/>
-    <row r="500" ht="15.75" customHeight="1"/>
-    <row r="501" ht="15.75" customHeight="1"/>
-    <row r="502" ht="15.75" customHeight="1"/>
-    <row r="503" ht="15.75" customHeight="1"/>
-    <row r="504" ht="15.75" customHeight="1"/>
-    <row r="505" ht="15.75" customHeight="1"/>
-    <row r="506" ht="15.75" customHeight="1"/>
-    <row r="507" ht="15.75" customHeight="1"/>
-    <row r="508" ht="15.75" customHeight="1"/>
-    <row r="509" ht="15.75" customHeight="1"/>
-    <row r="510" ht="15.75" customHeight="1"/>
-    <row r="511" ht="15.75" customHeight="1"/>
-    <row r="512" ht="15.75" customHeight="1"/>
-    <row r="513" ht="15.75" customHeight="1"/>
-    <row r="514" ht="15.75" customHeight="1"/>
-    <row r="515" ht="15.75" customHeight="1"/>
-    <row r="516" ht="15.75" customHeight="1"/>
-    <row r="517" ht="15.75" customHeight="1"/>
-    <row r="518" ht="15.75" customHeight="1"/>
-    <row r="519" ht="15.75" customHeight="1"/>
-    <row r="520" ht="15.75" customHeight="1"/>
-    <row r="521" ht="15.75" customHeight="1"/>
-    <row r="522" ht="15.75" customHeight="1"/>
-    <row r="523" ht="15.75" customHeight="1"/>
-    <row r="524" ht="15.75" customHeight="1"/>
-    <row r="525" ht="15.75" customHeight="1"/>
-    <row r="526" ht="15.75" customHeight="1"/>
-    <row r="527" ht="15.75" customHeight="1"/>
-    <row r="528" ht="15.75" customHeight="1"/>
-    <row r="529" ht="15.75" customHeight="1"/>
-    <row r="530" ht="15.75" customHeight="1"/>
-    <row r="531" ht="15.75" customHeight="1"/>
-    <row r="532" ht="15.75" customHeight="1"/>
-    <row r="533" ht="15.75" customHeight="1"/>
-    <row r="534" ht="15.75" customHeight="1"/>
-    <row r="535" ht="15.75" customHeight="1"/>
-    <row r="536" ht="15.75" customHeight="1"/>
-    <row r="537" ht="15.75" customHeight="1"/>
-    <row r="538" ht="15.75" customHeight="1"/>
-    <row r="539" ht="15.75" customHeight="1"/>
-    <row r="540" ht="15.75" customHeight="1"/>
-    <row r="541" ht="15.75" customHeight="1"/>
-    <row r="542" ht="15.75" customHeight="1"/>
-    <row r="543" ht="15.75" customHeight="1"/>
-    <row r="544" ht="15.75" customHeight="1"/>
-    <row r="545" ht="15.75" customHeight="1"/>
-    <row r="546" ht="15.75" customHeight="1"/>
-    <row r="547" ht="15.75" customHeight="1"/>
-    <row r="548" ht="15.75" customHeight="1"/>
-    <row r="549" ht="15.75" customHeight="1"/>
-    <row r="550" ht="15.75" customHeight="1"/>
-    <row r="551" ht="15.75" customHeight="1"/>
-    <row r="552" ht="15.75" customHeight="1"/>
-    <row r="553" ht="15.75" customHeight="1"/>
-    <row r="554" ht="15.75" customHeight="1"/>
-    <row r="555" ht="15.75" customHeight="1"/>
-    <row r="556" ht="15.75" customHeight="1"/>
-    <row r="557" ht="15.75" customHeight="1"/>
-    <row r="558" ht="15.75" customHeight="1"/>
-    <row r="559" ht="15.75" customHeight="1"/>
-    <row r="560" ht="15.75" customHeight="1"/>
-    <row r="561" ht="15.75" customHeight="1"/>
-    <row r="562" ht="15.75" customHeight="1"/>
-    <row r="563" ht="15.75" customHeight="1"/>
-    <row r="564" ht="15.75" customHeight="1"/>
-    <row r="565" ht="15.75" customHeight="1"/>
-    <row r="566" ht="15.75" customHeight="1"/>
-    <row r="567" ht="15.75" customHeight="1"/>
-    <row r="568" ht="15.75" customHeight="1"/>
-    <row r="569" ht="15.75" customHeight="1"/>
-    <row r="570" ht="15.75" customHeight="1"/>
-    <row r="571" ht="15.75" customHeight="1"/>
-    <row r="572" ht="15.75" customHeight="1"/>
-    <row r="573" ht="15.75" customHeight="1"/>
-    <row r="574" ht="15.75" customHeight="1"/>
-    <row r="575" ht="15.75" customHeight="1"/>
-    <row r="576" ht="15.75" customHeight="1"/>
-    <row r="577" ht="15.75" customHeight="1"/>
-    <row r="578" ht="15.75" customHeight="1"/>
-    <row r="579" ht="15.75" customHeight="1"/>
-    <row r="580" ht="15.75" customHeight="1"/>
-    <row r="581" ht="15.75" customHeight="1"/>
-    <row r="582" ht="15.75" customHeight="1"/>
-    <row r="583" ht="15.75" customHeight="1"/>
-    <row r="584" ht="15.75" customHeight="1"/>
-    <row r="585" ht="15.75" customHeight="1"/>
-    <row r="586" ht="15.75" customHeight="1"/>
-    <row r="587" ht="15.75" customHeight="1"/>
-    <row r="588" ht="15.75" customHeight="1"/>
-    <row r="589" ht="15.75" customHeight="1"/>
-    <row r="590" ht="15.75" customHeight="1"/>
-    <row r="591" ht="15.75" customHeight="1"/>
-    <row r="592" ht="15.75" customHeight="1"/>
-    <row r="593" ht="15.75" customHeight="1"/>
-    <row r="594" ht="15.75" customHeight="1"/>
-    <row r="595" ht="15.75" customHeight="1"/>
-    <row r="596" ht="15.75" customHeight="1"/>
-    <row r="597" ht="15.75" customHeight="1"/>
-    <row r="598" ht="15.75" customHeight="1"/>
-    <row r="599" ht="15.75" customHeight="1"/>
-    <row r="600" ht="15.75" customHeight="1"/>
-    <row r="601" ht="15.75" customHeight="1"/>
-    <row r="602" ht="15.75" customHeight="1"/>
-    <row r="603" ht="15.75" customHeight="1"/>
-    <row r="604" ht="15.75" customHeight="1"/>
-    <row r="605" ht="15.75" customHeight="1"/>
-    <row r="606" ht="15.75" customHeight="1"/>
-    <row r="607" ht="15.75" customHeight="1"/>
-    <row r="608" ht="15.75" customHeight="1"/>
-    <row r="609" ht="15.75" customHeight="1"/>
-    <row r="610" ht="15.75" customHeight="1"/>
-    <row r="611" ht="15.75" customHeight="1"/>
-    <row r="612" ht="15.75" customHeight="1"/>
-    <row r="613" ht="15.75" customHeight="1"/>
-    <row r="614" ht="15.75" customHeight="1"/>
-    <row r="615" ht="15.75" customHeight="1"/>
-    <row r="616" ht="15.75" customHeight="1"/>
-    <row r="617" ht="15.75" customHeight="1"/>
-    <row r="618" ht="15.75" customHeight="1"/>
-    <row r="619" ht="15.75" customHeight="1"/>
-    <row r="620" ht="15.75" customHeight="1"/>
-    <row r="621" ht="15.75" customHeight="1"/>
-    <row r="622" ht="15.75" customHeight="1"/>
-    <row r="623" ht="15.75" customHeight="1"/>
-    <row r="624" ht="15.75" customHeight="1"/>
-    <row r="625" ht="15.75" customHeight="1"/>
-    <row r="626" ht="15.75" customHeight="1"/>
-    <row r="627" ht="15.75" customHeight="1"/>
-    <row r="628" ht="15.75" customHeight="1"/>
-    <row r="629" ht="15.75" customHeight="1"/>
-    <row r="630" ht="15.75" customHeight="1"/>
-    <row r="631" ht="15.75" customHeight="1"/>
-    <row r="632" ht="15.75" customHeight="1"/>
-    <row r="633" ht="15.75" customHeight="1"/>
-    <row r="634" ht="15.75" customHeight="1"/>
-    <row r="635" ht="15.75" customHeight="1"/>
-    <row r="636" ht="15.75" customHeight="1"/>
-    <row r="637" ht="15.75" customHeight="1"/>
-    <row r="638" ht="15.75" customHeight="1"/>
-    <row r="639" ht="15.75" customHeight="1"/>
-    <row r="640" ht="15.75" customHeight="1"/>
-    <row r="641" ht="15.75" customHeight="1"/>
-    <row r="642" ht="15.75" customHeight="1"/>
-    <row r="643" ht="15.75" customHeight="1"/>
-    <row r="644" ht="15.75" customHeight="1"/>
-    <row r="645" ht="15.75" customHeight="1"/>
-    <row r="646" ht="15.75" customHeight="1"/>
-    <row r="647" ht="15.75" customHeight="1"/>
-    <row r="648" ht="15.75" customHeight="1"/>
-    <row r="649" ht="15.75" customHeight="1"/>
-    <row r="650" ht="15.75" customHeight="1"/>
-    <row r="651" ht="15.75" customHeight="1"/>
-    <row r="652" ht="15.75" customHeight="1"/>
-    <row r="653" ht="15.75" customHeight="1"/>
-    <row r="654" ht="15.75" customHeight="1"/>
-    <row r="655" ht="15.75" customHeight="1"/>
-    <row r="656" ht="15.75" customHeight="1"/>
-    <row r="657" ht="15.75" customHeight="1"/>
-    <row r="658" ht="15.75" customHeight="1"/>
-    <row r="659" ht="15.75" customHeight="1"/>
-    <row r="660" ht="15.75" customHeight="1"/>
-    <row r="661" ht="15.75" customHeight="1"/>
-    <row r="662" ht="15.75" customHeight="1"/>
-    <row r="663" ht="15.75" customHeight="1"/>
-    <row r="664" ht="15.75" customHeight="1"/>
-    <row r="665" ht="15.75" customHeight="1"/>
-    <row r="666" ht="15.75" customHeight="1"/>
-    <row r="667" ht="15.75" customHeight="1"/>
-    <row r="668" ht="15.75" customHeight="1"/>
-    <row r="669" ht="15.75" customHeight="1"/>
-    <row r="670" ht="15.75" customHeight="1"/>
-    <row r="671" ht="15.75" customHeight="1"/>
-    <row r="672" ht="15.75" customHeight="1"/>
-    <row r="673" ht="15.75" customHeight="1"/>
-    <row r="674" ht="15.75" customHeight="1"/>
-    <row r="675" ht="15.75" customHeight="1"/>
-    <row r="676" ht="15.75" customHeight="1"/>
-    <row r="677" ht="15.75" customHeight="1"/>
-    <row r="678" ht="15.75" customHeight="1"/>
-    <row r="679" ht="15.75" customHeight="1"/>
-    <row r="680" ht="15.75" customHeight="1"/>
-    <row r="681" ht="15.75" customHeight="1"/>
-    <row r="682" ht="15.75" customHeight="1"/>
-    <row r="683" ht="15.75" customHeight="1"/>
-    <row r="684" ht="15.75" customHeight="1"/>
-    <row r="685" ht="15.75" customHeight="1"/>
-    <row r="686" ht="15.75" customHeight="1"/>
-    <row r="687" ht="15.75" customHeight="1"/>
-    <row r="688" ht="15.75" customHeight="1"/>
-    <row r="689" ht="15.75" customHeight="1"/>
-    <row r="690" ht="15.75" customHeight="1"/>
-    <row r="691" ht="15.75" customHeight="1"/>
-    <row r="692" ht="15.75" customHeight="1"/>
-    <row r="693" ht="15.75" customHeight="1"/>
-    <row r="694" ht="15.75" customHeight="1"/>
-    <row r="695" ht="15.75" customHeight="1"/>
-    <row r="696" ht="15.75" customHeight="1"/>
-    <row r="697" ht="15.75" customHeight="1"/>
-    <row r="698" ht="15.75" customHeight="1"/>
-    <row r="699" ht="15.75" customHeight="1"/>
-    <row r="700" ht="15.75" customHeight="1"/>
-    <row r="701" ht="15.75" customHeight="1"/>
-    <row r="702" ht="15.75" customHeight="1"/>
-    <row r="703" ht="15.75" customHeight="1"/>
-    <row r="704" ht="15.75" customHeight="1"/>
-    <row r="705" ht="15.75" customHeight="1"/>
-    <row r="706" ht="15.75" customHeight="1"/>
-    <row r="707" ht="15.75" customHeight="1"/>
-    <row r="708" ht="15.75" customHeight="1"/>
-    <row r="709" ht="15.75" customHeight="1"/>
-    <row r="710" ht="15.75" customHeight="1"/>
-    <row r="711" ht="15.75" customHeight="1"/>
-    <row r="712" ht="15.75" customHeight="1"/>
-    <row r="713" ht="15.75" customHeight="1"/>
-    <row r="714" ht="15.75" customHeight="1"/>
-    <row r="715" ht="15.75" customHeight="1"/>
-    <row r="716" ht="15.75" customHeight="1"/>
-    <row r="717" ht="15.75" customHeight="1"/>
-    <row r="718" ht="15.75" customHeight="1"/>
-    <row r="719" ht="15.75" customHeight="1"/>
-    <row r="720" ht="15.75" customHeight="1"/>
-    <row r="721" ht="15.75" customHeight="1"/>
-    <row r="722" ht="15.75" customHeight="1"/>
-    <row r="723" ht="15.75" customHeight="1"/>
-    <row r="724" ht="15.75" customHeight="1"/>
-    <row r="725" ht="15.75" customHeight="1"/>
-    <row r="726" ht="15.75" customHeight="1"/>
-    <row r="727" ht="15.75" customHeight="1"/>
-    <row r="728" ht="15.75" customHeight="1"/>
-    <row r="729" ht="15.75" customHeight="1"/>
-    <row r="730" ht="15.75" customHeight="1"/>
-    <row r="731" ht="15.75" customHeight="1"/>
-    <row r="732" ht="15.75" customHeight="1"/>
-    <row r="733" ht="15.75" customHeight="1"/>
-    <row r="734" ht="15.75" customHeight="1"/>
-    <row r="735" ht="15.75" customHeight="1"/>
-    <row r="736" ht="15.75" customHeight="1"/>
-    <row r="737" ht="15.75" customHeight="1"/>
-    <row r="738" ht="15.75" customHeight="1"/>
-    <row r="739" ht="15.75" customHeight="1"/>
-    <row r="740" ht="15.75" customHeight="1"/>
-    <row r="741" ht="15.75" customHeight="1"/>
-    <row r="742" ht="15.75" customHeight="1"/>
-    <row r="743" ht="15.75" customHeight="1"/>
-    <row r="744" ht="15.75" customHeight="1"/>
-    <row r="745" ht="15.75" customHeight="1"/>
-    <row r="746" ht="15.75" customHeight="1"/>
-    <row r="747" ht="15.75" customHeight="1"/>
-    <row r="748" ht="15.75" customHeight="1"/>
-    <row r="749" ht="15.75" customHeight="1"/>
-    <row r="750" ht="15.75" customHeight="1"/>
-    <row r="751" ht="15.75" customHeight="1"/>
-    <row r="752" ht="15.75" customHeight="1"/>
-    <row r="753" ht="15.75" customHeight="1"/>
-    <row r="754" ht="15.75" customHeight="1"/>
-    <row r="755" ht="15.75" customHeight="1"/>
-    <row r="756" ht="15.75" customHeight="1"/>
-    <row r="757" ht="15.75" customHeight="1"/>
-    <row r="758" ht="15.75" customHeight="1"/>
-    <row r="759" ht="15.75" customHeight="1"/>
-    <row r="760" ht="15.75" customHeight="1"/>
-    <row r="761" ht="15.75" customHeight="1"/>
-    <row r="762" ht="15.75" customHeight="1"/>
-    <row r="763" ht="15.75" customHeight="1"/>
-    <row r="764" ht="15.75" customHeight="1"/>
-    <row r="765" ht="15.75" customHeight="1"/>
-    <row r="766" ht="15.75" customHeight="1"/>
-    <row r="767" ht="15.75" customHeight="1"/>
-    <row r="768" ht="15.75" customHeight="1"/>
-    <row r="769" ht="15.75" customHeight="1"/>
-    <row r="770" ht="15.75" customHeight="1"/>
-    <row r="771" ht="15.75" customHeight="1"/>
-    <row r="772" ht="15.75" customHeight="1"/>
-    <row r="773" ht="15.75" customHeight="1"/>
-    <row r="774" ht="15.75" customHeight="1"/>
-    <row r="775" ht="15.75" customHeight="1"/>
-    <row r="776" ht="15.75" customHeight="1"/>
-    <row r="777" ht="15.75" customHeight="1"/>
-    <row r="778" ht="15.75" customHeight="1"/>
-    <row r="779" ht="15.75" customHeight="1"/>
-    <row r="780" ht="15.75" customHeight="1"/>
-    <row r="781" ht="15.75" customHeight="1"/>
-    <row r="782" ht="15.75" customHeight="1"/>
-    <row r="783" ht="15.75" customHeight="1"/>
-    <row r="784" ht="15.75" customHeight="1"/>
-    <row r="785" ht="15.75" customHeight="1"/>
-    <row r="786" ht="15.75" customHeight="1"/>
-    <row r="787" ht="15.75" customHeight="1"/>
-    <row r="788" ht="15.75" customHeight="1"/>
-    <row r="789" ht="15.75" customHeight="1"/>
-    <row r="790" ht="15.75" customHeight="1"/>
-    <row r="791" ht="15.75" customHeight="1"/>
-    <row r="792" ht="15.75" customHeight="1"/>
-    <row r="793" ht="15.75" customHeight="1"/>
-    <row r="794" ht="15.75" customHeight="1"/>
-    <row r="795" ht="15.75" customHeight="1"/>
-    <row r="796" ht="15.75" customHeight="1"/>
-    <row r="797" ht="15.75" customHeight="1"/>
-    <row r="798" ht="15.75" customHeight="1"/>
-    <row r="799" ht="15.75" customHeight="1"/>
-    <row r="800" ht="15.75" customHeight="1"/>
-    <row r="801" ht="15.75" customHeight="1"/>
-    <row r="802" ht="15.75" customHeight="1"/>
-    <row r="803" ht="15.75" customHeight="1"/>
-    <row r="804" ht="15.75" customHeight="1"/>
-    <row r="805" ht="15.75" customHeight="1"/>
-    <row r="806" ht="15.75" customHeight="1"/>
-    <row r="807" ht="15.75" customHeight="1"/>
-    <row r="808" ht="15.75" customHeight="1"/>
-    <row r="809" ht="15.75" customHeight="1"/>
+    <row r="128" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="G4:Q13 G15:Q16 G23:Q24 G34:Q34">
@@ -16407,16 +16419,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:Q105"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="6.1328125" customWidth="1"/>
-    <col min="2" max="2" width="24.73046875" customWidth="1"/>
-    <col min="3" max="6" width="20.73046875" customWidth="1"/>
-    <col min="7" max="7" width="5.73046875" customWidth="1"/>
-    <col min="8" max="8" width="56.86328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.1640625" customWidth="1"/>
+    <col min="2" max="2" width="24.6640625" customWidth="1"/>
+    <col min="3" max="6" width="20.6640625" customWidth="1"/>
+    <col min="7" max="7" width="5.6640625" customWidth="1"/>
+    <col min="8" max="8" width="56.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="13.9">
+    <row r="2" spans="2:8" ht="16" x14ac:dyDescent="0.25">
       <c r="B2" s="36" t="s">
         <v>53</v>
       </c>
@@ -16428,7 +16440,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="3" spans="2:8" ht="13.15">
+    <row r="3" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B3" s="109" t="s">
         <v>159</v>
       </c>
@@ -16441,7 +16453,7 @@
       </c>
       <c r="H3" s="120"/>
     </row>
-    <row r="4" spans="2:8">
+    <row r="4" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B4" s="100" t="s">
         <v>124</v>
       </c>
@@ -16462,7 +16474,7 @@
       </c>
       <c r="H4" s="120"/>
     </row>
-    <row r="5" spans="2:8">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B5" s="205" t="s">
         <v>119</v>
       </c>
@@ -16473,7 +16485,7 @@
       <c r="E5" s="148"/>
       <c r="H5" s="120"/>
     </row>
-    <row r="6" spans="2:8" ht="13.35" customHeight="1">
+    <row r="6" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B6" s="149" t="s">
         <v>224</v>
       </c>
@@ -16491,7 +16503,7 @@
       <c r="F6" s="378"/>
       <c r="H6" s="120"/>
     </row>
-    <row r="7" spans="2:8">
+    <row r="7" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B7" s="148" t="s">
         <v>220</v>
       </c>
@@ -16507,7 +16519,7 @@
       <c r="F7" s="378"/>
       <c r="H7" s="120"/>
     </row>
-    <row r="8" spans="2:8">
+    <row r="8" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B8" s="148" t="s">
         <v>221</v>
       </c>
@@ -16523,7 +16535,7 @@
       <c r="F8" s="378"/>
       <c r="H8" s="120"/>
     </row>
-    <row r="9" spans="2:8">
+    <row r="9" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B9" s="205" t="s">
         <v>186</v>
       </c>
@@ -16539,7 +16551,7 @@
       <c r="F9" s="378"/>
       <c r="H9" s="120"/>
     </row>
-    <row r="10" spans="2:8" ht="13.15">
+    <row r="10" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B10" s="149" t="s">
         <v>223</v>
       </c>
@@ -16553,7 +16565,7 @@
       </c>
       <c r="H10" s="120"/>
     </row>
-    <row r="11" spans="2:8" ht="13.15" thickBot="1">
+    <row r="11" spans="2:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B11" s="207" t="s">
         <v>162</v>
       </c>
@@ -16567,7 +16579,7 @@
       </c>
       <c r="H11" s="120"/>
     </row>
-    <row r="12" spans="2:8" ht="13.5" thickTop="1">
+    <row r="12" spans="2:8" ht="14" thickTop="1" x14ac:dyDescent="0.15">
       <c r="B12" s="149" t="s">
         <v>99</v>
       </c>
@@ -16581,10 +16593,10 @@
       </c>
       <c r="H12" s="120"/>
     </row>
-    <row r="13" spans="2:8">
+    <row r="13" spans="2:8" x14ac:dyDescent="0.15">
       <c r="H13" s="120"/>
     </row>
-    <row r="14" spans="2:8" ht="13.9">
+    <row r="14" spans="2:8" ht="16" x14ac:dyDescent="0.25">
       <c r="B14" s="36" t="s">
         <v>225</v>
       </c>
@@ -16594,13 +16606,13 @@
       <c r="F14" s="37"/>
       <c r="H14" s="120"/>
     </row>
-    <row r="15" spans="2:8" ht="13.15">
+    <row r="15" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B15" s="119" t="s">
         <v>131</v>
       </c>
       <c r="H15" s="120"/>
     </row>
-    <row r="16" spans="2:8" ht="13.35" customHeight="1">
+    <row r="16" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B16" s="152" t="s">
         <v>129</v>
       </c>
@@ -16610,7 +16622,7 @@
       </c>
       <c r="H16" s="120"/>
     </row>
-    <row r="17" spans="2:17" ht="13.35" customHeight="1">
+    <row r="17" spans="2:17" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="118" t="s">
         <v>130</v>
       </c>
@@ -16620,7 +16632,7 @@
       </c>
       <c r="H17" s="120"/>
     </row>
-    <row r="18" spans="2:17" ht="13.35" customHeight="1">
+    <row r="18" spans="2:17" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="153" t="s">
         <v>103</v>
       </c>
@@ -16634,10 +16646,10 @@
       </c>
       <c r="H18" s="120"/>
     </row>
-    <row r="19" spans="2:17">
+    <row r="19" spans="2:17" x14ac:dyDescent="0.15">
       <c r="H19" s="120"/>
     </row>
-    <row r="20" spans="2:17" ht="13.15">
+    <row r="20" spans="2:17" ht="14" x14ac:dyDescent="0.2">
       <c r="B20" s="128" t="s">
         <v>104</v>
       </c>
@@ -16655,7 +16667,7 @@
       </c>
       <c r="H20" s="120"/>
     </row>
-    <row r="21" spans="2:17">
+    <row r="21" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B21" s="122">
         <v>1</v>
       </c>
@@ -16677,7 +16689,7 @@
       </c>
       <c r="H21" s="120"/>
     </row>
-    <row r="22" spans="2:17">
+    <row r="22" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B22" s="122">
         <v>2</v>
       </c>
@@ -16699,7 +16711,7 @@
       </c>
       <c r="H22" s="120"/>
     </row>
-    <row r="23" spans="2:17">
+    <row r="23" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B23" s="122">
         <v>3</v>
       </c>
@@ -16731,7 +16743,7 @@
       <c r="P23" s="338"/>
       <c r="Q23" s="338"/>
     </row>
-    <row r="24" spans="2:17">
+    <row r="24" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B24" s="122">
         <v>4</v>
       </c>
@@ -16763,7 +16775,7 @@
       <c r="P24" s="338"/>
       <c r="Q24" s="338"/>
     </row>
-    <row r="25" spans="2:17">
+    <row r="25" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B25" s="122">
         <v>5</v>
       </c>
@@ -16795,7 +16807,7 @@
       <c r="P25" s="338"/>
       <c r="Q25" s="338"/>
     </row>
-    <row r="26" spans="2:17">
+    <row r="26" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B26" s="122">
         <v>6</v>
       </c>
@@ -16817,7 +16829,7 @@
       </c>
       <c r="H26" s="120"/>
     </row>
-    <row r="27" spans="2:17">
+    <row r="27" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B27" s="122">
         <v>7</v>
       </c>
@@ -16839,7 +16851,7 @@
       </c>
       <c r="H27" s="120"/>
     </row>
-    <row r="28" spans="2:17">
+    <row r="28" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B28" s="122">
         <v>8</v>
       </c>
@@ -16861,7 +16873,7 @@
       </c>
       <c r="H28" s="120"/>
     </row>
-    <row r="29" spans="2:17">
+    <row r="29" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B29" s="122">
         <v>9</v>
       </c>
@@ -16883,7 +16895,7 @@
       </c>
       <c r="H29" s="120"/>
     </row>
-    <row r="30" spans="2:17">
+    <row r="30" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B30" s="122">
         <v>10</v>
       </c>
@@ -16905,7 +16917,7 @@
       </c>
       <c r="H30" s="120"/>
     </row>
-    <row r="31" spans="2:17">
+    <row r="31" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B31" s="122">
         <v>11</v>
       </c>
@@ -16927,7 +16939,7 @@
       </c>
       <c r="H31" s="120"/>
     </row>
-    <row r="32" spans="2:17">
+    <row r="32" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B32" s="122">
         <v>12</v>
       </c>
@@ -16949,7 +16961,7 @@
       </c>
       <c r="H32" s="120"/>
     </row>
-    <row r="33" spans="2:17">
+    <row r="33" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B33" s="122">
         <v>13</v>
       </c>
@@ -16981,7 +16993,7 @@
       <c r="P33" s="338"/>
       <c r="Q33" s="338"/>
     </row>
-    <row r="34" spans="2:17">
+    <row r="34" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B34" s="122">
         <v>14</v>
       </c>
@@ -17013,7 +17025,7 @@
       <c r="P34" s="338"/>
       <c r="Q34" s="338"/>
     </row>
-    <row r="35" spans="2:17">
+    <row r="35" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B35" s="122">
         <v>15</v>
       </c>
@@ -17045,7 +17057,7 @@
       <c r="P35" s="338"/>
       <c r="Q35" s="338"/>
     </row>
-    <row r="36" spans="2:17">
+    <row r="36" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B36" s="122">
         <v>16</v>
       </c>
@@ -17067,7 +17079,7 @@
       </c>
       <c r="H36" s="120"/>
     </row>
-    <row r="37" spans="2:17">
+    <row r="37" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B37" s="122">
         <v>17</v>
       </c>
@@ -17089,7 +17101,7 @@
       </c>
       <c r="H37" s="120"/>
     </row>
-    <row r="38" spans="2:17">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B38" s="122">
         <v>18</v>
       </c>
@@ -17111,7 +17123,7 @@
       </c>
       <c r="H38" s="120"/>
     </row>
-    <row r="39" spans="2:17">
+    <row r="39" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B39" s="122">
         <v>19</v>
       </c>
@@ -17133,7 +17145,7 @@
       </c>
       <c r="H39" s="120"/>
     </row>
-    <row r="40" spans="2:17">
+    <row r="40" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B40" s="122">
         <v>20</v>
       </c>
@@ -17155,7 +17167,7 @@
       </c>
       <c r="H40" s="120"/>
     </row>
-    <row r="41" spans="2:17">
+    <row r="41" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B41" s="122">
         <v>21</v>
       </c>
@@ -17177,7 +17189,7 @@
       </c>
       <c r="H41" s="120"/>
     </row>
-    <row r="42" spans="2:17">
+    <row r="42" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B42" s="122">
         <v>22</v>
       </c>
@@ -17199,7 +17211,7 @@
       </c>
       <c r="H42" s="120"/>
     </row>
-    <row r="43" spans="2:17">
+    <row r="43" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B43" s="122">
         <v>23</v>
       </c>
@@ -17221,7 +17233,7 @@
       </c>
       <c r="H43" s="120"/>
     </row>
-    <row r="44" spans="2:17">
+    <row r="44" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B44" s="122">
         <v>24</v>
       </c>
@@ -17243,7 +17255,7 @@
       </c>
       <c r="H44" s="120"/>
     </row>
-    <row r="45" spans="2:17">
+    <row r="45" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B45" s="122">
         <v>25</v>
       </c>
@@ -17265,7 +17277,7 @@
       </c>
       <c r="H45" s="120"/>
     </row>
-    <row r="46" spans="2:17">
+    <row r="46" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B46" s="122">
         <v>26</v>
       </c>
@@ -17287,7 +17299,7 @@
       </c>
       <c r="H46" s="120"/>
     </row>
-    <row r="47" spans="2:17">
+    <row r="47" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B47" s="122">
         <v>27</v>
       </c>
@@ -17319,7 +17331,7 @@
       <c r="P47" s="338"/>
       <c r="Q47" s="338"/>
     </row>
-    <row r="48" spans="2:17">
+    <row r="48" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B48" s="122">
         <v>28</v>
       </c>
@@ -17351,7 +17363,7 @@
       <c r="P48" s="338"/>
       <c r="Q48" s="338"/>
     </row>
-    <row r="49" spans="1:17">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.15">
       <c r="B49" s="122">
         <v>29</v>
       </c>
@@ -17383,7 +17395,7 @@
       <c r="P49" s="338"/>
       <c r="Q49" s="338"/>
     </row>
-    <row r="50" spans="1:17">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.15">
       <c r="B50" s="122">
         <v>30</v>
       </c>
@@ -17415,7 +17427,7 @@
       <c r="P50" s="338"/>
       <c r="Q50" s="338"/>
     </row>
-    <row r="51" spans="1:17">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.15">
       <c r="B51" s="126" t="s">
         <v>127</v>
       </c>
@@ -17437,7 +17449,7 @@
       </c>
       <c r="H51" s="120"/>
     </row>
-    <row r="52" spans="1:17">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.15">
       <c r="C52" s="114"/>
       <c r="E52" s="127" t="s">
         <v>97</v>
@@ -17448,11 +17460,11 @@
       </c>
       <c r="H52" s="120"/>
     </row>
-    <row r="53" spans="1:17">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.15">
       <c r="C53" s="114"/>
       <c r="H53" s="120"/>
     </row>
-    <row r="54" spans="1:17" ht="13.15">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.15">
       <c r="B54" s="119" t="s">
         <v>125</v>
       </c>
@@ -17462,7 +17474,7 @@
       <c r="F54" s="117"/>
       <c r="H54" s="120"/>
     </row>
-    <row r="55" spans="1:17" ht="13.15">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A55" s="133">
         <f>F52</f>
         <v>14586853.730770443</v>
@@ -17489,7 +17501,7 @@
       </c>
       <c r="H55" s="120"/>
     </row>
-    <row r="56" spans="1:17" ht="13.15">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A56" s="143">
         <v>5</v>
       </c>
@@ -17511,7 +17523,7 @@
       </c>
       <c r="H56" s="120"/>
     </row>
-    <row r="57" spans="1:17" ht="13.15">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A57" s="143">
         <v>10</v>
       </c>
@@ -17532,7 +17544,7 @@
       </c>
       <c r="H57" s="120"/>
     </row>
-    <row r="58" spans="1:17" ht="13.15">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A58" s="143">
         <v>15</v>
       </c>
@@ -17563,7 +17575,7 @@
       <c r="P58" s="338"/>
       <c r="Q58" s="338"/>
     </row>
-    <row r="59" spans="1:17" ht="13.15">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A59" s="144">
         <v>20</v>
       </c>
@@ -17594,7 +17606,7 @@
       <c r="P59" s="338"/>
       <c r="Q59" s="338"/>
     </row>
-    <row r="60" spans="1:17" ht="13.15">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A60" s="144">
         <v>25</v>
       </c>
@@ -17625,7 +17637,7 @@
       <c r="P60" s="338"/>
       <c r="Q60" s="338"/>
     </row>
-    <row r="61" spans="1:17" ht="13.15">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A61" s="144">
         <v>30</v>
       </c>
@@ -17656,7 +17668,7 @@
       <c r="P61" s="338"/>
       <c r="Q61" s="338"/>
     </row>
-    <row r="62" spans="1:17">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.15">
       <c r="C62" s="338"/>
       <c r="D62" s="114"/>
       <c r="E62" s="114"/>
@@ -17673,7 +17685,7 @@
       <c r="P62" s="338"/>
       <c r="Q62" s="338"/>
     </row>
-    <row r="63" spans="1:17" ht="13.15">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.15">
       <c r="B63" s="119" t="s">
         <v>126</v>
       </c>
@@ -17693,7 +17705,7 @@
       <c r="P63" s="338"/>
       <c r="Q63" s="338"/>
     </row>
-    <row r="64" spans="1:17" ht="13.15">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.15">
       <c r="B64" s="132">
         <f>B55</f>
         <v>-0.04</v>
@@ -17716,7 +17728,7 @@
       </c>
       <c r="H64" s="120"/>
     </row>
-    <row r="65" spans="1:8" ht="13.15">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A65" s="143">
         <v>0</v>
       </c>
@@ -17742,7 +17754,7 @@
       </c>
       <c r="H65" s="120"/>
     </row>
-    <row r="66" spans="1:8" ht="13.15">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A66" s="143">
         <f t="shared" ref="A66:A71" si="3">A56</f>
         <v>5</v>
@@ -17769,7 +17781,7 @@
       </c>
       <c r="H66" s="120"/>
     </row>
-    <row r="67" spans="1:8" ht="13.15">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A67" s="143">
         <f t="shared" si="3"/>
         <v>10</v>
@@ -17796,7 +17808,7 @@
       </c>
       <c r="H67" s="120"/>
     </row>
-    <row r="68" spans="1:8" ht="13.15">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A68" s="143">
         <f t="shared" si="3"/>
         <v>15</v>
@@ -17823,7 +17835,7 @@
       </c>
       <c r="H68" s="120"/>
     </row>
-    <row r="69" spans="1:8" ht="13.15">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A69" s="144">
         <f t="shared" si="3"/>
         <v>20</v>
@@ -17850,7 +17862,7 @@
       </c>
       <c r="H69" s="120"/>
     </row>
-    <row r="70" spans="1:8" ht="13.15">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A70" s="144">
         <f t="shared" si="3"/>
         <v>25</v>
@@ -17876,7 +17888,7 @@
         <v>5.6971768140748962</v>
       </c>
     </row>
-    <row r="71" spans="1:8" ht="13.15">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A71" s="144">
         <f t="shared" si="3"/>
         <v>30</v>
@@ -17902,7 +17914,7 @@
         <v>5.9741052361049229</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="13.15">
+    <row r="73" spans="1:8" ht="14" x14ac:dyDescent="0.2">
       <c r="B73" s="171" t="s">
         <v>113</v>
       </c>
@@ -17919,7 +17931,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="74" spans="1:8">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B74" s="127" t="str">
         <f>Scenarios!B54</f>
         <v>Snowball Scenario</v>
@@ -17941,7 +17953,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="75" spans="1:8">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B75" s="127" t="str">
         <f>Scenarios!B36</f>
         <v>Optimistic</v>
@@ -17964,7 +17976,7 @@
       </c>
       <c r="H75" s="120"/>
     </row>
-    <row r="76" spans="1:8">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B76" s="127" t="str">
         <f>Scenarios!B24</f>
         <v>Base</v>
@@ -17987,7 +17999,7 @@
       </c>
       <c r="H76" s="120"/>
     </row>
-    <row r="77" spans="1:8">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B77" s="127" t="str">
         <f>Scenarios!B30</f>
         <v>Pessimistic</v>
@@ -18010,7 +18022,7 @@
       </c>
       <c r="H77" s="120"/>
     </row>
-    <row r="78" spans="1:8">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B78" s="127" t="str">
         <f>Scenarios!B48</f>
         <v>Devil's advocate</v>
@@ -18032,14 +18044,14 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="79" spans="1:8">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B79" s="155"/>
       <c r="C79" s="155"/>
       <c r="D79" s="155"/>
       <c r="E79" s="155"/>
       <c r="F79" s="156"/>
     </row>
-    <row r="80" spans="1:8">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B80" s="155" t="s">
         <v>302</v>
       </c>
@@ -18047,26 +18059,26 @@
         <v>102</v>
       </c>
     </row>
-    <row r="81" spans="3:3">
+    <row r="81" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C81" s="155" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="82" spans="3:3">
+    <row r="82" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C82" s="155" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="92" spans="3:3">
+    <row r="92" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C92" s="115"/>
     </row>
-    <row r="93" spans="3:3">
+    <row r="93" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C93" s="115"/>
     </row>
-    <row r="94" spans="3:3">
+    <row r="94" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C94" s="115"/>
     </row>
-    <row r="101" spans="3:17">
+    <row r="101" spans="3:17" x14ac:dyDescent="0.15">
       <c r="C101" s="338"/>
       <c r="G101" s="338"/>
       <c r="H101" s="338"/>
@@ -18080,7 +18092,7 @@
       <c r="P101" s="338"/>
       <c r="Q101" s="338"/>
     </row>
-    <row r="102" spans="3:17">
+    <row r="102" spans="3:17" x14ac:dyDescent="0.15">
       <c r="C102" s="338"/>
       <c r="G102" s="338"/>
       <c r="H102" s="338"/>
@@ -18094,7 +18106,7 @@
       <c r="P102" s="338"/>
       <c r="Q102" s="338"/>
     </row>
-    <row r="103" spans="3:17">
+    <row r="103" spans="3:17" x14ac:dyDescent="0.15">
       <c r="C103" s="338"/>
       <c r="G103" s="338"/>
       <c r="H103" s="338"/>
@@ -18108,7 +18120,7 @@
       <c r="P103" s="338"/>
       <c r="Q103" s="338"/>
     </row>
-    <row r="104" spans="3:17">
+    <row r="104" spans="3:17" x14ac:dyDescent="0.15">
       <c r="C104" s="338"/>
       <c r="G104" s="338"/>
       <c r="H104" s="338"/>
@@ -18122,7 +18134,7 @@
       <c r="P104" s="338"/>
       <c r="Q104" s="338"/>
     </row>
-    <row r="105" spans="3:17">
+    <row r="105" spans="3:17" x14ac:dyDescent="0.15">
       <c r="C105" s="338"/>
       <c r="G105" s="338"/>
       <c r="H105" s="338"/>
@@ -18167,16 +18179,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:H89"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="6.1328125" customWidth="1"/>
-    <col min="2" max="2" width="24.73046875" customWidth="1"/>
-    <col min="3" max="6" width="20.73046875" customWidth="1"/>
-    <col min="7" max="7" width="5.73046875" customWidth="1"/>
-    <col min="8" max="8" width="56.86328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.1640625" customWidth="1"/>
+    <col min="2" max="2" width="24.6640625" customWidth="1"/>
+    <col min="3" max="6" width="20.6640625" customWidth="1"/>
+    <col min="7" max="7" width="5.6640625" customWidth="1"/>
+    <col min="8" max="8" width="56.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="13.9">
+    <row r="2" spans="2:8" ht="16" x14ac:dyDescent="0.25">
       <c r="B2" s="36" t="s">
         <v>419</v>
       </c>
@@ -18188,7 +18200,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="3" spans="2:8" ht="13.15">
+    <row r="3" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B3" s="109" t="s">
         <v>418</v>
       </c>
@@ -18201,7 +18213,7 @@
       </c>
       <c r="H3" s="120"/>
     </row>
-    <row r="4" spans="2:8">
+    <row r="4" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B4" s="100" t="s">
         <v>416</v>
       </c>
@@ -18222,7 +18234,7 @@
       </c>
       <c r="H4" s="120"/>
     </row>
-    <row r="5" spans="2:8">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B5" s="205" t="s">
         <v>119</v>
       </c>
@@ -18233,7 +18245,7 @@
       <c r="E5" s="148"/>
       <c r="H5" s="120"/>
     </row>
-    <row r="6" spans="2:8" ht="13.35" customHeight="1">
+    <row r="6" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B6" s="149" t="s">
         <v>417</v>
       </c>
@@ -18249,7 +18261,7 @@
       <c r="F6" s="378"/>
       <c r="H6" s="120"/>
     </row>
-    <row r="7" spans="2:8" ht="13.15">
+    <row r="7" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B7" s="149" t="s">
         <v>420</v>
       </c>
@@ -18263,10 +18275,10 @@
       </c>
       <c r="H7" s="120"/>
     </row>
-    <row r="8" spans="2:8">
+    <row r="8" spans="2:8" x14ac:dyDescent="0.15">
       <c r="H8" s="120"/>
     </row>
-    <row r="9" spans="2:8" ht="13.9">
+    <row r="9" spans="2:8" ht="16" x14ac:dyDescent="0.25">
       <c r="B9" s="36" t="s">
         <v>225</v>
       </c>
@@ -18276,13 +18288,13 @@
       <c r="F9" s="37"/>
       <c r="H9" s="120"/>
     </row>
-    <row r="10" spans="2:8" ht="13.15">
+    <row r="10" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B10" s="119" t="s">
         <v>131</v>
       </c>
       <c r="H10" s="120"/>
     </row>
-    <row r="11" spans="2:8" ht="13.35" customHeight="1">
+    <row r="11" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B11" s="152" t="s">
         <v>129</v>
       </c>
@@ -18292,7 +18304,7 @@
       </c>
       <c r="H11" s="120"/>
     </row>
-    <row r="12" spans="2:8" ht="13.35" customHeight="1">
+    <row r="12" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B12" s="118" t="s">
         <v>130</v>
       </c>
@@ -18302,7 +18314,7 @@
       </c>
       <c r="H12" s="120"/>
     </row>
-    <row r="13" spans="2:8" ht="13.35" customHeight="1">
+    <row r="13" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B13" s="153" t="s">
         <v>103</v>
       </c>
@@ -18316,10 +18328,10 @@
       </c>
       <c r="H13" s="120"/>
     </row>
-    <row r="14" spans="2:8">
+    <row r="14" spans="2:8" x14ac:dyDescent="0.15">
       <c r="H14" s="120"/>
     </row>
-    <row r="15" spans="2:8" ht="13.15">
+    <row r="15" spans="2:8" ht="14" x14ac:dyDescent="0.2">
       <c r="B15" s="128" t="s">
         <v>104</v>
       </c>
@@ -18337,7 +18349,7 @@
       </c>
       <c r="H15" s="120"/>
     </row>
-    <row r="16" spans="2:8">
+    <row r="16" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B16" s="122">
         <v>1</v>
       </c>
@@ -18359,7 +18371,7 @@
       </c>
       <c r="H16" s="120"/>
     </row>
-    <row r="17" spans="2:8">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B17" s="122">
         <v>2</v>
       </c>
@@ -18381,7 +18393,7 @@
       </c>
       <c r="H17" s="120"/>
     </row>
-    <row r="18" spans="2:8">
+    <row r="18" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B18" s="122">
         <v>3</v>
       </c>
@@ -18403,7 +18415,7 @@
       </c>
       <c r="H18" s="120"/>
     </row>
-    <row r="19" spans="2:8">
+    <row r="19" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B19" s="122">
         <v>4</v>
       </c>
@@ -18425,7 +18437,7 @@
       </c>
       <c r="H19" s="120"/>
     </row>
-    <row r="20" spans="2:8">
+    <row r="20" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B20" s="122">
         <v>5</v>
       </c>
@@ -18447,7 +18459,7 @@
       </c>
       <c r="H20" s="120"/>
     </row>
-    <row r="21" spans="2:8">
+    <row r="21" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B21" s="122">
         <v>6</v>
       </c>
@@ -18469,7 +18481,7 @@
       </c>
       <c r="H21" s="120"/>
     </row>
-    <row r="22" spans="2:8">
+    <row r="22" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B22" s="122">
         <v>7</v>
       </c>
@@ -18491,7 +18503,7 @@
       </c>
       <c r="H22" s="120"/>
     </row>
-    <row r="23" spans="2:8">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B23" s="122">
         <v>8</v>
       </c>
@@ -18513,7 +18525,7 @@
       </c>
       <c r="H23" s="120"/>
     </row>
-    <row r="24" spans="2:8">
+    <row r="24" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B24" s="122">
         <v>9</v>
       </c>
@@ -18535,7 +18547,7 @@
       </c>
       <c r="H24" s="120"/>
     </row>
-    <row r="25" spans="2:8">
+    <row r="25" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B25" s="122">
         <v>10</v>
       </c>
@@ -18557,7 +18569,7 @@
       </c>
       <c r="H25" s="120"/>
     </row>
-    <row r="26" spans="2:8">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B26" s="122">
         <v>11</v>
       </c>
@@ -18579,7 +18591,7 @@
       </c>
       <c r="H26" s="120"/>
     </row>
-    <row r="27" spans="2:8">
+    <row r="27" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B27" s="122">
         <v>12</v>
       </c>
@@ -18601,7 +18613,7 @@
       </c>
       <c r="H27" s="120"/>
     </row>
-    <row r="28" spans="2:8">
+    <row r="28" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B28" s="122">
         <v>13</v>
       </c>
@@ -18623,7 +18635,7 @@
       </c>
       <c r="H28" s="120"/>
     </row>
-    <row r="29" spans="2:8">
+    <row r="29" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B29" s="122">
         <v>14</v>
       </c>
@@ -18645,7 +18657,7 @@
       </c>
       <c r="H29" s="120"/>
     </row>
-    <row r="30" spans="2:8">
+    <row r="30" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B30" s="122">
         <v>15</v>
       </c>
@@ -18667,7 +18679,7 @@
       </c>
       <c r="H30" s="120"/>
     </row>
-    <row r="31" spans="2:8">
+    <row r="31" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B31" s="122">
         <v>16</v>
       </c>
@@ -18689,7 +18701,7 @@
       </c>
       <c r="H31" s="120"/>
     </row>
-    <row r="32" spans="2:8">
+    <row r="32" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B32" s="122">
         <v>17</v>
       </c>
@@ -18711,7 +18723,7 @@
       </c>
       <c r="H32" s="120"/>
     </row>
-    <row r="33" spans="2:8">
+    <row r="33" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B33" s="122">
         <v>18</v>
       </c>
@@ -18733,7 +18745,7 @@
       </c>
       <c r="H33" s="120"/>
     </row>
-    <row r="34" spans="2:8">
+    <row r="34" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B34" s="122">
         <v>19</v>
       </c>
@@ -18755,7 +18767,7 @@
       </c>
       <c r="H34" s="120"/>
     </row>
-    <row r="35" spans="2:8">
+    <row r="35" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B35" s="122">
         <v>20</v>
       </c>
@@ -18777,7 +18789,7 @@
       </c>
       <c r="H35" s="120"/>
     </row>
-    <row r="36" spans="2:8">
+    <row r="36" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B36" s="122">
         <v>21</v>
       </c>
@@ -18799,7 +18811,7 @@
       </c>
       <c r="H36" s="120"/>
     </row>
-    <row r="37" spans="2:8">
+    <row r="37" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B37" s="122">
         <v>22</v>
       </c>
@@ -18821,7 +18833,7 @@
       </c>
       <c r="H37" s="120"/>
     </row>
-    <row r="38" spans="2:8">
+    <row r="38" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B38" s="122">
         <v>23</v>
       </c>
@@ -18843,7 +18855,7 @@
       </c>
       <c r="H38" s="120"/>
     </row>
-    <row r="39" spans="2:8">
+    <row r="39" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B39" s="122">
         <v>24</v>
       </c>
@@ -18865,7 +18877,7 @@
       </c>
       <c r="H39" s="120"/>
     </row>
-    <row r="40" spans="2:8">
+    <row r="40" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B40"